--- a/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
+++ b/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3B5418-76C7-40E1-B9A8-1661C1EFDB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC89E0E-4170-4F2C-B00E-ADC5B38EEB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="2700" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="3045" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="28" r:id="rId1"/>
@@ -7673,10 +7673,6 @@
     <t>Jakarta Transactions</t>
   </si>
   <si>
-    <t>JBatch / JSR352</t>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
     <t>Jakarta Batch</t>
   </si>
   <si>
@@ -7783,6 +7779,10 @@
       <t>サイヨウ</t>
     </rPh>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>jBatch / JSR352</t>
+    <phoneticPr fontId="11"/>
   </si>
 </sst>
 </file>
@@ -8355,7 +8355,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="371">
+  <cellXfs count="372">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8828,89 +8828,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="31" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -9026,14 +8948,86 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -9044,6 +9038,15 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9052,6 +9055,33 @@
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9134,32 +9164,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9209,15 +9221,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -9230,12 +9233,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -9243,18 +9240,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -9275,59 +9260,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9335,41 +9299,56 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9386,45 +9365,67 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="パーセント 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -27486,12 +27487,12 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="172">
+      <c r="I25" s="173">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
         <v>43336</v>
       </c>
-      <c r="J25" s="172"/>
-      <c r="K25" s="172"/>
+      <c r="J25" s="173"/>
+      <c r="K25" s="173"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="3"/>
@@ -28084,55 +28085,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="209"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="216" t="s">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="225" t="s">
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="199" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="226"/>
-      <c r="U1" s="226"/>
-      <c r="V1" s="226"/>
-      <c r="W1" s="226"/>
-      <c r="X1" s="226"/>
-      <c r="Y1" s="226"/>
-      <c r="Z1" s="227"/>
-      <c r="AA1" s="206" t="s">
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="201"/>
+      <c r="AA1" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="208"/>
-      <c r="AC1" s="234" t="str">
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="208" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="235"/>
-      <c r="AE1" s="235"/>
-      <c r="AF1" s="236"/>
-      <c r="AG1" s="200">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="174">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="201"/>
-      <c r="AI1" s="202"/>
+      <c r="AH1" s="175"/>
+      <c r="AI1" s="176"/>
       <c r="AJ1" s="7"/>
       <c r="AK1" s="7"/>
       <c r="AL1" s="7"/>
@@ -28140,51 +28141,51 @@
       <c r="AN1" s="8"/>
     </row>
     <row r="2" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="206" t="s">
+      <c r="A2" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="219"/>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="221"/>
-      <c r="S2" s="228"/>
-      <c r="T2" s="229"/>
-      <c r="U2" s="229"/>
-      <c r="V2" s="229"/>
-      <c r="W2" s="229"/>
-      <c r="X2" s="229"/>
-      <c r="Y2" s="229"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="206" t="s">
+      <c r="B2" s="181"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="184"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="185"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="203"/>
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="180" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="208"/>
-      <c r="AC2" s="212" t="str">
+      <c r="AB2" s="182"/>
+      <c r="AC2" s="186" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="213"/>
-      <c r="AE2" s="213"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="200" t="str">
+      <c r="AD2" s="187"/>
+      <c r="AE2" s="187"/>
+      <c r="AF2" s="188"/>
+      <c r="AG2" s="174" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="201"/>
-      <c r="AI2" s="202"/>
+      <c r="AH2" s="175"/>
+      <c r="AI2" s="176"/>
       <c r="AJ2" s="7"/>
       <c r="AK2" s="7"/>
       <c r="AL2" s="7"/>
@@ -28192,43 +28193,43 @@
       <c r="AN2" s="7"/>
     </row>
     <row r="3" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="206" t="s">
+      <c r="A3" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="M3" s="210"/>
-      <c r="N3" s="211"/>
-      <c r="O3" s="222"/>
-      <c r="P3" s="223"/>
-      <c r="Q3" s="223"/>
-      <c r="R3" s="224"/>
-      <c r="S3" s="231"/>
-      <c r="T3" s="232"/>
-      <c r="U3" s="232"/>
-      <c r="V3" s="232"/>
-      <c r="W3" s="232"/>
-      <c r="X3" s="232"/>
-      <c r="Y3" s="232"/>
-      <c r="Z3" s="233"/>
-      <c r="AA3" s="206"/>
-      <c r="AB3" s="208"/>
-      <c r="AC3" s="234"/>
-      <c r="AD3" s="235"/>
-      <c r="AE3" s="235"/>
-      <c r="AF3" s="236"/>
-      <c r="AG3" s="200"/>
-      <c r="AH3" s="201"/>
-      <c r="AI3" s="202"/>
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+      <c r="M3" s="184"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="197"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="198"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="206"/>
+      <c r="U3" s="206"/>
+      <c r="V3" s="206"/>
+      <c r="W3" s="206"/>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="207"/>
+      <c r="AA3" s="180"/>
+      <c r="AB3" s="182"/>
+      <c r="AC3" s="208"/>
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="174"/>
+      <c r="AH3" s="175"/>
+      <c r="AI3" s="176"/>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
       <c r="AL3" s="7"/>
@@ -28265,1034 +28266,1190 @@
       <c r="A7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="203" t="s">
+      <c r="B7" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="204"/>
-      <c r="D7" s="203" t="s">
+      <c r="C7" s="178"/>
+      <c r="D7" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="205"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="203" t="s">
+      <c r="E7" s="179"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="177" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="205"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="203" t="s">
+      <c r="H7" s="179"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
-      <c r="N7" s="205"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="204"/>
-      <c r="Q7" s="203" t="s">
+      <c r="K7" s="179"/>
+      <c r="L7" s="179"/>
+      <c r="M7" s="179"/>
+      <c r="N7" s="179"/>
+      <c r="O7" s="179"/>
+      <c r="P7" s="178"/>
+      <c r="Q7" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="R7" s="205"/>
-      <c r="S7" s="205"/>
-      <c r="T7" s="205"/>
-      <c r="U7" s="205"/>
-      <c r="V7" s="205"/>
-      <c r="W7" s="205"/>
-      <c r="X7" s="205"/>
-      <c r="Y7" s="205"/>
-      <c r="Z7" s="205"/>
-      <c r="AA7" s="205"/>
-      <c r="AB7" s="205"/>
-      <c r="AC7" s="205"/>
-      <c r="AD7" s="205"/>
-      <c r="AE7" s="204"/>
-      <c r="AF7" s="203" t="s">
+      <c r="R7" s="179"/>
+      <c r="S7" s="179"/>
+      <c r="T7" s="179"/>
+      <c r="U7" s="179"/>
+      <c r="V7" s="179"/>
+      <c r="W7" s="179"/>
+      <c r="X7" s="179"/>
+      <c r="Y7" s="179"/>
+      <c r="Z7" s="179"/>
+      <c r="AA7" s="179"/>
+      <c r="AB7" s="179"/>
+      <c r="AC7" s="179"/>
+      <c r="AD7" s="179"/>
+      <c r="AE7" s="178"/>
+      <c r="AF7" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="205"/>
-      <c r="AH7" s="205"/>
-      <c r="AI7" s="204"/>
+      <c r="AG7" s="179"/>
+      <c r="AH7" s="179"/>
+      <c r="AI7" s="178"/>
     </row>
     <row r="8" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="90">
         <v>1</v>
       </c>
-      <c r="B8" s="186" t="s">
+      <c r="B8" s="224" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="187"/>
-      <c r="D8" s="188">
+      <c r="C8" s="225"/>
+      <c r="D8" s="226">
         <v>43336</v>
       </c>
-      <c r="E8" s="189"/>
-      <c r="F8" s="190"/>
-      <c r="G8" s="191" t="s">
+      <c r="E8" s="227"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="229" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="192"/>
-      <c r="I8" s="193"/>
-      <c r="J8" s="194" t="s">
+      <c r="H8" s="230"/>
+      <c r="I8" s="231"/>
+      <c r="J8" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="195"/>
-      <c r="L8" s="195"/>
-      <c r="M8" s="195"/>
-      <c r="N8" s="195"/>
-      <c r="O8" s="195"/>
-      <c r="P8" s="196"/>
-      <c r="Q8" s="197" t="s">
+      <c r="K8" s="233"/>
+      <c r="L8" s="233"/>
+      <c r="M8" s="233"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="233"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="235" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="198"/>
-      <c r="S8" s="198"/>
-      <c r="T8" s="198"/>
-      <c r="U8" s="198"/>
-      <c r="V8" s="198"/>
-      <c r="W8" s="198"/>
-      <c r="X8" s="198"/>
-      <c r="Y8" s="198"/>
-      <c r="Z8" s="198"/>
-      <c r="AA8" s="198"/>
-      <c r="AB8" s="198"/>
-      <c r="AC8" s="198"/>
-      <c r="AD8" s="198"/>
-      <c r="AE8" s="199"/>
-      <c r="AF8" s="194" t="s">
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="236"/>
+      <c r="U8" s="236"/>
+      <c r="V8" s="236"/>
+      <c r="W8" s="236"/>
+      <c r="X8" s="236"/>
+      <c r="Y8" s="236"/>
+      <c r="Z8" s="236"/>
+      <c r="AA8" s="236"/>
+      <c r="AB8" s="236"/>
+      <c r="AC8" s="236"/>
+      <c r="AD8" s="236"/>
+      <c r="AE8" s="237"/>
+      <c r="AF8" s="232" t="s">
         <v>23</v>
       </c>
-      <c r="AG8" s="195"/>
-      <c r="AH8" s="195"/>
-      <c r="AI8" s="196"/>
+      <c r="AG8" s="233"/>
+      <c r="AH8" s="233"/>
+      <c r="AI8" s="234"/>
     </row>
     <row r="9" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="89"/>
-      <c r="B9" s="173"/>
-      <c r="C9" s="174"/>
-      <c r="D9" s="175"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="177"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="178"/>
-      <c r="I9" s="174"/>
-      <c r="J9" s="179"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="180"/>
-      <c r="M9" s="180"/>
-      <c r="N9" s="180"/>
-      <c r="O9" s="180"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="182"/>
-      <c r="R9" s="183"/>
-      <c r="S9" s="183"/>
-      <c r="T9" s="183"/>
-      <c r="U9" s="183"/>
-      <c r="V9" s="183"/>
-      <c r="W9" s="183"/>
-      <c r="X9" s="183"/>
-      <c r="Y9" s="183"/>
-      <c r="Z9" s="183"/>
-      <c r="AA9" s="183"/>
-      <c r="AB9" s="183"/>
-      <c r="AC9" s="183"/>
-      <c r="AD9" s="183"/>
-      <c r="AE9" s="184"/>
-      <c r="AF9" s="179"/>
-      <c r="AG9" s="180"/>
-      <c r="AH9" s="180"/>
-      <c r="AI9" s="181"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="213"/>
+      <c r="D9" s="214"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="214"/>
+      <c r="H9" s="217"/>
+      <c r="I9" s="213"/>
+      <c r="J9" s="218"/>
+      <c r="K9" s="219"/>
+      <c r="L9" s="219"/>
+      <c r="M9" s="219"/>
+      <c r="N9" s="219"/>
+      <c r="O9" s="219"/>
+      <c r="P9" s="220"/>
+      <c r="Q9" s="221"/>
+      <c r="R9" s="222"/>
+      <c r="S9" s="222"/>
+      <c r="T9" s="222"/>
+      <c r="U9" s="222"/>
+      <c r="V9" s="222"/>
+      <c r="W9" s="222"/>
+      <c r="X9" s="222"/>
+      <c r="Y9" s="222"/>
+      <c r="Z9" s="222"/>
+      <c r="AA9" s="222"/>
+      <c r="AB9" s="222"/>
+      <c r="AC9" s="222"/>
+      <c r="AD9" s="222"/>
+      <c r="AE9" s="223"/>
+      <c r="AF9" s="218"/>
+      <c r="AG9" s="219"/>
+      <c r="AH9" s="219"/>
+      <c r="AI9" s="220"/>
     </row>
     <row r="10" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="89"/>
-      <c r="B10" s="173"/>
-      <c r="C10" s="174"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="177"/>
-      <c r="G10" s="173"/>
-      <c r="H10" s="178"/>
-      <c r="I10" s="174"/>
-      <c r="J10" s="179"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="180"/>
-      <c r="M10" s="180"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="180"/>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="182"/>
-      <c r="R10" s="183"/>
-      <c r="S10" s="183"/>
-      <c r="T10" s="183"/>
-      <c r="U10" s="183"/>
-      <c r="V10" s="183"/>
-      <c r="W10" s="183"/>
-      <c r="X10" s="183"/>
-      <c r="Y10" s="183"/>
-      <c r="Z10" s="183"/>
-      <c r="AA10" s="183"/>
-      <c r="AB10" s="183"/>
-      <c r="AC10" s="183"/>
-      <c r="AD10" s="183"/>
-      <c r="AE10" s="184"/>
-      <c r="AF10" s="179"/>
-      <c r="AG10" s="180"/>
-      <c r="AH10" s="180"/>
-      <c r="AI10" s="181"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="214"/>
+      <c r="E10" s="215"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="212"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="213"/>
+      <c r="J10" s="218"/>
+      <c r="K10" s="219"/>
+      <c r="L10" s="219"/>
+      <c r="M10" s="219"/>
+      <c r="N10" s="219"/>
+      <c r="O10" s="219"/>
+      <c r="P10" s="220"/>
+      <c r="Q10" s="221"/>
+      <c r="R10" s="222"/>
+      <c r="S10" s="222"/>
+      <c r="T10" s="222"/>
+      <c r="U10" s="222"/>
+      <c r="V10" s="222"/>
+      <c r="W10" s="222"/>
+      <c r="X10" s="222"/>
+      <c r="Y10" s="222"/>
+      <c r="Z10" s="222"/>
+      <c r="AA10" s="222"/>
+      <c r="AB10" s="222"/>
+      <c r="AC10" s="222"/>
+      <c r="AD10" s="222"/>
+      <c r="AE10" s="223"/>
+      <c r="AF10" s="218"/>
+      <c r="AG10" s="219"/>
+      <c r="AH10" s="219"/>
+      <c r="AI10" s="220"/>
     </row>
     <row r="11" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="89"/>
-      <c r="B11" s="173"/>
-      <c r="C11" s="174"/>
-      <c r="D11" s="175"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="177"/>
-      <c r="G11" s="173"/>
-      <c r="H11" s="178"/>
-      <c r="I11" s="174"/>
-      <c r="J11" s="179"/>
-      <c r="K11" s="180"/>
-      <c r="L11" s="180"/>
-      <c r="M11" s="180"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="180"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="182"/>
-      <c r="R11" s="183"/>
-      <c r="S11" s="183"/>
-      <c r="T11" s="183"/>
-      <c r="U11" s="183"/>
-      <c r="V11" s="183"/>
-      <c r="W11" s="183"/>
-      <c r="X11" s="183"/>
-      <c r="Y11" s="183"/>
-      <c r="Z11" s="183"/>
-      <c r="AA11" s="183"/>
-      <c r="AB11" s="183"/>
-      <c r="AC11" s="183"/>
-      <c r="AD11" s="183"/>
-      <c r="AE11" s="184"/>
-      <c r="AF11" s="179"/>
-      <c r="AG11" s="180"/>
-      <c r="AH11" s="180"/>
-      <c r="AI11" s="181"/>
+      <c r="B11" s="212"/>
+      <c r="C11" s="213"/>
+      <c r="D11" s="214"/>
+      <c r="E11" s="215"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="212"/>
+      <c r="H11" s="217"/>
+      <c r="I11" s="213"/>
+      <c r="J11" s="218"/>
+      <c r="K11" s="219"/>
+      <c r="L11" s="219"/>
+      <c r="M11" s="219"/>
+      <c r="N11" s="219"/>
+      <c r="O11" s="219"/>
+      <c r="P11" s="220"/>
+      <c r="Q11" s="221"/>
+      <c r="R11" s="222"/>
+      <c r="S11" s="222"/>
+      <c r="T11" s="222"/>
+      <c r="U11" s="222"/>
+      <c r="V11" s="222"/>
+      <c r="W11" s="222"/>
+      <c r="X11" s="222"/>
+      <c r="Y11" s="222"/>
+      <c r="Z11" s="222"/>
+      <c r="AA11" s="222"/>
+      <c r="AB11" s="222"/>
+      <c r="AC11" s="222"/>
+      <c r="AD11" s="222"/>
+      <c r="AE11" s="223"/>
+      <c r="AF11" s="218"/>
+      <c r="AG11" s="219"/>
+      <c r="AH11" s="219"/>
+      <c r="AI11" s="220"/>
     </row>
     <row r="12" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="89"/>
-      <c r="B12" s="173"/>
-      <c r="C12" s="174"/>
-      <c r="D12" s="175"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="173"/>
-      <c r="H12" s="178"/>
-      <c r="I12" s="174"/>
-      <c r="J12" s="179"/>
-      <c r="K12" s="180"/>
-      <c r="L12" s="180"/>
-      <c r="M12" s="180"/>
-      <c r="N12" s="180"/>
-      <c r="O12" s="180"/>
-      <c r="P12" s="181"/>
-      <c r="Q12" s="182"/>
-      <c r="R12" s="183"/>
-      <c r="S12" s="183"/>
-      <c r="T12" s="183"/>
-      <c r="U12" s="183"/>
-      <c r="V12" s="183"/>
-      <c r="W12" s="183"/>
-      <c r="X12" s="183"/>
-      <c r="Y12" s="183"/>
-      <c r="Z12" s="183"/>
-      <c r="AA12" s="183"/>
-      <c r="AB12" s="183"/>
-      <c r="AC12" s="183"/>
-      <c r="AD12" s="183"/>
-      <c r="AE12" s="184"/>
-      <c r="AF12" s="179"/>
-      <c r="AG12" s="180"/>
-      <c r="AH12" s="180"/>
-      <c r="AI12" s="181"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="213"/>
+      <c r="D12" s="214"/>
+      <c r="E12" s="215"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="217"/>
+      <c r="I12" s="213"/>
+      <c r="J12" s="218"/>
+      <c r="K12" s="219"/>
+      <c r="L12" s="219"/>
+      <c r="M12" s="219"/>
+      <c r="N12" s="219"/>
+      <c r="O12" s="219"/>
+      <c r="P12" s="220"/>
+      <c r="Q12" s="221"/>
+      <c r="R12" s="222"/>
+      <c r="S12" s="222"/>
+      <c r="T12" s="222"/>
+      <c r="U12" s="222"/>
+      <c r="V12" s="222"/>
+      <c r="W12" s="222"/>
+      <c r="X12" s="222"/>
+      <c r="Y12" s="222"/>
+      <c r="Z12" s="222"/>
+      <c r="AA12" s="222"/>
+      <c r="AB12" s="222"/>
+      <c r="AC12" s="222"/>
+      <c r="AD12" s="222"/>
+      <c r="AE12" s="223"/>
+      <c r="AF12" s="218"/>
+      <c r="AG12" s="219"/>
+      <c r="AH12" s="219"/>
+      <c r="AI12" s="220"/>
     </row>
     <row r="13" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="89"/>
-      <c r="B13" s="173"/>
-      <c r="C13" s="174"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="178"/>
-      <c r="I13" s="174"/>
-      <c r="J13" s="179"/>
-      <c r="K13" s="180"/>
-      <c r="L13" s="180"/>
-      <c r="M13" s="180"/>
-      <c r="N13" s="180"/>
-      <c r="O13" s="180"/>
-      <c r="P13" s="181"/>
-      <c r="Q13" s="182"/>
-      <c r="R13" s="183"/>
-      <c r="S13" s="183"/>
-      <c r="T13" s="183"/>
-      <c r="U13" s="183"/>
-      <c r="V13" s="183"/>
-      <c r="W13" s="183"/>
-      <c r="X13" s="183"/>
-      <c r="Y13" s="183"/>
-      <c r="Z13" s="183"/>
-      <c r="AA13" s="183"/>
-      <c r="AB13" s="183"/>
-      <c r="AC13" s="183"/>
-      <c r="AD13" s="183"/>
-      <c r="AE13" s="184"/>
-      <c r="AF13" s="179"/>
-      <c r="AG13" s="180"/>
-      <c r="AH13" s="180"/>
-      <c r="AI13" s="181"/>
+      <c r="B13" s="212"/>
+      <c r="C13" s="213"/>
+      <c r="D13" s="214"/>
+      <c r="E13" s="215"/>
+      <c r="F13" s="216"/>
+      <c r="G13" s="212"/>
+      <c r="H13" s="217"/>
+      <c r="I13" s="213"/>
+      <c r="J13" s="218"/>
+      <c r="K13" s="219"/>
+      <c r="L13" s="219"/>
+      <c r="M13" s="219"/>
+      <c r="N13" s="219"/>
+      <c r="O13" s="219"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="221"/>
+      <c r="R13" s="222"/>
+      <c r="S13" s="222"/>
+      <c r="T13" s="222"/>
+      <c r="U13" s="222"/>
+      <c r="V13" s="222"/>
+      <c r="W13" s="222"/>
+      <c r="X13" s="222"/>
+      <c r="Y13" s="222"/>
+      <c r="Z13" s="222"/>
+      <c r="AA13" s="222"/>
+      <c r="AB13" s="222"/>
+      <c r="AC13" s="222"/>
+      <c r="AD13" s="222"/>
+      <c r="AE13" s="223"/>
+      <c r="AF13" s="218"/>
+      <c r="AG13" s="219"/>
+      <c r="AH13" s="219"/>
+      <c r="AI13" s="220"/>
     </row>
     <row r="14" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="89"/>
-      <c r="B14" s="173"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="175"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="177"/>
-      <c r="G14" s="173"/>
-      <c r="H14" s="178"/>
-      <c r="I14" s="174"/>
-      <c r="J14" s="179"/>
-      <c r="K14" s="180"/>
-      <c r="L14" s="180"/>
-      <c r="M14" s="180"/>
-      <c r="N14" s="180"/>
-      <c r="O14" s="180"/>
-      <c r="P14" s="181"/>
-      <c r="Q14" s="182"/>
-      <c r="R14" s="183"/>
-      <c r="S14" s="183"/>
-      <c r="T14" s="183"/>
-      <c r="U14" s="183"/>
-      <c r="V14" s="183"/>
-      <c r="W14" s="183"/>
-      <c r="X14" s="183"/>
-      <c r="Y14" s="183"/>
-      <c r="Z14" s="183"/>
-      <c r="AA14" s="183"/>
-      <c r="AB14" s="183"/>
-      <c r="AC14" s="183"/>
-      <c r="AD14" s="183"/>
-      <c r="AE14" s="184"/>
-      <c r="AF14" s="179"/>
-      <c r="AG14" s="180"/>
-      <c r="AH14" s="180"/>
-      <c r="AI14" s="181"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="213"/>
+      <c r="D14" s="214"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="216"/>
+      <c r="G14" s="212"/>
+      <c r="H14" s="217"/>
+      <c r="I14" s="213"/>
+      <c r="J14" s="218"/>
+      <c r="K14" s="219"/>
+      <c r="L14" s="219"/>
+      <c r="M14" s="219"/>
+      <c r="N14" s="219"/>
+      <c r="O14" s="219"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="221"/>
+      <c r="R14" s="222"/>
+      <c r="S14" s="222"/>
+      <c r="T14" s="222"/>
+      <c r="U14" s="222"/>
+      <c r="V14" s="222"/>
+      <c r="W14" s="222"/>
+      <c r="X14" s="222"/>
+      <c r="Y14" s="222"/>
+      <c r="Z14" s="222"/>
+      <c r="AA14" s="222"/>
+      <c r="AB14" s="222"/>
+      <c r="AC14" s="222"/>
+      <c r="AD14" s="222"/>
+      <c r="AE14" s="223"/>
+      <c r="AF14" s="218"/>
+      <c r="AG14" s="219"/>
+      <c r="AH14" s="219"/>
+      <c r="AI14" s="220"/>
     </row>
     <row r="15" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="89"/>
-      <c r="B15" s="173"/>
-      <c r="C15" s="174"/>
-      <c r="D15" s="175"/>
-      <c r="E15" s="176"/>
-      <c r="F15" s="177"/>
-      <c r="G15" s="173"/>
-      <c r="H15" s="178"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="179"/>
-      <c r="K15" s="180"/>
-      <c r="L15" s="180"/>
-      <c r="M15" s="180"/>
-      <c r="N15" s="180"/>
-      <c r="O15" s="180"/>
-      <c r="P15" s="181"/>
-      <c r="Q15" s="182"/>
-      <c r="R15" s="183"/>
-      <c r="S15" s="183"/>
-      <c r="T15" s="183"/>
-      <c r="U15" s="183"/>
-      <c r="V15" s="183"/>
-      <c r="W15" s="183"/>
-      <c r="X15" s="183"/>
-      <c r="Y15" s="183"/>
-      <c r="Z15" s="183"/>
-      <c r="AA15" s="183"/>
-      <c r="AB15" s="183"/>
-      <c r="AC15" s="183"/>
-      <c r="AD15" s="183"/>
-      <c r="AE15" s="184"/>
-      <c r="AF15" s="179"/>
-      <c r="AG15" s="180"/>
-      <c r="AH15" s="180"/>
-      <c r="AI15" s="181"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="213"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="216"/>
+      <c r="G15" s="212"/>
+      <c r="H15" s="217"/>
+      <c r="I15" s="213"/>
+      <c r="J15" s="218"/>
+      <c r="K15" s="219"/>
+      <c r="L15" s="219"/>
+      <c r="M15" s="219"/>
+      <c r="N15" s="219"/>
+      <c r="O15" s="219"/>
+      <c r="P15" s="220"/>
+      <c r="Q15" s="221"/>
+      <c r="R15" s="222"/>
+      <c r="S15" s="222"/>
+      <c r="T15" s="222"/>
+      <c r="U15" s="222"/>
+      <c r="V15" s="222"/>
+      <c r="W15" s="222"/>
+      <c r="X15" s="222"/>
+      <c r="Y15" s="222"/>
+      <c r="Z15" s="222"/>
+      <c r="AA15" s="222"/>
+      <c r="AB15" s="222"/>
+      <c r="AC15" s="222"/>
+      <c r="AD15" s="222"/>
+      <c r="AE15" s="223"/>
+      <c r="AF15" s="218"/>
+      <c r="AG15" s="219"/>
+      <c r="AH15" s="219"/>
+      <c r="AI15" s="220"/>
     </row>
     <row r="16" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="89"/>
-      <c r="B16" s="173"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="175"/>
-      <c r="E16" s="176"/>
-      <c r="F16" s="177"/>
-      <c r="G16" s="173"/>
-      <c r="H16" s="178"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="179"/>
-      <c r="K16" s="180"/>
-      <c r="L16" s="180"/>
-      <c r="M16" s="180"/>
-      <c r="N16" s="180"/>
-      <c r="O16" s="180"/>
-      <c r="P16" s="181"/>
-      <c r="Q16" s="182"/>
-      <c r="R16" s="183"/>
-      <c r="S16" s="183"/>
-      <c r="T16" s="183"/>
-      <c r="U16" s="183"/>
-      <c r="V16" s="183"/>
-      <c r="W16" s="183"/>
-      <c r="X16" s="183"/>
-      <c r="Y16" s="183"/>
-      <c r="Z16" s="183"/>
-      <c r="AA16" s="183"/>
-      <c r="AB16" s="183"/>
-      <c r="AC16" s="183"/>
-      <c r="AD16" s="183"/>
-      <c r="AE16" s="184"/>
-      <c r="AF16" s="179"/>
-      <c r="AG16" s="180"/>
-      <c r="AH16" s="180"/>
-      <c r="AI16" s="181"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="213"/>
+      <c r="D16" s="214"/>
+      <c r="E16" s="215"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="217"/>
+      <c r="I16" s="213"/>
+      <c r="J16" s="218"/>
+      <c r="K16" s="219"/>
+      <c r="L16" s="219"/>
+      <c r="M16" s="219"/>
+      <c r="N16" s="219"/>
+      <c r="O16" s="219"/>
+      <c r="P16" s="220"/>
+      <c r="Q16" s="221"/>
+      <c r="R16" s="222"/>
+      <c r="S16" s="222"/>
+      <c r="T16" s="222"/>
+      <c r="U16" s="222"/>
+      <c r="V16" s="222"/>
+      <c r="W16" s="222"/>
+      <c r="X16" s="222"/>
+      <c r="Y16" s="222"/>
+      <c r="Z16" s="222"/>
+      <c r="AA16" s="222"/>
+      <c r="AB16" s="222"/>
+      <c r="AC16" s="222"/>
+      <c r="AD16" s="222"/>
+      <c r="AE16" s="223"/>
+      <c r="AF16" s="218"/>
+      <c r="AG16" s="219"/>
+      <c r="AH16" s="219"/>
+      <c r="AI16" s="220"/>
     </row>
     <row r="17" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="89"/>
-      <c r="B17" s="173"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="176"/>
-      <c r="F17" s="177"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="178"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="179"/>
-      <c r="K17" s="180"/>
-      <c r="L17" s="180"/>
-      <c r="M17" s="180"/>
-      <c r="N17" s="180"/>
-      <c r="O17" s="180"/>
-      <c r="P17" s="181"/>
-      <c r="Q17" s="182"/>
-      <c r="R17" s="183"/>
-      <c r="S17" s="183"/>
-      <c r="T17" s="183"/>
-      <c r="U17" s="183"/>
-      <c r="V17" s="183"/>
-      <c r="W17" s="183"/>
-      <c r="X17" s="183"/>
-      <c r="Y17" s="183"/>
-      <c r="Z17" s="183"/>
-      <c r="AA17" s="183"/>
-      <c r="AB17" s="183"/>
-      <c r="AC17" s="183"/>
-      <c r="AD17" s="183"/>
-      <c r="AE17" s="184"/>
-      <c r="AF17" s="179"/>
-      <c r="AG17" s="180"/>
-      <c r="AH17" s="180"/>
-      <c r="AI17" s="181"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="213"/>
+      <c r="D17" s="214"/>
+      <c r="E17" s="215"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="217"/>
+      <c r="I17" s="213"/>
+      <c r="J17" s="218"/>
+      <c r="K17" s="219"/>
+      <c r="L17" s="219"/>
+      <c r="M17" s="219"/>
+      <c r="N17" s="219"/>
+      <c r="O17" s="219"/>
+      <c r="P17" s="220"/>
+      <c r="Q17" s="221"/>
+      <c r="R17" s="222"/>
+      <c r="S17" s="222"/>
+      <c r="T17" s="222"/>
+      <c r="U17" s="222"/>
+      <c r="V17" s="222"/>
+      <c r="W17" s="222"/>
+      <c r="X17" s="222"/>
+      <c r="Y17" s="222"/>
+      <c r="Z17" s="222"/>
+      <c r="AA17" s="222"/>
+      <c r="AB17" s="222"/>
+      <c r="AC17" s="222"/>
+      <c r="AD17" s="222"/>
+      <c r="AE17" s="223"/>
+      <c r="AF17" s="218"/>
+      <c r="AG17" s="219"/>
+      <c r="AH17" s="219"/>
+      <c r="AI17" s="220"/>
     </row>
     <row r="18" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="89"/>
-      <c r="B18" s="173"/>
-      <c r="C18" s="174"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="177"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="178"/>
-      <c r="I18" s="174"/>
-      <c r="J18" s="179"/>
-      <c r="K18" s="180"/>
-      <c r="L18" s="180"/>
-      <c r="M18" s="180"/>
-      <c r="N18" s="180"/>
-      <c r="O18" s="180"/>
-      <c r="P18" s="181"/>
-      <c r="Q18" s="182"/>
-      <c r="R18" s="183"/>
-      <c r="S18" s="183"/>
-      <c r="T18" s="183"/>
-      <c r="U18" s="183"/>
-      <c r="V18" s="183"/>
-      <c r="W18" s="183"/>
-      <c r="X18" s="183"/>
-      <c r="Y18" s="183"/>
-      <c r="Z18" s="183"/>
-      <c r="AA18" s="183"/>
-      <c r="AB18" s="183"/>
-      <c r="AC18" s="183"/>
-      <c r="AD18" s="183"/>
-      <c r="AE18" s="184"/>
-      <c r="AF18" s="179"/>
-      <c r="AG18" s="180"/>
-      <c r="AH18" s="180"/>
-      <c r="AI18" s="181"/>
+      <c r="B18" s="212"/>
+      <c r="C18" s="213"/>
+      <c r="D18" s="214"/>
+      <c r="E18" s="215"/>
+      <c r="F18" s="216"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="217"/>
+      <c r="I18" s="213"/>
+      <c r="J18" s="218"/>
+      <c r="K18" s="219"/>
+      <c r="L18" s="219"/>
+      <c r="M18" s="219"/>
+      <c r="N18" s="219"/>
+      <c r="O18" s="219"/>
+      <c r="P18" s="220"/>
+      <c r="Q18" s="221"/>
+      <c r="R18" s="222"/>
+      <c r="S18" s="222"/>
+      <c r="T18" s="222"/>
+      <c r="U18" s="222"/>
+      <c r="V18" s="222"/>
+      <c r="W18" s="222"/>
+      <c r="X18" s="222"/>
+      <c r="Y18" s="222"/>
+      <c r="Z18" s="222"/>
+      <c r="AA18" s="222"/>
+      <c r="AB18" s="222"/>
+      <c r="AC18" s="222"/>
+      <c r="AD18" s="222"/>
+      <c r="AE18" s="223"/>
+      <c r="AF18" s="218"/>
+      <c r="AG18" s="219"/>
+      <c r="AH18" s="219"/>
+      <c r="AI18" s="220"/>
     </row>
     <row r="19" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="89"/>
-      <c r="B19" s="173"/>
-      <c r="C19" s="174"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="177"/>
-      <c r="G19" s="173"/>
-      <c r="H19" s="178"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="179"/>
-      <c r="K19" s="180"/>
-      <c r="L19" s="180"/>
-      <c r="M19" s="180"/>
-      <c r="N19" s="180"/>
-      <c r="O19" s="180"/>
-      <c r="P19" s="181"/>
-      <c r="Q19" s="182"/>
-      <c r="R19" s="183"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="183"/>
-      <c r="U19" s="183"/>
-      <c r="V19" s="183"/>
-      <c r="W19" s="183"/>
-      <c r="X19" s="183"/>
-      <c r="Y19" s="183"/>
-      <c r="Z19" s="183"/>
-      <c r="AA19" s="183"/>
-      <c r="AB19" s="183"/>
-      <c r="AC19" s="183"/>
-      <c r="AD19" s="183"/>
-      <c r="AE19" s="184"/>
-      <c r="AF19" s="179"/>
-      <c r="AG19" s="180"/>
-      <c r="AH19" s="180"/>
-      <c r="AI19" s="181"/>
+      <c r="B19" s="212"/>
+      <c r="C19" s="213"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="212"/>
+      <c r="H19" s="217"/>
+      <c r="I19" s="213"/>
+      <c r="J19" s="218"/>
+      <c r="K19" s="219"/>
+      <c r="L19" s="219"/>
+      <c r="M19" s="219"/>
+      <c r="N19" s="219"/>
+      <c r="O19" s="219"/>
+      <c r="P19" s="220"/>
+      <c r="Q19" s="221"/>
+      <c r="R19" s="222"/>
+      <c r="S19" s="222"/>
+      <c r="T19" s="222"/>
+      <c r="U19" s="222"/>
+      <c r="V19" s="222"/>
+      <c r="W19" s="222"/>
+      <c r="X19" s="222"/>
+      <c r="Y19" s="222"/>
+      <c r="Z19" s="222"/>
+      <c r="AA19" s="222"/>
+      <c r="AB19" s="222"/>
+      <c r="AC19" s="222"/>
+      <c r="AD19" s="222"/>
+      <c r="AE19" s="223"/>
+      <c r="AF19" s="218"/>
+      <c r="AG19" s="219"/>
+      <c r="AH19" s="219"/>
+      <c r="AI19" s="220"/>
     </row>
     <row r="20" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="89"/>
-      <c r="B20" s="173"/>
-      <c r="C20" s="174"/>
-      <c r="D20" s="175"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="177"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="178"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="179"/>
-      <c r="K20" s="180"/>
-      <c r="L20" s="180"/>
-      <c r="M20" s="180"/>
-      <c r="N20" s="180"/>
-      <c r="O20" s="180"/>
-      <c r="P20" s="181"/>
-      <c r="Q20" s="182"/>
-      <c r="R20" s="183"/>
-      <c r="S20" s="183"/>
-      <c r="T20" s="183"/>
-      <c r="U20" s="183"/>
-      <c r="V20" s="183"/>
-      <c r="W20" s="183"/>
-      <c r="X20" s="183"/>
-      <c r="Y20" s="183"/>
-      <c r="Z20" s="183"/>
-      <c r="AA20" s="183"/>
-      <c r="AB20" s="183"/>
-      <c r="AC20" s="183"/>
-      <c r="AD20" s="183"/>
-      <c r="AE20" s="184"/>
-      <c r="AF20" s="179"/>
-      <c r="AG20" s="180"/>
-      <c r="AH20" s="180"/>
-      <c r="AI20" s="181"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="213"/>
+      <c r="D20" s="214"/>
+      <c r="E20" s="215"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="212"/>
+      <c r="H20" s="217"/>
+      <c r="I20" s="213"/>
+      <c r="J20" s="218"/>
+      <c r="K20" s="219"/>
+      <c r="L20" s="219"/>
+      <c r="M20" s="219"/>
+      <c r="N20" s="219"/>
+      <c r="O20" s="219"/>
+      <c r="P20" s="220"/>
+      <c r="Q20" s="221"/>
+      <c r="R20" s="222"/>
+      <c r="S20" s="222"/>
+      <c r="T20" s="222"/>
+      <c r="U20" s="222"/>
+      <c r="V20" s="222"/>
+      <c r="W20" s="222"/>
+      <c r="X20" s="222"/>
+      <c r="Y20" s="222"/>
+      <c r="Z20" s="222"/>
+      <c r="AA20" s="222"/>
+      <c r="AB20" s="222"/>
+      <c r="AC20" s="222"/>
+      <c r="AD20" s="222"/>
+      <c r="AE20" s="223"/>
+      <c r="AF20" s="218"/>
+      <c r="AG20" s="219"/>
+      <c r="AH20" s="219"/>
+      <c r="AI20" s="220"/>
     </row>
     <row r="21" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="89"/>
-      <c r="B21" s="173"/>
-      <c r="C21" s="174"/>
-      <c r="D21" s="175"/>
-      <c r="E21" s="176"/>
-      <c r="F21" s="177"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="178"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="179"/>
-      <c r="K21" s="180"/>
-      <c r="L21" s="180"/>
-      <c r="M21" s="180"/>
-      <c r="N21" s="180"/>
-      <c r="O21" s="180"/>
-      <c r="P21" s="181"/>
-      <c r="Q21" s="182"/>
-      <c r="R21" s="183"/>
-      <c r="S21" s="183"/>
-      <c r="T21" s="183"/>
-      <c r="U21" s="183"/>
-      <c r="V21" s="183"/>
-      <c r="W21" s="183"/>
-      <c r="X21" s="183"/>
-      <c r="Y21" s="183"/>
-      <c r="Z21" s="183"/>
-      <c r="AA21" s="183"/>
-      <c r="AB21" s="183"/>
-      <c r="AC21" s="183"/>
-      <c r="AD21" s="183"/>
-      <c r="AE21" s="184"/>
-      <c r="AF21" s="179"/>
-      <c r="AG21" s="180"/>
-      <c r="AH21" s="180"/>
-      <c r="AI21" s="181"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="213"/>
+      <c r="D21" s="214"/>
+      <c r="E21" s="215"/>
+      <c r="F21" s="216"/>
+      <c r="G21" s="212"/>
+      <c r="H21" s="217"/>
+      <c r="I21" s="213"/>
+      <c r="J21" s="218"/>
+      <c r="K21" s="219"/>
+      <c r="L21" s="219"/>
+      <c r="M21" s="219"/>
+      <c r="N21" s="219"/>
+      <c r="O21" s="219"/>
+      <c r="P21" s="220"/>
+      <c r="Q21" s="221"/>
+      <c r="R21" s="222"/>
+      <c r="S21" s="222"/>
+      <c r="T21" s="222"/>
+      <c r="U21" s="222"/>
+      <c r="V21" s="222"/>
+      <c r="W21" s="222"/>
+      <c r="X21" s="222"/>
+      <c r="Y21" s="222"/>
+      <c r="Z21" s="222"/>
+      <c r="AA21" s="222"/>
+      <c r="AB21" s="222"/>
+      <c r="AC21" s="222"/>
+      <c r="AD21" s="222"/>
+      <c r="AE21" s="223"/>
+      <c r="AF21" s="218"/>
+      <c r="AG21" s="219"/>
+      <c r="AH21" s="219"/>
+      <c r="AI21" s="220"/>
     </row>
     <row r="22" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="89"/>
-      <c r="B22" s="173"/>
-      <c r="C22" s="174"/>
-      <c r="D22" s="175"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="178"/>
-      <c r="I22" s="174"/>
-      <c r="J22" s="179"/>
-      <c r="K22" s="180"/>
-      <c r="L22" s="180"/>
-      <c r="M22" s="180"/>
-      <c r="N22" s="180"/>
-      <c r="O22" s="180"/>
-      <c r="P22" s="181"/>
-      <c r="Q22" s="182"/>
-      <c r="R22" s="183"/>
-      <c r="S22" s="183"/>
-      <c r="T22" s="183"/>
-      <c r="U22" s="183"/>
-      <c r="V22" s="183"/>
-      <c r="W22" s="183"/>
-      <c r="X22" s="183"/>
-      <c r="Y22" s="183"/>
-      <c r="Z22" s="183"/>
-      <c r="AA22" s="183"/>
-      <c r="AB22" s="183"/>
-      <c r="AC22" s="183"/>
-      <c r="AD22" s="183"/>
-      <c r="AE22" s="184"/>
-      <c r="AF22" s="179"/>
-      <c r="AG22" s="180"/>
-      <c r="AH22" s="180"/>
-      <c r="AI22" s="181"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="213"/>
+      <c r="D22" s="214"/>
+      <c r="E22" s="215"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="212"/>
+      <c r="H22" s="217"/>
+      <c r="I22" s="213"/>
+      <c r="J22" s="218"/>
+      <c r="K22" s="219"/>
+      <c r="L22" s="219"/>
+      <c r="M22" s="219"/>
+      <c r="N22" s="219"/>
+      <c r="O22" s="219"/>
+      <c r="P22" s="220"/>
+      <c r="Q22" s="221"/>
+      <c r="R22" s="222"/>
+      <c r="S22" s="222"/>
+      <c r="T22" s="222"/>
+      <c r="U22" s="222"/>
+      <c r="V22" s="222"/>
+      <c r="W22" s="222"/>
+      <c r="X22" s="222"/>
+      <c r="Y22" s="222"/>
+      <c r="Z22" s="222"/>
+      <c r="AA22" s="222"/>
+      <c r="AB22" s="222"/>
+      <c r="AC22" s="222"/>
+      <c r="AD22" s="222"/>
+      <c r="AE22" s="223"/>
+      <c r="AF22" s="218"/>
+      <c r="AG22" s="219"/>
+      <c r="AH22" s="219"/>
+      <c r="AI22" s="220"/>
     </row>
     <row r="23" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="89"/>
-      <c r="B23" s="173"/>
-      <c r="C23" s="174"/>
-      <c r="D23" s="175"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="177"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="178"/>
-      <c r="I23" s="174"/>
-      <c r="J23" s="179"/>
-      <c r="K23" s="180"/>
-      <c r="L23" s="180"/>
-      <c r="M23" s="180"/>
-      <c r="N23" s="180"/>
-      <c r="O23" s="180"/>
-      <c r="P23" s="181"/>
-      <c r="Q23" s="182"/>
-      <c r="R23" s="183"/>
-      <c r="S23" s="183"/>
-      <c r="T23" s="183"/>
-      <c r="U23" s="183"/>
-      <c r="V23" s="183"/>
-      <c r="W23" s="183"/>
-      <c r="X23" s="183"/>
-      <c r="Y23" s="183"/>
-      <c r="Z23" s="183"/>
-      <c r="AA23" s="183"/>
-      <c r="AB23" s="183"/>
-      <c r="AC23" s="183"/>
-      <c r="AD23" s="183"/>
-      <c r="AE23" s="184"/>
-      <c r="AF23" s="179"/>
-      <c r="AG23" s="180"/>
-      <c r="AH23" s="180"/>
-      <c r="AI23" s="181"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="213"/>
+      <c r="D23" s="214"/>
+      <c r="E23" s="215"/>
+      <c r="F23" s="216"/>
+      <c r="G23" s="212"/>
+      <c r="H23" s="217"/>
+      <c r="I23" s="213"/>
+      <c r="J23" s="218"/>
+      <c r="K23" s="219"/>
+      <c r="L23" s="219"/>
+      <c r="M23" s="219"/>
+      <c r="N23" s="219"/>
+      <c r="O23" s="219"/>
+      <c r="P23" s="220"/>
+      <c r="Q23" s="221"/>
+      <c r="R23" s="222"/>
+      <c r="S23" s="222"/>
+      <c r="T23" s="222"/>
+      <c r="U23" s="222"/>
+      <c r="V23" s="222"/>
+      <c r="W23" s="222"/>
+      <c r="X23" s="222"/>
+      <c r="Y23" s="222"/>
+      <c r="Z23" s="222"/>
+      <c r="AA23" s="222"/>
+      <c r="AB23" s="222"/>
+      <c r="AC23" s="222"/>
+      <c r="AD23" s="222"/>
+      <c r="AE23" s="223"/>
+      <c r="AF23" s="218"/>
+      <c r="AG23" s="219"/>
+      <c r="AH23" s="219"/>
+      <c r="AI23" s="220"/>
     </row>
     <row r="24" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="89"/>
-      <c r="B24" s="173"/>
-      <c r="C24" s="174"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="177"/>
-      <c r="G24" s="173"/>
-      <c r="H24" s="178"/>
-      <c r="I24" s="174"/>
-      <c r="J24" s="179"/>
-      <c r="K24" s="180"/>
-      <c r="L24" s="180"/>
-      <c r="M24" s="180"/>
-      <c r="N24" s="180"/>
-      <c r="O24" s="180"/>
-      <c r="P24" s="181"/>
-      <c r="Q24" s="182"/>
-      <c r="R24" s="183"/>
-      <c r="S24" s="183"/>
-      <c r="T24" s="183"/>
-      <c r="U24" s="183"/>
-      <c r="V24" s="183"/>
-      <c r="W24" s="183"/>
-      <c r="X24" s="183"/>
-      <c r="Y24" s="183"/>
-      <c r="Z24" s="183"/>
-      <c r="AA24" s="183"/>
-      <c r="AB24" s="183"/>
-      <c r="AC24" s="183"/>
-      <c r="AD24" s="183"/>
-      <c r="AE24" s="184"/>
-      <c r="AF24" s="179"/>
-      <c r="AG24" s="180"/>
-      <c r="AH24" s="180"/>
-      <c r="AI24" s="181"/>
+      <c r="B24" s="212"/>
+      <c r="C24" s="213"/>
+      <c r="D24" s="214"/>
+      <c r="E24" s="215"/>
+      <c r="F24" s="216"/>
+      <c r="G24" s="212"/>
+      <c r="H24" s="217"/>
+      <c r="I24" s="213"/>
+      <c r="J24" s="218"/>
+      <c r="K24" s="219"/>
+      <c r="L24" s="219"/>
+      <c r="M24" s="219"/>
+      <c r="N24" s="219"/>
+      <c r="O24" s="219"/>
+      <c r="P24" s="220"/>
+      <c r="Q24" s="221"/>
+      <c r="R24" s="222"/>
+      <c r="S24" s="222"/>
+      <c r="T24" s="222"/>
+      <c r="U24" s="222"/>
+      <c r="V24" s="222"/>
+      <c r="W24" s="222"/>
+      <c r="X24" s="222"/>
+      <c r="Y24" s="222"/>
+      <c r="Z24" s="222"/>
+      <c r="AA24" s="222"/>
+      <c r="AB24" s="222"/>
+      <c r="AC24" s="222"/>
+      <c r="AD24" s="222"/>
+      <c r="AE24" s="223"/>
+      <c r="AF24" s="218"/>
+      <c r="AG24" s="219"/>
+      <c r="AH24" s="219"/>
+      <c r="AI24" s="220"/>
     </row>
     <row r="25" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="89"/>
-      <c r="B25" s="173"/>
-      <c r="C25" s="174"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="176"/>
-      <c r="F25" s="177"/>
-      <c r="G25" s="173"/>
-      <c r="H25" s="178"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="179"/>
-      <c r="K25" s="180"/>
-      <c r="L25" s="180"/>
-      <c r="M25" s="180"/>
-      <c r="N25" s="180"/>
-      <c r="O25" s="180"/>
-      <c r="P25" s="181"/>
-      <c r="Q25" s="182"/>
-      <c r="R25" s="183"/>
-      <c r="S25" s="183"/>
-      <c r="T25" s="183"/>
-      <c r="U25" s="183"/>
-      <c r="V25" s="183"/>
-      <c r="W25" s="183"/>
-      <c r="X25" s="183"/>
-      <c r="Y25" s="183"/>
-      <c r="Z25" s="183"/>
-      <c r="AA25" s="183"/>
-      <c r="AB25" s="183"/>
-      <c r="AC25" s="183"/>
-      <c r="AD25" s="183"/>
-      <c r="AE25" s="184"/>
-      <c r="AF25" s="179"/>
-      <c r="AG25" s="180"/>
-      <c r="AH25" s="180"/>
-      <c r="AI25" s="181"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="213"/>
+      <c r="D25" s="214"/>
+      <c r="E25" s="215"/>
+      <c r="F25" s="216"/>
+      <c r="G25" s="212"/>
+      <c r="H25" s="217"/>
+      <c r="I25" s="213"/>
+      <c r="J25" s="218"/>
+      <c r="K25" s="219"/>
+      <c r="L25" s="219"/>
+      <c r="M25" s="219"/>
+      <c r="N25" s="219"/>
+      <c r="O25" s="219"/>
+      <c r="P25" s="220"/>
+      <c r="Q25" s="221"/>
+      <c r="R25" s="222"/>
+      <c r="S25" s="222"/>
+      <c r="T25" s="222"/>
+      <c r="U25" s="222"/>
+      <c r="V25" s="222"/>
+      <c r="W25" s="222"/>
+      <c r="X25" s="222"/>
+      <c r="Y25" s="222"/>
+      <c r="Z25" s="222"/>
+      <c r="AA25" s="222"/>
+      <c r="AB25" s="222"/>
+      <c r="AC25" s="222"/>
+      <c r="AD25" s="222"/>
+      <c r="AE25" s="223"/>
+      <c r="AF25" s="218"/>
+      <c r="AG25" s="219"/>
+      <c r="AH25" s="219"/>
+      <c r="AI25" s="220"/>
     </row>
     <row r="26" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="89"/>
-      <c r="B26" s="173"/>
-      <c r="C26" s="174"/>
-      <c r="D26" s="175"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="177"/>
-      <c r="G26" s="173"/>
-      <c r="H26" s="178"/>
-      <c r="I26" s="174"/>
-      <c r="J26" s="179"/>
-      <c r="K26" s="180"/>
-      <c r="L26" s="180"/>
-      <c r="M26" s="180"/>
-      <c r="N26" s="180"/>
-      <c r="O26" s="180"/>
-      <c r="P26" s="181"/>
-      <c r="Q26" s="182"/>
-      <c r="R26" s="183"/>
-      <c r="S26" s="183"/>
-      <c r="T26" s="183"/>
-      <c r="U26" s="183"/>
-      <c r="V26" s="183"/>
-      <c r="W26" s="183"/>
-      <c r="X26" s="183"/>
-      <c r="Y26" s="183"/>
-      <c r="Z26" s="183"/>
-      <c r="AA26" s="183"/>
-      <c r="AB26" s="183"/>
-      <c r="AC26" s="183"/>
-      <c r="AD26" s="183"/>
-      <c r="AE26" s="184"/>
-      <c r="AF26" s="179"/>
-      <c r="AG26" s="180"/>
-      <c r="AH26" s="180"/>
-      <c r="AI26" s="181"/>
+      <c r="B26" s="212"/>
+      <c r="C26" s="213"/>
+      <c r="D26" s="214"/>
+      <c r="E26" s="215"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="217"/>
+      <c r="I26" s="213"/>
+      <c r="J26" s="218"/>
+      <c r="K26" s="219"/>
+      <c r="L26" s="219"/>
+      <c r="M26" s="219"/>
+      <c r="N26" s="219"/>
+      <c r="O26" s="219"/>
+      <c r="P26" s="220"/>
+      <c r="Q26" s="221"/>
+      <c r="R26" s="222"/>
+      <c r="S26" s="222"/>
+      <c r="T26" s="222"/>
+      <c r="U26" s="222"/>
+      <c r="V26" s="222"/>
+      <c r="W26" s="222"/>
+      <c r="X26" s="222"/>
+      <c r="Y26" s="222"/>
+      <c r="Z26" s="222"/>
+      <c r="AA26" s="222"/>
+      <c r="AB26" s="222"/>
+      <c r="AC26" s="222"/>
+      <c r="AD26" s="222"/>
+      <c r="AE26" s="223"/>
+      <c r="AF26" s="218"/>
+      <c r="AG26" s="219"/>
+      <c r="AH26" s="219"/>
+      <c r="AI26" s="220"/>
     </row>
     <row r="27" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="89"/>
-      <c r="B27" s="173"/>
-      <c r="C27" s="174"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="176"/>
-      <c r="F27" s="177"/>
-      <c r="G27" s="173"/>
-      <c r="H27" s="178"/>
-      <c r="I27" s="174"/>
-      <c r="J27" s="179"/>
-      <c r="K27" s="180"/>
-      <c r="L27" s="180"/>
-      <c r="M27" s="180"/>
-      <c r="N27" s="180"/>
-      <c r="O27" s="180"/>
-      <c r="P27" s="181"/>
-      <c r="Q27" s="182"/>
-      <c r="R27" s="183"/>
-      <c r="S27" s="183"/>
-      <c r="T27" s="183"/>
-      <c r="U27" s="183"/>
-      <c r="V27" s="183"/>
-      <c r="W27" s="183"/>
-      <c r="X27" s="183"/>
-      <c r="Y27" s="183"/>
-      <c r="Z27" s="183"/>
-      <c r="AA27" s="183"/>
-      <c r="AB27" s="183"/>
-      <c r="AC27" s="183"/>
-      <c r="AD27" s="183"/>
-      <c r="AE27" s="184"/>
-      <c r="AF27" s="179"/>
-      <c r="AG27" s="180"/>
-      <c r="AH27" s="180"/>
-      <c r="AI27" s="181"/>
+      <c r="B27" s="212"/>
+      <c r="C27" s="213"/>
+      <c r="D27" s="214"/>
+      <c r="E27" s="215"/>
+      <c r="F27" s="216"/>
+      <c r="G27" s="212"/>
+      <c r="H27" s="217"/>
+      <c r="I27" s="213"/>
+      <c r="J27" s="218"/>
+      <c r="K27" s="219"/>
+      <c r="L27" s="219"/>
+      <c r="M27" s="219"/>
+      <c r="N27" s="219"/>
+      <c r="O27" s="219"/>
+      <c r="P27" s="220"/>
+      <c r="Q27" s="221"/>
+      <c r="R27" s="222"/>
+      <c r="S27" s="222"/>
+      <c r="T27" s="222"/>
+      <c r="U27" s="222"/>
+      <c r="V27" s="222"/>
+      <c r="W27" s="222"/>
+      <c r="X27" s="222"/>
+      <c r="Y27" s="222"/>
+      <c r="Z27" s="222"/>
+      <c r="AA27" s="222"/>
+      <c r="AB27" s="222"/>
+      <c r="AC27" s="222"/>
+      <c r="AD27" s="222"/>
+      <c r="AE27" s="223"/>
+      <c r="AF27" s="218"/>
+      <c r="AG27" s="219"/>
+      <c r="AH27" s="219"/>
+      <c r="AI27" s="220"/>
     </row>
     <row r="28" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="89"/>
-      <c r="B28" s="173"/>
-      <c r="C28" s="174"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="177"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="178"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="179"/>
-      <c r="K28" s="180"/>
-      <c r="L28" s="180"/>
-      <c r="M28" s="180"/>
-      <c r="N28" s="180"/>
-      <c r="O28" s="180"/>
-      <c r="P28" s="181"/>
-      <c r="Q28" s="182"/>
-      <c r="R28" s="183"/>
-      <c r="S28" s="183"/>
-      <c r="T28" s="183"/>
-      <c r="U28" s="183"/>
-      <c r="V28" s="183"/>
-      <c r="W28" s="183"/>
-      <c r="X28" s="183"/>
-      <c r="Y28" s="183"/>
-      <c r="Z28" s="183"/>
-      <c r="AA28" s="183"/>
-      <c r="AB28" s="183"/>
-      <c r="AC28" s="183"/>
-      <c r="AD28" s="183"/>
-      <c r="AE28" s="184"/>
-      <c r="AF28" s="179"/>
-      <c r="AG28" s="180"/>
-      <c r="AH28" s="180"/>
-      <c r="AI28" s="181"/>
+      <c r="B28" s="212"/>
+      <c r="C28" s="213"/>
+      <c r="D28" s="214"/>
+      <c r="E28" s="215"/>
+      <c r="F28" s="216"/>
+      <c r="G28" s="212"/>
+      <c r="H28" s="217"/>
+      <c r="I28" s="213"/>
+      <c r="J28" s="218"/>
+      <c r="K28" s="219"/>
+      <c r="L28" s="219"/>
+      <c r="M28" s="219"/>
+      <c r="N28" s="219"/>
+      <c r="O28" s="219"/>
+      <c r="P28" s="220"/>
+      <c r="Q28" s="221"/>
+      <c r="R28" s="222"/>
+      <c r="S28" s="222"/>
+      <c r="T28" s="222"/>
+      <c r="U28" s="222"/>
+      <c r="V28" s="222"/>
+      <c r="W28" s="222"/>
+      <c r="X28" s="222"/>
+      <c r="Y28" s="222"/>
+      <c r="Z28" s="222"/>
+      <c r="AA28" s="222"/>
+      <c r="AB28" s="222"/>
+      <c r="AC28" s="222"/>
+      <c r="AD28" s="222"/>
+      <c r="AE28" s="223"/>
+      <c r="AF28" s="218"/>
+      <c r="AG28" s="219"/>
+      <c r="AH28" s="219"/>
+      <c r="AI28" s="220"/>
     </row>
     <row r="29" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="89"/>
-      <c r="B29" s="173"/>
-      <c r="C29" s="174"/>
-      <c r="D29" s="175"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="177"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="179"/>
-      <c r="K29" s="180"/>
-      <c r="L29" s="180"/>
-      <c r="M29" s="180"/>
-      <c r="N29" s="180"/>
-      <c r="O29" s="180"/>
-      <c r="P29" s="181"/>
-      <c r="Q29" s="182"/>
-      <c r="R29" s="183"/>
-      <c r="S29" s="183"/>
-      <c r="T29" s="183"/>
-      <c r="U29" s="183"/>
-      <c r="V29" s="183"/>
-      <c r="W29" s="183"/>
-      <c r="X29" s="183"/>
-      <c r="Y29" s="183"/>
-      <c r="Z29" s="183"/>
-      <c r="AA29" s="183"/>
-      <c r="AB29" s="183"/>
-      <c r="AC29" s="183"/>
-      <c r="AD29" s="183"/>
-      <c r="AE29" s="184"/>
-      <c r="AF29" s="179"/>
-      <c r="AG29" s="180"/>
-      <c r="AH29" s="180"/>
-      <c r="AI29" s="181"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="214"/>
+      <c r="E29" s="215"/>
+      <c r="F29" s="216"/>
+      <c r="G29" s="212"/>
+      <c r="H29" s="217"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="218"/>
+      <c r="K29" s="219"/>
+      <c r="L29" s="219"/>
+      <c r="M29" s="219"/>
+      <c r="N29" s="219"/>
+      <c r="O29" s="219"/>
+      <c r="P29" s="220"/>
+      <c r="Q29" s="221"/>
+      <c r="R29" s="222"/>
+      <c r="S29" s="222"/>
+      <c r="T29" s="222"/>
+      <c r="U29" s="222"/>
+      <c r="V29" s="222"/>
+      <c r="W29" s="222"/>
+      <c r="X29" s="222"/>
+      <c r="Y29" s="222"/>
+      <c r="Z29" s="222"/>
+      <c r="AA29" s="222"/>
+      <c r="AB29" s="222"/>
+      <c r="AC29" s="222"/>
+      <c r="AD29" s="222"/>
+      <c r="AE29" s="223"/>
+      <c r="AF29" s="218"/>
+      <c r="AG29" s="219"/>
+      <c r="AH29" s="219"/>
+      <c r="AI29" s="220"/>
     </row>
     <row r="30" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="89"/>
-      <c r="B30" s="173"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="177"/>
-      <c r="G30" s="173"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="180"/>
-      <c r="L30" s="180"/>
-      <c r="M30" s="180"/>
-      <c r="N30" s="180"/>
-      <c r="O30" s="180"/>
-      <c r="P30" s="181"/>
-      <c r="Q30" s="182"/>
-      <c r="R30" s="183"/>
-      <c r="S30" s="183"/>
-      <c r="T30" s="183"/>
-      <c r="U30" s="183"/>
-      <c r="V30" s="183"/>
-      <c r="W30" s="183"/>
-      <c r="X30" s="183"/>
-      <c r="Y30" s="183"/>
-      <c r="Z30" s="183"/>
-      <c r="AA30" s="183"/>
-      <c r="AB30" s="183"/>
-      <c r="AC30" s="183"/>
-      <c r="AD30" s="183"/>
-      <c r="AE30" s="184"/>
-      <c r="AF30" s="179"/>
-      <c r="AG30" s="180"/>
-      <c r="AH30" s="180"/>
-      <c r="AI30" s="181"/>
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="214"/>
+      <c r="E30" s="215"/>
+      <c r="F30" s="216"/>
+      <c r="G30" s="212"/>
+      <c r="H30" s="217"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="218"/>
+      <c r="K30" s="219"/>
+      <c r="L30" s="219"/>
+      <c r="M30" s="219"/>
+      <c r="N30" s="219"/>
+      <c r="O30" s="219"/>
+      <c r="P30" s="220"/>
+      <c r="Q30" s="221"/>
+      <c r="R30" s="222"/>
+      <c r="S30" s="222"/>
+      <c r="T30" s="222"/>
+      <c r="U30" s="222"/>
+      <c r="V30" s="222"/>
+      <c r="W30" s="222"/>
+      <c r="X30" s="222"/>
+      <c r="Y30" s="222"/>
+      <c r="Z30" s="222"/>
+      <c r="AA30" s="222"/>
+      <c r="AB30" s="222"/>
+      <c r="AC30" s="222"/>
+      <c r="AD30" s="222"/>
+      <c r="AE30" s="223"/>
+      <c r="AF30" s="218"/>
+      <c r="AG30" s="219"/>
+      <c r="AH30" s="219"/>
+      <c r="AI30" s="220"/>
     </row>
     <row r="31" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="89"/>
-      <c r="B31" s="173"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="177"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="180"/>
-      <c r="L31" s="180"/>
-      <c r="M31" s="180"/>
-      <c r="N31" s="180"/>
-      <c r="O31" s="180"/>
-      <c r="P31" s="181"/>
-      <c r="Q31" s="182"/>
-      <c r="R31" s="183"/>
-      <c r="S31" s="183"/>
-      <c r="T31" s="183"/>
-      <c r="U31" s="183"/>
-      <c r="V31" s="183"/>
-      <c r="W31" s="183"/>
-      <c r="X31" s="183"/>
-      <c r="Y31" s="183"/>
-      <c r="Z31" s="183"/>
-      <c r="AA31" s="183"/>
-      <c r="AB31" s="183"/>
-      <c r="AC31" s="183"/>
-      <c r="AD31" s="183"/>
-      <c r="AE31" s="184"/>
-      <c r="AF31" s="179"/>
-      <c r="AG31" s="180"/>
-      <c r="AH31" s="180"/>
-      <c r="AI31" s="181"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="214"/>
+      <c r="E31" s="215"/>
+      <c r="F31" s="216"/>
+      <c r="G31" s="212"/>
+      <c r="H31" s="217"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="218"/>
+      <c r="K31" s="219"/>
+      <c r="L31" s="219"/>
+      <c r="M31" s="219"/>
+      <c r="N31" s="219"/>
+      <c r="O31" s="219"/>
+      <c r="P31" s="220"/>
+      <c r="Q31" s="221"/>
+      <c r="R31" s="222"/>
+      <c r="S31" s="222"/>
+      <c r="T31" s="222"/>
+      <c r="U31" s="222"/>
+      <c r="V31" s="222"/>
+      <c r="W31" s="222"/>
+      <c r="X31" s="222"/>
+      <c r="Y31" s="222"/>
+      <c r="Z31" s="222"/>
+      <c r="AA31" s="222"/>
+      <c r="AB31" s="222"/>
+      <c r="AC31" s="222"/>
+      <c r="AD31" s="222"/>
+      <c r="AE31" s="223"/>
+      <c r="AF31" s="218"/>
+      <c r="AG31" s="219"/>
+      <c r="AH31" s="219"/>
+      <c r="AI31" s="220"/>
     </row>
     <row r="32" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="89"/>
-      <c r="B32" s="173"/>
-      <c r="C32" s="174"/>
-      <c r="D32" s="175"/>
-      <c r="E32" s="176"/>
-      <c r="F32" s="177"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="178"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="179"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="180"/>
-      <c r="M32" s="180"/>
-      <c r="N32" s="180"/>
-      <c r="O32" s="180"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="182"/>
-      <c r="R32" s="183"/>
-      <c r="S32" s="183"/>
-      <c r="T32" s="183"/>
-      <c r="U32" s="183"/>
-      <c r="V32" s="183"/>
-      <c r="W32" s="183"/>
-      <c r="X32" s="183"/>
-      <c r="Y32" s="183"/>
-      <c r="Z32" s="183"/>
-      <c r="AA32" s="183"/>
-      <c r="AB32" s="183"/>
-      <c r="AC32" s="183"/>
-      <c r="AD32" s="183"/>
-      <c r="AE32" s="184"/>
-      <c r="AF32" s="179"/>
-      <c r="AG32" s="180"/>
-      <c r="AH32" s="180"/>
-      <c r="AI32" s="181"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="214"/>
+      <c r="E32" s="215"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="212"/>
+      <c r="H32" s="217"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="218"/>
+      <c r="K32" s="238"/>
+      <c r="L32" s="219"/>
+      <c r="M32" s="219"/>
+      <c r="N32" s="219"/>
+      <c r="O32" s="219"/>
+      <c r="P32" s="220"/>
+      <c r="Q32" s="221"/>
+      <c r="R32" s="222"/>
+      <c r="S32" s="222"/>
+      <c r="T32" s="222"/>
+      <c r="U32" s="222"/>
+      <c r="V32" s="222"/>
+      <c r="W32" s="222"/>
+      <c r="X32" s="222"/>
+      <c r="Y32" s="222"/>
+      <c r="Z32" s="222"/>
+      <c r="AA32" s="222"/>
+      <c r="AB32" s="222"/>
+      <c r="AC32" s="222"/>
+      <c r="AD32" s="222"/>
+      <c r="AE32" s="223"/>
+      <c r="AF32" s="218"/>
+      <c r="AG32" s="219"/>
+      <c r="AH32" s="219"/>
+      <c r="AI32" s="220"/>
     </row>
     <row r="33" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="89"/>
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="177"/>
-      <c r="G33" s="173"/>
-      <c r="H33" s="178"/>
-      <c r="I33" s="174"/>
-      <c r="J33" s="179"/>
-      <c r="K33" s="180"/>
-      <c r="L33" s="180"/>
-      <c r="M33" s="180"/>
-      <c r="N33" s="180"/>
-      <c r="O33" s="180"/>
-      <c r="P33" s="181"/>
-      <c r="Q33" s="182"/>
-      <c r="R33" s="183"/>
-      <c r="S33" s="183"/>
-      <c r="T33" s="183"/>
-      <c r="U33" s="183"/>
-      <c r="V33" s="183"/>
-      <c r="W33" s="183"/>
-      <c r="X33" s="183"/>
-      <c r="Y33" s="183"/>
-      <c r="Z33" s="183"/>
-      <c r="AA33" s="183"/>
-      <c r="AB33" s="183"/>
-      <c r="AC33" s="183"/>
-      <c r="AD33" s="183"/>
-      <c r="AE33" s="184"/>
-      <c r="AF33" s="179"/>
-      <c r="AG33" s="180"/>
-      <c r="AH33" s="180"/>
-      <c r="AI33" s="181"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="214"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="212"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="218"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
+      <c r="M33" s="219"/>
+      <c r="N33" s="219"/>
+      <c r="O33" s="219"/>
+      <c r="P33" s="220"/>
+      <c r="Q33" s="221"/>
+      <c r="R33" s="222"/>
+      <c r="S33" s="222"/>
+      <c r="T33" s="222"/>
+      <c r="U33" s="222"/>
+      <c r="V33" s="222"/>
+      <c r="W33" s="222"/>
+      <c r="X33" s="222"/>
+      <c r="Y33" s="222"/>
+      <c r="Z33" s="222"/>
+      <c r="AA33" s="222"/>
+      <c r="AB33" s="222"/>
+      <c r="AC33" s="222"/>
+      <c r="AD33" s="222"/>
+      <c r="AE33" s="223"/>
+      <c r="AF33" s="218"/>
+      <c r="AG33" s="219"/>
+      <c r="AH33" s="219"/>
+      <c r="AI33" s="220"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -29316,162 +29473,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -29623,158 +29624,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="237" t="str">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="216" t="s">
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="238" t="str">
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="244" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="226"/>
-      <c r="U1" s="226"/>
-      <c r="V1" s="226"/>
-      <c r="W1" s="226"/>
-      <c r="X1" s="226"/>
-      <c r="Y1" s="226"/>
-      <c r="Z1" s="227"/>
-      <c r="AA1" s="239" t="s">
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="201"/>
+      <c r="AA1" s="242" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="240"/>
-      <c r="AC1" s="234" t="str">
+      <c r="AB1" s="243"/>
+      <c r="AC1" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="235"/>
-      <c r="AE1" s="235"/>
-      <c r="AF1" s="236"/>
-      <c r="AG1" s="241">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="239">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="242"/>
-      <c r="AI1" s="243"/>
+      <c r="AH1" s="240"/>
+      <c r="AI1" s="241"/>
       <c r="AL1" s="91"/>
     </row>
     <row r="2" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="206" t="s">
+      <c r="A2" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="237" t="str">
+      <c r="B2" s="181"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="219"/>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="221"/>
-      <c r="S2" s="228"/>
-      <c r="T2" s="229"/>
-      <c r="U2" s="229"/>
-      <c r="V2" s="229"/>
-      <c r="W2" s="229"/>
-      <c r="X2" s="229"/>
-      <c r="Y2" s="229"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="239" t="s">
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="184"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="185"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="203"/>
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="242" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="234" t="str">
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="235"/>
-      <c r="AE2" s="235"/>
-      <c r="AF2" s="236"/>
-      <c r="AG2" s="241" t="str">
+      <c r="AD2" s="209"/>
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="210"/>
+      <c r="AG2" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="242"/>
-      <c r="AI2" s="243"/>
+      <c r="AH2" s="240"/>
+      <c r="AI2" s="241"/>
     </row>
     <row r="3" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="206" t="s">
+      <c r="A3" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="237" t="str">
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="M3" s="210"/>
-      <c r="N3" s="211"/>
-      <c r="O3" s="222"/>
-      <c r="P3" s="223"/>
-      <c r="Q3" s="223"/>
-      <c r="R3" s="224"/>
-      <c r="S3" s="231"/>
-      <c r="T3" s="232"/>
-      <c r="U3" s="232"/>
-      <c r="V3" s="232"/>
-      <c r="W3" s="232"/>
-      <c r="X3" s="232"/>
-      <c r="Y3" s="232"/>
-      <c r="Z3" s="233"/>
-      <c r="AA3" s="239"/>
-      <c r="AB3" s="240"/>
-      <c r="AC3" s="234" t="str">
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+      <c r="M3" s="184"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="197"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="198"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="206"/>
+      <c r="U3" s="206"/>
+      <c r="V3" s="206"/>
+      <c r="W3" s="206"/>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="207"/>
+      <c r="AA3" s="242"/>
+      <c r="AB3" s="243"/>
+      <c r="AC3" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="235"/>
-      <c r="AE3" s="235"/>
-      <c r="AF3" s="236"/>
-      <c r="AG3" s="241" t="str">
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="242"/>
-      <c r="AI3" s="243"/>
+      <c r="AH3" s="240"/>
+      <c r="AI3" s="241"/>
     </row>
     <row r="4" spans="1:53" s="31" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AC4" s="92"/>
@@ -29887,7 +29888,7 @@
       <c r="A10" s="31"/>
       <c r="B10" s="94"/>
       <c r="C10" s="94" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D10" s="31"/>
       <c r="E10" s="31"/>
@@ -32193,14 +32194,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -32210,6 +32203,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -32232,157 +32233,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="247" t="s">
+      <c r="A1" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="250"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
-      <c r="N1" s="252"/>
-      <c r="O1" s="256" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="257"/>
-      <c r="Q1" s="257"/>
-      <c r="R1" s="258"/>
-      <c r="S1" s="265" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="266"/>
-      <c r="U1" s="266"/>
-      <c r="V1" s="266"/>
-      <c r="W1" s="266"/>
-      <c r="X1" s="266"/>
-      <c r="Y1" s="266"/>
-      <c r="Z1" s="267"/>
-      <c r="AA1" s="247" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="249"/>
-      <c r="AC1" s="253" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="254"/>
-      <c r="AE1" s="254"/>
-      <c r="AF1" s="255"/>
-      <c r="AG1" s="244">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="245">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="245"/>
-      <c r="AI1" s="246"/>
+      <c r="AH1" s="246"/>
+      <c r="AI1" s="247"/>
       <c r="AN1" s="17"/>
       <c r="AO1" s="17"/>
       <c r="AP1" s="17"/>
     </row>
     <row r="2" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="250"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="259"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="268"/>
-      <c r="T2" s="269"/>
-      <c r="U2" s="269"/>
-      <c r="V2" s="269"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="269"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="247" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="253" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="254"/>
-      <c r="AE2" s="254"/>
-      <c r="AF2" s="255"/>
-      <c r="AG2" s="244" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="245" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="245"/>
-      <c r="AI2" s="246"/>
+      <c r="AH2" s="246"/>
+      <c r="AI2" s="247"/>
       <c r="AN2" s="17"/>
       <c r="AO2" s="17"/>
       <c r="AP2" s="17"/>
     </row>
     <row r="3" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="247" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="249"/>
-      <c r="E3" s="250" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="251"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="251"/>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
-      <c r="M3" s="251"/>
-      <c r="N3" s="252"/>
-      <c r="O3" s="262"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="264"/>
-      <c r="S3" s="271"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="273"/>
-      <c r="AA3" s="247"/>
-      <c r="AB3" s="249"/>
-      <c r="AC3" s="253" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="254"/>
-      <c r="AE3" s="254"/>
-      <c r="AF3" s="255"/>
-      <c r="AG3" s="244" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="245" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="245"/>
-      <c r="AI3" s="246"/>
+      <c r="AH3" s="246"/>
+      <c r="AI3" s="247"/>
       <c r="AN3" s="17"/>
       <c r="AO3" s="17"/>
       <c r="AP3" s="17"/>
@@ -32432,74 +32433,74 @@
       <c r="C14" s="36"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="D15" s="274" t="s">
+      <c r="D15" s="248" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="275"/>
-      <c r="F15" s="275"/>
-      <c r="G15" s="275"/>
-      <c r="H15" s="275"/>
-      <c r="I15" s="275"/>
-      <c r="J15" s="276"/>
-      <c r="K15" s="274" t="s">
+      <c r="E15" s="249"/>
+      <c r="F15" s="249"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="250"/>
+      <c r="K15" s="248" t="s">
         <v>55</v>
       </c>
-      <c r="L15" s="275"/>
-      <c r="M15" s="275"/>
-      <c r="N15" s="275"/>
-      <c r="O15" s="275"/>
-      <c r="P15" s="275"/>
-      <c r="Q15" s="275"/>
-      <c r="R15" s="275"/>
-      <c r="S15" s="275"/>
-      <c r="T15" s="275"/>
-      <c r="U15" s="275"/>
-      <c r="V15" s="275"/>
-      <c r="W15" s="275"/>
-      <c r="X15" s="275"/>
-      <c r="Y15" s="275"/>
-      <c r="Z15" s="275"/>
-      <c r="AA15" s="275"/>
-      <c r="AB15" s="275"/>
-      <c r="AC15" s="275"/>
-      <c r="AD15" s="276"/>
+      <c r="L15" s="249"/>
+      <c r="M15" s="249"/>
+      <c r="N15" s="249"/>
+      <c r="O15" s="249"/>
+      <c r="P15" s="249"/>
+      <c r="Q15" s="249"/>
+      <c r="R15" s="249"/>
+      <c r="S15" s="249"/>
+      <c r="T15" s="249"/>
+      <c r="U15" s="249"/>
+      <c r="V15" s="249"/>
+      <c r="W15" s="249"/>
+      <c r="X15" s="249"/>
+      <c r="Y15" s="249"/>
+      <c r="Z15" s="249"/>
+      <c r="AA15" s="249"/>
+      <c r="AB15" s="249"/>
+      <c r="AC15" s="249"/>
+      <c r="AD15" s="250"/>
     </row>
     <row r="16" spans="1:42" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D16" s="280" t="s">
+      <c r="D16" s="254" t="s">
         <v>272</v>
       </c>
-      <c r="E16" s="281"/>
-      <c r="F16" s="281"/>
-      <c r="G16" s="281"/>
-      <c r="H16" s="281"/>
-      <c r="I16" s="281"/>
-      <c r="J16" s="282"/>
-      <c r="K16" s="277" t="s">
+      <c r="E16" s="255"/>
+      <c r="F16" s="255"/>
+      <c r="G16" s="255"/>
+      <c r="H16" s="255"/>
+      <c r="I16" s="255"/>
+      <c r="J16" s="256"/>
+      <c r="K16" s="251" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="278"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
-      <c r="O16" s="278"/>
-      <c r="P16" s="278"/>
-      <c r="Q16" s="278"/>
-      <c r="R16" s="278"/>
-      <c r="S16" s="278"/>
-      <c r="T16" s="278"/>
-      <c r="U16" s="278"/>
-      <c r="V16" s="278"/>
-      <c r="W16" s="278"/>
-      <c r="X16" s="278"/>
-      <c r="Y16" s="278"/>
-      <c r="Z16" s="278"/>
-      <c r="AA16" s="278"/>
-      <c r="AB16" s="278"/>
-      <c r="AC16" s="278"/>
-      <c r="AD16" s="279"/>
+      <c r="L16" s="252"/>
+      <c r="M16" s="252"/>
+      <c r="N16" s="252"/>
+      <c r="O16" s="252"/>
+      <c r="P16" s="252"/>
+      <c r="Q16" s="252"/>
+      <c r="R16" s="252"/>
+      <c r="S16" s="252"/>
+      <c r="T16" s="252"/>
+      <c r="U16" s="252"/>
+      <c r="V16" s="252"/>
+      <c r="W16" s="252"/>
+      <c r="X16" s="252"/>
+      <c r="Y16" s="252"/>
+      <c r="Z16" s="252"/>
+      <c r="AA16" s="252"/>
+      <c r="AB16" s="252"/>
+      <c r="AC16" s="252"/>
+      <c r="AD16" s="253"/>
     </row>
     <row r="19" spans="3:21" s="156" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C19" s="166" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="20" spans="3:21" s="156" customFormat="1" x14ac:dyDescent="0.15"/>
@@ -32695,14 +32696,14 @@
       <c r="D30" s="162">
         <v>7</v>
       </c>
-      <c r="E30" s="162" t="s">
-        <v>691</v>
+      <c r="E30" s="371" t="s">
+        <v>720</v>
       </c>
       <c r="F30" s="163"/>
       <c r="G30" s="163"/>
       <c r="H30" s="163"/>
       <c r="I30" s="164" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J30" s="165"/>
       <c r="K30" s="163"/>
@@ -32722,13 +32723,13 @@
         <v>8</v>
       </c>
       <c r="E31" s="162" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F31" s="163"/>
       <c r="G31" s="163"/>
       <c r="H31" s="163"/>
       <c r="I31" s="164" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J31" s="165"/>
       <c r="K31" s="163"/>
@@ -32748,13 +32749,13 @@
         <v>9</v>
       </c>
       <c r="E32" s="162" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F32" s="163"/>
       <c r="G32" s="163"/>
       <c r="H32" s="163"/>
       <c r="I32" s="164" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="J32" s="165"/>
       <c r="K32" s="163"/>
@@ -32774,13 +32775,13 @@
         <v>10</v>
       </c>
       <c r="E33" s="162" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F33" s="163"/>
       <c r="G33" s="163"/>
       <c r="H33" s="163"/>
       <c r="I33" s="164" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J33" s="165"/>
       <c r="K33" s="163"/>
@@ -32800,13 +32801,13 @@
         <v>11</v>
       </c>
       <c r="E34" s="162" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F34" s="163"/>
       <c r="G34" s="163"/>
       <c r="H34" s="163"/>
       <c r="I34" s="164" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J34" s="165"/>
       <c r="K34" s="163"/>
@@ -32826,13 +32827,13 @@
         <v>12</v>
       </c>
       <c r="E35" s="162" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F35" s="163"/>
       <c r="G35" s="163"/>
       <c r="H35" s="163"/>
       <c r="I35" s="164" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="J35" s="165"/>
       <c r="K35" s="163"/>
@@ -32852,13 +32853,13 @@
         <v>13</v>
       </c>
       <c r="E36" s="162" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F36" s="163"/>
       <c r="G36" s="163"/>
       <c r="H36" s="163"/>
       <c r="I36" s="164" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="J36" s="165"/>
       <c r="K36" s="163"/>
@@ -32878,13 +32879,13 @@
         <v>14</v>
       </c>
       <c r="E37" s="162" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F37" s="163"/>
       <c r="G37" s="163"/>
       <c r="H37" s="163"/>
       <c r="I37" s="164" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="J37" s="165"/>
       <c r="K37" s="163"/>
@@ -32904,13 +32905,13 @@
         <v>15</v>
       </c>
       <c r="E38" s="162" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F38" s="163"/>
       <c r="G38" s="163"/>
       <c r="H38" s="163"/>
       <c r="I38" s="164" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="J38" s="165"/>
       <c r="K38" s="163"/>
@@ -32930,13 +32931,13 @@
         <v>16</v>
       </c>
       <c r="E39" s="162" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F39" s="163"/>
       <c r="G39" s="163"/>
       <c r="H39" s="163"/>
       <c r="I39" s="164" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="J39" s="165"/>
       <c r="K39" s="163"/>
@@ -32956,13 +32957,13 @@
         <v>17</v>
       </c>
       <c r="E40" s="162" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F40" s="163"/>
       <c r="G40" s="163"/>
       <c r="H40" s="163"/>
       <c r="I40" s="164" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="J40" s="165"/>
       <c r="K40" s="163"/>
@@ -32982,13 +32983,13 @@
         <v>18</v>
       </c>
       <c r="E41" s="162" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F41" s="163"/>
       <c r="G41" s="163"/>
       <c r="H41" s="163"/>
       <c r="I41" s="164" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="J41" s="165"/>
       <c r="K41" s="163"/>
@@ -33008,13 +33009,13 @@
         <v>19</v>
       </c>
       <c r="E42" s="162" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F42" s="163"/>
       <c r="G42" s="163"/>
       <c r="H42" s="163"/>
       <c r="I42" s="164" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J42" s="165"/>
       <c r="K42" s="163"/>
@@ -33034,11 +33035,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="K15:AD15"/>
-    <mergeCell ref="K16:AD16"/>
-    <mergeCell ref="D15:J15"/>
-    <mergeCell ref="D16:J16"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
@@ -33055,6 +33051,11 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="K15:AD15"/>
+    <mergeCell ref="K16:AD16"/>
+    <mergeCell ref="D15:J15"/>
+    <mergeCell ref="D16:J16"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <hyperlinks>
@@ -33100,157 +33101,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="247" t="s">
+      <c r="A1" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="250"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
-      <c r="N1" s="252"/>
-      <c r="O1" s="256" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="257"/>
-      <c r="Q1" s="257"/>
-      <c r="R1" s="258"/>
-      <c r="S1" s="265" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="266"/>
-      <c r="U1" s="266"/>
-      <c r="V1" s="266"/>
-      <c r="W1" s="266"/>
-      <c r="X1" s="266"/>
-      <c r="Y1" s="266"/>
-      <c r="Z1" s="267"/>
-      <c r="AA1" s="247" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="249"/>
-      <c r="AC1" s="253" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="254"/>
-      <c r="AE1" s="254"/>
-      <c r="AF1" s="255"/>
-      <c r="AG1" s="299">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="284">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="300"/>
-      <c r="AI1" s="301"/>
+      <c r="AH1" s="285"/>
+      <c r="AI1" s="286"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="250"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="259"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="268"/>
-      <c r="T2" s="269"/>
-      <c r="U2" s="269"/>
-      <c r="V2" s="269"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="269"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="247" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="253" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="254"/>
-      <c r="AE2" s="254"/>
-      <c r="AF2" s="255"/>
-      <c r="AG2" s="299" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="300"/>
-      <c r="AI2" s="301"/>
+      <c r="AH2" s="285"/>
+      <c r="AI2" s="286"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="247" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="249"/>
-      <c r="E3" s="250" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="251"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="251"/>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
-      <c r="M3" s="251"/>
-      <c r="N3" s="252"/>
-      <c r="O3" s="262"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="264"/>
-      <c r="S3" s="271"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="273"/>
-      <c r="AA3" s="247"/>
-      <c r="AB3" s="249"/>
-      <c r="AC3" s="253" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="254"/>
-      <c r="AE3" s="254"/>
-      <c r="AF3" s="255"/>
-      <c r="AG3" s="299" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="300"/>
-      <c r="AI3" s="301"/>
+      <c r="AH3" s="285"/>
+      <c r="AI3" s="286"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -33366,12 +33367,12 @@
       <c r="V20" s="30"/>
     </row>
     <row r="21" spans="4:23" x14ac:dyDescent="0.15">
-      <c r="F21" s="283" t="s">
+      <c r="F21" s="287" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="284"/>
-      <c r="H21" s="284"/>
-      <c r="I21" s="285"/>
+      <c r="G21" s="288"/>
+      <c r="H21" s="288"/>
+      <c r="I21" s="289"/>
       <c r="J21" s="58" t="s">
         <v>26</v>
       </c>
@@ -34348,8 +34349,8 @@
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
-      <c r="F54" s="370" t="s">
-        <v>719</v>
+      <c r="F54" s="172" t="s">
+        <v>718</v>
       </c>
       <c r="G54" s="79"/>
       <c r="H54" s="79"/>
@@ -34410,7 +34411,7 @@
       <c r="M55" s="151"/>
       <c r="N55" s="152"/>
       <c r="O55" s="153" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="P55" s="154"/>
       <c r="Q55" s="154"/>
@@ -34784,17 +34785,17 @@
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="30"/>
-      <c r="G63" s="296" t="s">
+      <c r="G63" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="297"/>
-      <c r="I63" s="297"/>
-      <c r="J63" s="298"/>
-      <c r="K63" s="274" t="s">
+      <c r="H63" s="301"/>
+      <c r="I63" s="301"/>
+      <c r="J63" s="302"/>
+      <c r="K63" s="248" t="s">
         <v>69</v>
       </c>
-      <c r="L63" s="275"/>
-      <c r="M63" s="276"/>
+      <c r="L63" s="249"/>
+      <c r="M63" s="250"/>
       <c r="N63" s="58" t="s">
         <v>198</v>
       </c>
@@ -34836,17 +34837,17 @@
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
       <c r="F64" s="29"/>
-      <c r="G64" s="286" t="s">
+      <c r="G64" s="290" t="s">
         <v>566</v>
       </c>
-      <c r="H64" s="287"/>
-      <c r="I64" s="287"/>
-      <c r="J64" s="288"/>
-      <c r="K64" s="286" t="s">
+      <c r="H64" s="291"/>
+      <c r="I64" s="291"/>
+      <c r="J64" s="292"/>
+      <c r="K64" s="290" t="s">
         <v>567</v>
       </c>
-      <c r="L64" s="287"/>
-      <c r="M64" s="288"/>
+      <c r="L64" s="291"/>
+      <c r="M64" s="292"/>
       <c r="N64" s="64" t="s">
         <v>396</v>
       </c>
@@ -34888,13 +34889,13 @@
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="29"/>
-      <c r="G65" s="289"/>
-      <c r="H65" s="290"/>
-      <c r="I65" s="290"/>
-      <c r="J65" s="291"/>
-      <c r="K65" s="295"/>
-      <c r="L65" s="290"/>
-      <c r="M65" s="291"/>
+      <c r="G65" s="293"/>
+      <c r="H65" s="294"/>
+      <c r="I65" s="294"/>
+      <c r="J65" s="295"/>
+      <c r="K65" s="299"/>
+      <c r="L65" s="294"/>
+      <c r="M65" s="295"/>
       <c r="N65" s="54" t="s">
         <v>397</v>
       </c>
@@ -34936,13 +34937,13 @@
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
       <c r="F66" s="29"/>
-      <c r="G66" s="289"/>
-      <c r="H66" s="290"/>
-      <c r="I66" s="290"/>
-      <c r="J66" s="291"/>
-      <c r="K66" s="289"/>
-      <c r="L66" s="290"/>
-      <c r="M66" s="291"/>
+      <c r="G66" s="293"/>
+      <c r="H66" s="294"/>
+      <c r="I66" s="294"/>
+      <c r="J66" s="295"/>
+      <c r="K66" s="293"/>
+      <c r="L66" s="294"/>
+      <c r="M66" s="295"/>
       <c r="N66" s="54" t="s">
         <v>390</v>
       </c>
@@ -34984,13 +34985,13 @@
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
       <c r="F67" s="29"/>
-      <c r="G67" s="289"/>
-      <c r="H67" s="290"/>
-      <c r="I67" s="290"/>
-      <c r="J67" s="291"/>
-      <c r="K67" s="289"/>
-      <c r="L67" s="290"/>
-      <c r="M67" s="291"/>
+      <c r="G67" s="293"/>
+      <c r="H67" s="294"/>
+      <c r="I67" s="294"/>
+      <c r="J67" s="295"/>
+      <c r="K67" s="293"/>
+      <c r="L67" s="294"/>
+      <c r="M67" s="295"/>
       <c r="N67" s="54" t="s">
         <v>633</v>
       </c>
@@ -35032,13 +35033,13 @@
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68"/>
-      <c r="G68" s="292"/>
-      <c r="H68" s="293"/>
-      <c r="I68" s="293"/>
-      <c r="J68" s="294"/>
-      <c r="K68" s="292"/>
-      <c r="L68" s="293"/>
-      <c r="M68" s="294"/>
+      <c r="G68" s="296"/>
+      <c r="H68" s="297"/>
+      <c r="I68" s="297"/>
+      <c r="J68" s="298"/>
+      <c r="K68" s="296"/>
+      <c r="L68" s="297"/>
+      <c r="M68" s="298"/>
       <c r="N68" s="73"/>
       <c r="O68" s="74"/>
       <c r="P68" s="74"/>
@@ -35423,6 +35424,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="G64:J68"/>
+    <mergeCell ref="K64:M68"/>
+    <mergeCell ref="G63:J63"/>
+    <mergeCell ref="K63:M63"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
@@ -35439,12 +35446,6 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="G64:J68"/>
-    <mergeCell ref="K64:M68"/>
-    <mergeCell ref="G63:J63"/>
-    <mergeCell ref="K63:M63"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -35474,157 +35475,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="247" t="s">
+      <c r="A1" s="257" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="250"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
-      <c r="N1" s="252"/>
-      <c r="O1" s="302" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="303" t="s">
         <v>96</v>
       </c>
-      <c r="P1" s="257"/>
-      <c r="Q1" s="257"/>
-      <c r="R1" s="303"/>
-      <c r="S1" s="304" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="304"/>
+      <c r="S1" s="305" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="266"/>
-      <c r="U1" s="266"/>
-      <c r="V1" s="266"/>
-      <c r="W1" s="266"/>
-      <c r="X1" s="266"/>
-      <c r="Y1" s="266"/>
-      <c r="Z1" s="305"/>
-      <c r="AA1" s="247" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="306"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="249"/>
-      <c r="AC1" s="253" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="254"/>
-      <c r="AE1" s="254"/>
-      <c r="AF1" s="255"/>
-      <c r="AG1" s="299">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="284">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="300"/>
-      <c r="AI1" s="301"/>
+      <c r="AH1" s="285"/>
+      <c r="AI1" s="286"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="250"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="259"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="268"/>
-      <c r="T2" s="269"/>
-      <c r="U2" s="269"/>
-      <c r="V2" s="269"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="269"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="247" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="253" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="254"/>
-      <c r="AE2" s="254"/>
-      <c r="AF2" s="255"/>
-      <c r="AG2" s="299" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="300"/>
-      <c r="AI2" s="301"/>
+      <c r="AH2" s="285"/>
+      <c r="AI2" s="286"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="247" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="249"/>
-      <c r="E3" s="250" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="251"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="251"/>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
-      <c r="M3" s="251"/>
-      <c r="N3" s="252"/>
-      <c r="O3" s="262"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="264"/>
-      <c r="S3" s="271"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="273"/>
-      <c r="AA3" s="247"/>
-      <c r="AB3" s="249"/>
-      <c r="AC3" s="253" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="254"/>
-      <c r="AE3" s="254"/>
-      <c r="AF3" s="255"/>
-      <c r="AG3" s="299" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="300"/>
-      <c r="AI3" s="301"/>
+      <c r="AH3" s="285"/>
+      <c r="AI3" s="286"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -35658,41 +35659,41 @@
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="E14" s="296" t="s">
+      <c r="E14" s="300" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="297"/>
-      <c r="G14" s="297"/>
-      <c r="H14" s="297"/>
-      <c r="I14" s="297"/>
-      <c r="J14" s="298"/>
-      <c r="K14" s="296" t="s">
+      <c r="F14" s="301"/>
+      <c r="G14" s="301"/>
+      <c r="H14" s="301"/>
+      <c r="I14" s="301"/>
+      <c r="J14" s="302"/>
+      <c r="K14" s="300" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="297"/>
-      <c r="M14" s="297"/>
-      <c r="N14" s="297"/>
-      <c r="O14" s="297"/>
-      <c r="P14" s="297"/>
-      <c r="Q14" s="297"/>
-      <c r="R14" s="297"/>
-      <c r="S14" s="298"/>
-      <c r="T14" s="296" t="s">
+      <c r="L14" s="301"/>
+      <c r="M14" s="301"/>
+      <c r="N14" s="301"/>
+      <c r="O14" s="301"/>
+      <c r="P14" s="301"/>
+      <c r="Q14" s="301"/>
+      <c r="R14" s="301"/>
+      <c r="S14" s="302"/>
+      <c r="T14" s="300" t="s">
         <v>94</v>
       </c>
-      <c r="U14" s="297"/>
-      <c r="V14" s="297"/>
-      <c r="W14" s="297"/>
-      <c r="X14" s="297"/>
-      <c r="Y14" s="297"/>
-      <c r="Z14" s="297"/>
-      <c r="AA14" s="297"/>
-      <c r="AB14" s="297"/>
-      <c r="AC14" s="297"/>
-      <c r="AD14" s="297"/>
-      <c r="AE14" s="297"/>
-      <c r="AF14" s="297"/>
-      <c r="AG14" s="298"/>
+      <c r="U14" s="301"/>
+      <c r="V14" s="301"/>
+      <c r="W14" s="301"/>
+      <c r="X14" s="301"/>
+      <c r="Y14" s="301"/>
+      <c r="Z14" s="301"/>
+      <c r="AA14" s="301"/>
+      <c r="AB14" s="301"/>
+      <c r="AC14" s="301"/>
+      <c r="AD14" s="301"/>
+      <c r="AE14" s="301"/>
+      <c r="AF14" s="301"/>
+      <c r="AG14" s="302"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.15">
       <c r="E15" s="80" t="s">
@@ -38334,6 +38335,11 @@
     <row r="346" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="E14:J14"/>
+    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -38349,11 +38355,6 @@
     <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="K14:S14"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AG1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>
@@ -38395,151 +38396,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="247" t="s">
+      <c r="A1" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="250"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
-      <c r="N1" s="252"/>
-      <c r="O1" s="256" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="266" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="257"/>
-      <c r="Q1" s="257"/>
-      <c r="R1" s="258"/>
-      <c r="S1" s="265" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="266"/>
-      <c r="U1" s="266"/>
-      <c r="V1" s="266"/>
-      <c r="W1" s="266"/>
-      <c r="X1" s="266"/>
-      <c r="Y1" s="266"/>
-      <c r="Z1" s="267"/>
-      <c r="AA1" s="247" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="249"/>
-      <c r="AC1" s="253" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="254"/>
-      <c r="AE1" s="254"/>
-      <c r="AF1" s="255"/>
-      <c r="AG1" s="299">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="284">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="300"/>
-      <c r="AI1" s="301"/>
+      <c r="AH1" s="285"/>
+      <c r="AI1" s="286"/>
     </row>
     <row r="2" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="250"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="259"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="268"/>
-      <c r="T2" s="269"/>
-      <c r="U2" s="269"/>
-      <c r="V2" s="269"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="269"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="247" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="253" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="254"/>
-      <c r="AE2" s="254"/>
-      <c r="AF2" s="255"/>
-      <c r="AG2" s="299" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="300"/>
-      <c r="AI2" s="301"/>
+      <c r="AH2" s="285"/>
+      <c r="AI2" s="286"/>
     </row>
     <row r="3" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="247" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="249"/>
-      <c r="E3" s="250" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="251"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="251"/>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
-      <c r="M3" s="251"/>
-      <c r="N3" s="252"/>
-      <c r="O3" s="262"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="264"/>
-      <c r="S3" s="271"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="273"/>
-      <c r="AA3" s="247"/>
-      <c r="AB3" s="249"/>
-      <c r="AC3" s="253" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="254"/>
-      <c r="AE3" s="254"/>
-      <c r="AF3" s="255"/>
-      <c r="AG3" s="299" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="300"/>
-      <c r="AI3" s="301"/>
+      <c r="AH3" s="285"/>
+      <c r="AI3" s="286"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B5" s="32" t="s">
@@ -39643,12 +39644,12 @@
     <row r="74" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A74" s="30"/>
       <c r="E74" s="30"/>
-      <c r="F74" s="274" t="s">
+      <c r="F74" s="248" t="s">
         <v>50</v>
       </c>
-      <c r="G74" s="275"/>
-      <c r="H74" s="275"/>
-      <c r="I74" s="276"/>
+      <c r="G74" s="249"/>
+      <c r="H74" s="249"/>
+      <c r="I74" s="250"/>
       <c r="J74" s="58" t="s">
         <v>190</v>
       </c>
@@ -39677,12 +39678,12 @@
     <row r="75" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="30"/>
       <c r="E75" s="30"/>
-      <c r="F75" s="308" t="s">
+      <c r="F75" s="307" t="s">
         <v>229</v>
       </c>
-      <c r="G75" s="309"/>
-      <c r="H75" s="309"/>
-      <c r="I75" s="310"/>
+      <c r="G75" s="308"/>
+      <c r="H75" s="308"/>
+      <c r="I75" s="309"/>
       <c r="J75" s="83" t="s">
         <v>237</v>
       </c>
@@ -39712,12 +39713,12 @@
       <c r="A76" s="30"/>
       <c r="C76" s="30"/>
       <c r="E76" s="30"/>
-      <c r="F76" s="315" t="s">
+      <c r="F76" s="310" t="s">
         <v>330</v>
       </c>
-      <c r="G76" s="316"/>
-      <c r="H76" s="316"/>
-      <c r="I76" s="317"/>
+      <c r="G76" s="311"/>
+      <c r="H76" s="311"/>
+      <c r="I76" s="312"/>
       <c r="J76" s="72" t="s">
         <v>191</v>
       </c>
@@ -39747,10 +39748,10 @@
       <c r="A77" s="30"/>
       <c r="C77" s="30"/>
       <c r="E77" s="30"/>
-      <c r="F77" s="318"/>
-      <c r="G77" s="319"/>
-      <c r="H77" s="319"/>
-      <c r="I77" s="320"/>
+      <c r="F77" s="313"/>
+      <c r="G77" s="314"/>
+      <c r="H77" s="314"/>
+      <c r="I77" s="315"/>
       <c r="J77" s="73"/>
       <c r="K77" s="74"/>
       <c r="L77" s="74"/>
@@ -39775,12 +39776,12 @@
     <row r="78" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A78" s="30"/>
       <c r="E78" s="30"/>
-      <c r="F78" s="308" t="s">
+      <c r="F78" s="307" t="s">
         <v>230</v>
       </c>
-      <c r="G78" s="309"/>
-      <c r="H78" s="309"/>
-      <c r="I78" s="310"/>
+      <c r="G78" s="308"/>
+      <c r="H78" s="308"/>
+      <c r="I78" s="309"/>
       <c r="J78" s="80" t="s">
         <v>192</v>
       </c>
@@ -39809,12 +39810,12 @@
     <row r="79" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A79" s="30"/>
       <c r="E79" s="30"/>
-      <c r="F79" s="308" t="s">
+      <c r="F79" s="307" t="s">
         <v>228</v>
       </c>
-      <c r="G79" s="309"/>
-      <c r="H79" s="309"/>
-      <c r="I79" s="310"/>
+      <c r="G79" s="308"/>
+      <c r="H79" s="308"/>
+      <c r="I79" s="309"/>
       <c r="J79" s="83" t="s">
         <v>195</v>
       </c>
@@ -39844,12 +39845,12 @@
     <row r="80" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A80" s="30"/>
       <c r="E80" s="30"/>
-      <c r="F80" s="308" t="s">
+      <c r="F80" s="307" t="s">
         <v>227</v>
       </c>
-      <c r="G80" s="309"/>
-      <c r="H80" s="309"/>
-      <c r="I80" s="310"/>
+      <c r="G80" s="308"/>
+      <c r="H80" s="308"/>
+      <c r="I80" s="309"/>
       <c r="J80" s="80" t="s">
         <v>193</v>
       </c>
@@ -39995,7 +39996,7 @@
       <c r="AG137" s="51"/>
     </row>
     <row r="138" spans="5:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F138" s="311">
+      <c r="F138" s="318">
         <v>1</v>
       </c>
       <c r="G138" s="64" t="s">
@@ -40031,7 +40032,7 @@
       <c r="AG138" s="51"/>
     </row>
     <row r="139" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F139" s="312"/>
+      <c r="F139" s="319"/>
       <c r="G139" s="54"/>
       <c r="H139" s="30"/>
       <c r="I139" s="30"/>
@@ -40063,7 +40064,7 @@
       <c r="AG139" s="51"/>
     </row>
     <row r="140" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F140" s="312"/>
+      <c r="F140" s="319"/>
       <c r="G140" s="54"/>
       <c r="H140" s="30"/>
       <c r="I140" s="30"/>
@@ -40095,7 +40096,7 @@
       <c r="AG140" s="51"/>
     </row>
     <row r="141" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F141" s="312"/>
+      <c r="F141" s="319"/>
       <c r="G141" s="54"/>
       <c r="H141" s="30"/>
       <c r="I141" s="30"/>
@@ -40127,7 +40128,7 @@
       <c r="AG141" s="51"/>
     </row>
     <row r="142" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F142" s="312"/>
+      <c r="F142" s="319"/>
       <c r="G142" s="54"/>
       <c r="H142" s="30"/>
       <c r="I142" s="30"/>
@@ -40159,7 +40160,7 @@
       <c r="AG142" s="51"/>
     </row>
     <row r="143" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F143" s="312"/>
+      <c r="F143" s="319"/>
       <c r="G143" s="54"/>
       <c r="H143" s="30"/>
       <c r="I143" s="30"/>
@@ -40191,7 +40192,7 @@
       <c r="AG143" s="51"/>
     </row>
     <row r="144" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F144" s="312"/>
+      <c r="F144" s="319"/>
       <c r="G144" s="54"/>
       <c r="H144" s="30"/>
       <c r="I144" s="30"/>
@@ -40223,7 +40224,7 @@
       <c r="AG144" s="51"/>
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F145" s="313"/>
+      <c r="F145" s="320"/>
       <c r="G145" s="54"/>
       <c r="H145" s="30"/>
       <c r="I145" s="30"/>
@@ -40321,7 +40322,7 @@
       <c r="AG147" s="17"/>
     </row>
     <row r="148" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F148" s="311">
+      <c r="F148" s="318">
         <v>3</v>
       </c>
       <c r="G148" s="54" t="s">
@@ -40357,7 +40358,7 @@
       <c r="AG148" s="51"/>
     </row>
     <row r="149" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F149" s="312"/>
+      <c r="F149" s="319"/>
       <c r="G149" s="54"/>
       <c r="H149" s="30"/>
       <c r="I149" s="30"/>
@@ -40389,7 +40390,7 @@
       <c r="AG149" s="51"/>
     </row>
     <row r="150" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F150" s="312"/>
+      <c r="F150" s="319"/>
       <c r="G150" s="54"/>
       <c r="H150" s="30"/>
       <c r="I150" s="30"/>
@@ -40421,7 +40422,7 @@
       <c r="AG150" s="51"/>
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F151" s="312"/>
+      <c r="F151" s="319"/>
       <c r="G151" s="54"/>
       <c r="H151" s="30"/>
       <c r="I151" s="30"/>
@@ -40453,7 +40454,7 @@
       <c r="AG151" s="51"/>
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F152" s="312"/>
+      <c r="F152" s="319"/>
       <c r="G152" s="54"/>
       <c r="H152" s="30"/>
       <c r="I152" s="30"/>
@@ -40485,7 +40486,7 @@
       <c r="AG152" s="51"/>
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F153" s="313"/>
+      <c r="F153" s="320"/>
       <c r="G153" s="54"/>
       <c r="H153" s="30"/>
       <c r="I153" s="30"/>
@@ -40517,7 +40518,7 @@
       <c r="AG153" s="51"/>
     </row>
     <row r="154" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F154" s="314">
+      <c r="F154" s="321">
         <v>4</v>
       </c>
       <c r="G154" s="64" t="s">
@@ -40553,7 +40554,7 @@
       <c r="AG154" s="51"/>
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F155" s="314"/>
+      <c r="F155" s="321"/>
       <c r="G155" s="73"/>
       <c r="H155" s="74"/>
       <c r="I155" s="74"/>
@@ -41026,7 +41027,7 @@
     </row>
     <row r="228" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A228" s="30"/>
-      <c r="F228" s="306"/>
+      <c r="F228" s="316"/>
       <c r="G228" s="83" t="s">
         <v>239</v>
       </c>
@@ -41063,7 +41064,7 @@
       <c r="AD228" s="113"/>
     </row>
     <row r="229" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="F229" s="306"/>
+      <c r="F229" s="316"/>
       <c r="G229" s="83" t="s">
         <v>279</v>
       </c>
@@ -41100,7 +41101,7 @@
       <c r="AD229" s="113"/>
     </row>
     <row r="230" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="F230" s="307"/>
+      <c r="F230" s="317"/>
       <c r="G230" s="84" t="s">
         <v>280</v>
       </c>
@@ -41611,6 +41612,21 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="F228:F230"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F138:F145"/>
+    <mergeCell ref="F148:F153"/>
+    <mergeCell ref="F154:F155"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="F76:I77"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="AG3:AI3"/>
@@ -41623,21 +41639,6 @@
     <mergeCell ref="S1:Z3"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F74:I74"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="F76:I77"/>
-    <mergeCell ref="F228:F230"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F138:F145"/>
-    <mergeCell ref="F148:F153"/>
-    <mergeCell ref="F154:F155"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -41674,157 +41675,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="237"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="256" t="s">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="257"/>
-      <c r="Q1" s="257"/>
-      <c r="R1" s="258"/>
-      <c r="S1" s="265" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="266"/>
-      <c r="U1" s="266"/>
-      <c r="V1" s="266"/>
-      <c r="W1" s="266"/>
-      <c r="X1" s="266"/>
-      <c r="Y1" s="266"/>
-      <c r="Z1" s="267"/>
-      <c r="AA1" s="206" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="180" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="208"/>
-      <c r="AC1" s="234" t="str">
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="235"/>
-      <c r="AE1" s="235"/>
-      <c r="AF1" s="236"/>
-      <c r="AG1" s="355">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="348">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="356"/>
-      <c r="AI1" s="357"/>
+      <c r="AH1" s="349"/>
+      <c r="AI1" s="350"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="206" t="s">
+      <c r="A2" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="259"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="268"/>
-      <c r="T2" s="269"/>
-      <c r="U2" s="269"/>
-      <c r="V2" s="269"/>
-      <c r="W2" s="269"/>
-      <c r="X2" s="269"/>
-      <c r="Y2" s="269"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="206" t="s">
+      <c r="B2" s="181"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="184"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="185"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="208"/>
-      <c r="AC2" s="234" t="str">
+      <c r="AB2" s="182"/>
+      <c r="AC2" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="235"/>
-      <c r="AE2" s="235"/>
-      <c r="AF2" s="236"/>
-      <c r="AG2" s="355" t="str">
+      <c r="AD2" s="209"/>
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="210"/>
+      <c r="AG2" s="348" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="356"/>
-      <c r="AI2" s="357"/>
+      <c r="AH2" s="349"/>
+      <c r="AI2" s="350"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="206" t="s">
+      <c r="A3" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="237" t="str">
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="M3" s="210"/>
-      <c r="N3" s="211"/>
-      <c r="O3" s="262"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="264"/>
-      <c r="S3" s="271"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="273"/>
-      <c r="AA3" s="206"/>
-      <c r="AB3" s="208"/>
-      <c r="AC3" s="234" t="str">
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+      <c r="M3" s="184"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="180"/>
+      <c r="AB3" s="182"/>
+      <c r="AC3" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="235"/>
-      <c r="AE3" s="235"/>
-      <c r="AF3" s="236"/>
-      <c r="AG3" s="355" t="str">
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="348" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="356"/>
-      <c r="AI3" s="357"/>
+      <c r="AH3" s="349"/>
+      <c r="AI3" s="350"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -42307,477 +42308,477 @@
     </row>
     <row r="150" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="151" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D151" s="274" t="s">
+      <c r="D151" s="248" t="s">
         <v>325</v>
       </c>
-      <c r="E151" s="339"/>
-      <c r="F151" s="339"/>
-      <c r="G151" s="339"/>
-      <c r="H151" s="339"/>
-      <c r="I151" s="339"/>
-      <c r="J151" s="340"/>
-      <c r="K151" s="358" t="s">
+      <c r="E151" s="327"/>
+      <c r="F151" s="327"/>
+      <c r="G151" s="327"/>
+      <c r="H151" s="327"/>
+      <c r="I151" s="327"/>
+      <c r="J151" s="328"/>
+      <c r="K151" s="325" t="s">
         <v>50</v>
       </c>
-      <c r="L151" s="358"/>
-      <c r="M151" s="358"/>
-      <c r="N151" s="358"/>
-      <c r="O151" s="358"/>
-      <c r="P151" s="358"/>
-      <c r="Q151" s="358"/>
-      <c r="R151" s="358"/>
-      <c r="S151" s="358"/>
-      <c r="T151" s="358"/>
-      <c r="U151" s="358"/>
-      <c r="V151" s="358"/>
-      <c r="W151" s="358"/>
-      <c r="X151" s="358"/>
-      <c r="Y151" s="358"/>
-      <c r="Z151" s="358"/>
-      <c r="AA151" s="365" t="s">
+      <c r="L151" s="325"/>
+      <c r="M151" s="325"/>
+      <c r="N151" s="325"/>
+      <c r="O151" s="325"/>
+      <c r="P151" s="325"/>
+      <c r="Q151" s="325"/>
+      <c r="R151" s="325"/>
+      <c r="S151" s="325"/>
+      <c r="T151" s="325"/>
+      <c r="U151" s="325"/>
+      <c r="V151" s="325"/>
+      <c r="W151" s="325"/>
+      <c r="X151" s="325"/>
+      <c r="Y151" s="325"/>
+      <c r="Z151" s="325"/>
+      <c r="AA151" s="324" t="s">
         <v>51</v>
       </c>
-      <c r="AB151" s="358"/>
-      <c r="AC151" s="358"/>
-      <c r="AD151" s="358"/>
-      <c r="AE151" s="358"/>
-      <c r="AF151" s="358"/>
-      <c r="AG151" s="358"/>
-      <c r="AH151" s="358"/>
+      <c r="AB151" s="325"/>
+      <c r="AC151" s="325"/>
+      <c r="AD151" s="325"/>
+      <c r="AE151" s="325"/>
+      <c r="AF151" s="325"/>
+      <c r="AG151" s="325"/>
+      <c r="AH151" s="325"/>
     </row>
     <row r="152" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D152" s="277" t="s">
+      <c r="D152" s="251" t="s">
         <v>52</v>
       </c>
-      <c r="E152" s="278"/>
-      <c r="F152" s="278"/>
-      <c r="G152" s="278"/>
-      <c r="H152" s="278"/>
-      <c r="I152" s="278"/>
-      <c r="J152" s="279"/>
-      <c r="K152" s="354" t="s">
+      <c r="E152" s="252"/>
+      <c r="F152" s="252"/>
+      <c r="G152" s="252"/>
+      <c r="H152" s="252"/>
+      <c r="I152" s="252"/>
+      <c r="J152" s="253"/>
+      <c r="K152" s="347" t="s">
         <v>289</v>
       </c>
-      <c r="L152" s="354"/>
-      <c r="M152" s="354"/>
-      <c r="N152" s="354"/>
-      <c r="O152" s="354"/>
-      <c r="P152" s="354"/>
-      <c r="Q152" s="354"/>
-      <c r="R152" s="354"/>
-      <c r="S152" s="354"/>
-      <c r="T152" s="354"/>
-      <c r="U152" s="354"/>
-      <c r="V152" s="354"/>
-      <c r="W152" s="354"/>
-      <c r="X152" s="354"/>
-      <c r="Y152" s="354"/>
-      <c r="Z152" s="354"/>
-      <c r="AA152" s="359" t="s">
+      <c r="L152" s="347"/>
+      <c r="M152" s="347"/>
+      <c r="N152" s="347"/>
+      <c r="O152" s="347"/>
+      <c r="P152" s="347"/>
+      <c r="Q152" s="347"/>
+      <c r="R152" s="347"/>
+      <c r="S152" s="347"/>
+      <c r="T152" s="347"/>
+      <c r="U152" s="347"/>
+      <c r="V152" s="347"/>
+      <c r="W152" s="347"/>
+      <c r="X152" s="347"/>
+      <c r="Y152" s="347"/>
+      <c r="Z152" s="347"/>
+      <c r="AA152" s="322" t="s">
         <v>75</v>
       </c>
-      <c r="AB152" s="360"/>
-      <c r="AC152" s="360"/>
-      <c r="AD152" s="360"/>
-      <c r="AE152" s="360"/>
-      <c r="AF152" s="360"/>
-      <c r="AG152" s="360"/>
-      <c r="AH152" s="360"/>
+      <c r="AB152" s="323"/>
+      <c r="AC152" s="323"/>
+      <c r="AD152" s="323"/>
+      <c r="AE152" s="323"/>
+      <c r="AF152" s="323"/>
+      <c r="AG152" s="323"/>
+      <c r="AH152" s="323"/>
     </row>
     <row r="153" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D153" s="308" t="s">
+      <c r="D153" s="307" t="s">
         <v>304</v>
       </c>
-      <c r="E153" s="309"/>
-      <c r="F153" s="309"/>
-      <c r="G153" s="309"/>
-      <c r="H153" s="309"/>
-      <c r="I153" s="309"/>
-      <c r="J153" s="310"/>
-      <c r="K153" s="354" t="s">
+      <c r="E153" s="308"/>
+      <c r="F153" s="308"/>
+      <c r="G153" s="308"/>
+      <c r="H153" s="308"/>
+      <c r="I153" s="308"/>
+      <c r="J153" s="309"/>
+      <c r="K153" s="347" t="s">
         <v>290</v>
       </c>
-      <c r="L153" s="354"/>
-      <c r="M153" s="354"/>
-      <c r="N153" s="354"/>
-      <c r="O153" s="354"/>
-      <c r="P153" s="354"/>
-      <c r="Q153" s="354"/>
-      <c r="R153" s="354"/>
-      <c r="S153" s="354"/>
-      <c r="T153" s="354"/>
-      <c r="U153" s="354"/>
-      <c r="V153" s="354"/>
-      <c r="W153" s="354"/>
-      <c r="X153" s="354"/>
-      <c r="Y153" s="354"/>
-      <c r="Z153" s="354"/>
-      <c r="AA153" s="359" t="s">
+      <c r="L153" s="347"/>
+      <c r="M153" s="347"/>
+      <c r="N153" s="347"/>
+      <c r="O153" s="347"/>
+      <c r="P153" s="347"/>
+      <c r="Q153" s="347"/>
+      <c r="R153" s="347"/>
+      <c r="S153" s="347"/>
+      <c r="T153" s="347"/>
+      <c r="U153" s="347"/>
+      <c r="V153" s="347"/>
+      <c r="W153" s="347"/>
+      <c r="X153" s="347"/>
+      <c r="Y153" s="347"/>
+      <c r="Z153" s="347"/>
+      <c r="AA153" s="322" t="s">
         <v>75</v>
       </c>
-      <c r="AB153" s="360"/>
-      <c r="AC153" s="360"/>
-      <c r="AD153" s="360"/>
-      <c r="AE153" s="360"/>
-      <c r="AF153" s="360"/>
-      <c r="AG153" s="360"/>
-      <c r="AH153" s="360"/>
+      <c r="AB153" s="323"/>
+      <c r="AC153" s="323"/>
+      <c r="AD153" s="323"/>
+      <c r="AE153" s="323"/>
+      <c r="AF153" s="323"/>
+      <c r="AG153" s="323"/>
+      <c r="AH153" s="323"/>
     </row>
     <row r="154" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D154" s="369" t="s">
+      <c r="D154" s="333" t="s">
         <v>320</v>
       </c>
-      <c r="E154" s="281"/>
-      <c r="F154" s="281"/>
-      <c r="G154" s="281"/>
-      <c r="H154" s="281"/>
-      <c r="I154" s="281"/>
-      <c r="J154" s="282"/>
-      <c r="K154" s="361" t="s">
+      <c r="E154" s="255"/>
+      <c r="F154" s="255"/>
+      <c r="G154" s="255"/>
+      <c r="H154" s="255"/>
+      <c r="I154" s="255"/>
+      <c r="J154" s="256"/>
+      <c r="K154" s="335" t="s">
         <v>322</v>
       </c>
-      <c r="L154" s="362"/>
-      <c r="M154" s="362"/>
-      <c r="N154" s="362"/>
-      <c r="O154" s="362"/>
-      <c r="P154" s="362"/>
-      <c r="Q154" s="362"/>
-      <c r="R154" s="362"/>
-      <c r="S154" s="362"/>
-      <c r="T154" s="362"/>
-      <c r="U154" s="362"/>
-      <c r="V154" s="362"/>
-      <c r="W154" s="362"/>
-      <c r="X154" s="362"/>
-      <c r="Y154" s="362"/>
-      <c r="Z154" s="348"/>
-      <c r="AA154" s="361" t="s">
+      <c r="L154" s="336"/>
+      <c r="M154" s="336"/>
+      <c r="N154" s="336"/>
+      <c r="O154" s="336"/>
+      <c r="P154" s="336"/>
+      <c r="Q154" s="336"/>
+      <c r="R154" s="336"/>
+      <c r="S154" s="336"/>
+      <c r="T154" s="336"/>
+      <c r="U154" s="336"/>
+      <c r="V154" s="336"/>
+      <c r="W154" s="336"/>
+      <c r="X154" s="336"/>
+      <c r="Y154" s="336"/>
+      <c r="Z154" s="337"/>
+      <c r="AA154" s="335" t="s">
         <v>321</v>
       </c>
-      <c r="AB154" s="362"/>
-      <c r="AC154" s="362"/>
-      <c r="AD154" s="362"/>
-      <c r="AE154" s="362"/>
-      <c r="AF154" s="362"/>
-      <c r="AG154" s="362"/>
-      <c r="AH154" s="348"/>
+      <c r="AB154" s="336"/>
+      <c r="AC154" s="336"/>
+      <c r="AD154" s="336"/>
+      <c r="AE154" s="336"/>
+      <c r="AF154" s="336"/>
+      <c r="AG154" s="336"/>
+      <c r="AH154" s="337"/>
     </row>
     <row r="155" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D155" s="367"/>
-      <c r="E155" s="345" t="s">
+      <c r="D155" s="331"/>
+      <c r="E155" s="334" t="s">
         <v>324</v>
       </c>
-      <c r="F155" s="284"/>
-      <c r="G155" s="284"/>
-      <c r="H155" s="284"/>
-      <c r="I155" s="284"/>
-      <c r="J155" s="285"/>
-      <c r="K155" s="354" t="s">
+      <c r="F155" s="288"/>
+      <c r="G155" s="288"/>
+      <c r="H155" s="288"/>
+      <c r="I155" s="288"/>
+      <c r="J155" s="289"/>
+      <c r="K155" s="347" t="s">
         <v>163</v>
       </c>
-      <c r="L155" s="354"/>
-      <c r="M155" s="354"/>
-      <c r="N155" s="354"/>
-      <c r="O155" s="354"/>
-      <c r="P155" s="354"/>
-      <c r="Q155" s="354"/>
-      <c r="R155" s="354"/>
-      <c r="S155" s="354"/>
-      <c r="T155" s="354"/>
-      <c r="U155" s="354"/>
-      <c r="V155" s="354"/>
-      <c r="W155" s="354"/>
-      <c r="X155" s="354"/>
-      <c r="Y155" s="354"/>
-      <c r="Z155" s="354"/>
-      <c r="AA155" s="353" t="s">
+      <c r="L155" s="347"/>
+      <c r="M155" s="347"/>
+      <c r="N155" s="347"/>
+      <c r="O155" s="347"/>
+      <c r="P155" s="347"/>
+      <c r="Q155" s="347"/>
+      <c r="R155" s="347"/>
+      <c r="S155" s="347"/>
+      <c r="T155" s="347"/>
+      <c r="U155" s="347"/>
+      <c r="V155" s="347"/>
+      <c r="W155" s="347"/>
+      <c r="X155" s="347"/>
+      <c r="Y155" s="347"/>
+      <c r="Z155" s="347"/>
+      <c r="AA155" s="346" t="s">
         <v>326</v>
       </c>
-      <c r="AB155" s="354"/>
-      <c r="AC155" s="354"/>
-      <c r="AD155" s="354"/>
-      <c r="AE155" s="354"/>
-      <c r="AF155" s="354"/>
-      <c r="AG155" s="354"/>
-      <c r="AH155" s="354"/>
+      <c r="AB155" s="347"/>
+      <c r="AC155" s="347"/>
+      <c r="AD155" s="347"/>
+      <c r="AE155" s="347"/>
+      <c r="AF155" s="347"/>
+      <c r="AG155" s="347"/>
+      <c r="AH155" s="347"/>
     </row>
     <row r="156" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D156" s="367"/>
-      <c r="E156" s="345"/>
-      <c r="F156" s="284"/>
-      <c r="G156" s="284"/>
-      <c r="H156" s="284"/>
-      <c r="I156" s="284"/>
-      <c r="J156" s="285"/>
-      <c r="K156" s="354" t="s">
+      <c r="D156" s="331"/>
+      <c r="E156" s="334"/>
+      <c r="F156" s="288"/>
+      <c r="G156" s="288"/>
+      <c r="H156" s="288"/>
+      <c r="I156" s="288"/>
+      <c r="J156" s="289"/>
+      <c r="K156" s="347" t="s">
         <v>70</v>
       </c>
-      <c r="L156" s="354"/>
-      <c r="M156" s="354"/>
-      <c r="N156" s="354"/>
-      <c r="O156" s="354"/>
-      <c r="P156" s="354"/>
-      <c r="Q156" s="354"/>
-      <c r="R156" s="354"/>
-      <c r="S156" s="354"/>
-      <c r="T156" s="354"/>
-      <c r="U156" s="354"/>
-      <c r="V156" s="354"/>
-      <c r="W156" s="354"/>
-      <c r="X156" s="354"/>
-      <c r="Y156" s="354"/>
-      <c r="Z156" s="354"/>
-      <c r="AA156" s="359" t="s">
+      <c r="L156" s="347"/>
+      <c r="M156" s="347"/>
+      <c r="N156" s="347"/>
+      <c r="O156" s="347"/>
+      <c r="P156" s="347"/>
+      <c r="Q156" s="347"/>
+      <c r="R156" s="347"/>
+      <c r="S156" s="347"/>
+      <c r="T156" s="347"/>
+      <c r="U156" s="347"/>
+      <c r="V156" s="347"/>
+      <c r="W156" s="347"/>
+      <c r="X156" s="347"/>
+      <c r="Y156" s="347"/>
+      <c r="Z156" s="347"/>
+      <c r="AA156" s="322" t="s">
         <v>283</v>
       </c>
-      <c r="AB156" s="354"/>
-      <c r="AC156" s="354"/>
-      <c r="AD156" s="354"/>
-      <c r="AE156" s="354"/>
-      <c r="AF156" s="354"/>
-      <c r="AG156" s="354"/>
-      <c r="AH156" s="354"/>
+      <c r="AB156" s="347"/>
+      <c r="AC156" s="347"/>
+      <c r="AD156" s="347"/>
+      <c r="AE156" s="347"/>
+      <c r="AF156" s="347"/>
+      <c r="AG156" s="347"/>
+      <c r="AH156" s="347"/>
     </row>
     <row r="157" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D157" s="367"/>
-      <c r="E157" s="345"/>
-      <c r="F157" s="284"/>
-      <c r="G157" s="284"/>
-      <c r="H157" s="284"/>
-      <c r="I157" s="284"/>
-      <c r="J157" s="285"/>
-      <c r="K157" s="354"/>
-      <c r="L157" s="354"/>
-      <c r="M157" s="354"/>
-      <c r="N157" s="354"/>
-      <c r="O157" s="354"/>
-      <c r="P157" s="354"/>
-      <c r="Q157" s="354"/>
-      <c r="R157" s="354"/>
-      <c r="S157" s="354"/>
-      <c r="T157" s="354"/>
-      <c r="U157" s="354"/>
-      <c r="V157" s="354"/>
-      <c r="W157" s="354"/>
-      <c r="X157" s="354"/>
-      <c r="Y157" s="354"/>
-      <c r="Z157" s="354"/>
-      <c r="AA157" s="354"/>
-      <c r="AB157" s="354"/>
-      <c r="AC157" s="354"/>
-      <c r="AD157" s="354"/>
-      <c r="AE157" s="354"/>
-      <c r="AF157" s="354"/>
-      <c r="AG157" s="354"/>
-      <c r="AH157" s="354"/>
+      <c r="D157" s="331"/>
+      <c r="E157" s="334"/>
+      <c r="F157" s="288"/>
+      <c r="G157" s="288"/>
+      <c r="H157" s="288"/>
+      <c r="I157" s="288"/>
+      <c r="J157" s="289"/>
+      <c r="K157" s="347"/>
+      <c r="L157" s="347"/>
+      <c r="M157" s="347"/>
+      <c r="N157" s="347"/>
+      <c r="O157" s="347"/>
+      <c r="P157" s="347"/>
+      <c r="Q157" s="347"/>
+      <c r="R157" s="347"/>
+      <c r="S157" s="347"/>
+      <c r="T157" s="347"/>
+      <c r="U157" s="347"/>
+      <c r="V157" s="347"/>
+      <c r="W157" s="347"/>
+      <c r="X157" s="347"/>
+      <c r="Y157" s="347"/>
+      <c r="Z157" s="347"/>
+      <c r="AA157" s="347"/>
+      <c r="AB157" s="347"/>
+      <c r="AC157" s="347"/>
+      <c r="AD157" s="347"/>
+      <c r="AE157" s="347"/>
+      <c r="AF157" s="347"/>
+      <c r="AG157" s="347"/>
+      <c r="AH157" s="347"/>
     </row>
     <row r="158" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D158" s="367"/>
-      <c r="E158" s="345"/>
-      <c r="F158" s="284"/>
-      <c r="G158" s="284"/>
-      <c r="H158" s="284"/>
-      <c r="I158" s="284"/>
-      <c r="J158" s="285"/>
-      <c r="K158" s="354"/>
-      <c r="L158" s="354"/>
-      <c r="M158" s="354"/>
-      <c r="N158" s="354"/>
-      <c r="O158" s="354"/>
-      <c r="P158" s="354"/>
-      <c r="Q158" s="354"/>
-      <c r="R158" s="354"/>
-      <c r="S158" s="354"/>
-      <c r="T158" s="354"/>
-      <c r="U158" s="354"/>
-      <c r="V158" s="354"/>
-      <c r="W158" s="354"/>
-      <c r="X158" s="354"/>
-      <c r="Y158" s="354"/>
-      <c r="Z158" s="354"/>
-      <c r="AA158" s="354"/>
-      <c r="AB158" s="354"/>
-      <c r="AC158" s="354"/>
-      <c r="AD158" s="354"/>
-      <c r="AE158" s="354"/>
-      <c r="AF158" s="354"/>
-      <c r="AG158" s="354"/>
-      <c r="AH158" s="354"/>
+      <c r="D158" s="331"/>
+      <c r="E158" s="334"/>
+      <c r="F158" s="288"/>
+      <c r="G158" s="288"/>
+      <c r="H158" s="288"/>
+      <c r="I158" s="288"/>
+      <c r="J158" s="289"/>
+      <c r="K158" s="347"/>
+      <c r="L158" s="347"/>
+      <c r="M158" s="347"/>
+      <c r="N158" s="347"/>
+      <c r="O158" s="347"/>
+      <c r="P158" s="347"/>
+      <c r="Q158" s="347"/>
+      <c r="R158" s="347"/>
+      <c r="S158" s="347"/>
+      <c r="T158" s="347"/>
+      <c r="U158" s="347"/>
+      <c r="V158" s="347"/>
+      <c r="W158" s="347"/>
+      <c r="X158" s="347"/>
+      <c r="Y158" s="347"/>
+      <c r="Z158" s="347"/>
+      <c r="AA158" s="347"/>
+      <c r="AB158" s="347"/>
+      <c r="AC158" s="347"/>
+      <c r="AD158" s="347"/>
+      <c r="AE158" s="347"/>
+      <c r="AF158" s="347"/>
+      <c r="AG158" s="347"/>
+      <c r="AH158" s="347"/>
     </row>
     <row r="159" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D159" s="367"/>
-      <c r="E159" s="345"/>
-      <c r="F159" s="284"/>
-      <c r="G159" s="284"/>
-      <c r="H159" s="284"/>
-      <c r="I159" s="284"/>
-      <c r="J159" s="285"/>
-      <c r="K159" s="354"/>
-      <c r="L159" s="354"/>
-      <c r="M159" s="354"/>
-      <c r="N159" s="354"/>
-      <c r="O159" s="354"/>
-      <c r="P159" s="354"/>
-      <c r="Q159" s="354"/>
-      <c r="R159" s="354"/>
-      <c r="S159" s="354"/>
-      <c r="T159" s="354"/>
-      <c r="U159" s="354"/>
-      <c r="V159" s="354"/>
-      <c r="W159" s="354"/>
-      <c r="X159" s="354"/>
-      <c r="Y159" s="354"/>
-      <c r="Z159" s="354"/>
-      <c r="AA159" s="354"/>
-      <c r="AB159" s="354"/>
-      <c r="AC159" s="354"/>
-      <c r="AD159" s="354"/>
-      <c r="AE159" s="354"/>
-      <c r="AF159" s="354"/>
-      <c r="AG159" s="354"/>
-      <c r="AH159" s="354"/>
+      <c r="D159" s="331"/>
+      <c r="E159" s="334"/>
+      <c r="F159" s="288"/>
+      <c r="G159" s="288"/>
+      <c r="H159" s="288"/>
+      <c r="I159" s="288"/>
+      <c r="J159" s="289"/>
+      <c r="K159" s="347"/>
+      <c r="L159" s="347"/>
+      <c r="M159" s="347"/>
+      <c r="N159" s="347"/>
+      <c r="O159" s="347"/>
+      <c r="P159" s="347"/>
+      <c r="Q159" s="347"/>
+      <c r="R159" s="347"/>
+      <c r="S159" s="347"/>
+      <c r="T159" s="347"/>
+      <c r="U159" s="347"/>
+      <c r="V159" s="347"/>
+      <c r="W159" s="347"/>
+      <c r="X159" s="347"/>
+      <c r="Y159" s="347"/>
+      <c r="Z159" s="347"/>
+      <c r="AA159" s="347"/>
+      <c r="AB159" s="347"/>
+      <c r="AC159" s="347"/>
+      <c r="AD159" s="347"/>
+      <c r="AE159" s="347"/>
+      <c r="AF159" s="347"/>
+      <c r="AG159" s="347"/>
+      <c r="AH159" s="347"/>
     </row>
     <row r="160" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D160" s="367"/>
-      <c r="E160" s="345"/>
-      <c r="F160" s="284"/>
-      <c r="G160" s="284"/>
-      <c r="H160" s="284"/>
-      <c r="I160" s="284"/>
-      <c r="J160" s="285"/>
-      <c r="K160" s="354"/>
-      <c r="L160" s="354"/>
-      <c r="M160" s="354"/>
-      <c r="N160" s="354"/>
-      <c r="O160" s="354"/>
-      <c r="P160" s="354"/>
-      <c r="Q160" s="354"/>
-      <c r="R160" s="354"/>
-      <c r="S160" s="354"/>
-      <c r="T160" s="354"/>
-      <c r="U160" s="354"/>
-      <c r="V160" s="354"/>
-      <c r="W160" s="354"/>
-      <c r="X160" s="354"/>
-      <c r="Y160" s="354"/>
-      <c r="Z160" s="354"/>
-      <c r="AA160" s="354"/>
-      <c r="AB160" s="354"/>
-      <c r="AC160" s="354"/>
-      <c r="AD160" s="354"/>
-      <c r="AE160" s="354"/>
-      <c r="AF160" s="354"/>
-      <c r="AG160" s="354"/>
-      <c r="AH160" s="354"/>
+      <c r="D160" s="331"/>
+      <c r="E160" s="334"/>
+      <c r="F160" s="288"/>
+      <c r="G160" s="288"/>
+      <c r="H160" s="288"/>
+      <c r="I160" s="288"/>
+      <c r="J160" s="289"/>
+      <c r="K160" s="347"/>
+      <c r="L160" s="347"/>
+      <c r="M160" s="347"/>
+      <c r="N160" s="347"/>
+      <c r="O160" s="347"/>
+      <c r="P160" s="347"/>
+      <c r="Q160" s="347"/>
+      <c r="R160" s="347"/>
+      <c r="S160" s="347"/>
+      <c r="T160" s="347"/>
+      <c r="U160" s="347"/>
+      <c r="V160" s="347"/>
+      <c r="W160" s="347"/>
+      <c r="X160" s="347"/>
+      <c r="Y160" s="347"/>
+      <c r="Z160" s="347"/>
+      <c r="AA160" s="347"/>
+      <c r="AB160" s="347"/>
+      <c r="AC160" s="347"/>
+      <c r="AD160" s="347"/>
+      <c r="AE160" s="347"/>
+      <c r="AF160" s="347"/>
+      <c r="AG160" s="347"/>
+      <c r="AH160" s="347"/>
     </row>
     <row r="161" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D161" s="367"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="284"/>
-      <c r="G161" s="284"/>
-      <c r="H161" s="284"/>
-      <c r="I161" s="284"/>
-      <c r="J161" s="285"/>
-      <c r="K161" s="353" t="s">
+      <c r="D161" s="331"/>
+      <c r="E161" s="334"/>
+      <c r="F161" s="288"/>
+      <c r="G161" s="288"/>
+      <c r="H161" s="288"/>
+      <c r="I161" s="288"/>
+      <c r="J161" s="289"/>
+      <c r="K161" s="346" t="s">
         <v>629</v>
       </c>
-      <c r="L161" s="354"/>
-      <c r="M161" s="354"/>
-      <c r="N161" s="354"/>
-      <c r="O161" s="354"/>
-      <c r="P161" s="354"/>
-      <c r="Q161" s="354"/>
-      <c r="R161" s="354"/>
-      <c r="S161" s="354"/>
-      <c r="T161" s="354"/>
-      <c r="U161" s="354"/>
-      <c r="V161" s="354"/>
-      <c r="W161" s="354"/>
-      <c r="X161" s="354"/>
-      <c r="Y161" s="354"/>
-      <c r="Z161" s="354"/>
-      <c r="AA161" s="359" t="s">
+      <c r="L161" s="347"/>
+      <c r="M161" s="347"/>
+      <c r="N161" s="347"/>
+      <c r="O161" s="347"/>
+      <c r="P161" s="347"/>
+      <c r="Q161" s="347"/>
+      <c r="R161" s="347"/>
+      <c r="S161" s="347"/>
+      <c r="T161" s="347"/>
+      <c r="U161" s="347"/>
+      <c r="V161" s="347"/>
+      <c r="W161" s="347"/>
+      <c r="X161" s="347"/>
+      <c r="Y161" s="347"/>
+      <c r="Z161" s="347"/>
+      <c r="AA161" s="322" t="s">
         <v>75</v>
       </c>
-      <c r="AB161" s="360"/>
-      <c r="AC161" s="360"/>
-      <c r="AD161" s="360"/>
-      <c r="AE161" s="360"/>
-      <c r="AF161" s="360"/>
-      <c r="AG161" s="360"/>
-      <c r="AH161" s="360"/>
+      <c r="AB161" s="323"/>
+      <c r="AC161" s="323"/>
+      <c r="AD161" s="323"/>
+      <c r="AE161" s="323"/>
+      <c r="AF161" s="323"/>
+      <c r="AG161" s="323"/>
+      <c r="AH161" s="323"/>
     </row>
     <row r="162" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D162" s="367"/>
-      <c r="E162" s="345" t="s">
+      <c r="D162" s="331"/>
+      <c r="E162" s="334" t="s">
         <v>323</v>
       </c>
-      <c r="F162" s="284"/>
-      <c r="G162" s="284"/>
-      <c r="H162" s="284"/>
-      <c r="I162" s="284"/>
-      <c r="J162" s="285"/>
-      <c r="K162" s="345" t="s">
+      <c r="F162" s="288"/>
+      <c r="G162" s="288"/>
+      <c r="H162" s="288"/>
+      <c r="I162" s="288"/>
+      <c r="J162" s="289"/>
+      <c r="K162" s="334" t="s">
         <v>628</v>
       </c>
-      <c r="L162" s="284"/>
-      <c r="M162" s="284"/>
-      <c r="N162" s="284"/>
-      <c r="O162" s="284"/>
-      <c r="P162" s="284"/>
-      <c r="Q162" s="284"/>
-      <c r="R162" s="284"/>
-      <c r="S162" s="284"/>
-      <c r="T162" s="284"/>
-      <c r="U162" s="284"/>
-      <c r="V162" s="284"/>
-      <c r="W162" s="284"/>
-      <c r="X162" s="284"/>
-      <c r="Y162" s="284"/>
-      <c r="Z162" s="285"/>
-      <c r="AA162" s="360" t="s">
+      <c r="L162" s="288"/>
+      <c r="M162" s="288"/>
+      <c r="N162" s="288"/>
+      <c r="O162" s="288"/>
+      <c r="P162" s="288"/>
+      <c r="Q162" s="288"/>
+      <c r="R162" s="288"/>
+      <c r="S162" s="288"/>
+      <c r="T162" s="288"/>
+      <c r="U162" s="288"/>
+      <c r="V162" s="288"/>
+      <c r="W162" s="288"/>
+      <c r="X162" s="288"/>
+      <c r="Y162" s="288"/>
+      <c r="Z162" s="289"/>
+      <c r="AA162" s="323" t="s">
         <v>71</v>
       </c>
-      <c r="AB162" s="360"/>
-      <c r="AC162" s="360"/>
-      <c r="AD162" s="360"/>
-      <c r="AE162" s="360"/>
-      <c r="AF162" s="360"/>
-      <c r="AG162" s="360"/>
-      <c r="AH162" s="360"/>
+      <c r="AB162" s="323"/>
+      <c r="AC162" s="323"/>
+      <c r="AD162" s="323"/>
+      <c r="AE162" s="323"/>
+      <c r="AF162" s="323"/>
+      <c r="AG162" s="323"/>
+      <c r="AH162" s="323"/>
     </row>
     <row r="163" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D163" s="368"/>
-      <c r="E163" s="345"/>
-      <c r="F163" s="284"/>
-      <c r="G163" s="284"/>
-      <c r="H163" s="284"/>
-      <c r="I163" s="284"/>
-      <c r="J163" s="285"/>
-      <c r="K163" s="360"/>
-      <c r="L163" s="360"/>
-      <c r="M163" s="360"/>
-      <c r="N163" s="360"/>
-      <c r="O163" s="360"/>
-      <c r="P163" s="360"/>
-      <c r="Q163" s="360"/>
-      <c r="R163" s="360"/>
-      <c r="S163" s="360"/>
-      <c r="T163" s="360"/>
-      <c r="U163" s="360"/>
-      <c r="V163" s="360"/>
-      <c r="W163" s="360"/>
-      <c r="X163" s="360"/>
-      <c r="Y163" s="360"/>
-      <c r="Z163" s="360"/>
-      <c r="AA163" s="360"/>
-      <c r="AB163" s="360"/>
-      <c r="AC163" s="360"/>
-      <c r="AD163" s="360"/>
-      <c r="AE163" s="360"/>
-      <c r="AF163" s="360"/>
-      <c r="AG163" s="360"/>
-      <c r="AH163" s="360"/>
+      <c r="D163" s="332"/>
+      <c r="E163" s="334"/>
+      <c r="F163" s="288"/>
+      <c r="G163" s="288"/>
+      <c r="H163" s="288"/>
+      <c r="I163" s="288"/>
+      <c r="J163" s="289"/>
+      <c r="K163" s="323"/>
+      <c r="L163" s="323"/>
+      <c r="M163" s="323"/>
+      <c r="N163" s="323"/>
+      <c r="O163" s="323"/>
+      <c r="P163" s="323"/>
+      <c r="Q163" s="323"/>
+      <c r="R163" s="323"/>
+      <c r="S163" s="323"/>
+      <c r="T163" s="323"/>
+      <c r="U163" s="323"/>
+      <c r="V163" s="323"/>
+      <c r="W163" s="323"/>
+      <c r="X163" s="323"/>
+      <c r="Y163" s="323"/>
+      <c r="Z163" s="323"/>
+      <c r="AA163" s="323"/>
+      <c r="AB163" s="323"/>
+      <c r="AC163" s="323"/>
+      <c r="AD163" s="323"/>
+      <c r="AE163" s="323"/>
+      <c r="AF163" s="323"/>
+      <c r="AG163" s="323"/>
+      <c r="AH163" s="323"/>
     </row>
     <row r="164" spans="3:34" x14ac:dyDescent="0.15">
       <c r="D164" s="55"/>
@@ -42877,815 +42878,815 @@
     </row>
     <row r="173" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="174" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F174" s="274" t="s">
+      <c r="F174" s="248" t="s">
         <v>642</v>
       </c>
-      <c r="G174" s="339"/>
-      <c r="H174" s="339"/>
-      <c r="I174" s="339"/>
-      <c r="J174" s="340"/>
-      <c r="K174" s="351" t="s">
+      <c r="G174" s="327"/>
+      <c r="H174" s="327"/>
+      <c r="I174" s="327"/>
+      <c r="J174" s="328"/>
+      <c r="K174" s="329" t="s">
         <v>30</v>
       </c>
-      <c r="L174" s="352"/>
-      <c r="M174" s="351" t="s">
+      <c r="L174" s="330"/>
+      <c r="M174" s="329" t="s">
         <v>45</v>
       </c>
-      <c r="N174" s="352"/>
-      <c r="O174" s="366" t="s">
+      <c r="N174" s="330"/>
+      <c r="O174" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="P174" s="339"/>
-      <c r="Q174" s="339"/>
-      <c r="R174" s="339"/>
-      <c r="S174" s="339"/>
-      <c r="T174" s="339"/>
-      <c r="U174" s="339"/>
-      <c r="V174" s="339"/>
-      <c r="W174" s="339"/>
-      <c r="X174" s="339"/>
-      <c r="Y174" s="339"/>
-      <c r="Z174" s="339"/>
-      <c r="AA174" s="339"/>
-      <c r="AB174" s="339"/>
-      <c r="AC174" s="339"/>
-      <c r="AD174" s="339"/>
-      <c r="AE174" s="339"/>
-      <c r="AF174" s="339"/>
-      <c r="AG174" s="339"/>
-      <c r="AH174" s="340"/>
+      <c r="P174" s="327"/>
+      <c r="Q174" s="327"/>
+      <c r="R174" s="327"/>
+      <c r="S174" s="327"/>
+      <c r="T174" s="327"/>
+      <c r="U174" s="327"/>
+      <c r="V174" s="327"/>
+      <c r="W174" s="327"/>
+      <c r="X174" s="327"/>
+      <c r="Y174" s="327"/>
+      <c r="Z174" s="327"/>
+      <c r="AA174" s="327"/>
+      <c r="AB174" s="327"/>
+      <c r="AC174" s="327"/>
+      <c r="AD174" s="327"/>
+      <c r="AE174" s="327"/>
+      <c r="AF174" s="327"/>
+      <c r="AG174" s="327"/>
+      <c r="AH174" s="328"/>
     </row>
     <row r="175" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F175" s="308" t="s">
+      <c r="F175" s="307" t="s">
         <v>285</v>
       </c>
-      <c r="G175" s="278"/>
-      <c r="H175" s="278"/>
-      <c r="I175" s="278"/>
-      <c r="J175" s="279"/>
-      <c r="K175" s="335" t="s">
+      <c r="G175" s="252"/>
+      <c r="H175" s="252"/>
+      <c r="I175" s="252"/>
+      <c r="J175" s="253"/>
+      <c r="K175" s="340" t="s">
         <v>32</v>
       </c>
-      <c r="L175" s="288"/>
-      <c r="M175" s="361" t="s">
+      <c r="L175" s="292"/>
+      <c r="M175" s="335" t="s">
         <v>302</v>
       </c>
-      <c r="N175" s="348"/>
-      <c r="O175" s="280" t="s">
+      <c r="N175" s="337"/>
+      <c r="O175" s="254" t="s">
         <v>307</v>
       </c>
-      <c r="P175" s="363"/>
-      <c r="Q175" s="363"/>
-      <c r="R175" s="363"/>
-      <c r="S175" s="363"/>
-      <c r="T175" s="363"/>
-      <c r="U175" s="363"/>
-      <c r="V175" s="363"/>
-      <c r="W175" s="363"/>
-      <c r="X175" s="363"/>
-      <c r="Y175" s="363"/>
-      <c r="Z175" s="363"/>
-      <c r="AA175" s="363"/>
-      <c r="AB175" s="363"/>
-      <c r="AC175" s="363"/>
-      <c r="AD175" s="363"/>
-      <c r="AE175" s="363"/>
-      <c r="AF175" s="363"/>
-      <c r="AG175" s="363"/>
-      <c r="AH175" s="364"/>
+      <c r="P175" s="342"/>
+      <c r="Q175" s="342"/>
+      <c r="R175" s="342"/>
+      <c r="S175" s="342"/>
+      <c r="T175" s="342"/>
+      <c r="U175" s="342"/>
+      <c r="V175" s="342"/>
+      <c r="W175" s="342"/>
+      <c r="X175" s="342"/>
+      <c r="Y175" s="342"/>
+      <c r="Z175" s="342"/>
+      <c r="AA175" s="342"/>
+      <c r="AB175" s="342"/>
+      <c r="AC175" s="342"/>
+      <c r="AD175" s="342"/>
+      <c r="AE175" s="342"/>
+      <c r="AF175" s="342"/>
+      <c r="AG175" s="342"/>
+      <c r="AH175" s="343"/>
     </row>
     <row r="176" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F176" s="286" t="s">
+      <c r="F176" s="290" t="s">
         <v>303</v>
       </c>
-      <c r="G176" s="287"/>
-      <c r="H176" s="287"/>
-      <c r="I176" s="287"/>
-      <c r="J176" s="288"/>
-      <c r="K176" s="335" t="s">
+      <c r="G176" s="291"/>
+      <c r="H176" s="291"/>
+      <c r="I176" s="291"/>
+      <c r="J176" s="292"/>
+      <c r="K176" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L176" s="288"/>
-      <c r="M176" s="315" t="s">
+      <c r="L176" s="292"/>
+      <c r="M176" s="310" t="s">
         <v>339</v>
       </c>
-      <c r="N176" s="317"/>
-      <c r="O176" s="286" t="s">
+      <c r="N176" s="312"/>
+      <c r="O176" s="290" t="s">
         <v>306</v>
       </c>
-      <c r="P176" s="287"/>
-      <c r="Q176" s="287"/>
-      <c r="R176" s="287"/>
-      <c r="S176" s="287"/>
-      <c r="T176" s="287"/>
-      <c r="U176" s="287"/>
-      <c r="V176" s="287"/>
-      <c r="W176" s="287"/>
-      <c r="X176" s="287"/>
-      <c r="Y176" s="287"/>
-      <c r="Z176" s="287"/>
-      <c r="AA176" s="287"/>
-      <c r="AB176" s="287"/>
-      <c r="AC176" s="287"/>
-      <c r="AD176" s="287"/>
-      <c r="AE176" s="287"/>
-      <c r="AF176" s="287"/>
-      <c r="AG176" s="287"/>
-      <c r="AH176" s="288"/>
+      <c r="P176" s="291"/>
+      <c r="Q176" s="291"/>
+      <c r="R176" s="291"/>
+      <c r="S176" s="291"/>
+      <c r="T176" s="291"/>
+      <c r="U176" s="291"/>
+      <c r="V176" s="291"/>
+      <c r="W176" s="291"/>
+      <c r="X176" s="291"/>
+      <c r="Y176" s="291"/>
+      <c r="Z176" s="291"/>
+      <c r="AA176" s="291"/>
+      <c r="AB176" s="291"/>
+      <c r="AC176" s="291"/>
+      <c r="AD176" s="291"/>
+      <c r="AE176" s="291"/>
+      <c r="AF176" s="291"/>
+      <c r="AG176" s="291"/>
+      <c r="AH176" s="292"/>
     </row>
     <row r="177" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F177" s="295"/>
-      <c r="G177" s="290"/>
-      <c r="H177" s="290"/>
-      <c r="I177" s="290"/>
-      <c r="J177" s="291"/>
-      <c r="K177" s="289"/>
-      <c r="L177" s="291"/>
-      <c r="M177" s="332"/>
-      <c r="N177" s="342"/>
-      <c r="O177" s="295"/>
-      <c r="P177" s="290"/>
-      <c r="Q177" s="290"/>
-      <c r="R177" s="290"/>
-      <c r="S177" s="290"/>
-      <c r="T177" s="290"/>
-      <c r="U177" s="290"/>
-      <c r="V177" s="290"/>
-      <c r="W177" s="290"/>
-      <c r="X177" s="290"/>
-      <c r="Y177" s="290"/>
-      <c r="Z177" s="290"/>
-      <c r="AA177" s="290"/>
-      <c r="AB177" s="290"/>
-      <c r="AC177" s="290"/>
-      <c r="AD177" s="290"/>
-      <c r="AE177" s="290"/>
-      <c r="AF177" s="290"/>
-      <c r="AG177" s="290"/>
-      <c r="AH177" s="291"/>
+      <c r="F177" s="299"/>
+      <c r="G177" s="294"/>
+      <c r="H177" s="294"/>
+      <c r="I177" s="294"/>
+      <c r="J177" s="295"/>
+      <c r="K177" s="293"/>
+      <c r="L177" s="295"/>
+      <c r="M177" s="338"/>
+      <c r="N177" s="339"/>
+      <c r="O177" s="299"/>
+      <c r="P177" s="294"/>
+      <c r="Q177" s="294"/>
+      <c r="R177" s="294"/>
+      <c r="S177" s="294"/>
+      <c r="T177" s="294"/>
+      <c r="U177" s="294"/>
+      <c r="V177" s="294"/>
+      <c r="W177" s="294"/>
+      <c r="X177" s="294"/>
+      <c r="Y177" s="294"/>
+      <c r="Z177" s="294"/>
+      <c r="AA177" s="294"/>
+      <c r="AB177" s="294"/>
+      <c r="AC177" s="294"/>
+      <c r="AD177" s="294"/>
+      <c r="AE177" s="294"/>
+      <c r="AF177" s="294"/>
+      <c r="AG177" s="294"/>
+      <c r="AH177" s="295"/>
     </row>
     <row r="178" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F178" s="295"/>
-      <c r="G178" s="290"/>
-      <c r="H178" s="290"/>
-      <c r="I178" s="290"/>
-      <c r="J178" s="291"/>
-      <c r="K178" s="289"/>
-      <c r="L178" s="291"/>
-      <c r="M178" s="332"/>
-      <c r="N178" s="342"/>
-      <c r="O178" s="295"/>
-      <c r="P178" s="290"/>
-      <c r="Q178" s="290"/>
-      <c r="R178" s="290"/>
-      <c r="S178" s="290"/>
-      <c r="T178" s="290"/>
-      <c r="U178" s="290"/>
-      <c r="V178" s="290"/>
-      <c r="W178" s="290"/>
-      <c r="X178" s="290"/>
-      <c r="Y178" s="290"/>
-      <c r="Z178" s="290"/>
-      <c r="AA178" s="290"/>
-      <c r="AB178" s="290"/>
-      <c r="AC178" s="290"/>
-      <c r="AD178" s="290"/>
-      <c r="AE178" s="290"/>
-      <c r="AF178" s="290"/>
-      <c r="AG178" s="290"/>
-      <c r="AH178" s="291"/>
+      <c r="F178" s="299"/>
+      <c r="G178" s="294"/>
+      <c r="H178" s="294"/>
+      <c r="I178" s="294"/>
+      <c r="J178" s="295"/>
+      <c r="K178" s="293"/>
+      <c r="L178" s="295"/>
+      <c r="M178" s="338"/>
+      <c r="N178" s="339"/>
+      <c r="O178" s="299"/>
+      <c r="P178" s="294"/>
+      <c r="Q178" s="294"/>
+      <c r="R178" s="294"/>
+      <c r="S178" s="294"/>
+      <c r="T178" s="294"/>
+      <c r="U178" s="294"/>
+      <c r="V178" s="294"/>
+      <c r="W178" s="294"/>
+      <c r="X178" s="294"/>
+      <c r="Y178" s="294"/>
+      <c r="Z178" s="294"/>
+      <c r="AA178" s="294"/>
+      <c r="AB178" s="294"/>
+      <c r="AC178" s="294"/>
+      <c r="AD178" s="294"/>
+      <c r="AE178" s="294"/>
+      <c r="AF178" s="294"/>
+      <c r="AG178" s="294"/>
+      <c r="AH178" s="295"/>
     </row>
     <row r="179" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F179" s="292"/>
-      <c r="G179" s="293"/>
-      <c r="H179" s="293"/>
-      <c r="I179" s="293"/>
-      <c r="J179" s="294"/>
-      <c r="K179" s="292"/>
-      <c r="L179" s="294"/>
-      <c r="M179" s="318"/>
-      <c r="N179" s="320"/>
-      <c r="O179" s="292"/>
-      <c r="P179" s="293"/>
-      <c r="Q179" s="293"/>
-      <c r="R179" s="293"/>
-      <c r="S179" s="293"/>
-      <c r="T179" s="293"/>
-      <c r="U179" s="293"/>
-      <c r="V179" s="293"/>
-      <c r="W179" s="293"/>
-      <c r="X179" s="293"/>
-      <c r="Y179" s="293"/>
-      <c r="Z179" s="293"/>
-      <c r="AA179" s="293"/>
-      <c r="AB179" s="293"/>
-      <c r="AC179" s="293"/>
-      <c r="AD179" s="293"/>
-      <c r="AE179" s="293"/>
-      <c r="AF179" s="293"/>
-      <c r="AG179" s="293"/>
-      <c r="AH179" s="294"/>
+      <c r="F179" s="296"/>
+      <c r="G179" s="297"/>
+      <c r="H179" s="297"/>
+      <c r="I179" s="297"/>
+      <c r="J179" s="298"/>
+      <c r="K179" s="296"/>
+      <c r="L179" s="298"/>
+      <c r="M179" s="313"/>
+      <c r="N179" s="315"/>
+      <c r="O179" s="296"/>
+      <c r="P179" s="297"/>
+      <c r="Q179" s="297"/>
+      <c r="R179" s="297"/>
+      <c r="S179" s="297"/>
+      <c r="T179" s="297"/>
+      <c r="U179" s="297"/>
+      <c r="V179" s="297"/>
+      <c r="W179" s="297"/>
+      <c r="X179" s="297"/>
+      <c r="Y179" s="297"/>
+      <c r="Z179" s="297"/>
+      <c r="AA179" s="297"/>
+      <c r="AB179" s="297"/>
+      <c r="AC179" s="297"/>
+      <c r="AD179" s="297"/>
+      <c r="AE179" s="297"/>
+      <c r="AF179" s="297"/>
+      <c r="AG179" s="297"/>
+      <c r="AH179" s="298"/>
     </row>
     <row r="180" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F180" s="335" t="s">
+      <c r="F180" s="340" t="s">
         <v>47</v>
       </c>
-      <c r="G180" s="287"/>
-      <c r="H180" s="287"/>
-      <c r="I180" s="287"/>
-      <c r="J180" s="288"/>
-      <c r="K180" s="335" t="s">
+      <c r="G180" s="291"/>
+      <c r="H180" s="291"/>
+      <c r="I180" s="291"/>
+      <c r="J180" s="292"/>
+      <c r="K180" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L180" s="288"/>
-      <c r="M180" s="335" t="s">
+      <c r="L180" s="292"/>
+      <c r="M180" s="340" t="s">
         <v>48</v>
       </c>
-      <c r="N180" s="317"/>
-      <c r="O180" s="315" t="s">
+      <c r="N180" s="312"/>
+      <c r="O180" s="310" t="s">
         <v>310</v>
       </c>
-      <c r="P180" s="316"/>
-      <c r="Q180" s="316"/>
-      <c r="R180" s="316"/>
-      <c r="S180" s="316"/>
-      <c r="T180" s="316"/>
-      <c r="U180" s="316"/>
-      <c r="V180" s="316"/>
-      <c r="W180" s="316"/>
-      <c r="X180" s="316"/>
-      <c r="Y180" s="316"/>
-      <c r="Z180" s="316"/>
-      <c r="AA180" s="316"/>
-      <c r="AB180" s="316"/>
-      <c r="AC180" s="316"/>
-      <c r="AD180" s="316"/>
-      <c r="AE180" s="316"/>
-      <c r="AF180" s="316"/>
-      <c r="AG180" s="316"/>
-      <c r="AH180" s="317"/>
+      <c r="P180" s="311"/>
+      <c r="Q180" s="311"/>
+      <c r="R180" s="311"/>
+      <c r="S180" s="311"/>
+      <c r="T180" s="311"/>
+      <c r="U180" s="311"/>
+      <c r="V180" s="311"/>
+      <c r="W180" s="311"/>
+      <c r="X180" s="311"/>
+      <c r="Y180" s="311"/>
+      <c r="Z180" s="311"/>
+      <c r="AA180" s="311"/>
+      <c r="AB180" s="311"/>
+      <c r="AC180" s="311"/>
+      <c r="AD180" s="311"/>
+      <c r="AE180" s="311"/>
+      <c r="AF180" s="311"/>
+      <c r="AG180" s="311"/>
+      <c r="AH180" s="312"/>
     </row>
     <row r="181" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F181" s="286" t="s">
+      <c r="F181" s="290" t="s">
         <v>286</v>
       </c>
-      <c r="G181" s="287"/>
-      <c r="H181" s="287"/>
-      <c r="I181" s="287"/>
-      <c r="J181" s="288"/>
-      <c r="K181" s="335" t="s">
+      <c r="G181" s="291"/>
+      <c r="H181" s="291"/>
+      <c r="I181" s="291"/>
+      <c r="J181" s="292"/>
+      <c r="K181" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L181" s="288"/>
-      <c r="M181" s="335" t="s">
+      <c r="L181" s="292"/>
+      <c r="M181" s="340" t="s">
         <v>76</v>
       </c>
-      <c r="N181" s="317"/>
-      <c r="O181" s="315" t="s">
+      <c r="N181" s="312"/>
+      <c r="O181" s="310" t="s">
         <v>311</v>
       </c>
-      <c r="P181" s="316"/>
-      <c r="Q181" s="316"/>
-      <c r="R181" s="316"/>
-      <c r="S181" s="316"/>
-      <c r="T181" s="316"/>
-      <c r="U181" s="316"/>
-      <c r="V181" s="316"/>
-      <c r="W181" s="316"/>
-      <c r="X181" s="316"/>
-      <c r="Y181" s="316"/>
-      <c r="Z181" s="316"/>
-      <c r="AA181" s="316"/>
-      <c r="AB181" s="316"/>
-      <c r="AC181" s="316"/>
-      <c r="AD181" s="316"/>
-      <c r="AE181" s="316"/>
-      <c r="AF181" s="316"/>
-      <c r="AG181" s="316"/>
-      <c r="AH181" s="317"/>
+      <c r="P181" s="311"/>
+      <c r="Q181" s="311"/>
+      <c r="R181" s="311"/>
+      <c r="S181" s="311"/>
+      <c r="T181" s="311"/>
+      <c r="U181" s="311"/>
+      <c r="V181" s="311"/>
+      <c r="W181" s="311"/>
+      <c r="X181" s="311"/>
+      <c r="Y181" s="311"/>
+      <c r="Z181" s="311"/>
+      <c r="AA181" s="311"/>
+      <c r="AB181" s="311"/>
+      <c r="AC181" s="311"/>
+      <c r="AD181" s="311"/>
+      <c r="AE181" s="311"/>
+      <c r="AF181" s="311"/>
+      <c r="AG181" s="311"/>
+      <c r="AH181" s="312"/>
     </row>
     <row r="182" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F182" s="295"/>
-      <c r="G182" s="341"/>
-      <c r="H182" s="341"/>
-      <c r="I182" s="341"/>
-      <c r="J182" s="342"/>
-      <c r="K182" s="289"/>
-      <c r="L182" s="291"/>
-      <c r="M182" s="295"/>
-      <c r="N182" s="342"/>
-      <c r="O182" s="295"/>
-      <c r="P182" s="341"/>
-      <c r="Q182" s="341"/>
-      <c r="R182" s="341"/>
-      <c r="S182" s="341"/>
-      <c r="T182" s="341"/>
-      <c r="U182" s="341"/>
-      <c r="V182" s="341"/>
-      <c r="W182" s="341"/>
-      <c r="X182" s="341"/>
-      <c r="Y182" s="341"/>
-      <c r="Z182" s="341"/>
-      <c r="AA182" s="341"/>
-      <c r="AB182" s="341"/>
-      <c r="AC182" s="341"/>
-      <c r="AD182" s="341"/>
-      <c r="AE182" s="341"/>
-      <c r="AF182" s="341"/>
-      <c r="AG182" s="341"/>
-      <c r="AH182" s="342"/>
+      <c r="F182" s="299"/>
+      <c r="G182" s="363"/>
+      <c r="H182" s="363"/>
+      <c r="I182" s="363"/>
+      <c r="J182" s="339"/>
+      <c r="K182" s="293"/>
+      <c r="L182" s="295"/>
+      <c r="M182" s="299"/>
+      <c r="N182" s="339"/>
+      <c r="O182" s="299"/>
+      <c r="P182" s="363"/>
+      <c r="Q182" s="363"/>
+      <c r="R182" s="363"/>
+      <c r="S182" s="363"/>
+      <c r="T182" s="363"/>
+      <c r="U182" s="363"/>
+      <c r="V182" s="363"/>
+      <c r="W182" s="363"/>
+      <c r="X182" s="363"/>
+      <c r="Y182" s="363"/>
+      <c r="Z182" s="363"/>
+      <c r="AA182" s="363"/>
+      <c r="AB182" s="363"/>
+      <c r="AC182" s="363"/>
+      <c r="AD182" s="363"/>
+      <c r="AE182" s="363"/>
+      <c r="AF182" s="363"/>
+      <c r="AG182" s="363"/>
+      <c r="AH182" s="339"/>
     </row>
     <row r="183" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F183" s="295"/>
-      <c r="G183" s="341"/>
-      <c r="H183" s="341"/>
-      <c r="I183" s="341"/>
-      <c r="J183" s="342"/>
-      <c r="K183" s="289"/>
-      <c r="L183" s="291"/>
-      <c r="M183" s="295"/>
-      <c r="N183" s="342"/>
-      <c r="O183" s="295"/>
-      <c r="P183" s="341"/>
-      <c r="Q183" s="341"/>
-      <c r="R183" s="341"/>
-      <c r="S183" s="341"/>
-      <c r="T183" s="341"/>
-      <c r="U183" s="341"/>
-      <c r="V183" s="341"/>
-      <c r="W183" s="341"/>
-      <c r="X183" s="341"/>
-      <c r="Y183" s="341"/>
-      <c r="Z183" s="341"/>
-      <c r="AA183" s="341"/>
-      <c r="AB183" s="341"/>
-      <c r="AC183" s="341"/>
-      <c r="AD183" s="341"/>
-      <c r="AE183" s="341"/>
-      <c r="AF183" s="341"/>
-      <c r="AG183" s="341"/>
-      <c r="AH183" s="342"/>
+      <c r="F183" s="299"/>
+      <c r="G183" s="363"/>
+      <c r="H183" s="363"/>
+      <c r="I183" s="363"/>
+      <c r="J183" s="339"/>
+      <c r="K183" s="293"/>
+      <c r="L183" s="295"/>
+      <c r="M183" s="299"/>
+      <c r="N183" s="339"/>
+      <c r="O183" s="299"/>
+      <c r="P183" s="363"/>
+      <c r="Q183" s="363"/>
+      <c r="R183" s="363"/>
+      <c r="S183" s="363"/>
+      <c r="T183" s="363"/>
+      <c r="U183" s="363"/>
+      <c r="V183" s="363"/>
+      <c r="W183" s="363"/>
+      <c r="X183" s="363"/>
+      <c r="Y183" s="363"/>
+      <c r="Z183" s="363"/>
+      <c r="AA183" s="363"/>
+      <c r="AB183" s="363"/>
+      <c r="AC183" s="363"/>
+      <c r="AD183" s="363"/>
+      <c r="AE183" s="363"/>
+      <c r="AF183" s="363"/>
+      <c r="AG183" s="363"/>
+      <c r="AH183" s="339"/>
     </row>
     <row r="184" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F184" s="318"/>
-      <c r="G184" s="319"/>
-      <c r="H184" s="319"/>
-      <c r="I184" s="319"/>
-      <c r="J184" s="320"/>
-      <c r="K184" s="292"/>
-      <c r="L184" s="294"/>
-      <c r="M184" s="318"/>
-      <c r="N184" s="320"/>
-      <c r="O184" s="318"/>
-      <c r="P184" s="319"/>
-      <c r="Q184" s="319"/>
-      <c r="R184" s="319"/>
-      <c r="S184" s="319"/>
-      <c r="T184" s="319"/>
-      <c r="U184" s="319"/>
-      <c r="V184" s="319"/>
-      <c r="W184" s="319"/>
-      <c r="X184" s="319"/>
-      <c r="Y184" s="319"/>
-      <c r="Z184" s="319"/>
-      <c r="AA184" s="319"/>
-      <c r="AB184" s="319"/>
-      <c r="AC184" s="319"/>
-      <c r="AD184" s="319"/>
-      <c r="AE184" s="319"/>
-      <c r="AF184" s="319"/>
-      <c r="AG184" s="319"/>
-      <c r="AH184" s="320"/>
+      <c r="F184" s="313"/>
+      <c r="G184" s="314"/>
+      <c r="H184" s="314"/>
+      <c r="I184" s="314"/>
+      <c r="J184" s="315"/>
+      <c r="K184" s="296"/>
+      <c r="L184" s="298"/>
+      <c r="M184" s="313"/>
+      <c r="N184" s="315"/>
+      <c r="O184" s="313"/>
+      <c r="P184" s="314"/>
+      <c r="Q184" s="314"/>
+      <c r="R184" s="314"/>
+      <c r="S184" s="314"/>
+      <c r="T184" s="314"/>
+      <c r="U184" s="314"/>
+      <c r="V184" s="314"/>
+      <c r="W184" s="314"/>
+      <c r="X184" s="314"/>
+      <c r="Y184" s="314"/>
+      <c r="Z184" s="314"/>
+      <c r="AA184" s="314"/>
+      <c r="AB184" s="314"/>
+      <c r="AC184" s="314"/>
+      <c r="AD184" s="314"/>
+      <c r="AE184" s="314"/>
+      <c r="AF184" s="314"/>
+      <c r="AG184" s="314"/>
+      <c r="AH184" s="315"/>
     </row>
     <row r="185" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F185" s="335" t="s">
+      <c r="F185" s="340" t="s">
         <v>38</v>
       </c>
-      <c r="G185" s="287"/>
-      <c r="H185" s="287"/>
-      <c r="I185" s="287"/>
-      <c r="J185" s="288"/>
-      <c r="K185" s="335" t="s">
+      <c r="G185" s="291"/>
+      <c r="H185" s="291"/>
+      <c r="I185" s="291"/>
+      <c r="J185" s="292"/>
+      <c r="K185" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L185" s="288"/>
-      <c r="M185" s="335" t="s">
+      <c r="L185" s="292"/>
+      <c r="M185" s="340" t="s">
         <v>48</v>
       </c>
-      <c r="N185" s="317"/>
-      <c r="O185" s="315" t="s">
+      <c r="N185" s="312"/>
+      <c r="O185" s="310" t="s">
         <v>500</v>
       </c>
-      <c r="P185" s="316"/>
-      <c r="Q185" s="316"/>
-      <c r="R185" s="316"/>
-      <c r="S185" s="316"/>
-      <c r="T185" s="316"/>
-      <c r="U185" s="316"/>
-      <c r="V185" s="316"/>
-      <c r="W185" s="316"/>
-      <c r="X185" s="316"/>
-      <c r="Y185" s="316"/>
-      <c r="Z185" s="316"/>
-      <c r="AA185" s="316"/>
-      <c r="AB185" s="316"/>
-      <c r="AC185" s="316"/>
-      <c r="AD185" s="316"/>
-      <c r="AE185" s="316"/>
-      <c r="AF185" s="316"/>
-      <c r="AG185" s="316"/>
-      <c r="AH185" s="317"/>
+      <c r="P185" s="311"/>
+      <c r="Q185" s="311"/>
+      <c r="R185" s="311"/>
+      <c r="S185" s="311"/>
+      <c r="T185" s="311"/>
+      <c r="U185" s="311"/>
+      <c r="V185" s="311"/>
+      <c r="W185" s="311"/>
+      <c r="X185" s="311"/>
+      <c r="Y185" s="311"/>
+      <c r="Z185" s="311"/>
+      <c r="AA185" s="311"/>
+      <c r="AB185" s="311"/>
+      <c r="AC185" s="311"/>
+      <c r="AD185" s="311"/>
+      <c r="AE185" s="311"/>
+      <c r="AF185" s="311"/>
+      <c r="AG185" s="311"/>
+      <c r="AH185" s="312"/>
     </row>
     <row r="186" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F186" s="318"/>
-      <c r="G186" s="319"/>
-      <c r="H186" s="319"/>
-      <c r="I186" s="319"/>
-      <c r="J186" s="320"/>
-      <c r="K186" s="292"/>
-      <c r="L186" s="294"/>
-      <c r="M186" s="318"/>
-      <c r="N186" s="320"/>
-      <c r="O186" s="318"/>
-      <c r="P186" s="319"/>
-      <c r="Q186" s="319"/>
-      <c r="R186" s="319"/>
-      <c r="S186" s="319"/>
-      <c r="T186" s="319"/>
-      <c r="U186" s="319"/>
-      <c r="V186" s="319"/>
-      <c r="W186" s="319"/>
-      <c r="X186" s="319"/>
-      <c r="Y186" s="319"/>
-      <c r="Z186" s="319"/>
-      <c r="AA186" s="319"/>
-      <c r="AB186" s="319"/>
-      <c r="AC186" s="319"/>
-      <c r="AD186" s="319"/>
-      <c r="AE186" s="319"/>
-      <c r="AF186" s="319"/>
-      <c r="AG186" s="319"/>
-      <c r="AH186" s="320"/>
+      <c r="F186" s="313"/>
+      <c r="G186" s="314"/>
+      <c r="H186" s="314"/>
+      <c r="I186" s="314"/>
+      <c r="J186" s="315"/>
+      <c r="K186" s="296"/>
+      <c r="L186" s="298"/>
+      <c r="M186" s="313"/>
+      <c r="N186" s="315"/>
+      <c r="O186" s="313"/>
+      <c r="P186" s="314"/>
+      <c r="Q186" s="314"/>
+      <c r="R186" s="314"/>
+      <c r="S186" s="314"/>
+      <c r="T186" s="314"/>
+      <c r="U186" s="314"/>
+      <c r="V186" s="314"/>
+      <c r="W186" s="314"/>
+      <c r="X186" s="314"/>
+      <c r="Y186" s="314"/>
+      <c r="Z186" s="314"/>
+      <c r="AA186" s="314"/>
+      <c r="AB186" s="314"/>
+      <c r="AC186" s="314"/>
+      <c r="AD186" s="314"/>
+      <c r="AE186" s="314"/>
+      <c r="AF186" s="314"/>
+      <c r="AG186" s="314"/>
+      <c r="AH186" s="315"/>
     </row>
     <row r="187" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F187" s="335" t="s">
+      <c r="F187" s="340" t="s">
         <v>39</v>
       </c>
-      <c r="G187" s="287"/>
-      <c r="H187" s="287"/>
-      <c r="I187" s="287"/>
-      <c r="J187" s="288"/>
-      <c r="K187" s="335" t="s">
+      <c r="G187" s="291"/>
+      <c r="H187" s="291"/>
+      <c r="I187" s="291"/>
+      <c r="J187" s="292"/>
+      <c r="K187" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L187" s="288"/>
-      <c r="M187" s="335" t="s">
+      <c r="L187" s="292"/>
+      <c r="M187" s="340" t="s">
         <v>79</v>
       </c>
-      <c r="N187" s="317"/>
-      <c r="O187" s="315" t="s">
+      <c r="N187" s="312"/>
+      <c r="O187" s="310" t="s">
         <v>499</v>
       </c>
-      <c r="P187" s="316"/>
-      <c r="Q187" s="316"/>
-      <c r="R187" s="316"/>
-      <c r="S187" s="316"/>
-      <c r="T187" s="316"/>
-      <c r="U187" s="316"/>
-      <c r="V187" s="316"/>
-      <c r="W187" s="316"/>
-      <c r="X187" s="316"/>
-      <c r="Y187" s="316"/>
-      <c r="Z187" s="316"/>
-      <c r="AA187" s="316"/>
-      <c r="AB187" s="316"/>
-      <c r="AC187" s="316"/>
-      <c r="AD187" s="316"/>
-      <c r="AE187" s="316"/>
-      <c r="AF187" s="316"/>
-      <c r="AG187" s="316"/>
-      <c r="AH187" s="317"/>
+      <c r="P187" s="311"/>
+      <c r="Q187" s="311"/>
+      <c r="R187" s="311"/>
+      <c r="S187" s="311"/>
+      <c r="T187" s="311"/>
+      <c r="U187" s="311"/>
+      <c r="V187" s="311"/>
+      <c r="W187" s="311"/>
+      <c r="X187" s="311"/>
+      <c r="Y187" s="311"/>
+      <c r="Z187" s="311"/>
+      <c r="AA187" s="311"/>
+      <c r="AB187" s="311"/>
+      <c r="AC187" s="311"/>
+      <c r="AD187" s="311"/>
+      <c r="AE187" s="311"/>
+      <c r="AF187" s="311"/>
+      <c r="AG187" s="311"/>
+      <c r="AH187" s="312"/>
     </row>
     <row r="188" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F188" s="318"/>
-      <c r="G188" s="319"/>
-      <c r="H188" s="319"/>
-      <c r="I188" s="319"/>
-      <c r="J188" s="320"/>
-      <c r="K188" s="292"/>
-      <c r="L188" s="294"/>
-      <c r="M188" s="318"/>
-      <c r="N188" s="320"/>
-      <c r="O188" s="318"/>
-      <c r="P188" s="319"/>
-      <c r="Q188" s="319"/>
-      <c r="R188" s="319"/>
-      <c r="S188" s="319"/>
-      <c r="T188" s="319"/>
-      <c r="U188" s="319"/>
-      <c r="V188" s="319"/>
-      <c r="W188" s="319"/>
-      <c r="X188" s="319"/>
-      <c r="Y188" s="319"/>
-      <c r="Z188" s="319"/>
-      <c r="AA188" s="319"/>
-      <c r="AB188" s="319"/>
-      <c r="AC188" s="319"/>
-      <c r="AD188" s="319"/>
-      <c r="AE188" s="319"/>
-      <c r="AF188" s="319"/>
-      <c r="AG188" s="319"/>
-      <c r="AH188" s="320"/>
+      <c r="F188" s="313"/>
+      <c r="G188" s="314"/>
+      <c r="H188" s="314"/>
+      <c r="I188" s="314"/>
+      <c r="J188" s="315"/>
+      <c r="K188" s="296"/>
+      <c r="L188" s="298"/>
+      <c r="M188" s="313"/>
+      <c r="N188" s="315"/>
+      <c r="O188" s="313"/>
+      <c r="P188" s="314"/>
+      <c r="Q188" s="314"/>
+      <c r="R188" s="314"/>
+      <c r="S188" s="314"/>
+      <c r="T188" s="314"/>
+      <c r="U188" s="314"/>
+      <c r="V188" s="314"/>
+      <c r="W188" s="314"/>
+      <c r="X188" s="314"/>
+      <c r="Y188" s="314"/>
+      <c r="Z188" s="314"/>
+      <c r="AA188" s="314"/>
+      <c r="AB188" s="314"/>
+      <c r="AC188" s="314"/>
+      <c r="AD188" s="314"/>
+      <c r="AE188" s="314"/>
+      <c r="AF188" s="314"/>
+      <c r="AG188" s="314"/>
+      <c r="AH188" s="315"/>
     </row>
     <row r="189" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F189" s="335" t="s">
+      <c r="F189" s="340" t="s">
         <v>137</v>
       </c>
-      <c r="G189" s="287"/>
-      <c r="H189" s="287"/>
-      <c r="I189" s="287"/>
-      <c r="J189" s="288"/>
-      <c r="K189" s="335" t="s">
+      <c r="G189" s="291"/>
+      <c r="H189" s="291"/>
+      <c r="I189" s="291"/>
+      <c r="J189" s="292"/>
+      <c r="K189" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L189" s="288"/>
-      <c r="M189" s="335" t="s">
+      <c r="L189" s="292"/>
+      <c r="M189" s="340" t="s">
         <v>72</v>
       </c>
-      <c r="N189" s="317"/>
-      <c r="O189" s="286" t="s">
+      <c r="N189" s="312"/>
+      <c r="O189" s="290" t="s">
         <v>308</v>
       </c>
-      <c r="P189" s="287"/>
-      <c r="Q189" s="287"/>
-      <c r="R189" s="287"/>
-      <c r="S189" s="287"/>
-      <c r="T189" s="287"/>
-      <c r="U189" s="287"/>
-      <c r="V189" s="287"/>
-      <c r="W189" s="287"/>
-      <c r="X189" s="287"/>
-      <c r="Y189" s="287"/>
-      <c r="Z189" s="287"/>
-      <c r="AA189" s="287"/>
-      <c r="AB189" s="287"/>
-      <c r="AC189" s="287"/>
-      <c r="AD189" s="287"/>
-      <c r="AE189" s="287"/>
-      <c r="AF189" s="287"/>
-      <c r="AG189" s="287"/>
-      <c r="AH189" s="288"/>
+      <c r="P189" s="291"/>
+      <c r="Q189" s="291"/>
+      <c r="R189" s="291"/>
+      <c r="S189" s="291"/>
+      <c r="T189" s="291"/>
+      <c r="U189" s="291"/>
+      <c r="V189" s="291"/>
+      <c r="W189" s="291"/>
+      <c r="X189" s="291"/>
+      <c r="Y189" s="291"/>
+      <c r="Z189" s="291"/>
+      <c r="AA189" s="291"/>
+      <c r="AB189" s="291"/>
+      <c r="AC189" s="291"/>
+      <c r="AD189" s="291"/>
+      <c r="AE189" s="291"/>
+      <c r="AF189" s="291"/>
+      <c r="AG189" s="291"/>
+      <c r="AH189" s="292"/>
     </row>
     <row r="190" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F190" s="318"/>
-      <c r="G190" s="319"/>
-      <c r="H190" s="319"/>
-      <c r="I190" s="319"/>
-      <c r="J190" s="320"/>
-      <c r="K190" s="292"/>
-      <c r="L190" s="294"/>
-      <c r="M190" s="318"/>
-      <c r="N190" s="320"/>
-      <c r="O190" s="318"/>
-      <c r="P190" s="319"/>
-      <c r="Q190" s="319"/>
-      <c r="R190" s="319"/>
-      <c r="S190" s="319"/>
-      <c r="T190" s="319"/>
-      <c r="U190" s="319"/>
-      <c r="V190" s="319"/>
-      <c r="W190" s="319"/>
-      <c r="X190" s="319"/>
-      <c r="Y190" s="319"/>
-      <c r="Z190" s="319"/>
-      <c r="AA190" s="319"/>
-      <c r="AB190" s="319"/>
-      <c r="AC190" s="319"/>
-      <c r="AD190" s="319"/>
-      <c r="AE190" s="319"/>
-      <c r="AF190" s="319"/>
-      <c r="AG190" s="319"/>
-      <c r="AH190" s="320"/>
+      <c r="F190" s="313"/>
+      <c r="G190" s="314"/>
+      <c r="H190" s="314"/>
+      <c r="I190" s="314"/>
+      <c r="J190" s="315"/>
+      <c r="K190" s="296"/>
+      <c r="L190" s="298"/>
+      <c r="M190" s="313"/>
+      <c r="N190" s="315"/>
+      <c r="O190" s="313"/>
+      <c r="P190" s="314"/>
+      <c r="Q190" s="314"/>
+      <c r="R190" s="314"/>
+      <c r="S190" s="314"/>
+      <c r="T190" s="314"/>
+      <c r="U190" s="314"/>
+      <c r="V190" s="314"/>
+      <c r="W190" s="314"/>
+      <c r="X190" s="314"/>
+      <c r="Y190" s="314"/>
+      <c r="Z190" s="314"/>
+      <c r="AA190" s="314"/>
+      <c r="AB190" s="314"/>
+      <c r="AC190" s="314"/>
+      <c r="AD190" s="314"/>
+      <c r="AE190" s="314"/>
+      <c r="AF190" s="314"/>
+      <c r="AG190" s="314"/>
+      <c r="AH190" s="315"/>
     </row>
     <row r="191" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F191" s="308" t="s">
+      <c r="F191" s="307" t="s">
         <v>138</v>
       </c>
-      <c r="G191" s="278"/>
-      <c r="H191" s="278"/>
-      <c r="I191" s="278"/>
-      <c r="J191" s="279"/>
-      <c r="K191" s="343" t="s">
+      <c r="G191" s="252"/>
+      <c r="H191" s="252"/>
+      <c r="I191" s="252"/>
+      <c r="J191" s="253"/>
+      <c r="K191" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="L191" s="344"/>
-      <c r="M191" s="343" t="s">
+      <c r="L191" s="364"/>
+      <c r="M191" s="341" t="s">
         <v>72</v>
       </c>
-      <c r="N191" s="348"/>
-      <c r="O191" s="308" t="s">
+      <c r="N191" s="337"/>
+      <c r="O191" s="307" t="s">
         <v>309</v>
       </c>
-      <c r="P191" s="278"/>
-      <c r="Q191" s="278"/>
-      <c r="R191" s="278"/>
-      <c r="S191" s="278"/>
-      <c r="T191" s="278"/>
-      <c r="U191" s="278"/>
-      <c r="V191" s="278"/>
-      <c r="W191" s="278"/>
-      <c r="X191" s="278"/>
-      <c r="Y191" s="278"/>
-      <c r="Z191" s="278"/>
-      <c r="AA191" s="278"/>
-      <c r="AB191" s="278"/>
-      <c r="AC191" s="278"/>
-      <c r="AD191" s="278"/>
-      <c r="AE191" s="278"/>
-      <c r="AF191" s="278"/>
-      <c r="AG191" s="278"/>
-      <c r="AH191" s="279"/>
+      <c r="P191" s="252"/>
+      <c r="Q191" s="252"/>
+      <c r="R191" s="252"/>
+      <c r="S191" s="252"/>
+      <c r="T191" s="252"/>
+      <c r="U191" s="252"/>
+      <c r="V191" s="252"/>
+      <c r="W191" s="252"/>
+      <c r="X191" s="252"/>
+      <c r="Y191" s="252"/>
+      <c r="Z191" s="252"/>
+      <c r="AA191" s="252"/>
+      <c r="AB191" s="252"/>
+      <c r="AC191" s="252"/>
+      <c r="AD191" s="252"/>
+      <c r="AE191" s="252"/>
+      <c r="AF191" s="252"/>
+      <c r="AG191" s="252"/>
+      <c r="AH191" s="253"/>
     </row>
     <row r="192" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F192" s="335" t="s">
+      <c r="F192" s="340" t="s">
         <v>49</v>
       </c>
-      <c r="G192" s="287"/>
-      <c r="H192" s="287"/>
-      <c r="I192" s="287"/>
-      <c r="J192" s="288"/>
-      <c r="K192" s="335" t="s">
+      <c r="G192" s="291"/>
+      <c r="H192" s="291"/>
+      <c r="I192" s="291"/>
+      <c r="J192" s="292"/>
+      <c r="K192" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L192" s="288"/>
-      <c r="M192" s="335" t="s">
+      <c r="L192" s="292"/>
+      <c r="M192" s="340" t="s">
         <v>77</v>
       </c>
-      <c r="N192" s="317"/>
-      <c r="O192" s="286" t="s">
+      <c r="N192" s="312"/>
+      <c r="O192" s="290" t="s">
         <v>498</v>
       </c>
-      <c r="P192" s="316"/>
-      <c r="Q192" s="316"/>
-      <c r="R192" s="316"/>
-      <c r="S192" s="316"/>
-      <c r="T192" s="316"/>
-      <c r="U192" s="316"/>
-      <c r="V192" s="316"/>
-      <c r="W192" s="316"/>
-      <c r="X192" s="316"/>
-      <c r="Y192" s="316"/>
-      <c r="Z192" s="316"/>
-      <c r="AA192" s="316"/>
-      <c r="AB192" s="316"/>
-      <c r="AC192" s="316"/>
-      <c r="AD192" s="316"/>
-      <c r="AE192" s="316"/>
-      <c r="AF192" s="316"/>
-      <c r="AG192" s="316"/>
-      <c r="AH192" s="317"/>
+      <c r="P192" s="311"/>
+      <c r="Q192" s="311"/>
+      <c r="R192" s="311"/>
+      <c r="S192" s="311"/>
+      <c r="T192" s="311"/>
+      <c r="U192" s="311"/>
+      <c r="V192" s="311"/>
+      <c r="W192" s="311"/>
+      <c r="X192" s="311"/>
+      <c r="Y192" s="311"/>
+      <c r="Z192" s="311"/>
+      <c r="AA192" s="311"/>
+      <c r="AB192" s="311"/>
+      <c r="AC192" s="311"/>
+      <c r="AD192" s="311"/>
+      <c r="AE192" s="311"/>
+      <c r="AF192" s="311"/>
+      <c r="AG192" s="311"/>
+      <c r="AH192" s="312"/>
     </row>
     <row r="193" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F193" s="318"/>
-      <c r="G193" s="319"/>
-      <c r="H193" s="319"/>
-      <c r="I193" s="319"/>
-      <c r="J193" s="320"/>
-      <c r="K193" s="292"/>
-      <c r="L193" s="294"/>
-      <c r="M193" s="318"/>
-      <c r="N193" s="320"/>
-      <c r="O193" s="318"/>
-      <c r="P193" s="319"/>
-      <c r="Q193" s="319"/>
-      <c r="R193" s="319"/>
-      <c r="S193" s="319"/>
-      <c r="T193" s="319"/>
-      <c r="U193" s="319"/>
-      <c r="V193" s="319"/>
-      <c r="W193" s="319"/>
-      <c r="X193" s="319"/>
-      <c r="Y193" s="319"/>
-      <c r="Z193" s="319"/>
-      <c r="AA193" s="319"/>
-      <c r="AB193" s="319"/>
-      <c r="AC193" s="319"/>
-      <c r="AD193" s="319"/>
-      <c r="AE193" s="319"/>
-      <c r="AF193" s="319"/>
-      <c r="AG193" s="319"/>
-      <c r="AH193" s="320"/>
+      <c r="F193" s="313"/>
+      <c r="G193" s="314"/>
+      <c r="H193" s="314"/>
+      <c r="I193" s="314"/>
+      <c r="J193" s="315"/>
+      <c r="K193" s="296"/>
+      <c r="L193" s="298"/>
+      <c r="M193" s="313"/>
+      <c r="N193" s="315"/>
+      <c r="O193" s="313"/>
+      <c r="P193" s="314"/>
+      <c r="Q193" s="314"/>
+      <c r="R193" s="314"/>
+      <c r="S193" s="314"/>
+      <c r="T193" s="314"/>
+      <c r="U193" s="314"/>
+      <c r="V193" s="314"/>
+      <c r="W193" s="314"/>
+      <c r="X193" s="314"/>
+      <c r="Y193" s="314"/>
+      <c r="Z193" s="314"/>
+      <c r="AA193" s="314"/>
+      <c r="AB193" s="314"/>
+      <c r="AC193" s="314"/>
+      <c r="AD193" s="314"/>
+      <c r="AE193" s="314"/>
+      <c r="AF193" s="314"/>
+      <c r="AG193" s="314"/>
+      <c r="AH193" s="315"/>
     </row>
     <row r="194" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F194" s="277" t="s">
+      <c r="F194" s="251" t="s">
         <v>42</v>
       </c>
-      <c r="G194" s="278"/>
-      <c r="H194" s="278"/>
-      <c r="I194" s="278"/>
-      <c r="J194" s="279"/>
-      <c r="K194" s="343" t="s">
+      <c r="G194" s="252"/>
+      <c r="H194" s="252"/>
+      <c r="I194" s="252"/>
+      <c r="J194" s="253"/>
+      <c r="K194" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="L194" s="344"/>
-      <c r="M194" s="343" t="s">
+      <c r="L194" s="364"/>
+      <c r="M194" s="341" t="s">
         <v>76</v>
       </c>
-      <c r="N194" s="348"/>
-      <c r="O194" s="308" t="s">
+      <c r="N194" s="337"/>
+      <c r="O194" s="307" t="s">
         <v>309</v>
       </c>
-      <c r="P194" s="278"/>
-      <c r="Q194" s="278"/>
-      <c r="R194" s="278"/>
-      <c r="S194" s="278"/>
-      <c r="T194" s="278"/>
-      <c r="U194" s="278"/>
-      <c r="V194" s="278"/>
-      <c r="W194" s="278"/>
-      <c r="X194" s="278"/>
-      <c r="Y194" s="278"/>
-      <c r="Z194" s="278"/>
-      <c r="AA194" s="278"/>
-      <c r="AB194" s="278"/>
-      <c r="AC194" s="278"/>
-      <c r="AD194" s="278"/>
-      <c r="AE194" s="278"/>
-      <c r="AF194" s="278"/>
-      <c r="AG194" s="278"/>
-      <c r="AH194" s="279"/>
+      <c r="P194" s="252"/>
+      <c r="Q194" s="252"/>
+      <c r="R194" s="252"/>
+      <c r="S194" s="252"/>
+      <c r="T194" s="252"/>
+      <c r="U194" s="252"/>
+      <c r="V194" s="252"/>
+      <c r="W194" s="252"/>
+      <c r="X194" s="252"/>
+      <c r="Y194" s="252"/>
+      <c r="Z194" s="252"/>
+      <c r="AA194" s="252"/>
+      <c r="AB194" s="252"/>
+      <c r="AC194" s="252"/>
+      <c r="AD194" s="252"/>
+      <c r="AE194" s="252"/>
+      <c r="AF194" s="252"/>
+      <c r="AG194" s="252"/>
+      <c r="AH194" s="253"/>
     </row>
     <row r="195" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E195" s="30"/>
-      <c r="F195" s="315" t="s">
+      <c r="F195" s="310" t="s">
         <v>270</v>
       </c>
-      <c r="G195" s="316"/>
-      <c r="H195" s="316"/>
-      <c r="I195" s="316"/>
-      <c r="J195" s="317"/>
-      <c r="K195" s="326" t="s">
+      <c r="G195" s="311"/>
+      <c r="H195" s="311"/>
+      <c r="I195" s="311"/>
+      <c r="J195" s="312"/>
+      <c r="K195" s="351" t="s">
         <v>46</v>
       </c>
-      <c r="L195" s="327"/>
-      <c r="M195" s="335" t="s">
+      <c r="L195" s="352"/>
+      <c r="M195" s="340" t="s">
         <v>76</v>
       </c>
-      <c r="N195" s="317"/>
-      <c r="O195" s="286" t="s">
+      <c r="N195" s="312"/>
+      <c r="O195" s="290" t="s">
         <v>309</v>
       </c>
-      <c r="P195" s="287"/>
-      <c r="Q195" s="287"/>
-      <c r="R195" s="287"/>
-      <c r="S195" s="287"/>
-      <c r="T195" s="287"/>
-      <c r="U195" s="287"/>
-      <c r="V195" s="287"/>
-      <c r="W195" s="287"/>
-      <c r="X195" s="287"/>
-      <c r="Y195" s="287"/>
-      <c r="Z195" s="287"/>
-      <c r="AA195" s="287"/>
-      <c r="AB195" s="287"/>
-      <c r="AC195" s="287"/>
-      <c r="AD195" s="287"/>
-      <c r="AE195" s="287"/>
-      <c r="AF195" s="287"/>
-      <c r="AG195" s="287"/>
-      <c r="AH195" s="288"/>
+      <c r="P195" s="291"/>
+      <c r="Q195" s="291"/>
+      <c r="R195" s="291"/>
+      <c r="S195" s="291"/>
+      <c r="T195" s="291"/>
+      <c r="U195" s="291"/>
+      <c r="V195" s="291"/>
+      <c r="W195" s="291"/>
+      <c r="X195" s="291"/>
+      <c r="Y195" s="291"/>
+      <c r="Z195" s="291"/>
+      <c r="AA195" s="291"/>
+      <c r="AB195" s="291"/>
+      <c r="AC195" s="291"/>
+      <c r="AD195" s="291"/>
+      <c r="AE195" s="291"/>
+      <c r="AF195" s="291"/>
+      <c r="AG195" s="291"/>
+      <c r="AH195" s="292"/>
     </row>
     <row r="196" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E196" s="30"/>
-      <c r="F196" s="318"/>
-      <c r="G196" s="319"/>
-      <c r="H196" s="319"/>
-      <c r="I196" s="319"/>
-      <c r="J196" s="320"/>
-      <c r="K196" s="323"/>
-      <c r="L196" s="325"/>
-      <c r="M196" s="318"/>
-      <c r="N196" s="320"/>
-      <c r="O196" s="318"/>
-      <c r="P196" s="319"/>
-      <c r="Q196" s="319"/>
-      <c r="R196" s="319"/>
-      <c r="S196" s="319"/>
-      <c r="T196" s="319"/>
-      <c r="U196" s="319"/>
-      <c r="V196" s="319"/>
-      <c r="W196" s="319"/>
-      <c r="X196" s="319"/>
-      <c r="Y196" s="319"/>
-      <c r="Z196" s="319"/>
-      <c r="AA196" s="319"/>
-      <c r="AB196" s="319"/>
-      <c r="AC196" s="319"/>
-      <c r="AD196" s="319"/>
-      <c r="AE196" s="319"/>
-      <c r="AF196" s="319"/>
-      <c r="AG196" s="319"/>
-      <c r="AH196" s="320"/>
+      <c r="F196" s="313"/>
+      <c r="G196" s="314"/>
+      <c r="H196" s="314"/>
+      <c r="I196" s="314"/>
+      <c r="J196" s="315"/>
+      <c r="K196" s="359"/>
+      <c r="L196" s="361"/>
+      <c r="M196" s="313"/>
+      <c r="N196" s="315"/>
+      <c r="O196" s="313"/>
+      <c r="P196" s="314"/>
+      <c r="Q196" s="314"/>
+      <c r="R196" s="314"/>
+      <c r="S196" s="314"/>
+      <c r="T196" s="314"/>
+      <c r="U196" s="314"/>
+      <c r="V196" s="314"/>
+      <c r="W196" s="314"/>
+      <c r="X196" s="314"/>
+      <c r="Y196" s="314"/>
+      <c r="Z196" s="314"/>
+      <c r="AA196" s="314"/>
+      <c r="AB196" s="314"/>
+      <c r="AC196" s="314"/>
+      <c r="AD196" s="314"/>
+      <c r="AE196" s="314"/>
+      <c r="AF196" s="314"/>
+      <c r="AG196" s="314"/>
+      <c r="AH196" s="315"/>
     </row>
     <row r="197" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="198" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -43696,689 +43697,689 @@
     </row>
     <row r="200" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="201" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F201" s="329" t="s">
+      <c r="F201" s="365" t="s">
         <v>630</v>
       </c>
-      <c r="G201" s="330"/>
-      <c r="H201" s="330"/>
-      <c r="I201" s="330"/>
-      <c r="J201" s="331"/>
-      <c r="K201" s="346" t="s">
+      <c r="G201" s="366"/>
+      <c r="H201" s="366"/>
+      <c r="I201" s="366"/>
+      <c r="J201" s="367"/>
+      <c r="K201" s="355" t="s">
         <v>30</v>
       </c>
-      <c r="L201" s="347"/>
-      <c r="M201" s="346" t="s">
+      <c r="L201" s="356"/>
+      <c r="M201" s="355" t="s">
         <v>31</v>
       </c>
-      <c r="N201" s="347"/>
-      <c r="O201" s="274" t="s">
+      <c r="N201" s="356"/>
+      <c r="O201" s="248" t="s">
         <v>305</v>
       </c>
-      <c r="P201" s="275"/>
-      <c r="Q201" s="275"/>
-      <c r="R201" s="275"/>
-      <c r="S201" s="275"/>
-      <c r="T201" s="275"/>
-      <c r="U201" s="275"/>
-      <c r="V201" s="275"/>
-      <c r="W201" s="275"/>
-      <c r="X201" s="275"/>
-      <c r="Y201" s="275"/>
-      <c r="Z201" s="275"/>
-      <c r="AA201" s="275"/>
-      <c r="AB201" s="275"/>
-      <c r="AC201" s="275"/>
-      <c r="AD201" s="275"/>
-      <c r="AE201" s="275"/>
-      <c r="AF201" s="275"/>
-      <c r="AG201" s="275"/>
-      <c r="AH201" s="276"/>
+      <c r="P201" s="249"/>
+      <c r="Q201" s="249"/>
+      <c r="R201" s="249"/>
+      <c r="S201" s="249"/>
+      <c r="T201" s="249"/>
+      <c r="U201" s="249"/>
+      <c r="V201" s="249"/>
+      <c r="W201" s="249"/>
+      <c r="X201" s="249"/>
+      <c r="Y201" s="249"/>
+      <c r="Z201" s="249"/>
+      <c r="AA201" s="249"/>
+      <c r="AB201" s="249"/>
+      <c r="AC201" s="249"/>
+      <c r="AD201" s="249"/>
+      <c r="AE201" s="249"/>
+      <c r="AF201" s="249"/>
+      <c r="AG201" s="249"/>
+      <c r="AH201" s="250"/>
     </row>
     <row r="202" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F202" s="315" t="s">
+      <c r="F202" s="310" t="s">
         <v>285</v>
       </c>
-      <c r="G202" s="321"/>
-      <c r="H202" s="321"/>
-      <c r="I202" s="321"/>
-      <c r="J202" s="322"/>
-      <c r="K202" s="335" t="s">
+      <c r="G202" s="357"/>
+      <c r="H202" s="357"/>
+      <c r="I202" s="357"/>
+      <c r="J202" s="358"/>
+      <c r="K202" s="340" t="s">
         <v>32</v>
       </c>
-      <c r="L202" s="288"/>
-      <c r="M202" s="335" t="s">
+      <c r="L202" s="292"/>
+      <c r="M202" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N202" s="288"/>
-      <c r="O202" s="315" t="s">
+      <c r="N202" s="292"/>
+      <c r="O202" s="310" t="s">
         <v>287</v>
       </c>
-      <c r="P202" s="321"/>
-      <c r="Q202" s="321"/>
-      <c r="R202" s="321"/>
-      <c r="S202" s="321"/>
-      <c r="T202" s="321"/>
-      <c r="U202" s="321"/>
-      <c r="V202" s="321"/>
-      <c r="W202" s="321"/>
-      <c r="X202" s="321"/>
-      <c r="Y202" s="321"/>
-      <c r="Z202" s="321"/>
-      <c r="AA202" s="321"/>
-      <c r="AB202" s="321"/>
-      <c r="AC202" s="321"/>
-      <c r="AD202" s="321"/>
-      <c r="AE202" s="321"/>
-      <c r="AF202" s="321"/>
-      <c r="AG202" s="321"/>
-      <c r="AH202" s="322"/>
+      <c r="P202" s="357"/>
+      <c r="Q202" s="357"/>
+      <c r="R202" s="357"/>
+      <c r="S202" s="357"/>
+      <c r="T202" s="357"/>
+      <c r="U202" s="357"/>
+      <c r="V202" s="357"/>
+      <c r="W202" s="357"/>
+      <c r="X202" s="357"/>
+      <c r="Y202" s="357"/>
+      <c r="Z202" s="357"/>
+      <c r="AA202" s="357"/>
+      <c r="AB202" s="357"/>
+      <c r="AC202" s="357"/>
+      <c r="AD202" s="357"/>
+      <c r="AE202" s="357"/>
+      <c r="AF202" s="357"/>
+      <c r="AG202" s="357"/>
+      <c r="AH202" s="358"/>
     </row>
     <row r="203" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F203" s="323"/>
-      <c r="G203" s="324"/>
-      <c r="H203" s="324"/>
-      <c r="I203" s="324"/>
-      <c r="J203" s="325"/>
-      <c r="K203" s="292"/>
-      <c r="L203" s="294"/>
-      <c r="M203" s="292"/>
-      <c r="N203" s="294"/>
-      <c r="O203" s="323"/>
-      <c r="P203" s="324"/>
-      <c r="Q203" s="324"/>
-      <c r="R203" s="324"/>
-      <c r="S203" s="324"/>
-      <c r="T203" s="324"/>
-      <c r="U203" s="324"/>
-      <c r="V203" s="324"/>
-      <c r="W203" s="324"/>
-      <c r="X203" s="324"/>
-      <c r="Y203" s="324"/>
-      <c r="Z203" s="324"/>
-      <c r="AA203" s="324"/>
-      <c r="AB203" s="324"/>
-      <c r="AC203" s="324"/>
-      <c r="AD203" s="324"/>
-      <c r="AE203" s="324"/>
-      <c r="AF203" s="324"/>
-      <c r="AG203" s="324"/>
-      <c r="AH203" s="325"/>
+      <c r="F203" s="359"/>
+      <c r="G203" s="360"/>
+      <c r="H203" s="360"/>
+      <c r="I203" s="360"/>
+      <c r="J203" s="361"/>
+      <c r="K203" s="296"/>
+      <c r="L203" s="298"/>
+      <c r="M203" s="296"/>
+      <c r="N203" s="298"/>
+      <c r="O203" s="359"/>
+      <c r="P203" s="360"/>
+      <c r="Q203" s="360"/>
+      <c r="R203" s="360"/>
+      <c r="S203" s="360"/>
+      <c r="T203" s="360"/>
+      <c r="U203" s="360"/>
+      <c r="V203" s="360"/>
+      <c r="W203" s="360"/>
+      <c r="X203" s="360"/>
+      <c r="Y203" s="360"/>
+      <c r="Z203" s="360"/>
+      <c r="AA203" s="360"/>
+      <c r="AB203" s="360"/>
+      <c r="AC203" s="360"/>
+      <c r="AD203" s="360"/>
+      <c r="AE203" s="360"/>
+      <c r="AF203" s="360"/>
+      <c r="AG203" s="360"/>
+      <c r="AH203" s="361"/>
     </row>
     <row r="204" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F204" s="326" t="s">
+      <c r="F204" s="351" t="s">
         <v>40</v>
       </c>
-      <c r="G204" s="328"/>
-      <c r="H204" s="328"/>
-      <c r="I204" s="328"/>
-      <c r="J204" s="327"/>
-      <c r="K204" s="335" t="s">
+      <c r="G204" s="362"/>
+      <c r="H204" s="362"/>
+      <c r="I204" s="362"/>
+      <c r="J204" s="352"/>
+      <c r="K204" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L204" s="288"/>
-      <c r="M204" s="335" t="s">
+      <c r="L204" s="292"/>
+      <c r="M204" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N204" s="288"/>
-      <c r="O204" s="315" t="s">
+      <c r="N204" s="292"/>
+      <c r="O204" s="310" t="s">
         <v>493</v>
       </c>
-      <c r="P204" s="321"/>
-      <c r="Q204" s="321"/>
-      <c r="R204" s="321"/>
-      <c r="S204" s="321"/>
-      <c r="T204" s="321"/>
-      <c r="U204" s="321"/>
-      <c r="V204" s="321"/>
-      <c r="W204" s="321"/>
-      <c r="X204" s="321"/>
-      <c r="Y204" s="321"/>
-      <c r="Z204" s="321"/>
-      <c r="AA204" s="321"/>
-      <c r="AB204" s="321"/>
-      <c r="AC204" s="321"/>
-      <c r="AD204" s="321"/>
-      <c r="AE204" s="321"/>
-      <c r="AF204" s="321"/>
-      <c r="AG204" s="321"/>
-      <c r="AH204" s="322"/>
+      <c r="P204" s="357"/>
+      <c r="Q204" s="357"/>
+      <c r="R204" s="357"/>
+      <c r="S204" s="357"/>
+      <c r="T204" s="357"/>
+      <c r="U204" s="357"/>
+      <c r="V204" s="357"/>
+      <c r="W204" s="357"/>
+      <c r="X204" s="357"/>
+      <c r="Y204" s="357"/>
+      <c r="Z204" s="357"/>
+      <c r="AA204" s="357"/>
+      <c r="AB204" s="357"/>
+      <c r="AC204" s="357"/>
+      <c r="AD204" s="357"/>
+      <c r="AE204" s="357"/>
+      <c r="AF204" s="357"/>
+      <c r="AG204" s="357"/>
+      <c r="AH204" s="358"/>
     </row>
     <row r="205" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F205" s="323"/>
-      <c r="G205" s="324"/>
-      <c r="H205" s="324"/>
-      <c r="I205" s="324"/>
-      <c r="J205" s="325"/>
-      <c r="K205" s="292"/>
-      <c r="L205" s="294"/>
-      <c r="M205" s="292"/>
-      <c r="N205" s="294"/>
-      <c r="O205" s="323"/>
-      <c r="P205" s="324"/>
-      <c r="Q205" s="324"/>
-      <c r="R205" s="324"/>
-      <c r="S205" s="324"/>
-      <c r="T205" s="324"/>
-      <c r="U205" s="324"/>
-      <c r="V205" s="324"/>
-      <c r="W205" s="324"/>
-      <c r="X205" s="324"/>
-      <c r="Y205" s="324"/>
-      <c r="Z205" s="324"/>
-      <c r="AA205" s="324"/>
-      <c r="AB205" s="324"/>
-      <c r="AC205" s="324"/>
-      <c r="AD205" s="324"/>
-      <c r="AE205" s="324"/>
-      <c r="AF205" s="324"/>
-      <c r="AG205" s="324"/>
-      <c r="AH205" s="325"/>
+      <c r="F205" s="359"/>
+      <c r="G205" s="360"/>
+      <c r="H205" s="360"/>
+      <c r="I205" s="360"/>
+      <c r="J205" s="361"/>
+      <c r="K205" s="296"/>
+      <c r="L205" s="298"/>
+      <c r="M205" s="296"/>
+      <c r="N205" s="298"/>
+      <c r="O205" s="359"/>
+      <c r="P205" s="360"/>
+      <c r="Q205" s="360"/>
+      <c r="R205" s="360"/>
+      <c r="S205" s="360"/>
+      <c r="T205" s="360"/>
+      <c r="U205" s="360"/>
+      <c r="V205" s="360"/>
+      <c r="W205" s="360"/>
+      <c r="X205" s="360"/>
+      <c r="Y205" s="360"/>
+      <c r="Z205" s="360"/>
+      <c r="AA205" s="360"/>
+      <c r="AB205" s="360"/>
+      <c r="AC205" s="360"/>
+      <c r="AD205" s="360"/>
+      <c r="AE205" s="360"/>
+      <c r="AF205" s="360"/>
+      <c r="AG205" s="360"/>
+      <c r="AH205" s="361"/>
     </row>
     <row r="206" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F206" s="326" t="s">
+      <c r="F206" s="351" t="s">
         <v>41</v>
       </c>
-      <c r="G206" s="328"/>
-      <c r="H206" s="328"/>
-      <c r="I206" s="328"/>
-      <c r="J206" s="327"/>
-      <c r="K206" s="326" t="s">
+      <c r="G206" s="362"/>
+      <c r="H206" s="362"/>
+      <c r="I206" s="362"/>
+      <c r="J206" s="352"/>
+      <c r="K206" s="351" t="s">
         <v>35</v>
       </c>
-      <c r="L206" s="327"/>
-      <c r="M206" s="326" t="s">
+      <c r="L206" s="352"/>
+      <c r="M206" s="351" t="s">
         <v>33</v>
       </c>
-      <c r="N206" s="327"/>
-      <c r="O206" s="315" t="s">
+      <c r="N206" s="352"/>
+      <c r="O206" s="310" t="s">
         <v>494</v>
       </c>
-      <c r="P206" s="321"/>
-      <c r="Q206" s="321"/>
-      <c r="R206" s="321"/>
-      <c r="S206" s="321"/>
-      <c r="T206" s="321"/>
-      <c r="U206" s="321"/>
-      <c r="V206" s="321"/>
-      <c r="W206" s="321"/>
-      <c r="X206" s="321"/>
-      <c r="Y206" s="321"/>
-      <c r="Z206" s="321"/>
-      <c r="AA206" s="321"/>
-      <c r="AB206" s="321"/>
-      <c r="AC206" s="321"/>
-      <c r="AD206" s="321"/>
-      <c r="AE206" s="321"/>
-      <c r="AF206" s="321"/>
-      <c r="AG206" s="321"/>
-      <c r="AH206" s="322"/>
+      <c r="P206" s="357"/>
+      <c r="Q206" s="357"/>
+      <c r="R206" s="357"/>
+      <c r="S206" s="357"/>
+      <c r="T206" s="357"/>
+      <c r="U206" s="357"/>
+      <c r="V206" s="357"/>
+      <c r="W206" s="357"/>
+      <c r="X206" s="357"/>
+      <c r="Y206" s="357"/>
+      <c r="Z206" s="357"/>
+      <c r="AA206" s="357"/>
+      <c r="AB206" s="357"/>
+      <c r="AC206" s="357"/>
+      <c r="AD206" s="357"/>
+      <c r="AE206" s="357"/>
+      <c r="AF206" s="357"/>
+      <c r="AG206" s="357"/>
+      <c r="AH206" s="358"/>
     </row>
     <row r="207" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F207" s="323"/>
-      <c r="G207" s="324"/>
-      <c r="H207" s="324"/>
-      <c r="I207" s="324"/>
-      <c r="J207" s="325"/>
-      <c r="K207" s="349"/>
-      <c r="L207" s="350"/>
-      <c r="M207" s="349"/>
-      <c r="N207" s="350"/>
-      <c r="O207" s="323"/>
-      <c r="P207" s="324"/>
-      <c r="Q207" s="324"/>
-      <c r="R207" s="324"/>
-      <c r="S207" s="324"/>
-      <c r="T207" s="324"/>
-      <c r="U207" s="324"/>
-      <c r="V207" s="324"/>
-      <c r="W207" s="324"/>
-      <c r="X207" s="324"/>
-      <c r="Y207" s="324"/>
-      <c r="Z207" s="324"/>
-      <c r="AA207" s="324"/>
-      <c r="AB207" s="324"/>
-      <c r="AC207" s="324"/>
-      <c r="AD207" s="324"/>
-      <c r="AE207" s="324"/>
-      <c r="AF207" s="324"/>
-      <c r="AG207" s="324"/>
-      <c r="AH207" s="325"/>
+      <c r="F207" s="359"/>
+      <c r="G207" s="360"/>
+      <c r="H207" s="360"/>
+      <c r="I207" s="360"/>
+      <c r="J207" s="361"/>
+      <c r="K207" s="353"/>
+      <c r="L207" s="354"/>
+      <c r="M207" s="353"/>
+      <c r="N207" s="354"/>
+      <c r="O207" s="359"/>
+      <c r="P207" s="360"/>
+      <c r="Q207" s="360"/>
+      <c r="R207" s="360"/>
+      <c r="S207" s="360"/>
+      <c r="T207" s="360"/>
+      <c r="U207" s="360"/>
+      <c r="V207" s="360"/>
+      <c r="W207" s="360"/>
+      <c r="X207" s="360"/>
+      <c r="Y207" s="360"/>
+      <c r="Z207" s="360"/>
+      <c r="AA207" s="360"/>
+      <c r="AB207" s="360"/>
+      <c r="AC207" s="360"/>
+      <c r="AD207" s="360"/>
+      <c r="AE207" s="360"/>
+      <c r="AF207" s="360"/>
+      <c r="AG207" s="360"/>
+      <c r="AH207" s="361"/>
     </row>
     <row r="208" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F208" s="315" t="s">
+      <c r="F208" s="310" t="s">
         <v>286</v>
       </c>
-      <c r="G208" s="321"/>
-      <c r="H208" s="321"/>
-      <c r="I208" s="321"/>
-      <c r="J208" s="322"/>
-      <c r="K208" s="335" t="s">
+      <c r="G208" s="357"/>
+      <c r="H208" s="357"/>
+      <c r="I208" s="357"/>
+      <c r="J208" s="358"/>
+      <c r="K208" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L208" s="288"/>
-      <c r="M208" s="335" t="s">
+      <c r="L208" s="292"/>
+      <c r="M208" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N208" s="288"/>
-      <c r="O208" s="315" t="s">
+      <c r="N208" s="292"/>
+      <c r="O208" s="310" t="s">
         <v>495</v>
       </c>
-      <c r="P208" s="321"/>
-      <c r="Q208" s="321"/>
-      <c r="R208" s="321"/>
-      <c r="S208" s="321"/>
-      <c r="T208" s="321"/>
-      <c r="U208" s="321"/>
-      <c r="V208" s="321"/>
-      <c r="W208" s="321"/>
-      <c r="X208" s="321"/>
-      <c r="Y208" s="321"/>
-      <c r="Z208" s="321"/>
-      <c r="AA208" s="321"/>
-      <c r="AB208" s="321"/>
-      <c r="AC208" s="321"/>
-      <c r="AD208" s="321"/>
-      <c r="AE208" s="321"/>
-      <c r="AF208" s="321"/>
-      <c r="AG208" s="321"/>
-      <c r="AH208" s="322"/>
+      <c r="P208" s="357"/>
+      <c r="Q208" s="357"/>
+      <c r="R208" s="357"/>
+      <c r="S208" s="357"/>
+      <c r="T208" s="357"/>
+      <c r="U208" s="357"/>
+      <c r="V208" s="357"/>
+      <c r="W208" s="357"/>
+      <c r="X208" s="357"/>
+      <c r="Y208" s="357"/>
+      <c r="Z208" s="357"/>
+      <c r="AA208" s="357"/>
+      <c r="AB208" s="357"/>
+      <c r="AC208" s="357"/>
+      <c r="AD208" s="357"/>
+      <c r="AE208" s="357"/>
+      <c r="AF208" s="357"/>
+      <c r="AG208" s="357"/>
+      <c r="AH208" s="358"/>
     </row>
     <row r="209" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F209" s="323"/>
-      <c r="G209" s="324"/>
-      <c r="H209" s="324"/>
-      <c r="I209" s="324"/>
-      <c r="J209" s="325"/>
-      <c r="K209" s="292"/>
-      <c r="L209" s="294"/>
-      <c r="M209" s="292"/>
-      <c r="N209" s="294"/>
-      <c r="O209" s="323"/>
-      <c r="P209" s="324"/>
-      <c r="Q209" s="324"/>
-      <c r="R209" s="324"/>
-      <c r="S209" s="324"/>
-      <c r="T209" s="324"/>
-      <c r="U209" s="324"/>
-      <c r="V209" s="324"/>
-      <c r="W209" s="324"/>
-      <c r="X209" s="324"/>
-      <c r="Y209" s="324"/>
-      <c r="Z209" s="324"/>
-      <c r="AA209" s="324"/>
-      <c r="AB209" s="324"/>
-      <c r="AC209" s="324"/>
-      <c r="AD209" s="324"/>
-      <c r="AE209" s="324"/>
-      <c r="AF209" s="324"/>
-      <c r="AG209" s="324"/>
-      <c r="AH209" s="325"/>
+      <c r="F209" s="359"/>
+      <c r="G209" s="360"/>
+      <c r="H209" s="360"/>
+      <c r="I209" s="360"/>
+      <c r="J209" s="361"/>
+      <c r="K209" s="296"/>
+      <c r="L209" s="298"/>
+      <c r="M209" s="296"/>
+      <c r="N209" s="298"/>
+      <c r="O209" s="359"/>
+      <c r="P209" s="360"/>
+      <c r="Q209" s="360"/>
+      <c r="R209" s="360"/>
+      <c r="S209" s="360"/>
+      <c r="T209" s="360"/>
+      <c r="U209" s="360"/>
+      <c r="V209" s="360"/>
+      <c r="W209" s="360"/>
+      <c r="X209" s="360"/>
+      <c r="Y209" s="360"/>
+      <c r="Z209" s="360"/>
+      <c r="AA209" s="360"/>
+      <c r="AB209" s="360"/>
+      <c r="AC209" s="360"/>
+      <c r="AD209" s="360"/>
+      <c r="AE209" s="360"/>
+      <c r="AF209" s="360"/>
+      <c r="AG209" s="360"/>
+      <c r="AH209" s="361"/>
     </row>
     <row r="210" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F210" s="277" t="s">
+      <c r="F210" s="251" t="s">
         <v>38</v>
       </c>
-      <c r="G210" s="278"/>
-      <c r="H210" s="278"/>
-      <c r="I210" s="278"/>
-      <c r="J210" s="279"/>
-      <c r="K210" s="179" t="s">
+      <c r="G210" s="252"/>
+      <c r="H210" s="252"/>
+      <c r="I210" s="252"/>
+      <c r="J210" s="253"/>
+      <c r="K210" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L210" s="181"/>
-      <c r="M210" s="179" t="s">
+      <c r="L210" s="220"/>
+      <c r="M210" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N210" s="181"/>
-      <c r="O210" s="345" t="s">
+      <c r="N210" s="220"/>
+      <c r="O210" s="334" t="s">
         <v>340</v>
       </c>
-      <c r="P210" s="337"/>
-      <c r="Q210" s="337"/>
-      <c r="R210" s="337"/>
-      <c r="S210" s="337"/>
-      <c r="T210" s="337"/>
-      <c r="U210" s="337"/>
-      <c r="V210" s="337"/>
-      <c r="W210" s="337"/>
-      <c r="X210" s="337"/>
-      <c r="Y210" s="337"/>
-      <c r="Z210" s="337"/>
-      <c r="AA210" s="337"/>
-      <c r="AB210" s="337"/>
-      <c r="AC210" s="337"/>
-      <c r="AD210" s="337"/>
-      <c r="AE210" s="337"/>
-      <c r="AF210" s="337"/>
-      <c r="AG210" s="337"/>
-      <c r="AH210" s="338"/>
+      <c r="P210" s="344"/>
+      <c r="Q210" s="344"/>
+      <c r="R210" s="344"/>
+      <c r="S210" s="344"/>
+      <c r="T210" s="344"/>
+      <c r="U210" s="344"/>
+      <c r="V210" s="344"/>
+      <c r="W210" s="344"/>
+      <c r="X210" s="344"/>
+      <c r="Y210" s="344"/>
+      <c r="Z210" s="344"/>
+      <c r="AA210" s="344"/>
+      <c r="AB210" s="344"/>
+      <c r="AC210" s="344"/>
+      <c r="AD210" s="344"/>
+      <c r="AE210" s="344"/>
+      <c r="AF210" s="344"/>
+      <c r="AG210" s="344"/>
+      <c r="AH210" s="345"/>
     </row>
     <row r="211" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F211" s="277" t="s">
+      <c r="F211" s="251" t="s">
         <v>39</v>
       </c>
-      <c r="G211" s="278"/>
-      <c r="H211" s="278"/>
-      <c r="I211" s="278"/>
-      <c r="J211" s="279"/>
-      <c r="K211" s="179" t="s">
+      <c r="G211" s="252"/>
+      <c r="H211" s="252"/>
+      <c r="I211" s="252"/>
+      <c r="J211" s="253"/>
+      <c r="K211" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L211" s="181"/>
-      <c r="M211" s="179" t="s">
+      <c r="L211" s="220"/>
+      <c r="M211" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N211" s="181"/>
-      <c r="O211" s="345" t="s">
+      <c r="N211" s="220"/>
+      <c r="O211" s="334" t="s">
         <v>284</v>
       </c>
-      <c r="P211" s="284"/>
-      <c r="Q211" s="284"/>
-      <c r="R211" s="284"/>
-      <c r="S211" s="284"/>
-      <c r="T211" s="284"/>
-      <c r="U211" s="284"/>
-      <c r="V211" s="284"/>
-      <c r="W211" s="284"/>
-      <c r="X211" s="284"/>
-      <c r="Y211" s="284"/>
-      <c r="Z211" s="284"/>
-      <c r="AA211" s="284"/>
-      <c r="AB211" s="284"/>
-      <c r="AC211" s="284"/>
-      <c r="AD211" s="284"/>
-      <c r="AE211" s="284"/>
-      <c r="AF211" s="284"/>
-      <c r="AG211" s="284"/>
-      <c r="AH211" s="285"/>
+      <c r="P211" s="288"/>
+      <c r="Q211" s="288"/>
+      <c r="R211" s="288"/>
+      <c r="S211" s="288"/>
+      <c r="T211" s="288"/>
+      <c r="U211" s="288"/>
+      <c r="V211" s="288"/>
+      <c r="W211" s="288"/>
+      <c r="X211" s="288"/>
+      <c r="Y211" s="288"/>
+      <c r="Z211" s="288"/>
+      <c r="AA211" s="288"/>
+      <c r="AB211" s="288"/>
+      <c r="AC211" s="288"/>
+      <c r="AD211" s="288"/>
+      <c r="AE211" s="288"/>
+      <c r="AF211" s="288"/>
+      <c r="AG211" s="288"/>
+      <c r="AH211" s="289"/>
     </row>
     <row r="212" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F212" s="326" t="s">
+      <c r="F212" s="351" t="s">
         <v>34</v>
       </c>
-      <c r="G212" s="328"/>
-      <c r="H212" s="328"/>
-      <c r="I212" s="328"/>
-      <c r="J212" s="327"/>
-      <c r="K212" s="335" t="s">
+      <c r="G212" s="362"/>
+      <c r="H212" s="362"/>
+      <c r="I212" s="362"/>
+      <c r="J212" s="352"/>
+      <c r="K212" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L212" s="288"/>
-      <c r="M212" s="335" t="s">
+      <c r="L212" s="292"/>
+      <c r="M212" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N212" s="288"/>
-      <c r="O212" s="315" t="s">
+      <c r="N212" s="292"/>
+      <c r="O212" s="310" t="s">
         <v>496</v>
       </c>
-      <c r="P212" s="321"/>
-      <c r="Q212" s="321"/>
-      <c r="R212" s="321"/>
-      <c r="S212" s="321"/>
-      <c r="T212" s="321"/>
-      <c r="U212" s="321"/>
-      <c r="V212" s="321"/>
-      <c r="W212" s="321"/>
-      <c r="X212" s="321"/>
-      <c r="Y212" s="321"/>
-      <c r="Z212" s="321"/>
-      <c r="AA212" s="321"/>
-      <c r="AB212" s="321"/>
-      <c r="AC212" s="321"/>
-      <c r="AD212" s="321"/>
-      <c r="AE212" s="321"/>
-      <c r="AF212" s="321"/>
-      <c r="AG212" s="321"/>
-      <c r="AH212" s="322"/>
+      <c r="P212" s="357"/>
+      <c r="Q212" s="357"/>
+      <c r="R212" s="357"/>
+      <c r="S212" s="357"/>
+      <c r="T212" s="357"/>
+      <c r="U212" s="357"/>
+      <c r="V212" s="357"/>
+      <c r="W212" s="357"/>
+      <c r="X212" s="357"/>
+      <c r="Y212" s="357"/>
+      <c r="Z212" s="357"/>
+      <c r="AA212" s="357"/>
+      <c r="AB212" s="357"/>
+      <c r="AC212" s="357"/>
+      <c r="AD212" s="357"/>
+      <c r="AE212" s="357"/>
+      <c r="AF212" s="357"/>
+      <c r="AG212" s="357"/>
+      <c r="AH212" s="358"/>
     </row>
     <row r="213" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F213" s="332"/>
-      <c r="G213" s="333"/>
-      <c r="H213" s="333"/>
-      <c r="I213" s="333"/>
-      <c r="J213" s="334"/>
-      <c r="K213" s="289"/>
-      <c r="L213" s="291"/>
-      <c r="M213" s="289"/>
-      <c r="N213" s="291"/>
-      <c r="O213" s="332"/>
-      <c r="P213" s="333"/>
-      <c r="Q213" s="333"/>
-      <c r="R213" s="333"/>
-      <c r="S213" s="333"/>
-      <c r="T213" s="333"/>
-      <c r="U213" s="333"/>
-      <c r="V213" s="333"/>
-      <c r="W213" s="333"/>
-      <c r="X213" s="333"/>
-      <c r="Y213" s="333"/>
-      <c r="Z213" s="333"/>
-      <c r="AA213" s="333"/>
-      <c r="AB213" s="333"/>
-      <c r="AC213" s="333"/>
-      <c r="AD213" s="333"/>
-      <c r="AE213" s="333"/>
-      <c r="AF213" s="333"/>
-      <c r="AG213" s="333"/>
-      <c r="AH213" s="334"/>
+      <c r="F213" s="338"/>
+      <c r="G213" s="368"/>
+      <c r="H213" s="368"/>
+      <c r="I213" s="368"/>
+      <c r="J213" s="369"/>
+      <c r="K213" s="293"/>
+      <c r="L213" s="295"/>
+      <c r="M213" s="293"/>
+      <c r="N213" s="295"/>
+      <c r="O213" s="338"/>
+      <c r="P213" s="368"/>
+      <c r="Q213" s="368"/>
+      <c r="R213" s="368"/>
+      <c r="S213" s="368"/>
+      <c r="T213" s="368"/>
+      <c r="U213" s="368"/>
+      <c r="V213" s="368"/>
+      <c r="W213" s="368"/>
+      <c r="X213" s="368"/>
+      <c r="Y213" s="368"/>
+      <c r="Z213" s="368"/>
+      <c r="AA213" s="368"/>
+      <c r="AB213" s="368"/>
+      <c r="AC213" s="368"/>
+      <c r="AD213" s="368"/>
+      <c r="AE213" s="368"/>
+      <c r="AF213" s="368"/>
+      <c r="AG213" s="368"/>
+      <c r="AH213" s="369"/>
     </row>
     <row r="214" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F214" s="323"/>
-      <c r="G214" s="324"/>
-      <c r="H214" s="324"/>
-      <c r="I214" s="324"/>
-      <c r="J214" s="325"/>
-      <c r="K214" s="292"/>
-      <c r="L214" s="294"/>
-      <c r="M214" s="292"/>
-      <c r="N214" s="294"/>
-      <c r="O214" s="323"/>
-      <c r="P214" s="324"/>
-      <c r="Q214" s="324"/>
-      <c r="R214" s="324"/>
-      <c r="S214" s="324"/>
-      <c r="T214" s="324"/>
-      <c r="U214" s="324"/>
-      <c r="V214" s="324"/>
-      <c r="W214" s="324"/>
-      <c r="X214" s="324"/>
-      <c r="Y214" s="324"/>
-      <c r="Z214" s="324"/>
-      <c r="AA214" s="324"/>
-      <c r="AB214" s="324"/>
-      <c r="AC214" s="324"/>
-      <c r="AD214" s="324"/>
-      <c r="AE214" s="324"/>
-      <c r="AF214" s="324"/>
-      <c r="AG214" s="324"/>
-      <c r="AH214" s="325"/>
+      <c r="F214" s="359"/>
+      <c r="G214" s="360"/>
+      <c r="H214" s="360"/>
+      <c r="I214" s="360"/>
+      <c r="J214" s="361"/>
+      <c r="K214" s="296"/>
+      <c r="L214" s="298"/>
+      <c r="M214" s="296"/>
+      <c r="N214" s="298"/>
+      <c r="O214" s="359"/>
+      <c r="P214" s="360"/>
+      <c r="Q214" s="360"/>
+      <c r="R214" s="360"/>
+      <c r="S214" s="360"/>
+      <c r="T214" s="360"/>
+      <c r="U214" s="360"/>
+      <c r="V214" s="360"/>
+      <c r="W214" s="360"/>
+      <c r="X214" s="360"/>
+      <c r="Y214" s="360"/>
+      <c r="Z214" s="360"/>
+      <c r="AA214" s="360"/>
+      <c r="AB214" s="360"/>
+      <c r="AC214" s="360"/>
+      <c r="AD214" s="360"/>
+      <c r="AE214" s="360"/>
+      <c r="AF214" s="360"/>
+      <c r="AG214" s="360"/>
+      <c r="AH214" s="361"/>
     </row>
     <row r="215" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F215" s="277" t="s">
+      <c r="F215" s="251" t="s">
         <v>265</v>
       </c>
-      <c r="G215" s="278"/>
-      <c r="H215" s="278"/>
-      <c r="I215" s="278"/>
-      <c r="J215" s="279"/>
-      <c r="K215" s="179" t="s">
+      <c r="G215" s="252"/>
+      <c r="H215" s="252"/>
+      <c r="I215" s="252"/>
+      <c r="J215" s="253"/>
+      <c r="K215" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L215" s="181"/>
-      <c r="M215" s="179" t="s">
+      <c r="L215" s="220"/>
+      <c r="M215" s="218" t="s">
         <v>36</v>
       </c>
-      <c r="N215" s="181"/>
-      <c r="O215" s="336" t="s">
+      <c r="N215" s="220"/>
+      <c r="O215" s="370" t="s">
         <v>37</v>
       </c>
-      <c r="P215" s="337"/>
-      <c r="Q215" s="337"/>
-      <c r="R215" s="337"/>
-      <c r="S215" s="337"/>
-      <c r="T215" s="337"/>
-      <c r="U215" s="337"/>
-      <c r="V215" s="337"/>
-      <c r="W215" s="337"/>
-      <c r="X215" s="337"/>
-      <c r="Y215" s="337"/>
-      <c r="Z215" s="337"/>
-      <c r="AA215" s="337"/>
-      <c r="AB215" s="337"/>
-      <c r="AC215" s="337"/>
-      <c r="AD215" s="337"/>
-      <c r="AE215" s="337"/>
-      <c r="AF215" s="337"/>
-      <c r="AG215" s="337"/>
-      <c r="AH215" s="338"/>
+      <c r="P215" s="344"/>
+      <c r="Q215" s="344"/>
+      <c r="R215" s="344"/>
+      <c r="S215" s="344"/>
+      <c r="T215" s="344"/>
+      <c r="U215" s="344"/>
+      <c r="V215" s="344"/>
+      <c r="W215" s="344"/>
+      <c r="X215" s="344"/>
+      <c r="Y215" s="344"/>
+      <c r="Z215" s="344"/>
+      <c r="AA215" s="344"/>
+      <c r="AB215" s="344"/>
+      <c r="AC215" s="344"/>
+      <c r="AD215" s="344"/>
+      <c r="AE215" s="344"/>
+      <c r="AF215" s="344"/>
+      <c r="AG215" s="344"/>
+      <c r="AH215" s="345"/>
     </row>
     <row r="216" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F216" s="277" t="s">
+      <c r="F216" s="251" t="s">
         <v>139</v>
       </c>
-      <c r="G216" s="278"/>
-      <c r="H216" s="278"/>
-      <c r="I216" s="278"/>
-      <c r="J216" s="279"/>
-      <c r="K216" s="179" t="s">
+      <c r="G216" s="252"/>
+      <c r="H216" s="252"/>
+      <c r="I216" s="252"/>
+      <c r="J216" s="253"/>
+      <c r="K216" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L216" s="181"/>
-      <c r="M216" s="179" t="s">
+      <c r="L216" s="220"/>
+      <c r="M216" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N216" s="181"/>
-      <c r="O216" s="345" t="s">
+      <c r="N216" s="220"/>
+      <c r="O216" s="334" t="s">
         <v>497</v>
       </c>
-      <c r="P216" s="337"/>
-      <c r="Q216" s="337"/>
-      <c r="R216" s="337"/>
-      <c r="S216" s="337"/>
-      <c r="T216" s="337"/>
-      <c r="U216" s="337"/>
-      <c r="V216" s="337"/>
-      <c r="W216" s="337"/>
-      <c r="X216" s="337"/>
-      <c r="Y216" s="337"/>
-      <c r="Z216" s="337"/>
-      <c r="AA216" s="337"/>
-      <c r="AB216" s="337"/>
-      <c r="AC216" s="337"/>
-      <c r="AD216" s="337"/>
-      <c r="AE216" s="337"/>
-      <c r="AF216" s="337"/>
-      <c r="AG216" s="337"/>
-      <c r="AH216" s="338"/>
+      <c r="P216" s="344"/>
+      <c r="Q216" s="344"/>
+      <c r="R216" s="344"/>
+      <c r="S216" s="344"/>
+      <c r="T216" s="344"/>
+      <c r="U216" s="344"/>
+      <c r="V216" s="344"/>
+      <c r="W216" s="344"/>
+      <c r="X216" s="344"/>
+      <c r="Y216" s="344"/>
+      <c r="Z216" s="344"/>
+      <c r="AA216" s="344"/>
+      <c r="AB216" s="344"/>
+      <c r="AC216" s="344"/>
+      <c r="AD216" s="344"/>
+      <c r="AE216" s="344"/>
+      <c r="AF216" s="344"/>
+      <c r="AG216" s="344"/>
+      <c r="AH216" s="345"/>
     </row>
     <row r="217" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F217" s="277" t="s">
+      <c r="F217" s="251" t="s">
         <v>42</v>
       </c>
-      <c r="G217" s="278"/>
-      <c r="H217" s="278"/>
-      <c r="I217" s="278"/>
-      <c r="J217" s="279"/>
-      <c r="K217" s="179" t="s">
+      <c r="G217" s="252"/>
+      <c r="H217" s="252"/>
+      <c r="I217" s="252"/>
+      <c r="J217" s="253"/>
+      <c r="K217" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L217" s="181"/>
-      <c r="M217" s="179" t="s">
+      <c r="L217" s="220"/>
+      <c r="M217" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N217" s="181"/>
-      <c r="O217" s="345" t="s">
+      <c r="N217" s="220"/>
+      <c r="O217" s="334" t="s">
         <v>492</v>
       </c>
-      <c r="P217" s="337"/>
-      <c r="Q217" s="337"/>
-      <c r="R217" s="337"/>
-      <c r="S217" s="337"/>
-      <c r="T217" s="337"/>
-      <c r="U217" s="337"/>
-      <c r="V217" s="337"/>
-      <c r="W217" s="337"/>
-      <c r="X217" s="337"/>
-      <c r="Y217" s="337"/>
-      <c r="Z217" s="337"/>
-      <c r="AA217" s="337"/>
-      <c r="AB217" s="337"/>
-      <c r="AC217" s="337"/>
-      <c r="AD217" s="337"/>
-      <c r="AE217" s="337"/>
-      <c r="AF217" s="337"/>
-      <c r="AG217" s="337"/>
-      <c r="AH217" s="338"/>
+      <c r="P217" s="344"/>
+      <c r="Q217" s="344"/>
+      <c r="R217" s="344"/>
+      <c r="S217" s="344"/>
+      <c r="T217" s="344"/>
+      <c r="U217" s="344"/>
+      <c r="V217" s="344"/>
+      <c r="W217" s="344"/>
+      <c r="X217" s="344"/>
+      <c r="Y217" s="344"/>
+      <c r="Z217" s="344"/>
+      <c r="AA217" s="344"/>
+      <c r="AB217" s="344"/>
+      <c r="AC217" s="344"/>
+      <c r="AD217" s="344"/>
+      <c r="AE217" s="344"/>
+      <c r="AF217" s="344"/>
+      <c r="AG217" s="344"/>
+      <c r="AH217" s="345"/>
     </row>
     <row r="218" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F218" s="315" t="s">
+      <c r="F218" s="310" t="s">
         <v>270</v>
       </c>
-      <c r="G218" s="321"/>
-      <c r="H218" s="321"/>
-      <c r="I218" s="321"/>
-      <c r="J218" s="322"/>
-      <c r="K218" s="326" t="s">
+      <c r="G218" s="357"/>
+      <c r="H218" s="357"/>
+      <c r="I218" s="357"/>
+      <c r="J218" s="358"/>
+      <c r="K218" s="351" t="s">
         <v>35</v>
       </c>
-      <c r="L218" s="327"/>
-      <c r="M218" s="326" t="s">
+      <c r="L218" s="352"/>
+      <c r="M218" s="351" t="s">
         <v>36</v>
       </c>
-      <c r="N218" s="327"/>
-      <c r="O218" s="326" t="s">
+      <c r="N218" s="352"/>
+      <c r="O218" s="351" t="s">
         <v>43</v>
       </c>
-      <c r="P218" s="328"/>
-      <c r="Q218" s="328"/>
-      <c r="R218" s="328"/>
-      <c r="S218" s="328"/>
-      <c r="T218" s="328"/>
-      <c r="U218" s="328"/>
-      <c r="V218" s="328"/>
-      <c r="W218" s="328"/>
-      <c r="X218" s="328"/>
-      <c r="Y218" s="328"/>
-      <c r="Z218" s="328"/>
-      <c r="AA218" s="328"/>
-      <c r="AB218" s="328"/>
-      <c r="AC218" s="328"/>
-      <c r="AD218" s="328"/>
-      <c r="AE218" s="328"/>
-      <c r="AF218" s="328"/>
-      <c r="AG218" s="328"/>
-      <c r="AH218" s="327"/>
+      <c r="P218" s="362"/>
+      <c r="Q218" s="362"/>
+      <c r="R218" s="362"/>
+      <c r="S218" s="362"/>
+      <c r="T218" s="362"/>
+      <c r="U218" s="362"/>
+      <c r="V218" s="362"/>
+      <c r="W218" s="362"/>
+      <c r="X218" s="362"/>
+      <c r="Y218" s="362"/>
+      <c r="Z218" s="362"/>
+      <c r="AA218" s="362"/>
+      <c r="AB218" s="362"/>
+      <c r="AC218" s="362"/>
+      <c r="AD218" s="362"/>
+      <c r="AE218" s="362"/>
+      <c r="AF218" s="362"/>
+      <c r="AG218" s="362"/>
+      <c r="AH218" s="352"/>
     </row>
     <row r="219" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F219" s="323"/>
-      <c r="G219" s="324"/>
-      <c r="H219" s="324"/>
-      <c r="I219" s="324"/>
-      <c r="J219" s="325"/>
-      <c r="K219" s="323"/>
-      <c r="L219" s="325"/>
-      <c r="M219" s="323"/>
-      <c r="N219" s="325"/>
-      <c r="O219" s="323"/>
-      <c r="P219" s="324"/>
-      <c r="Q219" s="324"/>
-      <c r="R219" s="324"/>
-      <c r="S219" s="324"/>
-      <c r="T219" s="324"/>
-      <c r="U219" s="324"/>
-      <c r="V219" s="324"/>
-      <c r="W219" s="324"/>
-      <c r="X219" s="324"/>
-      <c r="Y219" s="324"/>
-      <c r="Z219" s="324"/>
-      <c r="AA219" s="324"/>
-      <c r="AB219" s="324"/>
-      <c r="AC219" s="324"/>
-      <c r="AD219" s="324"/>
-      <c r="AE219" s="324"/>
-      <c r="AF219" s="324"/>
-      <c r="AG219" s="324"/>
-      <c r="AH219" s="325"/>
+      <c r="F219" s="359"/>
+      <c r="G219" s="360"/>
+      <c r="H219" s="360"/>
+      <c r="I219" s="360"/>
+      <c r="J219" s="361"/>
+      <c r="K219" s="359"/>
+      <c r="L219" s="361"/>
+      <c r="M219" s="359"/>
+      <c r="N219" s="361"/>
+      <c r="O219" s="359"/>
+      <c r="P219" s="360"/>
+      <c r="Q219" s="360"/>
+      <c r="R219" s="360"/>
+      <c r="S219" s="360"/>
+      <c r="T219" s="360"/>
+      <c r="U219" s="360"/>
+      <c r="V219" s="360"/>
+      <c r="W219" s="360"/>
+      <c r="X219" s="360"/>
+      <c r="Y219" s="360"/>
+      <c r="Z219" s="360"/>
+      <c r="AA219" s="360"/>
+      <c r="AB219" s="360"/>
+      <c r="AC219" s="360"/>
+      <c r="AD219" s="360"/>
+      <c r="AE219" s="360"/>
+      <c r="AF219" s="360"/>
+      <c r="AG219" s="360"/>
+      <c r="AH219" s="361"/>
     </row>
     <row r="220" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F220" s="55"/>
@@ -45083,6 +45084,118 @@
     </row>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="F218:J219"/>
+    <mergeCell ref="K218:L219"/>
+    <mergeCell ref="M218:N219"/>
+    <mergeCell ref="F216:J216"/>
+    <mergeCell ref="O218:AH219"/>
+    <mergeCell ref="F201:J201"/>
+    <mergeCell ref="O192:AH193"/>
+    <mergeCell ref="K215:L215"/>
+    <mergeCell ref="M215:N215"/>
+    <mergeCell ref="O201:AH201"/>
+    <mergeCell ref="O194:AH194"/>
+    <mergeCell ref="O202:AH203"/>
+    <mergeCell ref="O204:AH205"/>
+    <mergeCell ref="O206:AH207"/>
+    <mergeCell ref="O208:AH209"/>
+    <mergeCell ref="O212:AH214"/>
+    <mergeCell ref="M208:N209"/>
+    <mergeCell ref="M217:N217"/>
+    <mergeCell ref="O215:AH215"/>
+    <mergeCell ref="F210:J210"/>
+    <mergeCell ref="F211:J211"/>
+    <mergeCell ref="F215:J215"/>
+    <mergeCell ref="F208:J209"/>
+    <mergeCell ref="F212:J214"/>
+    <mergeCell ref="F174:J174"/>
+    <mergeCell ref="F175:J175"/>
+    <mergeCell ref="F176:J179"/>
+    <mergeCell ref="F180:J180"/>
+    <mergeCell ref="F181:J184"/>
+    <mergeCell ref="K195:L196"/>
+    <mergeCell ref="K191:L191"/>
+    <mergeCell ref="F191:J191"/>
+    <mergeCell ref="F194:J194"/>
+    <mergeCell ref="F189:J190"/>
+    <mergeCell ref="F192:J193"/>
+    <mergeCell ref="F195:J196"/>
+    <mergeCell ref="K175:L175"/>
+    <mergeCell ref="O210:AH210"/>
+    <mergeCell ref="O211:AH211"/>
+    <mergeCell ref="K181:L184"/>
+    <mergeCell ref="K176:L179"/>
+    <mergeCell ref="F185:J186"/>
+    <mergeCell ref="F187:J188"/>
+    <mergeCell ref="K187:L188"/>
+    <mergeCell ref="K189:L190"/>
+    <mergeCell ref="M201:N201"/>
+    <mergeCell ref="F202:J203"/>
+    <mergeCell ref="F204:J205"/>
+    <mergeCell ref="F206:J207"/>
+    <mergeCell ref="O181:AH184"/>
+    <mergeCell ref="O195:AH196"/>
+    <mergeCell ref="K194:L194"/>
+    <mergeCell ref="K201:L201"/>
+    <mergeCell ref="M192:N193"/>
+    <mergeCell ref="M194:N194"/>
+    <mergeCell ref="M195:N196"/>
+    <mergeCell ref="K185:L186"/>
+    <mergeCell ref="K180:L180"/>
+    <mergeCell ref="K192:L193"/>
+    <mergeCell ref="K217:L217"/>
+    <mergeCell ref="K204:L205"/>
+    <mergeCell ref="K206:L207"/>
+    <mergeCell ref="K211:L211"/>
+    <mergeCell ref="K210:L210"/>
+    <mergeCell ref="K202:L203"/>
+    <mergeCell ref="K212:L214"/>
+    <mergeCell ref="K216:L216"/>
+    <mergeCell ref="M216:N216"/>
+    <mergeCell ref="K208:L209"/>
+    <mergeCell ref="M206:N207"/>
+    <mergeCell ref="M211:N211"/>
+    <mergeCell ref="M210:N210"/>
+    <mergeCell ref="M202:N203"/>
+    <mergeCell ref="M212:N214"/>
+    <mergeCell ref="M204:N205"/>
+    <mergeCell ref="O216:AH216"/>
+    <mergeCell ref="O217:AH217"/>
+    <mergeCell ref="M174:N174"/>
+    <mergeCell ref="K161:Z161"/>
+    <mergeCell ref="F217:J217"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AA155:AH155"/>
+    <mergeCell ref="K151:Z151"/>
+    <mergeCell ref="K152:Z152"/>
+    <mergeCell ref="K153:Z153"/>
+    <mergeCell ref="K155:Z155"/>
+    <mergeCell ref="K156:Z160"/>
+    <mergeCell ref="AA156:AH160"/>
+    <mergeCell ref="AA162:AH163"/>
+    <mergeCell ref="AA161:AH161"/>
+    <mergeCell ref="AA152:AH152"/>
+    <mergeCell ref="AA154:AH154"/>
+    <mergeCell ref="M175:N175"/>
+    <mergeCell ref="M176:N179"/>
+    <mergeCell ref="M180:N180"/>
+    <mergeCell ref="M181:N184"/>
+    <mergeCell ref="M185:N186"/>
+    <mergeCell ref="M187:N188"/>
+    <mergeCell ref="M189:N190"/>
+    <mergeCell ref="M191:N191"/>
+    <mergeCell ref="O185:AH186"/>
+    <mergeCell ref="O187:AH188"/>
+    <mergeCell ref="O189:AH190"/>
+    <mergeCell ref="O191:AH191"/>
+    <mergeCell ref="O175:AH175"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
@@ -45107,118 +45220,6 @@
     <mergeCell ref="K162:Z163"/>
     <mergeCell ref="O1:R3"/>
     <mergeCell ref="S1:Z3"/>
-    <mergeCell ref="M175:N175"/>
-    <mergeCell ref="M176:N179"/>
-    <mergeCell ref="M180:N180"/>
-    <mergeCell ref="M181:N184"/>
-    <mergeCell ref="M185:N186"/>
-    <mergeCell ref="M187:N188"/>
-    <mergeCell ref="M189:N190"/>
-    <mergeCell ref="M191:N191"/>
-    <mergeCell ref="O185:AH186"/>
-    <mergeCell ref="O187:AH188"/>
-    <mergeCell ref="O189:AH190"/>
-    <mergeCell ref="O191:AH191"/>
-    <mergeCell ref="O175:AH175"/>
-    <mergeCell ref="O216:AH216"/>
-    <mergeCell ref="O217:AH217"/>
-    <mergeCell ref="M174:N174"/>
-    <mergeCell ref="K161:Z161"/>
-    <mergeCell ref="F217:J217"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AA155:AH155"/>
-    <mergeCell ref="K151:Z151"/>
-    <mergeCell ref="K152:Z152"/>
-    <mergeCell ref="K153:Z153"/>
-    <mergeCell ref="K155:Z155"/>
-    <mergeCell ref="K156:Z160"/>
-    <mergeCell ref="AA156:AH160"/>
-    <mergeCell ref="AA162:AH163"/>
-    <mergeCell ref="AA161:AH161"/>
-    <mergeCell ref="AA152:AH152"/>
-    <mergeCell ref="AA154:AH154"/>
-    <mergeCell ref="K217:L217"/>
-    <mergeCell ref="K204:L205"/>
-    <mergeCell ref="K206:L207"/>
-    <mergeCell ref="K211:L211"/>
-    <mergeCell ref="K210:L210"/>
-    <mergeCell ref="K202:L203"/>
-    <mergeCell ref="K212:L214"/>
-    <mergeCell ref="K216:L216"/>
-    <mergeCell ref="M216:N216"/>
-    <mergeCell ref="K208:L209"/>
-    <mergeCell ref="M206:N207"/>
-    <mergeCell ref="M211:N211"/>
-    <mergeCell ref="M210:N210"/>
-    <mergeCell ref="M202:N203"/>
-    <mergeCell ref="M212:N214"/>
-    <mergeCell ref="M204:N205"/>
-    <mergeCell ref="O210:AH210"/>
-    <mergeCell ref="O211:AH211"/>
-    <mergeCell ref="K181:L184"/>
-    <mergeCell ref="K176:L179"/>
-    <mergeCell ref="F185:J186"/>
-    <mergeCell ref="F187:J188"/>
-    <mergeCell ref="K187:L188"/>
-    <mergeCell ref="K189:L190"/>
-    <mergeCell ref="M201:N201"/>
-    <mergeCell ref="F202:J203"/>
-    <mergeCell ref="F204:J205"/>
-    <mergeCell ref="F206:J207"/>
-    <mergeCell ref="O181:AH184"/>
-    <mergeCell ref="O195:AH196"/>
-    <mergeCell ref="K194:L194"/>
-    <mergeCell ref="K201:L201"/>
-    <mergeCell ref="M192:N193"/>
-    <mergeCell ref="M194:N194"/>
-    <mergeCell ref="M195:N196"/>
-    <mergeCell ref="K185:L186"/>
-    <mergeCell ref="K180:L180"/>
-    <mergeCell ref="K192:L193"/>
-    <mergeCell ref="F174:J174"/>
-    <mergeCell ref="F175:J175"/>
-    <mergeCell ref="F176:J179"/>
-    <mergeCell ref="F180:J180"/>
-    <mergeCell ref="F181:J184"/>
-    <mergeCell ref="K195:L196"/>
-    <mergeCell ref="K191:L191"/>
-    <mergeCell ref="F191:J191"/>
-    <mergeCell ref="F194:J194"/>
-    <mergeCell ref="F189:J190"/>
-    <mergeCell ref="F192:J193"/>
-    <mergeCell ref="F195:J196"/>
-    <mergeCell ref="K175:L175"/>
-    <mergeCell ref="F218:J219"/>
-    <mergeCell ref="K218:L219"/>
-    <mergeCell ref="M218:N219"/>
-    <mergeCell ref="F216:J216"/>
-    <mergeCell ref="O218:AH219"/>
-    <mergeCell ref="F201:J201"/>
-    <mergeCell ref="O192:AH193"/>
-    <mergeCell ref="K215:L215"/>
-    <mergeCell ref="M215:N215"/>
-    <mergeCell ref="O201:AH201"/>
-    <mergeCell ref="O194:AH194"/>
-    <mergeCell ref="O202:AH203"/>
-    <mergeCell ref="O204:AH205"/>
-    <mergeCell ref="O206:AH207"/>
-    <mergeCell ref="O208:AH209"/>
-    <mergeCell ref="O212:AH214"/>
-    <mergeCell ref="M208:N209"/>
-    <mergeCell ref="M217:N217"/>
-    <mergeCell ref="O215:AH215"/>
-    <mergeCell ref="F210:J210"/>
-    <mergeCell ref="F211:J211"/>
-    <mergeCell ref="F215:J215"/>
-    <mergeCell ref="F208:J209"/>
-    <mergeCell ref="F212:J214"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>

--- a/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
+++ b/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC89E0E-4170-4F2C-B00E-ADC5B38EEB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83854C20-3F73-4EE6-BF4D-4AA6D5A0E79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="3045" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2220" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="28" r:id="rId1"/>
@@ -8831,8 +8831,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="31" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -8948,86 +9030,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -9038,15 +9048,6 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9055,33 +9056,6 @@
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9164,14 +9138,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9221,6 +9213,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -9233,6 +9234,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -9240,6 +9247,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -9260,38 +9279,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9299,56 +9339,41 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9365,67 +9390,42 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="パーセント 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -27487,12 +27487,12 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="173">
+      <c r="I25" s="174">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>43336</v>
-      </c>
-      <c r="J25" s="173"/>
-      <c r="K25" s="173"/>
+        <v>45565</v>
+      </c>
+      <c r="J25" s="174"/>
+      <c r="K25" s="174"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="3"/>
@@ -28085,55 +28085,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="217" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="183"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-      <c r="M1" s="184"/>
-      <c r="N1" s="185"/>
-      <c r="O1" s="190" t="s">
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="191"/>
-      <c r="Q1" s="191"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="199" t="s">
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="227" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
-      <c r="Y1" s="200"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="180" t="s">
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="208" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="182"/>
-      <c r="AC1" s="208" t="str">
+      <c r="AB1" s="210"/>
+      <c r="AC1" s="236" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="209"/>
-      <c r="AE1" s="209"/>
-      <c r="AF1" s="210"/>
-      <c r="AG1" s="174">
+      <c r="AD1" s="237"/>
+      <c r="AE1" s="237"/>
+      <c r="AF1" s="238"/>
+      <c r="AG1" s="202">
         <f>IF(D8="","",D8)</f>
-        <v>43336</v>
-      </c>
-      <c r="AH1" s="175"/>
-      <c r="AI1" s="176"/>
+        <v>45565</v>
+      </c>
+      <c r="AH1" s="203"/>
+      <c r="AI1" s="204"/>
       <c r="AJ1" s="7"/>
       <c r="AK1" s="7"/>
       <c r="AL1" s="7"/>
@@ -28141,51 +28141,51 @@
       <c r="AN1" s="8"/>
     </row>
     <row r="2" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="180" t="s">
+      <c r="A2" s="208" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="181"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="184"/>
-      <c r="K2" s="184"/>
-      <c r="L2" s="184"/>
-      <c r="M2" s="184"/>
-      <c r="N2" s="185"/>
-      <c r="O2" s="193"/>
-      <c r="P2" s="194"/>
-      <c r="Q2" s="194"/>
-      <c r="R2" s="195"/>
-      <c r="S2" s="202"/>
-      <c r="T2" s="203"/>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="203"/>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="204"/>
-      <c r="AA2" s="180" t="s">
+      <c r="B2" s="209"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="213"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="222"/>
+      <c r="Q2" s="222"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="230"/>
+      <c r="T2" s="231"/>
+      <c r="U2" s="231"/>
+      <c r="V2" s="231"/>
+      <c r="W2" s="231"/>
+      <c r="X2" s="231"/>
+      <c r="Y2" s="231"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="208" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="182"/>
-      <c r="AC2" s="186" t="str">
+      <c r="AB2" s="210"/>
+      <c r="AC2" s="214" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="187"/>
-      <c r="AE2" s="187"/>
-      <c r="AF2" s="188"/>
-      <c r="AG2" s="174" t="str">
+      <c r="AD2" s="215"/>
+      <c r="AE2" s="215"/>
+      <c r="AF2" s="216"/>
+      <c r="AG2" s="202" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="175"/>
-      <c r="AI2" s="176"/>
+      <c r="AH2" s="203"/>
+      <c r="AI2" s="204"/>
       <c r="AJ2" s="7"/>
       <c r="AK2" s="7"/>
       <c r="AL2" s="7"/>
@@ -28193,43 +28193,43 @@
       <c r="AN2" s="7"/>
     </row>
     <row r="3" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="180" t="s">
+      <c r="A3" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="181"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="211"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
-      <c r="M3" s="184"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="196"/>
-      <c r="P3" s="197"/>
-      <c r="Q3" s="197"/>
-      <c r="R3" s="198"/>
-      <c r="S3" s="205"/>
-      <c r="T3" s="206"/>
-      <c r="U3" s="206"/>
-      <c r="V3" s="206"/>
-      <c r="W3" s="206"/>
-      <c r="X3" s="206"/>
-      <c r="Y3" s="206"/>
-      <c r="Z3" s="207"/>
-      <c r="AA3" s="180"/>
-      <c r="AB3" s="182"/>
-      <c r="AC3" s="208"/>
-      <c r="AD3" s="209"/>
-      <c r="AE3" s="209"/>
-      <c r="AF3" s="210"/>
-      <c r="AG3" s="174"/>
-      <c r="AH3" s="175"/>
-      <c r="AI3" s="176"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="239"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="213"/>
+      <c r="O3" s="224"/>
+      <c r="P3" s="225"/>
+      <c r="Q3" s="225"/>
+      <c r="R3" s="226"/>
+      <c r="S3" s="233"/>
+      <c r="T3" s="234"/>
+      <c r="U3" s="234"/>
+      <c r="V3" s="234"/>
+      <c r="W3" s="234"/>
+      <c r="X3" s="234"/>
+      <c r="Y3" s="234"/>
+      <c r="Z3" s="235"/>
+      <c r="AA3" s="208"/>
+      <c r="AB3" s="210"/>
+      <c r="AC3" s="236"/>
+      <c r="AD3" s="237"/>
+      <c r="AE3" s="237"/>
+      <c r="AF3" s="238"/>
+      <c r="AG3" s="202"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="204"/>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
       <c r="AL3" s="7"/>
@@ -28266,1190 +28266,1034 @@
       <c r="A7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="177" t="s">
+      <c r="B7" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="178"/>
-      <c r="D7" s="177" t="s">
+      <c r="C7" s="206"/>
+      <c r="D7" s="205" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="179"/>
-      <c r="F7" s="178"/>
-      <c r="G7" s="177" t="s">
+      <c r="E7" s="207"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="179"/>
-      <c r="I7" s="178"/>
-      <c r="J7" s="177" t="s">
+      <c r="H7" s="207"/>
+      <c r="I7" s="206"/>
+      <c r="J7" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="179"/>
-      <c r="L7" s="179"/>
-      <c r="M7" s="179"/>
-      <c r="N7" s="179"/>
-      <c r="O7" s="179"/>
-      <c r="P7" s="178"/>
-      <c r="Q7" s="177" t="s">
+      <c r="K7" s="207"/>
+      <c r="L7" s="207"/>
+      <c r="M7" s="207"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
+      <c r="P7" s="206"/>
+      <c r="Q7" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="R7" s="179"/>
-      <c r="S7" s="179"/>
-      <c r="T7" s="179"/>
-      <c r="U7" s="179"/>
-      <c r="V7" s="179"/>
-      <c r="W7" s="179"/>
-      <c r="X7" s="179"/>
-      <c r="Y7" s="179"/>
-      <c r="Z7" s="179"/>
-      <c r="AA7" s="179"/>
-      <c r="AB7" s="179"/>
-      <c r="AC7" s="179"/>
-      <c r="AD7" s="179"/>
-      <c r="AE7" s="178"/>
-      <c r="AF7" s="177" t="s">
+      <c r="R7" s="207"/>
+      <c r="S7" s="207"/>
+      <c r="T7" s="207"/>
+      <c r="U7" s="207"/>
+      <c r="V7" s="207"/>
+      <c r="W7" s="207"/>
+      <c r="X7" s="207"/>
+      <c r="Y7" s="207"/>
+      <c r="Z7" s="207"/>
+      <c r="AA7" s="207"/>
+      <c r="AB7" s="207"/>
+      <c r="AC7" s="207"/>
+      <c r="AD7" s="207"/>
+      <c r="AE7" s="206"/>
+      <c r="AF7" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="179"/>
-      <c r="AH7" s="179"/>
-      <c r="AI7" s="178"/>
+      <c r="AG7" s="207"/>
+      <c r="AH7" s="207"/>
+      <c r="AI7" s="206"/>
     </row>
     <row r="8" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="90">
         <v>1</v>
       </c>
-      <c r="B8" s="224" t="s">
+      <c r="B8" s="188" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="225"/>
-      <c r="D8" s="226">
-        <v>43336</v>
-      </c>
-      <c r="E8" s="227"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="229" t="s">
+      <c r="C8" s="189"/>
+      <c r="D8" s="190">
+        <v>45565</v>
+      </c>
+      <c r="E8" s="191"/>
+      <c r="F8" s="192"/>
+      <c r="G8" s="193" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="230"/>
-      <c r="I8" s="231"/>
-      <c r="J8" s="232" t="s">
+      <c r="H8" s="194"/>
+      <c r="I8" s="195"/>
+      <c r="J8" s="196" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="234"/>
-      <c r="Q8" s="235" t="s">
+      <c r="K8" s="197"/>
+      <c r="L8" s="197"/>
+      <c r="M8" s="197"/>
+      <c r="N8" s="197"/>
+      <c r="O8" s="197"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="199" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="236"/>
-      <c r="S8" s="236"/>
-      <c r="T8" s="236"/>
-      <c r="U8" s="236"/>
-      <c r="V8" s="236"/>
-      <c r="W8" s="236"/>
-      <c r="X8" s="236"/>
-      <c r="Y8" s="236"/>
-      <c r="Z8" s="236"/>
-      <c r="AA8" s="236"/>
-      <c r="AB8" s="236"/>
-      <c r="AC8" s="236"/>
-      <c r="AD8" s="236"/>
-      <c r="AE8" s="237"/>
-      <c r="AF8" s="232" t="s">
+      <c r="R8" s="200"/>
+      <c r="S8" s="200"/>
+      <c r="T8" s="200"/>
+      <c r="U8" s="200"/>
+      <c r="V8" s="200"/>
+      <c r="W8" s="200"/>
+      <c r="X8" s="200"/>
+      <c r="Y8" s="200"/>
+      <c r="Z8" s="200"/>
+      <c r="AA8" s="200"/>
+      <c r="AB8" s="200"/>
+      <c r="AC8" s="200"/>
+      <c r="AD8" s="200"/>
+      <c r="AE8" s="201"/>
+      <c r="AF8" s="196" t="s">
         <v>23</v>
       </c>
-      <c r="AG8" s="233"/>
-      <c r="AH8" s="233"/>
-      <c r="AI8" s="234"/>
+      <c r="AG8" s="197"/>
+      <c r="AH8" s="197"/>
+      <c r="AI8" s="198"/>
     </row>
     <row r="9" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="89"/>
-      <c r="B9" s="212"/>
-      <c r="C9" s="213"/>
-      <c r="D9" s="214"/>
-      <c r="E9" s="215"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="214"/>
-      <c r="H9" s="217"/>
-      <c r="I9" s="213"/>
-      <c r="J9" s="218"/>
-      <c r="K9" s="219"/>
-      <c r="L9" s="219"/>
-      <c r="M9" s="219"/>
-      <c r="N9" s="219"/>
-      <c r="O9" s="219"/>
-      <c r="P9" s="220"/>
-      <c r="Q9" s="221"/>
-      <c r="R9" s="222"/>
-      <c r="S9" s="222"/>
-      <c r="T9" s="222"/>
-      <c r="U9" s="222"/>
-      <c r="V9" s="222"/>
-      <c r="W9" s="222"/>
-      <c r="X9" s="222"/>
-      <c r="Y9" s="222"/>
-      <c r="Z9" s="222"/>
-      <c r="AA9" s="222"/>
-      <c r="AB9" s="222"/>
-      <c r="AC9" s="222"/>
-      <c r="AD9" s="222"/>
-      <c r="AE9" s="223"/>
-      <c r="AF9" s="218"/>
-      <c r="AG9" s="219"/>
-      <c r="AH9" s="219"/>
-      <c r="AI9" s="220"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="178"/>
+      <c r="F9" s="179"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="180"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="181"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="182"/>
+      <c r="M9" s="182"/>
+      <c r="N9" s="182"/>
+      <c r="O9" s="182"/>
+      <c r="P9" s="183"/>
+      <c r="Q9" s="184"/>
+      <c r="R9" s="185"/>
+      <c r="S9" s="185"/>
+      <c r="T9" s="185"/>
+      <c r="U9" s="185"/>
+      <c r="V9" s="185"/>
+      <c r="W9" s="185"/>
+      <c r="X9" s="185"/>
+      <c r="Y9" s="185"/>
+      <c r="Z9" s="185"/>
+      <c r="AA9" s="185"/>
+      <c r="AB9" s="185"/>
+      <c r="AC9" s="185"/>
+      <c r="AD9" s="185"/>
+      <c r="AE9" s="186"/>
+      <c r="AF9" s="181"/>
+      <c r="AG9" s="182"/>
+      <c r="AH9" s="182"/>
+      <c r="AI9" s="183"/>
     </row>
     <row r="10" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="89"/>
-      <c r="B10" s="212"/>
-      <c r="C10" s="213"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="216"/>
-      <c r="G10" s="212"/>
-      <c r="H10" s="217"/>
-      <c r="I10" s="213"/>
-      <c r="J10" s="218"/>
-      <c r="K10" s="219"/>
-      <c r="L10" s="219"/>
-      <c r="M10" s="219"/>
-      <c r="N10" s="219"/>
-      <c r="O10" s="219"/>
-      <c r="P10" s="220"/>
-      <c r="Q10" s="221"/>
-      <c r="R10" s="222"/>
-      <c r="S10" s="222"/>
-      <c r="T10" s="222"/>
-      <c r="U10" s="222"/>
-      <c r="V10" s="222"/>
-      <c r="W10" s="222"/>
-      <c r="X10" s="222"/>
-      <c r="Y10" s="222"/>
-      <c r="Z10" s="222"/>
-      <c r="AA10" s="222"/>
-      <c r="AB10" s="222"/>
-      <c r="AC10" s="222"/>
-      <c r="AD10" s="222"/>
-      <c r="AE10" s="223"/>
-      <c r="AF10" s="218"/>
-      <c r="AG10" s="219"/>
-      <c r="AH10" s="219"/>
-      <c r="AI10" s="220"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="177"/>
+      <c r="E10" s="178"/>
+      <c r="F10" s="179"/>
+      <c r="G10" s="175"/>
+      <c r="H10" s="180"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="181"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="182"/>
+      <c r="M10" s="182"/>
+      <c r="N10" s="182"/>
+      <c r="O10" s="182"/>
+      <c r="P10" s="183"/>
+      <c r="Q10" s="184"/>
+      <c r="R10" s="185"/>
+      <c r="S10" s="185"/>
+      <c r="T10" s="185"/>
+      <c r="U10" s="185"/>
+      <c r="V10" s="185"/>
+      <c r="W10" s="185"/>
+      <c r="X10" s="185"/>
+      <c r="Y10" s="185"/>
+      <c r="Z10" s="185"/>
+      <c r="AA10" s="185"/>
+      <c r="AB10" s="185"/>
+      <c r="AC10" s="185"/>
+      <c r="AD10" s="185"/>
+      <c r="AE10" s="186"/>
+      <c r="AF10" s="181"/>
+      <c r="AG10" s="182"/>
+      <c r="AH10" s="182"/>
+      <c r="AI10" s="183"/>
     </row>
     <row r="11" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="89"/>
-      <c r="B11" s="212"/>
-      <c r="C11" s="213"/>
-      <c r="D11" s="214"/>
-      <c r="E11" s="215"/>
-      <c r="F11" s="216"/>
-      <c r="G11" s="212"/>
-      <c r="H11" s="217"/>
-      <c r="I11" s="213"/>
-      <c r="J11" s="218"/>
-      <c r="K11" s="219"/>
-      <c r="L11" s="219"/>
-      <c r="M11" s="219"/>
-      <c r="N11" s="219"/>
-      <c r="O11" s="219"/>
-      <c r="P11" s="220"/>
-      <c r="Q11" s="221"/>
-      <c r="R11" s="222"/>
-      <c r="S11" s="222"/>
-      <c r="T11" s="222"/>
-      <c r="U11" s="222"/>
-      <c r="V11" s="222"/>
-      <c r="W11" s="222"/>
-      <c r="X11" s="222"/>
-      <c r="Y11" s="222"/>
-      <c r="Z11" s="222"/>
-      <c r="AA11" s="222"/>
-      <c r="AB11" s="222"/>
-      <c r="AC11" s="222"/>
-      <c r="AD11" s="222"/>
-      <c r="AE11" s="223"/>
-      <c r="AF11" s="218"/>
-      <c r="AG11" s="219"/>
-      <c r="AH11" s="219"/>
-      <c r="AI11" s="220"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="177"/>
+      <c r="E11" s="178"/>
+      <c r="F11" s="179"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="180"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="182"/>
+      <c r="M11" s="182"/>
+      <c r="N11" s="182"/>
+      <c r="O11" s="182"/>
+      <c r="P11" s="183"/>
+      <c r="Q11" s="184"/>
+      <c r="R11" s="185"/>
+      <c r="S11" s="185"/>
+      <c r="T11" s="185"/>
+      <c r="U11" s="185"/>
+      <c r="V11" s="185"/>
+      <c r="W11" s="185"/>
+      <c r="X11" s="185"/>
+      <c r="Y11" s="185"/>
+      <c r="Z11" s="185"/>
+      <c r="AA11" s="185"/>
+      <c r="AB11" s="185"/>
+      <c r="AC11" s="185"/>
+      <c r="AD11" s="185"/>
+      <c r="AE11" s="186"/>
+      <c r="AF11" s="181"/>
+      <c r="AG11" s="182"/>
+      <c r="AH11" s="182"/>
+      <c r="AI11" s="183"/>
     </row>
     <row r="12" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="89"/>
-      <c r="B12" s="212"/>
-      <c r="C12" s="213"/>
-      <c r="D12" s="214"/>
-      <c r="E12" s="215"/>
-      <c r="F12" s="216"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="217"/>
-      <c r="I12" s="213"/>
-      <c r="J12" s="218"/>
-      <c r="K12" s="219"/>
-      <c r="L12" s="219"/>
-      <c r="M12" s="219"/>
-      <c r="N12" s="219"/>
-      <c r="O12" s="219"/>
-      <c r="P12" s="220"/>
-      <c r="Q12" s="221"/>
-      <c r="R12" s="222"/>
-      <c r="S12" s="222"/>
-      <c r="T12" s="222"/>
-      <c r="U12" s="222"/>
-      <c r="V12" s="222"/>
-      <c r="W12" s="222"/>
-      <c r="X12" s="222"/>
-      <c r="Y12" s="222"/>
-      <c r="Z12" s="222"/>
-      <c r="AA12" s="222"/>
-      <c r="AB12" s="222"/>
-      <c r="AC12" s="222"/>
-      <c r="AD12" s="222"/>
-      <c r="AE12" s="223"/>
-      <c r="AF12" s="218"/>
-      <c r="AG12" s="219"/>
-      <c r="AH12" s="219"/>
-      <c r="AI12" s="220"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="177"/>
+      <c r="E12" s="178"/>
+      <c r="F12" s="179"/>
+      <c r="G12" s="175"/>
+      <c r="H12" s="180"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="182"/>
+      <c r="M12" s="182"/>
+      <c r="N12" s="182"/>
+      <c r="O12" s="182"/>
+      <c r="P12" s="183"/>
+      <c r="Q12" s="184"/>
+      <c r="R12" s="185"/>
+      <c r="S12" s="185"/>
+      <c r="T12" s="185"/>
+      <c r="U12" s="185"/>
+      <c r="V12" s="185"/>
+      <c r="W12" s="185"/>
+      <c r="X12" s="185"/>
+      <c r="Y12" s="185"/>
+      <c r="Z12" s="185"/>
+      <c r="AA12" s="185"/>
+      <c r="AB12" s="185"/>
+      <c r="AC12" s="185"/>
+      <c r="AD12" s="185"/>
+      <c r="AE12" s="186"/>
+      <c r="AF12" s="181"/>
+      <c r="AG12" s="182"/>
+      <c r="AH12" s="182"/>
+      <c r="AI12" s="183"/>
     </row>
     <row r="13" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="89"/>
-      <c r="B13" s="212"/>
-      <c r="C13" s="213"/>
-      <c r="D13" s="214"/>
-      <c r="E13" s="215"/>
-      <c r="F13" s="216"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="217"/>
-      <c r="I13" s="213"/>
-      <c r="J13" s="218"/>
-      <c r="K13" s="219"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
-      <c r="O13" s="219"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="221"/>
-      <c r="R13" s="222"/>
-      <c r="S13" s="222"/>
-      <c r="T13" s="222"/>
-      <c r="U13" s="222"/>
-      <c r="V13" s="222"/>
-      <c r="W13" s="222"/>
-      <c r="X13" s="222"/>
-      <c r="Y13" s="222"/>
-      <c r="Z13" s="222"/>
-      <c r="AA13" s="222"/>
-      <c r="AB13" s="222"/>
-      <c r="AC13" s="222"/>
-      <c r="AD13" s="222"/>
-      <c r="AE13" s="223"/>
-      <c r="AF13" s="218"/>
-      <c r="AG13" s="219"/>
-      <c r="AH13" s="219"/>
-      <c r="AI13" s="220"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="177"/>
+      <c r="E13" s="178"/>
+      <c r="F13" s="179"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="182"/>
+      <c r="L13" s="182"/>
+      <c r="M13" s="182"/>
+      <c r="N13" s="182"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="183"/>
+      <c r="Q13" s="184"/>
+      <c r="R13" s="185"/>
+      <c r="S13" s="185"/>
+      <c r="T13" s="185"/>
+      <c r="U13" s="185"/>
+      <c r="V13" s="185"/>
+      <c r="W13" s="185"/>
+      <c r="X13" s="185"/>
+      <c r="Y13" s="185"/>
+      <c r="Z13" s="185"/>
+      <c r="AA13" s="185"/>
+      <c r="AB13" s="185"/>
+      <c r="AC13" s="185"/>
+      <c r="AD13" s="185"/>
+      <c r="AE13" s="186"/>
+      <c r="AF13" s="181"/>
+      <c r="AG13" s="182"/>
+      <c r="AH13" s="182"/>
+      <c r="AI13" s="183"/>
     </row>
     <row r="14" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="89"/>
-      <c r="B14" s="212"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="215"/>
-      <c r="F14" s="216"/>
-      <c r="G14" s="212"/>
-      <c r="H14" s="217"/>
-      <c r="I14" s="213"/>
-      <c r="J14" s="218"/>
-      <c r="K14" s="219"/>
-      <c r="L14" s="219"/>
-      <c r="M14" s="219"/>
-      <c r="N14" s="219"/>
-      <c r="O14" s="219"/>
-      <c r="P14" s="220"/>
-      <c r="Q14" s="221"/>
-      <c r="R14" s="222"/>
-      <c r="S14" s="222"/>
-      <c r="T14" s="222"/>
-      <c r="U14" s="222"/>
-      <c r="V14" s="222"/>
-      <c r="W14" s="222"/>
-      <c r="X14" s="222"/>
-      <c r="Y14" s="222"/>
-      <c r="Z14" s="222"/>
-      <c r="AA14" s="222"/>
-      <c r="AB14" s="222"/>
-      <c r="AC14" s="222"/>
-      <c r="AD14" s="222"/>
-      <c r="AE14" s="223"/>
-      <c r="AF14" s="218"/>
-      <c r="AG14" s="219"/>
-      <c r="AH14" s="219"/>
-      <c r="AI14" s="220"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="177"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="179"/>
+      <c r="G14" s="175"/>
+      <c r="H14" s="180"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="182"/>
+      <c r="L14" s="182"/>
+      <c r="M14" s="182"/>
+      <c r="N14" s="182"/>
+      <c r="O14" s="182"/>
+      <c r="P14" s="183"/>
+      <c r="Q14" s="184"/>
+      <c r="R14" s="185"/>
+      <c r="S14" s="185"/>
+      <c r="T14" s="185"/>
+      <c r="U14" s="185"/>
+      <c r="V14" s="185"/>
+      <c r="W14" s="185"/>
+      <c r="X14" s="185"/>
+      <c r="Y14" s="185"/>
+      <c r="Z14" s="185"/>
+      <c r="AA14" s="185"/>
+      <c r="AB14" s="185"/>
+      <c r="AC14" s="185"/>
+      <c r="AD14" s="185"/>
+      <c r="AE14" s="186"/>
+      <c r="AF14" s="181"/>
+      <c r="AG14" s="182"/>
+      <c r="AH14" s="182"/>
+      <c r="AI14" s="183"/>
     </row>
     <row r="15" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="89"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="214"/>
-      <c r="E15" s="215"/>
-      <c r="F15" s="216"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="217"/>
-      <c r="I15" s="213"/>
-      <c r="J15" s="218"/>
-      <c r="K15" s="219"/>
-      <c r="L15" s="219"/>
-      <c r="M15" s="219"/>
-      <c r="N15" s="219"/>
-      <c r="O15" s="219"/>
-      <c r="P15" s="220"/>
-      <c r="Q15" s="221"/>
-      <c r="R15" s="222"/>
-      <c r="S15" s="222"/>
-      <c r="T15" s="222"/>
-      <c r="U15" s="222"/>
-      <c r="V15" s="222"/>
-      <c r="W15" s="222"/>
-      <c r="X15" s="222"/>
-      <c r="Y15" s="222"/>
-      <c r="Z15" s="222"/>
-      <c r="AA15" s="222"/>
-      <c r="AB15" s="222"/>
-      <c r="AC15" s="222"/>
-      <c r="AD15" s="222"/>
-      <c r="AE15" s="223"/>
-      <c r="AF15" s="218"/>
-      <c r="AG15" s="219"/>
-      <c r="AH15" s="219"/>
-      <c r="AI15" s="220"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="175"/>
+      <c r="H15" s="180"/>
+      <c r="I15" s="176"/>
+      <c r="J15" s="181"/>
+      <c r="K15" s="182"/>
+      <c r="L15" s="182"/>
+      <c r="M15" s="182"/>
+      <c r="N15" s="182"/>
+      <c r="O15" s="182"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="184"/>
+      <c r="R15" s="185"/>
+      <c r="S15" s="185"/>
+      <c r="T15" s="185"/>
+      <c r="U15" s="185"/>
+      <c r="V15" s="185"/>
+      <c r="W15" s="185"/>
+      <c r="X15" s="185"/>
+      <c r="Y15" s="185"/>
+      <c r="Z15" s="185"/>
+      <c r="AA15" s="185"/>
+      <c r="AB15" s="185"/>
+      <c r="AC15" s="185"/>
+      <c r="AD15" s="185"/>
+      <c r="AE15" s="186"/>
+      <c r="AF15" s="181"/>
+      <c r="AG15" s="182"/>
+      <c r="AH15" s="182"/>
+      <c r="AI15" s="183"/>
     </row>
     <row r="16" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="89"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="214"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="216"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="217"/>
-      <c r="I16" s="213"/>
-      <c r="J16" s="218"/>
-      <c r="K16" s="219"/>
-      <c r="L16" s="219"/>
-      <c r="M16" s="219"/>
-      <c r="N16" s="219"/>
-      <c r="O16" s="219"/>
-      <c r="P16" s="220"/>
-      <c r="Q16" s="221"/>
-      <c r="R16" s="222"/>
-      <c r="S16" s="222"/>
-      <c r="T16" s="222"/>
-      <c r="U16" s="222"/>
-      <c r="V16" s="222"/>
-      <c r="W16" s="222"/>
-      <c r="X16" s="222"/>
-      <c r="Y16" s="222"/>
-      <c r="Z16" s="222"/>
-      <c r="AA16" s="222"/>
-      <c r="AB16" s="222"/>
-      <c r="AC16" s="222"/>
-      <c r="AD16" s="222"/>
-      <c r="AE16" s="223"/>
-      <c r="AF16" s="218"/>
-      <c r="AG16" s="219"/>
-      <c r="AH16" s="219"/>
-      <c r="AI16" s="220"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="177"/>
+      <c r="E16" s="178"/>
+      <c r="F16" s="179"/>
+      <c r="G16" s="175"/>
+      <c r="H16" s="180"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="181"/>
+      <c r="K16" s="182"/>
+      <c r="L16" s="182"/>
+      <c r="M16" s="182"/>
+      <c r="N16" s="182"/>
+      <c r="O16" s="182"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="184"/>
+      <c r="R16" s="185"/>
+      <c r="S16" s="185"/>
+      <c r="T16" s="185"/>
+      <c r="U16" s="185"/>
+      <c r="V16" s="185"/>
+      <c r="W16" s="185"/>
+      <c r="X16" s="185"/>
+      <c r="Y16" s="185"/>
+      <c r="Z16" s="185"/>
+      <c r="AA16" s="185"/>
+      <c r="AB16" s="185"/>
+      <c r="AC16" s="185"/>
+      <c r="AD16" s="185"/>
+      <c r="AE16" s="186"/>
+      <c r="AF16" s="181"/>
+      <c r="AG16" s="182"/>
+      <c r="AH16" s="182"/>
+      <c r="AI16" s="183"/>
     </row>
     <row r="17" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="89"/>
-      <c r="B17" s="212"/>
-      <c r="C17" s="213"/>
-      <c r="D17" s="214"/>
-      <c r="E17" s="215"/>
-      <c r="F17" s="216"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="217"/>
-      <c r="I17" s="213"/>
-      <c r="J17" s="218"/>
-      <c r="K17" s="219"/>
-      <c r="L17" s="219"/>
-      <c r="M17" s="219"/>
-      <c r="N17" s="219"/>
-      <c r="O17" s="219"/>
-      <c r="P17" s="220"/>
-      <c r="Q17" s="221"/>
-      <c r="R17" s="222"/>
-      <c r="S17" s="222"/>
-      <c r="T17" s="222"/>
-      <c r="U17" s="222"/>
-      <c r="V17" s="222"/>
-      <c r="W17" s="222"/>
-      <c r="X17" s="222"/>
-      <c r="Y17" s="222"/>
-      <c r="Z17" s="222"/>
-      <c r="AA17" s="222"/>
-      <c r="AB17" s="222"/>
-      <c r="AC17" s="222"/>
-      <c r="AD17" s="222"/>
-      <c r="AE17" s="223"/>
-      <c r="AF17" s="218"/>
-      <c r="AG17" s="219"/>
-      <c r="AH17" s="219"/>
-      <c r="AI17" s="220"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="177"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="175"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="176"/>
+      <c r="J17" s="181"/>
+      <c r="K17" s="182"/>
+      <c r="L17" s="182"/>
+      <c r="M17" s="182"/>
+      <c r="N17" s="182"/>
+      <c r="O17" s="182"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="184"/>
+      <c r="R17" s="185"/>
+      <c r="S17" s="185"/>
+      <c r="T17" s="185"/>
+      <c r="U17" s="185"/>
+      <c r="V17" s="185"/>
+      <c r="W17" s="185"/>
+      <c r="X17" s="185"/>
+      <c r="Y17" s="185"/>
+      <c r="Z17" s="185"/>
+      <c r="AA17" s="185"/>
+      <c r="AB17" s="185"/>
+      <c r="AC17" s="185"/>
+      <c r="AD17" s="185"/>
+      <c r="AE17" s="186"/>
+      <c r="AF17" s="181"/>
+      <c r="AG17" s="182"/>
+      <c r="AH17" s="182"/>
+      <c r="AI17" s="183"/>
     </row>
     <row r="18" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="89"/>
-      <c r="B18" s="212"/>
-      <c r="C18" s="213"/>
-      <c r="D18" s="214"/>
-      <c r="E18" s="215"/>
-      <c r="F18" s="216"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="217"/>
-      <c r="I18" s="213"/>
-      <c r="J18" s="218"/>
-      <c r="K18" s="219"/>
-      <c r="L18" s="219"/>
-      <c r="M18" s="219"/>
-      <c r="N18" s="219"/>
-      <c r="O18" s="219"/>
-      <c r="P18" s="220"/>
-      <c r="Q18" s="221"/>
-      <c r="R18" s="222"/>
-      <c r="S18" s="222"/>
-      <c r="T18" s="222"/>
-      <c r="U18" s="222"/>
-      <c r="V18" s="222"/>
-      <c r="W18" s="222"/>
-      <c r="X18" s="222"/>
-      <c r="Y18" s="222"/>
-      <c r="Z18" s="222"/>
-      <c r="AA18" s="222"/>
-      <c r="AB18" s="222"/>
-      <c r="AC18" s="222"/>
-      <c r="AD18" s="222"/>
-      <c r="AE18" s="223"/>
-      <c r="AF18" s="218"/>
-      <c r="AG18" s="219"/>
-      <c r="AH18" s="219"/>
-      <c r="AI18" s="220"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="179"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="180"/>
+      <c r="I18" s="176"/>
+      <c r="J18" s="181"/>
+      <c r="K18" s="182"/>
+      <c r="L18" s="182"/>
+      <c r="M18" s="182"/>
+      <c r="N18" s="182"/>
+      <c r="O18" s="182"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="184"/>
+      <c r="R18" s="185"/>
+      <c r="S18" s="185"/>
+      <c r="T18" s="185"/>
+      <c r="U18" s="185"/>
+      <c r="V18" s="185"/>
+      <c r="W18" s="185"/>
+      <c r="X18" s="185"/>
+      <c r="Y18" s="185"/>
+      <c r="Z18" s="185"/>
+      <c r="AA18" s="185"/>
+      <c r="AB18" s="185"/>
+      <c r="AC18" s="185"/>
+      <c r="AD18" s="185"/>
+      <c r="AE18" s="186"/>
+      <c r="AF18" s="181"/>
+      <c r="AG18" s="182"/>
+      <c r="AH18" s="182"/>
+      <c r="AI18" s="183"/>
     </row>
     <row r="19" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="89"/>
-      <c r="B19" s="212"/>
-      <c r="C19" s="213"/>
-      <c r="D19" s="214"/>
-      <c r="E19" s="215"/>
-      <c r="F19" s="216"/>
-      <c r="G19" s="212"/>
-      <c r="H19" s="217"/>
-      <c r="I19" s="213"/>
-      <c r="J19" s="218"/>
-      <c r="K19" s="219"/>
-      <c r="L19" s="219"/>
-      <c r="M19" s="219"/>
-      <c r="N19" s="219"/>
-      <c r="O19" s="219"/>
-      <c r="P19" s="220"/>
-      <c r="Q19" s="221"/>
-      <c r="R19" s="222"/>
-      <c r="S19" s="222"/>
-      <c r="T19" s="222"/>
-      <c r="U19" s="222"/>
-      <c r="V19" s="222"/>
-      <c r="W19" s="222"/>
-      <c r="X19" s="222"/>
-      <c r="Y19" s="222"/>
-      <c r="Z19" s="222"/>
-      <c r="AA19" s="222"/>
-      <c r="AB19" s="222"/>
-      <c r="AC19" s="222"/>
-      <c r="AD19" s="222"/>
-      <c r="AE19" s="223"/>
-      <c r="AF19" s="218"/>
-      <c r="AG19" s="219"/>
-      <c r="AH19" s="219"/>
-      <c r="AI19" s="220"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="179"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="180"/>
+      <c r="I19" s="176"/>
+      <c r="J19" s="181"/>
+      <c r="K19" s="182"/>
+      <c r="L19" s="182"/>
+      <c r="M19" s="182"/>
+      <c r="N19" s="182"/>
+      <c r="O19" s="182"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="184"/>
+      <c r="R19" s="185"/>
+      <c r="S19" s="185"/>
+      <c r="T19" s="185"/>
+      <c r="U19" s="185"/>
+      <c r="V19" s="185"/>
+      <c r="W19" s="185"/>
+      <c r="X19" s="185"/>
+      <c r="Y19" s="185"/>
+      <c r="Z19" s="185"/>
+      <c r="AA19" s="185"/>
+      <c r="AB19" s="185"/>
+      <c r="AC19" s="185"/>
+      <c r="AD19" s="185"/>
+      <c r="AE19" s="186"/>
+      <c r="AF19" s="181"/>
+      <c r="AG19" s="182"/>
+      <c r="AH19" s="182"/>
+      <c r="AI19" s="183"/>
     </row>
     <row r="20" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="89"/>
-      <c r="B20" s="212"/>
-      <c r="C20" s="213"/>
-      <c r="D20" s="214"/>
-      <c r="E20" s="215"/>
-      <c r="F20" s="216"/>
-      <c r="G20" s="212"/>
-      <c r="H20" s="217"/>
-      <c r="I20" s="213"/>
-      <c r="J20" s="218"/>
-      <c r="K20" s="219"/>
-      <c r="L20" s="219"/>
-      <c r="M20" s="219"/>
-      <c r="N20" s="219"/>
-      <c r="O20" s="219"/>
-      <c r="P20" s="220"/>
-      <c r="Q20" s="221"/>
-      <c r="R20" s="222"/>
-      <c r="S20" s="222"/>
-      <c r="T20" s="222"/>
-      <c r="U20" s="222"/>
-      <c r="V20" s="222"/>
-      <c r="W20" s="222"/>
-      <c r="X20" s="222"/>
-      <c r="Y20" s="222"/>
-      <c r="Z20" s="222"/>
-      <c r="AA20" s="222"/>
-      <c r="AB20" s="222"/>
-      <c r="AC20" s="222"/>
-      <c r="AD20" s="222"/>
-      <c r="AE20" s="223"/>
-      <c r="AF20" s="218"/>
-      <c r="AG20" s="219"/>
-      <c r="AH20" s="219"/>
-      <c r="AI20" s="220"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="179"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="180"/>
+      <c r="I20" s="176"/>
+      <c r="J20" s="181"/>
+      <c r="K20" s="182"/>
+      <c r="L20" s="182"/>
+      <c r="M20" s="182"/>
+      <c r="N20" s="182"/>
+      <c r="O20" s="182"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="184"/>
+      <c r="R20" s="185"/>
+      <c r="S20" s="185"/>
+      <c r="T20" s="185"/>
+      <c r="U20" s="185"/>
+      <c r="V20" s="185"/>
+      <c r="W20" s="185"/>
+      <c r="X20" s="185"/>
+      <c r="Y20" s="185"/>
+      <c r="Z20" s="185"/>
+      <c r="AA20" s="185"/>
+      <c r="AB20" s="185"/>
+      <c r="AC20" s="185"/>
+      <c r="AD20" s="185"/>
+      <c r="AE20" s="186"/>
+      <c r="AF20" s="181"/>
+      <c r="AG20" s="182"/>
+      <c r="AH20" s="182"/>
+      <c r="AI20" s="183"/>
     </row>
     <row r="21" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="89"/>
-      <c r="B21" s="212"/>
-      <c r="C21" s="213"/>
-      <c r="D21" s="214"/>
-      <c r="E21" s="215"/>
-      <c r="F21" s="216"/>
-      <c r="G21" s="212"/>
-      <c r="H21" s="217"/>
-      <c r="I21" s="213"/>
-      <c r="J21" s="218"/>
-      <c r="K21" s="219"/>
-      <c r="L21" s="219"/>
-      <c r="M21" s="219"/>
-      <c r="N21" s="219"/>
-      <c r="O21" s="219"/>
-      <c r="P21" s="220"/>
-      <c r="Q21" s="221"/>
-      <c r="R21" s="222"/>
-      <c r="S21" s="222"/>
-      <c r="T21" s="222"/>
-      <c r="U21" s="222"/>
-      <c r="V21" s="222"/>
-      <c r="W21" s="222"/>
-      <c r="X21" s="222"/>
-      <c r="Y21" s="222"/>
-      <c r="Z21" s="222"/>
-      <c r="AA21" s="222"/>
-      <c r="AB21" s="222"/>
-      <c r="AC21" s="222"/>
-      <c r="AD21" s="222"/>
-      <c r="AE21" s="223"/>
-      <c r="AF21" s="218"/>
-      <c r="AG21" s="219"/>
-      <c r="AH21" s="219"/>
-      <c r="AI21" s="220"/>
+      <c r="B21" s="175"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="180"/>
+      <c r="I21" s="176"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="182"/>
+      <c r="L21" s="182"/>
+      <c r="M21" s="182"/>
+      <c r="N21" s="182"/>
+      <c r="O21" s="182"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="184"/>
+      <c r="R21" s="185"/>
+      <c r="S21" s="185"/>
+      <c r="T21" s="185"/>
+      <c r="U21" s="185"/>
+      <c r="V21" s="185"/>
+      <c r="W21" s="185"/>
+      <c r="X21" s="185"/>
+      <c r="Y21" s="185"/>
+      <c r="Z21" s="185"/>
+      <c r="AA21" s="185"/>
+      <c r="AB21" s="185"/>
+      <c r="AC21" s="185"/>
+      <c r="AD21" s="185"/>
+      <c r="AE21" s="186"/>
+      <c r="AF21" s="181"/>
+      <c r="AG21" s="182"/>
+      <c r="AH21" s="182"/>
+      <c r="AI21" s="183"/>
     </row>
     <row r="22" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="89"/>
-      <c r="B22" s="212"/>
-      <c r="C22" s="213"/>
-      <c r="D22" s="214"/>
-      <c r="E22" s="215"/>
-      <c r="F22" s="216"/>
-      <c r="G22" s="212"/>
-      <c r="H22" s="217"/>
-      <c r="I22" s="213"/>
-      <c r="J22" s="218"/>
-      <c r="K22" s="219"/>
-      <c r="L22" s="219"/>
-      <c r="M22" s="219"/>
-      <c r="N22" s="219"/>
-      <c r="O22" s="219"/>
-      <c r="P22" s="220"/>
-      <c r="Q22" s="221"/>
-      <c r="R22" s="222"/>
-      <c r="S22" s="222"/>
-      <c r="T22" s="222"/>
-      <c r="U22" s="222"/>
-      <c r="V22" s="222"/>
-      <c r="W22" s="222"/>
-      <c r="X22" s="222"/>
-      <c r="Y22" s="222"/>
-      <c r="Z22" s="222"/>
-      <c r="AA22" s="222"/>
-      <c r="AB22" s="222"/>
-      <c r="AC22" s="222"/>
-      <c r="AD22" s="222"/>
-      <c r="AE22" s="223"/>
-      <c r="AF22" s="218"/>
-      <c r="AG22" s="219"/>
-      <c r="AH22" s="219"/>
-      <c r="AI22" s="220"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="178"/>
+      <c r="F22" s="179"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="180"/>
+      <c r="I22" s="176"/>
+      <c r="J22" s="181"/>
+      <c r="K22" s="182"/>
+      <c r="L22" s="182"/>
+      <c r="M22" s="182"/>
+      <c r="N22" s="182"/>
+      <c r="O22" s="182"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="184"/>
+      <c r="R22" s="185"/>
+      <c r="S22" s="185"/>
+      <c r="T22" s="185"/>
+      <c r="U22" s="185"/>
+      <c r="V22" s="185"/>
+      <c r="W22" s="185"/>
+      <c r="X22" s="185"/>
+      <c r="Y22" s="185"/>
+      <c r="Z22" s="185"/>
+      <c r="AA22" s="185"/>
+      <c r="AB22" s="185"/>
+      <c r="AC22" s="185"/>
+      <c r="AD22" s="185"/>
+      <c r="AE22" s="186"/>
+      <c r="AF22" s="181"/>
+      <c r="AG22" s="182"/>
+      <c r="AH22" s="182"/>
+      <c r="AI22" s="183"/>
     </row>
     <row r="23" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="89"/>
-      <c r="B23" s="212"/>
-      <c r="C23" s="213"/>
-      <c r="D23" s="214"/>
-      <c r="E23" s="215"/>
-      <c r="F23" s="216"/>
-      <c r="G23" s="212"/>
-      <c r="H23" s="217"/>
-      <c r="I23" s="213"/>
-      <c r="J23" s="218"/>
-      <c r="K23" s="219"/>
-      <c r="L23" s="219"/>
-      <c r="M23" s="219"/>
-      <c r="N23" s="219"/>
-      <c r="O23" s="219"/>
-      <c r="P23" s="220"/>
-      <c r="Q23" s="221"/>
-      <c r="R23" s="222"/>
-      <c r="S23" s="222"/>
-      <c r="T23" s="222"/>
-      <c r="U23" s="222"/>
-      <c r="V23" s="222"/>
-      <c r="W23" s="222"/>
-      <c r="X23" s="222"/>
-      <c r="Y23" s="222"/>
-      <c r="Z23" s="222"/>
-      <c r="AA23" s="222"/>
-      <c r="AB23" s="222"/>
-      <c r="AC23" s="222"/>
-      <c r="AD23" s="222"/>
-      <c r="AE23" s="223"/>
-      <c r="AF23" s="218"/>
-      <c r="AG23" s="219"/>
-      <c r="AH23" s="219"/>
-      <c r="AI23" s="220"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="177"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="179"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="180"/>
+      <c r="I23" s="176"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="182"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="182"/>
+      <c r="N23" s="182"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="184"/>
+      <c r="R23" s="185"/>
+      <c r="S23" s="185"/>
+      <c r="T23" s="185"/>
+      <c r="U23" s="185"/>
+      <c r="V23" s="185"/>
+      <c r="W23" s="185"/>
+      <c r="X23" s="185"/>
+      <c r="Y23" s="185"/>
+      <c r="Z23" s="185"/>
+      <c r="AA23" s="185"/>
+      <c r="AB23" s="185"/>
+      <c r="AC23" s="185"/>
+      <c r="AD23" s="185"/>
+      <c r="AE23" s="186"/>
+      <c r="AF23" s="181"/>
+      <c r="AG23" s="182"/>
+      <c r="AH23" s="182"/>
+      <c r="AI23" s="183"/>
     </row>
     <row r="24" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="89"/>
-      <c r="B24" s="212"/>
-      <c r="C24" s="213"/>
-      <c r="D24" s="214"/>
-      <c r="E24" s="215"/>
-      <c r="F24" s="216"/>
-      <c r="G24" s="212"/>
-      <c r="H24" s="217"/>
-      <c r="I24" s="213"/>
-      <c r="J24" s="218"/>
-      <c r="K24" s="219"/>
-      <c r="L24" s="219"/>
-      <c r="M24" s="219"/>
-      <c r="N24" s="219"/>
-      <c r="O24" s="219"/>
-      <c r="P24" s="220"/>
-      <c r="Q24" s="221"/>
-      <c r="R24" s="222"/>
-      <c r="S24" s="222"/>
-      <c r="T24" s="222"/>
-      <c r="U24" s="222"/>
-      <c r="V24" s="222"/>
-      <c r="W24" s="222"/>
-      <c r="X24" s="222"/>
-      <c r="Y24" s="222"/>
-      <c r="Z24" s="222"/>
-      <c r="AA24" s="222"/>
-      <c r="AB24" s="222"/>
-      <c r="AC24" s="222"/>
-      <c r="AD24" s="222"/>
-      <c r="AE24" s="223"/>
-      <c r="AF24" s="218"/>
-      <c r="AG24" s="219"/>
-      <c r="AH24" s="219"/>
-      <c r="AI24" s="220"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="177"/>
+      <c r="E24" s="178"/>
+      <c r="F24" s="179"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="180"/>
+      <c r="I24" s="176"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="182"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="184"/>
+      <c r="R24" s="185"/>
+      <c r="S24" s="185"/>
+      <c r="T24" s="185"/>
+      <c r="U24" s="185"/>
+      <c r="V24" s="185"/>
+      <c r="W24" s="185"/>
+      <c r="X24" s="185"/>
+      <c r="Y24" s="185"/>
+      <c r="Z24" s="185"/>
+      <c r="AA24" s="185"/>
+      <c r="AB24" s="185"/>
+      <c r="AC24" s="185"/>
+      <c r="AD24" s="185"/>
+      <c r="AE24" s="186"/>
+      <c r="AF24" s="181"/>
+      <c r="AG24" s="182"/>
+      <c r="AH24" s="182"/>
+      <c r="AI24" s="183"/>
     </row>
     <row r="25" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="89"/>
-      <c r="B25" s="212"/>
-      <c r="C25" s="213"/>
-      <c r="D25" s="214"/>
-      <c r="E25" s="215"/>
-      <c r="F25" s="216"/>
-      <c r="G25" s="212"/>
-      <c r="H25" s="217"/>
-      <c r="I25" s="213"/>
-      <c r="J25" s="218"/>
-      <c r="K25" s="219"/>
-      <c r="L25" s="219"/>
-      <c r="M25" s="219"/>
-      <c r="N25" s="219"/>
-      <c r="O25" s="219"/>
-      <c r="P25" s="220"/>
-      <c r="Q25" s="221"/>
-      <c r="R25" s="222"/>
-      <c r="S25" s="222"/>
-      <c r="T25" s="222"/>
-      <c r="U25" s="222"/>
-      <c r="V25" s="222"/>
-      <c r="W25" s="222"/>
-      <c r="X25" s="222"/>
-      <c r="Y25" s="222"/>
-      <c r="Z25" s="222"/>
-      <c r="AA25" s="222"/>
-      <c r="AB25" s="222"/>
-      <c r="AC25" s="222"/>
-      <c r="AD25" s="222"/>
-      <c r="AE25" s="223"/>
-      <c r="AF25" s="218"/>
-      <c r="AG25" s="219"/>
-      <c r="AH25" s="219"/>
-      <c r="AI25" s="220"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="177"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="179"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="180"/>
+      <c r="I25" s="176"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="182"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="184"/>
+      <c r="R25" s="185"/>
+      <c r="S25" s="185"/>
+      <c r="T25" s="185"/>
+      <c r="U25" s="185"/>
+      <c r="V25" s="185"/>
+      <c r="W25" s="185"/>
+      <c r="X25" s="185"/>
+      <c r="Y25" s="185"/>
+      <c r="Z25" s="185"/>
+      <c r="AA25" s="185"/>
+      <c r="AB25" s="185"/>
+      <c r="AC25" s="185"/>
+      <c r="AD25" s="185"/>
+      <c r="AE25" s="186"/>
+      <c r="AF25" s="181"/>
+      <c r="AG25" s="182"/>
+      <c r="AH25" s="182"/>
+      <c r="AI25" s="183"/>
     </row>
     <row r="26" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="89"/>
-      <c r="B26" s="212"/>
-      <c r="C26" s="213"/>
-      <c r="D26" s="214"/>
-      <c r="E26" s="215"/>
-      <c r="F26" s="216"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="217"/>
-      <c r="I26" s="213"/>
-      <c r="J26" s="218"/>
-      <c r="K26" s="219"/>
-      <c r="L26" s="219"/>
-      <c r="M26" s="219"/>
-      <c r="N26" s="219"/>
-      <c r="O26" s="219"/>
-      <c r="P26" s="220"/>
-      <c r="Q26" s="221"/>
-      <c r="R26" s="222"/>
-      <c r="S26" s="222"/>
-      <c r="T26" s="222"/>
-      <c r="U26" s="222"/>
-      <c r="V26" s="222"/>
-      <c r="W26" s="222"/>
-      <c r="X26" s="222"/>
-      <c r="Y26" s="222"/>
-      <c r="Z26" s="222"/>
-      <c r="AA26" s="222"/>
-      <c r="AB26" s="222"/>
-      <c r="AC26" s="222"/>
-      <c r="AD26" s="222"/>
-      <c r="AE26" s="223"/>
-      <c r="AF26" s="218"/>
-      <c r="AG26" s="219"/>
-      <c r="AH26" s="219"/>
-      <c r="AI26" s="220"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="177"/>
+      <c r="E26" s="178"/>
+      <c r="F26" s="179"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="180"/>
+      <c r="I26" s="176"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="182"/>
+      <c r="N26" s="182"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="184"/>
+      <c r="R26" s="185"/>
+      <c r="S26" s="185"/>
+      <c r="T26" s="185"/>
+      <c r="U26" s="185"/>
+      <c r="V26" s="185"/>
+      <c r="W26" s="185"/>
+      <c r="X26" s="185"/>
+      <c r="Y26" s="185"/>
+      <c r="Z26" s="185"/>
+      <c r="AA26" s="185"/>
+      <c r="AB26" s="185"/>
+      <c r="AC26" s="185"/>
+      <c r="AD26" s="185"/>
+      <c r="AE26" s="186"/>
+      <c r="AF26" s="181"/>
+      <c r="AG26" s="182"/>
+      <c r="AH26" s="182"/>
+      <c r="AI26" s="183"/>
     </row>
     <row r="27" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="89"/>
-      <c r="B27" s="212"/>
-      <c r="C27" s="213"/>
-      <c r="D27" s="214"/>
-      <c r="E27" s="215"/>
-      <c r="F27" s="216"/>
-      <c r="G27" s="212"/>
-      <c r="H27" s="217"/>
-      <c r="I27" s="213"/>
-      <c r="J27" s="218"/>
-      <c r="K27" s="219"/>
-      <c r="L27" s="219"/>
-      <c r="M27" s="219"/>
-      <c r="N27" s="219"/>
-      <c r="O27" s="219"/>
-      <c r="P27" s="220"/>
-      <c r="Q27" s="221"/>
-      <c r="R27" s="222"/>
-      <c r="S27" s="222"/>
-      <c r="T27" s="222"/>
-      <c r="U27" s="222"/>
-      <c r="V27" s="222"/>
-      <c r="W27" s="222"/>
-      <c r="X27" s="222"/>
-      <c r="Y27" s="222"/>
-      <c r="Z27" s="222"/>
-      <c r="AA27" s="222"/>
-      <c r="AB27" s="222"/>
-      <c r="AC27" s="222"/>
-      <c r="AD27" s="222"/>
-      <c r="AE27" s="223"/>
-      <c r="AF27" s="218"/>
-      <c r="AG27" s="219"/>
-      <c r="AH27" s="219"/>
-      <c r="AI27" s="220"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="177"/>
+      <c r="E27" s="178"/>
+      <c r="F27" s="179"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="180"/>
+      <c r="I27" s="176"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="182"/>
+      <c r="M27" s="182"/>
+      <c r="N27" s="182"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="184"/>
+      <c r="R27" s="185"/>
+      <c r="S27" s="185"/>
+      <c r="T27" s="185"/>
+      <c r="U27" s="185"/>
+      <c r="V27" s="185"/>
+      <c r="W27" s="185"/>
+      <c r="X27" s="185"/>
+      <c r="Y27" s="185"/>
+      <c r="Z27" s="185"/>
+      <c r="AA27" s="185"/>
+      <c r="AB27" s="185"/>
+      <c r="AC27" s="185"/>
+      <c r="AD27" s="185"/>
+      <c r="AE27" s="186"/>
+      <c r="AF27" s="181"/>
+      <c r="AG27" s="182"/>
+      <c r="AH27" s="182"/>
+      <c r="AI27" s="183"/>
     </row>
     <row r="28" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="89"/>
-      <c r="B28" s="212"/>
-      <c r="C28" s="213"/>
-      <c r="D28" s="214"/>
-      <c r="E28" s="215"/>
-      <c r="F28" s="216"/>
-      <c r="G28" s="212"/>
-      <c r="H28" s="217"/>
-      <c r="I28" s="213"/>
-      <c r="J28" s="218"/>
-      <c r="K28" s="219"/>
-      <c r="L28" s="219"/>
-      <c r="M28" s="219"/>
-      <c r="N28" s="219"/>
-      <c r="O28" s="219"/>
-      <c r="P28" s="220"/>
-      <c r="Q28" s="221"/>
-      <c r="R28" s="222"/>
-      <c r="S28" s="222"/>
-      <c r="T28" s="222"/>
-      <c r="U28" s="222"/>
-      <c r="V28" s="222"/>
-      <c r="W28" s="222"/>
-      <c r="X28" s="222"/>
-      <c r="Y28" s="222"/>
-      <c r="Z28" s="222"/>
-      <c r="AA28" s="222"/>
-      <c r="AB28" s="222"/>
-      <c r="AC28" s="222"/>
-      <c r="AD28" s="222"/>
-      <c r="AE28" s="223"/>
-      <c r="AF28" s="218"/>
-      <c r="AG28" s="219"/>
-      <c r="AH28" s="219"/>
-      <c r="AI28" s="220"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="177"/>
+      <c r="E28" s="178"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="180"/>
+      <c r="I28" s="176"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="182"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="182"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="184"/>
+      <c r="R28" s="185"/>
+      <c r="S28" s="185"/>
+      <c r="T28" s="185"/>
+      <c r="U28" s="185"/>
+      <c r="V28" s="185"/>
+      <c r="W28" s="185"/>
+      <c r="X28" s="185"/>
+      <c r="Y28" s="185"/>
+      <c r="Z28" s="185"/>
+      <c r="AA28" s="185"/>
+      <c r="AB28" s="185"/>
+      <c r="AC28" s="185"/>
+      <c r="AD28" s="185"/>
+      <c r="AE28" s="186"/>
+      <c r="AF28" s="181"/>
+      <c r="AG28" s="182"/>
+      <c r="AH28" s="182"/>
+      <c r="AI28" s="183"/>
     </row>
     <row r="29" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="89"/>
-      <c r="B29" s="212"/>
-      <c r="C29" s="213"/>
-      <c r="D29" s="214"/>
-      <c r="E29" s="215"/>
-      <c r="F29" s="216"/>
-      <c r="G29" s="212"/>
-      <c r="H29" s="217"/>
-      <c r="I29" s="213"/>
-      <c r="J29" s="218"/>
-      <c r="K29" s="219"/>
-      <c r="L29" s="219"/>
-      <c r="M29" s="219"/>
-      <c r="N29" s="219"/>
-      <c r="O29" s="219"/>
-      <c r="P29" s="220"/>
-      <c r="Q29" s="221"/>
-      <c r="R29" s="222"/>
-      <c r="S29" s="222"/>
-      <c r="T29" s="222"/>
-      <c r="U29" s="222"/>
-      <c r="V29" s="222"/>
-      <c r="W29" s="222"/>
-      <c r="X29" s="222"/>
-      <c r="Y29" s="222"/>
-      <c r="Z29" s="222"/>
-      <c r="AA29" s="222"/>
-      <c r="AB29" s="222"/>
-      <c r="AC29" s="222"/>
-      <c r="AD29" s="222"/>
-      <c r="AE29" s="223"/>
-      <c r="AF29" s="218"/>
-      <c r="AG29" s="219"/>
-      <c r="AH29" s="219"/>
-      <c r="AI29" s="220"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="177"/>
+      <c r="E29" s="178"/>
+      <c r="F29" s="179"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="180"/>
+      <c r="I29" s="176"/>
+      <c r="J29" s="181"/>
+      <c r="K29" s="182"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="182"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
+      <c r="R29" s="185"/>
+      <c r="S29" s="185"/>
+      <c r="T29" s="185"/>
+      <c r="U29" s="185"/>
+      <c r="V29" s="185"/>
+      <c r="W29" s="185"/>
+      <c r="X29" s="185"/>
+      <c r="Y29" s="185"/>
+      <c r="Z29" s="185"/>
+      <c r="AA29" s="185"/>
+      <c r="AB29" s="185"/>
+      <c r="AC29" s="185"/>
+      <c r="AD29" s="185"/>
+      <c r="AE29" s="186"/>
+      <c r="AF29" s="181"/>
+      <c r="AG29" s="182"/>
+      <c r="AH29" s="182"/>
+      <c r="AI29" s="183"/>
     </row>
     <row r="30" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="89"/>
-      <c r="B30" s="212"/>
-      <c r="C30" s="213"/>
-      <c r="D30" s="214"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="216"/>
-      <c r="G30" s="212"/>
-      <c r="H30" s="217"/>
-      <c r="I30" s="213"/>
-      <c r="J30" s="218"/>
-      <c r="K30" s="219"/>
-      <c r="L30" s="219"/>
-      <c r="M30" s="219"/>
-      <c r="N30" s="219"/>
-      <c r="O30" s="219"/>
-      <c r="P30" s="220"/>
-      <c r="Q30" s="221"/>
-      <c r="R30" s="222"/>
-      <c r="S30" s="222"/>
-      <c r="T30" s="222"/>
-      <c r="U30" s="222"/>
-      <c r="V30" s="222"/>
-      <c r="W30" s="222"/>
-      <c r="X30" s="222"/>
-      <c r="Y30" s="222"/>
-      <c r="Z30" s="222"/>
-      <c r="AA30" s="222"/>
-      <c r="AB30" s="222"/>
-      <c r="AC30" s="222"/>
-      <c r="AD30" s="222"/>
-      <c r="AE30" s="223"/>
-      <c r="AF30" s="218"/>
-      <c r="AG30" s="219"/>
-      <c r="AH30" s="219"/>
-      <c r="AI30" s="220"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="178"/>
+      <c r="F30" s="179"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="180"/>
+      <c r="I30" s="176"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="182"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="182"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="183"/>
+      <c r="Q30" s="184"/>
+      <c r="R30" s="185"/>
+      <c r="S30" s="185"/>
+      <c r="T30" s="185"/>
+      <c r="U30" s="185"/>
+      <c r="V30" s="185"/>
+      <c r="W30" s="185"/>
+      <c r="X30" s="185"/>
+      <c r="Y30" s="185"/>
+      <c r="Z30" s="185"/>
+      <c r="AA30" s="185"/>
+      <c r="AB30" s="185"/>
+      <c r="AC30" s="185"/>
+      <c r="AD30" s="185"/>
+      <c r="AE30" s="186"/>
+      <c r="AF30" s="181"/>
+      <c r="AG30" s="182"/>
+      <c r="AH30" s="182"/>
+      <c r="AI30" s="183"/>
     </row>
     <row r="31" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="89"/>
-      <c r="B31" s="212"/>
-      <c r="C31" s="213"/>
-      <c r="D31" s="214"/>
-      <c r="E31" s="215"/>
-      <c r="F31" s="216"/>
-      <c r="G31" s="212"/>
-      <c r="H31" s="217"/>
-      <c r="I31" s="213"/>
-      <c r="J31" s="218"/>
-      <c r="K31" s="219"/>
-      <c r="L31" s="219"/>
-      <c r="M31" s="219"/>
-      <c r="N31" s="219"/>
-      <c r="O31" s="219"/>
-      <c r="P31" s="220"/>
-      <c r="Q31" s="221"/>
-      <c r="R31" s="222"/>
-      <c r="S31" s="222"/>
-      <c r="T31" s="222"/>
-      <c r="U31" s="222"/>
-      <c r="V31" s="222"/>
-      <c r="W31" s="222"/>
-      <c r="X31" s="222"/>
-      <c r="Y31" s="222"/>
-      <c r="Z31" s="222"/>
-      <c r="AA31" s="222"/>
-      <c r="AB31" s="222"/>
-      <c r="AC31" s="222"/>
-      <c r="AD31" s="222"/>
-      <c r="AE31" s="223"/>
-      <c r="AF31" s="218"/>
-      <c r="AG31" s="219"/>
-      <c r="AH31" s="219"/>
-      <c r="AI31" s="220"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="178"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="180"/>
+      <c r="I31" s="176"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="182"/>
+      <c r="L31" s="182"/>
+      <c r="M31" s="182"/>
+      <c r="N31" s="182"/>
+      <c r="O31" s="182"/>
+      <c r="P31" s="183"/>
+      <c r="Q31" s="184"/>
+      <c r="R31" s="185"/>
+      <c r="S31" s="185"/>
+      <c r="T31" s="185"/>
+      <c r="U31" s="185"/>
+      <c r="V31" s="185"/>
+      <c r="W31" s="185"/>
+      <c r="X31" s="185"/>
+      <c r="Y31" s="185"/>
+      <c r="Z31" s="185"/>
+      <c r="AA31" s="185"/>
+      <c r="AB31" s="185"/>
+      <c r="AC31" s="185"/>
+      <c r="AD31" s="185"/>
+      <c r="AE31" s="186"/>
+      <c r="AF31" s="181"/>
+      <c r="AG31" s="182"/>
+      <c r="AH31" s="182"/>
+      <c r="AI31" s="183"/>
     </row>
     <row r="32" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="89"/>
-      <c r="B32" s="212"/>
-      <c r="C32" s="213"/>
-      <c r="D32" s="214"/>
-      <c r="E32" s="215"/>
-      <c r="F32" s="216"/>
-      <c r="G32" s="212"/>
-      <c r="H32" s="217"/>
-      <c r="I32" s="213"/>
-      <c r="J32" s="218"/>
-      <c r="K32" s="238"/>
-      <c r="L32" s="219"/>
-      <c r="M32" s="219"/>
-      <c r="N32" s="219"/>
-      <c r="O32" s="219"/>
-      <c r="P32" s="220"/>
-      <c r="Q32" s="221"/>
-      <c r="R32" s="222"/>
-      <c r="S32" s="222"/>
-      <c r="T32" s="222"/>
-      <c r="U32" s="222"/>
-      <c r="V32" s="222"/>
-      <c r="W32" s="222"/>
-      <c r="X32" s="222"/>
-      <c r="Y32" s="222"/>
-      <c r="Z32" s="222"/>
-      <c r="AA32" s="222"/>
-      <c r="AB32" s="222"/>
-      <c r="AC32" s="222"/>
-      <c r="AD32" s="222"/>
-      <c r="AE32" s="223"/>
-      <c r="AF32" s="218"/>
-      <c r="AG32" s="219"/>
-      <c r="AH32" s="219"/>
-      <c r="AI32" s="220"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="177"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="175"/>
+      <c r="H32" s="180"/>
+      <c r="I32" s="176"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="187"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="182"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="183"/>
+      <c r="Q32" s="184"/>
+      <c r="R32" s="185"/>
+      <c r="S32" s="185"/>
+      <c r="T32" s="185"/>
+      <c r="U32" s="185"/>
+      <c r="V32" s="185"/>
+      <c r="W32" s="185"/>
+      <c r="X32" s="185"/>
+      <c r="Y32" s="185"/>
+      <c r="Z32" s="185"/>
+      <c r="AA32" s="185"/>
+      <c r="AB32" s="185"/>
+      <c r="AC32" s="185"/>
+      <c r="AD32" s="185"/>
+      <c r="AE32" s="186"/>
+      <c r="AF32" s="181"/>
+      <c r="AG32" s="182"/>
+      <c r="AH32" s="182"/>
+      <c r="AI32" s="183"/>
     </row>
     <row r="33" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="89"/>
-      <c r="B33" s="212"/>
-      <c r="C33" s="213"/>
-      <c r="D33" s="214"/>
-      <c r="E33" s="215"/>
-      <c r="F33" s="216"/>
-      <c r="G33" s="212"/>
-      <c r="H33" s="217"/>
-      <c r="I33" s="213"/>
-      <c r="J33" s="218"/>
-      <c r="K33" s="219"/>
-      <c r="L33" s="219"/>
-      <c r="M33" s="219"/>
-      <c r="N33" s="219"/>
-      <c r="O33" s="219"/>
-      <c r="P33" s="220"/>
-      <c r="Q33" s="221"/>
-      <c r="R33" s="222"/>
-      <c r="S33" s="222"/>
-      <c r="T33" s="222"/>
-      <c r="U33" s="222"/>
-      <c r="V33" s="222"/>
-      <c r="W33" s="222"/>
-      <c r="X33" s="222"/>
-      <c r="Y33" s="222"/>
-      <c r="Z33" s="222"/>
-      <c r="AA33" s="222"/>
-      <c r="AB33" s="222"/>
-      <c r="AC33" s="222"/>
-      <c r="AD33" s="222"/>
-      <c r="AE33" s="223"/>
-      <c r="AF33" s="218"/>
-      <c r="AG33" s="219"/>
-      <c r="AH33" s="219"/>
-      <c r="AI33" s="220"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="178"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="175"/>
+      <c r="H33" s="180"/>
+      <c r="I33" s="176"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="182"/>
+      <c r="L33" s="182"/>
+      <c r="M33" s="182"/>
+      <c r="N33" s="182"/>
+      <c r="O33" s="182"/>
+      <c r="P33" s="183"/>
+      <c r="Q33" s="184"/>
+      <c r="R33" s="185"/>
+      <c r="S33" s="185"/>
+      <c r="T33" s="185"/>
+      <c r="U33" s="185"/>
+      <c r="V33" s="185"/>
+      <c r="W33" s="185"/>
+      <c r="X33" s="185"/>
+      <c r="Y33" s="185"/>
+      <c r="Z33" s="185"/>
+      <c r="AA33" s="185"/>
+      <c r="AB33" s="185"/>
+      <c r="AC33" s="185"/>
+      <c r="AD33" s="185"/>
+      <c r="AE33" s="186"/>
+      <c r="AF33" s="181"/>
+      <c r="AG33" s="182"/>
+      <c r="AH33" s="182"/>
+      <c r="AI33" s="183"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -29473,6 +29317,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -29624,158 +29624,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="211" t="str">
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-      <c r="M1" s="184"/>
-      <c r="N1" s="185"/>
-      <c r="O1" s="190" t="s">
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="191"/>
-      <c r="Q1" s="191"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="244" t="str">
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="240" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
-      <c r="Y1" s="200"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="242" t="s">
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="241" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="243"/>
-      <c r="AC1" s="208" t="str">
+      <c r="AB1" s="242"/>
+      <c r="AC1" s="236" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="209"/>
-      <c r="AE1" s="209"/>
-      <c r="AF1" s="210"/>
-      <c r="AG1" s="239">
+      <c r="AD1" s="237"/>
+      <c r="AE1" s="237"/>
+      <c r="AF1" s="238"/>
+      <c r="AG1" s="243">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
-      </c>
-      <c r="AH1" s="240"/>
-      <c r="AI1" s="241"/>
+        <v>45565</v>
+      </c>
+      <c r="AH1" s="244"/>
+      <c r="AI1" s="245"/>
       <c r="AL1" s="91"/>
     </row>
     <row r="2" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="180" t="s">
+      <c r="A2" s="208" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="181"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="211" t="str">
+      <c r="B2" s="209"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="184"/>
-      <c r="K2" s="184"/>
-      <c r="L2" s="184"/>
-      <c r="M2" s="184"/>
-      <c r="N2" s="185"/>
-      <c r="O2" s="193"/>
-      <c r="P2" s="194"/>
-      <c r="Q2" s="194"/>
-      <c r="R2" s="195"/>
-      <c r="S2" s="202"/>
-      <c r="T2" s="203"/>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="203"/>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="204"/>
-      <c r="AA2" s="242" t="s">
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="213"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="222"/>
+      <c r="Q2" s="222"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="230"/>
+      <c r="T2" s="231"/>
+      <c r="U2" s="231"/>
+      <c r="V2" s="231"/>
+      <c r="W2" s="231"/>
+      <c r="X2" s="231"/>
+      <c r="Y2" s="231"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="241" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="208" t="str">
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="236" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="209"/>
-      <c r="AE2" s="209"/>
-      <c r="AF2" s="210"/>
-      <c r="AG2" s="239" t="str">
+      <c r="AD2" s="237"/>
+      <c r="AE2" s="237"/>
+      <c r="AF2" s="238"/>
+      <c r="AG2" s="243" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="240"/>
-      <c r="AI2" s="241"/>
+      <c r="AH2" s="244"/>
+      <c r="AI2" s="245"/>
     </row>
     <row r="3" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="180" t="s">
+      <c r="A3" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="181"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="211" t="str">
+      <c r="B3" s="209"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
-      <c r="M3" s="184"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="196"/>
-      <c r="P3" s="197"/>
-      <c r="Q3" s="197"/>
-      <c r="R3" s="198"/>
-      <c r="S3" s="205"/>
-      <c r="T3" s="206"/>
-      <c r="U3" s="206"/>
-      <c r="V3" s="206"/>
-      <c r="W3" s="206"/>
-      <c r="X3" s="206"/>
-      <c r="Y3" s="206"/>
-      <c r="Z3" s="207"/>
-      <c r="AA3" s="242"/>
-      <c r="AB3" s="243"/>
-      <c r="AC3" s="208" t="str">
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="213"/>
+      <c r="O3" s="224"/>
+      <c r="P3" s="225"/>
+      <c r="Q3" s="225"/>
+      <c r="R3" s="226"/>
+      <c r="S3" s="233"/>
+      <c r="T3" s="234"/>
+      <c r="U3" s="234"/>
+      <c r="V3" s="234"/>
+      <c r="W3" s="234"/>
+      <c r="X3" s="234"/>
+      <c r="Y3" s="234"/>
+      <c r="Z3" s="235"/>
+      <c r="AA3" s="241"/>
+      <c r="AB3" s="242"/>
+      <c r="AC3" s="236" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="209"/>
-      <c r="AE3" s="209"/>
-      <c r="AF3" s="210"/>
-      <c r="AG3" s="239" t="str">
+      <c r="AD3" s="237"/>
+      <c r="AE3" s="237"/>
+      <c r="AF3" s="238"/>
+      <c r="AG3" s="243" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="240"/>
-      <c r="AI3" s="241"/>
+      <c r="AH3" s="244"/>
+      <c r="AI3" s="245"/>
     </row>
     <row r="4" spans="1:53" s="31" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AC4" s="92"/>
@@ -32194,6 +32194,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -32203,14 +32211,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -32233,157 +32233,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="257" t="s">
+      <c r="A1" s="249" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="261"/>
-      <c r="G1" s="261"/>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261"/>
-      <c r="K1" s="261"/>
-      <c r="L1" s="261"/>
-      <c r="M1" s="261"/>
-      <c r="N1" s="262"/>
-      <c r="O1" s="266" t="s">
+      <c r="B1" s="250"/>
+      <c r="C1" s="250"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="253"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="258" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="267"/>
-      <c r="Q1" s="267"/>
-      <c r="R1" s="268"/>
-      <c r="S1" s="275" t="str">
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="260"/>
+      <c r="S1" s="267" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="276"/>
-      <c r="U1" s="276"/>
-      <c r="V1" s="276"/>
-      <c r="W1" s="276"/>
-      <c r="X1" s="276"/>
-      <c r="Y1" s="276"/>
-      <c r="Z1" s="277"/>
-      <c r="AA1" s="257" t="s">
+      <c r="T1" s="268"/>
+      <c r="U1" s="268"/>
+      <c r="V1" s="268"/>
+      <c r="W1" s="268"/>
+      <c r="X1" s="268"/>
+      <c r="Y1" s="268"/>
+      <c r="Z1" s="269"/>
+      <c r="AA1" s="249" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="259"/>
-      <c r="AC1" s="263" t="str">
+      <c r="AB1" s="251"/>
+      <c r="AC1" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="264"/>
-      <c r="AE1" s="264"/>
-      <c r="AF1" s="265"/>
-      <c r="AG1" s="245">
+      <c r="AD1" s="256"/>
+      <c r="AE1" s="256"/>
+      <c r="AF1" s="257"/>
+      <c r="AG1" s="246">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
-      </c>
-      <c r="AH1" s="246"/>
-      <c r="AI1" s="247"/>
+        <v>45565</v>
+      </c>
+      <c r="AH1" s="247"/>
+      <c r="AI1" s="248"/>
       <c r="AN1" s="17"/>
       <c r="AO1" s="17"/>
       <c r="AP1" s="17"/>
     </row>
     <row r="2" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="257" t="s">
+      <c r="A2" s="249" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="258"/>
-      <c r="C2" s="258"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="261"/>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="269"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="271"/>
-      <c r="S2" s="278"/>
-      <c r="T2" s="279"/>
-      <c r="U2" s="279"/>
-      <c r="V2" s="279"/>
-      <c r="W2" s="279"/>
-      <c r="X2" s="279"/>
-      <c r="Y2" s="279"/>
-      <c r="Z2" s="280"/>
-      <c r="AA2" s="257" t="s">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="271"/>
+      <c r="U2" s="271"/>
+      <c r="V2" s="271"/>
+      <c r="W2" s="271"/>
+      <c r="X2" s="271"/>
+      <c r="Y2" s="271"/>
+      <c r="Z2" s="272"/>
+      <c r="AA2" s="249" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="259"/>
-      <c r="AC2" s="263" t="str">
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="264"/>
-      <c r="AE2" s="264"/>
-      <c r="AF2" s="265"/>
-      <c r="AG2" s="245" t="str">
+      <c r="AD2" s="256"/>
+      <c r="AE2" s="256"/>
+      <c r="AF2" s="257"/>
+      <c r="AG2" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="246"/>
-      <c r="AI2" s="247"/>
+      <c r="AH2" s="247"/>
+      <c r="AI2" s="248"/>
       <c r="AN2" s="17"/>
       <c r="AO2" s="17"/>
       <c r="AP2" s="17"/>
     </row>
     <row r="3" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="257" t="s">
+      <c r="A3" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="258"/>
-      <c r="C3" s="258"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="260" t="str">
+      <c r="B3" s="250"/>
+      <c r="C3" s="250"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="252" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="261"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="261"/>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="M3" s="261"/>
-      <c r="N3" s="262"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="274"/>
-      <c r="S3" s="281"/>
-      <c r="T3" s="282"/>
-      <c r="U3" s="282"/>
-      <c r="V3" s="282"/>
-      <c r="W3" s="282"/>
-      <c r="X3" s="282"/>
-      <c r="Y3" s="282"/>
-      <c r="Z3" s="283"/>
-      <c r="AA3" s="257"/>
-      <c r="AB3" s="259"/>
-      <c r="AC3" s="263" t="str">
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="254"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="266"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="275"/>
+      <c r="AA3" s="249"/>
+      <c r="AB3" s="251"/>
+      <c r="AC3" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="264"/>
-      <c r="AE3" s="264"/>
-      <c r="AF3" s="265"/>
-      <c r="AG3" s="245" t="str">
+      <c r="AD3" s="256"/>
+      <c r="AE3" s="256"/>
+      <c r="AF3" s="257"/>
+      <c r="AG3" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="246"/>
-      <c r="AI3" s="247"/>
+      <c r="AH3" s="247"/>
+      <c r="AI3" s="248"/>
       <c r="AN3" s="17"/>
       <c r="AO3" s="17"/>
       <c r="AP3" s="17"/>
@@ -32433,70 +32433,70 @@
       <c r="C14" s="36"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="D15" s="248" t="s">
+      <c r="D15" s="276" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="249"/>
-      <c r="F15" s="249"/>
-      <c r="G15" s="249"/>
-      <c r="H15" s="249"/>
-      <c r="I15" s="249"/>
-      <c r="J15" s="250"/>
-      <c r="K15" s="248" t="s">
+      <c r="E15" s="277"/>
+      <c r="F15" s="277"/>
+      <c r="G15" s="277"/>
+      <c r="H15" s="277"/>
+      <c r="I15" s="277"/>
+      <c r="J15" s="278"/>
+      <c r="K15" s="276" t="s">
         <v>55</v>
       </c>
-      <c r="L15" s="249"/>
-      <c r="M15" s="249"/>
-      <c r="N15" s="249"/>
-      <c r="O15" s="249"/>
-      <c r="P15" s="249"/>
-      <c r="Q15" s="249"/>
-      <c r="R15" s="249"/>
-      <c r="S15" s="249"/>
-      <c r="T15" s="249"/>
-      <c r="U15" s="249"/>
-      <c r="V15" s="249"/>
-      <c r="W15" s="249"/>
-      <c r="X15" s="249"/>
-      <c r="Y15" s="249"/>
-      <c r="Z15" s="249"/>
-      <c r="AA15" s="249"/>
-      <c r="AB15" s="249"/>
-      <c r="AC15" s="249"/>
-      <c r="AD15" s="250"/>
+      <c r="L15" s="277"/>
+      <c r="M15" s="277"/>
+      <c r="N15" s="277"/>
+      <c r="O15" s="277"/>
+      <c r="P15" s="277"/>
+      <c r="Q15" s="277"/>
+      <c r="R15" s="277"/>
+      <c r="S15" s="277"/>
+      <c r="T15" s="277"/>
+      <c r="U15" s="277"/>
+      <c r="V15" s="277"/>
+      <c r="W15" s="277"/>
+      <c r="X15" s="277"/>
+      <c r="Y15" s="277"/>
+      <c r="Z15" s="277"/>
+      <c r="AA15" s="277"/>
+      <c r="AB15" s="277"/>
+      <c r="AC15" s="277"/>
+      <c r="AD15" s="278"/>
     </row>
     <row r="16" spans="1:42" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D16" s="254" t="s">
+      <c r="D16" s="282" t="s">
         <v>272</v>
       </c>
-      <c r="E16" s="255"/>
-      <c r="F16" s="255"/>
-      <c r="G16" s="255"/>
-      <c r="H16" s="255"/>
-      <c r="I16" s="255"/>
-      <c r="J16" s="256"/>
-      <c r="K16" s="251" t="s">
+      <c r="E16" s="283"/>
+      <c r="F16" s="283"/>
+      <c r="G16" s="283"/>
+      <c r="H16" s="283"/>
+      <c r="I16" s="283"/>
+      <c r="J16" s="284"/>
+      <c r="K16" s="279" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="252"/>
-      <c r="M16" s="252"/>
-      <c r="N16" s="252"/>
-      <c r="O16" s="252"/>
-      <c r="P16" s="252"/>
-      <c r="Q16" s="252"/>
-      <c r="R16" s="252"/>
-      <c r="S16" s="252"/>
-      <c r="T16" s="252"/>
-      <c r="U16" s="252"/>
-      <c r="V16" s="252"/>
-      <c r="W16" s="252"/>
-      <c r="X16" s="252"/>
-      <c r="Y16" s="252"/>
-      <c r="Z16" s="252"/>
-      <c r="AA16" s="252"/>
-      <c r="AB16" s="252"/>
-      <c r="AC16" s="252"/>
-      <c r="AD16" s="253"/>
+      <c r="L16" s="280"/>
+      <c r="M16" s="280"/>
+      <c r="N16" s="280"/>
+      <c r="O16" s="280"/>
+      <c r="P16" s="280"/>
+      <c r="Q16" s="280"/>
+      <c r="R16" s="280"/>
+      <c r="S16" s="280"/>
+      <c r="T16" s="280"/>
+      <c r="U16" s="280"/>
+      <c r="V16" s="280"/>
+      <c r="W16" s="280"/>
+      <c r="X16" s="280"/>
+      <c r="Y16" s="280"/>
+      <c r="Z16" s="280"/>
+      <c r="AA16" s="280"/>
+      <c r="AB16" s="280"/>
+      <c r="AC16" s="280"/>
+      <c r="AD16" s="281"/>
     </row>
     <row r="19" spans="3:21" s="156" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C19" s="166" t="s">
@@ -32696,7 +32696,7 @@
       <c r="D30" s="162">
         <v>7</v>
       </c>
-      <c r="E30" s="371" t="s">
+      <c r="E30" s="173" t="s">
         <v>720</v>
       </c>
       <c r="F30" s="163"/>
@@ -33035,6 +33035,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="K15:AD15"/>
+    <mergeCell ref="K16:AD16"/>
+    <mergeCell ref="D15:J15"/>
+    <mergeCell ref="D16:J16"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
@@ -33051,11 +33056,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="K15:AD15"/>
-    <mergeCell ref="K16:AD16"/>
-    <mergeCell ref="D15:J15"/>
-    <mergeCell ref="D16:J16"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <hyperlinks>
@@ -33101,157 +33101,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="257" t="s">
+      <c r="A1" s="249" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="261"/>
-      <c r="G1" s="261"/>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261"/>
-      <c r="K1" s="261"/>
-      <c r="L1" s="261"/>
-      <c r="M1" s="261"/>
-      <c r="N1" s="262"/>
-      <c r="O1" s="266" t="s">
+      <c r="B1" s="250"/>
+      <c r="C1" s="250"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="253"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="258" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="267"/>
-      <c r="Q1" s="267"/>
-      <c r="R1" s="268"/>
-      <c r="S1" s="275" t="str">
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="260"/>
+      <c r="S1" s="267" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="276"/>
-      <c r="U1" s="276"/>
-      <c r="V1" s="276"/>
-      <c r="W1" s="276"/>
-      <c r="X1" s="276"/>
-      <c r="Y1" s="276"/>
-      <c r="Z1" s="277"/>
-      <c r="AA1" s="257" t="s">
+      <c r="T1" s="268"/>
+      <c r="U1" s="268"/>
+      <c r="V1" s="268"/>
+      <c r="W1" s="268"/>
+      <c r="X1" s="268"/>
+      <c r="Y1" s="268"/>
+      <c r="Z1" s="269"/>
+      <c r="AA1" s="249" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="259"/>
-      <c r="AC1" s="263" t="str">
+      <c r="AB1" s="251"/>
+      <c r="AC1" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="264"/>
-      <c r="AE1" s="264"/>
-      <c r="AF1" s="265"/>
-      <c r="AG1" s="284">
+      <c r="AD1" s="256"/>
+      <c r="AE1" s="256"/>
+      <c r="AF1" s="257"/>
+      <c r="AG1" s="301">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
-      </c>
-      <c r="AH1" s="285"/>
-      <c r="AI1" s="286"/>
+        <v>45565</v>
+      </c>
+      <c r="AH1" s="302"/>
+      <c r="AI1" s="303"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="257" t="s">
+      <c r="A2" s="249" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="258"/>
-      <c r="C2" s="258"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="261"/>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="269"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="271"/>
-      <c r="S2" s="278"/>
-      <c r="T2" s="279"/>
-      <c r="U2" s="279"/>
-      <c r="V2" s="279"/>
-      <c r="W2" s="279"/>
-      <c r="X2" s="279"/>
-      <c r="Y2" s="279"/>
-      <c r="Z2" s="280"/>
-      <c r="AA2" s="257" t="s">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="271"/>
+      <c r="U2" s="271"/>
+      <c r="V2" s="271"/>
+      <c r="W2" s="271"/>
+      <c r="X2" s="271"/>
+      <c r="Y2" s="271"/>
+      <c r="Z2" s="272"/>
+      <c r="AA2" s="249" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="259"/>
-      <c r="AC2" s="263" t="str">
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="264"/>
-      <c r="AE2" s="264"/>
-      <c r="AF2" s="265"/>
-      <c r="AG2" s="284" t="str">
+      <c r="AD2" s="256"/>
+      <c r="AE2" s="256"/>
+      <c r="AF2" s="257"/>
+      <c r="AG2" s="301" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="285"/>
-      <c r="AI2" s="286"/>
+      <c r="AH2" s="302"/>
+      <c r="AI2" s="303"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="257" t="s">
+      <c r="A3" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="258"/>
-      <c r="C3" s="258"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="260" t="str">
+      <c r="B3" s="250"/>
+      <c r="C3" s="250"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="252" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="261"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="261"/>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="M3" s="261"/>
-      <c r="N3" s="262"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="274"/>
-      <c r="S3" s="281"/>
-      <c r="T3" s="282"/>
-      <c r="U3" s="282"/>
-      <c r="V3" s="282"/>
-      <c r="W3" s="282"/>
-      <c r="X3" s="282"/>
-      <c r="Y3" s="282"/>
-      <c r="Z3" s="283"/>
-      <c r="AA3" s="257"/>
-      <c r="AB3" s="259"/>
-      <c r="AC3" s="263" t="str">
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="254"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="266"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="275"/>
+      <c r="AA3" s="249"/>
+      <c r="AB3" s="251"/>
+      <c r="AC3" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="264"/>
-      <c r="AE3" s="264"/>
-      <c r="AF3" s="265"/>
-      <c r="AG3" s="284" t="str">
+      <c r="AD3" s="256"/>
+      <c r="AE3" s="256"/>
+      <c r="AF3" s="257"/>
+      <c r="AG3" s="301" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="285"/>
-      <c r="AI3" s="286"/>
+      <c r="AH3" s="302"/>
+      <c r="AI3" s="303"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -33367,12 +33367,12 @@
       <c r="V20" s="30"/>
     </row>
     <row r="21" spans="4:23" x14ac:dyDescent="0.15">
-      <c r="F21" s="287" t="s">
+      <c r="F21" s="285" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="288"/>
-      <c r="H21" s="288"/>
-      <c r="I21" s="289"/>
+      <c r="G21" s="286"/>
+      <c r="H21" s="286"/>
+      <c r="I21" s="287"/>
       <c r="J21" s="58" t="s">
         <v>26</v>
       </c>
@@ -34785,17 +34785,17 @@
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="30"/>
-      <c r="G63" s="300" t="s">
+      <c r="G63" s="298" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="301"/>
-      <c r="I63" s="301"/>
-      <c r="J63" s="302"/>
-      <c r="K63" s="248" t="s">
+      <c r="H63" s="299"/>
+      <c r="I63" s="299"/>
+      <c r="J63" s="300"/>
+      <c r="K63" s="276" t="s">
         <v>69</v>
       </c>
-      <c r="L63" s="249"/>
-      <c r="M63" s="250"/>
+      <c r="L63" s="277"/>
+      <c r="M63" s="278"/>
       <c r="N63" s="58" t="s">
         <v>198</v>
       </c>
@@ -34837,17 +34837,17 @@
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
       <c r="F64" s="29"/>
-      <c r="G64" s="290" t="s">
+      <c r="G64" s="288" t="s">
         <v>566</v>
       </c>
-      <c r="H64" s="291"/>
-      <c r="I64" s="291"/>
-      <c r="J64" s="292"/>
-      <c r="K64" s="290" t="s">
+      <c r="H64" s="289"/>
+      <c r="I64" s="289"/>
+      <c r="J64" s="290"/>
+      <c r="K64" s="288" t="s">
         <v>567</v>
       </c>
-      <c r="L64" s="291"/>
-      <c r="M64" s="292"/>
+      <c r="L64" s="289"/>
+      <c r="M64" s="290"/>
       <c r="N64" s="64" t="s">
         <v>396</v>
       </c>
@@ -34889,13 +34889,13 @@
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="29"/>
-      <c r="G65" s="293"/>
-      <c r="H65" s="294"/>
-      <c r="I65" s="294"/>
-      <c r="J65" s="295"/>
-      <c r="K65" s="299"/>
-      <c r="L65" s="294"/>
-      <c r="M65" s="295"/>
+      <c r="G65" s="291"/>
+      <c r="H65" s="292"/>
+      <c r="I65" s="292"/>
+      <c r="J65" s="293"/>
+      <c r="K65" s="297"/>
+      <c r="L65" s="292"/>
+      <c r="M65" s="293"/>
       <c r="N65" s="54" t="s">
         <v>397</v>
       </c>
@@ -34937,13 +34937,13 @@
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
       <c r="F66" s="29"/>
-      <c r="G66" s="293"/>
-      <c r="H66" s="294"/>
-      <c r="I66" s="294"/>
-      <c r="J66" s="295"/>
-      <c r="K66" s="293"/>
-      <c r="L66" s="294"/>
-      <c r="M66" s="295"/>
+      <c r="G66" s="291"/>
+      <c r="H66" s="292"/>
+      <c r="I66" s="292"/>
+      <c r="J66" s="293"/>
+      <c r="K66" s="291"/>
+      <c r="L66" s="292"/>
+      <c r="M66" s="293"/>
       <c r="N66" s="54" t="s">
         <v>390</v>
       </c>
@@ -34985,13 +34985,13 @@
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
       <c r="F67" s="29"/>
-      <c r="G67" s="293"/>
-      <c r="H67" s="294"/>
-      <c r="I67" s="294"/>
-      <c r="J67" s="295"/>
-      <c r="K67" s="293"/>
-      <c r="L67" s="294"/>
-      <c r="M67" s="295"/>
+      <c r="G67" s="291"/>
+      <c r="H67" s="292"/>
+      <c r="I67" s="292"/>
+      <c r="J67" s="293"/>
+      <c r="K67" s="291"/>
+      <c r="L67" s="292"/>
+      <c r="M67" s="293"/>
       <c r="N67" s="54" t="s">
         <v>633</v>
       </c>
@@ -35033,13 +35033,13 @@
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68"/>
-      <c r="G68" s="296"/>
-      <c r="H68" s="297"/>
-      <c r="I68" s="297"/>
-      <c r="J68" s="298"/>
-      <c r="K68" s="296"/>
-      <c r="L68" s="297"/>
-      <c r="M68" s="298"/>
+      <c r="G68" s="294"/>
+      <c r="H68" s="295"/>
+      <c r="I68" s="295"/>
+      <c r="J68" s="296"/>
+      <c r="K68" s="294"/>
+      <c r="L68" s="295"/>
+      <c r="M68" s="296"/>
       <c r="N68" s="73"/>
       <c r="O68" s="74"/>
       <c r="P68" s="74"/>
@@ -35424,12 +35424,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="G64:J68"/>
-    <mergeCell ref="K64:M68"/>
-    <mergeCell ref="G63:J63"/>
-    <mergeCell ref="K63:M63"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
@@ -35446,6 +35440,12 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="G64:J68"/>
+    <mergeCell ref="K64:M68"/>
+    <mergeCell ref="G63:J63"/>
+    <mergeCell ref="K63:M63"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -35475,157 +35475,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="257" t="s">
+      <c r="A1" s="249" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="261"/>
-      <c r="G1" s="261"/>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261"/>
-      <c r="K1" s="261"/>
-      <c r="L1" s="261"/>
-      <c r="M1" s="261"/>
-      <c r="N1" s="262"/>
-      <c r="O1" s="303" t="s">
+      <c r="B1" s="250"/>
+      <c r="C1" s="250"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="253"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="304" t="s">
         <v>96</v>
       </c>
-      <c r="P1" s="267"/>
-      <c r="Q1" s="267"/>
-      <c r="R1" s="304"/>
-      <c r="S1" s="305" t="str">
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="305"/>
+      <c r="S1" s="306" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="276"/>
-      <c r="U1" s="276"/>
-      <c r="V1" s="276"/>
-      <c r="W1" s="276"/>
-      <c r="X1" s="276"/>
-      <c r="Y1" s="276"/>
-      <c r="Z1" s="306"/>
-      <c r="AA1" s="257" t="s">
+      <c r="T1" s="268"/>
+      <c r="U1" s="268"/>
+      <c r="V1" s="268"/>
+      <c r="W1" s="268"/>
+      <c r="X1" s="268"/>
+      <c r="Y1" s="268"/>
+      <c r="Z1" s="307"/>
+      <c r="AA1" s="249" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="259"/>
-      <c r="AC1" s="263" t="str">
+      <c r="AB1" s="251"/>
+      <c r="AC1" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="264"/>
-      <c r="AE1" s="264"/>
-      <c r="AF1" s="265"/>
-      <c r="AG1" s="284">
+      <c r="AD1" s="256"/>
+      <c r="AE1" s="256"/>
+      <c r="AF1" s="257"/>
+      <c r="AG1" s="301">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
-      </c>
-      <c r="AH1" s="285"/>
-      <c r="AI1" s="286"/>
+        <v>45565</v>
+      </c>
+      <c r="AH1" s="302"/>
+      <c r="AI1" s="303"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="257" t="s">
+      <c r="A2" s="249" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="258"/>
-      <c r="C2" s="258"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="261"/>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="269"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="271"/>
-      <c r="S2" s="278"/>
-      <c r="T2" s="279"/>
-      <c r="U2" s="279"/>
-      <c r="V2" s="279"/>
-      <c r="W2" s="279"/>
-      <c r="X2" s="279"/>
-      <c r="Y2" s="279"/>
-      <c r="Z2" s="280"/>
-      <c r="AA2" s="257" t="s">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="271"/>
+      <c r="U2" s="271"/>
+      <c r="V2" s="271"/>
+      <c r="W2" s="271"/>
+      <c r="X2" s="271"/>
+      <c r="Y2" s="271"/>
+      <c r="Z2" s="272"/>
+      <c r="AA2" s="249" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="259"/>
-      <c r="AC2" s="263" t="str">
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="264"/>
-      <c r="AE2" s="264"/>
-      <c r="AF2" s="265"/>
-      <c r="AG2" s="284" t="str">
+      <c r="AD2" s="256"/>
+      <c r="AE2" s="256"/>
+      <c r="AF2" s="257"/>
+      <c r="AG2" s="301" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="285"/>
-      <c r="AI2" s="286"/>
+      <c r="AH2" s="302"/>
+      <c r="AI2" s="303"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="257" t="s">
+      <c r="A3" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="258"/>
-      <c r="C3" s="258"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="260" t="str">
+      <c r="B3" s="250"/>
+      <c r="C3" s="250"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="252" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="261"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="261"/>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="M3" s="261"/>
-      <c r="N3" s="262"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="274"/>
-      <c r="S3" s="281"/>
-      <c r="T3" s="282"/>
-      <c r="U3" s="282"/>
-      <c r="V3" s="282"/>
-      <c r="W3" s="282"/>
-      <c r="X3" s="282"/>
-      <c r="Y3" s="282"/>
-      <c r="Z3" s="283"/>
-      <c r="AA3" s="257"/>
-      <c r="AB3" s="259"/>
-      <c r="AC3" s="263" t="str">
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="254"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="266"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="275"/>
+      <c r="AA3" s="249"/>
+      <c r="AB3" s="251"/>
+      <c r="AC3" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="264"/>
-      <c r="AE3" s="264"/>
-      <c r="AF3" s="265"/>
-      <c r="AG3" s="284" t="str">
+      <c r="AD3" s="256"/>
+      <c r="AE3" s="256"/>
+      <c r="AF3" s="257"/>
+      <c r="AG3" s="301" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="285"/>
-      <c r="AI3" s="286"/>
+      <c r="AH3" s="302"/>
+      <c r="AI3" s="303"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -35659,41 +35659,41 @@
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="E14" s="300" t="s">
+      <c r="E14" s="298" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="301"/>
-      <c r="G14" s="301"/>
-      <c r="H14" s="301"/>
-      <c r="I14" s="301"/>
-      <c r="J14" s="302"/>
-      <c r="K14" s="300" t="s">
+      <c r="F14" s="299"/>
+      <c r="G14" s="299"/>
+      <c r="H14" s="299"/>
+      <c r="I14" s="299"/>
+      <c r="J14" s="300"/>
+      <c r="K14" s="298" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="301"/>
-      <c r="M14" s="301"/>
-      <c r="N14" s="301"/>
-      <c r="O14" s="301"/>
-      <c r="P14" s="301"/>
-      <c r="Q14" s="301"/>
-      <c r="R14" s="301"/>
-      <c r="S14" s="302"/>
-      <c r="T14" s="300" t="s">
+      <c r="L14" s="299"/>
+      <c r="M14" s="299"/>
+      <c r="N14" s="299"/>
+      <c r="O14" s="299"/>
+      <c r="P14" s="299"/>
+      <c r="Q14" s="299"/>
+      <c r="R14" s="299"/>
+      <c r="S14" s="300"/>
+      <c r="T14" s="298" t="s">
         <v>94</v>
       </c>
-      <c r="U14" s="301"/>
-      <c r="V14" s="301"/>
-      <c r="W14" s="301"/>
-      <c r="X14" s="301"/>
-      <c r="Y14" s="301"/>
-      <c r="Z14" s="301"/>
-      <c r="AA14" s="301"/>
-      <c r="AB14" s="301"/>
-      <c r="AC14" s="301"/>
-      <c r="AD14" s="301"/>
-      <c r="AE14" s="301"/>
-      <c r="AF14" s="301"/>
-      <c r="AG14" s="302"/>
+      <c r="U14" s="299"/>
+      <c r="V14" s="299"/>
+      <c r="W14" s="299"/>
+      <c r="X14" s="299"/>
+      <c r="Y14" s="299"/>
+      <c r="Z14" s="299"/>
+      <c r="AA14" s="299"/>
+      <c r="AB14" s="299"/>
+      <c r="AC14" s="299"/>
+      <c r="AD14" s="299"/>
+      <c r="AE14" s="299"/>
+      <c r="AF14" s="299"/>
+      <c r="AG14" s="300"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.15">
       <c r="E15" s="80" t="s">
@@ -38335,11 +38335,6 @@
     <row r="346" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="K14:S14"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -38355,6 +38350,11 @@
     <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="E14:J14"/>
+    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AG1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>
@@ -38396,151 +38396,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="257" t="s">
+      <c r="A1" s="249" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="261"/>
-      <c r="G1" s="261"/>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261"/>
-      <c r="K1" s="261"/>
-      <c r="L1" s="261"/>
-      <c r="M1" s="261"/>
-      <c r="N1" s="262"/>
-      <c r="O1" s="266" t="s">
+      <c r="B1" s="250"/>
+      <c r="C1" s="250"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="253"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="258" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="267"/>
-      <c r="Q1" s="267"/>
-      <c r="R1" s="268"/>
-      <c r="S1" s="275" t="str">
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="260"/>
+      <c r="S1" s="267" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="276"/>
-      <c r="U1" s="276"/>
-      <c r="V1" s="276"/>
-      <c r="W1" s="276"/>
-      <c r="X1" s="276"/>
-      <c r="Y1" s="276"/>
-      <c r="Z1" s="277"/>
-      <c r="AA1" s="257" t="s">
+      <c r="T1" s="268"/>
+      <c r="U1" s="268"/>
+      <c r="V1" s="268"/>
+      <c r="W1" s="268"/>
+      <c r="X1" s="268"/>
+      <c r="Y1" s="268"/>
+      <c r="Z1" s="269"/>
+      <c r="AA1" s="249" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="259"/>
-      <c r="AC1" s="263" t="str">
+      <c r="AB1" s="251"/>
+      <c r="AC1" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="264"/>
-      <c r="AE1" s="264"/>
-      <c r="AF1" s="265"/>
-      <c r="AG1" s="284">
+      <c r="AD1" s="256"/>
+      <c r="AE1" s="256"/>
+      <c r="AF1" s="257"/>
+      <c r="AG1" s="301">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
-      </c>
-      <c r="AH1" s="285"/>
-      <c r="AI1" s="286"/>
+        <v>45565</v>
+      </c>
+      <c r="AH1" s="302"/>
+      <c r="AI1" s="303"/>
     </row>
     <row r="2" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="257" t="s">
+      <c r="A2" s="249" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="258"/>
-      <c r="C2" s="258"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="261"/>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="269"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="271"/>
-      <c r="S2" s="278"/>
-      <c r="T2" s="279"/>
-      <c r="U2" s="279"/>
-      <c r="V2" s="279"/>
-      <c r="W2" s="279"/>
-      <c r="X2" s="279"/>
-      <c r="Y2" s="279"/>
-      <c r="Z2" s="280"/>
-      <c r="AA2" s="257" t="s">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="271"/>
+      <c r="U2" s="271"/>
+      <c r="V2" s="271"/>
+      <c r="W2" s="271"/>
+      <c r="X2" s="271"/>
+      <c r="Y2" s="271"/>
+      <c r="Z2" s="272"/>
+      <c r="AA2" s="249" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="259"/>
-      <c r="AC2" s="263" t="str">
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="264"/>
-      <c r="AE2" s="264"/>
-      <c r="AF2" s="265"/>
-      <c r="AG2" s="284" t="str">
+      <c r="AD2" s="256"/>
+      <c r="AE2" s="256"/>
+      <c r="AF2" s="257"/>
+      <c r="AG2" s="301" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="285"/>
-      <c r="AI2" s="286"/>
+      <c r="AH2" s="302"/>
+      <c r="AI2" s="303"/>
     </row>
     <row r="3" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="257" t="s">
+      <c r="A3" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="258"/>
-      <c r="C3" s="258"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="260" t="str">
+      <c r="B3" s="250"/>
+      <c r="C3" s="250"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="252" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="261"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="261"/>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="M3" s="261"/>
-      <c r="N3" s="262"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="274"/>
-      <c r="S3" s="281"/>
-      <c r="T3" s="282"/>
-      <c r="U3" s="282"/>
-      <c r="V3" s="282"/>
-      <c r="W3" s="282"/>
-      <c r="X3" s="282"/>
-      <c r="Y3" s="282"/>
-      <c r="Z3" s="283"/>
-      <c r="AA3" s="257"/>
-      <c r="AB3" s="259"/>
-      <c r="AC3" s="263" t="str">
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="254"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="266"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="275"/>
+      <c r="AA3" s="249"/>
+      <c r="AB3" s="251"/>
+      <c r="AC3" s="255" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="264"/>
-      <c r="AE3" s="264"/>
-      <c r="AF3" s="265"/>
-      <c r="AG3" s="284" t="str">
+      <c r="AD3" s="256"/>
+      <c r="AE3" s="256"/>
+      <c r="AF3" s="257"/>
+      <c r="AG3" s="301" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="285"/>
-      <c r="AI3" s="286"/>
+      <c r="AH3" s="302"/>
+      <c r="AI3" s="303"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B5" s="32" t="s">
@@ -39644,12 +39644,12 @@
     <row r="74" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A74" s="30"/>
       <c r="E74" s="30"/>
-      <c r="F74" s="248" t="s">
+      <c r="F74" s="276" t="s">
         <v>50</v>
       </c>
-      <c r="G74" s="249"/>
-      <c r="H74" s="249"/>
-      <c r="I74" s="250"/>
+      <c r="G74" s="277"/>
+      <c r="H74" s="277"/>
+      <c r="I74" s="278"/>
       <c r="J74" s="58" t="s">
         <v>190</v>
       </c>
@@ -39678,12 +39678,12 @@
     <row r="75" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="30"/>
       <c r="E75" s="30"/>
-      <c r="F75" s="307" t="s">
+      <c r="F75" s="310" t="s">
         <v>229</v>
       </c>
-      <c r="G75" s="308"/>
-      <c r="H75" s="308"/>
-      <c r="I75" s="309"/>
+      <c r="G75" s="311"/>
+      <c r="H75" s="311"/>
+      <c r="I75" s="312"/>
       <c r="J75" s="83" t="s">
         <v>237</v>
       </c>
@@ -39713,12 +39713,12 @@
       <c r="A76" s="30"/>
       <c r="C76" s="30"/>
       <c r="E76" s="30"/>
-      <c r="F76" s="310" t="s">
+      <c r="F76" s="317" t="s">
         <v>330</v>
       </c>
-      <c r="G76" s="311"/>
-      <c r="H76" s="311"/>
-      <c r="I76" s="312"/>
+      <c r="G76" s="318"/>
+      <c r="H76" s="318"/>
+      <c r="I76" s="319"/>
       <c r="J76" s="72" t="s">
         <v>191</v>
       </c>
@@ -39748,10 +39748,10 @@
       <c r="A77" s="30"/>
       <c r="C77" s="30"/>
       <c r="E77" s="30"/>
-      <c r="F77" s="313"/>
-      <c r="G77" s="314"/>
-      <c r="H77" s="314"/>
-      <c r="I77" s="315"/>
+      <c r="F77" s="320"/>
+      <c r="G77" s="321"/>
+      <c r="H77" s="321"/>
+      <c r="I77" s="322"/>
       <c r="J77" s="73"/>
       <c r="K77" s="74"/>
       <c r="L77" s="74"/>
@@ -39776,12 +39776,12 @@
     <row r="78" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A78" s="30"/>
       <c r="E78" s="30"/>
-      <c r="F78" s="307" t="s">
+      <c r="F78" s="310" t="s">
         <v>230</v>
       </c>
-      <c r="G78" s="308"/>
-      <c r="H78" s="308"/>
-      <c r="I78" s="309"/>
+      <c r="G78" s="311"/>
+      <c r="H78" s="311"/>
+      <c r="I78" s="312"/>
       <c r="J78" s="80" t="s">
         <v>192</v>
       </c>
@@ -39810,12 +39810,12 @@
     <row r="79" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A79" s="30"/>
       <c r="E79" s="30"/>
-      <c r="F79" s="307" t="s">
+      <c r="F79" s="310" t="s">
         <v>228</v>
       </c>
-      <c r="G79" s="308"/>
-      <c r="H79" s="308"/>
-      <c r="I79" s="309"/>
+      <c r="G79" s="311"/>
+      <c r="H79" s="311"/>
+      <c r="I79" s="312"/>
       <c r="J79" s="83" t="s">
         <v>195</v>
       </c>
@@ -39845,12 +39845,12 @@
     <row r="80" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A80" s="30"/>
       <c r="E80" s="30"/>
-      <c r="F80" s="307" t="s">
+      <c r="F80" s="310" t="s">
         <v>227</v>
       </c>
-      <c r="G80" s="308"/>
-      <c r="H80" s="308"/>
-      <c r="I80" s="309"/>
+      <c r="G80" s="311"/>
+      <c r="H80" s="311"/>
+      <c r="I80" s="312"/>
       <c r="J80" s="80" t="s">
         <v>193</v>
       </c>
@@ -39996,7 +39996,7 @@
       <c r="AG137" s="51"/>
     </row>
     <row r="138" spans="5:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F138" s="318">
+      <c r="F138" s="313">
         <v>1</v>
       </c>
       <c r="G138" s="64" t="s">
@@ -40032,7 +40032,7 @@
       <c r="AG138" s="51"/>
     </row>
     <row r="139" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F139" s="319"/>
+      <c r="F139" s="314"/>
       <c r="G139" s="54"/>
       <c r="H139" s="30"/>
       <c r="I139" s="30"/>
@@ -40064,7 +40064,7 @@
       <c r="AG139" s="51"/>
     </row>
     <row r="140" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F140" s="319"/>
+      <c r="F140" s="314"/>
       <c r="G140" s="54"/>
       <c r="H140" s="30"/>
       <c r="I140" s="30"/>
@@ -40096,7 +40096,7 @@
       <c r="AG140" s="51"/>
     </row>
     <row r="141" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F141" s="319"/>
+      <c r="F141" s="314"/>
       <c r="G141" s="54"/>
       <c r="H141" s="30"/>
       <c r="I141" s="30"/>
@@ -40128,7 +40128,7 @@
       <c r="AG141" s="51"/>
     </row>
     <row r="142" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F142" s="319"/>
+      <c r="F142" s="314"/>
       <c r="G142" s="54"/>
       <c r="H142" s="30"/>
       <c r="I142" s="30"/>
@@ -40160,7 +40160,7 @@
       <c r="AG142" s="51"/>
     </row>
     <row r="143" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F143" s="319"/>
+      <c r="F143" s="314"/>
       <c r="G143" s="54"/>
       <c r="H143" s="30"/>
       <c r="I143" s="30"/>
@@ -40192,7 +40192,7 @@
       <c r="AG143" s="51"/>
     </row>
     <row r="144" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F144" s="319"/>
+      <c r="F144" s="314"/>
       <c r="G144" s="54"/>
       <c r="H144" s="30"/>
       <c r="I144" s="30"/>
@@ -40224,7 +40224,7 @@
       <c r="AG144" s="51"/>
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F145" s="320"/>
+      <c r="F145" s="315"/>
       <c r="G145" s="54"/>
       <c r="H145" s="30"/>
       <c r="I145" s="30"/>
@@ -40322,7 +40322,7 @@
       <c r="AG147" s="17"/>
     </row>
     <row r="148" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F148" s="318">
+      <c r="F148" s="313">
         <v>3</v>
       </c>
       <c r="G148" s="54" t="s">
@@ -40358,7 +40358,7 @@
       <c r="AG148" s="51"/>
     </row>
     <row r="149" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F149" s="319"/>
+      <c r="F149" s="314"/>
       <c r="G149" s="54"/>
       <c r="H149" s="30"/>
       <c r="I149" s="30"/>
@@ -40390,7 +40390,7 @@
       <c r="AG149" s="51"/>
     </row>
     <row r="150" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F150" s="319"/>
+      <c r="F150" s="314"/>
       <c r="G150" s="54"/>
       <c r="H150" s="30"/>
       <c r="I150" s="30"/>
@@ -40422,7 +40422,7 @@
       <c r="AG150" s="51"/>
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F151" s="319"/>
+      <c r="F151" s="314"/>
       <c r="G151" s="54"/>
       <c r="H151" s="30"/>
       <c r="I151" s="30"/>
@@ -40454,7 +40454,7 @@
       <c r="AG151" s="51"/>
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F152" s="319"/>
+      <c r="F152" s="314"/>
       <c r="G152" s="54"/>
       <c r="H152" s="30"/>
       <c r="I152" s="30"/>
@@ -40486,7 +40486,7 @@
       <c r="AG152" s="51"/>
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F153" s="320"/>
+      <c r="F153" s="315"/>
       <c r="G153" s="54"/>
       <c r="H153" s="30"/>
       <c r="I153" s="30"/>
@@ -40518,7 +40518,7 @@
       <c r="AG153" s="51"/>
     </row>
     <row r="154" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F154" s="321">
+      <c r="F154" s="316">
         <v>4</v>
       </c>
       <c r="G154" s="64" t="s">
@@ -40554,7 +40554,7 @@
       <c r="AG154" s="51"/>
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F155" s="321"/>
+      <c r="F155" s="316"/>
       <c r="G155" s="73"/>
       <c r="H155" s="74"/>
       <c r="I155" s="74"/>
@@ -41027,7 +41027,7 @@
     </row>
     <row r="228" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A228" s="30"/>
-      <c r="F228" s="316"/>
+      <c r="F228" s="308"/>
       <c r="G228" s="83" t="s">
         <v>239</v>
       </c>
@@ -41064,7 +41064,7 @@
       <c r="AD228" s="113"/>
     </row>
     <row r="229" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="F229" s="316"/>
+      <c r="F229" s="308"/>
       <c r="G229" s="83" t="s">
         <v>279</v>
       </c>
@@ -41101,7 +41101,7 @@
       <c r="AD229" s="113"/>
     </row>
     <row r="230" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="F230" s="317"/>
+      <c r="F230" s="309"/>
       <c r="G230" s="84" t="s">
         <v>280</v>
       </c>
@@ -41612,21 +41612,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F228:F230"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F138:F145"/>
-    <mergeCell ref="F148:F153"/>
-    <mergeCell ref="F154:F155"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F74:I74"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="F76:I77"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="AG3:AI3"/>
@@ -41639,6 +41624,21 @@
     <mergeCell ref="S1:Z3"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="F76:I77"/>
+    <mergeCell ref="F228:F230"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F138:F145"/>
+    <mergeCell ref="F148:F153"/>
+    <mergeCell ref="F154:F155"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -41675,157 +41675,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-      <c r="M1" s="184"/>
-      <c r="N1" s="185"/>
-      <c r="O1" s="266" t="s">
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="258" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="267"/>
-      <c r="Q1" s="267"/>
-      <c r="R1" s="268"/>
-      <c r="S1" s="275" t="str">
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="260"/>
+      <c r="S1" s="267" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="276"/>
-      <c r="U1" s="276"/>
-      <c r="V1" s="276"/>
-      <c r="W1" s="276"/>
-      <c r="X1" s="276"/>
-      <c r="Y1" s="276"/>
-      <c r="Z1" s="277"/>
-      <c r="AA1" s="180" t="s">
+      <c r="T1" s="268"/>
+      <c r="U1" s="268"/>
+      <c r="V1" s="268"/>
+      <c r="W1" s="268"/>
+      <c r="X1" s="268"/>
+      <c r="Y1" s="268"/>
+      <c r="Z1" s="269"/>
+      <c r="AA1" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="182"/>
-      <c r="AC1" s="208" t="str">
+      <c r="AB1" s="210"/>
+      <c r="AC1" s="236" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="209"/>
-      <c r="AE1" s="209"/>
-      <c r="AF1" s="210"/>
-      <c r="AG1" s="348">
+      <c r="AD1" s="237"/>
+      <c r="AE1" s="237"/>
+      <c r="AF1" s="238"/>
+      <c r="AG1" s="357">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
-      </c>
-      <c r="AH1" s="349"/>
-      <c r="AI1" s="350"/>
+        <v>45565</v>
+      </c>
+      <c r="AH1" s="358"/>
+      <c r="AI1" s="359"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="180" t="s">
+      <c r="A2" s="208" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="181"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="184"/>
-      <c r="K2" s="184"/>
-      <c r="L2" s="184"/>
-      <c r="M2" s="184"/>
-      <c r="N2" s="185"/>
-      <c r="O2" s="269"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="271"/>
-      <c r="S2" s="278"/>
-      <c r="T2" s="279"/>
-      <c r="U2" s="279"/>
-      <c r="V2" s="279"/>
-      <c r="W2" s="279"/>
-      <c r="X2" s="279"/>
-      <c r="Y2" s="279"/>
-      <c r="Z2" s="280"/>
-      <c r="AA2" s="180" t="s">
+      <c r="B2" s="209"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="213"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="271"/>
+      <c r="U2" s="271"/>
+      <c r="V2" s="271"/>
+      <c r="W2" s="271"/>
+      <c r="X2" s="271"/>
+      <c r="Y2" s="271"/>
+      <c r="Z2" s="272"/>
+      <c r="AA2" s="208" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="182"/>
-      <c r="AC2" s="208" t="str">
+      <c r="AB2" s="210"/>
+      <c r="AC2" s="236" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="209"/>
-      <c r="AE2" s="209"/>
-      <c r="AF2" s="210"/>
-      <c r="AG2" s="348" t="str">
+      <c r="AD2" s="237"/>
+      <c r="AE2" s="237"/>
+      <c r="AF2" s="238"/>
+      <c r="AG2" s="357" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="349"/>
-      <c r="AI2" s="350"/>
+      <c r="AH2" s="358"/>
+      <c r="AI2" s="359"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="180" t="s">
+      <c r="A3" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="181"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="211" t="str">
+      <c r="B3" s="209"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
-      <c r="M3" s="184"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="274"/>
-      <c r="S3" s="281"/>
-      <c r="T3" s="282"/>
-      <c r="U3" s="282"/>
-      <c r="V3" s="282"/>
-      <c r="W3" s="282"/>
-      <c r="X3" s="282"/>
-      <c r="Y3" s="282"/>
-      <c r="Z3" s="283"/>
-      <c r="AA3" s="180"/>
-      <c r="AB3" s="182"/>
-      <c r="AC3" s="208" t="str">
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="213"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="266"/>
+      <c r="S3" s="273"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="275"/>
+      <c r="AA3" s="208"/>
+      <c r="AB3" s="210"/>
+      <c r="AC3" s="236" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="209"/>
-      <c r="AE3" s="209"/>
-      <c r="AF3" s="210"/>
-      <c r="AG3" s="348" t="str">
+      <c r="AD3" s="237"/>
+      <c r="AE3" s="237"/>
+      <c r="AF3" s="238"/>
+      <c r="AG3" s="357" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="349"/>
-      <c r="AI3" s="350"/>
+      <c r="AH3" s="358"/>
+      <c r="AI3" s="359"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -42308,477 +42308,477 @@
     </row>
     <row r="150" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="151" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D151" s="248" t="s">
+      <c r="D151" s="276" t="s">
         <v>325</v>
       </c>
-      <c r="E151" s="327"/>
-      <c r="F151" s="327"/>
-      <c r="G151" s="327"/>
-      <c r="H151" s="327"/>
-      <c r="I151" s="327"/>
-      <c r="J151" s="328"/>
-      <c r="K151" s="325" t="s">
+      <c r="E151" s="341"/>
+      <c r="F151" s="341"/>
+      <c r="G151" s="341"/>
+      <c r="H151" s="341"/>
+      <c r="I151" s="341"/>
+      <c r="J151" s="342"/>
+      <c r="K151" s="360" t="s">
         <v>50</v>
       </c>
-      <c r="L151" s="325"/>
-      <c r="M151" s="325"/>
-      <c r="N151" s="325"/>
-      <c r="O151" s="325"/>
-      <c r="P151" s="325"/>
-      <c r="Q151" s="325"/>
-      <c r="R151" s="325"/>
-      <c r="S151" s="325"/>
-      <c r="T151" s="325"/>
-      <c r="U151" s="325"/>
-      <c r="V151" s="325"/>
-      <c r="W151" s="325"/>
-      <c r="X151" s="325"/>
-      <c r="Y151" s="325"/>
-      <c r="Z151" s="325"/>
-      <c r="AA151" s="324" t="s">
+      <c r="L151" s="360"/>
+      <c r="M151" s="360"/>
+      <c r="N151" s="360"/>
+      <c r="O151" s="360"/>
+      <c r="P151" s="360"/>
+      <c r="Q151" s="360"/>
+      <c r="R151" s="360"/>
+      <c r="S151" s="360"/>
+      <c r="T151" s="360"/>
+      <c r="U151" s="360"/>
+      <c r="V151" s="360"/>
+      <c r="W151" s="360"/>
+      <c r="X151" s="360"/>
+      <c r="Y151" s="360"/>
+      <c r="Z151" s="360"/>
+      <c r="AA151" s="367" t="s">
         <v>51</v>
       </c>
-      <c r="AB151" s="325"/>
-      <c r="AC151" s="325"/>
-      <c r="AD151" s="325"/>
-      <c r="AE151" s="325"/>
-      <c r="AF151" s="325"/>
-      <c r="AG151" s="325"/>
-      <c r="AH151" s="325"/>
+      <c r="AB151" s="360"/>
+      <c r="AC151" s="360"/>
+      <c r="AD151" s="360"/>
+      <c r="AE151" s="360"/>
+      <c r="AF151" s="360"/>
+      <c r="AG151" s="360"/>
+      <c r="AH151" s="360"/>
     </row>
     <row r="152" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D152" s="251" t="s">
+      <c r="D152" s="279" t="s">
         <v>52</v>
       </c>
-      <c r="E152" s="252"/>
-      <c r="F152" s="252"/>
-      <c r="G152" s="252"/>
-      <c r="H152" s="252"/>
-      <c r="I152" s="252"/>
-      <c r="J152" s="253"/>
-      <c r="K152" s="347" t="s">
+      <c r="E152" s="280"/>
+      <c r="F152" s="280"/>
+      <c r="G152" s="280"/>
+      <c r="H152" s="280"/>
+      <c r="I152" s="280"/>
+      <c r="J152" s="281"/>
+      <c r="K152" s="356" t="s">
         <v>289</v>
       </c>
-      <c r="L152" s="347"/>
-      <c r="M152" s="347"/>
-      <c r="N152" s="347"/>
-      <c r="O152" s="347"/>
-      <c r="P152" s="347"/>
-      <c r="Q152" s="347"/>
-      <c r="R152" s="347"/>
-      <c r="S152" s="347"/>
-      <c r="T152" s="347"/>
-      <c r="U152" s="347"/>
-      <c r="V152" s="347"/>
-      <c r="W152" s="347"/>
-      <c r="X152" s="347"/>
-      <c r="Y152" s="347"/>
-      <c r="Z152" s="347"/>
-      <c r="AA152" s="322" t="s">
+      <c r="L152" s="356"/>
+      <c r="M152" s="356"/>
+      <c r="N152" s="356"/>
+      <c r="O152" s="356"/>
+      <c r="P152" s="356"/>
+      <c r="Q152" s="356"/>
+      <c r="R152" s="356"/>
+      <c r="S152" s="356"/>
+      <c r="T152" s="356"/>
+      <c r="U152" s="356"/>
+      <c r="V152" s="356"/>
+      <c r="W152" s="356"/>
+      <c r="X152" s="356"/>
+      <c r="Y152" s="356"/>
+      <c r="Z152" s="356"/>
+      <c r="AA152" s="361" t="s">
         <v>75</v>
       </c>
-      <c r="AB152" s="323"/>
-      <c r="AC152" s="323"/>
-      <c r="AD152" s="323"/>
-      <c r="AE152" s="323"/>
-      <c r="AF152" s="323"/>
-      <c r="AG152" s="323"/>
-      <c r="AH152" s="323"/>
+      <c r="AB152" s="362"/>
+      <c r="AC152" s="362"/>
+      <c r="AD152" s="362"/>
+      <c r="AE152" s="362"/>
+      <c r="AF152" s="362"/>
+      <c r="AG152" s="362"/>
+      <c r="AH152" s="362"/>
     </row>
     <row r="153" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D153" s="307" t="s">
+      <c r="D153" s="310" t="s">
         <v>304</v>
       </c>
-      <c r="E153" s="308"/>
-      <c r="F153" s="308"/>
-      <c r="G153" s="308"/>
-      <c r="H153" s="308"/>
-      <c r="I153" s="308"/>
-      <c r="J153" s="309"/>
-      <c r="K153" s="347" t="s">
+      <c r="E153" s="311"/>
+      <c r="F153" s="311"/>
+      <c r="G153" s="311"/>
+      <c r="H153" s="311"/>
+      <c r="I153" s="311"/>
+      <c r="J153" s="312"/>
+      <c r="K153" s="356" t="s">
         <v>290</v>
       </c>
-      <c r="L153" s="347"/>
-      <c r="M153" s="347"/>
-      <c r="N153" s="347"/>
-      <c r="O153" s="347"/>
-      <c r="P153" s="347"/>
-      <c r="Q153" s="347"/>
-      <c r="R153" s="347"/>
-      <c r="S153" s="347"/>
-      <c r="T153" s="347"/>
-      <c r="U153" s="347"/>
-      <c r="V153" s="347"/>
-      <c r="W153" s="347"/>
-      <c r="X153" s="347"/>
-      <c r="Y153" s="347"/>
-      <c r="Z153" s="347"/>
-      <c r="AA153" s="322" t="s">
+      <c r="L153" s="356"/>
+      <c r="M153" s="356"/>
+      <c r="N153" s="356"/>
+      <c r="O153" s="356"/>
+      <c r="P153" s="356"/>
+      <c r="Q153" s="356"/>
+      <c r="R153" s="356"/>
+      <c r="S153" s="356"/>
+      <c r="T153" s="356"/>
+      <c r="U153" s="356"/>
+      <c r="V153" s="356"/>
+      <c r="W153" s="356"/>
+      <c r="X153" s="356"/>
+      <c r="Y153" s="356"/>
+      <c r="Z153" s="356"/>
+      <c r="AA153" s="361" t="s">
         <v>75</v>
       </c>
-      <c r="AB153" s="323"/>
-      <c r="AC153" s="323"/>
-      <c r="AD153" s="323"/>
-      <c r="AE153" s="323"/>
-      <c r="AF153" s="323"/>
-      <c r="AG153" s="323"/>
-      <c r="AH153" s="323"/>
+      <c r="AB153" s="362"/>
+      <c r="AC153" s="362"/>
+      <c r="AD153" s="362"/>
+      <c r="AE153" s="362"/>
+      <c r="AF153" s="362"/>
+      <c r="AG153" s="362"/>
+      <c r="AH153" s="362"/>
     </row>
     <row r="154" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D154" s="333" t="s">
+      <c r="D154" s="371" t="s">
         <v>320</v>
       </c>
-      <c r="E154" s="255"/>
-      <c r="F154" s="255"/>
-      <c r="G154" s="255"/>
-      <c r="H154" s="255"/>
-      <c r="I154" s="255"/>
-      <c r="J154" s="256"/>
-      <c r="K154" s="335" t="s">
+      <c r="E154" s="283"/>
+      <c r="F154" s="283"/>
+      <c r="G154" s="283"/>
+      <c r="H154" s="283"/>
+      <c r="I154" s="283"/>
+      <c r="J154" s="284"/>
+      <c r="K154" s="363" t="s">
         <v>322</v>
       </c>
-      <c r="L154" s="336"/>
-      <c r="M154" s="336"/>
-      <c r="N154" s="336"/>
-      <c r="O154" s="336"/>
-      <c r="P154" s="336"/>
-      <c r="Q154" s="336"/>
-      <c r="R154" s="336"/>
-      <c r="S154" s="336"/>
-      <c r="T154" s="336"/>
-      <c r="U154" s="336"/>
-      <c r="V154" s="336"/>
-      <c r="W154" s="336"/>
-      <c r="X154" s="336"/>
-      <c r="Y154" s="336"/>
-      <c r="Z154" s="337"/>
-      <c r="AA154" s="335" t="s">
+      <c r="L154" s="364"/>
+      <c r="M154" s="364"/>
+      <c r="N154" s="364"/>
+      <c r="O154" s="364"/>
+      <c r="P154" s="364"/>
+      <c r="Q154" s="364"/>
+      <c r="R154" s="364"/>
+      <c r="S154" s="364"/>
+      <c r="T154" s="364"/>
+      <c r="U154" s="364"/>
+      <c r="V154" s="364"/>
+      <c r="W154" s="364"/>
+      <c r="X154" s="364"/>
+      <c r="Y154" s="364"/>
+      <c r="Z154" s="350"/>
+      <c r="AA154" s="363" t="s">
         <v>321</v>
       </c>
-      <c r="AB154" s="336"/>
-      <c r="AC154" s="336"/>
-      <c r="AD154" s="336"/>
-      <c r="AE154" s="336"/>
-      <c r="AF154" s="336"/>
-      <c r="AG154" s="336"/>
-      <c r="AH154" s="337"/>
+      <c r="AB154" s="364"/>
+      <c r="AC154" s="364"/>
+      <c r="AD154" s="364"/>
+      <c r="AE154" s="364"/>
+      <c r="AF154" s="364"/>
+      <c r="AG154" s="364"/>
+      <c r="AH154" s="350"/>
     </row>
     <row r="155" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D155" s="331"/>
-      <c r="E155" s="334" t="s">
+      <c r="D155" s="369"/>
+      <c r="E155" s="347" t="s">
         <v>324</v>
       </c>
-      <c r="F155" s="288"/>
-      <c r="G155" s="288"/>
-      <c r="H155" s="288"/>
-      <c r="I155" s="288"/>
-      <c r="J155" s="289"/>
-      <c r="K155" s="347" t="s">
+      <c r="F155" s="286"/>
+      <c r="G155" s="286"/>
+      <c r="H155" s="286"/>
+      <c r="I155" s="286"/>
+      <c r="J155" s="287"/>
+      <c r="K155" s="356" t="s">
         <v>163</v>
       </c>
-      <c r="L155" s="347"/>
-      <c r="M155" s="347"/>
-      <c r="N155" s="347"/>
-      <c r="O155" s="347"/>
-      <c r="P155" s="347"/>
-      <c r="Q155" s="347"/>
-      <c r="R155" s="347"/>
-      <c r="S155" s="347"/>
-      <c r="T155" s="347"/>
-      <c r="U155" s="347"/>
-      <c r="V155" s="347"/>
-      <c r="W155" s="347"/>
-      <c r="X155" s="347"/>
-      <c r="Y155" s="347"/>
-      <c r="Z155" s="347"/>
-      <c r="AA155" s="346" t="s">
+      <c r="L155" s="356"/>
+      <c r="M155" s="356"/>
+      <c r="N155" s="356"/>
+      <c r="O155" s="356"/>
+      <c r="P155" s="356"/>
+      <c r="Q155" s="356"/>
+      <c r="R155" s="356"/>
+      <c r="S155" s="356"/>
+      <c r="T155" s="356"/>
+      <c r="U155" s="356"/>
+      <c r="V155" s="356"/>
+      <c r="W155" s="356"/>
+      <c r="X155" s="356"/>
+      <c r="Y155" s="356"/>
+      <c r="Z155" s="356"/>
+      <c r="AA155" s="355" t="s">
         <v>326</v>
       </c>
-      <c r="AB155" s="347"/>
-      <c r="AC155" s="347"/>
-      <c r="AD155" s="347"/>
-      <c r="AE155" s="347"/>
-      <c r="AF155" s="347"/>
-      <c r="AG155" s="347"/>
-      <c r="AH155" s="347"/>
+      <c r="AB155" s="356"/>
+      <c r="AC155" s="356"/>
+      <c r="AD155" s="356"/>
+      <c r="AE155" s="356"/>
+      <c r="AF155" s="356"/>
+      <c r="AG155" s="356"/>
+      <c r="AH155" s="356"/>
     </row>
     <row r="156" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D156" s="331"/>
-      <c r="E156" s="334"/>
-      <c r="F156" s="288"/>
-      <c r="G156" s="288"/>
-      <c r="H156" s="288"/>
-      <c r="I156" s="288"/>
-      <c r="J156" s="289"/>
-      <c r="K156" s="347" t="s">
+      <c r="D156" s="369"/>
+      <c r="E156" s="347"/>
+      <c r="F156" s="286"/>
+      <c r="G156" s="286"/>
+      <c r="H156" s="286"/>
+      <c r="I156" s="286"/>
+      <c r="J156" s="287"/>
+      <c r="K156" s="356" t="s">
         <v>70</v>
       </c>
-      <c r="L156" s="347"/>
-      <c r="M156" s="347"/>
-      <c r="N156" s="347"/>
-      <c r="O156" s="347"/>
-      <c r="P156" s="347"/>
-      <c r="Q156" s="347"/>
-      <c r="R156" s="347"/>
-      <c r="S156" s="347"/>
-      <c r="T156" s="347"/>
-      <c r="U156" s="347"/>
-      <c r="V156" s="347"/>
-      <c r="W156" s="347"/>
-      <c r="X156" s="347"/>
-      <c r="Y156" s="347"/>
-      <c r="Z156" s="347"/>
-      <c r="AA156" s="322" t="s">
+      <c r="L156" s="356"/>
+      <c r="M156" s="356"/>
+      <c r="N156" s="356"/>
+      <c r="O156" s="356"/>
+      <c r="P156" s="356"/>
+      <c r="Q156" s="356"/>
+      <c r="R156" s="356"/>
+      <c r="S156" s="356"/>
+      <c r="T156" s="356"/>
+      <c r="U156" s="356"/>
+      <c r="V156" s="356"/>
+      <c r="W156" s="356"/>
+      <c r="X156" s="356"/>
+      <c r="Y156" s="356"/>
+      <c r="Z156" s="356"/>
+      <c r="AA156" s="361" t="s">
         <v>283</v>
       </c>
-      <c r="AB156" s="347"/>
-      <c r="AC156" s="347"/>
-      <c r="AD156" s="347"/>
-      <c r="AE156" s="347"/>
-      <c r="AF156" s="347"/>
-      <c r="AG156" s="347"/>
-      <c r="AH156" s="347"/>
+      <c r="AB156" s="356"/>
+      <c r="AC156" s="356"/>
+      <c r="AD156" s="356"/>
+      <c r="AE156" s="356"/>
+      <c r="AF156" s="356"/>
+      <c r="AG156" s="356"/>
+      <c r="AH156" s="356"/>
     </row>
     <row r="157" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D157" s="331"/>
-      <c r="E157" s="334"/>
-      <c r="F157" s="288"/>
-      <c r="G157" s="288"/>
-      <c r="H157" s="288"/>
-      <c r="I157" s="288"/>
-      <c r="J157" s="289"/>
-      <c r="K157" s="347"/>
-      <c r="L157" s="347"/>
-      <c r="M157" s="347"/>
-      <c r="N157" s="347"/>
-      <c r="O157" s="347"/>
-      <c r="P157" s="347"/>
-      <c r="Q157" s="347"/>
-      <c r="R157" s="347"/>
-      <c r="S157" s="347"/>
-      <c r="T157" s="347"/>
-      <c r="U157" s="347"/>
-      <c r="V157" s="347"/>
-      <c r="W157" s="347"/>
-      <c r="X157" s="347"/>
-      <c r="Y157" s="347"/>
-      <c r="Z157" s="347"/>
-      <c r="AA157" s="347"/>
-      <c r="AB157" s="347"/>
-      <c r="AC157" s="347"/>
-      <c r="AD157" s="347"/>
-      <c r="AE157" s="347"/>
-      <c r="AF157" s="347"/>
-      <c r="AG157" s="347"/>
-      <c r="AH157" s="347"/>
+      <c r="D157" s="369"/>
+      <c r="E157" s="347"/>
+      <c r="F157" s="286"/>
+      <c r="G157" s="286"/>
+      <c r="H157" s="286"/>
+      <c r="I157" s="286"/>
+      <c r="J157" s="287"/>
+      <c r="K157" s="356"/>
+      <c r="L157" s="356"/>
+      <c r="M157" s="356"/>
+      <c r="N157" s="356"/>
+      <c r="O157" s="356"/>
+      <c r="P157" s="356"/>
+      <c r="Q157" s="356"/>
+      <c r="R157" s="356"/>
+      <c r="S157" s="356"/>
+      <c r="T157" s="356"/>
+      <c r="U157" s="356"/>
+      <c r="V157" s="356"/>
+      <c r="W157" s="356"/>
+      <c r="X157" s="356"/>
+      <c r="Y157" s="356"/>
+      <c r="Z157" s="356"/>
+      <c r="AA157" s="356"/>
+      <c r="AB157" s="356"/>
+      <c r="AC157" s="356"/>
+      <c r="AD157" s="356"/>
+      <c r="AE157" s="356"/>
+      <c r="AF157" s="356"/>
+      <c r="AG157" s="356"/>
+      <c r="AH157" s="356"/>
     </row>
     <row r="158" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D158" s="331"/>
-      <c r="E158" s="334"/>
-      <c r="F158" s="288"/>
-      <c r="G158" s="288"/>
-      <c r="H158" s="288"/>
-      <c r="I158" s="288"/>
-      <c r="J158" s="289"/>
-      <c r="K158" s="347"/>
-      <c r="L158" s="347"/>
-      <c r="M158" s="347"/>
-      <c r="N158" s="347"/>
-      <c r="O158" s="347"/>
-      <c r="P158" s="347"/>
-      <c r="Q158" s="347"/>
-      <c r="R158" s="347"/>
-      <c r="S158" s="347"/>
-      <c r="T158" s="347"/>
-      <c r="U158" s="347"/>
-      <c r="V158" s="347"/>
-      <c r="W158" s="347"/>
-      <c r="X158" s="347"/>
-      <c r="Y158" s="347"/>
-      <c r="Z158" s="347"/>
-      <c r="AA158" s="347"/>
-      <c r="AB158" s="347"/>
-      <c r="AC158" s="347"/>
-      <c r="AD158" s="347"/>
-      <c r="AE158" s="347"/>
-      <c r="AF158" s="347"/>
-      <c r="AG158" s="347"/>
-      <c r="AH158" s="347"/>
+      <c r="D158" s="369"/>
+      <c r="E158" s="347"/>
+      <c r="F158" s="286"/>
+      <c r="G158" s="286"/>
+      <c r="H158" s="286"/>
+      <c r="I158" s="286"/>
+      <c r="J158" s="287"/>
+      <c r="K158" s="356"/>
+      <c r="L158" s="356"/>
+      <c r="M158" s="356"/>
+      <c r="N158" s="356"/>
+      <c r="O158" s="356"/>
+      <c r="P158" s="356"/>
+      <c r="Q158" s="356"/>
+      <c r="R158" s="356"/>
+      <c r="S158" s="356"/>
+      <c r="T158" s="356"/>
+      <c r="U158" s="356"/>
+      <c r="V158" s="356"/>
+      <c r="W158" s="356"/>
+      <c r="X158" s="356"/>
+      <c r="Y158" s="356"/>
+      <c r="Z158" s="356"/>
+      <c r="AA158" s="356"/>
+      <c r="AB158" s="356"/>
+      <c r="AC158" s="356"/>
+      <c r="AD158" s="356"/>
+      <c r="AE158" s="356"/>
+      <c r="AF158" s="356"/>
+      <c r="AG158" s="356"/>
+      <c r="AH158" s="356"/>
     </row>
     <row r="159" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D159" s="331"/>
-      <c r="E159" s="334"/>
-      <c r="F159" s="288"/>
-      <c r="G159" s="288"/>
-      <c r="H159" s="288"/>
-      <c r="I159" s="288"/>
-      <c r="J159" s="289"/>
-      <c r="K159" s="347"/>
-      <c r="L159" s="347"/>
-      <c r="M159" s="347"/>
-      <c r="N159" s="347"/>
-      <c r="O159" s="347"/>
-      <c r="P159" s="347"/>
-      <c r="Q159" s="347"/>
-      <c r="R159" s="347"/>
-      <c r="S159" s="347"/>
-      <c r="T159" s="347"/>
-      <c r="U159" s="347"/>
-      <c r="V159" s="347"/>
-      <c r="W159" s="347"/>
-      <c r="X159" s="347"/>
-      <c r="Y159" s="347"/>
-      <c r="Z159" s="347"/>
-      <c r="AA159" s="347"/>
-      <c r="AB159" s="347"/>
-      <c r="AC159" s="347"/>
-      <c r="AD159" s="347"/>
-      <c r="AE159" s="347"/>
-      <c r="AF159" s="347"/>
-      <c r="AG159" s="347"/>
-      <c r="AH159" s="347"/>
+      <c r="D159" s="369"/>
+      <c r="E159" s="347"/>
+      <c r="F159" s="286"/>
+      <c r="G159" s="286"/>
+      <c r="H159" s="286"/>
+      <c r="I159" s="286"/>
+      <c r="J159" s="287"/>
+      <c r="K159" s="356"/>
+      <c r="L159" s="356"/>
+      <c r="M159" s="356"/>
+      <c r="N159" s="356"/>
+      <c r="O159" s="356"/>
+      <c r="P159" s="356"/>
+      <c r="Q159" s="356"/>
+      <c r="R159" s="356"/>
+      <c r="S159" s="356"/>
+      <c r="T159" s="356"/>
+      <c r="U159" s="356"/>
+      <c r="V159" s="356"/>
+      <c r="W159" s="356"/>
+      <c r="X159" s="356"/>
+      <c r="Y159" s="356"/>
+      <c r="Z159" s="356"/>
+      <c r="AA159" s="356"/>
+      <c r="AB159" s="356"/>
+      <c r="AC159" s="356"/>
+      <c r="AD159" s="356"/>
+      <c r="AE159" s="356"/>
+      <c r="AF159" s="356"/>
+      <c r="AG159" s="356"/>
+      <c r="AH159" s="356"/>
     </row>
     <row r="160" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D160" s="331"/>
-      <c r="E160" s="334"/>
-      <c r="F160" s="288"/>
-      <c r="G160" s="288"/>
-      <c r="H160" s="288"/>
-      <c r="I160" s="288"/>
-      <c r="J160" s="289"/>
-      <c r="K160" s="347"/>
-      <c r="L160" s="347"/>
-      <c r="M160" s="347"/>
-      <c r="N160" s="347"/>
-      <c r="O160" s="347"/>
-      <c r="P160" s="347"/>
-      <c r="Q160" s="347"/>
-      <c r="R160" s="347"/>
-      <c r="S160" s="347"/>
-      <c r="T160" s="347"/>
-      <c r="U160" s="347"/>
-      <c r="V160" s="347"/>
-      <c r="W160" s="347"/>
-      <c r="X160" s="347"/>
-      <c r="Y160" s="347"/>
-      <c r="Z160" s="347"/>
-      <c r="AA160" s="347"/>
-      <c r="AB160" s="347"/>
-      <c r="AC160" s="347"/>
-      <c r="AD160" s="347"/>
-      <c r="AE160" s="347"/>
-      <c r="AF160" s="347"/>
-      <c r="AG160" s="347"/>
-      <c r="AH160" s="347"/>
+      <c r="D160" s="369"/>
+      <c r="E160" s="347"/>
+      <c r="F160" s="286"/>
+      <c r="G160" s="286"/>
+      <c r="H160" s="286"/>
+      <c r="I160" s="286"/>
+      <c r="J160" s="287"/>
+      <c r="K160" s="356"/>
+      <c r="L160" s="356"/>
+      <c r="M160" s="356"/>
+      <c r="N160" s="356"/>
+      <c r="O160" s="356"/>
+      <c r="P160" s="356"/>
+      <c r="Q160" s="356"/>
+      <c r="R160" s="356"/>
+      <c r="S160" s="356"/>
+      <c r="T160" s="356"/>
+      <c r="U160" s="356"/>
+      <c r="V160" s="356"/>
+      <c r="W160" s="356"/>
+      <c r="X160" s="356"/>
+      <c r="Y160" s="356"/>
+      <c r="Z160" s="356"/>
+      <c r="AA160" s="356"/>
+      <c r="AB160" s="356"/>
+      <c r="AC160" s="356"/>
+      <c r="AD160" s="356"/>
+      <c r="AE160" s="356"/>
+      <c r="AF160" s="356"/>
+      <c r="AG160" s="356"/>
+      <c r="AH160" s="356"/>
     </row>
     <row r="161" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D161" s="331"/>
-      <c r="E161" s="334"/>
-      <c r="F161" s="288"/>
-      <c r="G161" s="288"/>
-      <c r="H161" s="288"/>
-      <c r="I161" s="288"/>
-      <c r="J161" s="289"/>
-      <c r="K161" s="346" t="s">
+      <c r="D161" s="369"/>
+      <c r="E161" s="347"/>
+      <c r="F161" s="286"/>
+      <c r="G161" s="286"/>
+      <c r="H161" s="286"/>
+      <c r="I161" s="286"/>
+      <c r="J161" s="287"/>
+      <c r="K161" s="355" t="s">
         <v>629</v>
       </c>
-      <c r="L161" s="347"/>
-      <c r="M161" s="347"/>
-      <c r="N161" s="347"/>
-      <c r="O161" s="347"/>
-      <c r="P161" s="347"/>
-      <c r="Q161" s="347"/>
-      <c r="R161" s="347"/>
-      <c r="S161" s="347"/>
-      <c r="T161" s="347"/>
-      <c r="U161" s="347"/>
-      <c r="V161" s="347"/>
-      <c r="W161" s="347"/>
-      <c r="X161" s="347"/>
-      <c r="Y161" s="347"/>
-      <c r="Z161" s="347"/>
-      <c r="AA161" s="322" t="s">
+      <c r="L161" s="356"/>
+      <c r="M161" s="356"/>
+      <c r="N161" s="356"/>
+      <c r="O161" s="356"/>
+      <c r="P161" s="356"/>
+      <c r="Q161" s="356"/>
+      <c r="R161" s="356"/>
+      <c r="S161" s="356"/>
+      <c r="T161" s="356"/>
+      <c r="U161" s="356"/>
+      <c r="V161" s="356"/>
+      <c r="W161" s="356"/>
+      <c r="X161" s="356"/>
+      <c r="Y161" s="356"/>
+      <c r="Z161" s="356"/>
+      <c r="AA161" s="361" t="s">
         <v>75</v>
       </c>
-      <c r="AB161" s="323"/>
-      <c r="AC161" s="323"/>
-      <c r="AD161" s="323"/>
-      <c r="AE161" s="323"/>
-      <c r="AF161" s="323"/>
-      <c r="AG161" s="323"/>
-      <c r="AH161" s="323"/>
+      <c r="AB161" s="362"/>
+      <c r="AC161" s="362"/>
+      <c r="AD161" s="362"/>
+      <c r="AE161" s="362"/>
+      <c r="AF161" s="362"/>
+      <c r="AG161" s="362"/>
+      <c r="AH161" s="362"/>
     </row>
     <row r="162" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D162" s="331"/>
-      <c r="E162" s="334" t="s">
+      <c r="D162" s="369"/>
+      <c r="E162" s="347" t="s">
         <v>323</v>
       </c>
-      <c r="F162" s="288"/>
-      <c r="G162" s="288"/>
-      <c r="H162" s="288"/>
-      <c r="I162" s="288"/>
-      <c r="J162" s="289"/>
-      <c r="K162" s="334" t="s">
+      <c r="F162" s="286"/>
+      <c r="G162" s="286"/>
+      <c r="H162" s="286"/>
+      <c r="I162" s="286"/>
+      <c r="J162" s="287"/>
+      <c r="K162" s="347" t="s">
         <v>628</v>
       </c>
-      <c r="L162" s="288"/>
-      <c r="M162" s="288"/>
-      <c r="N162" s="288"/>
-      <c r="O162" s="288"/>
-      <c r="P162" s="288"/>
-      <c r="Q162" s="288"/>
-      <c r="R162" s="288"/>
-      <c r="S162" s="288"/>
-      <c r="T162" s="288"/>
-      <c r="U162" s="288"/>
-      <c r="V162" s="288"/>
-      <c r="W162" s="288"/>
-      <c r="X162" s="288"/>
-      <c r="Y162" s="288"/>
-      <c r="Z162" s="289"/>
-      <c r="AA162" s="323" t="s">
+      <c r="L162" s="286"/>
+      <c r="M162" s="286"/>
+      <c r="N162" s="286"/>
+      <c r="O162" s="286"/>
+      <c r="P162" s="286"/>
+      <c r="Q162" s="286"/>
+      <c r="R162" s="286"/>
+      <c r="S162" s="286"/>
+      <c r="T162" s="286"/>
+      <c r="U162" s="286"/>
+      <c r="V162" s="286"/>
+      <c r="W162" s="286"/>
+      <c r="X162" s="286"/>
+      <c r="Y162" s="286"/>
+      <c r="Z162" s="287"/>
+      <c r="AA162" s="362" t="s">
         <v>71</v>
       </c>
-      <c r="AB162" s="323"/>
-      <c r="AC162" s="323"/>
-      <c r="AD162" s="323"/>
-      <c r="AE162" s="323"/>
-      <c r="AF162" s="323"/>
-      <c r="AG162" s="323"/>
-      <c r="AH162" s="323"/>
+      <c r="AB162" s="362"/>
+      <c r="AC162" s="362"/>
+      <c r="AD162" s="362"/>
+      <c r="AE162" s="362"/>
+      <c r="AF162" s="362"/>
+      <c r="AG162" s="362"/>
+      <c r="AH162" s="362"/>
     </row>
     <row r="163" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D163" s="332"/>
-      <c r="E163" s="334"/>
-      <c r="F163" s="288"/>
-      <c r="G163" s="288"/>
-      <c r="H163" s="288"/>
-      <c r="I163" s="288"/>
-      <c r="J163" s="289"/>
-      <c r="K163" s="323"/>
-      <c r="L163" s="323"/>
-      <c r="M163" s="323"/>
-      <c r="N163" s="323"/>
-      <c r="O163" s="323"/>
-      <c r="P163" s="323"/>
-      <c r="Q163" s="323"/>
-      <c r="R163" s="323"/>
-      <c r="S163" s="323"/>
-      <c r="T163" s="323"/>
-      <c r="U163" s="323"/>
-      <c r="V163" s="323"/>
-      <c r="W163" s="323"/>
-      <c r="X163" s="323"/>
-      <c r="Y163" s="323"/>
-      <c r="Z163" s="323"/>
-      <c r="AA163" s="323"/>
-      <c r="AB163" s="323"/>
-      <c r="AC163" s="323"/>
-      <c r="AD163" s="323"/>
-      <c r="AE163" s="323"/>
-      <c r="AF163" s="323"/>
-      <c r="AG163" s="323"/>
-      <c r="AH163" s="323"/>
+      <c r="D163" s="370"/>
+      <c r="E163" s="347"/>
+      <c r="F163" s="286"/>
+      <c r="G163" s="286"/>
+      <c r="H163" s="286"/>
+      <c r="I163" s="286"/>
+      <c r="J163" s="287"/>
+      <c r="K163" s="362"/>
+      <c r="L163" s="362"/>
+      <c r="M163" s="362"/>
+      <c r="N163" s="362"/>
+      <c r="O163" s="362"/>
+      <c r="P163" s="362"/>
+      <c r="Q163" s="362"/>
+      <c r="R163" s="362"/>
+      <c r="S163" s="362"/>
+      <c r="T163" s="362"/>
+      <c r="U163" s="362"/>
+      <c r="V163" s="362"/>
+      <c r="W163" s="362"/>
+      <c r="X163" s="362"/>
+      <c r="Y163" s="362"/>
+      <c r="Z163" s="362"/>
+      <c r="AA163" s="362"/>
+      <c r="AB163" s="362"/>
+      <c r="AC163" s="362"/>
+      <c r="AD163" s="362"/>
+      <c r="AE163" s="362"/>
+      <c r="AF163" s="362"/>
+      <c r="AG163" s="362"/>
+      <c r="AH163" s="362"/>
     </row>
     <row r="164" spans="3:34" x14ac:dyDescent="0.15">
       <c r="D164" s="55"/>
@@ -42878,815 +42878,815 @@
     </row>
     <row r="173" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="174" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F174" s="248" t="s">
+      <c r="F174" s="276" t="s">
         <v>642</v>
       </c>
-      <c r="G174" s="327"/>
-      <c r="H174" s="327"/>
-      <c r="I174" s="327"/>
-      <c r="J174" s="328"/>
-      <c r="K174" s="329" t="s">
+      <c r="G174" s="341"/>
+      <c r="H174" s="341"/>
+      <c r="I174" s="341"/>
+      <c r="J174" s="342"/>
+      <c r="K174" s="353" t="s">
         <v>30</v>
       </c>
-      <c r="L174" s="330"/>
-      <c r="M174" s="329" t="s">
+      <c r="L174" s="354"/>
+      <c r="M174" s="353" t="s">
         <v>45</v>
       </c>
-      <c r="N174" s="330"/>
-      <c r="O174" s="326" t="s">
+      <c r="N174" s="354"/>
+      <c r="O174" s="368" t="s">
         <v>44</v>
       </c>
-      <c r="P174" s="327"/>
-      <c r="Q174" s="327"/>
-      <c r="R174" s="327"/>
-      <c r="S174" s="327"/>
-      <c r="T174" s="327"/>
-      <c r="U174" s="327"/>
-      <c r="V174" s="327"/>
-      <c r="W174" s="327"/>
-      <c r="X174" s="327"/>
-      <c r="Y174" s="327"/>
-      <c r="Z174" s="327"/>
-      <c r="AA174" s="327"/>
-      <c r="AB174" s="327"/>
-      <c r="AC174" s="327"/>
-      <c r="AD174" s="327"/>
-      <c r="AE174" s="327"/>
-      <c r="AF174" s="327"/>
-      <c r="AG174" s="327"/>
-      <c r="AH174" s="328"/>
+      <c r="P174" s="341"/>
+      <c r="Q174" s="341"/>
+      <c r="R174" s="341"/>
+      <c r="S174" s="341"/>
+      <c r="T174" s="341"/>
+      <c r="U174" s="341"/>
+      <c r="V174" s="341"/>
+      <c r="W174" s="341"/>
+      <c r="X174" s="341"/>
+      <c r="Y174" s="341"/>
+      <c r="Z174" s="341"/>
+      <c r="AA174" s="341"/>
+      <c r="AB174" s="341"/>
+      <c r="AC174" s="341"/>
+      <c r="AD174" s="341"/>
+      <c r="AE174" s="341"/>
+      <c r="AF174" s="341"/>
+      <c r="AG174" s="341"/>
+      <c r="AH174" s="342"/>
     </row>
     <row r="175" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F175" s="307" t="s">
+      <c r="F175" s="310" t="s">
         <v>285</v>
       </c>
-      <c r="G175" s="252"/>
-      <c r="H175" s="252"/>
-      <c r="I175" s="252"/>
-      <c r="J175" s="253"/>
-      <c r="K175" s="340" t="s">
+      <c r="G175" s="280"/>
+      <c r="H175" s="280"/>
+      <c r="I175" s="280"/>
+      <c r="J175" s="281"/>
+      <c r="K175" s="337" t="s">
         <v>32</v>
       </c>
-      <c r="L175" s="292"/>
-      <c r="M175" s="335" t="s">
+      <c r="L175" s="290"/>
+      <c r="M175" s="363" t="s">
         <v>302</v>
       </c>
-      <c r="N175" s="337"/>
-      <c r="O175" s="254" t="s">
+      <c r="N175" s="350"/>
+      <c r="O175" s="282" t="s">
         <v>307</v>
       </c>
-      <c r="P175" s="342"/>
-      <c r="Q175" s="342"/>
-      <c r="R175" s="342"/>
-      <c r="S175" s="342"/>
-      <c r="T175" s="342"/>
-      <c r="U175" s="342"/>
-      <c r="V175" s="342"/>
-      <c r="W175" s="342"/>
-      <c r="X175" s="342"/>
-      <c r="Y175" s="342"/>
-      <c r="Z175" s="342"/>
-      <c r="AA175" s="342"/>
-      <c r="AB175" s="342"/>
-      <c r="AC175" s="342"/>
-      <c r="AD175" s="342"/>
-      <c r="AE175" s="342"/>
-      <c r="AF175" s="342"/>
-      <c r="AG175" s="342"/>
-      <c r="AH175" s="343"/>
+      <c r="P175" s="365"/>
+      <c r="Q175" s="365"/>
+      <c r="R175" s="365"/>
+      <c r="S175" s="365"/>
+      <c r="T175" s="365"/>
+      <c r="U175" s="365"/>
+      <c r="V175" s="365"/>
+      <c r="W175" s="365"/>
+      <c r="X175" s="365"/>
+      <c r="Y175" s="365"/>
+      <c r="Z175" s="365"/>
+      <c r="AA175" s="365"/>
+      <c r="AB175" s="365"/>
+      <c r="AC175" s="365"/>
+      <c r="AD175" s="365"/>
+      <c r="AE175" s="365"/>
+      <c r="AF175" s="365"/>
+      <c r="AG175" s="365"/>
+      <c r="AH175" s="366"/>
     </row>
     <row r="176" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F176" s="290" t="s">
+      <c r="F176" s="288" t="s">
         <v>303</v>
       </c>
-      <c r="G176" s="291"/>
-      <c r="H176" s="291"/>
-      <c r="I176" s="291"/>
-      <c r="J176" s="292"/>
-      <c r="K176" s="340" t="s">
+      <c r="G176" s="289"/>
+      <c r="H176" s="289"/>
+      <c r="I176" s="289"/>
+      <c r="J176" s="290"/>
+      <c r="K176" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="L176" s="292"/>
-      <c r="M176" s="310" t="s">
+      <c r="L176" s="290"/>
+      <c r="M176" s="317" t="s">
         <v>339</v>
       </c>
-      <c r="N176" s="312"/>
-      <c r="O176" s="290" t="s">
+      <c r="N176" s="319"/>
+      <c r="O176" s="288" t="s">
         <v>306</v>
       </c>
-      <c r="P176" s="291"/>
-      <c r="Q176" s="291"/>
-      <c r="R176" s="291"/>
-      <c r="S176" s="291"/>
-      <c r="T176" s="291"/>
-      <c r="U176" s="291"/>
-      <c r="V176" s="291"/>
-      <c r="W176" s="291"/>
-      <c r="X176" s="291"/>
-      <c r="Y176" s="291"/>
-      <c r="Z176" s="291"/>
-      <c r="AA176" s="291"/>
-      <c r="AB176" s="291"/>
-      <c r="AC176" s="291"/>
-      <c r="AD176" s="291"/>
-      <c r="AE176" s="291"/>
-      <c r="AF176" s="291"/>
-      <c r="AG176" s="291"/>
-      <c r="AH176" s="292"/>
+      <c r="P176" s="289"/>
+      <c r="Q176" s="289"/>
+      <c r="R176" s="289"/>
+      <c r="S176" s="289"/>
+      <c r="T176" s="289"/>
+      <c r="U176" s="289"/>
+      <c r="V176" s="289"/>
+      <c r="W176" s="289"/>
+      <c r="X176" s="289"/>
+      <c r="Y176" s="289"/>
+      <c r="Z176" s="289"/>
+      <c r="AA176" s="289"/>
+      <c r="AB176" s="289"/>
+      <c r="AC176" s="289"/>
+      <c r="AD176" s="289"/>
+      <c r="AE176" s="289"/>
+      <c r="AF176" s="289"/>
+      <c r="AG176" s="289"/>
+      <c r="AH176" s="290"/>
     </row>
     <row r="177" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F177" s="299"/>
-      <c r="G177" s="294"/>
-      <c r="H177" s="294"/>
-      <c r="I177" s="294"/>
-      <c r="J177" s="295"/>
-      <c r="K177" s="293"/>
-      <c r="L177" s="295"/>
-      <c r="M177" s="338"/>
-      <c r="N177" s="339"/>
-      <c r="O177" s="299"/>
-      <c r="P177" s="294"/>
-      <c r="Q177" s="294"/>
-      <c r="R177" s="294"/>
-      <c r="S177" s="294"/>
-      <c r="T177" s="294"/>
-      <c r="U177" s="294"/>
-      <c r="V177" s="294"/>
-      <c r="W177" s="294"/>
-      <c r="X177" s="294"/>
-      <c r="Y177" s="294"/>
-      <c r="Z177" s="294"/>
-      <c r="AA177" s="294"/>
-      <c r="AB177" s="294"/>
-      <c r="AC177" s="294"/>
-      <c r="AD177" s="294"/>
-      <c r="AE177" s="294"/>
-      <c r="AF177" s="294"/>
-      <c r="AG177" s="294"/>
-      <c r="AH177" s="295"/>
+      <c r="F177" s="297"/>
+      <c r="G177" s="292"/>
+      <c r="H177" s="292"/>
+      <c r="I177" s="292"/>
+      <c r="J177" s="293"/>
+      <c r="K177" s="291"/>
+      <c r="L177" s="293"/>
+      <c r="M177" s="334"/>
+      <c r="N177" s="344"/>
+      <c r="O177" s="297"/>
+      <c r="P177" s="292"/>
+      <c r="Q177" s="292"/>
+      <c r="R177" s="292"/>
+      <c r="S177" s="292"/>
+      <c r="T177" s="292"/>
+      <c r="U177" s="292"/>
+      <c r="V177" s="292"/>
+      <c r="W177" s="292"/>
+      <c r="X177" s="292"/>
+      <c r="Y177" s="292"/>
+      <c r="Z177" s="292"/>
+      <c r="AA177" s="292"/>
+      <c r="AB177" s="292"/>
+      <c r="AC177" s="292"/>
+      <c r="AD177" s="292"/>
+      <c r="AE177" s="292"/>
+      <c r="AF177" s="292"/>
+      <c r="AG177" s="292"/>
+      <c r="AH177" s="293"/>
     </row>
     <row r="178" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F178" s="299"/>
-      <c r="G178" s="294"/>
-      <c r="H178" s="294"/>
-      <c r="I178" s="294"/>
-      <c r="J178" s="295"/>
-      <c r="K178" s="293"/>
-      <c r="L178" s="295"/>
-      <c r="M178" s="338"/>
-      <c r="N178" s="339"/>
-      <c r="O178" s="299"/>
-      <c r="P178" s="294"/>
-      <c r="Q178" s="294"/>
-      <c r="R178" s="294"/>
-      <c r="S178" s="294"/>
-      <c r="T178" s="294"/>
-      <c r="U178" s="294"/>
-      <c r="V178" s="294"/>
-      <c r="W178" s="294"/>
-      <c r="X178" s="294"/>
-      <c r="Y178" s="294"/>
-      <c r="Z178" s="294"/>
-      <c r="AA178" s="294"/>
-      <c r="AB178" s="294"/>
-      <c r="AC178" s="294"/>
-      <c r="AD178" s="294"/>
-      <c r="AE178" s="294"/>
-      <c r="AF178" s="294"/>
-      <c r="AG178" s="294"/>
-      <c r="AH178" s="295"/>
+      <c r="F178" s="297"/>
+      <c r="G178" s="292"/>
+      <c r="H178" s="292"/>
+      <c r="I178" s="292"/>
+      <c r="J178" s="293"/>
+      <c r="K178" s="291"/>
+      <c r="L178" s="293"/>
+      <c r="M178" s="334"/>
+      <c r="N178" s="344"/>
+      <c r="O178" s="297"/>
+      <c r="P178" s="292"/>
+      <c r="Q178" s="292"/>
+      <c r="R178" s="292"/>
+      <c r="S178" s="292"/>
+      <c r="T178" s="292"/>
+      <c r="U178" s="292"/>
+      <c r="V178" s="292"/>
+      <c r="W178" s="292"/>
+      <c r="X178" s="292"/>
+      <c r="Y178" s="292"/>
+      <c r="Z178" s="292"/>
+      <c r="AA178" s="292"/>
+      <c r="AB178" s="292"/>
+      <c r="AC178" s="292"/>
+      <c r="AD178" s="292"/>
+      <c r="AE178" s="292"/>
+      <c r="AF178" s="292"/>
+      <c r="AG178" s="292"/>
+      <c r="AH178" s="293"/>
     </row>
     <row r="179" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F179" s="296"/>
-      <c r="G179" s="297"/>
-      <c r="H179" s="297"/>
-      <c r="I179" s="297"/>
-      <c r="J179" s="298"/>
-      <c r="K179" s="296"/>
-      <c r="L179" s="298"/>
-      <c r="M179" s="313"/>
-      <c r="N179" s="315"/>
-      <c r="O179" s="296"/>
-      <c r="P179" s="297"/>
-      <c r="Q179" s="297"/>
-      <c r="R179" s="297"/>
-      <c r="S179" s="297"/>
-      <c r="T179" s="297"/>
-      <c r="U179" s="297"/>
-      <c r="V179" s="297"/>
-      <c r="W179" s="297"/>
-      <c r="X179" s="297"/>
-      <c r="Y179" s="297"/>
-      <c r="Z179" s="297"/>
-      <c r="AA179" s="297"/>
-      <c r="AB179" s="297"/>
-      <c r="AC179" s="297"/>
-      <c r="AD179" s="297"/>
-      <c r="AE179" s="297"/>
-      <c r="AF179" s="297"/>
-      <c r="AG179" s="297"/>
-      <c r="AH179" s="298"/>
+      <c r="F179" s="294"/>
+      <c r="G179" s="295"/>
+      <c r="H179" s="295"/>
+      <c r="I179" s="295"/>
+      <c r="J179" s="296"/>
+      <c r="K179" s="294"/>
+      <c r="L179" s="296"/>
+      <c r="M179" s="320"/>
+      <c r="N179" s="322"/>
+      <c r="O179" s="294"/>
+      <c r="P179" s="295"/>
+      <c r="Q179" s="295"/>
+      <c r="R179" s="295"/>
+      <c r="S179" s="295"/>
+      <c r="T179" s="295"/>
+      <c r="U179" s="295"/>
+      <c r="V179" s="295"/>
+      <c r="W179" s="295"/>
+      <c r="X179" s="295"/>
+      <c r="Y179" s="295"/>
+      <c r="Z179" s="295"/>
+      <c r="AA179" s="295"/>
+      <c r="AB179" s="295"/>
+      <c r="AC179" s="295"/>
+      <c r="AD179" s="295"/>
+      <c r="AE179" s="295"/>
+      <c r="AF179" s="295"/>
+      <c r="AG179" s="295"/>
+      <c r="AH179" s="296"/>
     </row>
     <row r="180" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F180" s="340" t="s">
+      <c r="F180" s="337" t="s">
         <v>47</v>
       </c>
-      <c r="G180" s="291"/>
-      <c r="H180" s="291"/>
-      <c r="I180" s="291"/>
-      <c r="J180" s="292"/>
-      <c r="K180" s="340" t="s">
+      <c r="G180" s="289"/>
+      <c r="H180" s="289"/>
+      <c r="I180" s="289"/>
+      <c r="J180" s="290"/>
+      <c r="K180" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="L180" s="292"/>
-      <c r="M180" s="340" t="s">
+      <c r="L180" s="290"/>
+      <c r="M180" s="337" t="s">
         <v>48</v>
       </c>
-      <c r="N180" s="312"/>
-      <c r="O180" s="310" t="s">
+      <c r="N180" s="319"/>
+      <c r="O180" s="317" t="s">
         <v>310</v>
       </c>
-      <c r="P180" s="311"/>
-      <c r="Q180" s="311"/>
-      <c r="R180" s="311"/>
-      <c r="S180" s="311"/>
-      <c r="T180" s="311"/>
-      <c r="U180" s="311"/>
-      <c r="V180" s="311"/>
-      <c r="W180" s="311"/>
-      <c r="X180" s="311"/>
-      <c r="Y180" s="311"/>
-      <c r="Z180" s="311"/>
-      <c r="AA180" s="311"/>
-      <c r="AB180" s="311"/>
-      <c r="AC180" s="311"/>
-      <c r="AD180" s="311"/>
-      <c r="AE180" s="311"/>
-      <c r="AF180" s="311"/>
-      <c r="AG180" s="311"/>
-      <c r="AH180" s="312"/>
+      <c r="P180" s="318"/>
+      <c r="Q180" s="318"/>
+      <c r="R180" s="318"/>
+      <c r="S180" s="318"/>
+      <c r="T180" s="318"/>
+      <c r="U180" s="318"/>
+      <c r="V180" s="318"/>
+      <c r="W180" s="318"/>
+      <c r="X180" s="318"/>
+      <c r="Y180" s="318"/>
+      <c r="Z180" s="318"/>
+      <c r="AA180" s="318"/>
+      <c r="AB180" s="318"/>
+      <c r="AC180" s="318"/>
+      <c r="AD180" s="318"/>
+      <c r="AE180" s="318"/>
+      <c r="AF180" s="318"/>
+      <c r="AG180" s="318"/>
+      <c r="AH180" s="319"/>
     </row>
     <row r="181" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F181" s="290" t="s">
+      <c r="F181" s="288" t="s">
         <v>286</v>
       </c>
-      <c r="G181" s="291"/>
-      <c r="H181" s="291"/>
-      <c r="I181" s="291"/>
-      <c r="J181" s="292"/>
-      <c r="K181" s="340" t="s">
+      <c r="G181" s="289"/>
+      <c r="H181" s="289"/>
+      <c r="I181" s="289"/>
+      <c r="J181" s="290"/>
+      <c r="K181" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="L181" s="292"/>
-      <c r="M181" s="340" t="s">
+      <c r="L181" s="290"/>
+      <c r="M181" s="337" t="s">
         <v>76</v>
       </c>
-      <c r="N181" s="312"/>
-      <c r="O181" s="310" t="s">
+      <c r="N181" s="319"/>
+      <c r="O181" s="317" t="s">
         <v>311</v>
       </c>
-      <c r="P181" s="311"/>
-      <c r="Q181" s="311"/>
-      <c r="R181" s="311"/>
-      <c r="S181" s="311"/>
-      <c r="T181" s="311"/>
-      <c r="U181" s="311"/>
-      <c r="V181" s="311"/>
-      <c r="W181" s="311"/>
-      <c r="X181" s="311"/>
-      <c r="Y181" s="311"/>
-      <c r="Z181" s="311"/>
-      <c r="AA181" s="311"/>
-      <c r="AB181" s="311"/>
-      <c r="AC181" s="311"/>
-      <c r="AD181" s="311"/>
-      <c r="AE181" s="311"/>
-      <c r="AF181" s="311"/>
-      <c r="AG181" s="311"/>
-      <c r="AH181" s="312"/>
+      <c r="P181" s="318"/>
+      <c r="Q181" s="318"/>
+      <c r="R181" s="318"/>
+      <c r="S181" s="318"/>
+      <c r="T181" s="318"/>
+      <c r="U181" s="318"/>
+      <c r="V181" s="318"/>
+      <c r="W181" s="318"/>
+      <c r="X181" s="318"/>
+      <c r="Y181" s="318"/>
+      <c r="Z181" s="318"/>
+      <c r="AA181" s="318"/>
+      <c r="AB181" s="318"/>
+      <c r="AC181" s="318"/>
+      <c r="AD181" s="318"/>
+      <c r="AE181" s="318"/>
+      <c r="AF181" s="318"/>
+      <c r="AG181" s="318"/>
+      <c r="AH181" s="319"/>
     </row>
     <row r="182" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F182" s="299"/>
-      <c r="G182" s="363"/>
-      <c r="H182" s="363"/>
-      <c r="I182" s="363"/>
-      <c r="J182" s="339"/>
-      <c r="K182" s="293"/>
-      <c r="L182" s="295"/>
-      <c r="M182" s="299"/>
-      <c r="N182" s="339"/>
-      <c r="O182" s="299"/>
-      <c r="P182" s="363"/>
-      <c r="Q182" s="363"/>
-      <c r="R182" s="363"/>
-      <c r="S182" s="363"/>
-      <c r="T182" s="363"/>
-      <c r="U182" s="363"/>
-      <c r="V182" s="363"/>
-      <c r="W182" s="363"/>
-      <c r="X182" s="363"/>
-      <c r="Y182" s="363"/>
-      <c r="Z182" s="363"/>
-      <c r="AA182" s="363"/>
-      <c r="AB182" s="363"/>
-      <c r="AC182" s="363"/>
-      <c r="AD182" s="363"/>
-      <c r="AE182" s="363"/>
-      <c r="AF182" s="363"/>
-      <c r="AG182" s="363"/>
-      <c r="AH182" s="339"/>
+      <c r="F182" s="297"/>
+      <c r="G182" s="343"/>
+      <c r="H182" s="343"/>
+      <c r="I182" s="343"/>
+      <c r="J182" s="344"/>
+      <c r="K182" s="291"/>
+      <c r="L182" s="293"/>
+      <c r="M182" s="297"/>
+      <c r="N182" s="344"/>
+      <c r="O182" s="297"/>
+      <c r="P182" s="343"/>
+      <c r="Q182" s="343"/>
+      <c r="R182" s="343"/>
+      <c r="S182" s="343"/>
+      <c r="T182" s="343"/>
+      <c r="U182" s="343"/>
+      <c r="V182" s="343"/>
+      <c r="W182" s="343"/>
+      <c r="X182" s="343"/>
+      <c r="Y182" s="343"/>
+      <c r="Z182" s="343"/>
+      <c r="AA182" s="343"/>
+      <c r="AB182" s="343"/>
+      <c r="AC182" s="343"/>
+      <c r="AD182" s="343"/>
+      <c r="AE182" s="343"/>
+      <c r="AF182" s="343"/>
+      <c r="AG182" s="343"/>
+      <c r="AH182" s="344"/>
     </row>
     <row r="183" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F183" s="299"/>
-      <c r="G183" s="363"/>
-      <c r="H183" s="363"/>
-      <c r="I183" s="363"/>
-      <c r="J183" s="339"/>
-      <c r="K183" s="293"/>
-      <c r="L183" s="295"/>
-      <c r="M183" s="299"/>
-      <c r="N183" s="339"/>
-      <c r="O183" s="299"/>
-      <c r="P183" s="363"/>
-      <c r="Q183" s="363"/>
-      <c r="R183" s="363"/>
-      <c r="S183" s="363"/>
-      <c r="T183" s="363"/>
-      <c r="U183" s="363"/>
-      <c r="V183" s="363"/>
-      <c r="W183" s="363"/>
-      <c r="X183" s="363"/>
-      <c r="Y183" s="363"/>
-      <c r="Z183" s="363"/>
-      <c r="AA183" s="363"/>
-      <c r="AB183" s="363"/>
-      <c r="AC183" s="363"/>
-      <c r="AD183" s="363"/>
-      <c r="AE183" s="363"/>
-      <c r="AF183" s="363"/>
-      <c r="AG183" s="363"/>
-      <c r="AH183" s="339"/>
+      <c r="F183" s="297"/>
+      <c r="G183" s="343"/>
+      <c r="H183" s="343"/>
+      <c r="I183" s="343"/>
+      <c r="J183" s="344"/>
+      <c r="K183" s="291"/>
+      <c r="L183" s="293"/>
+      <c r="M183" s="297"/>
+      <c r="N183" s="344"/>
+      <c r="O183" s="297"/>
+      <c r="P183" s="343"/>
+      <c r="Q183" s="343"/>
+      <c r="R183" s="343"/>
+      <c r="S183" s="343"/>
+      <c r="T183" s="343"/>
+      <c r="U183" s="343"/>
+      <c r="V183" s="343"/>
+      <c r="W183" s="343"/>
+      <c r="X183" s="343"/>
+      <c r="Y183" s="343"/>
+      <c r="Z183" s="343"/>
+      <c r="AA183" s="343"/>
+      <c r="AB183" s="343"/>
+      <c r="AC183" s="343"/>
+      <c r="AD183" s="343"/>
+      <c r="AE183" s="343"/>
+      <c r="AF183" s="343"/>
+      <c r="AG183" s="343"/>
+      <c r="AH183" s="344"/>
     </row>
     <row r="184" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F184" s="313"/>
-      <c r="G184" s="314"/>
-      <c r="H184" s="314"/>
-      <c r="I184" s="314"/>
-      <c r="J184" s="315"/>
-      <c r="K184" s="296"/>
-      <c r="L184" s="298"/>
-      <c r="M184" s="313"/>
-      <c r="N184" s="315"/>
-      <c r="O184" s="313"/>
-      <c r="P184" s="314"/>
-      <c r="Q184" s="314"/>
-      <c r="R184" s="314"/>
-      <c r="S184" s="314"/>
-      <c r="T184" s="314"/>
-      <c r="U184" s="314"/>
-      <c r="V184" s="314"/>
-      <c r="W184" s="314"/>
-      <c r="X184" s="314"/>
-      <c r="Y184" s="314"/>
-      <c r="Z184" s="314"/>
-      <c r="AA184" s="314"/>
-      <c r="AB184" s="314"/>
-      <c r="AC184" s="314"/>
-      <c r="AD184" s="314"/>
-      <c r="AE184" s="314"/>
-      <c r="AF184" s="314"/>
-      <c r="AG184" s="314"/>
-      <c r="AH184" s="315"/>
+      <c r="F184" s="320"/>
+      <c r="G184" s="321"/>
+      <c r="H184" s="321"/>
+      <c r="I184" s="321"/>
+      <c r="J184" s="322"/>
+      <c r="K184" s="294"/>
+      <c r="L184" s="296"/>
+      <c r="M184" s="320"/>
+      <c r="N184" s="322"/>
+      <c r="O184" s="320"/>
+      <c r="P184" s="321"/>
+      <c r="Q184" s="321"/>
+      <c r="R184" s="321"/>
+      <c r="S184" s="321"/>
+      <c r="T184" s="321"/>
+      <c r="U184" s="321"/>
+      <c r="V184" s="321"/>
+      <c r="W184" s="321"/>
+      <c r="X184" s="321"/>
+      <c r="Y184" s="321"/>
+      <c r="Z184" s="321"/>
+      <c r="AA184" s="321"/>
+      <c r="AB184" s="321"/>
+      <c r="AC184" s="321"/>
+      <c r="AD184" s="321"/>
+      <c r="AE184" s="321"/>
+      <c r="AF184" s="321"/>
+      <c r="AG184" s="321"/>
+      <c r="AH184" s="322"/>
     </row>
     <row r="185" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F185" s="340" t="s">
+      <c r="F185" s="337" t="s">
         <v>38</v>
       </c>
-      <c r="G185" s="291"/>
-      <c r="H185" s="291"/>
-      <c r="I185" s="291"/>
-      <c r="J185" s="292"/>
-      <c r="K185" s="340" t="s">
+      <c r="G185" s="289"/>
+      <c r="H185" s="289"/>
+      <c r="I185" s="289"/>
+      <c r="J185" s="290"/>
+      <c r="K185" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="L185" s="292"/>
-      <c r="M185" s="340" t="s">
+      <c r="L185" s="290"/>
+      <c r="M185" s="337" t="s">
         <v>48</v>
       </c>
-      <c r="N185" s="312"/>
-      <c r="O185" s="310" t="s">
+      <c r="N185" s="319"/>
+      <c r="O185" s="317" t="s">
         <v>500</v>
       </c>
-      <c r="P185" s="311"/>
-      <c r="Q185" s="311"/>
-      <c r="R185" s="311"/>
-      <c r="S185" s="311"/>
-      <c r="T185" s="311"/>
-      <c r="U185" s="311"/>
-      <c r="V185" s="311"/>
-      <c r="W185" s="311"/>
-      <c r="X185" s="311"/>
-      <c r="Y185" s="311"/>
-      <c r="Z185" s="311"/>
-      <c r="AA185" s="311"/>
-      <c r="AB185" s="311"/>
-      <c r="AC185" s="311"/>
-      <c r="AD185" s="311"/>
-      <c r="AE185" s="311"/>
-      <c r="AF185" s="311"/>
-      <c r="AG185" s="311"/>
-      <c r="AH185" s="312"/>
+      <c r="P185" s="318"/>
+      <c r="Q185" s="318"/>
+      <c r="R185" s="318"/>
+      <c r="S185" s="318"/>
+      <c r="T185" s="318"/>
+      <c r="U185" s="318"/>
+      <c r="V185" s="318"/>
+      <c r="W185" s="318"/>
+      <c r="X185" s="318"/>
+      <c r="Y185" s="318"/>
+      <c r="Z185" s="318"/>
+      <c r="AA185" s="318"/>
+      <c r="AB185" s="318"/>
+      <c r="AC185" s="318"/>
+      <c r="AD185" s="318"/>
+      <c r="AE185" s="318"/>
+      <c r="AF185" s="318"/>
+      <c r="AG185" s="318"/>
+      <c r="AH185" s="319"/>
     </row>
     <row r="186" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F186" s="313"/>
-      <c r="G186" s="314"/>
-      <c r="H186" s="314"/>
-      <c r="I186" s="314"/>
-      <c r="J186" s="315"/>
-      <c r="K186" s="296"/>
-      <c r="L186" s="298"/>
-      <c r="M186" s="313"/>
-      <c r="N186" s="315"/>
-      <c r="O186" s="313"/>
-      <c r="P186" s="314"/>
-      <c r="Q186" s="314"/>
-      <c r="R186" s="314"/>
-      <c r="S186" s="314"/>
-      <c r="T186" s="314"/>
-      <c r="U186" s="314"/>
-      <c r="V186" s="314"/>
-      <c r="W186" s="314"/>
-      <c r="X186" s="314"/>
-      <c r="Y186" s="314"/>
-      <c r="Z186" s="314"/>
-      <c r="AA186" s="314"/>
-      <c r="AB186" s="314"/>
-      <c r="AC186" s="314"/>
-      <c r="AD186" s="314"/>
-      <c r="AE186" s="314"/>
-      <c r="AF186" s="314"/>
-      <c r="AG186" s="314"/>
-      <c r="AH186" s="315"/>
+      <c r="F186" s="320"/>
+      <c r="G186" s="321"/>
+      <c r="H186" s="321"/>
+      <c r="I186" s="321"/>
+      <c r="J186" s="322"/>
+      <c r="K186" s="294"/>
+      <c r="L186" s="296"/>
+      <c r="M186" s="320"/>
+      <c r="N186" s="322"/>
+      <c r="O186" s="320"/>
+      <c r="P186" s="321"/>
+      <c r="Q186" s="321"/>
+      <c r="R186" s="321"/>
+      <c r="S186" s="321"/>
+      <c r="T186" s="321"/>
+      <c r="U186" s="321"/>
+      <c r="V186" s="321"/>
+      <c r="W186" s="321"/>
+      <c r="X186" s="321"/>
+      <c r="Y186" s="321"/>
+      <c r="Z186" s="321"/>
+      <c r="AA186" s="321"/>
+      <c r="AB186" s="321"/>
+      <c r="AC186" s="321"/>
+      <c r="AD186" s="321"/>
+      <c r="AE186" s="321"/>
+      <c r="AF186" s="321"/>
+      <c r="AG186" s="321"/>
+      <c r="AH186" s="322"/>
     </row>
     <row r="187" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F187" s="340" t="s">
+      <c r="F187" s="337" t="s">
         <v>39</v>
       </c>
-      <c r="G187" s="291"/>
-      <c r="H187" s="291"/>
-      <c r="I187" s="291"/>
-      <c r="J187" s="292"/>
-      <c r="K187" s="340" t="s">
+      <c r="G187" s="289"/>
+      <c r="H187" s="289"/>
+      <c r="I187" s="289"/>
+      <c r="J187" s="290"/>
+      <c r="K187" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="L187" s="292"/>
-      <c r="M187" s="340" t="s">
+      <c r="L187" s="290"/>
+      <c r="M187" s="337" t="s">
         <v>79</v>
       </c>
-      <c r="N187" s="312"/>
-      <c r="O187" s="310" t="s">
+      <c r="N187" s="319"/>
+      <c r="O187" s="317" t="s">
         <v>499</v>
       </c>
-      <c r="P187" s="311"/>
-      <c r="Q187" s="311"/>
-      <c r="R187" s="311"/>
-      <c r="S187" s="311"/>
-      <c r="T187" s="311"/>
-      <c r="U187" s="311"/>
-      <c r="V187" s="311"/>
-      <c r="W187" s="311"/>
-      <c r="X187" s="311"/>
-      <c r="Y187" s="311"/>
-      <c r="Z187" s="311"/>
-      <c r="AA187" s="311"/>
-      <c r="AB187" s="311"/>
-      <c r="AC187" s="311"/>
-      <c r="AD187" s="311"/>
-      <c r="AE187" s="311"/>
-      <c r="AF187" s="311"/>
-      <c r="AG187" s="311"/>
-      <c r="AH187" s="312"/>
+      <c r="P187" s="318"/>
+      <c r="Q187" s="318"/>
+      <c r="R187" s="318"/>
+      <c r="S187" s="318"/>
+      <c r="T187" s="318"/>
+      <c r="U187" s="318"/>
+      <c r="V187" s="318"/>
+      <c r="W187" s="318"/>
+      <c r="X187" s="318"/>
+      <c r="Y187" s="318"/>
+      <c r="Z187" s="318"/>
+      <c r="AA187" s="318"/>
+      <c r="AB187" s="318"/>
+      <c r="AC187" s="318"/>
+      <c r="AD187" s="318"/>
+      <c r="AE187" s="318"/>
+      <c r="AF187" s="318"/>
+      <c r="AG187" s="318"/>
+      <c r="AH187" s="319"/>
     </row>
     <row r="188" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F188" s="313"/>
-      <c r="G188" s="314"/>
-      <c r="H188" s="314"/>
-      <c r="I188" s="314"/>
-      <c r="J188" s="315"/>
-      <c r="K188" s="296"/>
-      <c r="L188" s="298"/>
-      <c r="M188" s="313"/>
-      <c r="N188" s="315"/>
-      <c r="O188" s="313"/>
-      <c r="P188" s="314"/>
-      <c r="Q188" s="314"/>
-      <c r="R188" s="314"/>
-      <c r="S188" s="314"/>
-      <c r="T188" s="314"/>
-      <c r="U188" s="314"/>
-      <c r="V188" s="314"/>
-      <c r="W188" s="314"/>
-      <c r="X188" s="314"/>
-      <c r="Y188" s="314"/>
-      <c r="Z188" s="314"/>
-      <c r="AA188" s="314"/>
-      <c r="AB188" s="314"/>
-      <c r="AC188" s="314"/>
-      <c r="AD188" s="314"/>
-      <c r="AE188" s="314"/>
-      <c r="AF188" s="314"/>
-      <c r="AG188" s="314"/>
-      <c r="AH188" s="315"/>
+      <c r="F188" s="320"/>
+      <c r="G188" s="321"/>
+      <c r="H188" s="321"/>
+      <c r="I188" s="321"/>
+      <c r="J188" s="322"/>
+      <c r="K188" s="294"/>
+      <c r="L188" s="296"/>
+      <c r="M188" s="320"/>
+      <c r="N188" s="322"/>
+      <c r="O188" s="320"/>
+      <c r="P188" s="321"/>
+      <c r="Q188" s="321"/>
+      <c r="R188" s="321"/>
+      <c r="S188" s="321"/>
+      <c r="T188" s="321"/>
+      <c r="U188" s="321"/>
+      <c r="V188" s="321"/>
+      <c r="W188" s="321"/>
+      <c r="X188" s="321"/>
+      <c r="Y188" s="321"/>
+      <c r="Z188" s="321"/>
+      <c r="AA188" s="321"/>
+      <c r="AB188" s="321"/>
+      <c r="AC188" s="321"/>
+      <c r="AD188" s="321"/>
+      <c r="AE188" s="321"/>
+      <c r="AF188" s="321"/>
+      <c r="AG188" s="321"/>
+      <c r="AH188" s="322"/>
     </row>
     <row r="189" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F189" s="340" t="s">
+      <c r="F189" s="337" t="s">
         <v>137</v>
       </c>
-      <c r="G189" s="291"/>
-      <c r="H189" s="291"/>
-      <c r="I189" s="291"/>
-      <c r="J189" s="292"/>
-      <c r="K189" s="340" t="s">
+      <c r="G189" s="289"/>
+      <c r="H189" s="289"/>
+      <c r="I189" s="289"/>
+      <c r="J189" s="290"/>
+      <c r="K189" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="L189" s="292"/>
-      <c r="M189" s="340" t="s">
+      <c r="L189" s="290"/>
+      <c r="M189" s="337" t="s">
         <v>72</v>
       </c>
-      <c r="N189" s="312"/>
-      <c r="O189" s="290" t="s">
+      <c r="N189" s="319"/>
+      <c r="O189" s="288" t="s">
         <v>308</v>
       </c>
-      <c r="P189" s="291"/>
-      <c r="Q189" s="291"/>
-      <c r="R189" s="291"/>
-      <c r="S189" s="291"/>
-      <c r="T189" s="291"/>
-      <c r="U189" s="291"/>
-      <c r="V189" s="291"/>
-      <c r="W189" s="291"/>
-      <c r="X189" s="291"/>
-      <c r="Y189" s="291"/>
-      <c r="Z189" s="291"/>
-      <c r="AA189" s="291"/>
-      <c r="AB189" s="291"/>
-      <c r="AC189" s="291"/>
-      <c r="AD189" s="291"/>
-      <c r="AE189" s="291"/>
-      <c r="AF189" s="291"/>
-      <c r="AG189" s="291"/>
-      <c r="AH189" s="292"/>
+      <c r="P189" s="289"/>
+      <c r="Q189" s="289"/>
+      <c r="R189" s="289"/>
+      <c r="S189" s="289"/>
+      <c r="T189" s="289"/>
+      <c r="U189" s="289"/>
+      <c r="V189" s="289"/>
+      <c r="W189" s="289"/>
+      <c r="X189" s="289"/>
+      <c r="Y189" s="289"/>
+      <c r="Z189" s="289"/>
+      <c r="AA189" s="289"/>
+      <c r="AB189" s="289"/>
+      <c r="AC189" s="289"/>
+      <c r="AD189" s="289"/>
+      <c r="AE189" s="289"/>
+      <c r="AF189" s="289"/>
+      <c r="AG189" s="289"/>
+      <c r="AH189" s="290"/>
     </row>
     <row r="190" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F190" s="313"/>
-      <c r="G190" s="314"/>
-      <c r="H190" s="314"/>
-      <c r="I190" s="314"/>
-      <c r="J190" s="315"/>
-      <c r="K190" s="296"/>
-      <c r="L190" s="298"/>
-      <c r="M190" s="313"/>
-      <c r="N190" s="315"/>
-      <c r="O190" s="313"/>
-      <c r="P190" s="314"/>
-      <c r="Q190" s="314"/>
-      <c r="R190" s="314"/>
-      <c r="S190" s="314"/>
-      <c r="T190" s="314"/>
-      <c r="U190" s="314"/>
-      <c r="V190" s="314"/>
-      <c r="W190" s="314"/>
-      <c r="X190" s="314"/>
-      <c r="Y190" s="314"/>
-      <c r="Z190" s="314"/>
-      <c r="AA190" s="314"/>
-      <c r="AB190" s="314"/>
-      <c r="AC190" s="314"/>
-      <c r="AD190" s="314"/>
-      <c r="AE190" s="314"/>
-      <c r="AF190" s="314"/>
-      <c r="AG190" s="314"/>
-      <c r="AH190" s="315"/>
+      <c r="F190" s="320"/>
+      <c r="G190" s="321"/>
+      <c r="H190" s="321"/>
+      <c r="I190" s="321"/>
+      <c r="J190" s="322"/>
+      <c r="K190" s="294"/>
+      <c r="L190" s="296"/>
+      <c r="M190" s="320"/>
+      <c r="N190" s="322"/>
+      <c r="O190" s="320"/>
+      <c r="P190" s="321"/>
+      <c r="Q190" s="321"/>
+      <c r="R190" s="321"/>
+      <c r="S190" s="321"/>
+      <c r="T190" s="321"/>
+      <c r="U190" s="321"/>
+      <c r="V190" s="321"/>
+      <c r="W190" s="321"/>
+      <c r="X190" s="321"/>
+      <c r="Y190" s="321"/>
+      <c r="Z190" s="321"/>
+      <c r="AA190" s="321"/>
+      <c r="AB190" s="321"/>
+      <c r="AC190" s="321"/>
+      <c r="AD190" s="321"/>
+      <c r="AE190" s="321"/>
+      <c r="AF190" s="321"/>
+      <c r="AG190" s="321"/>
+      <c r="AH190" s="322"/>
     </row>
     <row r="191" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F191" s="307" t="s">
+      <c r="F191" s="310" t="s">
         <v>138</v>
       </c>
-      <c r="G191" s="252"/>
-      <c r="H191" s="252"/>
-      <c r="I191" s="252"/>
-      <c r="J191" s="253"/>
-      <c r="K191" s="341" t="s">
+      <c r="G191" s="280"/>
+      <c r="H191" s="280"/>
+      <c r="I191" s="280"/>
+      <c r="J191" s="281"/>
+      <c r="K191" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="L191" s="364"/>
-      <c r="M191" s="341" t="s">
+      <c r="L191" s="346"/>
+      <c r="M191" s="345" t="s">
         <v>72</v>
       </c>
-      <c r="N191" s="337"/>
-      <c r="O191" s="307" t="s">
+      <c r="N191" s="350"/>
+      <c r="O191" s="310" t="s">
         <v>309</v>
       </c>
-      <c r="P191" s="252"/>
-      <c r="Q191" s="252"/>
-      <c r="R191" s="252"/>
-      <c r="S191" s="252"/>
-      <c r="T191" s="252"/>
-      <c r="U191" s="252"/>
-      <c r="V191" s="252"/>
-      <c r="W191" s="252"/>
-      <c r="X191" s="252"/>
-      <c r="Y191" s="252"/>
-      <c r="Z191" s="252"/>
-      <c r="AA191" s="252"/>
-      <c r="AB191" s="252"/>
-      <c r="AC191" s="252"/>
-      <c r="AD191" s="252"/>
-      <c r="AE191" s="252"/>
-      <c r="AF191" s="252"/>
-      <c r="AG191" s="252"/>
-      <c r="AH191" s="253"/>
+      <c r="P191" s="280"/>
+      <c r="Q191" s="280"/>
+      <c r="R191" s="280"/>
+      <c r="S191" s="280"/>
+      <c r="T191" s="280"/>
+      <c r="U191" s="280"/>
+      <c r="V191" s="280"/>
+      <c r="W191" s="280"/>
+      <c r="X191" s="280"/>
+      <c r="Y191" s="280"/>
+      <c r="Z191" s="280"/>
+      <c r="AA191" s="280"/>
+      <c r="AB191" s="280"/>
+      <c r="AC191" s="280"/>
+      <c r="AD191" s="280"/>
+      <c r="AE191" s="280"/>
+      <c r="AF191" s="280"/>
+      <c r="AG191" s="280"/>
+      <c r="AH191" s="281"/>
     </row>
     <row r="192" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F192" s="340" t="s">
+      <c r="F192" s="337" t="s">
         <v>49</v>
       </c>
-      <c r="G192" s="291"/>
-      <c r="H192" s="291"/>
-      <c r="I192" s="291"/>
-      <c r="J192" s="292"/>
-      <c r="K192" s="340" t="s">
+      <c r="G192" s="289"/>
+      <c r="H192" s="289"/>
+      <c r="I192" s="289"/>
+      <c r="J192" s="290"/>
+      <c r="K192" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="L192" s="292"/>
-      <c r="M192" s="340" t="s">
+      <c r="L192" s="290"/>
+      <c r="M192" s="337" t="s">
         <v>77</v>
       </c>
-      <c r="N192" s="312"/>
-      <c r="O192" s="290" t="s">
+      <c r="N192" s="319"/>
+      <c r="O192" s="288" t="s">
         <v>498</v>
       </c>
-      <c r="P192" s="311"/>
-      <c r="Q192" s="311"/>
-      <c r="R192" s="311"/>
-      <c r="S192" s="311"/>
-      <c r="T192" s="311"/>
-      <c r="U192" s="311"/>
-      <c r="V192" s="311"/>
-      <c r="W192" s="311"/>
-      <c r="X192" s="311"/>
-      <c r="Y192" s="311"/>
-      <c r="Z192" s="311"/>
-      <c r="AA192" s="311"/>
-      <c r="AB192" s="311"/>
-      <c r="AC192" s="311"/>
-      <c r="AD192" s="311"/>
-      <c r="AE192" s="311"/>
-      <c r="AF192" s="311"/>
-      <c r="AG192" s="311"/>
-      <c r="AH192" s="312"/>
+      <c r="P192" s="318"/>
+      <c r="Q192" s="318"/>
+      <c r="R192" s="318"/>
+      <c r="S192" s="318"/>
+      <c r="T192" s="318"/>
+      <c r="U192" s="318"/>
+      <c r="V192" s="318"/>
+      <c r="W192" s="318"/>
+      <c r="X192" s="318"/>
+      <c r="Y192" s="318"/>
+      <c r="Z192" s="318"/>
+      <c r="AA192" s="318"/>
+      <c r="AB192" s="318"/>
+      <c r="AC192" s="318"/>
+      <c r="AD192" s="318"/>
+      <c r="AE192" s="318"/>
+      <c r="AF192" s="318"/>
+      <c r="AG192" s="318"/>
+      <c r="AH192" s="319"/>
     </row>
     <row r="193" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F193" s="313"/>
-      <c r="G193" s="314"/>
-      <c r="H193" s="314"/>
-      <c r="I193" s="314"/>
-      <c r="J193" s="315"/>
-      <c r="K193" s="296"/>
-      <c r="L193" s="298"/>
-      <c r="M193" s="313"/>
-      <c r="N193" s="315"/>
-      <c r="O193" s="313"/>
-      <c r="P193" s="314"/>
-      <c r="Q193" s="314"/>
-      <c r="R193" s="314"/>
-      <c r="S193" s="314"/>
-      <c r="T193" s="314"/>
-      <c r="U193" s="314"/>
-      <c r="V193" s="314"/>
-      <c r="W193" s="314"/>
-      <c r="X193" s="314"/>
-      <c r="Y193" s="314"/>
-      <c r="Z193" s="314"/>
-      <c r="AA193" s="314"/>
-      <c r="AB193" s="314"/>
-      <c r="AC193" s="314"/>
-      <c r="AD193" s="314"/>
-      <c r="AE193" s="314"/>
-      <c r="AF193" s="314"/>
-      <c r="AG193" s="314"/>
-      <c r="AH193" s="315"/>
+      <c r="F193" s="320"/>
+      <c r="G193" s="321"/>
+      <c r="H193" s="321"/>
+      <c r="I193" s="321"/>
+      <c r="J193" s="322"/>
+      <c r="K193" s="294"/>
+      <c r="L193" s="296"/>
+      <c r="M193" s="320"/>
+      <c r="N193" s="322"/>
+      <c r="O193" s="320"/>
+      <c r="P193" s="321"/>
+      <c r="Q193" s="321"/>
+      <c r="R193" s="321"/>
+      <c r="S193" s="321"/>
+      <c r="T193" s="321"/>
+      <c r="U193" s="321"/>
+      <c r="V193" s="321"/>
+      <c r="W193" s="321"/>
+      <c r="X193" s="321"/>
+      <c r="Y193" s="321"/>
+      <c r="Z193" s="321"/>
+      <c r="AA193" s="321"/>
+      <c r="AB193" s="321"/>
+      <c r="AC193" s="321"/>
+      <c r="AD193" s="321"/>
+      <c r="AE193" s="321"/>
+      <c r="AF193" s="321"/>
+      <c r="AG193" s="321"/>
+      <c r="AH193" s="322"/>
     </row>
     <row r="194" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F194" s="251" t="s">
+      <c r="F194" s="279" t="s">
         <v>42</v>
       </c>
-      <c r="G194" s="252"/>
-      <c r="H194" s="252"/>
-      <c r="I194" s="252"/>
-      <c r="J194" s="253"/>
-      <c r="K194" s="341" t="s">
+      <c r="G194" s="280"/>
+      <c r="H194" s="280"/>
+      <c r="I194" s="280"/>
+      <c r="J194" s="281"/>
+      <c r="K194" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="L194" s="364"/>
-      <c r="M194" s="341" t="s">
+      <c r="L194" s="346"/>
+      <c r="M194" s="345" t="s">
         <v>76</v>
       </c>
-      <c r="N194" s="337"/>
-      <c r="O194" s="307" t="s">
+      <c r="N194" s="350"/>
+      <c r="O194" s="310" t="s">
         <v>309</v>
       </c>
-      <c r="P194" s="252"/>
-      <c r="Q194" s="252"/>
-      <c r="R194" s="252"/>
-      <c r="S194" s="252"/>
-      <c r="T194" s="252"/>
-      <c r="U194" s="252"/>
-      <c r="V194" s="252"/>
-      <c r="W194" s="252"/>
-      <c r="X194" s="252"/>
-      <c r="Y194" s="252"/>
-      <c r="Z194" s="252"/>
-      <c r="AA194" s="252"/>
-      <c r="AB194" s="252"/>
-      <c r="AC194" s="252"/>
-      <c r="AD194" s="252"/>
-      <c r="AE194" s="252"/>
-      <c r="AF194" s="252"/>
-      <c r="AG194" s="252"/>
-      <c r="AH194" s="253"/>
+      <c r="P194" s="280"/>
+      <c r="Q194" s="280"/>
+      <c r="R194" s="280"/>
+      <c r="S194" s="280"/>
+      <c r="T194" s="280"/>
+      <c r="U194" s="280"/>
+      <c r="V194" s="280"/>
+      <c r="W194" s="280"/>
+      <c r="X194" s="280"/>
+      <c r="Y194" s="280"/>
+      <c r="Z194" s="280"/>
+      <c r="AA194" s="280"/>
+      <c r="AB194" s="280"/>
+      <c r="AC194" s="280"/>
+      <c r="AD194" s="280"/>
+      <c r="AE194" s="280"/>
+      <c r="AF194" s="280"/>
+      <c r="AG194" s="280"/>
+      <c r="AH194" s="281"/>
     </row>
     <row r="195" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E195" s="30"/>
-      <c r="F195" s="310" t="s">
+      <c r="F195" s="317" t="s">
         <v>270</v>
       </c>
-      <c r="G195" s="311"/>
-      <c r="H195" s="311"/>
-      <c r="I195" s="311"/>
-      <c r="J195" s="312"/>
-      <c r="K195" s="351" t="s">
+      <c r="G195" s="318"/>
+      <c r="H195" s="318"/>
+      <c r="I195" s="318"/>
+      <c r="J195" s="319"/>
+      <c r="K195" s="328" t="s">
         <v>46</v>
       </c>
-      <c r="L195" s="352"/>
-      <c r="M195" s="340" t="s">
+      <c r="L195" s="329"/>
+      <c r="M195" s="337" t="s">
         <v>76</v>
       </c>
-      <c r="N195" s="312"/>
-      <c r="O195" s="290" t="s">
+      <c r="N195" s="319"/>
+      <c r="O195" s="288" t="s">
         <v>309</v>
       </c>
-      <c r="P195" s="291"/>
-      <c r="Q195" s="291"/>
-      <c r="R195" s="291"/>
-      <c r="S195" s="291"/>
-      <c r="T195" s="291"/>
-      <c r="U195" s="291"/>
-      <c r="V195" s="291"/>
-      <c r="W195" s="291"/>
-      <c r="X195" s="291"/>
-      <c r="Y195" s="291"/>
-      <c r="Z195" s="291"/>
-      <c r="AA195" s="291"/>
-      <c r="AB195" s="291"/>
-      <c r="AC195" s="291"/>
-      <c r="AD195" s="291"/>
-      <c r="AE195" s="291"/>
-      <c r="AF195" s="291"/>
-      <c r="AG195" s="291"/>
-      <c r="AH195" s="292"/>
+      <c r="P195" s="289"/>
+      <c r="Q195" s="289"/>
+      <c r="R195" s="289"/>
+      <c r="S195" s="289"/>
+      <c r="T195" s="289"/>
+      <c r="U195" s="289"/>
+      <c r="V195" s="289"/>
+      <c r="W195" s="289"/>
+      <c r="X195" s="289"/>
+      <c r="Y195" s="289"/>
+      <c r="Z195" s="289"/>
+      <c r="AA195" s="289"/>
+      <c r="AB195" s="289"/>
+      <c r="AC195" s="289"/>
+      <c r="AD195" s="289"/>
+      <c r="AE195" s="289"/>
+      <c r="AF195" s="289"/>
+      <c r="AG195" s="289"/>
+      <c r="AH195" s="290"/>
     </row>
     <row r="196" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E196" s="30"/>
-      <c r="F196" s="313"/>
-      <c r="G196" s="314"/>
-      <c r="H196" s="314"/>
-      <c r="I196" s="314"/>
-      <c r="J196" s="315"/>
-      <c r="K196" s="359"/>
-      <c r="L196" s="361"/>
-      <c r="M196" s="313"/>
-      <c r="N196" s="315"/>
-      <c r="O196" s="313"/>
-      <c r="P196" s="314"/>
-      <c r="Q196" s="314"/>
-      <c r="R196" s="314"/>
-      <c r="S196" s="314"/>
-      <c r="T196" s="314"/>
-      <c r="U196" s="314"/>
-      <c r="V196" s="314"/>
-      <c r="W196" s="314"/>
-      <c r="X196" s="314"/>
-      <c r="Y196" s="314"/>
-      <c r="Z196" s="314"/>
-      <c r="AA196" s="314"/>
-      <c r="AB196" s="314"/>
-      <c r="AC196" s="314"/>
-      <c r="AD196" s="314"/>
-      <c r="AE196" s="314"/>
-      <c r="AF196" s="314"/>
-      <c r="AG196" s="314"/>
-      <c r="AH196" s="315"/>
+      <c r="F196" s="320"/>
+      <c r="G196" s="321"/>
+      <c r="H196" s="321"/>
+      <c r="I196" s="321"/>
+      <c r="J196" s="322"/>
+      <c r="K196" s="325"/>
+      <c r="L196" s="327"/>
+      <c r="M196" s="320"/>
+      <c r="N196" s="322"/>
+      <c r="O196" s="320"/>
+      <c r="P196" s="321"/>
+      <c r="Q196" s="321"/>
+      <c r="R196" s="321"/>
+      <c r="S196" s="321"/>
+      <c r="T196" s="321"/>
+      <c r="U196" s="321"/>
+      <c r="V196" s="321"/>
+      <c r="W196" s="321"/>
+      <c r="X196" s="321"/>
+      <c r="Y196" s="321"/>
+      <c r="Z196" s="321"/>
+      <c r="AA196" s="321"/>
+      <c r="AB196" s="321"/>
+      <c r="AC196" s="321"/>
+      <c r="AD196" s="321"/>
+      <c r="AE196" s="321"/>
+      <c r="AF196" s="321"/>
+      <c r="AG196" s="321"/>
+      <c r="AH196" s="322"/>
     </row>
     <row r="197" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="198" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -43697,689 +43697,689 @@
     </row>
     <row r="200" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="201" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F201" s="365" t="s">
+      <c r="F201" s="331" t="s">
         <v>630</v>
       </c>
-      <c r="G201" s="366"/>
-      <c r="H201" s="366"/>
-      <c r="I201" s="366"/>
-      <c r="J201" s="367"/>
-      <c r="K201" s="355" t="s">
+      <c r="G201" s="332"/>
+      <c r="H201" s="332"/>
+      <c r="I201" s="332"/>
+      <c r="J201" s="333"/>
+      <c r="K201" s="348" t="s">
         <v>30</v>
       </c>
-      <c r="L201" s="356"/>
-      <c r="M201" s="355" t="s">
+      <c r="L201" s="349"/>
+      <c r="M201" s="348" t="s">
         <v>31</v>
       </c>
-      <c r="N201" s="356"/>
-      <c r="O201" s="248" t="s">
+      <c r="N201" s="349"/>
+      <c r="O201" s="276" t="s">
         <v>305</v>
       </c>
-      <c r="P201" s="249"/>
-      <c r="Q201" s="249"/>
-      <c r="R201" s="249"/>
-      <c r="S201" s="249"/>
-      <c r="T201" s="249"/>
-      <c r="U201" s="249"/>
-      <c r="V201" s="249"/>
-      <c r="W201" s="249"/>
-      <c r="X201" s="249"/>
-      <c r="Y201" s="249"/>
-      <c r="Z201" s="249"/>
-      <c r="AA201" s="249"/>
-      <c r="AB201" s="249"/>
-      <c r="AC201" s="249"/>
-      <c r="AD201" s="249"/>
-      <c r="AE201" s="249"/>
-      <c r="AF201" s="249"/>
-      <c r="AG201" s="249"/>
-      <c r="AH201" s="250"/>
+      <c r="P201" s="277"/>
+      <c r="Q201" s="277"/>
+      <c r="R201" s="277"/>
+      <c r="S201" s="277"/>
+      <c r="T201" s="277"/>
+      <c r="U201" s="277"/>
+      <c r="V201" s="277"/>
+      <c r="W201" s="277"/>
+      <c r="X201" s="277"/>
+      <c r="Y201" s="277"/>
+      <c r="Z201" s="277"/>
+      <c r="AA201" s="277"/>
+      <c r="AB201" s="277"/>
+      <c r="AC201" s="277"/>
+      <c r="AD201" s="277"/>
+      <c r="AE201" s="277"/>
+      <c r="AF201" s="277"/>
+      <c r="AG201" s="277"/>
+      <c r="AH201" s="278"/>
     </row>
     <row r="202" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F202" s="310" t="s">
+      <c r="F202" s="317" t="s">
         <v>285</v>
       </c>
-      <c r="G202" s="357"/>
-      <c r="H202" s="357"/>
-      <c r="I202" s="357"/>
-      <c r="J202" s="358"/>
-      <c r="K202" s="340" t="s">
+      <c r="G202" s="323"/>
+      <c r="H202" s="323"/>
+      <c r="I202" s="323"/>
+      <c r="J202" s="324"/>
+      <c r="K202" s="337" t="s">
         <v>32</v>
       </c>
-      <c r="L202" s="292"/>
-      <c r="M202" s="340" t="s">
+      <c r="L202" s="290"/>
+      <c r="M202" s="337" t="s">
         <v>33</v>
       </c>
-      <c r="N202" s="292"/>
-      <c r="O202" s="310" t="s">
+      <c r="N202" s="290"/>
+      <c r="O202" s="317" t="s">
         <v>287</v>
       </c>
-      <c r="P202" s="357"/>
-      <c r="Q202" s="357"/>
-      <c r="R202" s="357"/>
-      <c r="S202" s="357"/>
-      <c r="T202" s="357"/>
-      <c r="U202" s="357"/>
-      <c r="V202" s="357"/>
-      <c r="W202" s="357"/>
-      <c r="X202" s="357"/>
-      <c r="Y202" s="357"/>
-      <c r="Z202" s="357"/>
-      <c r="AA202" s="357"/>
-      <c r="AB202" s="357"/>
-      <c r="AC202" s="357"/>
-      <c r="AD202" s="357"/>
-      <c r="AE202" s="357"/>
-      <c r="AF202" s="357"/>
-      <c r="AG202" s="357"/>
-      <c r="AH202" s="358"/>
+      <c r="P202" s="323"/>
+      <c r="Q202" s="323"/>
+      <c r="R202" s="323"/>
+      <c r="S202" s="323"/>
+      <c r="T202" s="323"/>
+      <c r="U202" s="323"/>
+      <c r="V202" s="323"/>
+      <c r="W202" s="323"/>
+      <c r="X202" s="323"/>
+      <c r="Y202" s="323"/>
+      <c r="Z202" s="323"/>
+      <c r="AA202" s="323"/>
+      <c r="AB202" s="323"/>
+      <c r="AC202" s="323"/>
+      <c r="AD202" s="323"/>
+      <c r="AE202" s="323"/>
+      <c r="AF202" s="323"/>
+      <c r="AG202" s="323"/>
+      <c r="AH202" s="324"/>
     </row>
     <row r="203" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F203" s="359"/>
-      <c r="G203" s="360"/>
-      <c r="H203" s="360"/>
-      <c r="I203" s="360"/>
-      <c r="J203" s="361"/>
-      <c r="K203" s="296"/>
-      <c r="L203" s="298"/>
-      <c r="M203" s="296"/>
-      <c r="N203" s="298"/>
-      <c r="O203" s="359"/>
-      <c r="P203" s="360"/>
-      <c r="Q203" s="360"/>
-      <c r="R203" s="360"/>
-      <c r="S203" s="360"/>
-      <c r="T203" s="360"/>
-      <c r="U203" s="360"/>
-      <c r="V203" s="360"/>
-      <c r="W203" s="360"/>
-      <c r="X203" s="360"/>
-      <c r="Y203" s="360"/>
-      <c r="Z203" s="360"/>
-      <c r="AA203" s="360"/>
-      <c r="AB203" s="360"/>
-      <c r="AC203" s="360"/>
-      <c r="AD203" s="360"/>
-      <c r="AE203" s="360"/>
-      <c r="AF203" s="360"/>
-      <c r="AG203" s="360"/>
-      <c r="AH203" s="361"/>
+      <c r="F203" s="325"/>
+      <c r="G203" s="326"/>
+      <c r="H203" s="326"/>
+      <c r="I203" s="326"/>
+      <c r="J203" s="327"/>
+      <c r="K203" s="294"/>
+      <c r="L203" s="296"/>
+      <c r="M203" s="294"/>
+      <c r="N203" s="296"/>
+      <c r="O203" s="325"/>
+      <c r="P203" s="326"/>
+      <c r="Q203" s="326"/>
+      <c r="R203" s="326"/>
+      <c r="S203" s="326"/>
+      <c r="T203" s="326"/>
+      <c r="U203" s="326"/>
+      <c r="V203" s="326"/>
+      <c r="W203" s="326"/>
+      <c r="X203" s="326"/>
+      <c r="Y203" s="326"/>
+      <c r="Z203" s="326"/>
+      <c r="AA203" s="326"/>
+      <c r="AB203" s="326"/>
+      <c r="AC203" s="326"/>
+      <c r="AD203" s="326"/>
+      <c r="AE203" s="326"/>
+      <c r="AF203" s="326"/>
+      <c r="AG203" s="326"/>
+      <c r="AH203" s="327"/>
     </row>
     <row r="204" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F204" s="351" t="s">
+      <c r="F204" s="328" t="s">
         <v>40</v>
       </c>
-      <c r="G204" s="362"/>
-      <c r="H204" s="362"/>
-      <c r="I204" s="362"/>
-      <c r="J204" s="352"/>
-      <c r="K204" s="340" t="s">
+      <c r="G204" s="330"/>
+      <c r="H204" s="330"/>
+      <c r="I204" s="330"/>
+      <c r="J204" s="329"/>
+      <c r="K204" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="L204" s="292"/>
-      <c r="M204" s="340" t="s">
+      <c r="L204" s="290"/>
+      <c r="M204" s="337" t="s">
         <v>33</v>
       </c>
-      <c r="N204" s="292"/>
-      <c r="O204" s="310" t="s">
+      <c r="N204" s="290"/>
+      <c r="O204" s="317" t="s">
         <v>493</v>
       </c>
-      <c r="P204" s="357"/>
-      <c r="Q204" s="357"/>
-      <c r="R204" s="357"/>
-      <c r="S204" s="357"/>
-      <c r="T204" s="357"/>
-      <c r="U204" s="357"/>
-      <c r="V204" s="357"/>
-      <c r="W204" s="357"/>
-      <c r="X204" s="357"/>
-      <c r="Y204" s="357"/>
-      <c r="Z204" s="357"/>
-      <c r="AA204" s="357"/>
-      <c r="AB204" s="357"/>
-      <c r="AC204" s="357"/>
-      <c r="AD204" s="357"/>
-      <c r="AE204" s="357"/>
-      <c r="AF204" s="357"/>
-      <c r="AG204" s="357"/>
-      <c r="AH204" s="358"/>
+      <c r="P204" s="323"/>
+      <c r="Q204" s="323"/>
+      <c r="R204" s="323"/>
+      <c r="S204" s="323"/>
+      <c r="T204" s="323"/>
+      <c r="U204" s="323"/>
+      <c r="V204" s="323"/>
+      <c r="W204" s="323"/>
+      <c r="X204" s="323"/>
+      <c r="Y204" s="323"/>
+      <c r="Z204" s="323"/>
+      <c r="AA204" s="323"/>
+      <c r="AB204" s="323"/>
+      <c r="AC204" s="323"/>
+      <c r="AD204" s="323"/>
+      <c r="AE204" s="323"/>
+      <c r="AF204" s="323"/>
+      <c r="AG204" s="323"/>
+      <c r="AH204" s="324"/>
     </row>
     <row r="205" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F205" s="359"/>
-      <c r="G205" s="360"/>
-      <c r="H205" s="360"/>
-      <c r="I205" s="360"/>
-      <c r="J205" s="361"/>
-      <c r="K205" s="296"/>
-      <c r="L205" s="298"/>
-      <c r="M205" s="296"/>
-      <c r="N205" s="298"/>
-      <c r="O205" s="359"/>
-      <c r="P205" s="360"/>
-      <c r="Q205" s="360"/>
-      <c r="R205" s="360"/>
-      <c r="S205" s="360"/>
-      <c r="T205" s="360"/>
-      <c r="U205" s="360"/>
-      <c r="V205" s="360"/>
-      <c r="W205" s="360"/>
-      <c r="X205" s="360"/>
-      <c r="Y205" s="360"/>
-      <c r="Z205" s="360"/>
-      <c r="AA205" s="360"/>
-      <c r="AB205" s="360"/>
-      <c r="AC205" s="360"/>
-      <c r="AD205" s="360"/>
-      <c r="AE205" s="360"/>
-      <c r="AF205" s="360"/>
-      <c r="AG205" s="360"/>
-      <c r="AH205" s="361"/>
+      <c r="F205" s="325"/>
+      <c r="G205" s="326"/>
+      <c r="H205" s="326"/>
+      <c r="I205" s="326"/>
+      <c r="J205" s="327"/>
+      <c r="K205" s="294"/>
+      <c r="L205" s="296"/>
+      <c r="M205" s="294"/>
+      <c r="N205" s="296"/>
+      <c r="O205" s="325"/>
+      <c r="P205" s="326"/>
+      <c r="Q205" s="326"/>
+      <c r="R205" s="326"/>
+      <c r="S205" s="326"/>
+      <c r="T205" s="326"/>
+      <c r="U205" s="326"/>
+      <c r="V205" s="326"/>
+      <c r="W205" s="326"/>
+      <c r="X205" s="326"/>
+      <c r="Y205" s="326"/>
+      <c r="Z205" s="326"/>
+      <c r="AA205" s="326"/>
+      <c r="AB205" s="326"/>
+      <c r="AC205" s="326"/>
+      <c r="AD205" s="326"/>
+      <c r="AE205" s="326"/>
+      <c r="AF205" s="326"/>
+      <c r="AG205" s="326"/>
+      <c r="AH205" s="327"/>
     </row>
     <row r="206" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F206" s="351" t="s">
+      <c r="F206" s="328" t="s">
         <v>41</v>
       </c>
-      <c r="G206" s="362"/>
-      <c r="H206" s="362"/>
-      <c r="I206" s="362"/>
-      <c r="J206" s="352"/>
-      <c r="K206" s="351" t="s">
+      <c r="G206" s="330"/>
+      <c r="H206" s="330"/>
+      <c r="I206" s="330"/>
+      <c r="J206" s="329"/>
+      <c r="K206" s="328" t="s">
         <v>35</v>
       </c>
-      <c r="L206" s="352"/>
-      <c r="M206" s="351" t="s">
+      <c r="L206" s="329"/>
+      <c r="M206" s="328" t="s">
         <v>33</v>
       </c>
-      <c r="N206" s="352"/>
-      <c r="O206" s="310" t="s">
+      <c r="N206" s="329"/>
+      <c r="O206" s="317" t="s">
         <v>494</v>
       </c>
-      <c r="P206" s="357"/>
-      <c r="Q206" s="357"/>
-      <c r="R206" s="357"/>
-      <c r="S206" s="357"/>
-      <c r="T206" s="357"/>
-      <c r="U206" s="357"/>
-      <c r="V206" s="357"/>
-      <c r="W206" s="357"/>
-      <c r="X206" s="357"/>
-      <c r="Y206" s="357"/>
-      <c r="Z206" s="357"/>
-      <c r="AA206" s="357"/>
-      <c r="AB206" s="357"/>
-      <c r="AC206" s="357"/>
-      <c r="AD206" s="357"/>
-      <c r="AE206" s="357"/>
-      <c r="AF206" s="357"/>
-      <c r="AG206" s="357"/>
-      <c r="AH206" s="358"/>
+      <c r="P206" s="323"/>
+      <c r="Q206" s="323"/>
+      <c r="R206" s="323"/>
+      <c r="S206" s="323"/>
+      <c r="T206" s="323"/>
+      <c r="U206" s="323"/>
+      <c r="V206" s="323"/>
+      <c r="W206" s="323"/>
+      <c r="X206" s="323"/>
+      <c r="Y206" s="323"/>
+      <c r="Z206" s="323"/>
+      <c r="AA206" s="323"/>
+      <c r="AB206" s="323"/>
+      <c r="AC206" s="323"/>
+      <c r="AD206" s="323"/>
+      <c r="AE206" s="323"/>
+      <c r="AF206" s="323"/>
+      <c r="AG206" s="323"/>
+      <c r="AH206" s="324"/>
     </row>
     <row r="207" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F207" s="359"/>
-      <c r="G207" s="360"/>
-      <c r="H207" s="360"/>
-      <c r="I207" s="360"/>
-      <c r="J207" s="361"/>
-      <c r="K207" s="353"/>
-      <c r="L207" s="354"/>
-      <c r="M207" s="353"/>
-      <c r="N207" s="354"/>
-      <c r="O207" s="359"/>
-      <c r="P207" s="360"/>
-      <c r="Q207" s="360"/>
-      <c r="R207" s="360"/>
-      <c r="S207" s="360"/>
-      <c r="T207" s="360"/>
-      <c r="U207" s="360"/>
-      <c r="V207" s="360"/>
-      <c r="W207" s="360"/>
-      <c r="X207" s="360"/>
-      <c r="Y207" s="360"/>
-      <c r="Z207" s="360"/>
-      <c r="AA207" s="360"/>
-      <c r="AB207" s="360"/>
-      <c r="AC207" s="360"/>
-      <c r="AD207" s="360"/>
-      <c r="AE207" s="360"/>
-      <c r="AF207" s="360"/>
-      <c r="AG207" s="360"/>
-      <c r="AH207" s="361"/>
+      <c r="F207" s="325"/>
+      <c r="G207" s="326"/>
+      <c r="H207" s="326"/>
+      <c r="I207" s="326"/>
+      <c r="J207" s="327"/>
+      <c r="K207" s="351"/>
+      <c r="L207" s="352"/>
+      <c r="M207" s="351"/>
+      <c r="N207" s="352"/>
+      <c r="O207" s="325"/>
+      <c r="P207" s="326"/>
+      <c r="Q207" s="326"/>
+      <c r="R207" s="326"/>
+      <c r="S207" s="326"/>
+      <c r="T207" s="326"/>
+      <c r="U207" s="326"/>
+      <c r="V207" s="326"/>
+      <c r="W207" s="326"/>
+      <c r="X207" s="326"/>
+      <c r="Y207" s="326"/>
+      <c r="Z207" s="326"/>
+      <c r="AA207" s="326"/>
+      <c r="AB207" s="326"/>
+      <c r="AC207" s="326"/>
+      <c r="AD207" s="326"/>
+      <c r="AE207" s="326"/>
+      <c r="AF207" s="326"/>
+      <c r="AG207" s="326"/>
+      <c r="AH207" s="327"/>
     </row>
     <row r="208" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F208" s="310" t="s">
+      <c r="F208" s="317" t="s">
         <v>286</v>
       </c>
-      <c r="G208" s="357"/>
-      <c r="H208" s="357"/>
-      <c r="I208" s="357"/>
-      <c r="J208" s="358"/>
-      <c r="K208" s="340" t="s">
+      <c r="G208" s="323"/>
+      <c r="H208" s="323"/>
+      <c r="I208" s="323"/>
+      <c r="J208" s="324"/>
+      <c r="K208" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="L208" s="292"/>
-      <c r="M208" s="340" t="s">
+      <c r="L208" s="290"/>
+      <c r="M208" s="337" t="s">
         <v>33</v>
       </c>
-      <c r="N208" s="292"/>
-      <c r="O208" s="310" t="s">
+      <c r="N208" s="290"/>
+      <c r="O208" s="317" t="s">
         <v>495</v>
       </c>
-      <c r="P208" s="357"/>
-      <c r="Q208" s="357"/>
-      <c r="R208" s="357"/>
-      <c r="S208" s="357"/>
-      <c r="T208" s="357"/>
-      <c r="U208" s="357"/>
-      <c r="V208" s="357"/>
-      <c r="W208" s="357"/>
-      <c r="X208" s="357"/>
-      <c r="Y208" s="357"/>
-      <c r="Z208" s="357"/>
-      <c r="AA208" s="357"/>
-      <c r="AB208" s="357"/>
-      <c r="AC208" s="357"/>
-      <c r="AD208" s="357"/>
-      <c r="AE208" s="357"/>
-      <c r="AF208" s="357"/>
-      <c r="AG208" s="357"/>
-      <c r="AH208" s="358"/>
+      <c r="P208" s="323"/>
+      <c r="Q208" s="323"/>
+      <c r="R208" s="323"/>
+      <c r="S208" s="323"/>
+      <c r="T208" s="323"/>
+      <c r="U208" s="323"/>
+      <c r="V208" s="323"/>
+      <c r="W208" s="323"/>
+      <c r="X208" s="323"/>
+      <c r="Y208" s="323"/>
+      <c r="Z208" s="323"/>
+      <c r="AA208" s="323"/>
+      <c r="AB208" s="323"/>
+      <c r="AC208" s="323"/>
+      <c r="AD208" s="323"/>
+      <c r="AE208" s="323"/>
+      <c r="AF208" s="323"/>
+      <c r="AG208" s="323"/>
+      <c r="AH208" s="324"/>
     </row>
     <row r="209" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F209" s="359"/>
-      <c r="G209" s="360"/>
-      <c r="H209" s="360"/>
-      <c r="I209" s="360"/>
-      <c r="J209" s="361"/>
-      <c r="K209" s="296"/>
-      <c r="L209" s="298"/>
-      <c r="M209" s="296"/>
-      <c r="N209" s="298"/>
-      <c r="O209" s="359"/>
-      <c r="P209" s="360"/>
-      <c r="Q209" s="360"/>
-      <c r="R209" s="360"/>
-      <c r="S209" s="360"/>
-      <c r="T209" s="360"/>
-      <c r="U209" s="360"/>
-      <c r="V209" s="360"/>
-      <c r="W209" s="360"/>
-      <c r="X209" s="360"/>
-      <c r="Y209" s="360"/>
-      <c r="Z209" s="360"/>
-      <c r="AA209" s="360"/>
-      <c r="AB209" s="360"/>
-      <c r="AC209" s="360"/>
-      <c r="AD209" s="360"/>
-      <c r="AE209" s="360"/>
-      <c r="AF209" s="360"/>
-      <c r="AG209" s="360"/>
-      <c r="AH209" s="361"/>
+      <c r="F209" s="325"/>
+      <c r="G209" s="326"/>
+      <c r="H209" s="326"/>
+      <c r="I209" s="326"/>
+      <c r="J209" s="327"/>
+      <c r="K209" s="294"/>
+      <c r="L209" s="296"/>
+      <c r="M209" s="294"/>
+      <c r="N209" s="296"/>
+      <c r="O209" s="325"/>
+      <c r="P209" s="326"/>
+      <c r="Q209" s="326"/>
+      <c r="R209" s="326"/>
+      <c r="S209" s="326"/>
+      <c r="T209" s="326"/>
+      <c r="U209" s="326"/>
+      <c r="V209" s="326"/>
+      <c r="W209" s="326"/>
+      <c r="X209" s="326"/>
+      <c r="Y209" s="326"/>
+      <c r="Z209" s="326"/>
+      <c r="AA209" s="326"/>
+      <c r="AB209" s="326"/>
+      <c r="AC209" s="326"/>
+      <c r="AD209" s="326"/>
+      <c r="AE209" s="326"/>
+      <c r="AF209" s="326"/>
+      <c r="AG209" s="326"/>
+      <c r="AH209" s="327"/>
     </row>
     <row r="210" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F210" s="251" t="s">
+      <c r="F210" s="279" t="s">
         <v>38</v>
       </c>
-      <c r="G210" s="252"/>
-      <c r="H210" s="252"/>
-      <c r="I210" s="252"/>
-      <c r="J210" s="253"/>
-      <c r="K210" s="218" t="s">
+      <c r="G210" s="280"/>
+      <c r="H210" s="280"/>
+      <c r="I210" s="280"/>
+      <c r="J210" s="281"/>
+      <c r="K210" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="L210" s="220"/>
-      <c r="M210" s="218" t="s">
+      <c r="L210" s="183"/>
+      <c r="M210" s="181" t="s">
         <v>33</v>
       </c>
-      <c r="N210" s="220"/>
-      <c r="O210" s="334" t="s">
+      <c r="N210" s="183"/>
+      <c r="O210" s="347" t="s">
         <v>340</v>
       </c>
-      <c r="P210" s="344"/>
-      <c r="Q210" s="344"/>
-      <c r="R210" s="344"/>
-      <c r="S210" s="344"/>
-      <c r="T210" s="344"/>
-      <c r="U210" s="344"/>
-      <c r="V210" s="344"/>
-      <c r="W210" s="344"/>
-      <c r="X210" s="344"/>
-      <c r="Y210" s="344"/>
-      <c r="Z210" s="344"/>
-      <c r="AA210" s="344"/>
-      <c r="AB210" s="344"/>
-      <c r="AC210" s="344"/>
-      <c r="AD210" s="344"/>
-      <c r="AE210" s="344"/>
-      <c r="AF210" s="344"/>
-      <c r="AG210" s="344"/>
-      <c r="AH210" s="345"/>
+      <c r="P210" s="339"/>
+      <c r="Q210" s="339"/>
+      <c r="R210" s="339"/>
+      <c r="S210" s="339"/>
+      <c r="T210" s="339"/>
+      <c r="U210" s="339"/>
+      <c r="V210" s="339"/>
+      <c r="W210" s="339"/>
+      <c r="X210" s="339"/>
+      <c r="Y210" s="339"/>
+      <c r="Z210" s="339"/>
+      <c r="AA210" s="339"/>
+      <c r="AB210" s="339"/>
+      <c r="AC210" s="339"/>
+      <c r="AD210" s="339"/>
+      <c r="AE210" s="339"/>
+      <c r="AF210" s="339"/>
+      <c r="AG210" s="339"/>
+      <c r="AH210" s="340"/>
     </row>
     <row r="211" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F211" s="251" t="s">
+      <c r="F211" s="279" t="s">
         <v>39</v>
       </c>
-      <c r="G211" s="252"/>
-      <c r="H211" s="252"/>
-      <c r="I211" s="252"/>
-      <c r="J211" s="253"/>
-      <c r="K211" s="218" t="s">
+      <c r="G211" s="280"/>
+      <c r="H211" s="280"/>
+      <c r="I211" s="280"/>
+      <c r="J211" s="281"/>
+      <c r="K211" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="L211" s="220"/>
-      <c r="M211" s="218" t="s">
+      <c r="L211" s="183"/>
+      <c r="M211" s="181" t="s">
         <v>33</v>
       </c>
-      <c r="N211" s="220"/>
-      <c r="O211" s="334" t="s">
+      <c r="N211" s="183"/>
+      <c r="O211" s="347" t="s">
         <v>284</v>
       </c>
-      <c r="P211" s="288"/>
-      <c r="Q211" s="288"/>
-      <c r="R211" s="288"/>
-      <c r="S211" s="288"/>
-      <c r="T211" s="288"/>
-      <c r="U211" s="288"/>
-      <c r="V211" s="288"/>
-      <c r="W211" s="288"/>
-      <c r="X211" s="288"/>
-      <c r="Y211" s="288"/>
-      <c r="Z211" s="288"/>
-      <c r="AA211" s="288"/>
-      <c r="AB211" s="288"/>
-      <c r="AC211" s="288"/>
-      <c r="AD211" s="288"/>
-      <c r="AE211" s="288"/>
-      <c r="AF211" s="288"/>
-      <c r="AG211" s="288"/>
-      <c r="AH211" s="289"/>
+      <c r="P211" s="286"/>
+      <c r="Q211" s="286"/>
+      <c r="R211" s="286"/>
+      <c r="S211" s="286"/>
+      <c r="T211" s="286"/>
+      <c r="U211" s="286"/>
+      <c r="V211" s="286"/>
+      <c r="W211" s="286"/>
+      <c r="X211" s="286"/>
+      <c r="Y211" s="286"/>
+      <c r="Z211" s="286"/>
+      <c r="AA211" s="286"/>
+      <c r="AB211" s="286"/>
+      <c r="AC211" s="286"/>
+      <c r="AD211" s="286"/>
+      <c r="AE211" s="286"/>
+      <c r="AF211" s="286"/>
+      <c r="AG211" s="286"/>
+      <c r="AH211" s="287"/>
     </row>
     <row r="212" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F212" s="351" t="s">
+      <c r="F212" s="328" t="s">
         <v>34</v>
       </c>
-      <c r="G212" s="362"/>
-      <c r="H212" s="362"/>
-      <c r="I212" s="362"/>
-      <c r="J212" s="352"/>
-      <c r="K212" s="340" t="s">
+      <c r="G212" s="330"/>
+      <c r="H212" s="330"/>
+      <c r="I212" s="330"/>
+      <c r="J212" s="329"/>
+      <c r="K212" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="L212" s="292"/>
-      <c r="M212" s="340" t="s">
+      <c r="L212" s="290"/>
+      <c r="M212" s="337" t="s">
         <v>33</v>
       </c>
-      <c r="N212" s="292"/>
-      <c r="O212" s="310" t="s">
+      <c r="N212" s="290"/>
+      <c r="O212" s="317" t="s">
         <v>496</v>
       </c>
-      <c r="P212" s="357"/>
-      <c r="Q212" s="357"/>
-      <c r="R212" s="357"/>
-      <c r="S212" s="357"/>
-      <c r="T212" s="357"/>
-      <c r="U212" s="357"/>
-      <c r="V212" s="357"/>
-      <c r="W212" s="357"/>
-      <c r="X212" s="357"/>
-      <c r="Y212" s="357"/>
-      <c r="Z212" s="357"/>
-      <c r="AA212" s="357"/>
-      <c r="AB212" s="357"/>
-      <c r="AC212" s="357"/>
-      <c r="AD212" s="357"/>
-      <c r="AE212" s="357"/>
-      <c r="AF212" s="357"/>
-      <c r="AG212" s="357"/>
-      <c r="AH212" s="358"/>
+      <c r="P212" s="323"/>
+      <c r="Q212" s="323"/>
+      <c r="R212" s="323"/>
+      <c r="S212" s="323"/>
+      <c r="T212" s="323"/>
+      <c r="U212" s="323"/>
+      <c r="V212" s="323"/>
+      <c r="W212" s="323"/>
+      <c r="X212" s="323"/>
+      <c r="Y212" s="323"/>
+      <c r="Z212" s="323"/>
+      <c r="AA212" s="323"/>
+      <c r="AB212" s="323"/>
+      <c r="AC212" s="323"/>
+      <c r="AD212" s="323"/>
+      <c r="AE212" s="323"/>
+      <c r="AF212" s="323"/>
+      <c r="AG212" s="323"/>
+      <c r="AH212" s="324"/>
     </row>
     <row r="213" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F213" s="338"/>
-      <c r="G213" s="368"/>
-      <c r="H213" s="368"/>
-      <c r="I213" s="368"/>
-      <c r="J213" s="369"/>
-      <c r="K213" s="293"/>
-      <c r="L213" s="295"/>
-      <c r="M213" s="293"/>
-      <c r="N213" s="295"/>
-      <c r="O213" s="338"/>
-      <c r="P213" s="368"/>
-      <c r="Q213" s="368"/>
-      <c r="R213" s="368"/>
-      <c r="S213" s="368"/>
-      <c r="T213" s="368"/>
-      <c r="U213" s="368"/>
-      <c r="V213" s="368"/>
-      <c r="W213" s="368"/>
-      <c r="X213" s="368"/>
-      <c r="Y213" s="368"/>
-      <c r="Z213" s="368"/>
-      <c r="AA213" s="368"/>
-      <c r="AB213" s="368"/>
-      <c r="AC213" s="368"/>
-      <c r="AD213" s="368"/>
-      <c r="AE213" s="368"/>
-      <c r="AF213" s="368"/>
-      <c r="AG213" s="368"/>
-      <c r="AH213" s="369"/>
+      <c r="F213" s="334"/>
+      <c r="G213" s="335"/>
+      <c r="H213" s="335"/>
+      <c r="I213" s="335"/>
+      <c r="J213" s="336"/>
+      <c r="K213" s="291"/>
+      <c r="L213" s="293"/>
+      <c r="M213" s="291"/>
+      <c r="N213" s="293"/>
+      <c r="O213" s="334"/>
+      <c r="P213" s="335"/>
+      <c r="Q213" s="335"/>
+      <c r="R213" s="335"/>
+      <c r="S213" s="335"/>
+      <c r="T213" s="335"/>
+      <c r="U213" s="335"/>
+      <c r="V213" s="335"/>
+      <c r="W213" s="335"/>
+      <c r="X213" s="335"/>
+      <c r="Y213" s="335"/>
+      <c r="Z213" s="335"/>
+      <c r="AA213" s="335"/>
+      <c r="AB213" s="335"/>
+      <c r="AC213" s="335"/>
+      <c r="AD213" s="335"/>
+      <c r="AE213" s="335"/>
+      <c r="AF213" s="335"/>
+      <c r="AG213" s="335"/>
+      <c r="AH213" s="336"/>
     </row>
     <row r="214" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F214" s="359"/>
-      <c r="G214" s="360"/>
-      <c r="H214" s="360"/>
-      <c r="I214" s="360"/>
-      <c r="J214" s="361"/>
-      <c r="K214" s="296"/>
-      <c r="L214" s="298"/>
-      <c r="M214" s="296"/>
-      <c r="N214" s="298"/>
-      <c r="O214" s="359"/>
-      <c r="P214" s="360"/>
-      <c r="Q214" s="360"/>
-      <c r="R214" s="360"/>
-      <c r="S214" s="360"/>
-      <c r="T214" s="360"/>
-      <c r="U214" s="360"/>
-      <c r="V214" s="360"/>
-      <c r="W214" s="360"/>
-      <c r="X214" s="360"/>
-      <c r="Y214" s="360"/>
-      <c r="Z214" s="360"/>
-      <c r="AA214" s="360"/>
-      <c r="AB214" s="360"/>
-      <c r="AC214" s="360"/>
-      <c r="AD214" s="360"/>
-      <c r="AE214" s="360"/>
-      <c r="AF214" s="360"/>
-      <c r="AG214" s="360"/>
-      <c r="AH214" s="361"/>
+      <c r="F214" s="325"/>
+      <c r="G214" s="326"/>
+      <c r="H214" s="326"/>
+      <c r="I214" s="326"/>
+      <c r="J214" s="327"/>
+      <c r="K214" s="294"/>
+      <c r="L214" s="296"/>
+      <c r="M214" s="294"/>
+      <c r="N214" s="296"/>
+      <c r="O214" s="325"/>
+      <c r="P214" s="326"/>
+      <c r="Q214" s="326"/>
+      <c r="R214" s="326"/>
+      <c r="S214" s="326"/>
+      <c r="T214" s="326"/>
+      <c r="U214" s="326"/>
+      <c r="V214" s="326"/>
+      <c r="W214" s="326"/>
+      <c r="X214" s="326"/>
+      <c r="Y214" s="326"/>
+      <c r="Z214" s="326"/>
+      <c r="AA214" s="326"/>
+      <c r="AB214" s="326"/>
+      <c r="AC214" s="326"/>
+      <c r="AD214" s="326"/>
+      <c r="AE214" s="326"/>
+      <c r="AF214" s="326"/>
+      <c r="AG214" s="326"/>
+      <c r="AH214" s="327"/>
     </row>
     <row r="215" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F215" s="251" t="s">
+      <c r="F215" s="279" t="s">
         <v>265</v>
       </c>
-      <c r="G215" s="252"/>
-      <c r="H215" s="252"/>
-      <c r="I215" s="252"/>
-      <c r="J215" s="253"/>
-      <c r="K215" s="218" t="s">
+      <c r="G215" s="280"/>
+      <c r="H215" s="280"/>
+      <c r="I215" s="280"/>
+      <c r="J215" s="281"/>
+      <c r="K215" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="L215" s="220"/>
-      <c r="M215" s="218" t="s">
+      <c r="L215" s="183"/>
+      <c r="M215" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="N215" s="220"/>
-      <c r="O215" s="370" t="s">
+      <c r="N215" s="183"/>
+      <c r="O215" s="338" t="s">
         <v>37</v>
       </c>
-      <c r="P215" s="344"/>
-      <c r="Q215" s="344"/>
-      <c r="R215" s="344"/>
-      <c r="S215" s="344"/>
-      <c r="T215" s="344"/>
-      <c r="U215" s="344"/>
-      <c r="V215" s="344"/>
-      <c r="W215" s="344"/>
-      <c r="X215" s="344"/>
-      <c r="Y215" s="344"/>
-      <c r="Z215" s="344"/>
-      <c r="AA215" s="344"/>
-      <c r="AB215" s="344"/>
-      <c r="AC215" s="344"/>
-      <c r="AD215" s="344"/>
-      <c r="AE215" s="344"/>
-      <c r="AF215" s="344"/>
-      <c r="AG215" s="344"/>
-      <c r="AH215" s="345"/>
+      <c r="P215" s="339"/>
+      <c r="Q215" s="339"/>
+      <c r="R215" s="339"/>
+      <c r="S215" s="339"/>
+      <c r="T215" s="339"/>
+      <c r="U215" s="339"/>
+      <c r="V215" s="339"/>
+      <c r="W215" s="339"/>
+      <c r="X215" s="339"/>
+      <c r="Y215" s="339"/>
+      <c r="Z215" s="339"/>
+      <c r="AA215" s="339"/>
+      <c r="AB215" s="339"/>
+      <c r="AC215" s="339"/>
+      <c r="AD215" s="339"/>
+      <c r="AE215" s="339"/>
+      <c r="AF215" s="339"/>
+      <c r="AG215" s="339"/>
+      <c r="AH215" s="340"/>
     </row>
     <row r="216" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F216" s="251" t="s">
+      <c r="F216" s="279" t="s">
         <v>139</v>
       </c>
-      <c r="G216" s="252"/>
-      <c r="H216" s="252"/>
-      <c r="I216" s="252"/>
-      <c r="J216" s="253"/>
-      <c r="K216" s="218" t="s">
+      <c r="G216" s="280"/>
+      <c r="H216" s="280"/>
+      <c r="I216" s="280"/>
+      <c r="J216" s="281"/>
+      <c r="K216" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="L216" s="220"/>
-      <c r="M216" s="218" t="s">
+      <c r="L216" s="183"/>
+      <c r="M216" s="181" t="s">
         <v>33</v>
       </c>
-      <c r="N216" s="220"/>
-      <c r="O216" s="334" t="s">
+      <c r="N216" s="183"/>
+      <c r="O216" s="347" t="s">
         <v>497</v>
       </c>
-      <c r="P216" s="344"/>
-      <c r="Q216" s="344"/>
-      <c r="R216" s="344"/>
-      <c r="S216" s="344"/>
-      <c r="T216" s="344"/>
-      <c r="U216" s="344"/>
-      <c r="V216" s="344"/>
-      <c r="W216" s="344"/>
-      <c r="X216" s="344"/>
-      <c r="Y216" s="344"/>
-      <c r="Z216" s="344"/>
-      <c r="AA216" s="344"/>
-      <c r="AB216" s="344"/>
-      <c r="AC216" s="344"/>
-      <c r="AD216" s="344"/>
-      <c r="AE216" s="344"/>
-      <c r="AF216" s="344"/>
-      <c r="AG216" s="344"/>
-      <c r="AH216" s="345"/>
+      <c r="P216" s="339"/>
+      <c r="Q216" s="339"/>
+      <c r="R216" s="339"/>
+      <c r="S216" s="339"/>
+      <c r="T216" s="339"/>
+      <c r="U216" s="339"/>
+      <c r="V216" s="339"/>
+      <c r="W216" s="339"/>
+      <c r="X216" s="339"/>
+      <c r="Y216" s="339"/>
+      <c r="Z216" s="339"/>
+      <c r="AA216" s="339"/>
+      <c r="AB216" s="339"/>
+      <c r="AC216" s="339"/>
+      <c r="AD216" s="339"/>
+      <c r="AE216" s="339"/>
+      <c r="AF216" s="339"/>
+      <c r="AG216" s="339"/>
+      <c r="AH216" s="340"/>
     </row>
     <row r="217" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F217" s="251" t="s">
+      <c r="F217" s="279" t="s">
         <v>42</v>
       </c>
-      <c r="G217" s="252"/>
-      <c r="H217" s="252"/>
-      <c r="I217" s="252"/>
-      <c r="J217" s="253"/>
-      <c r="K217" s="218" t="s">
+      <c r="G217" s="280"/>
+      <c r="H217" s="280"/>
+      <c r="I217" s="280"/>
+      <c r="J217" s="281"/>
+      <c r="K217" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="L217" s="220"/>
-      <c r="M217" s="218" t="s">
+      <c r="L217" s="183"/>
+      <c r="M217" s="181" t="s">
         <v>33</v>
       </c>
-      <c r="N217" s="220"/>
-      <c r="O217" s="334" t="s">
+      <c r="N217" s="183"/>
+      <c r="O217" s="347" t="s">
         <v>492</v>
       </c>
-      <c r="P217" s="344"/>
-      <c r="Q217" s="344"/>
-      <c r="R217" s="344"/>
-      <c r="S217" s="344"/>
-      <c r="T217" s="344"/>
-      <c r="U217" s="344"/>
-      <c r="V217" s="344"/>
-      <c r="W217" s="344"/>
-      <c r="X217" s="344"/>
-      <c r="Y217" s="344"/>
-      <c r="Z217" s="344"/>
-      <c r="AA217" s="344"/>
-      <c r="AB217" s="344"/>
-      <c r="AC217" s="344"/>
-      <c r="AD217" s="344"/>
-      <c r="AE217" s="344"/>
-      <c r="AF217" s="344"/>
-      <c r="AG217" s="344"/>
-      <c r="AH217" s="345"/>
+      <c r="P217" s="339"/>
+      <c r="Q217" s="339"/>
+      <c r="R217" s="339"/>
+      <c r="S217" s="339"/>
+      <c r="T217" s="339"/>
+      <c r="U217" s="339"/>
+      <c r="V217" s="339"/>
+      <c r="W217" s="339"/>
+      <c r="X217" s="339"/>
+      <c r="Y217" s="339"/>
+      <c r="Z217" s="339"/>
+      <c r="AA217" s="339"/>
+      <c r="AB217" s="339"/>
+      <c r="AC217" s="339"/>
+      <c r="AD217" s="339"/>
+      <c r="AE217" s="339"/>
+      <c r="AF217" s="339"/>
+      <c r="AG217" s="339"/>
+      <c r="AH217" s="340"/>
     </row>
     <row r="218" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F218" s="310" t="s">
+      <c r="F218" s="317" t="s">
         <v>270</v>
       </c>
-      <c r="G218" s="357"/>
-      <c r="H218" s="357"/>
-      <c r="I218" s="357"/>
-      <c r="J218" s="358"/>
-      <c r="K218" s="351" t="s">
+      <c r="G218" s="323"/>
+      <c r="H218" s="323"/>
+      <c r="I218" s="323"/>
+      <c r="J218" s="324"/>
+      <c r="K218" s="328" t="s">
         <v>35</v>
       </c>
-      <c r="L218" s="352"/>
-      <c r="M218" s="351" t="s">
+      <c r="L218" s="329"/>
+      <c r="M218" s="328" t="s">
         <v>36</v>
       </c>
-      <c r="N218" s="352"/>
-      <c r="O218" s="351" t="s">
+      <c r="N218" s="329"/>
+      <c r="O218" s="328" t="s">
         <v>43</v>
       </c>
-      <c r="P218" s="362"/>
-      <c r="Q218" s="362"/>
-      <c r="R218" s="362"/>
-      <c r="S218" s="362"/>
-      <c r="T218" s="362"/>
-      <c r="U218" s="362"/>
-      <c r="V218" s="362"/>
-      <c r="W218" s="362"/>
-      <c r="X218" s="362"/>
-      <c r="Y218" s="362"/>
-      <c r="Z218" s="362"/>
-      <c r="AA218" s="362"/>
-      <c r="AB218" s="362"/>
-      <c r="AC218" s="362"/>
-      <c r="AD218" s="362"/>
-      <c r="AE218" s="362"/>
-      <c r="AF218" s="362"/>
-      <c r="AG218" s="362"/>
-      <c r="AH218" s="352"/>
+      <c r="P218" s="330"/>
+      <c r="Q218" s="330"/>
+      <c r="R218" s="330"/>
+      <c r="S218" s="330"/>
+      <c r="T218" s="330"/>
+      <c r="U218" s="330"/>
+      <c r="V218" s="330"/>
+      <c r="W218" s="330"/>
+      <c r="X218" s="330"/>
+      <c r="Y218" s="330"/>
+      <c r="Z218" s="330"/>
+      <c r="AA218" s="330"/>
+      <c r="AB218" s="330"/>
+      <c r="AC218" s="330"/>
+      <c r="AD218" s="330"/>
+      <c r="AE218" s="330"/>
+      <c r="AF218" s="330"/>
+      <c r="AG218" s="330"/>
+      <c r="AH218" s="329"/>
     </row>
     <row r="219" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F219" s="359"/>
-      <c r="G219" s="360"/>
-      <c r="H219" s="360"/>
-      <c r="I219" s="360"/>
-      <c r="J219" s="361"/>
-      <c r="K219" s="359"/>
-      <c r="L219" s="361"/>
-      <c r="M219" s="359"/>
-      <c r="N219" s="361"/>
-      <c r="O219" s="359"/>
-      <c r="P219" s="360"/>
-      <c r="Q219" s="360"/>
-      <c r="R219" s="360"/>
-      <c r="S219" s="360"/>
-      <c r="T219" s="360"/>
-      <c r="U219" s="360"/>
-      <c r="V219" s="360"/>
-      <c r="W219" s="360"/>
-      <c r="X219" s="360"/>
-      <c r="Y219" s="360"/>
-      <c r="Z219" s="360"/>
-      <c r="AA219" s="360"/>
-      <c r="AB219" s="360"/>
-      <c r="AC219" s="360"/>
-      <c r="AD219" s="360"/>
-      <c r="AE219" s="360"/>
-      <c r="AF219" s="360"/>
-      <c r="AG219" s="360"/>
-      <c r="AH219" s="361"/>
+      <c r="F219" s="325"/>
+      <c r="G219" s="326"/>
+      <c r="H219" s="326"/>
+      <c r="I219" s="326"/>
+      <c r="J219" s="327"/>
+      <c r="K219" s="325"/>
+      <c r="L219" s="327"/>
+      <c r="M219" s="325"/>
+      <c r="N219" s="327"/>
+      <c r="O219" s="325"/>
+      <c r="P219" s="326"/>
+      <c r="Q219" s="326"/>
+      <c r="R219" s="326"/>
+      <c r="S219" s="326"/>
+      <c r="T219" s="326"/>
+      <c r="U219" s="326"/>
+      <c r="V219" s="326"/>
+      <c r="W219" s="326"/>
+      <c r="X219" s="326"/>
+      <c r="Y219" s="326"/>
+      <c r="Z219" s="326"/>
+      <c r="AA219" s="326"/>
+      <c r="AB219" s="326"/>
+      <c r="AC219" s="326"/>
+      <c r="AD219" s="326"/>
+      <c r="AE219" s="326"/>
+      <c r="AF219" s="326"/>
+      <c r="AG219" s="326"/>
+      <c r="AH219" s="327"/>
     </row>
     <row r="220" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F220" s="55"/>
@@ -45084,6 +45084,118 @@
     </row>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:N2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AA153:AH153"/>
+    <mergeCell ref="AA151:AH151"/>
+    <mergeCell ref="O176:AH179"/>
+    <mergeCell ref="O180:AH180"/>
+    <mergeCell ref="O174:AH174"/>
+    <mergeCell ref="K174:L174"/>
+    <mergeCell ref="D155:D163"/>
+    <mergeCell ref="D154:J154"/>
+    <mergeCell ref="E155:J161"/>
+    <mergeCell ref="E162:J163"/>
+    <mergeCell ref="D151:J151"/>
+    <mergeCell ref="D152:J152"/>
+    <mergeCell ref="D153:J153"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="K154:Z154"/>
+    <mergeCell ref="K162:Z163"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="M175:N175"/>
+    <mergeCell ref="M176:N179"/>
+    <mergeCell ref="M180:N180"/>
+    <mergeCell ref="M181:N184"/>
+    <mergeCell ref="M185:N186"/>
+    <mergeCell ref="M187:N188"/>
+    <mergeCell ref="M189:N190"/>
+    <mergeCell ref="M191:N191"/>
+    <mergeCell ref="O185:AH186"/>
+    <mergeCell ref="O187:AH188"/>
+    <mergeCell ref="O189:AH190"/>
+    <mergeCell ref="O191:AH191"/>
+    <mergeCell ref="O175:AH175"/>
+    <mergeCell ref="O216:AH216"/>
+    <mergeCell ref="O217:AH217"/>
+    <mergeCell ref="M174:N174"/>
+    <mergeCell ref="K161:Z161"/>
+    <mergeCell ref="F217:J217"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AA155:AH155"/>
+    <mergeCell ref="K151:Z151"/>
+    <mergeCell ref="K152:Z152"/>
+    <mergeCell ref="K153:Z153"/>
+    <mergeCell ref="K155:Z155"/>
+    <mergeCell ref="K156:Z160"/>
+    <mergeCell ref="AA156:AH160"/>
+    <mergeCell ref="AA162:AH163"/>
+    <mergeCell ref="AA161:AH161"/>
+    <mergeCell ref="AA152:AH152"/>
+    <mergeCell ref="AA154:AH154"/>
+    <mergeCell ref="K217:L217"/>
+    <mergeCell ref="K204:L205"/>
+    <mergeCell ref="K206:L207"/>
+    <mergeCell ref="K211:L211"/>
+    <mergeCell ref="K210:L210"/>
+    <mergeCell ref="K202:L203"/>
+    <mergeCell ref="K212:L214"/>
+    <mergeCell ref="K216:L216"/>
+    <mergeCell ref="M216:N216"/>
+    <mergeCell ref="K208:L209"/>
+    <mergeCell ref="M206:N207"/>
+    <mergeCell ref="M211:N211"/>
+    <mergeCell ref="M210:N210"/>
+    <mergeCell ref="M202:N203"/>
+    <mergeCell ref="M212:N214"/>
+    <mergeCell ref="M204:N205"/>
+    <mergeCell ref="O210:AH210"/>
+    <mergeCell ref="O211:AH211"/>
+    <mergeCell ref="K181:L184"/>
+    <mergeCell ref="K176:L179"/>
+    <mergeCell ref="F185:J186"/>
+    <mergeCell ref="F187:J188"/>
+    <mergeCell ref="K187:L188"/>
+    <mergeCell ref="K189:L190"/>
+    <mergeCell ref="M201:N201"/>
+    <mergeCell ref="F202:J203"/>
+    <mergeCell ref="F204:J205"/>
+    <mergeCell ref="F206:J207"/>
+    <mergeCell ref="O181:AH184"/>
+    <mergeCell ref="O195:AH196"/>
+    <mergeCell ref="K194:L194"/>
+    <mergeCell ref="K201:L201"/>
+    <mergeCell ref="M192:N193"/>
+    <mergeCell ref="M194:N194"/>
+    <mergeCell ref="M195:N196"/>
+    <mergeCell ref="K185:L186"/>
+    <mergeCell ref="K180:L180"/>
+    <mergeCell ref="K192:L193"/>
+    <mergeCell ref="F174:J174"/>
+    <mergeCell ref="F175:J175"/>
+    <mergeCell ref="F176:J179"/>
+    <mergeCell ref="F180:J180"/>
+    <mergeCell ref="F181:J184"/>
+    <mergeCell ref="K195:L196"/>
+    <mergeCell ref="K191:L191"/>
+    <mergeCell ref="F191:J191"/>
+    <mergeCell ref="F194:J194"/>
+    <mergeCell ref="F189:J190"/>
+    <mergeCell ref="F192:J193"/>
+    <mergeCell ref="F195:J196"/>
+    <mergeCell ref="K175:L175"/>
     <mergeCell ref="F218:J219"/>
     <mergeCell ref="K218:L219"/>
     <mergeCell ref="M218:N219"/>
@@ -45108,118 +45220,6 @@
     <mergeCell ref="F215:J215"/>
     <mergeCell ref="F208:J209"/>
     <mergeCell ref="F212:J214"/>
-    <mergeCell ref="F174:J174"/>
-    <mergeCell ref="F175:J175"/>
-    <mergeCell ref="F176:J179"/>
-    <mergeCell ref="F180:J180"/>
-    <mergeCell ref="F181:J184"/>
-    <mergeCell ref="K195:L196"/>
-    <mergeCell ref="K191:L191"/>
-    <mergeCell ref="F191:J191"/>
-    <mergeCell ref="F194:J194"/>
-    <mergeCell ref="F189:J190"/>
-    <mergeCell ref="F192:J193"/>
-    <mergeCell ref="F195:J196"/>
-    <mergeCell ref="K175:L175"/>
-    <mergeCell ref="O210:AH210"/>
-    <mergeCell ref="O211:AH211"/>
-    <mergeCell ref="K181:L184"/>
-    <mergeCell ref="K176:L179"/>
-    <mergeCell ref="F185:J186"/>
-    <mergeCell ref="F187:J188"/>
-    <mergeCell ref="K187:L188"/>
-    <mergeCell ref="K189:L190"/>
-    <mergeCell ref="M201:N201"/>
-    <mergeCell ref="F202:J203"/>
-    <mergeCell ref="F204:J205"/>
-    <mergeCell ref="F206:J207"/>
-    <mergeCell ref="O181:AH184"/>
-    <mergeCell ref="O195:AH196"/>
-    <mergeCell ref="K194:L194"/>
-    <mergeCell ref="K201:L201"/>
-    <mergeCell ref="M192:N193"/>
-    <mergeCell ref="M194:N194"/>
-    <mergeCell ref="M195:N196"/>
-    <mergeCell ref="K185:L186"/>
-    <mergeCell ref="K180:L180"/>
-    <mergeCell ref="K192:L193"/>
-    <mergeCell ref="K217:L217"/>
-    <mergeCell ref="K204:L205"/>
-    <mergeCell ref="K206:L207"/>
-    <mergeCell ref="K211:L211"/>
-    <mergeCell ref="K210:L210"/>
-    <mergeCell ref="K202:L203"/>
-    <mergeCell ref="K212:L214"/>
-    <mergeCell ref="K216:L216"/>
-    <mergeCell ref="M216:N216"/>
-    <mergeCell ref="K208:L209"/>
-    <mergeCell ref="M206:N207"/>
-    <mergeCell ref="M211:N211"/>
-    <mergeCell ref="M210:N210"/>
-    <mergeCell ref="M202:N203"/>
-    <mergeCell ref="M212:N214"/>
-    <mergeCell ref="M204:N205"/>
-    <mergeCell ref="O216:AH216"/>
-    <mergeCell ref="O217:AH217"/>
-    <mergeCell ref="M174:N174"/>
-    <mergeCell ref="K161:Z161"/>
-    <mergeCell ref="F217:J217"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AA155:AH155"/>
-    <mergeCell ref="K151:Z151"/>
-    <mergeCell ref="K152:Z152"/>
-    <mergeCell ref="K153:Z153"/>
-    <mergeCell ref="K155:Z155"/>
-    <mergeCell ref="K156:Z160"/>
-    <mergeCell ref="AA156:AH160"/>
-    <mergeCell ref="AA162:AH163"/>
-    <mergeCell ref="AA161:AH161"/>
-    <mergeCell ref="AA152:AH152"/>
-    <mergeCell ref="AA154:AH154"/>
-    <mergeCell ref="M175:N175"/>
-    <mergeCell ref="M176:N179"/>
-    <mergeCell ref="M180:N180"/>
-    <mergeCell ref="M181:N184"/>
-    <mergeCell ref="M185:N186"/>
-    <mergeCell ref="M187:N188"/>
-    <mergeCell ref="M189:N190"/>
-    <mergeCell ref="M191:N191"/>
-    <mergeCell ref="O185:AH186"/>
-    <mergeCell ref="O187:AH188"/>
-    <mergeCell ref="O189:AH190"/>
-    <mergeCell ref="O191:AH191"/>
-    <mergeCell ref="O175:AH175"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:N2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AA153:AH153"/>
-    <mergeCell ref="AA151:AH151"/>
-    <mergeCell ref="O176:AH179"/>
-    <mergeCell ref="O180:AH180"/>
-    <mergeCell ref="O174:AH174"/>
-    <mergeCell ref="K174:L174"/>
-    <mergeCell ref="D155:D163"/>
-    <mergeCell ref="D154:J154"/>
-    <mergeCell ref="E155:J161"/>
-    <mergeCell ref="E162:J163"/>
-    <mergeCell ref="D151:J151"/>
-    <mergeCell ref="D152:J152"/>
-    <mergeCell ref="D153:J153"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="K154:Z154"/>
-    <mergeCell ref="K162:Z163"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="S1:Z3"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>

--- a/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
+++ b/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83854C20-3F73-4EE6-BF4D-4AA6D5A0E79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC89E0E-4170-4F2C-B00E-ADC5B38EEB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2220" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="3045" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="28" r:id="rId1"/>
@@ -8831,90 +8831,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="31" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -9030,14 +8948,86 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -9048,6 +9038,15 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9056,6 +9055,33 @@
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9138,32 +9164,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9213,15 +9221,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -9234,12 +9233,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -9247,18 +9240,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -9279,59 +9260,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9339,41 +9299,56 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9390,42 +9365,67 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="パーセント 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -27487,12 +27487,12 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="174">
+      <c r="I25" s="173">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>45565</v>
-      </c>
-      <c r="J25" s="174"/>
-      <c r="K25" s="174"/>
+        <v>43336</v>
+      </c>
+      <c r="J25" s="173"/>
+      <c r="K25" s="173"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="3"/>
@@ -28085,55 +28085,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="217" t="s">
+      <c r="A1" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="213"/>
-      <c r="O1" s="218" t="s">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="219"/>
-      <c r="Q1" s="219"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="227" t="s">
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="199" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
-      <c r="W1" s="228"/>
-      <c r="X1" s="228"/>
-      <c r="Y1" s="228"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="208" t="s">
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="201"/>
+      <c r="AA1" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="210"/>
-      <c r="AC1" s="236" t="str">
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="208" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="237"/>
-      <c r="AE1" s="237"/>
-      <c r="AF1" s="238"/>
-      <c r="AG1" s="202">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="174">
         <f>IF(D8="","",D8)</f>
-        <v>45565</v>
-      </c>
-      <c r="AH1" s="203"/>
-      <c r="AI1" s="204"/>
+        <v>43336</v>
+      </c>
+      <c r="AH1" s="175"/>
+      <c r="AI1" s="176"/>
       <c r="AJ1" s="7"/>
       <c r="AK1" s="7"/>
       <c r="AL1" s="7"/>
@@ -28141,51 +28141,51 @@
       <c r="AN1" s="8"/>
     </row>
     <row r="2" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="209"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
-      <c r="M2" s="212"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="221"/>
-      <c r="P2" s="222"/>
-      <c r="Q2" s="222"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="231"/>
-      <c r="U2" s="231"/>
-      <c r="V2" s="231"/>
-      <c r="W2" s="231"/>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="231"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="208" t="s">
+      <c r="B2" s="181"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="184"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="185"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="203"/>
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="180" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="210"/>
-      <c r="AC2" s="214" t="str">
+      <c r="AB2" s="182"/>
+      <c r="AC2" s="186" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="215"/>
-      <c r="AE2" s="215"/>
-      <c r="AF2" s="216"/>
-      <c r="AG2" s="202" t="str">
+      <c r="AD2" s="187"/>
+      <c r="AE2" s="187"/>
+      <c r="AF2" s="188"/>
+      <c r="AG2" s="174" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="203"/>
-      <c r="AI2" s="204"/>
+      <c r="AH2" s="175"/>
+      <c r="AI2" s="176"/>
       <c r="AJ2" s="7"/>
       <c r="AK2" s="7"/>
       <c r="AL2" s="7"/>
@@ -28193,43 +28193,43 @@
       <c r="AN2" s="7"/>
     </row>
     <row r="3" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="209"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="239"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="213"/>
-      <c r="O3" s="224"/>
-      <c r="P3" s="225"/>
-      <c r="Q3" s="225"/>
-      <c r="R3" s="226"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="234"/>
-      <c r="U3" s="234"/>
-      <c r="V3" s="234"/>
-      <c r="W3" s="234"/>
-      <c r="X3" s="234"/>
-      <c r="Y3" s="234"/>
-      <c r="Z3" s="235"/>
-      <c r="AA3" s="208"/>
-      <c r="AB3" s="210"/>
-      <c r="AC3" s="236"/>
-      <c r="AD3" s="237"/>
-      <c r="AE3" s="237"/>
-      <c r="AF3" s="238"/>
-      <c r="AG3" s="202"/>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="204"/>
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+      <c r="M3" s="184"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="197"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="198"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="206"/>
+      <c r="U3" s="206"/>
+      <c r="V3" s="206"/>
+      <c r="W3" s="206"/>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="207"/>
+      <c r="AA3" s="180"/>
+      <c r="AB3" s="182"/>
+      <c r="AC3" s="208"/>
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="174"/>
+      <c r="AH3" s="175"/>
+      <c r="AI3" s="176"/>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
       <c r="AL3" s="7"/>
@@ -28266,1034 +28266,1190 @@
       <c r="A7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="205" t="s">
+      <c r="B7" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="206"/>
-      <c r="D7" s="205" t="s">
+      <c r="C7" s="178"/>
+      <c r="D7" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="207"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="205" t="s">
+      <c r="E7" s="179"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="177" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="207"/>
-      <c r="I7" s="206"/>
-      <c r="J7" s="205" t="s">
+      <c r="H7" s="179"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="207"/>
-      <c r="L7" s="207"/>
-      <c r="M7" s="207"/>
-      <c r="N7" s="207"/>
-      <c r="O7" s="207"/>
-      <c r="P7" s="206"/>
-      <c r="Q7" s="205" t="s">
+      <c r="K7" s="179"/>
+      <c r="L7" s="179"/>
+      <c r="M7" s="179"/>
+      <c r="N7" s="179"/>
+      <c r="O7" s="179"/>
+      <c r="P7" s="178"/>
+      <c r="Q7" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="R7" s="207"/>
-      <c r="S7" s="207"/>
-      <c r="T7" s="207"/>
-      <c r="U7" s="207"/>
-      <c r="V7" s="207"/>
-      <c r="W7" s="207"/>
-      <c r="X7" s="207"/>
-      <c r="Y7" s="207"/>
-      <c r="Z7" s="207"/>
-      <c r="AA7" s="207"/>
-      <c r="AB7" s="207"/>
-      <c r="AC7" s="207"/>
-      <c r="AD7" s="207"/>
-      <c r="AE7" s="206"/>
-      <c r="AF7" s="205" t="s">
+      <c r="R7" s="179"/>
+      <c r="S7" s="179"/>
+      <c r="T7" s="179"/>
+      <c r="U7" s="179"/>
+      <c r="V7" s="179"/>
+      <c r="W7" s="179"/>
+      <c r="X7" s="179"/>
+      <c r="Y7" s="179"/>
+      <c r="Z7" s="179"/>
+      <c r="AA7" s="179"/>
+      <c r="AB7" s="179"/>
+      <c r="AC7" s="179"/>
+      <c r="AD7" s="179"/>
+      <c r="AE7" s="178"/>
+      <c r="AF7" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="207"/>
-      <c r="AH7" s="207"/>
-      <c r="AI7" s="206"/>
+      <c r="AG7" s="179"/>
+      <c r="AH7" s="179"/>
+      <c r="AI7" s="178"/>
     </row>
     <row r="8" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="90">
         <v>1</v>
       </c>
-      <c r="B8" s="188" t="s">
+      <c r="B8" s="224" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="189"/>
-      <c r="D8" s="190">
-        <v>45565</v>
-      </c>
-      <c r="E8" s="191"/>
-      <c r="F8" s="192"/>
-      <c r="G8" s="193" t="s">
+      <c r="C8" s="225"/>
+      <c r="D8" s="226">
+        <v>43336</v>
+      </c>
+      <c r="E8" s="227"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="229" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="194"/>
-      <c r="I8" s="195"/>
-      <c r="J8" s="196" t="s">
+      <c r="H8" s="230"/>
+      <c r="I8" s="231"/>
+      <c r="J8" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="197"/>
-      <c r="L8" s="197"/>
-      <c r="M8" s="197"/>
-      <c r="N8" s="197"/>
-      <c r="O8" s="197"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="199" t="s">
+      <c r="K8" s="233"/>
+      <c r="L8" s="233"/>
+      <c r="M8" s="233"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="233"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="235" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="200"/>
-      <c r="S8" s="200"/>
-      <c r="T8" s="200"/>
-      <c r="U8" s="200"/>
-      <c r="V8" s="200"/>
-      <c r="W8" s="200"/>
-      <c r="X8" s="200"/>
-      <c r="Y8" s="200"/>
-      <c r="Z8" s="200"/>
-      <c r="AA8" s="200"/>
-      <c r="AB8" s="200"/>
-      <c r="AC8" s="200"/>
-      <c r="AD8" s="200"/>
-      <c r="AE8" s="201"/>
-      <c r="AF8" s="196" t="s">
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="236"/>
+      <c r="U8" s="236"/>
+      <c r="V8" s="236"/>
+      <c r="W8" s="236"/>
+      <c r="X8" s="236"/>
+      <c r="Y8" s="236"/>
+      <c r="Z8" s="236"/>
+      <c r="AA8" s="236"/>
+      <c r="AB8" s="236"/>
+      <c r="AC8" s="236"/>
+      <c r="AD8" s="236"/>
+      <c r="AE8" s="237"/>
+      <c r="AF8" s="232" t="s">
         <v>23</v>
       </c>
-      <c r="AG8" s="197"/>
-      <c r="AH8" s="197"/>
-      <c r="AI8" s="198"/>
+      <c r="AG8" s="233"/>
+      <c r="AH8" s="233"/>
+      <c r="AI8" s="234"/>
     </row>
     <row r="9" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="89"/>
-      <c r="B9" s="175"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="177"/>
-      <c r="E9" s="178"/>
-      <c r="F9" s="179"/>
-      <c r="G9" s="177"/>
-      <c r="H9" s="180"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="181"/>
-      <c r="K9" s="182"/>
-      <c r="L9" s="182"/>
-      <c r="M9" s="182"/>
-      <c r="N9" s="182"/>
-      <c r="O9" s="182"/>
-      <c r="P9" s="183"/>
-      <c r="Q9" s="184"/>
-      <c r="R9" s="185"/>
-      <c r="S9" s="185"/>
-      <c r="T9" s="185"/>
-      <c r="U9" s="185"/>
-      <c r="V9" s="185"/>
-      <c r="W9" s="185"/>
-      <c r="X9" s="185"/>
-      <c r="Y9" s="185"/>
-      <c r="Z9" s="185"/>
-      <c r="AA9" s="185"/>
-      <c r="AB9" s="185"/>
-      <c r="AC9" s="185"/>
-      <c r="AD9" s="185"/>
-      <c r="AE9" s="186"/>
-      <c r="AF9" s="181"/>
-      <c r="AG9" s="182"/>
-      <c r="AH9" s="182"/>
-      <c r="AI9" s="183"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="213"/>
+      <c r="D9" s="214"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="214"/>
+      <c r="H9" s="217"/>
+      <c r="I9" s="213"/>
+      <c r="J9" s="218"/>
+      <c r="K9" s="219"/>
+      <c r="L9" s="219"/>
+      <c r="M9" s="219"/>
+      <c r="N9" s="219"/>
+      <c r="O9" s="219"/>
+      <c r="P9" s="220"/>
+      <c r="Q9" s="221"/>
+      <c r="R9" s="222"/>
+      <c r="S9" s="222"/>
+      <c r="T9" s="222"/>
+      <c r="U9" s="222"/>
+      <c r="V9" s="222"/>
+      <c r="W9" s="222"/>
+      <c r="X9" s="222"/>
+      <c r="Y9" s="222"/>
+      <c r="Z9" s="222"/>
+      <c r="AA9" s="222"/>
+      <c r="AB9" s="222"/>
+      <c r="AC9" s="222"/>
+      <c r="AD9" s="222"/>
+      <c r="AE9" s="223"/>
+      <c r="AF9" s="218"/>
+      <c r="AG9" s="219"/>
+      <c r="AH9" s="219"/>
+      <c r="AI9" s="220"/>
     </row>
     <row r="10" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="89"/>
-      <c r="B10" s="175"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="180"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="182"/>
-      <c r="L10" s="182"/>
-      <c r="M10" s="182"/>
-      <c r="N10" s="182"/>
-      <c r="O10" s="182"/>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="184"/>
-      <c r="R10" s="185"/>
-      <c r="S10" s="185"/>
-      <c r="T10" s="185"/>
-      <c r="U10" s="185"/>
-      <c r="V10" s="185"/>
-      <c r="W10" s="185"/>
-      <c r="X10" s="185"/>
-      <c r="Y10" s="185"/>
-      <c r="Z10" s="185"/>
-      <c r="AA10" s="185"/>
-      <c r="AB10" s="185"/>
-      <c r="AC10" s="185"/>
-      <c r="AD10" s="185"/>
-      <c r="AE10" s="186"/>
-      <c r="AF10" s="181"/>
-      <c r="AG10" s="182"/>
-      <c r="AH10" s="182"/>
-      <c r="AI10" s="183"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="213"/>
+      <c r="D10" s="214"/>
+      <c r="E10" s="215"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="212"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="213"/>
+      <c r="J10" s="218"/>
+      <c r="K10" s="219"/>
+      <c r="L10" s="219"/>
+      <c r="M10" s="219"/>
+      <c r="N10" s="219"/>
+      <c r="O10" s="219"/>
+      <c r="P10" s="220"/>
+      <c r="Q10" s="221"/>
+      <c r="R10" s="222"/>
+      <c r="S10" s="222"/>
+      <c r="T10" s="222"/>
+      <c r="U10" s="222"/>
+      <c r="V10" s="222"/>
+      <c r="W10" s="222"/>
+      <c r="X10" s="222"/>
+      <c r="Y10" s="222"/>
+      <c r="Z10" s="222"/>
+      <c r="AA10" s="222"/>
+      <c r="AB10" s="222"/>
+      <c r="AC10" s="222"/>
+      <c r="AD10" s="222"/>
+      <c r="AE10" s="223"/>
+      <c r="AF10" s="218"/>
+      <c r="AG10" s="219"/>
+      <c r="AH10" s="219"/>
+      <c r="AI10" s="220"/>
     </row>
     <row r="11" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="89"/>
-      <c r="B11" s="175"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="177"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="179"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="180"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
-      <c r="L11" s="182"/>
-      <c r="M11" s="182"/>
-      <c r="N11" s="182"/>
-      <c r="O11" s="182"/>
-      <c r="P11" s="183"/>
-      <c r="Q11" s="184"/>
-      <c r="R11" s="185"/>
-      <c r="S11" s="185"/>
-      <c r="T11" s="185"/>
-      <c r="U11" s="185"/>
-      <c r="V11" s="185"/>
-      <c r="W11" s="185"/>
-      <c r="X11" s="185"/>
-      <c r="Y11" s="185"/>
-      <c r="Z11" s="185"/>
-      <c r="AA11" s="185"/>
-      <c r="AB11" s="185"/>
-      <c r="AC11" s="185"/>
-      <c r="AD11" s="185"/>
-      <c r="AE11" s="186"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="182"/>
-      <c r="AH11" s="182"/>
-      <c r="AI11" s="183"/>
+      <c r="B11" s="212"/>
+      <c r="C11" s="213"/>
+      <c r="D11" s="214"/>
+      <c r="E11" s="215"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="212"/>
+      <c r="H11" s="217"/>
+      <c r="I11" s="213"/>
+      <c r="J11" s="218"/>
+      <c r="K11" s="219"/>
+      <c r="L11" s="219"/>
+      <c r="M11" s="219"/>
+      <c r="N11" s="219"/>
+      <c r="O11" s="219"/>
+      <c r="P11" s="220"/>
+      <c r="Q11" s="221"/>
+      <c r="R11" s="222"/>
+      <c r="S11" s="222"/>
+      <c r="T11" s="222"/>
+      <c r="U11" s="222"/>
+      <c r="V11" s="222"/>
+      <c r="W11" s="222"/>
+      <c r="X11" s="222"/>
+      <c r="Y11" s="222"/>
+      <c r="Z11" s="222"/>
+      <c r="AA11" s="222"/>
+      <c r="AB11" s="222"/>
+      <c r="AC11" s="222"/>
+      <c r="AD11" s="222"/>
+      <c r="AE11" s="223"/>
+      <c r="AF11" s="218"/>
+      <c r="AG11" s="219"/>
+      <c r="AH11" s="219"/>
+      <c r="AI11" s="220"/>
     </row>
     <row r="12" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="89"/>
-      <c r="B12" s="175"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="177"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="180"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="182"/>
-      <c r="L12" s="182"/>
-      <c r="M12" s="182"/>
-      <c r="N12" s="182"/>
-      <c r="O12" s="182"/>
-      <c r="P12" s="183"/>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185"/>
-      <c r="S12" s="185"/>
-      <c r="T12" s="185"/>
-      <c r="U12" s="185"/>
-      <c r="V12" s="185"/>
-      <c r="W12" s="185"/>
-      <c r="X12" s="185"/>
-      <c r="Y12" s="185"/>
-      <c r="Z12" s="185"/>
-      <c r="AA12" s="185"/>
-      <c r="AB12" s="185"/>
-      <c r="AC12" s="185"/>
-      <c r="AD12" s="185"/>
-      <c r="AE12" s="186"/>
-      <c r="AF12" s="181"/>
-      <c r="AG12" s="182"/>
-      <c r="AH12" s="182"/>
-      <c r="AI12" s="183"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="213"/>
+      <c r="D12" s="214"/>
+      <c r="E12" s="215"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="217"/>
+      <c r="I12" s="213"/>
+      <c r="J12" s="218"/>
+      <c r="K12" s="219"/>
+      <c r="L12" s="219"/>
+      <c r="M12" s="219"/>
+      <c r="N12" s="219"/>
+      <c r="O12" s="219"/>
+      <c r="P12" s="220"/>
+      <c r="Q12" s="221"/>
+      <c r="R12" s="222"/>
+      <c r="S12" s="222"/>
+      <c r="T12" s="222"/>
+      <c r="U12" s="222"/>
+      <c r="V12" s="222"/>
+      <c r="W12" s="222"/>
+      <c r="X12" s="222"/>
+      <c r="Y12" s="222"/>
+      <c r="Z12" s="222"/>
+      <c r="AA12" s="222"/>
+      <c r="AB12" s="222"/>
+      <c r="AC12" s="222"/>
+      <c r="AD12" s="222"/>
+      <c r="AE12" s="223"/>
+      <c r="AF12" s="218"/>
+      <c r="AG12" s="219"/>
+      <c r="AH12" s="219"/>
+      <c r="AI12" s="220"/>
     </row>
     <row r="13" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="89"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="180"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="182"/>
-      <c r="L13" s="182"/>
-      <c r="M13" s="182"/>
-      <c r="N13" s="182"/>
-      <c r="O13" s="182"/>
-      <c r="P13" s="183"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
-      <c r="S13" s="185"/>
-      <c r="T13" s="185"/>
-      <c r="U13" s="185"/>
-      <c r="V13" s="185"/>
-      <c r="W13" s="185"/>
-      <c r="X13" s="185"/>
-      <c r="Y13" s="185"/>
-      <c r="Z13" s="185"/>
-      <c r="AA13" s="185"/>
-      <c r="AB13" s="185"/>
-      <c r="AC13" s="185"/>
-      <c r="AD13" s="185"/>
-      <c r="AE13" s="186"/>
-      <c r="AF13" s="181"/>
-      <c r="AG13" s="182"/>
-      <c r="AH13" s="182"/>
-      <c r="AI13" s="183"/>
+      <c r="B13" s="212"/>
+      <c r="C13" s="213"/>
+      <c r="D13" s="214"/>
+      <c r="E13" s="215"/>
+      <c r="F13" s="216"/>
+      <c r="G13" s="212"/>
+      <c r="H13" s="217"/>
+      <c r="I13" s="213"/>
+      <c r="J13" s="218"/>
+      <c r="K13" s="219"/>
+      <c r="L13" s="219"/>
+      <c r="M13" s="219"/>
+      <c r="N13" s="219"/>
+      <c r="O13" s="219"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="221"/>
+      <c r="R13" s="222"/>
+      <c r="S13" s="222"/>
+      <c r="T13" s="222"/>
+      <c r="U13" s="222"/>
+      <c r="V13" s="222"/>
+      <c r="W13" s="222"/>
+      <c r="X13" s="222"/>
+      <c r="Y13" s="222"/>
+      <c r="Z13" s="222"/>
+      <c r="AA13" s="222"/>
+      <c r="AB13" s="222"/>
+      <c r="AC13" s="222"/>
+      <c r="AD13" s="222"/>
+      <c r="AE13" s="223"/>
+      <c r="AF13" s="218"/>
+      <c r="AG13" s="219"/>
+      <c r="AH13" s="219"/>
+      <c r="AI13" s="220"/>
     </row>
     <row r="14" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="89"/>
-      <c r="B14" s="175"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="179"/>
-      <c r="G14" s="175"/>
-      <c r="H14" s="180"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="181"/>
-      <c r="K14" s="182"/>
-      <c r="L14" s="182"/>
-      <c r="M14" s="182"/>
-      <c r="N14" s="182"/>
-      <c r="O14" s="182"/>
-      <c r="P14" s="183"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
-      <c r="S14" s="185"/>
-      <c r="T14" s="185"/>
-      <c r="U14" s="185"/>
-      <c r="V14" s="185"/>
-      <c r="W14" s="185"/>
-      <c r="X14" s="185"/>
-      <c r="Y14" s="185"/>
-      <c r="Z14" s="185"/>
-      <c r="AA14" s="185"/>
-      <c r="AB14" s="185"/>
-      <c r="AC14" s="185"/>
-      <c r="AD14" s="185"/>
-      <c r="AE14" s="186"/>
-      <c r="AF14" s="181"/>
-      <c r="AG14" s="182"/>
-      <c r="AH14" s="182"/>
-      <c r="AI14" s="183"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="213"/>
+      <c r="D14" s="214"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="216"/>
+      <c r="G14" s="212"/>
+      <c r="H14" s="217"/>
+      <c r="I14" s="213"/>
+      <c r="J14" s="218"/>
+      <c r="K14" s="219"/>
+      <c r="L14" s="219"/>
+      <c r="M14" s="219"/>
+      <c r="N14" s="219"/>
+      <c r="O14" s="219"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="221"/>
+      <c r="R14" s="222"/>
+      <c r="S14" s="222"/>
+      <c r="T14" s="222"/>
+      <c r="U14" s="222"/>
+      <c r="V14" s="222"/>
+      <c r="W14" s="222"/>
+      <c r="X14" s="222"/>
+      <c r="Y14" s="222"/>
+      <c r="Z14" s="222"/>
+      <c r="AA14" s="222"/>
+      <c r="AB14" s="222"/>
+      <c r="AC14" s="222"/>
+      <c r="AD14" s="222"/>
+      <c r="AE14" s="223"/>
+      <c r="AF14" s="218"/>
+      <c r="AG14" s="219"/>
+      <c r="AH14" s="219"/>
+      <c r="AI14" s="220"/>
     </row>
     <row r="15" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="89"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="177"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="179"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="180"/>
-      <c r="I15" s="176"/>
-      <c r="J15" s="181"/>
-      <c r="K15" s="182"/>
-      <c r="L15" s="182"/>
-      <c r="M15" s="182"/>
-      <c r="N15" s="182"/>
-      <c r="O15" s="182"/>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="184"/>
-      <c r="R15" s="185"/>
-      <c r="S15" s="185"/>
-      <c r="T15" s="185"/>
-      <c r="U15" s="185"/>
-      <c r="V15" s="185"/>
-      <c r="W15" s="185"/>
-      <c r="X15" s="185"/>
-      <c r="Y15" s="185"/>
-      <c r="Z15" s="185"/>
-      <c r="AA15" s="185"/>
-      <c r="AB15" s="185"/>
-      <c r="AC15" s="185"/>
-      <c r="AD15" s="185"/>
-      <c r="AE15" s="186"/>
-      <c r="AF15" s="181"/>
-      <c r="AG15" s="182"/>
-      <c r="AH15" s="182"/>
-      <c r="AI15" s="183"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="213"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="216"/>
+      <c r="G15" s="212"/>
+      <c r="H15" s="217"/>
+      <c r="I15" s="213"/>
+      <c r="J15" s="218"/>
+      <c r="K15" s="219"/>
+      <c r="L15" s="219"/>
+      <c r="M15" s="219"/>
+      <c r="N15" s="219"/>
+      <c r="O15" s="219"/>
+      <c r="P15" s="220"/>
+      <c r="Q15" s="221"/>
+      <c r="R15" s="222"/>
+      <c r="S15" s="222"/>
+      <c r="T15" s="222"/>
+      <c r="U15" s="222"/>
+      <c r="V15" s="222"/>
+      <c r="W15" s="222"/>
+      <c r="X15" s="222"/>
+      <c r="Y15" s="222"/>
+      <c r="Z15" s="222"/>
+      <c r="AA15" s="222"/>
+      <c r="AB15" s="222"/>
+      <c r="AC15" s="222"/>
+      <c r="AD15" s="222"/>
+      <c r="AE15" s="223"/>
+      <c r="AF15" s="218"/>
+      <c r="AG15" s="219"/>
+      <c r="AH15" s="219"/>
+      <c r="AI15" s="220"/>
     </row>
     <row r="16" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="89"/>
-      <c r="B16" s="175"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="180"/>
-      <c r="I16" s="176"/>
-      <c r="J16" s="181"/>
-      <c r="K16" s="182"/>
-      <c r="L16" s="182"/>
-      <c r="M16" s="182"/>
-      <c r="N16" s="182"/>
-      <c r="O16" s="182"/>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="184"/>
-      <c r="R16" s="185"/>
-      <c r="S16" s="185"/>
-      <c r="T16" s="185"/>
-      <c r="U16" s="185"/>
-      <c r="V16" s="185"/>
-      <c r="W16" s="185"/>
-      <c r="X16" s="185"/>
-      <c r="Y16" s="185"/>
-      <c r="Z16" s="185"/>
-      <c r="AA16" s="185"/>
-      <c r="AB16" s="185"/>
-      <c r="AC16" s="185"/>
-      <c r="AD16" s="185"/>
-      <c r="AE16" s="186"/>
-      <c r="AF16" s="181"/>
-      <c r="AG16" s="182"/>
-      <c r="AH16" s="182"/>
-      <c r="AI16" s="183"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="213"/>
+      <c r="D16" s="214"/>
+      <c r="E16" s="215"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="217"/>
+      <c r="I16" s="213"/>
+      <c r="J16" s="218"/>
+      <c r="K16" s="219"/>
+      <c r="L16" s="219"/>
+      <c r="M16" s="219"/>
+      <c r="N16" s="219"/>
+      <c r="O16" s="219"/>
+      <c r="P16" s="220"/>
+      <c r="Q16" s="221"/>
+      <c r="R16" s="222"/>
+      <c r="S16" s="222"/>
+      <c r="T16" s="222"/>
+      <c r="U16" s="222"/>
+      <c r="V16" s="222"/>
+      <c r="W16" s="222"/>
+      <c r="X16" s="222"/>
+      <c r="Y16" s="222"/>
+      <c r="Z16" s="222"/>
+      <c r="AA16" s="222"/>
+      <c r="AB16" s="222"/>
+      <c r="AC16" s="222"/>
+      <c r="AD16" s="222"/>
+      <c r="AE16" s="223"/>
+      <c r="AF16" s="218"/>
+      <c r="AG16" s="219"/>
+      <c r="AH16" s="219"/>
+      <c r="AI16" s="220"/>
     </row>
     <row r="17" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="89"/>
-      <c r="B17" s="175"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="175"/>
-      <c r="H17" s="180"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="181"/>
-      <c r="K17" s="182"/>
-      <c r="L17" s="182"/>
-      <c r="M17" s="182"/>
-      <c r="N17" s="182"/>
-      <c r="O17" s="182"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="184"/>
-      <c r="R17" s="185"/>
-      <c r="S17" s="185"/>
-      <c r="T17" s="185"/>
-      <c r="U17" s="185"/>
-      <c r="V17" s="185"/>
-      <c r="W17" s="185"/>
-      <c r="X17" s="185"/>
-      <c r="Y17" s="185"/>
-      <c r="Z17" s="185"/>
-      <c r="AA17" s="185"/>
-      <c r="AB17" s="185"/>
-      <c r="AC17" s="185"/>
-      <c r="AD17" s="185"/>
-      <c r="AE17" s="186"/>
-      <c r="AF17" s="181"/>
-      <c r="AG17" s="182"/>
-      <c r="AH17" s="182"/>
-      <c r="AI17" s="183"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="213"/>
+      <c r="D17" s="214"/>
+      <c r="E17" s="215"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="217"/>
+      <c r="I17" s="213"/>
+      <c r="J17" s="218"/>
+      <c r="K17" s="219"/>
+      <c r="L17" s="219"/>
+      <c r="M17" s="219"/>
+      <c r="N17" s="219"/>
+      <c r="O17" s="219"/>
+      <c r="P17" s="220"/>
+      <c r="Q17" s="221"/>
+      <c r="R17" s="222"/>
+      <c r="S17" s="222"/>
+      <c r="T17" s="222"/>
+      <c r="U17" s="222"/>
+      <c r="V17" s="222"/>
+      <c r="W17" s="222"/>
+      <c r="X17" s="222"/>
+      <c r="Y17" s="222"/>
+      <c r="Z17" s="222"/>
+      <c r="AA17" s="222"/>
+      <c r="AB17" s="222"/>
+      <c r="AC17" s="222"/>
+      <c r="AD17" s="222"/>
+      <c r="AE17" s="223"/>
+      <c r="AF17" s="218"/>
+      <c r="AG17" s="219"/>
+      <c r="AH17" s="219"/>
+      <c r="AI17" s="220"/>
     </row>
     <row r="18" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="89"/>
-      <c r="B18" s="175"/>
-      <c r="C18" s="176"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="180"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="182"/>
-      <c r="L18" s="182"/>
-      <c r="M18" s="182"/>
-      <c r="N18" s="182"/>
-      <c r="O18" s="182"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="184"/>
-      <c r="R18" s="185"/>
-      <c r="S18" s="185"/>
-      <c r="T18" s="185"/>
-      <c r="U18" s="185"/>
-      <c r="V18" s="185"/>
-      <c r="W18" s="185"/>
-      <c r="X18" s="185"/>
-      <c r="Y18" s="185"/>
-      <c r="Z18" s="185"/>
-      <c r="AA18" s="185"/>
-      <c r="AB18" s="185"/>
-      <c r="AC18" s="185"/>
-      <c r="AD18" s="185"/>
-      <c r="AE18" s="186"/>
-      <c r="AF18" s="181"/>
-      <c r="AG18" s="182"/>
-      <c r="AH18" s="182"/>
-      <c r="AI18" s="183"/>
+      <c r="B18" s="212"/>
+      <c r="C18" s="213"/>
+      <c r="D18" s="214"/>
+      <c r="E18" s="215"/>
+      <c r="F18" s="216"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="217"/>
+      <c r="I18" s="213"/>
+      <c r="J18" s="218"/>
+      <c r="K18" s="219"/>
+      <c r="L18" s="219"/>
+      <c r="M18" s="219"/>
+      <c r="N18" s="219"/>
+      <c r="O18" s="219"/>
+      <c r="P18" s="220"/>
+      <c r="Q18" s="221"/>
+      <c r="R18" s="222"/>
+      <c r="S18" s="222"/>
+      <c r="T18" s="222"/>
+      <c r="U18" s="222"/>
+      <c r="V18" s="222"/>
+      <c r="W18" s="222"/>
+      <c r="X18" s="222"/>
+      <c r="Y18" s="222"/>
+      <c r="Z18" s="222"/>
+      <c r="AA18" s="222"/>
+      <c r="AB18" s="222"/>
+      <c r="AC18" s="222"/>
+      <c r="AD18" s="222"/>
+      <c r="AE18" s="223"/>
+      <c r="AF18" s="218"/>
+      <c r="AG18" s="219"/>
+      <c r="AH18" s="219"/>
+      <c r="AI18" s="220"/>
     </row>
     <row r="19" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="89"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="177"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="180"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="181"/>
-      <c r="K19" s="182"/>
-      <c r="L19" s="182"/>
-      <c r="M19" s="182"/>
-      <c r="N19" s="182"/>
-      <c r="O19" s="182"/>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="184"/>
-      <c r="R19" s="185"/>
-      <c r="S19" s="185"/>
-      <c r="T19" s="185"/>
-      <c r="U19" s="185"/>
-      <c r="V19" s="185"/>
-      <c r="W19" s="185"/>
-      <c r="X19" s="185"/>
-      <c r="Y19" s="185"/>
-      <c r="Z19" s="185"/>
-      <c r="AA19" s="185"/>
-      <c r="AB19" s="185"/>
-      <c r="AC19" s="185"/>
-      <c r="AD19" s="185"/>
-      <c r="AE19" s="186"/>
-      <c r="AF19" s="181"/>
-      <c r="AG19" s="182"/>
-      <c r="AH19" s="182"/>
-      <c r="AI19" s="183"/>
+      <c r="B19" s="212"/>
+      <c r="C19" s="213"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="212"/>
+      <c r="H19" s="217"/>
+      <c r="I19" s="213"/>
+      <c r="J19" s="218"/>
+      <c r="K19" s="219"/>
+      <c r="L19" s="219"/>
+      <c r="M19" s="219"/>
+      <c r="N19" s="219"/>
+      <c r="O19" s="219"/>
+      <c r="P19" s="220"/>
+      <c r="Q19" s="221"/>
+      <c r="R19" s="222"/>
+      <c r="S19" s="222"/>
+      <c r="T19" s="222"/>
+      <c r="U19" s="222"/>
+      <c r="V19" s="222"/>
+      <c r="W19" s="222"/>
+      <c r="X19" s="222"/>
+      <c r="Y19" s="222"/>
+      <c r="Z19" s="222"/>
+      <c r="AA19" s="222"/>
+      <c r="AB19" s="222"/>
+      <c r="AC19" s="222"/>
+      <c r="AD19" s="222"/>
+      <c r="AE19" s="223"/>
+      <c r="AF19" s="218"/>
+      <c r="AG19" s="219"/>
+      <c r="AH19" s="219"/>
+      <c r="AI19" s="220"/>
     </row>
     <row r="20" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="89"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="177"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="180"/>
-      <c r="I20" s="176"/>
-      <c r="J20" s="181"/>
-      <c r="K20" s="182"/>
-      <c r="L20" s="182"/>
-      <c r="M20" s="182"/>
-      <c r="N20" s="182"/>
-      <c r="O20" s="182"/>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="184"/>
-      <c r="R20" s="185"/>
-      <c r="S20" s="185"/>
-      <c r="T20" s="185"/>
-      <c r="U20" s="185"/>
-      <c r="V20" s="185"/>
-      <c r="W20" s="185"/>
-      <c r="X20" s="185"/>
-      <c r="Y20" s="185"/>
-      <c r="Z20" s="185"/>
-      <c r="AA20" s="185"/>
-      <c r="AB20" s="185"/>
-      <c r="AC20" s="185"/>
-      <c r="AD20" s="185"/>
-      <c r="AE20" s="186"/>
-      <c r="AF20" s="181"/>
-      <c r="AG20" s="182"/>
-      <c r="AH20" s="182"/>
-      <c r="AI20" s="183"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="213"/>
+      <c r="D20" s="214"/>
+      <c r="E20" s="215"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="212"/>
+      <c r="H20" s="217"/>
+      <c r="I20" s="213"/>
+      <c r="J20" s="218"/>
+      <c r="K20" s="219"/>
+      <c r="L20" s="219"/>
+      <c r="M20" s="219"/>
+      <c r="N20" s="219"/>
+      <c r="O20" s="219"/>
+      <c r="P20" s="220"/>
+      <c r="Q20" s="221"/>
+      <c r="R20" s="222"/>
+      <c r="S20" s="222"/>
+      <c r="T20" s="222"/>
+      <c r="U20" s="222"/>
+      <c r="V20" s="222"/>
+      <c r="W20" s="222"/>
+      <c r="X20" s="222"/>
+      <c r="Y20" s="222"/>
+      <c r="Z20" s="222"/>
+      <c r="AA20" s="222"/>
+      <c r="AB20" s="222"/>
+      <c r="AC20" s="222"/>
+      <c r="AD20" s="222"/>
+      <c r="AE20" s="223"/>
+      <c r="AF20" s="218"/>
+      <c r="AG20" s="219"/>
+      <c r="AH20" s="219"/>
+      <c r="AI20" s="220"/>
     </row>
     <row r="21" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="89"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="177"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="180"/>
-      <c r="I21" s="176"/>
-      <c r="J21" s="181"/>
-      <c r="K21" s="182"/>
-      <c r="L21" s="182"/>
-      <c r="M21" s="182"/>
-      <c r="N21" s="182"/>
-      <c r="O21" s="182"/>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="184"/>
-      <c r="R21" s="185"/>
-      <c r="S21" s="185"/>
-      <c r="T21" s="185"/>
-      <c r="U21" s="185"/>
-      <c r="V21" s="185"/>
-      <c r="W21" s="185"/>
-      <c r="X21" s="185"/>
-      <c r="Y21" s="185"/>
-      <c r="Z21" s="185"/>
-      <c r="AA21" s="185"/>
-      <c r="AB21" s="185"/>
-      <c r="AC21" s="185"/>
-      <c r="AD21" s="185"/>
-      <c r="AE21" s="186"/>
-      <c r="AF21" s="181"/>
-      <c r="AG21" s="182"/>
-      <c r="AH21" s="182"/>
-      <c r="AI21" s="183"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="213"/>
+      <c r="D21" s="214"/>
+      <c r="E21" s="215"/>
+      <c r="F21" s="216"/>
+      <c r="G21" s="212"/>
+      <c r="H21" s="217"/>
+      <c r="I21" s="213"/>
+      <c r="J21" s="218"/>
+      <c r="K21" s="219"/>
+      <c r="L21" s="219"/>
+      <c r="M21" s="219"/>
+      <c r="N21" s="219"/>
+      <c r="O21" s="219"/>
+      <c r="P21" s="220"/>
+      <c r="Q21" s="221"/>
+      <c r="R21" s="222"/>
+      <c r="S21" s="222"/>
+      <c r="T21" s="222"/>
+      <c r="U21" s="222"/>
+      <c r="V21" s="222"/>
+      <c r="W21" s="222"/>
+      <c r="X21" s="222"/>
+      <c r="Y21" s="222"/>
+      <c r="Z21" s="222"/>
+      <c r="AA21" s="222"/>
+      <c r="AB21" s="222"/>
+      <c r="AC21" s="222"/>
+      <c r="AD21" s="222"/>
+      <c r="AE21" s="223"/>
+      <c r="AF21" s="218"/>
+      <c r="AG21" s="219"/>
+      <c r="AH21" s="219"/>
+      <c r="AI21" s="220"/>
     </row>
     <row r="22" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="89"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="177"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="180"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="181"/>
-      <c r="K22" s="182"/>
-      <c r="L22" s="182"/>
-      <c r="M22" s="182"/>
-      <c r="N22" s="182"/>
-      <c r="O22" s="182"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="184"/>
-      <c r="R22" s="185"/>
-      <c r="S22" s="185"/>
-      <c r="T22" s="185"/>
-      <c r="U22" s="185"/>
-      <c r="V22" s="185"/>
-      <c r="W22" s="185"/>
-      <c r="X22" s="185"/>
-      <c r="Y22" s="185"/>
-      <c r="Z22" s="185"/>
-      <c r="AA22" s="185"/>
-      <c r="AB22" s="185"/>
-      <c r="AC22" s="185"/>
-      <c r="AD22" s="185"/>
-      <c r="AE22" s="186"/>
-      <c r="AF22" s="181"/>
-      <c r="AG22" s="182"/>
-      <c r="AH22" s="182"/>
-      <c r="AI22" s="183"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="213"/>
+      <c r="D22" s="214"/>
+      <c r="E22" s="215"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="212"/>
+      <c r="H22" s="217"/>
+      <c r="I22" s="213"/>
+      <c r="J22" s="218"/>
+      <c r="K22" s="219"/>
+      <c r="L22" s="219"/>
+      <c r="M22" s="219"/>
+      <c r="N22" s="219"/>
+      <c r="O22" s="219"/>
+      <c r="P22" s="220"/>
+      <c r="Q22" s="221"/>
+      <c r="R22" s="222"/>
+      <c r="S22" s="222"/>
+      <c r="T22" s="222"/>
+      <c r="U22" s="222"/>
+      <c r="V22" s="222"/>
+      <c r="W22" s="222"/>
+      <c r="X22" s="222"/>
+      <c r="Y22" s="222"/>
+      <c r="Z22" s="222"/>
+      <c r="AA22" s="222"/>
+      <c r="AB22" s="222"/>
+      <c r="AC22" s="222"/>
+      <c r="AD22" s="222"/>
+      <c r="AE22" s="223"/>
+      <c r="AF22" s="218"/>
+      <c r="AG22" s="219"/>
+      <c r="AH22" s="219"/>
+      <c r="AI22" s="220"/>
     </row>
     <row r="23" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="89"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="177"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="180"/>
-      <c r="I23" s="176"/>
-      <c r="J23" s="181"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="182"/>
-      <c r="M23" s="182"/>
-      <c r="N23" s="182"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="183"/>
-      <c r="Q23" s="184"/>
-      <c r="R23" s="185"/>
-      <c r="S23" s="185"/>
-      <c r="T23" s="185"/>
-      <c r="U23" s="185"/>
-      <c r="V23" s="185"/>
-      <c r="W23" s="185"/>
-      <c r="X23" s="185"/>
-      <c r="Y23" s="185"/>
-      <c r="Z23" s="185"/>
-      <c r="AA23" s="185"/>
-      <c r="AB23" s="185"/>
-      <c r="AC23" s="185"/>
-      <c r="AD23" s="185"/>
-      <c r="AE23" s="186"/>
-      <c r="AF23" s="181"/>
-      <c r="AG23" s="182"/>
-      <c r="AH23" s="182"/>
-      <c r="AI23" s="183"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="213"/>
+      <c r="D23" s="214"/>
+      <c r="E23" s="215"/>
+      <c r="F23" s="216"/>
+      <c r="G23" s="212"/>
+      <c r="H23" s="217"/>
+      <c r="I23" s="213"/>
+      <c r="J23" s="218"/>
+      <c r="K23" s="219"/>
+      <c r="L23" s="219"/>
+      <c r="M23" s="219"/>
+      <c r="N23" s="219"/>
+      <c r="O23" s="219"/>
+      <c r="P23" s="220"/>
+      <c r="Q23" s="221"/>
+      <c r="R23" s="222"/>
+      <c r="S23" s="222"/>
+      <c r="T23" s="222"/>
+      <c r="U23" s="222"/>
+      <c r="V23" s="222"/>
+      <c r="W23" s="222"/>
+      <c r="X23" s="222"/>
+      <c r="Y23" s="222"/>
+      <c r="Z23" s="222"/>
+      <c r="AA23" s="222"/>
+      <c r="AB23" s="222"/>
+      <c r="AC23" s="222"/>
+      <c r="AD23" s="222"/>
+      <c r="AE23" s="223"/>
+      <c r="AF23" s="218"/>
+      <c r="AG23" s="219"/>
+      <c r="AH23" s="219"/>
+      <c r="AI23" s="220"/>
     </row>
     <row r="24" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="89"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="177"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="179"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="180"/>
-      <c r="I24" s="176"/>
-      <c r="J24" s="181"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="182"/>
-      <c r="N24" s="182"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="184"/>
-      <c r="R24" s="185"/>
-      <c r="S24" s="185"/>
-      <c r="T24" s="185"/>
-      <c r="U24" s="185"/>
-      <c r="V24" s="185"/>
-      <c r="W24" s="185"/>
-      <c r="X24" s="185"/>
-      <c r="Y24" s="185"/>
-      <c r="Z24" s="185"/>
-      <c r="AA24" s="185"/>
-      <c r="AB24" s="185"/>
-      <c r="AC24" s="185"/>
-      <c r="AD24" s="185"/>
-      <c r="AE24" s="186"/>
-      <c r="AF24" s="181"/>
-      <c r="AG24" s="182"/>
-      <c r="AH24" s="182"/>
-      <c r="AI24" s="183"/>
+      <c r="B24" s="212"/>
+      <c r="C24" s="213"/>
+      <c r="D24" s="214"/>
+      <c r="E24" s="215"/>
+      <c r="F24" s="216"/>
+      <c r="G24" s="212"/>
+      <c r="H24" s="217"/>
+      <c r="I24" s="213"/>
+      <c r="J24" s="218"/>
+      <c r="K24" s="219"/>
+      <c r="L24" s="219"/>
+      <c r="M24" s="219"/>
+      <c r="N24" s="219"/>
+      <c r="O24" s="219"/>
+      <c r="P24" s="220"/>
+      <c r="Q24" s="221"/>
+      <c r="R24" s="222"/>
+      <c r="S24" s="222"/>
+      <c r="T24" s="222"/>
+      <c r="U24" s="222"/>
+      <c r="V24" s="222"/>
+      <c r="W24" s="222"/>
+      <c r="X24" s="222"/>
+      <c r="Y24" s="222"/>
+      <c r="Z24" s="222"/>
+      <c r="AA24" s="222"/>
+      <c r="AB24" s="222"/>
+      <c r="AC24" s="222"/>
+      <c r="AD24" s="222"/>
+      <c r="AE24" s="223"/>
+      <c r="AF24" s="218"/>
+      <c r="AG24" s="219"/>
+      <c r="AH24" s="219"/>
+      <c r="AI24" s="220"/>
     </row>
     <row r="25" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="89"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="177"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="180"/>
-      <c r="I25" s="176"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="182"/>
-      <c r="N25" s="182"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="184"/>
-      <c r="R25" s="185"/>
-      <c r="S25" s="185"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="185"/>
-      <c r="V25" s="185"/>
-      <c r="W25" s="185"/>
-      <c r="X25" s="185"/>
-      <c r="Y25" s="185"/>
-      <c r="Z25" s="185"/>
-      <c r="AA25" s="185"/>
-      <c r="AB25" s="185"/>
-      <c r="AC25" s="185"/>
-      <c r="AD25" s="185"/>
-      <c r="AE25" s="186"/>
-      <c r="AF25" s="181"/>
-      <c r="AG25" s="182"/>
-      <c r="AH25" s="182"/>
-      <c r="AI25" s="183"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="213"/>
+      <c r="D25" s="214"/>
+      <c r="E25" s="215"/>
+      <c r="F25" s="216"/>
+      <c r="G25" s="212"/>
+      <c r="H25" s="217"/>
+      <c r="I25" s="213"/>
+      <c r="J25" s="218"/>
+      <c r="K25" s="219"/>
+      <c r="L25" s="219"/>
+      <c r="M25" s="219"/>
+      <c r="N25" s="219"/>
+      <c r="O25" s="219"/>
+      <c r="P25" s="220"/>
+      <c r="Q25" s="221"/>
+      <c r="R25" s="222"/>
+      <c r="S25" s="222"/>
+      <c r="T25" s="222"/>
+      <c r="U25" s="222"/>
+      <c r="V25" s="222"/>
+      <c r="W25" s="222"/>
+      <c r="X25" s="222"/>
+      <c r="Y25" s="222"/>
+      <c r="Z25" s="222"/>
+      <c r="AA25" s="222"/>
+      <c r="AB25" s="222"/>
+      <c r="AC25" s="222"/>
+      <c r="AD25" s="222"/>
+      <c r="AE25" s="223"/>
+      <c r="AF25" s="218"/>
+      <c r="AG25" s="219"/>
+      <c r="AH25" s="219"/>
+      <c r="AI25" s="220"/>
     </row>
     <row r="26" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="89"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="177"/>
-      <c r="E26" s="178"/>
-      <c r="F26" s="179"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="180"/>
-      <c r="I26" s="176"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="182"/>
-      <c r="M26" s="182"/>
-      <c r="N26" s="182"/>
-      <c r="O26" s="182"/>
-      <c r="P26" s="183"/>
-      <c r="Q26" s="184"/>
-      <c r="R26" s="185"/>
-      <c r="S26" s="185"/>
-      <c r="T26" s="185"/>
-      <c r="U26" s="185"/>
-      <c r="V26" s="185"/>
-      <c r="W26" s="185"/>
-      <c r="X26" s="185"/>
-      <c r="Y26" s="185"/>
-      <c r="Z26" s="185"/>
-      <c r="AA26" s="185"/>
-      <c r="AB26" s="185"/>
-      <c r="AC26" s="185"/>
-      <c r="AD26" s="185"/>
-      <c r="AE26" s="186"/>
-      <c r="AF26" s="181"/>
-      <c r="AG26" s="182"/>
-      <c r="AH26" s="182"/>
-      <c r="AI26" s="183"/>
+      <c r="B26" s="212"/>
+      <c r="C26" s="213"/>
+      <c r="D26" s="214"/>
+      <c r="E26" s="215"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="217"/>
+      <c r="I26" s="213"/>
+      <c r="J26" s="218"/>
+      <c r="K26" s="219"/>
+      <c r="L26" s="219"/>
+      <c r="M26" s="219"/>
+      <c r="N26" s="219"/>
+      <c r="O26" s="219"/>
+      <c r="P26" s="220"/>
+      <c r="Q26" s="221"/>
+      <c r="R26" s="222"/>
+      <c r="S26" s="222"/>
+      <c r="T26" s="222"/>
+      <c r="U26" s="222"/>
+      <c r="V26" s="222"/>
+      <c r="W26" s="222"/>
+      <c r="X26" s="222"/>
+      <c r="Y26" s="222"/>
+      <c r="Z26" s="222"/>
+      <c r="AA26" s="222"/>
+      <c r="AB26" s="222"/>
+      <c r="AC26" s="222"/>
+      <c r="AD26" s="222"/>
+      <c r="AE26" s="223"/>
+      <c r="AF26" s="218"/>
+      <c r="AG26" s="219"/>
+      <c r="AH26" s="219"/>
+      <c r="AI26" s="220"/>
     </row>
     <row r="27" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="89"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="179"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="180"/>
-      <c r="I27" s="176"/>
-      <c r="J27" s="181"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="182"/>
-      <c r="M27" s="182"/>
-      <c r="N27" s="182"/>
-      <c r="O27" s="182"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="184"/>
-      <c r="R27" s="185"/>
-      <c r="S27" s="185"/>
-      <c r="T27" s="185"/>
-      <c r="U27" s="185"/>
-      <c r="V27" s="185"/>
-      <c r="W27" s="185"/>
-      <c r="X27" s="185"/>
-      <c r="Y27" s="185"/>
-      <c r="Z27" s="185"/>
-      <c r="AA27" s="185"/>
-      <c r="AB27" s="185"/>
-      <c r="AC27" s="185"/>
-      <c r="AD27" s="185"/>
-      <c r="AE27" s="186"/>
-      <c r="AF27" s="181"/>
-      <c r="AG27" s="182"/>
-      <c r="AH27" s="182"/>
-      <c r="AI27" s="183"/>
+      <c r="B27" s="212"/>
+      <c r="C27" s="213"/>
+      <c r="D27" s="214"/>
+      <c r="E27" s="215"/>
+      <c r="F27" s="216"/>
+      <c r="G27" s="212"/>
+      <c r="H27" s="217"/>
+      <c r="I27" s="213"/>
+      <c r="J27" s="218"/>
+      <c r="K27" s="219"/>
+      <c r="L27" s="219"/>
+      <c r="M27" s="219"/>
+      <c r="N27" s="219"/>
+      <c r="O27" s="219"/>
+      <c r="P27" s="220"/>
+      <c r="Q27" s="221"/>
+      <c r="R27" s="222"/>
+      <c r="S27" s="222"/>
+      <c r="T27" s="222"/>
+      <c r="U27" s="222"/>
+      <c r="V27" s="222"/>
+      <c r="W27" s="222"/>
+      <c r="X27" s="222"/>
+      <c r="Y27" s="222"/>
+      <c r="Z27" s="222"/>
+      <c r="AA27" s="222"/>
+      <c r="AB27" s="222"/>
+      <c r="AC27" s="222"/>
+      <c r="AD27" s="222"/>
+      <c r="AE27" s="223"/>
+      <c r="AF27" s="218"/>
+      <c r="AG27" s="219"/>
+      <c r="AH27" s="219"/>
+      <c r="AI27" s="220"/>
     </row>
     <row r="28" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="89"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="177"/>
-      <c r="E28" s="178"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="180"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="181"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="182"/>
-      <c r="M28" s="182"/>
-      <c r="N28" s="182"/>
-      <c r="O28" s="182"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="184"/>
-      <c r="R28" s="185"/>
-      <c r="S28" s="185"/>
-      <c r="T28" s="185"/>
-      <c r="U28" s="185"/>
-      <c r="V28" s="185"/>
-      <c r="W28" s="185"/>
-      <c r="X28" s="185"/>
-      <c r="Y28" s="185"/>
-      <c r="Z28" s="185"/>
-      <c r="AA28" s="185"/>
-      <c r="AB28" s="185"/>
-      <c r="AC28" s="185"/>
-      <c r="AD28" s="185"/>
-      <c r="AE28" s="186"/>
-      <c r="AF28" s="181"/>
-      <c r="AG28" s="182"/>
-      <c r="AH28" s="182"/>
-      <c r="AI28" s="183"/>
+      <c r="B28" s="212"/>
+      <c r="C28" s="213"/>
+      <c r="D28" s="214"/>
+      <c r="E28" s="215"/>
+      <c r="F28" s="216"/>
+      <c r="G28" s="212"/>
+      <c r="H28" s="217"/>
+      <c r="I28" s="213"/>
+      <c r="J28" s="218"/>
+      <c r="K28" s="219"/>
+      <c r="L28" s="219"/>
+      <c r="M28" s="219"/>
+      <c r="N28" s="219"/>
+      <c r="O28" s="219"/>
+      <c r="P28" s="220"/>
+      <c r="Q28" s="221"/>
+      <c r="R28" s="222"/>
+      <c r="S28" s="222"/>
+      <c r="T28" s="222"/>
+      <c r="U28" s="222"/>
+      <c r="V28" s="222"/>
+      <c r="W28" s="222"/>
+      <c r="X28" s="222"/>
+      <c r="Y28" s="222"/>
+      <c r="Z28" s="222"/>
+      <c r="AA28" s="222"/>
+      <c r="AB28" s="222"/>
+      <c r="AC28" s="222"/>
+      <c r="AD28" s="222"/>
+      <c r="AE28" s="223"/>
+      <c r="AF28" s="218"/>
+      <c r="AG28" s="219"/>
+      <c r="AH28" s="219"/>
+      <c r="AI28" s="220"/>
     </row>
     <row r="29" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="89"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="180"/>
-      <c r="I29" s="176"/>
-      <c r="J29" s="181"/>
-      <c r="K29" s="182"/>
-      <c r="L29" s="182"/>
-      <c r="M29" s="182"/>
-      <c r="N29" s="182"/>
-      <c r="O29" s="182"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="184"/>
-      <c r="R29" s="185"/>
-      <c r="S29" s="185"/>
-      <c r="T29" s="185"/>
-      <c r="U29" s="185"/>
-      <c r="V29" s="185"/>
-      <c r="W29" s="185"/>
-      <c r="X29" s="185"/>
-      <c r="Y29" s="185"/>
-      <c r="Z29" s="185"/>
-      <c r="AA29" s="185"/>
-      <c r="AB29" s="185"/>
-      <c r="AC29" s="185"/>
-      <c r="AD29" s="185"/>
-      <c r="AE29" s="186"/>
-      <c r="AF29" s="181"/>
-      <c r="AG29" s="182"/>
-      <c r="AH29" s="182"/>
-      <c r="AI29" s="183"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="214"/>
+      <c r="E29" s="215"/>
+      <c r="F29" s="216"/>
+      <c r="G29" s="212"/>
+      <c r="H29" s="217"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="218"/>
+      <c r="K29" s="219"/>
+      <c r="L29" s="219"/>
+      <c r="M29" s="219"/>
+      <c r="N29" s="219"/>
+      <c r="O29" s="219"/>
+      <c r="P29" s="220"/>
+      <c r="Q29" s="221"/>
+      <c r="R29" s="222"/>
+      <c r="S29" s="222"/>
+      <c r="T29" s="222"/>
+      <c r="U29" s="222"/>
+      <c r="V29" s="222"/>
+      <c r="W29" s="222"/>
+      <c r="X29" s="222"/>
+      <c r="Y29" s="222"/>
+      <c r="Z29" s="222"/>
+      <c r="AA29" s="222"/>
+      <c r="AB29" s="222"/>
+      <c r="AC29" s="222"/>
+      <c r="AD29" s="222"/>
+      <c r="AE29" s="223"/>
+      <c r="AF29" s="218"/>
+      <c r="AG29" s="219"/>
+      <c r="AH29" s="219"/>
+      <c r="AI29" s="220"/>
     </row>
     <row r="30" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="89"/>
-      <c r="B30" s="175"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="180"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="181"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="182"/>
-      <c r="N30" s="182"/>
-      <c r="O30" s="182"/>
-      <c r="P30" s="183"/>
-      <c r="Q30" s="184"/>
-      <c r="R30" s="185"/>
-      <c r="S30" s="185"/>
-      <c r="T30" s="185"/>
-      <c r="U30" s="185"/>
-      <c r="V30" s="185"/>
-      <c r="W30" s="185"/>
-      <c r="X30" s="185"/>
-      <c r="Y30" s="185"/>
-      <c r="Z30" s="185"/>
-      <c r="AA30" s="185"/>
-      <c r="AB30" s="185"/>
-      <c r="AC30" s="185"/>
-      <c r="AD30" s="185"/>
-      <c r="AE30" s="186"/>
-      <c r="AF30" s="181"/>
-      <c r="AG30" s="182"/>
-      <c r="AH30" s="182"/>
-      <c r="AI30" s="183"/>
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="214"/>
+      <c r="E30" s="215"/>
+      <c r="F30" s="216"/>
+      <c r="G30" s="212"/>
+      <c r="H30" s="217"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="218"/>
+      <c r="K30" s="219"/>
+      <c r="L30" s="219"/>
+      <c r="M30" s="219"/>
+      <c r="N30" s="219"/>
+      <c r="O30" s="219"/>
+      <c r="P30" s="220"/>
+      <c r="Q30" s="221"/>
+      <c r="R30" s="222"/>
+      <c r="S30" s="222"/>
+      <c r="T30" s="222"/>
+      <c r="U30" s="222"/>
+      <c r="V30" s="222"/>
+      <c r="W30" s="222"/>
+      <c r="X30" s="222"/>
+      <c r="Y30" s="222"/>
+      <c r="Z30" s="222"/>
+      <c r="AA30" s="222"/>
+      <c r="AB30" s="222"/>
+      <c r="AC30" s="222"/>
+      <c r="AD30" s="222"/>
+      <c r="AE30" s="223"/>
+      <c r="AF30" s="218"/>
+      <c r="AG30" s="219"/>
+      <c r="AH30" s="219"/>
+      <c r="AI30" s="220"/>
     </row>
     <row r="31" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="89"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="177"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="180"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="182"/>
-      <c r="L31" s="182"/>
-      <c r="M31" s="182"/>
-      <c r="N31" s="182"/>
-      <c r="O31" s="182"/>
-      <c r="P31" s="183"/>
-      <c r="Q31" s="184"/>
-      <c r="R31" s="185"/>
-      <c r="S31" s="185"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="185"/>
-      <c r="V31" s="185"/>
-      <c r="W31" s="185"/>
-      <c r="X31" s="185"/>
-      <c r="Y31" s="185"/>
-      <c r="Z31" s="185"/>
-      <c r="AA31" s="185"/>
-      <c r="AB31" s="185"/>
-      <c r="AC31" s="185"/>
-      <c r="AD31" s="185"/>
-      <c r="AE31" s="186"/>
-      <c r="AF31" s="181"/>
-      <c r="AG31" s="182"/>
-      <c r="AH31" s="182"/>
-      <c r="AI31" s="183"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="214"/>
+      <c r="E31" s="215"/>
+      <c r="F31" s="216"/>
+      <c r="G31" s="212"/>
+      <c r="H31" s="217"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="218"/>
+      <c r="K31" s="219"/>
+      <c r="L31" s="219"/>
+      <c r="M31" s="219"/>
+      <c r="N31" s="219"/>
+      <c r="O31" s="219"/>
+      <c r="P31" s="220"/>
+      <c r="Q31" s="221"/>
+      <c r="R31" s="222"/>
+      <c r="S31" s="222"/>
+      <c r="T31" s="222"/>
+      <c r="U31" s="222"/>
+      <c r="V31" s="222"/>
+      <c r="W31" s="222"/>
+      <c r="X31" s="222"/>
+      <c r="Y31" s="222"/>
+      <c r="Z31" s="222"/>
+      <c r="AA31" s="222"/>
+      <c r="AB31" s="222"/>
+      <c r="AC31" s="222"/>
+      <c r="AD31" s="222"/>
+      <c r="AE31" s="223"/>
+      <c r="AF31" s="218"/>
+      <c r="AG31" s="219"/>
+      <c r="AH31" s="219"/>
+      <c r="AI31" s="220"/>
     </row>
     <row r="32" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="89"/>
-      <c r="B32" s="175"/>
-      <c r="C32" s="176"/>
-      <c r="D32" s="177"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="175"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="176"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="187"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="182"/>
-      <c r="N32" s="182"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="183"/>
-      <c r="Q32" s="184"/>
-      <c r="R32" s="185"/>
-      <c r="S32" s="185"/>
-      <c r="T32" s="185"/>
-      <c r="U32" s="185"/>
-      <c r="V32" s="185"/>
-      <c r="W32" s="185"/>
-      <c r="X32" s="185"/>
-      <c r="Y32" s="185"/>
-      <c r="Z32" s="185"/>
-      <c r="AA32" s="185"/>
-      <c r="AB32" s="185"/>
-      <c r="AC32" s="185"/>
-      <c r="AD32" s="185"/>
-      <c r="AE32" s="186"/>
-      <c r="AF32" s="181"/>
-      <c r="AG32" s="182"/>
-      <c r="AH32" s="182"/>
-      <c r="AI32" s="183"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="214"/>
+      <c r="E32" s="215"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="212"/>
+      <c r="H32" s="217"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="218"/>
+      <c r="K32" s="238"/>
+      <c r="L32" s="219"/>
+      <c r="M32" s="219"/>
+      <c r="N32" s="219"/>
+      <c r="O32" s="219"/>
+      <c r="P32" s="220"/>
+      <c r="Q32" s="221"/>
+      <c r="R32" s="222"/>
+      <c r="S32" s="222"/>
+      <c r="T32" s="222"/>
+      <c r="U32" s="222"/>
+      <c r="V32" s="222"/>
+      <c r="W32" s="222"/>
+      <c r="X32" s="222"/>
+      <c r="Y32" s="222"/>
+      <c r="Z32" s="222"/>
+      <c r="AA32" s="222"/>
+      <c r="AB32" s="222"/>
+      <c r="AC32" s="222"/>
+      <c r="AD32" s="222"/>
+      <c r="AE32" s="223"/>
+      <c r="AF32" s="218"/>
+      <c r="AG32" s="219"/>
+      <c r="AH32" s="219"/>
+      <c r="AI32" s="220"/>
     </row>
     <row r="33" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="89"/>
-      <c r="B33" s="175"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="177"/>
-      <c r="E33" s="178"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="180"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="182"/>
-      <c r="L33" s="182"/>
-      <c r="M33" s="182"/>
-      <c r="N33" s="182"/>
-      <c r="O33" s="182"/>
-      <c r="P33" s="183"/>
-      <c r="Q33" s="184"/>
-      <c r="R33" s="185"/>
-      <c r="S33" s="185"/>
-      <c r="T33" s="185"/>
-      <c r="U33" s="185"/>
-      <c r="V33" s="185"/>
-      <c r="W33" s="185"/>
-      <c r="X33" s="185"/>
-      <c r="Y33" s="185"/>
-      <c r="Z33" s="185"/>
-      <c r="AA33" s="185"/>
-      <c r="AB33" s="185"/>
-      <c r="AC33" s="185"/>
-      <c r="AD33" s="185"/>
-      <c r="AE33" s="186"/>
-      <c r="AF33" s="181"/>
-      <c r="AG33" s="182"/>
-      <c r="AH33" s="182"/>
-      <c r="AI33" s="183"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="214"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="212"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="218"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
+      <c r="M33" s="219"/>
+      <c r="N33" s="219"/>
+      <c r="O33" s="219"/>
+      <c r="P33" s="220"/>
+      <c r="Q33" s="221"/>
+      <c r="R33" s="222"/>
+      <c r="S33" s="222"/>
+      <c r="T33" s="222"/>
+      <c r="U33" s="222"/>
+      <c r="V33" s="222"/>
+      <c r="W33" s="222"/>
+      <c r="X33" s="222"/>
+      <c r="Y33" s="222"/>
+      <c r="Z33" s="222"/>
+      <c r="AA33" s="222"/>
+      <c r="AB33" s="222"/>
+      <c r="AC33" s="222"/>
+      <c r="AD33" s="222"/>
+      <c r="AE33" s="223"/>
+      <c r="AF33" s="218"/>
+      <c r="AG33" s="219"/>
+      <c r="AH33" s="219"/>
+      <c r="AI33" s="220"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -29317,162 +29473,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -29624,158 +29624,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="239" t="str">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="213"/>
-      <c r="O1" s="218" t="s">
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="219"/>
-      <c r="Q1" s="219"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="240" t="str">
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="244" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
-      <c r="W1" s="228"/>
-      <c r="X1" s="228"/>
-      <c r="Y1" s="228"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="241" t="s">
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="201"/>
+      <c r="AA1" s="242" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="242"/>
-      <c r="AC1" s="236" t="str">
+      <c r="AB1" s="243"/>
+      <c r="AC1" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="237"/>
-      <c r="AE1" s="237"/>
-      <c r="AF1" s="238"/>
-      <c r="AG1" s="243">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="239">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45565</v>
-      </c>
-      <c r="AH1" s="244"/>
-      <c r="AI1" s="245"/>
+        <v>43336</v>
+      </c>
+      <c r="AH1" s="240"/>
+      <c r="AI1" s="241"/>
       <c r="AL1" s="91"/>
     </row>
     <row r="2" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="209"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="239" t="str">
+      <c r="B2" s="181"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
-      <c r="M2" s="212"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="221"/>
-      <c r="P2" s="222"/>
-      <c r="Q2" s="222"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="231"/>
-      <c r="U2" s="231"/>
-      <c r="V2" s="231"/>
-      <c r="W2" s="231"/>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="231"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="241" t="s">
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="184"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="185"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="203"/>
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="242" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="236" t="str">
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="237"/>
-      <c r="AF2" s="238"/>
-      <c r="AG2" s="243" t="str">
+      <c r="AD2" s="209"/>
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="210"/>
+      <c r="AG2" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="244"/>
-      <c r="AI2" s="245"/>
+      <c r="AH2" s="240"/>
+      <c r="AI2" s="241"/>
     </row>
     <row r="3" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="209"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="239" t="str">
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="213"/>
-      <c r="O3" s="224"/>
-      <c r="P3" s="225"/>
-      <c r="Q3" s="225"/>
-      <c r="R3" s="226"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="234"/>
-      <c r="U3" s="234"/>
-      <c r="V3" s="234"/>
-      <c r="W3" s="234"/>
-      <c r="X3" s="234"/>
-      <c r="Y3" s="234"/>
-      <c r="Z3" s="235"/>
-      <c r="AA3" s="241"/>
-      <c r="AB3" s="242"/>
-      <c r="AC3" s="236" t="str">
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+      <c r="M3" s="184"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="197"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="198"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="206"/>
+      <c r="U3" s="206"/>
+      <c r="V3" s="206"/>
+      <c r="W3" s="206"/>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="207"/>
+      <c r="AA3" s="242"/>
+      <c r="AB3" s="243"/>
+      <c r="AC3" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="237"/>
-      <c r="AE3" s="237"/>
-      <c r="AF3" s="238"/>
-      <c r="AG3" s="243" t="str">
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="239" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="244"/>
-      <c r="AI3" s="245"/>
+      <c r="AH3" s="240"/>
+      <c r="AI3" s="241"/>
     </row>
     <row r="4" spans="1:53" s="31" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AC4" s="92"/>
@@ -32194,14 +32194,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -32211,6 +32203,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -32233,157 +32233,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="249" t="s">
+      <c r="A1" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="250"/>
-      <c r="C1" s="250"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
-      <c r="L1" s="253"/>
-      <c r="M1" s="253"/>
-      <c r="N1" s="254"/>
-      <c r="O1" s="258" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="260"/>
-      <c r="S1" s="267" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="268"/>
-      <c r="U1" s="268"/>
-      <c r="V1" s="268"/>
-      <c r="W1" s="268"/>
-      <c r="X1" s="268"/>
-      <c r="Y1" s="268"/>
-      <c r="Z1" s="269"/>
-      <c r="AA1" s="249" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="251"/>
-      <c r="AC1" s="255" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="256"/>
-      <c r="AE1" s="256"/>
-      <c r="AF1" s="257"/>
-      <c r="AG1" s="246">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="245">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45565</v>
-      </c>
-      <c r="AH1" s="247"/>
-      <c r="AI1" s="248"/>
+        <v>43336</v>
+      </c>
+      <c r="AH1" s="246"/>
+      <c r="AI1" s="247"/>
       <c r="AN1" s="17"/>
       <c r="AO1" s="17"/>
       <c r="AP1" s="17"/>
     </row>
     <row r="2" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="249" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="250"/>
-      <c r="C2" s="250"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="253"/>
-      <c r="N2" s="254"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="271"/>
-      <c r="U2" s="271"/>
-      <c r="V2" s="271"/>
-      <c r="W2" s="271"/>
-      <c r="X2" s="271"/>
-      <c r="Y2" s="271"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="249" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="255" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="256"/>
-      <c r="AE2" s="256"/>
-      <c r="AF2" s="257"/>
-      <c r="AG2" s="246" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="245" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="247"/>
-      <c r="AI2" s="248"/>
+      <c r="AH2" s="246"/>
+      <c r="AI2" s="247"/>
       <c r="AN2" s="17"/>
       <c r="AO2" s="17"/>
       <c r="AP2" s="17"/>
     </row>
     <row r="3" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="249" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="250"/>
-      <c r="C3" s="250"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="252" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="254"/>
-      <c r="O3" s="264"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="274"/>
-      <c r="U3" s="274"/>
-      <c r="V3" s="274"/>
-      <c r="W3" s="274"/>
-      <c r="X3" s="274"/>
-      <c r="Y3" s="274"/>
-      <c r="Z3" s="275"/>
-      <c r="AA3" s="249"/>
-      <c r="AB3" s="251"/>
-      <c r="AC3" s="255" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="256"/>
-      <c r="AE3" s="256"/>
-      <c r="AF3" s="257"/>
-      <c r="AG3" s="246" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="245" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="247"/>
-      <c r="AI3" s="248"/>
+      <c r="AH3" s="246"/>
+      <c r="AI3" s="247"/>
       <c r="AN3" s="17"/>
       <c r="AO3" s="17"/>
       <c r="AP3" s="17"/>
@@ -32433,70 +32433,70 @@
       <c r="C14" s="36"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="D15" s="276" t="s">
+      <c r="D15" s="248" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="277"/>
-      <c r="F15" s="277"/>
-      <c r="G15" s="277"/>
-      <c r="H15" s="277"/>
-      <c r="I15" s="277"/>
-      <c r="J15" s="278"/>
-      <c r="K15" s="276" t="s">
+      <c r="E15" s="249"/>
+      <c r="F15" s="249"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="250"/>
+      <c r="K15" s="248" t="s">
         <v>55</v>
       </c>
-      <c r="L15" s="277"/>
-      <c r="M15" s="277"/>
-      <c r="N15" s="277"/>
-      <c r="O15" s="277"/>
-      <c r="P15" s="277"/>
-      <c r="Q15" s="277"/>
-      <c r="R15" s="277"/>
-      <c r="S15" s="277"/>
-      <c r="T15" s="277"/>
-      <c r="U15" s="277"/>
-      <c r="V15" s="277"/>
-      <c r="W15" s="277"/>
-      <c r="X15" s="277"/>
-      <c r="Y15" s="277"/>
-      <c r="Z15" s="277"/>
-      <c r="AA15" s="277"/>
-      <c r="AB15" s="277"/>
-      <c r="AC15" s="277"/>
-      <c r="AD15" s="278"/>
+      <c r="L15" s="249"/>
+      <c r="M15" s="249"/>
+      <c r="N15" s="249"/>
+      <c r="O15" s="249"/>
+      <c r="P15" s="249"/>
+      <c r="Q15" s="249"/>
+      <c r="R15" s="249"/>
+      <c r="S15" s="249"/>
+      <c r="T15" s="249"/>
+      <c r="U15" s="249"/>
+      <c r="V15" s="249"/>
+      <c r="W15" s="249"/>
+      <c r="X15" s="249"/>
+      <c r="Y15" s="249"/>
+      <c r="Z15" s="249"/>
+      <c r="AA15" s="249"/>
+      <c r="AB15" s="249"/>
+      <c r="AC15" s="249"/>
+      <c r="AD15" s="250"/>
     </row>
     <row r="16" spans="1:42" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D16" s="282" t="s">
+      <c r="D16" s="254" t="s">
         <v>272</v>
       </c>
-      <c r="E16" s="283"/>
-      <c r="F16" s="283"/>
-      <c r="G16" s="283"/>
-      <c r="H16" s="283"/>
-      <c r="I16" s="283"/>
-      <c r="J16" s="284"/>
-      <c r="K16" s="279" t="s">
+      <c r="E16" s="255"/>
+      <c r="F16" s="255"/>
+      <c r="G16" s="255"/>
+      <c r="H16" s="255"/>
+      <c r="I16" s="255"/>
+      <c r="J16" s="256"/>
+      <c r="K16" s="251" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="280"/>
-      <c r="M16" s="280"/>
-      <c r="N16" s="280"/>
-      <c r="O16" s="280"/>
-      <c r="P16" s="280"/>
-      <c r="Q16" s="280"/>
-      <c r="R16" s="280"/>
-      <c r="S16" s="280"/>
-      <c r="T16" s="280"/>
-      <c r="U16" s="280"/>
-      <c r="V16" s="280"/>
-      <c r="W16" s="280"/>
-      <c r="X16" s="280"/>
-      <c r="Y16" s="280"/>
-      <c r="Z16" s="280"/>
-      <c r="AA16" s="280"/>
-      <c r="AB16" s="280"/>
-      <c r="AC16" s="280"/>
-      <c r="AD16" s="281"/>
+      <c r="L16" s="252"/>
+      <c r="M16" s="252"/>
+      <c r="N16" s="252"/>
+      <c r="O16" s="252"/>
+      <c r="P16" s="252"/>
+      <c r="Q16" s="252"/>
+      <c r="R16" s="252"/>
+      <c r="S16" s="252"/>
+      <c r="T16" s="252"/>
+      <c r="U16" s="252"/>
+      <c r="V16" s="252"/>
+      <c r="W16" s="252"/>
+      <c r="X16" s="252"/>
+      <c r="Y16" s="252"/>
+      <c r="Z16" s="252"/>
+      <c r="AA16" s="252"/>
+      <c r="AB16" s="252"/>
+      <c r="AC16" s="252"/>
+      <c r="AD16" s="253"/>
     </row>
     <row r="19" spans="3:21" s="156" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C19" s="166" t="s">
@@ -32696,7 +32696,7 @@
       <c r="D30" s="162">
         <v>7</v>
       </c>
-      <c r="E30" s="173" t="s">
+      <c r="E30" s="371" t="s">
         <v>720</v>
       </c>
       <c r="F30" s="163"/>
@@ -33035,11 +33035,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="K15:AD15"/>
-    <mergeCell ref="K16:AD16"/>
-    <mergeCell ref="D15:J15"/>
-    <mergeCell ref="D16:J16"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
@@ -33056,6 +33051,11 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="K15:AD15"/>
+    <mergeCell ref="K16:AD16"/>
+    <mergeCell ref="D15:J15"/>
+    <mergeCell ref="D16:J16"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <hyperlinks>
@@ -33101,157 +33101,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="249" t="s">
+      <c r="A1" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="250"/>
-      <c r="C1" s="250"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
-      <c r="L1" s="253"/>
-      <c r="M1" s="253"/>
-      <c r="N1" s="254"/>
-      <c r="O1" s="258" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="260"/>
-      <c r="S1" s="267" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="268"/>
-      <c r="U1" s="268"/>
-      <c r="V1" s="268"/>
-      <c r="W1" s="268"/>
-      <c r="X1" s="268"/>
-      <c r="Y1" s="268"/>
-      <c r="Z1" s="269"/>
-      <c r="AA1" s="249" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="251"/>
-      <c r="AC1" s="255" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="256"/>
-      <c r="AE1" s="256"/>
-      <c r="AF1" s="257"/>
-      <c r="AG1" s="301">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="284">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45565</v>
-      </c>
-      <c r="AH1" s="302"/>
-      <c r="AI1" s="303"/>
+        <v>43336</v>
+      </c>
+      <c r="AH1" s="285"/>
+      <c r="AI1" s="286"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="249" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="250"/>
-      <c r="C2" s="250"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="253"/>
-      <c r="N2" s="254"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="271"/>
-      <c r="U2" s="271"/>
-      <c r="V2" s="271"/>
-      <c r="W2" s="271"/>
-      <c r="X2" s="271"/>
-      <c r="Y2" s="271"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="249" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="255" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="256"/>
-      <c r="AE2" s="256"/>
-      <c r="AF2" s="257"/>
-      <c r="AG2" s="301" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="302"/>
-      <c r="AI2" s="303"/>
+      <c r="AH2" s="285"/>
+      <c r="AI2" s="286"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="249" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="250"/>
-      <c r="C3" s="250"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="252" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="254"/>
-      <c r="O3" s="264"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="274"/>
-      <c r="U3" s="274"/>
-      <c r="V3" s="274"/>
-      <c r="W3" s="274"/>
-      <c r="X3" s="274"/>
-      <c r="Y3" s="274"/>
-      <c r="Z3" s="275"/>
-      <c r="AA3" s="249"/>
-      <c r="AB3" s="251"/>
-      <c r="AC3" s="255" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="256"/>
-      <c r="AE3" s="256"/>
-      <c r="AF3" s="257"/>
-      <c r="AG3" s="301" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="302"/>
-      <c r="AI3" s="303"/>
+      <c r="AH3" s="285"/>
+      <c r="AI3" s="286"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -33367,12 +33367,12 @@
       <c r="V20" s="30"/>
     </row>
     <row r="21" spans="4:23" x14ac:dyDescent="0.15">
-      <c r="F21" s="285" t="s">
+      <c r="F21" s="287" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="286"/>
-      <c r="H21" s="286"/>
-      <c r="I21" s="287"/>
+      <c r="G21" s="288"/>
+      <c r="H21" s="288"/>
+      <c r="I21" s="289"/>
       <c r="J21" s="58" t="s">
         <v>26</v>
       </c>
@@ -34785,17 +34785,17 @@
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="30"/>
-      <c r="G63" s="298" t="s">
+      <c r="G63" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="299"/>
-      <c r="I63" s="299"/>
-      <c r="J63" s="300"/>
-      <c r="K63" s="276" t="s">
+      <c r="H63" s="301"/>
+      <c r="I63" s="301"/>
+      <c r="J63" s="302"/>
+      <c r="K63" s="248" t="s">
         <v>69</v>
       </c>
-      <c r="L63" s="277"/>
-      <c r="M63" s="278"/>
+      <c r="L63" s="249"/>
+      <c r="M63" s="250"/>
       <c r="N63" s="58" t="s">
         <v>198</v>
       </c>
@@ -34837,17 +34837,17 @@
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
       <c r="F64" s="29"/>
-      <c r="G64" s="288" t="s">
+      <c r="G64" s="290" t="s">
         <v>566</v>
       </c>
-      <c r="H64" s="289"/>
-      <c r="I64" s="289"/>
-      <c r="J64" s="290"/>
-      <c r="K64" s="288" t="s">
+      <c r="H64" s="291"/>
+      <c r="I64" s="291"/>
+      <c r="J64" s="292"/>
+      <c r="K64" s="290" t="s">
         <v>567</v>
       </c>
-      <c r="L64" s="289"/>
-      <c r="M64" s="290"/>
+      <c r="L64" s="291"/>
+      <c r="M64" s="292"/>
       <c r="N64" s="64" t="s">
         <v>396</v>
       </c>
@@ -34889,13 +34889,13 @@
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="29"/>
-      <c r="G65" s="291"/>
-      <c r="H65" s="292"/>
-      <c r="I65" s="292"/>
-      <c r="J65" s="293"/>
-      <c r="K65" s="297"/>
-      <c r="L65" s="292"/>
-      <c r="M65" s="293"/>
+      <c r="G65" s="293"/>
+      <c r="H65" s="294"/>
+      <c r="I65" s="294"/>
+      <c r="J65" s="295"/>
+      <c r="K65" s="299"/>
+      <c r="L65" s="294"/>
+      <c r="M65" s="295"/>
       <c r="N65" s="54" t="s">
         <v>397</v>
       </c>
@@ -34937,13 +34937,13 @@
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
       <c r="F66" s="29"/>
-      <c r="G66" s="291"/>
-      <c r="H66" s="292"/>
-      <c r="I66" s="292"/>
-      <c r="J66" s="293"/>
-      <c r="K66" s="291"/>
-      <c r="L66" s="292"/>
-      <c r="M66" s="293"/>
+      <c r="G66" s="293"/>
+      <c r="H66" s="294"/>
+      <c r="I66" s="294"/>
+      <c r="J66" s="295"/>
+      <c r="K66" s="293"/>
+      <c r="L66" s="294"/>
+      <c r="M66" s="295"/>
       <c r="N66" s="54" t="s">
         <v>390</v>
       </c>
@@ -34985,13 +34985,13 @@
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
       <c r="F67" s="29"/>
-      <c r="G67" s="291"/>
-      <c r="H67" s="292"/>
-      <c r="I67" s="292"/>
-      <c r="J67" s="293"/>
-      <c r="K67" s="291"/>
-      <c r="L67" s="292"/>
-      <c r="M67" s="293"/>
+      <c r="G67" s="293"/>
+      <c r="H67" s="294"/>
+      <c r="I67" s="294"/>
+      <c r="J67" s="295"/>
+      <c r="K67" s="293"/>
+      <c r="L67" s="294"/>
+      <c r="M67" s="295"/>
       <c r="N67" s="54" t="s">
         <v>633</v>
       </c>
@@ -35033,13 +35033,13 @@
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68"/>
-      <c r="G68" s="294"/>
-      <c r="H68" s="295"/>
-      <c r="I68" s="295"/>
-      <c r="J68" s="296"/>
-      <c r="K68" s="294"/>
-      <c r="L68" s="295"/>
-      <c r="M68" s="296"/>
+      <c r="G68" s="296"/>
+      <c r="H68" s="297"/>
+      <c r="I68" s="297"/>
+      <c r="J68" s="298"/>
+      <c r="K68" s="296"/>
+      <c r="L68" s="297"/>
+      <c r="M68" s="298"/>
       <c r="N68" s="73"/>
       <c r="O68" s="74"/>
       <c r="P68" s="74"/>
@@ -35424,6 +35424,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="G64:J68"/>
+    <mergeCell ref="K64:M68"/>
+    <mergeCell ref="G63:J63"/>
+    <mergeCell ref="K63:M63"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
@@ -35440,12 +35446,6 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="G64:J68"/>
-    <mergeCell ref="K64:M68"/>
-    <mergeCell ref="G63:J63"/>
-    <mergeCell ref="K63:M63"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -35475,157 +35475,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="249" t="s">
+      <c r="A1" s="257" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="250"/>
-      <c r="C1" s="250"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
-      <c r="L1" s="253"/>
-      <c r="M1" s="253"/>
-      <c r="N1" s="254"/>
-      <c r="O1" s="304" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="303" t="s">
         <v>96</v>
       </c>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="305"/>
-      <c r="S1" s="306" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="304"/>
+      <c r="S1" s="305" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="268"/>
-      <c r="U1" s="268"/>
-      <c r="V1" s="268"/>
-      <c r="W1" s="268"/>
-      <c r="X1" s="268"/>
-      <c r="Y1" s="268"/>
-      <c r="Z1" s="307"/>
-      <c r="AA1" s="249" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="306"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="251"/>
-      <c r="AC1" s="255" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="256"/>
-      <c r="AE1" s="256"/>
-      <c r="AF1" s="257"/>
-      <c r="AG1" s="301">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="284">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45565</v>
-      </c>
-      <c r="AH1" s="302"/>
-      <c r="AI1" s="303"/>
+        <v>43336</v>
+      </c>
+      <c r="AH1" s="285"/>
+      <c r="AI1" s="286"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="249" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="250"/>
-      <c r="C2" s="250"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="253"/>
-      <c r="N2" s="254"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="271"/>
-      <c r="U2" s="271"/>
-      <c r="V2" s="271"/>
-      <c r="W2" s="271"/>
-      <c r="X2" s="271"/>
-      <c r="Y2" s="271"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="249" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="255" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="256"/>
-      <c r="AE2" s="256"/>
-      <c r="AF2" s="257"/>
-      <c r="AG2" s="301" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="302"/>
-      <c r="AI2" s="303"/>
+      <c r="AH2" s="285"/>
+      <c r="AI2" s="286"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="249" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="250"/>
-      <c r="C3" s="250"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="252" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="254"/>
-      <c r="O3" s="264"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="274"/>
-      <c r="U3" s="274"/>
-      <c r="V3" s="274"/>
-      <c r="W3" s="274"/>
-      <c r="X3" s="274"/>
-      <c r="Y3" s="274"/>
-      <c r="Z3" s="275"/>
-      <c r="AA3" s="249"/>
-      <c r="AB3" s="251"/>
-      <c r="AC3" s="255" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="256"/>
-      <c r="AE3" s="256"/>
-      <c r="AF3" s="257"/>
-      <c r="AG3" s="301" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="302"/>
-      <c r="AI3" s="303"/>
+      <c r="AH3" s="285"/>
+      <c r="AI3" s="286"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -35659,41 +35659,41 @@
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="E14" s="298" t="s">
+      <c r="E14" s="300" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="299"/>
-      <c r="G14" s="299"/>
-      <c r="H14" s="299"/>
-      <c r="I14" s="299"/>
-      <c r="J14" s="300"/>
-      <c r="K14" s="298" t="s">
+      <c r="F14" s="301"/>
+      <c r="G14" s="301"/>
+      <c r="H14" s="301"/>
+      <c r="I14" s="301"/>
+      <c r="J14" s="302"/>
+      <c r="K14" s="300" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="299"/>
-      <c r="M14" s="299"/>
-      <c r="N14" s="299"/>
-      <c r="O14" s="299"/>
-      <c r="P14" s="299"/>
-      <c r="Q14" s="299"/>
-      <c r="R14" s="299"/>
-      <c r="S14" s="300"/>
-      <c r="T14" s="298" t="s">
+      <c r="L14" s="301"/>
+      <c r="M14" s="301"/>
+      <c r="N14" s="301"/>
+      <c r="O14" s="301"/>
+      <c r="P14" s="301"/>
+      <c r="Q14" s="301"/>
+      <c r="R14" s="301"/>
+      <c r="S14" s="302"/>
+      <c r="T14" s="300" t="s">
         <v>94</v>
       </c>
-      <c r="U14" s="299"/>
-      <c r="V14" s="299"/>
-      <c r="W14" s="299"/>
-      <c r="X14" s="299"/>
-      <c r="Y14" s="299"/>
-      <c r="Z14" s="299"/>
-      <c r="AA14" s="299"/>
-      <c r="AB14" s="299"/>
-      <c r="AC14" s="299"/>
-      <c r="AD14" s="299"/>
-      <c r="AE14" s="299"/>
-      <c r="AF14" s="299"/>
-      <c r="AG14" s="300"/>
+      <c r="U14" s="301"/>
+      <c r="V14" s="301"/>
+      <c r="W14" s="301"/>
+      <c r="X14" s="301"/>
+      <c r="Y14" s="301"/>
+      <c r="Z14" s="301"/>
+      <c r="AA14" s="301"/>
+      <c r="AB14" s="301"/>
+      <c r="AC14" s="301"/>
+      <c r="AD14" s="301"/>
+      <c r="AE14" s="301"/>
+      <c r="AF14" s="301"/>
+      <c r="AG14" s="302"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.15">
       <c r="E15" s="80" t="s">
@@ -38335,6 +38335,11 @@
     <row r="346" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="E14:J14"/>
+    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -38350,11 +38355,6 @@
     <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="K14:S14"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AG1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>
@@ -38396,151 +38396,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="249" t="s">
+      <c r="A1" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="250"/>
-      <c r="C1" s="250"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
-      <c r="L1" s="253"/>
-      <c r="M1" s="253"/>
-      <c r="N1" s="254"/>
-      <c r="O1" s="258" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="266" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="260"/>
-      <c r="S1" s="267" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="268"/>
-      <c r="U1" s="268"/>
-      <c r="V1" s="268"/>
-      <c r="W1" s="268"/>
-      <c r="X1" s="268"/>
-      <c r="Y1" s="268"/>
-      <c r="Z1" s="269"/>
-      <c r="AA1" s="249" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="251"/>
-      <c r="AC1" s="255" t="str">
+      <c r="AB1" s="259"/>
+      <c r="AC1" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="256"/>
-      <c r="AE1" s="256"/>
-      <c r="AF1" s="257"/>
-      <c r="AG1" s="301">
+      <c r="AD1" s="264"/>
+      <c r="AE1" s="264"/>
+      <c r="AF1" s="265"/>
+      <c r="AG1" s="284">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45565</v>
-      </c>
-      <c r="AH1" s="302"/>
-      <c r="AI1" s="303"/>
+        <v>43336</v>
+      </c>
+      <c r="AH1" s="285"/>
+      <c r="AI1" s="286"/>
     </row>
     <row r="2" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="249" t="s">
+      <c r="A2" s="257" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="250"/>
-      <c r="C2" s="250"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="253"/>
-      <c r="N2" s="254"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="271"/>
-      <c r="U2" s="271"/>
-      <c r="V2" s="271"/>
-      <c r="W2" s="271"/>
-      <c r="X2" s="271"/>
-      <c r="Y2" s="271"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="249" t="s">
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="255" t="str">
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="256"/>
-      <c r="AE2" s="256"/>
-      <c r="AF2" s="257"/>
-      <c r="AG2" s="301" t="str">
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="265"/>
+      <c r="AG2" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="302"/>
-      <c r="AI2" s="303"/>
+      <c r="AH2" s="285"/>
+      <c r="AI2" s="286"/>
     </row>
     <row r="3" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="249" t="s">
+      <c r="A3" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="250"/>
-      <c r="C3" s="250"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="252" t="str">
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="260" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="254"/>
-      <c r="O3" s="264"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="274"/>
-      <c r="U3" s="274"/>
-      <c r="V3" s="274"/>
-      <c r="W3" s="274"/>
-      <c r="X3" s="274"/>
-      <c r="Y3" s="274"/>
-      <c r="Z3" s="275"/>
-      <c r="AA3" s="249"/>
-      <c r="AB3" s="251"/>
-      <c r="AC3" s="255" t="str">
+      <c r="F3" s="261"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="257"/>
+      <c r="AB3" s="259"/>
+      <c r="AC3" s="263" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="256"/>
-      <c r="AE3" s="256"/>
-      <c r="AF3" s="257"/>
-      <c r="AG3" s="301" t="str">
+      <c r="AD3" s="264"/>
+      <c r="AE3" s="264"/>
+      <c r="AF3" s="265"/>
+      <c r="AG3" s="284" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="302"/>
-      <c r="AI3" s="303"/>
+      <c r="AH3" s="285"/>
+      <c r="AI3" s="286"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B5" s="32" t="s">
@@ -39644,12 +39644,12 @@
     <row r="74" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A74" s="30"/>
       <c r="E74" s="30"/>
-      <c r="F74" s="276" t="s">
+      <c r="F74" s="248" t="s">
         <v>50</v>
       </c>
-      <c r="G74" s="277"/>
-      <c r="H74" s="277"/>
-      <c r="I74" s="278"/>
+      <c r="G74" s="249"/>
+      <c r="H74" s="249"/>
+      <c r="I74" s="250"/>
       <c r="J74" s="58" t="s">
         <v>190</v>
       </c>
@@ -39678,12 +39678,12 @@
     <row r="75" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="30"/>
       <c r="E75" s="30"/>
-      <c r="F75" s="310" t="s">
+      <c r="F75" s="307" t="s">
         <v>229</v>
       </c>
-      <c r="G75" s="311"/>
-      <c r="H75" s="311"/>
-      <c r="I75" s="312"/>
+      <c r="G75" s="308"/>
+      <c r="H75" s="308"/>
+      <c r="I75" s="309"/>
       <c r="J75" s="83" t="s">
         <v>237</v>
       </c>
@@ -39713,12 +39713,12 @@
       <c r="A76" s="30"/>
       <c r="C76" s="30"/>
       <c r="E76" s="30"/>
-      <c r="F76" s="317" t="s">
+      <c r="F76" s="310" t="s">
         <v>330</v>
       </c>
-      <c r="G76" s="318"/>
-      <c r="H76" s="318"/>
-      <c r="I76" s="319"/>
+      <c r="G76" s="311"/>
+      <c r="H76" s="311"/>
+      <c r="I76" s="312"/>
       <c r="J76" s="72" t="s">
         <v>191</v>
       </c>
@@ -39748,10 +39748,10 @@
       <c r="A77" s="30"/>
       <c r="C77" s="30"/>
       <c r="E77" s="30"/>
-      <c r="F77" s="320"/>
-      <c r="G77" s="321"/>
-      <c r="H77" s="321"/>
-      <c r="I77" s="322"/>
+      <c r="F77" s="313"/>
+      <c r="G77" s="314"/>
+      <c r="H77" s="314"/>
+      <c r="I77" s="315"/>
       <c r="J77" s="73"/>
       <c r="K77" s="74"/>
       <c r="L77" s="74"/>
@@ -39776,12 +39776,12 @@
     <row r="78" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A78" s="30"/>
       <c r="E78" s="30"/>
-      <c r="F78" s="310" t="s">
+      <c r="F78" s="307" t="s">
         <v>230</v>
       </c>
-      <c r="G78" s="311"/>
-      <c r="H78" s="311"/>
-      <c r="I78" s="312"/>
+      <c r="G78" s="308"/>
+      <c r="H78" s="308"/>
+      <c r="I78" s="309"/>
       <c r="J78" s="80" t="s">
         <v>192</v>
       </c>
@@ -39810,12 +39810,12 @@
     <row r="79" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A79" s="30"/>
       <c r="E79" s="30"/>
-      <c r="F79" s="310" t="s">
+      <c r="F79" s="307" t="s">
         <v>228</v>
       </c>
-      <c r="G79" s="311"/>
-      <c r="H79" s="311"/>
-      <c r="I79" s="312"/>
+      <c r="G79" s="308"/>
+      <c r="H79" s="308"/>
+      <c r="I79" s="309"/>
       <c r="J79" s="83" t="s">
         <v>195</v>
       </c>
@@ -39845,12 +39845,12 @@
     <row r="80" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A80" s="30"/>
       <c r="E80" s="30"/>
-      <c r="F80" s="310" t="s">
+      <c r="F80" s="307" t="s">
         <v>227</v>
       </c>
-      <c r="G80" s="311"/>
-      <c r="H80" s="311"/>
-      <c r="I80" s="312"/>
+      <c r="G80" s="308"/>
+      <c r="H80" s="308"/>
+      <c r="I80" s="309"/>
       <c r="J80" s="80" t="s">
         <v>193</v>
       </c>
@@ -39996,7 +39996,7 @@
       <c r="AG137" s="51"/>
     </row>
     <row r="138" spans="5:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F138" s="313">
+      <c r="F138" s="318">
         <v>1</v>
       </c>
       <c r="G138" s="64" t="s">
@@ -40032,7 +40032,7 @@
       <c r="AG138" s="51"/>
     </row>
     <row r="139" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F139" s="314"/>
+      <c r="F139" s="319"/>
       <c r="G139" s="54"/>
       <c r="H139" s="30"/>
       <c r="I139" s="30"/>
@@ -40064,7 +40064,7 @@
       <c r="AG139" s="51"/>
     </row>
     <row r="140" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F140" s="314"/>
+      <c r="F140" s="319"/>
       <c r="G140" s="54"/>
       <c r="H140" s="30"/>
       <c r="I140" s="30"/>
@@ -40096,7 +40096,7 @@
       <c r="AG140" s="51"/>
     </row>
     <row r="141" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F141" s="314"/>
+      <c r="F141" s="319"/>
       <c r="G141" s="54"/>
       <c r="H141" s="30"/>
       <c r="I141" s="30"/>
@@ -40128,7 +40128,7 @@
       <c r="AG141" s="51"/>
     </row>
     <row r="142" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F142" s="314"/>
+      <c r="F142" s="319"/>
       <c r="G142" s="54"/>
       <c r="H142" s="30"/>
       <c r="I142" s="30"/>
@@ -40160,7 +40160,7 @@
       <c r="AG142" s="51"/>
     </row>
     <row r="143" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F143" s="314"/>
+      <c r="F143" s="319"/>
       <c r="G143" s="54"/>
       <c r="H143" s="30"/>
       <c r="I143" s="30"/>
@@ -40192,7 +40192,7 @@
       <c r="AG143" s="51"/>
     </row>
     <row r="144" spans="5:33" x14ac:dyDescent="0.15">
-      <c r="F144" s="314"/>
+      <c r="F144" s="319"/>
       <c r="G144" s="54"/>
       <c r="H144" s="30"/>
       <c r="I144" s="30"/>
@@ -40224,7 +40224,7 @@
       <c r="AG144" s="51"/>
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F145" s="315"/>
+      <c r="F145" s="320"/>
       <c r="G145" s="54"/>
       <c r="H145" s="30"/>
       <c r="I145" s="30"/>
@@ -40322,7 +40322,7 @@
       <c r="AG147" s="17"/>
     </row>
     <row r="148" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F148" s="313">
+      <c r="F148" s="318">
         <v>3</v>
       </c>
       <c r="G148" s="54" t="s">
@@ -40358,7 +40358,7 @@
       <c r="AG148" s="51"/>
     </row>
     <row r="149" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F149" s="314"/>
+      <c r="F149" s="319"/>
       <c r="G149" s="54"/>
       <c r="H149" s="30"/>
       <c r="I149" s="30"/>
@@ -40390,7 +40390,7 @@
       <c r="AG149" s="51"/>
     </row>
     <row r="150" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F150" s="314"/>
+      <c r="F150" s="319"/>
       <c r="G150" s="54"/>
       <c r="H150" s="30"/>
       <c r="I150" s="30"/>
@@ -40422,7 +40422,7 @@
       <c r="AG150" s="51"/>
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F151" s="314"/>
+      <c r="F151" s="319"/>
       <c r="G151" s="54"/>
       <c r="H151" s="30"/>
       <c r="I151" s="30"/>
@@ -40454,7 +40454,7 @@
       <c r="AG151" s="51"/>
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F152" s="314"/>
+      <c r="F152" s="319"/>
       <c r="G152" s="54"/>
       <c r="H152" s="30"/>
       <c r="I152" s="30"/>
@@ -40486,7 +40486,7 @@
       <c r="AG152" s="51"/>
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F153" s="315"/>
+      <c r="F153" s="320"/>
       <c r="G153" s="54"/>
       <c r="H153" s="30"/>
       <c r="I153" s="30"/>
@@ -40518,7 +40518,7 @@
       <c r="AG153" s="51"/>
     </row>
     <row r="154" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F154" s="316">
+      <c r="F154" s="321">
         <v>4</v>
       </c>
       <c r="G154" s="64" t="s">
@@ -40554,7 +40554,7 @@
       <c r="AG154" s="51"/>
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="F155" s="316"/>
+      <c r="F155" s="321"/>
       <c r="G155" s="73"/>
       <c r="H155" s="74"/>
       <c r="I155" s="74"/>
@@ -41027,7 +41027,7 @@
     </row>
     <row r="228" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A228" s="30"/>
-      <c r="F228" s="308"/>
+      <c r="F228" s="316"/>
       <c r="G228" s="83" t="s">
         <v>239</v>
       </c>
@@ -41064,7 +41064,7 @@
       <c r="AD228" s="113"/>
     </row>
     <row r="229" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="F229" s="308"/>
+      <c r="F229" s="316"/>
       <c r="G229" s="83" t="s">
         <v>279</v>
       </c>
@@ -41101,7 +41101,7 @@
       <c r="AD229" s="113"/>
     </row>
     <row r="230" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="F230" s="309"/>
+      <c r="F230" s="317"/>
       <c r="G230" s="84" t="s">
         <v>280</v>
       </c>
@@ -41612,6 +41612,21 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="F228:F230"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F138:F145"/>
+    <mergeCell ref="F148:F153"/>
+    <mergeCell ref="F154:F155"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="F76:I77"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="AG3:AI3"/>
@@ -41624,21 +41639,6 @@
     <mergeCell ref="S1:Z3"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F74:I74"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="F76:I77"/>
-    <mergeCell ref="F228:F230"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F138:F145"/>
-    <mergeCell ref="F148:F153"/>
-    <mergeCell ref="F154:F155"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -41675,157 +41675,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="213"/>
-      <c r="O1" s="258" t="s">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="260"/>
-      <c r="S1" s="267" t="str">
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="268"/>
+      <c r="S1" s="275" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="268"/>
-      <c r="U1" s="268"/>
-      <c r="V1" s="268"/>
-      <c r="W1" s="268"/>
-      <c r="X1" s="268"/>
-      <c r="Y1" s="268"/>
-      <c r="Z1" s="269"/>
-      <c r="AA1" s="208" t="s">
+      <c r="T1" s="276"/>
+      <c r="U1" s="276"/>
+      <c r="V1" s="276"/>
+      <c r="W1" s="276"/>
+      <c r="X1" s="276"/>
+      <c r="Y1" s="276"/>
+      <c r="Z1" s="277"/>
+      <c r="AA1" s="180" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="210"/>
-      <c r="AC1" s="236" t="str">
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="237"/>
-      <c r="AE1" s="237"/>
-      <c r="AF1" s="238"/>
-      <c r="AG1" s="357">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="348">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45565</v>
-      </c>
-      <c r="AH1" s="358"/>
-      <c r="AI1" s="359"/>
+        <v>43336</v>
+      </c>
+      <c r="AH1" s="349"/>
+      <c r="AI1" s="350"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="209"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
-      <c r="M2" s="212"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="271"/>
-      <c r="U2" s="271"/>
-      <c r="V2" s="271"/>
-      <c r="W2" s="271"/>
-      <c r="X2" s="271"/>
-      <c r="Y2" s="271"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="208" t="s">
+      <c r="B2" s="181"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="184"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="185"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="280"/>
+      <c r="AA2" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="210"/>
-      <c r="AC2" s="236" t="str">
+      <c r="AB2" s="182"/>
+      <c r="AC2" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="237"/>
-      <c r="AF2" s="238"/>
-      <c r="AG2" s="357" t="str">
+      <c r="AD2" s="209"/>
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="210"/>
+      <c r="AG2" s="348" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="358"/>
-      <c r="AI2" s="359"/>
+      <c r="AH2" s="349"/>
+      <c r="AI2" s="350"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="209"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="239" t="str">
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="211" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="213"/>
-      <c r="O3" s="264"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="274"/>
-      <c r="U3" s="274"/>
-      <c r="V3" s="274"/>
-      <c r="W3" s="274"/>
-      <c r="X3" s="274"/>
-      <c r="Y3" s="274"/>
-      <c r="Z3" s="275"/>
-      <c r="AA3" s="208"/>
-      <c r="AB3" s="210"/>
-      <c r="AC3" s="236" t="str">
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+      <c r="M3" s="184"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="272"/>
+      <c r="P3" s="273"/>
+      <c r="Q3" s="273"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="281"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
+      <c r="W3" s="282"/>
+      <c r="X3" s="282"/>
+      <c r="Y3" s="282"/>
+      <c r="Z3" s="283"/>
+      <c r="AA3" s="180"/>
+      <c r="AB3" s="182"/>
+      <c r="AC3" s="208" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="237"/>
-      <c r="AE3" s="237"/>
-      <c r="AF3" s="238"/>
-      <c r="AG3" s="357" t="str">
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="348" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="358"/>
-      <c r="AI3" s="359"/>
+      <c r="AH3" s="349"/>
+      <c r="AI3" s="350"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -42308,477 +42308,477 @@
     </row>
     <row r="150" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="151" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D151" s="276" t="s">
+      <c r="D151" s="248" t="s">
         <v>325</v>
       </c>
-      <c r="E151" s="341"/>
-      <c r="F151" s="341"/>
-      <c r="G151" s="341"/>
-      <c r="H151" s="341"/>
-      <c r="I151" s="341"/>
-      <c r="J151" s="342"/>
-      <c r="K151" s="360" t="s">
+      <c r="E151" s="327"/>
+      <c r="F151" s="327"/>
+      <c r="G151" s="327"/>
+      <c r="H151" s="327"/>
+      <c r="I151" s="327"/>
+      <c r="J151" s="328"/>
+      <c r="K151" s="325" t="s">
         <v>50</v>
       </c>
-      <c r="L151" s="360"/>
-      <c r="M151" s="360"/>
-      <c r="N151" s="360"/>
-      <c r="O151" s="360"/>
-      <c r="P151" s="360"/>
-      <c r="Q151" s="360"/>
-      <c r="R151" s="360"/>
-      <c r="S151" s="360"/>
-      <c r="T151" s="360"/>
-      <c r="U151" s="360"/>
-      <c r="V151" s="360"/>
-      <c r="W151" s="360"/>
-      <c r="X151" s="360"/>
-      <c r="Y151" s="360"/>
-      <c r="Z151" s="360"/>
-      <c r="AA151" s="367" t="s">
+      <c r="L151" s="325"/>
+      <c r="M151" s="325"/>
+      <c r="N151" s="325"/>
+      <c r="O151" s="325"/>
+      <c r="P151" s="325"/>
+      <c r="Q151" s="325"/>
+      <c r="R151" s="325"/>
+      <c r="S151" s="325"/>
+      <c r="T151" s="325"/>
+      <c r="U151" s="325"/>
+      <c r="V151" s="325"/>
+      <c r="W151" s="325"/>
+      <c r="X151" s="325"/>
+      <c r="Y151" s="325"/>
+      <c r="Z151" s="325"/>
+      <c r="AA151" s="324" t="s">
         <v>51</v>
       </c>
-      <c r="AB151" s="360"/>
-      <c r="AC151" s="360"/>
-      <c r="AD151" s="360"/>
-      <c r="AE151" s="360"/>
-      <c r="AF151" s="360"/>
-      <c r="AG151" s="360"/>
-      <c r="AH151" s="360"/>
+      <c r="AB151" s="325"/>
+      <c r="AC151" s="325"/>
+      <c r="AD151" s="325"/>
+      <c r="AE151" s="325"/>
+      <c r="AF151" s="325"/>
+      <c r="AG151" s="325"/>
+      <c r="AH151" s="325"/>
     </row>
     <row r="152" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D152" s="279" t="s">
+      <c r="D152" s="251" t="s">
         <v>52</v>
       </c>
-      <c r="E152" s="280"/>
-      <c r="F152" s="280"/>
-      <c r="G152" s="280"/>
-      <c r="H152" s="280"/>
-      <c r="I152" s="280"/>
-      <c r="J152" s="281"/>
-      <c r="K152" s="356" t="s">
+      <c r="E152" s="252"/>
+      <c r="F152" s="252"/>
+      <c r="G152" s="252"/>
+      <c r="H152" s="252"/>
+      <c r="I152" s="252"/>
+      <c r="J152" s="253"/>
+      <c r="K152" s="347" t="s">
         <v>289</v>
       </c>
-      <c r="L152" s="356"/>
-      <c r="M152" s="356"/>
-      <c r="N152" s="356"/>
-      <c r="O152" s="356"/>
-      <c r="P152" s="356"/>
-      <c r="Q152" s="356"/>
-      <c r="R152" s="356"/>
-      <c r="S152" s="356"/>
-      <c r="T152" s="356"/>
-      <c r="U152" s="356"/>
-      <c r="V152" s="356"/>
-      <c r="W152" s="356"/>
-      <c r="X152" s="356"/>
-      <c r="Y152" s="356"/>
-      <c r="Z152" s="356"/>
-      <c r="AA152" s="361" t="s">
+      <c r="L152" s="347"/>
+      <c r="M152" s="347"/>
+      <c r="N152" s="347"/>
+      <c r="O152" s="347"/>
+      <c r="P152" s="347"/>
+      <c r="Q152" s="347"/>
+      <c r="R152" s="347"/>
+      <c r="S152" s="347"/>
+      <c r="T152" s="347"/>
+      <c r="U152" s="347"/>
+      <c r="V152" s="347"/>
+      <c r="W152" s="347"/>
+      <c r="X152" s="347"/>
+      <c r="Y152" s="347"/>
+      <c r="Z152" s="347"/>
+      <c r="AA152" s="322" t="s">
         <v>75</v>
       </c>
-      <c r="AB152" s="362"/>
-      <c r="AC152" s="362"/>
-      <c r="AD152" s="362"/>
-      <c r="AE152" s="362"/>
-      <c r="AF152" s="362"/>
-      <c r="AG152" s="362"/>
-      <c r="AH152" s="362"/>
+      <c r="AB152" s="323"/>
+      <c r="AC152" s="323"/>
+      <c r="AD152" s="323"/>
+      <c r="AE152" s="323"/>
+      <c r="AF152" s="323"/>
+      <c r="AG152" s="323"/>
+      <c r="AH152" s="323"/>
     </row>
     <row r="153" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D153" s="310" t="s">
+      <c r="D153" s="307" t="s">
         <v>304</v>
       </c>
-      <c r="E153" s="311"/>
-      <c r="F153" s="311"/>
-      <c r="G153" s="311"/>
-      <c r="H153" s="311"/>
-      <c r="I153" s="311"/>
-      <c r="J153" s="312"/>
-      <c r="K153" s="356" t="s">
+      <c r="E153" s="308"/>
+      <c r="F153" s="308"/>
+      <c r="G153" s="308"/>
+      <c r="H153" s="308"/>
+      <c r="I153" s="308"/>
+      <c r="J153" s="309"/>
+      <c r="K153" s="347" t="s">
         <v>290</v>
       </c>
-      <c r="L153" s="356"/>
-      <c r="M153" s="356"/>
-      <c r="N153" s="356"/>
-      <c r="O153" s="356"/>
-      <c r="P153" s="356"/>
-      <c r="Q153" s="356"/>
-      <c r="R153" s="356"/>
-      <c r="S153" s="356"/>
-      <c r="T153" s="356"/>
-      <c r="U153" s="356"/>
-      <c r="V153" s="356"/>
-      <c r="W153" s="356"/>
-      <c r="X153" s="356"/>
-      <c r="Y153" s="356"/>
-      <c r="Z153" s="356"/>
-      <c r="AA153" s="361" t="s">
+      <c r="L153" s="347"/>
+      <c r="M153" s="347"/>
+      <c r="N153" s="347"/>
+      <c r="O153" s="347"/>
+      <c r="P153" s="347"/>
+      <c r="Q153" s="347"/>
+      <c r="R153" s="347"/>
+      <c r="S153" s="347"/>
+      <c r="T153" s="347"/>
+      <c r="U153" s="347"/>
+      <c r="V153" s="347"/>
+      <c r="W153" s="347"/>
+      <c r="X153" s="347"/>
+      <c r="Y153" s="347"/>
+      <c r="Z153" s="347"/>
+      <c r="AA153" s="322" t="s">
         <v>75</v>
       </c>
-      <c r="AB153" s="362"/>
-      <c r="AC153" s="362"/>
-      <c r="AD153" s="362"/>
-      <c r="AE153" s="362"/>
-      <c r="AF153" s="362"/>
-      <c r="AG153" s="362"/>
-      <c r="AH153" s="362"/>
+      <c r="AB153" s="323"/>
+      <c r="AC153" s="323"/>
+      <c r="AD153" s="323"/>
+      <c r="AE153" s="323"/>
+      <c r="AF153" s="323"/>
+      <c r="AG153" s="323"/>
+      <c r="AH153" s="323"/>
     </row>
     <row r="154" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D154" s="371" t="s">
+      <c r="D154" s="333" t="s">
         <v>320</v>
       </c>
-      <c r="E154" s="283"/>
-      <c r="F154" s="283"/>
-      <c r="G154" s="283"/>
-      <c r="H154" s="283"/>
-      <c r="I154" s="283"/>
-      <c r="J154" s="284"/>
-      <c r="K154" s="363" t="s">
+      <c r="E154" s="255"/>
+      <c r="F154" s="255"/>
+      <c r="G154" s="255"/>
+      <c r="H154" s="255"/>
+      <c r="I154" s="255"/>
+      <c r="J154" s="256"/>
+      <c r="K154" s="335" t="s">
         <v>322</v>
       </c>
-      <c r="L154" s="364"/>
-      <c r="M154" s="364"/>
-      <c r="N154" s="364"/>
-      <c r="O154" s="364"/>
-      <c r="P154" s="364"/>
-      <c r="Q154" s="364"/>
-      <c r="R154" s="364"/>
-      <c r="S154" s="364"/>
-      <c r="T154" s="364"/>
-      <c r="U154" s="364"/>
-      <c r="V154" s="364"/>
-      <c r="W154" s="364"/>
-      <c r="X154" s="364"/>
-      <c r="Y154" s="364"/>
-      <c r="Z154" s="350"/>
-      <c r="AA154" s="363" t="s">
+      <c r="L154" s="336"/>
+      <c r="M154" s="336"/>
+      <c r="N154" s="336"/>
+      <c r="O154" s="336"/>
+      <c r="P154" s="336"/>
+      <c r="Q154" s="336"/>
+      <c r="R154" s="336"/>
+      <c r="S154" s="336"/>
+      <c r="T154" s="336"/>
+      <c r="U154" s="336"/>
+      <c r="V154" s="336"/>
+      <c r="W154" s="336"/>
+      <c r="X154" s="336"/>
+      <c r="Y154" s="336"/>
+      <c r="Z154" s="337"/>
+      <c r="AA154" s="335" t="s">
         <v>321</v>
       </c>
-      <c r="AB154" s="364"/>
-      <c r="AC154" s="364"/>
-      <c r="AD154" s="364"/>
-      <c r="AE154" s="364"/>
-      <c r="AF154" s="364"/>
-      <c r="AG154" s="364"/>
-      <c r="AH154" s="350"/>
+      <c r="AB154" s="336"/>
+      <c r="AC154" s="336"/>
+      <c r="AD154" s="336"/>
+      <c r="AE154" s="336"/>
+      <c r="AF154" s="336"/>
+      <c r="AG154" s="336"/>
+      <c r="AH154" s="337"/>
     </row>
     <row r="155" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D155" s="369"/>
-      <c r="E155" s="347" t="s">
+      <c r="D155" s="331"/>
+      <c r="E155" s="334" t="s">
         <v>324</v>
       </c>
-      <c r="F155" s="286"/>
-      <c r="G155" s="286"/>
-      <c r="H155" s="286"/>
-      <c r="I155" s="286"/>
-      <c r="J155" s="287"/>
-      <c r="K155" s="356" t="s">
+      <c r="F155" s="288"/>
+      <c r="G155" s="288"/>
+      <c r="H155" s="288"/>
+      <c r="I155" s="288"/>
+      <c r="J155" s="289"/>
+      <c r="K155" s="347" t="s">
         <v>163</v>
       </c>
-      <c r="L155" s="356"/>
-      <c r="M155" s="356"/>
-      <c r="N155" s="356"/>
-      <c r="O155" s="356"/>
-      <c r="P155" s="356"/>
-      <c r="Q155" s="356"/>
-      <c r="R155" s="356"/>
-      <c r="S155" s="356"/>
-      <c r="T155" s="356"/>
-      <c r="U155" s="356"/>
-      <c r="V155" s="356"/>
-      <c r="W155" s="356"/>
-      <c r="X155" s="356"/>
-      <c r="Y155" s="356"/>
-      <c r="Z155" s="356"/>
-      <c r="AA155" s="355" t="s">
+      <c r="L155" s="347"/>
+      <c r="M155" s="347"/>
+      <c r="N155" s="347"/>
+      <c r="O155" s="347"/>
+      <c r="P155" s="347"/>
+      <c r="Q155" s="347"/>
+      <c r="R155" s="347"/>
+      <c r="S155" s="347"/>
+      <c r="T155" s="347"/>
+      <c r="U155" s="347"/>
+      <c r="V155" s="347"/>
+      <c r="W155" s="347"/>
+      <c r="X155" s="347"/>
+      <c r="Y155" s="347"/>
+      <c r="Z155" s="347"/>
+      <c r="AA155" s="346" t="s">
         <v>326</v>
       </c>
-      <c r="AB155" s="356"/>
-      <c r="AC155" s="356"/>
-      <c r="AD155" s="356"/>
-      <c r="AE155" s="356"/>
-      <c r="AF155" s="356"/>
-      <c r="AG155" s="356"/>
-      <c r="AH155" s="356"/>
+      <c r="AB155" s="347"/>
+      <c r="AC155" s="347"/>
+      <c r="AD155" s="347"/>
+      <c r="AE155" s="347"/>
+      <c r="AF155" s="347"/>
+      <c r="AG155" s="347"/>
+      <c r="AH155" s="347"/>
     </row>
     <row r="156" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D156" s="369"/>
-      <c r="E156" s="347"/>
-      <c r="F156" s="286"/>
-      <c r="G156" s="286"/>
-      <c r="H156" s="286"/>
-      <c r="I156" s="286"/>
-      <c r="J156" s="287"/>
-      <c r="K156" s="356" t="s">
+      <c r="D156" s="331"/>
+      <c r="E156" s="334"/>
+      <c r="F156" s="288"/>
+      <c r="G156" s="288"/>
+      <c r="H156" s="288"/>
+      <c r="I156" s="288"/>
+      <c r="J156" s="289"/>
+      <c r="K156" s="347" t="s">
         <v>70</v>
       </c>
-      <c r="L156" s="356"/>
-      <c r="M156" s="356"/>
-      <c r="N156" s="356"/>
-      <c r="O156" s="356"/>
-      <c r="P156" s="356"/>
-      <c r="Q156" s="356"/>
-      <c r="R156" s="356"/>
-      <c r="S156" s="356"/>
-      <c r="T156" s="356"/>
-      <c r="U156" s="356"/>
-      <c r="V156" s="356"/>
-      <c r="W156" s="356"/>
-      <c r="X156" s="356"/>
-      <c r="Y156" s="356"/>
-      <c r="Z156" s="356"/>
-      <c r="AA156" s="361" t="s">
+      <c r="L156" s="347"/>
+      <c r="M156" s="347"/>
+      <c r="N156" s="347"/>
+      <c r="O156" s="347"/>
+      <c r="P156" s="347"/>
+      <c r="Q156" s="347"/>
+      <c r="R156" s="347"/>
+      <c r="S156" s="347"/>
+      <c r="T156" s="347"/>
+      <c r="U156" s="347"/>
+      <c r="V156" s="347"/>
+      <c r="W156" s="347"/>
+      <c r="X156" s="347"/>
+      <c r="Y156" s="347"/>
+      <c r="Z156" s="347"/>
+      <c r="AA156" s="322" t="s">
         <v>283</v>
       </c>
-      <c r="AB156" s="356"/>
-      <c r="AC156" s="356"/>
-      <c r="AD156" s="356"/>
-      <c r="AE156" s="356"/>
-      <c r="AF156" s="356"/>
-      <c r="AG156" s="356"/>
-      <c r="AH156" s="356"/>
+      <c r="AB156" s="347"/>
+      <c r="AC156" s="347"/>
+      <c r="AD156" s="347"/>
+      <c r="AE156" s="347"/>
+      <c r="AF156" s="347"/>
+      <c r="AG156" s="347"/>
+      <c r="AH156" s="347"/>
     </row>
     <row r="157" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D157" s="369"/>
-      <c r="E157" s="347"/>
-      <c r="F157" s="286"/>
-      <c r="G157" s="286"/>
-      <c r="H157" s="286"/>
-      <c r="I157" s="286"/>
-      <c r="J157" s="287"/>
-      <c r="K157" s="356"/>
-      <c r="L157" s="356"/>
-      <c r="M157" s="356"/>
-      <c r="N157" s="356"/>
-      <c r="O157" s="356"/>
-      <c r="P157" s="356"/>
-      <c r="Q157" s="356"/>
-      <c r="R157" s="356"/>
-      <c r="S157" s="356"/>
-      <c r="T157" s="356"/>
-      <c r="U157" s="356"/>
-      <c r="V157" s="356"/>
-      <c r="W157" s="356"/>
-      <c r="X157" s="356"/>
-      <c r="Y157" s="356"/>
-      <c r="Z157" s="356"/>
-      <c r="AA157" s="356"/>
-      <c r="AB157" s="356"/>
-      <c r="AC157" s="356"/>
-      <c r="AD157" s="356"/>
-      <c r="AE157" s="356"/>
-      <c r="AF157" s="356"/>
-      <c r="AG157" s="356"/>
-      <c r="AH157" s="356"/>
+      <c r="D157" s="331"/>
+      <c r="E157" s="334"/>
+      <c r="F157" s="288"/>
+      <c r="G157" s="288"/>
+      <c r="H157" s="288"/>
+      <c r="I157" s="288"/>
+      <c r="J157" s="289"/>
+      <c r="K157" s="347"/>
+      <c r="L157" s="347"/>
+      <c r="M157" s="347"/>
+      <c r="N157" s="347"/>
+      <c r="O157" s="347"/>
+      <c r="P157" s="347"/>
+      <c r="Q157" s="347"/>
+      <c r="R157" s="347"/>
+      <c r="S157" s="347"/>
+      <c r="T157" s="347"/>
+      <c r="U157" s="347"/>
+      <c r="V157" s="347"/>
+      <c r="W157" s="347"/>
+      <c r="X157" s="347"/>
+      <c r="Y157" s="347"/>
+      <c r="Z157" s="347"/>
+      <c r="AA157" s="347"/>
+      <c r="AB157" s="347"/>
+      <c r="AC157" s="347"/>
+      <c r="AD157" s="347"/>
+      <c r="AE157" s="347"/>
+      <c r="AF157" s="347"/>
+      <c r="AG157" s="347"/>
+      <c r="AH157" s="347"/>
     </row>
     <row r="158" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D158" s="369"/>
-      <c r="E158" s="347"/>
-      <c r="F158" s="286"/>
-      <c r="G158" s="286"/>
-      <c r="H158" s="286"/>
-      <c r="I158" s="286"/>
-      <c r="J158" s="287"/>
-      <c r="K158" s="356"/>
-      <c r="L158" s="356"/>
-      <c r="M158" s="356"/>
-      <c r="N158" s="356"/>
-      <c r="O158" s="356"/>
-      <c r="P158" s="356"/>
-      <c r="Q158" s="356"/>
-      <c r="R158" s="356"/>
-      <c r="S158" s="356"/>
-      <c r="T158" s="356"/>
-      <c r="U158" s="356"/>
-      <c r="V158" s="356"/>
-      <c r="W158" s="356"/>
-      <c r="X158" s="356"/>
-      <c r="Y158" s="356"/>
-      <c r="Z158" s="356"/>
-      <c r="AA158" s="356"/>
-      <c r="AB158" s="356"/>
-      <c r="AC158" s="356"/>
-      <c r="AD158" s="356"/>
-      <c r="AE158" s="356"/>
-      <c r="AF158" s="356"/>
-      <c r="AG158" s="356"/>
-      <c r="AH158" s="356"/>
+      <c r="D158" s="331"/>
+      <c r="E158" s="334"/>
+      <c r="F158" s="288"/>
+      <c r="G158" s="288"/>
+      <c r="H158" s="288"/>
+      <c r="I158" s="288"/>
+      <c r="J158" s="289"/>
+      <c r="K158" s="347"/>
+      <c r="L158" s="347"/>
+      <c r="M158" s="347"/>
+      <c r="N158" s="347"/>
+      <c r="O158" s="347"/>
+      <c r="P158" s="347"/>
+      <c r="Q158" s="347"/>
+      <c r="R158" s="347"/>
+      <c r="S158" s="347"/>
+      <c r="T158" s="347"/>
+      <c r="U158" s="347"/>
+      <c r="V158" s="347"/>
+      <c r="W158" s="347"/>
+      <c r="X158" s="347"/>
+      <c r="Y158" s="347"/>
+      <c r="Z158" s="347"/>
+      <c r="AA158" s="347"/>
+      <c r="AB158" s="347"/>
+      <c r="AC158" s="347"/>
+      <c r="AD158" s="347"/>
+      <c r="AE158" s="347"/>
+      <c r="AF158" s="347"/>
+      <c r="AG158" s="347"/>
+      <c r="AH158" s="347"/>
     </row>
     <row r="159" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D159" s="369"/>
-      <c r="E159" s="347"/>
-      <c r="F159" s="286"/>
-      <c r="G159" s="286"/>
-      <c r="H159" s="286"/>
-      <c r="I159" s="286"/>
-      <c r="J159" s="287"/>
-      <c r="K159" s="356"/>
-      <c r="L159" s="356"/>
-      <c r="M159" s="356"/>
-      <c r="N159" s="356"/>
-      <c r="O159" s="356"/>
-      <c r="P159" s="356"/>
-      <c r="Q159" s="356"/>
-      <c r="R159" s="356"/>
-      <c r="S159" s="356"/>
-      <c r="T159" s="356"/>
-      <c r="U159" s="356"/>
-      <c r="V159" s="356"/>
-      <c r="W159" s="356"/>
-      <c r="X159" s="356"/>
-      <c r="Y159" s="356"/>
-      <c r="Z159" s="356"/>
-      <c r="AA159" s="356"/>
-      <c r="AB159" s="356"/>
-      <c r="AC159" s="356"/>
-      <c r="AD159" s="356"/>
-      <c r="AE159" s="356"/>
-      <c r="AF159" s="356"/>
-      <c r="AG159" s="356"/>
-      <c r="AH159" s="356"/>
+      <c r="D159" s="331"/>
+      <c r="E159" s="334"/>
+      <c r="F159" s="288"/>
+      <c r="G159" s="288"/>
+      <c r="H159" s="288"/>
+      <c r="I159" s="288"/>
+      <c r="J159" s="289"/>
+      <c r="K159" s="347"/>
+      <c r="L159" s="347"/>
+      <c r="M159" s="347"/>
+      <c r="N159" s="347"/>
+      <c r="O159" s="347"/>
+      <c r="P159" s="347"/>
+      <c r="Q159" s="347"/>
+      <c r="R159" s="347"/>
+      <c r="S159" s="347"/>
+      <c r="T159" s="347"/>
+      <c r="U159" s="347"/>
+      <c r="V159" s="347"/>
+      <c r="W159" s="347"/>
+      <c r="X159" s="347"/>
+      <c r="Y159" s="347"/>
+      <c r="Z159" s="347"/>
+      <c r="AA159" s="347"/>
+      <c r="AB159" s="347"/>
+      <c r="AC159" s="347"/>
+      <c r="AD159" s="347"/>
+      <c r="AE159" s="347"/>
+      <c r="AF159" s="347"/>
+      <c r="AG159" s="347"/>
+      <c r="AH159" s="347"/>
     </row>
     <row r="160" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D160" s="369"/>
-      <c r="E160" s="347"/>
-      <c r="F160" s="286"/>
-      <c r="G160" s="286"/>
-      <c r="H160" s="286"/>
-      <c r="I160" s="286"/>
-      <c r="J160" s="287"/>
-      <c r="K160" s="356"/>
-      <c r="L160" s="356"/>
-      <c r="M160" s="356"/>
-      <c r="N160" s="356"/>
-      <c r="O160" s="356"/>
-      <c r="P160" s="356"/>
-      <c r="Q160" s="356"/>
-      <c r="R160" s="356"/>
-      <c r="S160" s="356"/>
-      <c r="T160" s="356"/>
-      <c r="U160" s="356"/>
-      <c r="V160" s="356"/>
-      <c r="W160" s="356"/>
-      <c r="X160" s="356"/>
-      <c r="Y160" s="356"/>
-      <c r="Z160" s="356"/>
-      <c r="AA160" s="356"/>
-      <c r="AB160" s="356"/>
-      <c r="AC160" s="356"/>
-      <c r="AD160" s="356"/>
-      <c r="AE160" s="356"/>
-      <c r="AF160" s="356"/>
-      <c r="AG160" s="356"/>
-      <c r="AH160" s="356"/>
+      <c r="D160" s="331"/>
+      <c r="E160" s="334"/>
+      <c r="F160" s="288"/>
+      <c r="G160" s="288"/>
+      <c r="H160" s="288"/>
+      <c r="I160" s="288"/>
+      <c r="J160" s="289"/>
+      <c r="K160" s="347"/>
+      <c r="L160" s="347"/>
+      <c r="M160" s="347"/>
+      <c r="N160" s="347"/>
+      <c r="O160" s="347"/>
+      <c r="P160" s="347"/>
+      <c r="Q160" s="347"/>
+      <c r="R160" s="347"/>
+      <c r="S160" s="347"/>
+      <c r="T160" s="347"/>
+      <c r="U160" s="347"/>
+      <c r="V160" s="347"/>
+      <c r="W160" s="347"/>
+      <c r="X160" s="347"/>
+      <c r="Y160" s="347"/>
+      <c r="Z160" s="347"/>
+      <c r="AA160" s="347"/>
+      <c r="AB160" s="347"/>
+      <c r="AC160" s="347"/>
+      <c r="AD160" s="347"/>
+      <c r="AE160" s="347"/>
+      <c r="AF160" s="347"/>
+      <c r="AG160" s="347"/>
+      <c r="AH160" s="347"/>
     </row>
     <row r="161" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D161" s="369"/>
-      <c r="E161" s="347"/>
-      <c r="F161" s="286"/>
-      <c r="G161" s="286"/>
-      <c r="H161" s="286"/>
-      <c r="I161" s="286"/>
-      <c r="J161" s="287"/>
-      <c r="K161" s="355" t="s">
+      <c r="D161" s="331"/>
+      <c r="E161" s="334"/>
+      <c r="F161" s="288"/>
+      <c r="G161" s="288"/>
+      <c r="H161" s="288"/>
+      <c r="I161" s="288"/>
+      <c r="J161" s="289"/>
+      <c r="K161" s="346" t="s">
         <v>629</v>
       </c>
-      <c r="L161" s="356"/>
-      <c r="M161" s="356"/>
-      <c r="N161" s="356"/>
-      <c r="O161" s="356"/>
-      <c r="P161" s="356"/>
-      <c r="Q161" s="356"/>
-      <c r="R161" s="356"/>
-      <c r="S161" s="356"/>
-      <c r="T161" s="356"/>
-      <c r="U161" s="356"/>
-      <c r="V161" s="356"/>
-      <c r="W161" s="356"/>
-      <c r="X161" s="356"/>
-      <c r="Y161" s="356"/>
-      <c r="Z161" s="356"/>
-      <c r="AA161" s="361" t="s">
+      <c r="L161" s="347"/>
+      <c r="M161" s="347"/>
+      <c r="N161" s="347"/>
+      <c r="O161" s="347"/>
+      <c r="P161" s="347"/>
+      <c r="Q161" s="347"/>
+      <c r="R161" s="347"/>
+      <c r="S161" s="347"/>
+      <c r="T161" s="347"/>
+      <c r="U161" s="347"/>
+      <c r="V161" s="347"/>
+      <c r="W161" s="347"/>
+      <c r="X161" s="347"/>
+      <c r="Y161" s="347"/>
+      <c r="Z161" s="347"/>
+      <c r="AA161" s="322" t="s">
         <v>75</v>
       </c>
-      <c r="AB161" s="362"/>
-      <c r="AC161" s="362"/>
-      <c r="AD161" s="362"/>
-      <c r="AE161" s="362"/>
-      <c r="AF161" s="362"/>
-      <c r="AG161" s="362"/>
-      <c r="AH161" s="362"/>
+      <c r="AB161" s="323"/>
+      <c r="AC161" s="323"/>
+      <c r="AD161" s="323"/>
+      <c r="AE161" s="323"/>
+      <c r="AF161" s="323"/>
+      <c r="AG161" s="323"/>
+      <c r="AH161" s="323"/>
     </row>
     <row r="162" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D162" s="369"/>
-      <c r="E162" s="347" t="s">
+      <c r="D162" s="331"/>
+      <c r="E162" s="334" t="s">
         <v>323</v>
       </c>
-      <c r="F162" s="286"/>
-      <c r="G162" s="286"/>
-      <c r="H162" s="286"/>
-      <c r="I162" s="286"/>
-      <c r="J162" s="287"/>
-      <c r="K162" s="347" t="s">
+      <c r="F162" s="288"/>
+      <c r="G162" s="288"/>
+      <c r="H162" s="288"/>
+      <c r="I162" s="288"/>
+      <c r="J162" s="289"/>
+      <c r="K162" s="334" t="s">
         <v>628</v>
       </c>
-      <c r="L162" s="286"/>
-      <c r="M162" s="286"/>
-      <c r="N162" s="286"/>
-      <c r="O162" s="286"/>
-      <c r="P162" s="286"/>
-      <c r="Q162" s="286"/>
-      <c r="R162" s="286"/>
-      <c r="S162" s="286"/>
-      <c r="T162" s="286"/>
-      <c r="U162" s="286"/>
-      <c r="V162" s="286"/>
-      <c r="W162" s="286"/>
-      <c r="X162" s="286"/>
-      <c r="Y162" s="286"/>
-      <c r="Z162" s="287"/>
-      <c r="AA162" s="362" t="s">
+      <c r="L162" s="288"/>
+      <c r="M162" s="288"/>
+      <c r="N162" s="288"/>
+      <c r="O162" s="288"/>
+      <c r="P162" s="288"/>
+      <c r="Q162" s="288"/>
+      <c r="R162" s="288"/>
+      <c r="S162" s="288"/>
+      <c r="T162" s="288"/>
+      <c r="U162" s="288"/>
+      <c r="V162" s="288"/>
+      <c r="W162" s="288"/>
+      <c r="X162" s="288"/>
+      <c r="Y162" s="288"/>
+      <c r="Z162" s="289"/>
+      <c r="AA162" s="323" t="s">
         <v>71</v>
       </c>
-      <c r="AB162" s="362"/>
-      <c r="AC162" s="362"/>
-      <c r="AD162" s="362"/>
-      <c r="AE162" s="362"/>
-      <c r="AF162" s="362"/>
-      <c r="AG162" s="362"/>
-      <c r="AH162" s="362"/>
+      <c r="AB162" s="323"/>
+      <c r="AC162" s="323"/>
+      <c r="AD162" s="323"/>
+      <c r="AE162" s="323"/>
+      <c r="AF162" s="323"/>
+      <c r="AG162" s="323"/>
+      <c r="AH162" s="323"/>
     </row>
     <row r="163" spans="3:34" x14ac:dyDescent="0.15">
-      <c r="D163" s="370"/>
-      <c r="E163" s="347"/>
-      <c r="F163" s="286"/>
-      <c r="G163" s="286"/>
-      <c r="H163" s="286"/>
-      <c r="I163" s="286"/>
-      <c r="J163" s="287"/>
-      <c r="K163" s="362"/>
-      <c r="L163" s="362"/>
-      <c r="M163" s="362"/>
-      <c r="N163" s="362"/>
-      <c r="O163" s="362"/>
-      <c r="P163" s="362"/>
-      <c r="Q163" s="362"/>
-      <c r="R163" s="362"/>
-      <c r="S163" s="362"/>
-      <c r="T163" s="362"/>
-      <c r="U163" s="362"/>
-      <c r="V163" s="362"/>
-      <c r="W163" s="362"/>
-      <c r="X163" s="362"/>
-      <c r="Y163" s="362"/>
-      <c r="Z163" s="362"/>
-      <c r="AA163" s="362"/>
-      <c r="AB163" s="362"/>
-      <c r="AC163" s="362"/>
-      <c r="AD163" s="362"/>
-      <c r="AE163" s="362"/>
-      <c r="AF163" s="362"/>
-      <c r="AG163" s="362"/>
-      <c r="AH163" s="362"/>
+      <c r="D163" s="332"/>
+      <c r="E163" s="334"/>
+      <c r="F163" s="288"/>
+      <c r="G163" s="288"/>
+      <c r="H163" s="288"/>
+      <c r="I163" s="288"/>
+      <c r="J163" s="289"/>
+      <c r="K163" s="323"/>
+      <c r="L163" s="323"/>
+      <c r="M163" s="323"/>
+      <c r="N163" s="323"/>
+      <c r="O163" s="323"/>
+      <c r="P163" s="323"/>
+      <c r="Q163" s="323"/>
+      <c r="R163" s="323"/>
+      <c r="S163" s="323"/>
+      <c r="T163" s="323"/>
+      <c r="U163" s="323"/>
+      <c r="V163" s="323"/>
+      <c r="W163" s="323"/>
+      <c r="X163" s="323"/>
+      <c r="Y163" s="323"/>
+      <c r="Z163" s="323"/>
+      <c r="AA163" s="323"/>
+      <c r="AB163" s="323"/>
+      <c r="AC163" s="323"/>
+      <c r="AD163" s="323"/>
+      <c r="AE163" s="323"/>
+      <c r="AF163" s="323"/>
+      <c r="AG163" s="323"/>
+      <c r="AH163" s="323"/>
     </row>
     <row r="164" spans="3:34" x14ac:dyDescent="0.15">
       <c r="D164" s="55"/>
@@ -42878,815 +42878,815 @@
     </row>
     <row r="173" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="174" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F174" s="276" t="s">
+      <c r="F174" s="248" t="s">
         <v>642</v>
       </c>
-      <c r="G174" s="341"/>
-      <c r="H174" s="341"/>
-      <c r="I174" s="341"/>
-      <c r="J174" s="342"/>
-      <c r="K174" s="353" t="s">
+      <c r="G174" s="327"/>
+      <c r="H174" s="327"/>
+      <c r="I174" s="327"/>
+      <c r="J174" s="328"/>
+      <c r="K174" s="329" t="s">
         <v>30</v>
       </c>
-      <c r="L174" s="354"/>
-      <c r="M174" s="353" t="s">
+      <c r="L174" s="330"/>
+      <c r="M174" s="329" t="s">
         <v>45</v>
       </c>
-      <c r="N174" s="354"/>
-      <c r="O174" s="368" t="s">
+      <c r="N174" s="330"/>
+      <c r="O174" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="P174" s="341"/>
-      <c r="Q174" s="341"/>
-      <c r="R174" s="341"/>
-      <c r="S174" s="341"/>
-      <c r="T174" s="341"/>
-      <c r="U174" s="341"/>
-      <c r="V174" s="341"/>
-      <c r="W174" s="341"/>
-      <c r="X174" s="341"/>
-      <c r="Y174" s="341"/>
-      <c r="Z174" s="341"/>
-      <c r="AA174" s="341"/>
-      <c r="AB174" s="341"/>
-      <c r="AC174" s="341"/>
-      <c r="AD174" s="341"/>
-      <c r="AE174" s="341"/>
-      <c r="AF174" s="341"/>
-      <c r="AG174" s="341"/>
-      <c r="AH174" s="342"/>
+      <c r="P174" s="327"/>
+      <c r="Q174" s="327"/>
+      <c r="R174" s="327"/>
+      <c r="S174" s="327"/>
+      <c r="T174" s="327"/>
+      <c r="U174" s="327"/>
+      <c r="V174" s="327"/>
+      <c r="W174" s="327"/>
+      <c r="X174" s="327"/>
+      <c r="Y174" s="327"/>
+      <c r="Z174" s="327"/>
+      <c r="AA174" s="327"/>
+      <c r="AB174" s="327"/>
+      <c r="AC174" s="327"/>
+      <c r="AD174" s="327"/>
+      <c r="AE174" s="327"/>
+      <c r="AF174" s="327"/>
+      <c r="AG174" s="327"/>
+      <c r="AH174" s="328"/>
     </row>
     <row r="175" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F175" s="310" t="s">
+      <c r="F175" s="307" t="s">
         <v>285</v>
       </c>
-      <c r="G175" s="280"/>
-      <c r="H175" s="280"/>
-      <c r="I175" s="280"/>
-      <c r="J175" s="281"/>
-      <c r="K175" s="337" t="s">
+      <c r="G175" s="252"/>
+      <c r="H175" s="252"/>
+      <c r="I175" s="252"/>
+      <c r="J175" s="253"/>
+      <c r="K175" s="340" t="s">
         <v>32</v>
       </c>
-      <c r="L175" s="290"/>
-      <c r="M175" s="363" t="s">
+      <c r="L175" s="292"/>
+      <c r="M175" s="335" t="s">
         <v>302</v>
       </c>
-      <c r="N175" s="350"/>
-      <c r="O175" s="282" t="s">
+      <c r="N175" s="337"/>
+      <c r="O175" s="254" t="s">
         <v>307</v>
       </c>
-      <c r="P175" s="365"/>
-      <c r="Q175" s="365"/>
-      <c r="R175" s="365"/>
-      <c r="S175" s="365"/>
-      <c r="T175" s="365"/>
-      <c r="U175" s="365"/>
-      <c r="V175" s="365"/>
-      <c r="W175" s="365"/>
-      <c r="X175" s="365"/>
-      <c r="Y175" s="365"/>
-      <c r="Z175" s="365"/>
-      <c r="AA175" s="365"/>
-      <c r="AB175" s="365"/>
-      <c r="AC175" s="365"/>
-      <c r="AD175" s="365"/>
-      <c r="AE175" s="365"/>
-      <c r="AF175" s="365"/>
-      <c r="AG175" s="365"/>
-      <c r="AH175" s="366"/>
+      <c r="P175" s="342"/>
+      <c r="Q175" s="342"/>
+      <c r="R175" s="342"/>
+      <c r="S175" s="342"/>
+      <c r="T175" s="342"/>
+      <c r="U175" s="342"/>
+      <c r="V175" s="342"/>
+      <c r="W175" s="342"/>
+      <c r="X175" s="342"/>
+      <c r="Y175" s="342"/>
+      <c r="Z175" s="342"/>
+      <c r="AA175" s="342"/>
+      <c r="AB175" s="342"/>
+      <c r="AC175" s="342"/>
+      <c r="AD175" s="342"/>
+      <c r="AE175" s="342"/>
+      <c r="AF175" s="342"/>
+      <c r="AG175" s="342"/>
+      <c r="AH175" s="343"/>
     </row>
     <row r="176" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F176" s="288" t="s">
+      <c r="F176" s="290" t="s">
         <v>303</v>
       </c>
-      <c r="G176" s="289"/>
-      <c r="H176" s="289"/>
-      <c r="I176" s="289"/>
-      <c r="J176" s="290"/>
-      <c r="K176" s="337" t="s">
+      <c r="G176" s="291"/>
+      <c r="H176" s="291"/>
+      <c r="I176" s="291"/>
+      <c r="J176" s="292"/>
+      <c r="K176" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L176" s="290"/>
-      <c r="M176" s="317" t="s">
+      <c r="L176" s="292"/>
+      <c r="M176" s="310" t="s">
         <v>339</v>
       </c>
-      <c r="N176" s="319"/>
-      <c r="O176" s="288" t="s">
+      <c r="N176" s="312"/>
+      <c r="O176" s="290" t="s">
         <v>306</v>
       </c>
-      <c r="P176" s="289"/>
-      <c r="Q176" s="289"/>
-      <c r="R176" s="289"/>
-      <c r="S176" s="289"/>
-      <c r="T176" s="289"/>
-      <c r="U176" s="289"/>
-      <c r="V176" s="289"/>
-      <c r="W176" s="289"/>
-      <c r="X176" s="289"/>
-      <c r="Y176" s="289"/>
-      <c r="Z176" s="289"/>
-      <c r="AA176" s="289"/>
-      <c r="AB176" s="289"/>
-      <c r="AC176" s="289"/>
-      <c r="AD176" s="289"/>
-      <c r="AE176" s="289"/>
-      <c r="AF176" s="289"/>
-      <c r="AG176" s="289"/>
-      <c r="AH176" s="290"/>
+      <c r="P176" s="291"/>
+      <c r="Q176" s="291"/>
+      <c r="R176" s="291"/>
+      <c r="S176" s="291"/>
+      <c r="T176" s="291"/>
+      <c r="U176" s="291"/>
+      <c r="V176" s="291"/>
+      <c r="W176" s="291"/>
+      <c r="X176" s="291"/>
+      <c r="Y176" s="291"/>
+      <c r="Z176" s="291"/>
+      <c r="AA176" s="291"/>
+      <c r="AB176" s="291"/>
+      <c r="AC176" s="291"/>
+      <c r="AD176" s="291"/>
+      <c r="AE176" s="291"/>
+      <c r="AF176" s="291"/>
+      <c r="AG176" s="291"/>
+      <c r="AH176" s="292"/>
     </row>
     <row r="177" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F177" s="297"/>
-      <c r="G177" s="292"/>
-      <c r="H177" s="292"/>
-      <c r="I177" s="292"/>
-      <c r="J177" s="293"/>
-      <c r="K177" s="291"/>
-      <c r="L177" s="293"/>
-      <c r="M177" s="334"/>
-      <c r="N177" s="344"/>
-      <c r="O177" s="297"/>
-      <c r="P177" s="292"/>
-      <c r="Q177" s="292"/>
-      <c r="R177" s="292"/>
-      <c r="S177" s="292"/>
-      <c r="T177" s="292"/>
-      <c r="U177" s="292"/>
-      <c r="V177" s="292"/>
-      <c r="W177" s="292"/>
-      <c r="X177" s="292"/>
-      <c r="Y177" s="292"/>
-      <c r="Z177" s="292"/>
-      <c r="AA177" s="292"/>
-      <c r="AB177" s="292"/>
-      <c r="AC177" s="292"/>
-      <c r="AD177" s="292"/>
-      <c r="AE177" s="292"/>
-      <c r="AF177" s="292"/>
-      <c r="AG177" s="292"/>
-      <c r="AH177" s="293"/>
+      <c r="F177" s="299"/>
+      <c r="G177" s="294"/>
+      <c r="H177" s="294"/>
+      <c r="I177" s="294"/>
+      <c r="J177" s="295"/>
+      <c r="K177" s="293"/>
+      <c r="L177" s="295"/>
+      <c r="M177" s="338"/>
+      <c r="N177" s="339"/>
+      <c r="O177" s="299"/>
+      <c r="P177" s="294"/>
+      <c r="Q177" s="294"/>
+      <c r="R177" s="294"/>
+      <c r="S177" s="294"/>
+      <c r="T177" s="294"/>
+      <c r="U177" s="294"/>
+      <c r="V177" s="294"/>
+      <c r="W177" s="294"/>
+      <c r="X177" s="294"/>
+      <c r="Y177" s="294"/>
+      <c r="Z177" s="294"/>
+      <c r="AA177" s="294"/>
+      <c r="AB177" s="294"/>
+      <c r="AC177" s="294"/>
+      <c r="AD177" s="294"/>
+      <c r="AE177" s="294"/>
+      <c r="AF177" s="294"/>
+      <c r="AG177" s="294"/>
+      <c r="AH177" s="295"/>
     </row>
     <row r="178" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F178" s="297"/>
-      <c r="G178" s="292"/>
-      <c r="H178" s="292"/>
-      <c r="I178" s="292"/>
-      <c r="J178" s="293"/>
-      <c r="K178" s="291"/>
-      <c r="L178" s="293"/>
-      <c r="M178" s="334"/>
-      <c r="N178" s="344"/>
-      <c r="O178" s="297"/>
-      <c r="P178" s="292"/>
-      <c r="Q178" s="292"/>
-      <c r="R178" s="292"/>
-      <c r="S178" s="292"/>
-      <c r="T178" s="292"/>
-      <c r="U178" s="292"/>
-      <c r="V178" s="292"/>
-      <c r="W178" s="292"/>
-      <c r="X178" s="292"/>
-      <c r="Y178" s="292"/>
-      <c r="Z178" s="292"/>
-      <c r="AA178" s="292"/>
-      <c r="AB178" s="292"/>
-      <c r="AC178" s="292"/>
-      <c r="AD178" s="292"/>
-      <c r="AE178" s="292"/>
-      <c r="AF178" s="292"/>
-      <c r="AG178" s="292"/>
-      <c r="AH178" s="293"/>
+      <c r="F178" s="299"/>
+      <c r="G178" s="294"/>
+      <c r="H178" s="294"/>
+      <c r="I178" s="294"/>
+      <c r="J178" s="295"/>
+      <c r="K178" s="293"/>
+      <c r="L178" s="295"/>
+      <c r="M178" s="338"/>
+      <c r="N178" s="339"/>
+      <c r="O178" s="299"/>
+      <c r="P178" s="294"/>
+      <c r="Q178" s="294"/>
+      <c r="R178" s="294"/>
+      <c r="S178" s="294"/>
+      <c r="T178" s="294"/>
+      <c r="U178" s="294"/>
+      <c r="V178" s="294"/>
+      <c r="W178" s="294"/>
+      <c r="X178" s="294"/>
+      <c r="Y178" s="294"/>
+      <c r="Z178" s="294"/>
+      <c r="AA178" s="294"/>
+      <c r="AB178" s="294"/>
+      <c r="AC178" s="294"/>
+      <c r="AD178" s="294"/>
+      <c r="AE178" s="294"/>
+      <c r="AF178" s="294"/>
+      <c r="AG178" s="294"/>
+      <c r="AH178" s="295"/>
     </row>
     <row r="179" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F179" s="294"/>
-      <c r="G179" s="295"/>
-      <c r="H179" s="295"/>
-      <c r="I179" s="295"/>
-      <c r="J179" s="296"/>
-      <c r="K179" s="294"/>
-      <c r="L179" s="296"/>
-      <c r="M179" s="320"/>
-      <c r="N179" s="322"/>
-      <c r="O179" s="294"/>
-      <c r="P179" s="295"/>
-      <c r="Q179" s="295"/>
-      <c r="R179" s="295"/>
-      <c r="S179" s="295"/>
-      <c r="T179" s="295"/>
-      <c r="U179" s="295"/>
-      <c r="V179" s="295"/>
-      <c r="W179" s="295"/>
-      <c r="X179" s="295"/>
-      <c r="Y179" s="295"/>
-      <c r="Z179" s="295"/>
-      <c r="AA179" s="295"/>
-      <c r="AB179" s="295"/>
-      <c r="AC179" s="295"/>
-      <c r="AD179" s="295"/>
-      <c r="AE179" s="295"/>
-      <c r="AF179" s="295"/>
-      <c r="AG179" s="295"/>
-      <c r="AH179" s="296"/>
+      <c r="F179" s="296"/>
+      <c r="G179" s="297"/>
+      <c r="H179" s="297"/>
+      <c r="I179" s="297"/>
+      <c r="J179" s="298"/>
+      <c r="K179" s="296"/>
+      <c r="L179" s="298"/>
+      <c r="M179" s="313"/>
+      <c r="N179" s="315"/>
+      <c r="O179" s="296"/>
+      <c r="P179" s="297"/>
+      <c r="Q179" s="297"/>
+      <c r="R179" s="297"/>
+      <c r="S179" s="297"/>
+      <c r="T179" s="297"/>
+      <c r="U179" s="297"/>
+      <c r="V179" s="297"/>
+      <c r="W179" s="297"/>
+      <c r="X179" s="297"/>
+      <c r="Y179" s="297"/>
+      <c r="Z179" s="297"/>
+      <c r="AA179" s="297"/>
+      <c r="AB179" s="297"/>
+      <c r="AC179" s="297"/>
+      <c r="AD179" s="297"/>
+      <c r="AE179" s="297"/>
+      <c r="AF179" s="297"/>
+      <c r="AG179" s="297"/>
+      <c r="AH179" s="298"/>
     </row>
     <row r="180" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F180" s="337" t="s">
+      <c r="F180" s="340" t="s">
         <v>47</v>
       </c>
-      <c r="G180" s="289"/>
-      <c r="H180" s="289"/>
-      <c r="I180" s="289"/>
-      <c r="J180" s="290"/>
-      <c r="K180" s="337" t="s">
+      <c r="G180" s="291"/>
+      <c r="H180" s="291"/>
+      <c r="I180" s="291"/>
+      <c r="J180" s="292"/>
+      <c r="K180" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L180" s="290"/>
-      <c r="M180" s="337" t="s">
+      <c r="L180" s="292"/>
+      <c r="M180" s="340" t="s">
         <v>48</v>
       </c>
-      <c r="N180" s="319"/>
-      <c r="O180" s="317" t="s">
+      <c r="N180" s="312"/>
+      <c r="O180" s="310" t="s">
         <v>310</v>
       </c>
-      <c r="P180" s="318"/>
-      <c r="Q180" s="318"/>
-      <c r="R180" s="318"/>
-      <c r="S180" s="318"/>
-      <c r="T180" s="318"/>
-      <c r="U180" s="318"/>
-      <c r="V180" s="318"/>
-      <c r="W180" s="318"/>
-      <c r="X180" s="318"/>
-      <c r="Y180" s="318"/>
-      <c r="Z180" s="318"/>
-      <c r="AA180" s="318"/>
-      <c r="AB180" s="318"/>
-      <c r="AC180" s="318"/>
-      <c r="AD180" s="318"/>
-      <c r="AE180" s="318"/>
-      <c r="AF180" s="318"/>
-      <c r="AG180" s="318"/>
-      <c r="AH180" s="319"/>
+      <c r="P180" s="311"/>
+      <c r="Q180" s="311"/>
+      <c r="R180" s="311"/>
+      <c r="S180" s="311"/>
+      <c r="T180" s="311"/>
+      <c r="U180" s="311"/>
+      <c r="V180" s="311"/>
+      <c r="W180" s="311"/>
+      <c r="X180" s="311"/>
+      <c r="Y180" s="311"/>
+      <c r="Z180" s="311"/>
+      <c r="AA180" s="311"/>
+      <c r="AB180" s="311"/>
+      <c r="AC180" s="311"/>
+      <c r="AD180" s="311"/>
+      <c r="AE180" s="311"/>
+      <c r="AF180" s="311"/>
+      <c r="AG180" s="311"/>
+      <c r="AH180" s="312"/>
     </row>
     <row r="181" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F181" s="288" t="s">
+      <c r="F181" s="290" t="s">
         <v>286</v>
       </c>
-      <c r="G181" s="289"/>
-      <c r="H181" s="289"/>
-      <c r="I181" s="289"/>
-      <c r="J181" s="290"/>
-      <c r="K181" s="337" t="s">
+      <c r="G181" s="291"/>
+      <c r="H181" s="291"/>
+      <c r="I181" s="291"/>
+      <c r="J181" s="292"/>
+      <c r="K181" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L181" s="290"/>
-      <c r="M181" s="337" t="s">
+      <c r="L181" s="292"/>
+      <c r="M181" s="340" t="s">
         <v>76</v>
       </c>
-      <c r="N181" s="319"/>
-      <c r="O181" s="317" t="s">
+      <c r="N181" s="312"/>
+      <c r="O181" s="310" t="s">
         <v>311</v>
       </c>
-      <c r="P181" s="318"/>
-      <c r="Q181" s="318"/>
-      <c r="R181" s="318"/>
-      <c r="S181" s="318"/>
-      <c r="T181" s="318"/>
-      <c r="U181" s="318"/>
-      <c r="V181" s="318"/>
-      <c r="W181" s="318"/>
-      <c r="X181" s="318"/>
-      <c r="Y181" s="318"/>
-      <c r="Z181" s="318"/>
-      <c r="AA181" s="318"/>
-      <c r="AB181" s="318"/>
-      <c r="AC181" s="318"/>
-      <c r="AD181" s="318"/>
-      <c r="AE181" s="318"/>
-      <c r="AF181" s="318"/>
-      <c r="AG181" s="318"/>
-      <c r="AH181" s="319"/>
+      <c r="P181" s="311"/>
+      <c r="Q181" s="311"/>
+      <c r="R181" s="311"/>
+      <c r="S181" s="311"/>
+      <c r="T181" s="311"/>
+      <c r="U181" s="311"/>
+      <c r="V181" s="311"/>
+      <c r="W181" s="311"/>
+      <c r="X181" s="311"/>
+      <c r="Y181" s="311"/>
+      <c r="Z181" s="311"/>
+      <c r="AA181" s="311"/>
+      <c r="AB181" s="311"/>
+      <c r="AC181" s="311"/>
+      <c r="AD181" s="311"/>
+      <c r="AE181" s="311"/>
+      <c r="AF181" s="311"/>
+      <c r="AG181" s="311"/>
+      <c r="AH181" s="312"/>
     </row>
     <row r="182" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F182" s="297"/>
-      <c r="G182" s="343"/>
-      <c r="H182" s="343"/>
-      <c r="I182" s="343"/>
-      <c r="J182" s="344"/>
-      <c r="K182" s="291"/>
-      <c r="L182" s="293"/>
-      <c r="M182" s="297"/>
-      <c r="N182" s="344"/>
-      <c r="O182" s="297"/>
-      <c r="P182" s="343"/>
-      <c r="Q182" s="343"/>
-      <c r="R182" s="343"/>
-      <c r="S182" s="343"/>
-      <c r="T182" s="343"/>
-      <c r="U182" s="343"/>
-      <c r="V182" s="343"/>
-      <c r="W182" s="343"/>
-      <c r="X182" s="343"/>
-      <c r="Y182" s="343"/>
-      <c r="Z182" s="343"/>
-      <c r="AA182" s="343"/>
-      <c r="AB182" s="343"/>
-      <c r="AC182" s="343"/>
-      <c r="AD182" s="343"/>
-      <c r="AE182" s="343"/>
-      <c r="AF182" s="343"/>
-      <c r="AG182" s="343"/>
-      <c r="AH182" s="344"/>
+      <c r="F182" s="299"/>
+      <c r="G182" s="363"/>
+      <c r="H182" s="363"/>
+      <c r="I182" s="363"/>
+      <c r="J182" s="339"/>
+      <c r="K182" s="293"/>
+      <c r="L182" s="295"/>
+      <c r="M182" s="299"/>
+      <c r="N182" s="339"/>
+      <c r="O182" s="299"/>
+      <c r="P182" s="363"/>
+      <c r="Q182" s="363"/>
+      <c r="R182" s="363"/>
+      <c r="S182" s="363"/>
+      <c r="T182" s="363"/>
+      <c r="U182" s="363"/>
+      <c r="V182" s="363"/>
+      <c r="W182" s="363"/>
+      <c r="X182" s="363"/>
+      <c r="Y182" s="363"/>
+      <c r="Z182" s="363"/>
+      <c r="AA182" s="363"/>
+      <c r="AB182" s="363"/>
+      <c r="AC182" s="363"/>
+      <c r="AD182" s="363"/>
+      <c r="AE182" s="363"/>
+      <c r="AF182" s="363"/>
+      <c r="AG182" s="363"/>
+      <c r="AH182" s="339"/>
     </row>
     <row r="183" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F183" s="297"/>
-      <c r="G183" s="343"/>
-      <c r="H183" s="343"/>
-      <c r="I183" s="343"/>
-      <c r="J183" s="344"/>
-      <c r="K183" s="291"/>
-      <c r="L183" s="293"/>
-      <c r="M183" s="297"/>
-      <c r="N183" s="344"/>
-      <c r="O183" s="297"/>
-      <c r="P183" s="343"/>
-      <c r="Q183" s="343"/>
-      <c r="R183" s="343"/>
-      <c r="S183" s="343"/>
-      <c r="T183" s="343"/>
-      <c r="U183" s="343"/>
-      <c r="V183" s="343"/>
-      <c r="W183" s="343"/>
-      <c r="X183" s="343"/>
-      <c r="Y183" s="343"/>
-      <c r="Z183" s="343"/>
-      <c r="AA183" s="343"/>
-      <c r="AB183" s="343"/>
-      <c r="AC183" s="343"/>
-      <c r="AD183" s="343"/>
-      <c r="AE183" s="343"/>
-      <c r="AF183" s="343"/>
-      <c r="AG183" s="343"/>
-      <c r="AH183" s="344"/>
+      <c r="F183" s="299"/>
+      <c r="G183" s="363"/>
+      <c r="H183" s="363"/>
+      <c r="I183" s="363"/>
+      <c r="J183" s="339"/>
+      <c r="K183" s="293"/>
+      <c r="L183" s="295"/>
+      <c r="M183" s="299"/>
+      <c r="N183" s="339"/>
+      <c r="O183" s="299"/>
+      <c r="P183" s="363"/>
+      <c r="Q183" s="363"/>
+      <c r="R183" s="363"/>
+      <c r="S183" s="363"/>
+      <c r="T183" s="363"/>
+      <c r="U183" s="363"/>
+      <c r="V183" s="363"/>
+      <c r="W183" s="363"/>
+      <c r="X183" s="363"/>
+      <c r="Y183" s="363"/>
+      <c r="Z183" s="363"/>
+      <c r="AA183" s="363"/>
+      <c r="AB183" s="363"/>
+      <c r="AC183" s="363"/>
+      <c r="AD183" s="363"/>
+      <c r="AE183" s="363"/>
+      <c r="AF183" s="363"/>
+      <c r="AG183" s="363"/>
+      <c r="AH183" s="339"/>
     </row>
     <row r="184" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F184" s="320"/>
-      <c r="G184" s="321"/>
-      <c r="H184" s="321"/>
-      <c r="I184" s="321"/>
-      <c r="J184" s="322"/>
-      <c r="K184" s="294"/>
-      <c r="L184" s="296"/>
-      <c r="M184" s="320"/>
-      <c r="N184" s="322"/>
-      <c r="O184" s="320"/>
-      <c r="P184" s="321"/>
-      <c r="Q184" s="321"/>
-      <c r="R184" s="321"/>
-      <c r="S184" s="321"/>
-      <c r="T184" s="321"/>
-      <c r="U184" s="321"/>
-      <c r="V184" s="321"/>
-      <c r="W184" s="321"/>
-      <c r="X184" s="321"/>
-      <c r="Y184" s="321"/>
-      <c r="Z184" s="321"/>
-      <c r="AA184" s="321"/>
-      <c r="AB184" s="321"/>
-      <c r="AC184" s="321"/>
-      <c r="AD184" s="321"/>
-      <c r="AE184" s="321"/>
-      <c r="AF184" s="321"/>
-      <c r="AG184" s="321"/>
-      <c r="AH184" s="322"/>
+      <c r="F184" s="313"/>
+      <c r="G184" s="314"/>
+      <c r="H184" s="314"/>
+      <c r="I184" s="314"/>
+      <c r="J184" s="315"/>
+      <c r="K184" s="296"/>
+      <c r="L184" s="298"/>
+      <c r="M184" s="313"/>
+      <c r="N184" s="315"/>
+      <c r="O184" s="313"/>
+      <c r="P184" s="314"/>
+      <c r="Q184" s="314"/>
+      <c r="R184" s="314"/>
+      <c r="S184" s="314"/>
+      <c r="T184" s="314"/>
+      <c r="U184" s="314"/>
+      <c r="V184" s="314"/>
+      <c r="W184" s="314"/>
+      <c r="X184" s="314"/>
+      <c r="Y184" s="314"/>
+      <c r="Z184" s="314"/>
+      <c r="AA184" s="314"/>
+      <c r="AB184" s="314"/>
+      <c r="AC184" s="314"/>
+      <c r="AD184" s="314"/>
+      <c r="AE184" s="314"/>
+      <c r="AF184" s="314"/>
+      <c r="AG184" s="314"/>
+      <c r="AH184" s="315"/>
     </row>
     <row r="185" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F185" s="337" t="s">
+      <c r="F185" s="340" t="s">
         <v>38</v>
       </c>
-      <c r="G185" s="289"/>
-      <c r="H185" s="289"/>
-      <c r="I185" s="289"/>
-      <c r="J185" s="290"/>
-      <c r="K185" s="337" t="s">
+      <c r="G185" s="291"/>
+      <c r="H185" s="291"/>
+      <c r="I185" s="291"/>
+      <c r="J185" s="292"/>
+      <c r="K185" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L185" s="290"/>
-      <c r="M185" s="337" t="s">
+      <c r="L185" s="292"/>
+      <c r="M185" s="340" t="s">
         <v>48</v>
       </c>
-      <c r="N185" s="319"/>
-      <c r="O185" s="317" t="s">
+      <c r="N185" s="312"/>
+      <c r="O185" s="310" t="s">
         <v>500</v>
       </c>
-      <c r="P185" s="318"/>
-      <c r="Q185" s="318"/>
-      <c r="R185" s="318"/>
-      <c r="S185" s="318"/>
-      <c r="T185" s="318"/>
-      <c r="U185" s="318"/>
-      <c r="V185" s="318"/>
-      <c r="W185" s="318"/>
-      <c r="X185" s="318"/>
-      <c r="Y185" s="318"/>
-      <c r="Z185" s="318"/>
-      <c r="AA185" s="318"/>
-      <c r="AB185" s="318"/>
-      <c r="AC185" s="318"/>
-      <c r="AD185" s="318"/>
-      <c r="AE185" s="318"/>
-      <c r="AF185" s="318"/>
-      <c r="AG185" s="318"/>
-      <c r="AH185" s="319"/>
+      <c r="P185" s="311"/>
+      <c r="Q185" s="311"/>
+      <c r="R185" s="311"/>
+      <c r="S185" s="311"/>
+      <c r="T185" s="311"/>
+      <c r="U185" s="311"/>
+      <c r="V185" s="311"/>
+      <c r="W185" s="311"/>
+      <c r="X185" s="311"/>
+      <c r="Y185" s="311"/>
+      <c r="Z185" s="311"/>
+      <c r="AA185" s="311"/>
+      <c r="AB185" s="311"/>
+      <c r="AC185" s="311"/>
+      <c r="AD185" s="311"/>
+      <c r="AE185" s="311"/>
+      <c r="AF185" s="311"/>
+      <c r="AG185" s="311"/>
+      <c r="AH185" s="312"/>
     </row>
     <row r="186" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F186" s="320"/>
-      <c r="G186" s="321"/>
-      <c r="H186" s="321"/>
-      <c r="I186" s="321"/>
-      <c r="J186" s="322"/>
-      <c r="K186" s="294"/>
-      <c r="L186" s="296"/>
-      <c r="M186" s="320"/>
-      <c r="N186" s="322"/>
-      <c r="O186" s="320"/>
-      <c r="P186" s="321"/>
-      <c r="Q186" s="321"/>
-      <c r="R186" s="321"/>
-      <c r="S186" s="321"/>
-      <c r="T186" s="321"/>
-      <c r="U186" s="321"/>
-      <c r="V186" s="321"/>
-      <c r="W186" s="321"/>
-      <c r="X186" s="321"/>
-      <c r="Y186" s="321"/>
-      <c r="Z186" s="321"/>
-      <c r="AA186" s="321"/>
-      <c r="AB186" s="321"/>
-      <c r="AC186" s="321"/>
-      <c r="AD186" s="321"/>
-      <c r="AE186" s="321"/>
-      <c r="AF186" s="321"/>
-      <c r="AG186" s="321"/>
-      <c r="AH186" s="322"/>
+      <c r="F186" s="313"/>
+      <c r="G186" s="314"/>
+      <c r="H186" s="314"/>
+      <c r="I186" s="314"/>
+      <c r="J186" s="315"/>
+      <c r="K186" s="296"/>
+      <c r="L186" s="298"/>
+      <c r="M186" s="313"/>
+      <c r="N186" s="315"/>
+      <c r="O186" s="313"/>
+      <c r="P186" s="314"/>
+      <c r="Q186" s="314"/>
+      <c r="R186" s="314"/>
+      <c r="S186" s="314"/>
+      <c r="T186" s="314"/>
+      <c r="U186" s="314"/>
+      <c r="V186" s="314"/>
+      <c r="W186" s="314"/>
+      <c r="X186" s="314"/>
+      <c r="Y186" s="314"/>
+      <c r="Z186" s="314"/>
+      <c r="AA186" s="314"/>
+      <c r="AB186" s="314"/>
+      <c r="AC186" s="314"/>
+      <c r="AD186" s="314"/>
+      <c r="AE186" s="314"/>
+      <c r="AF186" s="314"/>
+      <c r="AG186" s="314"/>
+      <c r="AH186" s="315"/>
     </row>
     <row r="187" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F187" s="337" t="s">
+      <c r="F187" s="340" t="s">
         <v>39</v>
       </c>
-      <c r="G187" s="289"/>
-      <c r="H187" s="289"/>
-      <c r="I187" s="289"/>
-      <c r="J187" s="290"/>
-      <c r="K187" s="337" t="s">
+      <c r="G187" s="291"/>
+      <c r="H187" s="291"/>
+      <c r="I187" s="291"/>
+      <c r="J187" s="292"/>
+      <c r="K187" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L187" s="290"/>
-      <c r="M187" s="337" t="s">
+      <c r="L187" s="292"/>
+      <c r="M187" s="340" t="s">
         <v>79</v>
       </c>
-      <c r="N187" s="319"/>
-      <c r="O187" s="317" t="s">
+      <c r="N187" s="312"/>
+      <c r="O187" s="310" t="s">
         <v>499</v>
       </c>
-      <c r="P187" s="318"/>
-      <c r="Q187" s="318"/>
-      <c r="R187" s="318"/>
-      <c r="S187" s="318"/>
-      <c r="T187" s="318"/>
-      <c r="U187" s="318"/>
-      <c r="V187" s="318"/>
-      <c r="W187" s="318"/>
-      <c r="X187" s="318"/>
-      <c r="Y187" s="318"/>
-      <c r="Z187" s="318"/>
-      <c r="AA187" s="318"/>
-      <c r="AB187" s="318"/>
-      <c r="AC187" s="318"/>
-      <c r="AD187" s="318"/>
-      <c r="AE187" s="318"/>
-      <c r="AF187" s="318"/>
-      <c r="AG187" s="318"/>
-      <c r="AH187" s="319"/>
+      <c r="P187" s="311"/>
+      <c r="Q187" s="311"/>
+      <c r="R187" s="311"/>
+      <c r="S187" s="311"/>
+      <c r="T187" s="311"/>
+      <c r="U187" s="311"/>
+      <c r="V187" s="311"/>
+      <c r="W187" s="311"/>
+      <c r="X187" s="311"/>
+      <c r="Y187" s="311"/>
+      <c r="Z187" s="311"/>
+      <c r="AA187" s="311"/>
+      <c r="AB187" s="311"/>
+      <c r="AC187" s="311"/>
+      <c r="AD187" s="311"/>
+      <c r="AE187" s="311"/>
+      <c r="AF187" s="311"/>
+      <c r="AG187" s="311"/>
+      <c r="AH187" s="312"/>
     </row>
     <row r="188" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F188" s="320"/>
-      <c r="G188" s="321"/>
-      <c r="H188" s="321"/>
-      <c r="I188" s="321"/>
-      <c r="J188" s="322"/>
-      <c r="K188" s="294"/>
-      <c r="L188" s="296"/>
-      <c r="M188" s="320"/>
-      <c r="N188" s="322"/>
-      <c r="O188" s="320"/>
-      <c r="P188" s="321"/>
-      <c r="Q188" s="321"/>
-      <c r="R188" s="321"/>
-      <c r="S188" s="321"/>
-      <c r="T188" s="321"/>
-      <c r="U188" s="321"/>
-      <c r="V188" s="321"/>
-      <c r="W188" s="321"/>
-      <c r="X188" s="321"/>
-      <c r="Y188" s="321"/>
-      <c r="Z188" s="321"/>
-      <c r="AA188" s="321"/>
-      <c r="AB188" s="321"/>
-      <c r="AC188" s="321"/>
-      <c r="AD188" s="321"/>
-      <c r="AE188" s="321"/>
-      <c r="AF188" s="321"/>
-      <c r="AG188" s="321"/>
-      <c r="AH188" s="322"/>
+      <c r="F188" s="313"/>
+      <c r="G188" s="314"/>
+      <c r="H188" s="314"/>
+      <c r="I188" s="314"/>
+      <c r="J188" s="315"/>
+      <c r="K188" s="296"/>
+      <c r="L188" s="298"/>
+      <c r="M188" s="313"/>
+      <c r="N188" s="315"/>
+      <c r="O188" s="313"/>
+      <c r="P188" s="314"/>
+      <c r="Q188" s="314"/>
+      <c r="R188" s="314"/>
+      <c r="S188" s="314"/>
+      <c r="T188" s="314"/>
+      <c r="U188" s="314"/>
+      <c r="V188" s="314"/>
+      <c r="W188" s="314"/>
+      <c r="X188" s="314"/>
+      <c r="Y188" s="314"/>
+      <c r="Z188" s="314"/>
+      <c r="AA188" s="314"/>
+      <c r="AB188" s="314"/>
+      <c r="AC188" s="314"/>
+      <c r="AD188" s="314"/>
+      <c r="AE188" s="314"/>
+      <c r="AF188" s="314"/>
+      <c r="AG188" s="314"/>
+      <c r="AH188" s="315"/>
     </row>
     <row r="189" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F189" s="337" t="s">
+      <c r="F189" s="340" t="s">
         <v>137</v>
       </c>
-      <c r="G189" s="289"/>
-      <c r="H189" s="289"/>
-      <c r="I189" s="289"/>
-      <c r="J189" s="290"/>
-      <c r="K189" s="337" t="s">
+      <c r="G189" s="291"/>
+      <c r="H189" s="291"/>
+      <c r="I189" s="291"/>
+      <c r="J189" s="292"/>
+      <c r="K189" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L189" s="290"/>
-      <c r="M189" s="337" t="s">
+      <c r="L189" s="292"/>
+      <c r="M189" s="340" t="s">
         <v>72</v>
       </c>
-      <c r="N189" s="319"/>
-      <c r="O189" s="288" t="s">
+      <c r="N189" s="312"/>
+      <c r="O189" s="290" t="s">
         <v>308</v>
       </c>
-      <c r="P189" s="289"/>
-      <c r="Q189" s="289"/>
-      <c r="R189" s="289"/>
-      <c r="S189" s="289"/>
-      <c r="T189" s="289"/>
-      <c r="U189" s="289"/>
-      <c r="V189" s="289"/>
-      <c r="W189" s="289"/>
-      <c r="X189" s="289"/>
-      <c r="Y189" s="289"/>
-      <c r="Z189" s="289"/>
-      <c r="AA189" s="289"/>
-      <c r="AB189" s="289"/>
-      <c r="AC189" s="289"/>
-      <c r="AD189" s="289"/>
-      <c r="AE189" s="289"/>
-      <c r="AF189" s="289"/>
-      <c r="AG189" s="289"/>
-      <c r="AH189" s="290"/>
+      <c r="P189" s="291"/>
+      <c r="Q189" s="291"/>
+      <c r="R189" s="291"/>
+      <c r="S189" s="291"/>
+      <c r="T189" s="291"/>
+      <c r="U189" s="291"/>
+      <c r="V189" s="291"/>
+      <c r="W189" s="291"/>
+      <c r="X189" s="291"/>
+      <c r="Y189" s="291"/>
+      <c r="Z189" s="291"/>
+      <c r="AA189" s="291"/>
+      <c r="AB189" s="291"/>
+      <c r="AC189" s="291"/>
+      <c r="AD189" s="291"/>
+      <c r="AE189" s="291"/>
+      <c r="AF189" s="291"/>
+      <c r="AG189" s="291"/>
+      <c r="AH189" s="292"/>
     </row>
     <row r="190" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F190" s="320"/>
-      <c r="G190" s="321"/>
-      <c r="H190" s="321"/>
-      <c r="I190" s="321"/>
-      <c r="J190" s="322"/>
-      <c r="K190" s="294"/>
-      <c r="L190" s="296"/>
-      <c r="M190" s="320"/>
-      <c r="N190" s="322"/>
-      <c r="O190" s="320"/>
-      <c r="P190" s="321"/>
-      <c r="Q190" s="321"/>
-      <c r="R190" s="321"/>
-      <c r="S190" s="321"/>
-      <c r="T190" s="321"/>
-      <c r="U190" s="321"/>
-      <c r="V190" s="321"/>
-      <c r="W190" s="321"/>
-      <c r="X190" s="321"/>
-      <c r="Y190" s="321"/>
-      <c r="Z190" s="321"/>
-      <c r="AA190" s="321"/>
-      <c r="AB190" s="321"/>
-      <c r="AC190" s="321"/>
-      <c r="AD190" s="321"/>
-      <c r="AE190" s="321"/>
-      <c r="AF190" s="321"/>
-      <c r="AG190" s="321"/>
-      <c r="AH190" s="322"/>
+      <c r="F190" s="313"/>
+      <c r="G190" s="314"/>
+      <c r="H190" s="314"/>
+      <c r="I190" s="314"/>
+      <c r="J190" s="315"/>
+      <c r="K190" s="296"/>
+      <c r="L190" s="298"/>
+      <c r="M190" s="313"/>
+      <c r="N190" s="315"/>
+      <c r="O190" s="313"/>
+      <c r="P190" s="314"/>
+      <c r="Q190" s="314"/>
+      <c r="R190" s="314"/>
+      <c r="S190" s="314"/>
+      <c r="T190" s="314"/>
+      <c r="U190" s="314"/>
+      <c r="V190" s="314"/>
+      <c r="W190" s="314"/>
+      <c r="X190" s="314"/>
+      <c r="Y190" s="314"/>
+      <c r="Z190" s="314"/>
+      <c r="AA190" s="314"/>
+      <c r="AB190" s="314"/>
+      <c r="AC190" s="314"/>
+      <c r="AD190" s="314"/>
+      <c r="AE190" s="314"/>
+      <c r="AF190" s="314"/>
+      <c r="AG190" s="314"/>
+      <c r="AH190" s="315"/>
     </row>
     <row r="191" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F191" s="310" t="s">
+      <c r="F191" s="307" t="s">
         <v>138</v>
       </c>
-      <c r="G191" s="280"/>
-      <c r="H191" s="280"/>
-      <c r="I191" s="280"/>
-      <c r="J191" s="281"/>
-      <c r="K191" s="345" t="s">
+      <c r="G191" s="252"/>
+      <c r="H191" s="252"/>
+      <c r="I191" s="252"/>
+      <c r="J191" s="253"/>
+      <c r="K191" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="L191" s="346"/>
-      <c r="M191" s="345" t="s">
+      <c r="L191" s="364"/>
+      <c r="M191" s="341" t="s">
         <v>72</v>
       </c>
-      <c r="N191" s="350"/>
-      <c r="O191" s="310" t="s">
+      <c r="N191" s="337"/>
+      <c r="O191" s="307" t="s">
         <v>309</v>
       </c>
-      <c r="P191" s="280"/>
-      <c r="Q191" s="280"/>
-      <c r="R191" s="280"/>
-      <c r="S191" s="280"/>
-      <c r="T191" s="280"/>
-      <c r="U191" s="280"/>
-      <c r="V191" s="280"/>
-      <c r="W191" s="280"/>
-      <c r="X191" s="280"/>
-      <c r="Y191" s="280"/>
-      <c r="Z191" s="280"/>
-      <c r="AA191" s="280"/>
-      <c r="AB191" s="280"/>
-      <c r="AC191" s="280"/>
-      <c r="AD191" s="280"/>
-      <c r="AE191" s="280"/>
-      <c r="AF191" s="280"/>
-      <c r="AG191" s="280"/>
-      <c r="AH191" s="281"/>
+      <c r="P191" s="252"/>
+      <c r="Q191" s="252"/>
+      <c r="R191" s="252"/>
+      <c r="S191" s="252"/>
+      <c r="T191" s="252"/>
+      <c r="U191" s="252"/>
+      <c r="V191" s="252"/>
+      <c r="W191" s="252"/>
+      <c r="X191" s="252"/>
+      <c r="Y191" s="252"/>
+      <c r="Z191" s="252"/>
+      <c r="AA191" s="252"/>
+      <c r="AB191" s="252"/>
+      <c r="AC191" s="252"/>
+      <c r="AD191" s="252"/>
+      <c r="AE191" s="252"/>
+      <c r="AF191" s="252"/>
+      <c r="AG191" s="252"/>
+      <c r="AH191" s="253"/>
     </row>
     <row r="192" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F192" s="337" t="s">
+      <c r="F192" s="340" t="s">
         <v>49</v>
       </c>
-      <c r="G192" s="289"/>
-      <c r="H192" s="289"/>
-      <c r="I192" s="289"/>
-      <c r="J192" s="290"/>
-      <c r="K192" s="337" t="s">
+      <c r="G192" s="291"/>
+      <c r="H192" s="291"/>
+      <c r="I192" s="291"/>
+      <c r="J192" s="292"/>
+      <c r="K192" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="L192" s="290"/>
-      <c r="M192" s="337" t="s">
+      <c r="L192" s="292"/>
+      <c r="M192" s="340" t="s">
         <v>77</v>
       </c>
-      <c r="N192" s="319"/>
-      <c r="O192" s="288" t="s">
+      <c r="N192" s="312"/>
+      <c r="O192" s="290" t="s">
         <v>498</v>
       </c>
-      <c r="P192" s="318"/>
-      <c r="Q192" s="318"/>
-      <c r="R192" s="318"/>
-      <c r="S192" s="318"/>
-      <c r="T192" s="318"/>
-      <c r="U192" s="318"/>
-      <c r="V192" s="318"/>
-      <c r="W192" s="318"/>
-      <c r="X192" s="318"/>
-      <c r="Y192" s="318"/>
-      <c r="Z192" s="318"/>
-      <c r="AA192" s="318"/>
-      <c r="AB192" s="318"/>
-      <c r="AC192" s="318"/>
-      <c r="AD192" s="318"/>
-      <c r="AE192" s="318"/>
-      <c r="AF192" s="318"/>
-      <c r="AG192" s="318"/>
-      <c r="AH192" s="319"/>
+      <c r="P192" s="311"/>
+      <c r="Q192" s="311"/>
+      <c r="R192" s="311"/>
+      <c r="S192" s="311"/>
+      <c r="T192" s="311"/>
+      <c r="U192" s="311"/>
+      <c r="V192" s="311"/>
+      <c r="W192" s="311"/>
+      <c r="X192" s="311"/>
+      <c r="Y192" s="311"/>
+      <c r="Z192" s="311"/>
+      <c r="AA192" s="311"/>
+      <c r="AB192" s="311"/>
+      <c r="AC192" s="311"/>
+      <c r="AD192" s="311"/>
+      <c r="AE192" s="311"/>
+      <c r="AF192" s="311"/>
+      <c r="AG192" s="311"/>
+      <c r="AH192" s="312"/>
     </row>
     <row r="193" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F193" s="320"/>
-      <c r="G193" s="321"/>
-      <c r="H193" s="321"/>
-      <c r="I193" s="321"/>
-      <c r="J193" s="322"/>
-      <c r="K193" s="294"/>
-      <c r="L193" s="296"/>
-      <c r="M193" s="320"/>
-      <c r="N193" s="322"/>
-      <c r="O193" s="320"/>
-      <c r="P193" s="321"/>
-      <c r="Q193" s="321"/>
-      <c r="R193" s="321"/>
-      <c r="S193" s="321"/>
-      <c r="T193" s="321"/>
-      <c r="U193" s="321"/>
-      <c r="V193" s="321"/>
-      <c r="W193" s="321"/>
-      <c r="X193" s="321"/>
-      <c r="Y193" s="321"/>
-      <c r="Z193" s="321"/>
-      <c r="AA193" s="321"/>
-      <c r="AB193" s="321"/>
-      <c r="AC193" s="321"/>
-      <c r="AD193" s="321"/>
-      <c r="AE193" s="321"/>
-      <c r="AF193" s="321"/>
-      <c r="AG193" s="321"/>
-      <c r="AH193" s="322"/>
+      <c r="F193" s="313"/>
+      <c r="G193" s="314"/>
+      <c r="H193" s="314"/>
+      <c r="I193" s="314"/>
+      <c r="J193" s="315"/>
+      <c r="K193" s="296"/>
+      <c r="L193" s="298"/>
+      <c r="M193" s="313"/>
+      <c r="N193" s="315"/>
+      <c r="O193" s="313"/>
+      <c r="P193" s="314"/>
+      <c r="Q193" s="314"/>
+      <c r="R193" s="314"/>
+      <c r="S193" s="314"/>
+      <c r="T193" s="314"/>
+      <c r="U193" s="314"/>
+      <c r="V193" s="314"/>
+      <c r="W193" s="314"/>
+      <c r="X193" s="314"/>
+      <c r="Y193" s="314"/>
+      <c r="Z193" s="314"/>
+      <c r="AA193" s="314"/>
+      <c r="AB193" s="314"/>
+      <c r="AC193" s="314"/>
+      <c r="AD193" s="314"/>
+      <c r="AE193" s="314"/>
+      <c r="AF193" s="314"/>
+      <c r="AG193" s="314"/>
+      <c r="AH193" s="315"/>
     </row>
     <row r="194" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F194" s="279" t="s">
+      <c r="F194" s="251" t="s">
         <v>42</v>
       </c>
-      <c r="G194" s="280"/>
-      <c r="H194" s="280"/>
-      <c r="I194" s="280"/>
-      <c r="J194" s="281"/>
-      <c r="K194" s="345" t="s">
+      <c r="G194" s="252"/>
+      <c r="H194" s="252"/>
+      <c r="I194" s="252"/>
+      <c r="J194" s="253"/>
+      <c r="K194" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="L194" s="346"/>
-      <c r="M194" s="345" t="s">
+      <c r="L194" s="364"/>
+      <c r="M194" s="341" t="s">
         <v>76</v>
       </c>
-      <c r="N194" s="350"/>
-      <c r="O194" s="310" t="s">
+      <c r="N194" s="337"/>
+      <c r="O194" s="307" t="s">
         <v>309</v>
       </c>
-      <c r="P194" s="280"/>
-      <c r="Q194" s="280"/>
-      <c r="R194" s="280"/>
-      <c r="S194" s="280"/>
-      <c r="T194" s="280"/>
-      <c r="U194" s="280"/>
-      <c r="V194" s="280"/>
-      <c r="W194" s="280"/>
-      <c r="X194" s="280"/>
-      <c r="Y194" s="280"/>
-      <c r="Z194" s="280"/>
-      <c r="AA194" s="280"/>
-      <c r="AB194" s="280"/>
-      <c r="AC194" s="280"/>
-      <c r="AD194" s="280"/>
-      <c r="AE194" s="280"/>
-      <c r="AF194" s="280"/>
-      <c r="AG194" s="280"/>
-      <c r="AH194" s="281"/>
+      <c r="P194" s="252"/>
+      <c r="Q194" s="252"/>
+      <c r="R194" s="252"/>
+      <c r="S194" s="252"/>
+      <c r="T194" s="252"/>
+      <c r="U194" s="252"/>
+      <c r="V194" s="252"/>
+      <c r="W194" s="252"/>
+      <c r="X194" s="252"/>
+      <c r="Y194" s="252"/>
+      <c r="Z194" s="252"/>
+      <c r="AA194" s="252"/>
+      <c r="AB194" s="252"/>
+      <c r="AC194" s="252"/>
+      <c r="AD194" s="252"/>
+      <c r="AE194" s="252"/>
+      <c r="AF194" s="252"/>
+      <c r="AG194" s="252"/>
+      <c r="AH194" s="253"/>
     </row>
     <row r="195" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E195" s="30"/>
-      <c r="F195" s="317" t="s">
+      <c r="F195" s="310" t="s">
         <v>270</v>
       </c>
-      <c r="G195" s="318"/>
-      <c r="H195" s="318"/>
-      <c r="I195" s="318"/>
-      <c r="J195" s="319"/>
-      <c r="K195" s="328" t="s">
+      <c r="G195" s="311"/>
+      <c r="H195" s="311"/>
+      <c r="I195" s="311"/>
+      <c r="J195" s="312"/>
+      <c r="K195" s="351" t="s">
         <v>46</v>
       </c>
-      <c r="L195" s="329"/>
-      <c r="M195" s="337" t="s">
+      <c r="L195" s="352"/>
+      <c r="M195" s="340" t="s">
         <v>76</v>
       </c>
-      <c r="N195" s="319"/>
-      <c r="O195" s="288" t="s">
+      <c r="N195" s="312"/>
+      <c r="O195" s="290" t="s">
         <v>309</v>
       </c>
-      <c r="P195" s="289"/>
-      <c r="Q195" s="289"/>
-      <c r="R195" s="289"/>
-      <c r="S195" s="289"/>
-      <c r="T195" s="289"/>
-      <c r="U195" s="289"/>
-      <c r="V195" s="289"/>
-      <c r="W195" s="289"/>
-      <c r="X195" s="289"/>
-      <c r="Y195" s="289"/>
-      <c r="Z195" s="289"/>
-      <c r="AA195" s="289"/>
-      <c r="AB195" s="289"/>
-      <c r="AC195" s="289"/>
-      <c r="AD195" s="289"/>
-      <c r="AE195" s="289"/>
-      <c r="AF195" s="289"/>
-      <c r="AG195" s="289"/>
-      <c r="AH195" s="290"/>
+      <c r="P195" s="291"/>
+      <c r="Q195" s="291"/>
+      <c r="R195" s="291"/>
+      <c r="S195" s="291"/>
+      <c r="T195" s="291"/>
+      <c r="U195" s="291"/>
+      <c r="V195" s="291"/>
+      <c r="W195" s="291"/>
+      <c r="X195" s="291"/>
+      <c r="Y195" s="291"/>
+      <c r="Z195" s="291"/>
+      <c r="AA195" s="291"/>
+      <c r="AB195" s="291"/>
+      <c r="AC195" s="291"/>
+      <c r="AD195" s="291"/>
+      <c r="AE195" s="291"/>
+      <c r="AF195" s="291"/>
+      <c r="AG195" s="291"/>
+      <c r="AH195" s="292"/>
     </row>
     <row r="196" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E196" s="30"/>
-      <c r="F196" s="320"/>
-      <c r="G196" s="321"/>
-      <c r="H196" s="321"/>
-      <c r="I196" s="321"/>
-      <c r="J196" s="322"/>
-      <c r="K196" s="325"/>
-      <c r="L196" s="327"/>
-      <c r="M196" s="320"/>
-      <c r="N196" s="322"/>
-      <c r="O196" s="320"/>
-      <c r="P196" s="321"/>
-      <c r="Q196" s="321"/>
-      <c r="R196" s="321"/>
-      <c r="S196" s="321"/>
-      <c r="T196" s="321"/>
-      <c r="U196" s="321"/>
-      <c r="V196" s="321"/>
-      <c r="W196" s="321"/>
-      <c r="X196" s="321"/>
-      <c r="Y196" s="321"/>
-      <c r="Z196" s="321"/>
-      <c r="AA196" s="321"/>
-      <c r="AB196" s="321"/>
-      <c r="AC196" s="321"/>
-      <c r="AD196" s="321"/>
-      <c r="AE196" s="321"/>
-      <c r="AF196" s="321"/>
-      <c r="AG196" s="321"/>
-      <c r="AH196" s="322"/>
+      <c r="F196" s="313"/>
+      <c r="G196" s="314"/>
+      <c r="H196" s="314"/>
+      <c r="I196" s="314"/>
+      <c r="J196" s="315"/>
+      <c r="K196" s="359"/>
+      <c r="L196" s="361"/>
+      <c r="M196" s="313"/>
+      <c r="N196" s="315"/>
+      <c r="O196" s="313"/>
+      <c r="P196" s="314"/>
+      <c r="Q196" s="314"/>
+      <c r="R196" s="314"/>
+      <c r="S196" s="314"/>
+      <c r="T196" s="314"/>
+      <c r="U196" s="314"/>
+      <c r="V196" s="314"/>
+      <c r="W196" s="314"/>
+      <c r="X196" s="314"/>
+      <c r="Y196" s="314"/>
+      <c r="Z196" s="314"/>
+      <c r="AA196" s="314"/>
+      <c r="AB196" s="314"/>
+      <c r="AC196" s="314"/>
+      <c r="AD196" s="314"/>
+      <c r="AE196" s="314"/>
+      <c r="AF196" s="314"/>
+      <c r="AG196" s="314"/>
+      <c r="AH196" s="315"/>
     </row>
     <row r="197" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="198" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -43697,689 +43697,689 @@
     </row>
     <row r="200" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="201" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F201" s="331" t="s">
+      <c r="F201" s="365" t="s">
         <v>630</v>
       </c>
-      <c r="G201" s="332"/>
-      <c r="H201" s="332"/>
-      <c r="I201" s="332"/>
-      <c r="J201" s="333"/>
-      <c r="K201" s="348" t="s">
+      <c r="G201" s="366"/>
+      <c r="H201" s="366"/>
+      <c r="I201" s="366"/>
+      <c r="J201" s="367"/>
+      <c r="K201" s="355" t="s">
         <v>30</v>
       </c>
-      <c r="L201" s="349"/>
-      <c r="M201" s="348" t="s">
+      <c r="L201" s="356"/>
+      <c r="M201" s="355" t="s">
         <v>31</v>
       </c>
-      <c r="N201" s="349"/>
-      <c r="O201" s="276" t="s">
+      <c r="N201" s="356"/>
+      <c r="O201" s="248" t="s">
         <v>305</v>
       </c>
-      <c r="P201" s="277"/>
-      <c r="Q201" s="277"/>
-      <c r="R201" s="277"/>
-      <c r="S201" s="277"/>
-      <c r="T201" s="277"/>
-      <c r="U201" s="277"/>
-      <c r="V201" s="277"/>
-      <c r="W201" s="277"/>
-      <c r="X201" s="277"/>
-      <c r="Y201" s="277"/>
-      <c r="Z201" s="277"/>
-      <c r="AA201" s="277"/>
-      <c r="AB201" s="277"/>
-      <c r="AC201" s="277"/>
-      <c r="AD201" s="277"/>
-      <c r="AE201" s="277"/>
-      <c r="AF201" s="277"/>
-      <c r="AG201" s="277"/>
-      <c r="AH201" s="278"/>
+      <c r="P201" s="249"/>
+      <c r="Q201" s="249"/>
+      <c r="R201" s="249"/>
+      <c r="S201" s="249"/>
+      <c r="T201" s="249"/>
+      <c r="U201" s="249"/>
+      <c r="V201" s="249"/>
+      <c r="W201" s="249"/>
+      <c r="X201" s="249"/>
+      <c r="Y201" s="249"/>
+      <c r="Z201" s="249"/>
+      <c r="AA201" s="249"/>
+      <c r="AB201" s="249"/>
+      <c r="AC201" s="249"/>
+      <c r="AD201" s="249"/>
+      <c r="AE201" s="249"/>
+      <c r="AF201" s="249"/>
+      <c r="AG201" s="249"/>
+      <c r="AH201" s="250"/>
     </row>
     <row r="202" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F202" s="317" t="s">
+      <c r="F202" s="310" t="s">
         <v>285</v>
       </c>
-      <c r="G202" s="323"/>
-      <c r="H202" s="323"/>
-      <c r="I202" s="323"/>
-      <c r="J202" s="324"/>
-      <c r="K202" s="337" t="s">
+      <c r="G202" s="357"/>
+      <c r="H202" s="357"/>
+      <c r="I202" s="357"/>
+      <c r="J202" s="358"/>
+      <c r="K202" s="340" t="s">
         <v>32</v>
       </c>
-      <c r="L202" s="290"/>
-      <c r="M202" s="337" t="s">
+      <c r="L202" s="292"/>
+      <c r="M202" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N202" s="290"/>
-      <c r="O202" s="317" t="s">
+      <c r="N202" s="292"/>
+      <c r="O202" s="310" t="s">
         <v>287</v>
       </c>
-      <c r="P202" s="323"/>
-      <c r="Q202" s="323"/>
-      <c r="R202" s="323"/>
-      <c r="S202" s="323"/>
-      <c r="T202" s="323"/>
-      <c r="U202" s="323"/>
-      <c r="V202" s="323"/>
-      <c r="W202" s="323"/>
-      <c r="X202" s="323"/>
-      <c r="Y202" s="323"/>
-      <c r="Z202" s="323"/>
-      <c r="AA202" s="323"/>
-      <c r="AB202" s="323"/>
-      <c r="AC202" s="323"/>
-      <c r="AD202" s="323"/>
-      <c r="AE202" s="323"/>
-      <c r="AF202" s="323"/>
-      <c r="AG202" s="323"/>
-      <c r="AH202" s="324"/>
+      <c r="P202" s="357"/>
+      <c r="Q202" s="357"/>
+      <c r="R202" s="357"/>
+      <c r="S202" s="357"/>
+      <c r="T202" s="357"/>
+      <c r="U202" s="357"/>
+      <c r="V202" s="357"/>
+      <c r="W202" s="357"/>
+      <c r="X202" s="357"/>
+      <c r="Y202" s="357"/>
+      <c r="Z202" s="357"/>
+      <c r="AA202" s="357"/>
+      <c r="AB202" s="357"/>
+      <c r="AC202" s="357"/>
+      <c r="AD202" s="357"/>
+      <c r="AE202" s="357"/>
+      <c r="AF202" s="357"/>
+      <c r="AG202" s="357"/>
+      <c r="AH202" s="358"/>
     </row>
     <row r="203" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F203" s="325"/>
-      <c r="G203" s="326"/>
-      <c r="H203" s="326"/>
-      <c r="I203" s="326"/>
-      <c r="J203" s="327"/>
-      <c r="K203" s="294"/>
-      <c r="L203" s="296"/>
-      <c r="M203" s="294"/>
-      <c r="N203" s="296"/>
-      <c r="O203" s="325"/>
-      <c r="P203" s="326"/>
-      <c r="Q203" s="326"/>
-      <c r="R203" s="326"/>
-      <c r="S203" s="326"/>
-      <c r="T203" s="326"/>
-      <c r="U203" s="326"/>
-      <c r="V203" s="326"/>
-      <c r="W203" s="326"/>
-      <c r="X203" s="326"/>
-      <c r="Y203" s="326"/>
-      <c r="Z203" s="326"/>
-      <c r="AA203" s="326"/>
-      <c r="AB203" s="326"/>
-      <c r="AC203" s="326"/>
-      <c r="AD203" s="326"/>
-      <c r="AE203" s="326"/>
-      <c r="AF203" s="326"/>
-      <c r="AG203" s="326"/>
-      <c r="AH203" s="327"/>
+      <c r="F203" s="359"/>
+      <c r="G203" s="360"/>
+      <c r="H203" s="360"/>
+      <c r="I203" s="360"/>
+      <c r="J203" s="361"/>
+      <c r="K203" s="296"/>
+      <c r="L203" s="298"/>
+      <c r="M203" s="296"/>
+      <c r="N203" s="298"/>
+      <c r="O203" s="359"/>
+      <c r="P203" s="360"/>
+      <c r="Q203" s="360"/>
+      <c r="R203" s="360"/>
+      <c r="S203" s="360"/>
+      <c r="T203" s="360"/>
+      <c r="U203" s="360"/>
+      <c r="V203" s="360"/>
+      <c r="W203" s="360"/>
+      <c r="X203" s="360"/>
+      <c r="Y203" s="360"/>
+      <c r="Z203" s="360"/>
+      <c r="AA203" s="360"/>
+      <c r="AB203" s="360"/>
+      <c r="AC203" s="360"/>
+      <c r="AD203" s="360"/>
+      <c r="AE203" s="360"/>
+      <c r="AF203" s="360"/>
+      <c r="AG203" s="360"/>
+      <c r="AH203" s="361"/>
     </row>
     <row r="204" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F204" s="328" t="s">
+      <c r="F204" s="351" t="s">
         <v>40</v>
       </c>
-      <c r="G204" s="330"/>
-      <c r="H204" s="330"/>
-      <c r="I204" s="330"/>
-      <c r="J204" s="329"/>
-      <c r="K204" s="337" t="s">
+      <c r="G204" s="362"/>
+      <c r="H204" s="362"/>
+      <c r="I204" s="362"/>
+      <c r="J204" s="352"/>
+      <c r="K204" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L204" s="290"/>
-      <c r="M204" s="337" t="s">
+      <c r="L204" s="292"/>
+      <c r="M204" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N204" s="290"/>
-      <c r="O204" s="317" t="s">
+      <c r="N204" s="292"/>
+      <c r="O204" s="310" t="s">
         <v>493</v>
       </c>
-      <c r="P204" s="323"/>
-      <c r="Q204" s="323"/>
-      <c r="R204" s="323"/>
-      <c r="S204" s="323"/>
-      <c r="T204" s="323"/>
-      <c r="U204" s="323"/>
-      <c r="V204" s="323"/>
-      <c r="W204" s="323"/>
-      <c r="X204" s="323"/>
-      <c r="Y204" s="323"/>
-      <c r="Z204" s="323"/>
-      <c r="AA204" s="323"/>
-      <c r="AB204" s="323"/>
-      <c r="AC204" s="323"/>
-      <c r="AD204" s="323"/>
-      <c r="AE204" s="323"/>
-      <c r="AF204" s="323"/>
-      <c r="AG204" s="323"/>
-      <c r="AH204" s="324"/>
+      <c r="P204" s="357"/>
+      <c r="Q204" s="357"/>
+      <c r="R204" s="357"/>
+      <c r="S204" s="357"/>
+      <c r="T204" s="357"/>
+      <c r="U204" s="357"/>
+      <c r="V204" s="357"/>
+      <c r="W204" s="357"/>
+      <c r="X204" s="357"/>
+      <c r="Y204" s="357"/>
+      <c r="Z204" s="357"/>
+      <c r="AA204" s="357"/>
+      <c r="AB204" s="357"/>
+      <c r="AC204" s="357"/>
+      <c r="AD204" s="357"/>
+      <c r="AE204" s="357"/>
+      <c r="AF204" s="357"/>
+      <c r="AG204" s="357"/>
+      <c r="AH204" s="358"/>
     </row>
     <row r="205" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F205" s="325"/>
-      <c r="G205" s="326"/>
-      <c r="H205" s="326"/>
-      <c r="I205" s="326"/>
-      <c r="J205" s="327"/>
-      <c r="K205" s="294"/>
-      <c r="L205" s="296"/>
-      <c r="M205" s="294"/>
-      <c r="N205" s="296"/>
-      <c r="O205" s="325"/>
-      <c r="P205" s="326"/>
-      <c r="Q205" s="326"/>
-      <c r="R205" s="326"/>
-      <c r="S205" s="326"/>
-      <c r="T205" s="326"/>
-      <c r="U205" s="326"/>
-      <c r="V205" s="326"/>
-      <c r="W205" s="326"/>
-      <c r="X205" s="326"/>
-      <c r="Y205" s="326"/>
-      <c r="Z205" s="326"/>
-      <c r="AA205" s="326"/>
-      <c r="AB205" s="326"/>
-      <c r="AC205" s="326"/>
-      <c r="AD205" s="326"/>
-      <c r="AE205" s="326"/>
-      <c r="AF205" s="326"/>
-      <c r="AG205" s="326"/>
-      <c r="AH205" s="327"/>
+      <c r="F205" s="359"/>
+      <c r="G205" s="360"/>
+      <c r="H205" s="360"/>
+      <c r="I205" s="360"/>
+      <c r="J205" s="361"/>
+      <c r="K205" s="296"/>
+      <c r="L205" s="298"/>
+      <c r="M205" s="296"/>
+      <c r="N205" s="298"/>
+      <c r="O205" s="359"/>
+      <c r="P205" s="360"/>
+      <c r="Q205" s="360"/>
+      <c r="R205" s="360"/>
+      <c r="S205" s="360"/>
+      <c r="T205" s="360"/>
+      <c r="U205" s="360"/>
+      <c r="V205" s="360"/>
+      <c r="W205" s="360"/>
+      <c r="X205" s="360"/>
+      <c r="Y205" s="360"/>
+      <c r="Z205" s="360"/>
+      <c r="AA205" s="360"/>
+      <c r="AB205" s="360"/>
+      <c r="AC205" s="360"/>
+      <c r="AD205" s="360"/>
+      <c r="AE205" s="360"/>
+      <c r="AF205" s="360"/>
+      <c r="AG205" s="360"/>
+      <c r="AH205" s="361"/>
     </row>
     <row r="206" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F206" s="328" t="s">
+      <c r="F206" s="351" t="s">
         <v>41</v>
       </c>
-      <c r="G206" s="330"/>
-      <c r="H206" s="330"/>
-      <c r="I206" s="330"/>
-      <c r="J206" s="329"/>
-      <c r="K206" s="328" t="s">
+      <c r="G206" s="362"/>
+      <c r="H206" s="362"/>
+      <c r="I206" s="362"/>
+      <c r="J206" s="352"/>
+      <c r="K206" s="351" t="s">
         <v>35</v>
       </c>
-      <c r="L206" s="329"/>
-      <c r="M206" s="328" t="s">
+      <c r="L206" s="352"/>
+      <c r="M206" s="351" t="s">
         <v>33</v>
       </c>
-      <c r="N206" s="329"/>
-      <c r="O206" s="317" t="s">
+      <c r="N206" s="352"/>
+      <c r="O206" s="310" t="s">
         <v>494</v>
       </c>
-      <c r="P206" s="323"/>
-      <c r="Q206" s="323"/>
-      <c r="R206" s="323"/>
-      <c r="S206" s="323"/>
-      <c r="T206" s="323"/>
-      <c r="U206" s="323"/>
-      <c r="V206" s="323"/>
-      <c r="W206" s="323"/>
-      <c r="X206" s="323"/>
-      <c r="Y206" s="323"/>
-      <c r="Z206" s="323"/>
-      <c r="AA206" s="323"/>
-      <c r="AB206" s="323"/>
-      <c r="AC206" s="323"/>
-      <c r="AD206" s="323"/>
-      <c r="AE206" s="323"/>
-      <c r="AF206" s="323"/>
-      <c r="AG206" s="323"/>
-      <c r="AH206" s="324"/>
+      <c r="P206" s="357"/>
+      <c r="Q206" s="357"/>
+      <c r="R206" s="357"/>
+      <c r="S206" s="357"/>
+      <c r="T206" s="357"/>
+      <c r="U206" s="357"/>
+      <c r="V206" s="357"/>
+      <c r="W206" s="357"/>
+      <c r="X206" s="357"/>
+      <c r="Y206" s="357"/>
+      <c r="Z206" s="357"/>
+      <c r="AA206" s="357"/>
+      <c r="AB206" s="357"/>
+      <c r="AC206" s="357"/>
+      <c r="AD206" s="357"/>
+      <c r="AE206" s="357"/>
+      <c r="AF206" s="357"/>
+      <c r="AG206" s="357"/>
+      <c r="AH206" s="358"/>
     </row>
     <row r="207" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F207" s="325"/>
-      <c r="G207" s="326"/>
-      <c r="H207" s="326"/>
-      <c r="I207" s="326"/>
-      <c r="J207" s="327"/>
-      <c r="K207" s="351"/>
-      <c r="L207" s="352"/>
-      <c r="M207" s="351"/>
-      <c r="N207" s="352"/>
-      <c r="O207" s="325"/>
-      <c r="P207" s="326"/>
-      <c r="Q207" s="326"/>
-      <c r="R207" s="326"/>
-      <c r="S207" s="326"/>
-      <c r="T207" s="326"/>
-      <c r="U207" s="326"/>
-      <c r="V207" s="326"/>
-      <c r="W207" s="326"/>
-      <c r="X207" s="326"/>
-      <c r="Y207" s="326"/>
-      <c r="Z207" s="326"/>
-      <c r="AA207" s="326"/>
-      <c r="AB207" s="326"/>
-      <c r="AC207" s="326"/>
-      <c r="AD207" s="326"/>
-      <c r="AE207" s="326"/>
-      <c r="AF207" s="326"/>
-      <c r="AG207" s="326"/>
-      <c r="AH207" s="327"/>
+      <c r="F207" s="359"/>
+      <c r="G207" s="360"/>
+      <c r="H207" s="360"/>
+      <c r="I207" s="360"/>
+      <c r="J207" s="361"/>
+      <c r="K207" s="353"/>
+      <c r="L207" s="354"/>
+      <c r="M207" s="353"/>
+      <c r="N207" s="354"/>
+      <c r="O207" s="359"/>
+      <c r="P207" s="360"/>
+      <c r="Q207" s="360"/>
+      <c r="R207" s="360"/>
+      <c r="S207" s="360"/>
+      <c r="T207" s="360"/>
+      <c r="U207" s="360"/>
+      <c r="V207" s="360"/>
+      <c r="W207" s="360"/>
+      <c r="X207" s="360"/>
+      <c r="Y207" s="360"/>
+      <c r="Z207" s="360"/>
+      <c r="AA207" s="360"/>
+      <c r="AB207" s="360"/>
+      <c r="AC207" s="360"/>
+      <c r="AD207" s="360"/>
+      <c r="AE207" s="360"/>
+      <c r="AF207" s="360"/>
+      <c r="AG207" s="360"/>
+      <c r="AH207" s="361"/>
     </row>
     <row r="208" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F208" s="317" t="s">
+      <c r="F208" s="310" t="s">
         <v>286</v>
       </c>
-      <c r="G208" s="323"/>
-      <c r="H208" s="323"/>
-      <c r="I208" s="323"/>
-      <c r="J208" s="324"/>
-      <c r="K208" s="337" t="s">
+      <c r="G208" s="357"/>
+      <c r="H208" s="357"/>
+      <c r="I208" s="357"/>
+      <c r="J208" s="358"/>
+      <c r="K208" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L208" s="290"/>
-      <c r="M208" s="337" t="s">
+      <c r="L208" s="292"/>
+      <c r="M208" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N208" s="290"/>
-      <c r="O208" s="317" t="s">
+      <c r="N208" s="292"/>
+      <c r="O208" s="310" t="s">
         <v>495</v>
       </c>
-      <c r="P208" s="323"/>
-      <c r="Q208" s="323"/>
-      <c r="R208" s="323"/>
-      <c r="S208" s="323"/>
-      <c r="T208" s="323"/>
-      <c r="U208" s="323"/>
-      <c r="V208" s="323"/>
-      <c r="W208" s="323"/>
-      <c r="X208" s="323"/>
-      <c r="Y208" s="323"/>
-      <c r="Z208" s="323"/>
-      <c r="AA208" s="323"/>
-      <c r="AB208" s="323"/>
-      <c r="AC208" s="323"/>
-      <c r="AD208" s="323"/>
-      <c r="AE208" s="323"/>
-      <c r="AF208" s="323"/>
-      <c r="AG208" s="323"/>
-      <c r="AH208" s="324"/>
+      <c r="P208" s="357"/>
+      <c r="Q208" s="357"/>
+      <c r="R208" s="357"/>
+      <c r="S208" s="357"/>
+      <c r="T208" s="357"/>
+      <c r="U208" s="357"/>
+      <c r="V208" s="357"/>
+      <c r="W208" s="357"/>
+      <c r="X208" s="357"/>
+      <c r="Y208" s="357"/>
+      <c r="Z208" s="357"/>
+      <c r="AA208" s="357"/>
+      <c r="AB208" s="357"/>
+      <c r="AC208" s="357"/>
+      <c r="AD208" s="357"/>
+      <c r="AE208" s="357"/>
+      <c r="AF208" s="357"/>
+      <c r="AG208" s="357"/>
+      <c r="AH208" s="358"/>
     </row>
     <row r="209" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F209" s="325"/>
-      <c r="G209" s="326"/>
-      <c r="H209" s="326"/>
-      <c r="I209" s="326"/>
-      <c r="J209" s="327"/>
-      <c r="K209" s="294"/>
-      <c r="L209" s="296"/>
-      <c r="M209" s="294"/>
-      <c r="N209" s="296"/>
-      <c r="O209" s="325"/>
-      <c r="P209" s="326"/>
-      <c r="Q209" s="326"/>
-      <c r="R209" s="326"/>
-      <c r="S209" s="326"/>
-      <c r="T209" s="326"/>
-      <c r="U209" s="326"/>
-      <c r="V209" s="326"/>
-      <c r="W209" s="326"/>
-      <c r="X209" s="326"/>
-      <c r="Y209" s="326"/>
-      <c r="Z209" s="326"/>
-      <c r="AA209" s="326"/>
-      <c r="AB209" s="326"/>
-      <c r="AC209" s="326"/>
-      <c r="AD209" s="326"/>
-      <c r="AE209" s="326"/>
-      <c r="AF209" s="326"/>
-      <c r="AG209" s="326"/>
-      <c r="AH209" s="327"/>
+      <c r="F209" s="359"/>
+      <c r="G209" s="360"/>
+      <c r="H209" s="360"/>
+      <c r="I209" s="360"/>
+      <c r="J209" s="361"/>
+      <c r="K209" s="296"/>
+      <c r="L209" s="298"/>
+      <c r="M209" s="296"/>
+      <c r="N209" s="298"/>
+      <c r="O209" s="359"/>
+      <c r="P209" s="360"/>
+      <c r="Q209" s="360"/>
+      <c r="R209" s="360"/>
+      <c r="S209" s="360"/>
+      <c r="T209" s="360"/>
+      <c r="U209" s="360"/>
+      <c r="V209" s="360"/>
+      <c r="W209" s="360"/>
+      <c r="X209" s="360"/>
+      <c r="Y209" s="360"/>
+      <c r="Z209" s="360"/>
+      <c r="AA209" s="360"/>
+      <c r="AB209" s="360"/>
+      <c r="AC209" s="360"/>
+      <c r="AD209" s="360"/>
+      <c r="AE209" s="360"/>
+      <c r="AF209" s="360"/>
+      <c r="AG209" s="360"/>
+      <c r="AH209" s="361"/>
     </row>
     <row r="210" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F210" s="279" t="s">
+      <c r="F210" s="251" t="s">
         <v>38</v>
       </c>
-      <c r="G210" s="280"/>
-      <c r="H210" s="280"/>
-      <c r="I210" s="280"/>
-      <c r="J210" s="281"/>
-      <c r="K210" s="181" t="s">
+      <c r="G210" s="252"/>
+      <c r="H210" s="252"/>
+      <c r="I210" s="252"/>
+      <c r="J210" s="253"/>
+      <c r="K210" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L210" s="183"/>
-      <c r="M210" s="181" t="s">
+      <c r="L210" s="220"/>
+      <c r="M210" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N210" s="183"/>
-      <c r="O210" s="347" t="s">
+      <c r="N210" s="220"/>
+      <c r="O210" s="334" t="s">
         <v>340</v>
       </c>
-      <c r="P210" s="339"/>
-      <c r="Q210" s="339"/>
-      <c r="R210" s="339"/>
-      <c r="S210" s="339"/>
-      <c r="T210" s="339"/>
-      <c r="U210" s="339"/>
-      <c r="V210" s="339"/>
-      <c r="W210" s="339"/>
-      <c r="X210" s="339"/>
-      <c r="Y210" s="339"/>
-      <c r="Z210" s="339"/>
-      <c r="AA210" s="339"/>
-      <c r="AB210" s="339"/>
-      <c r="AC210" s="339"/>
-      <c r="AD210" s="339"/>
-      <c r="AE210" s="339"/>
-      <c r="AF210" s="339"/>
-      <c r="AG210" s="339"/>
-      <c r="AH210" s="340"/>
+      <c r="P210" s="344"/>
+      <c r="Q210" s="344"/>
+      <c r="R210" s="344"/>
+      <c r="S210" s="344"/>
+      <c r="T210" s="344"/>
+      <c r="U210" s="344"/>
+      <c r="V210" s="344"/>
+      <c r="W210" s="344"/>
+      <c r="X210" s="344"/>
+      <c r="Y210" s="344"/>
+      <c r="Z210" s="344"/>
+      <c r="AA210" s="344"/>
+      <c r="AB210" s="344"/>
+      <c r="AC210" s="344"/>
+      <c r="AD210" s="344"/>
+      <c r="AE210" s="344"/>
+      <c r="AF210" s="344"/>
+      <c r="AG210" s="344"/>
+      <c r="AH210" s="345"/>
     </row>
     <row r="211" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F211" s="279" t="s">
+      <c r="F211" s="251" t="s">
         <v>39</v>
       </c>
-      <c r="G211" s="280"/>
-      <c r="H211" s="280"/>
-      <c r="I211" s="280"/>
-      <c r="J211" s="281"/>
-      <c r="K211" s="181" t="s">
+      <c r="G211" s="252"/>
+      <c r="H211" s="252"/>
+      <c r="I211" s="252"/>
+      <c r="J211" s="253"/>
+      <c r="K211" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L211" s="183"/>
-      <c r="M211" s="181" t="s">
+      <c r="L211" s="220"/>
+      <c r="M211" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N211" s="183"/>
-      <c r="O211" s="347" t="s">
+      <c r="N211" s="220"/>
+      <c r="O211" s="334" t="s">
         <v>284</v>
       </c>
-      <c r="P211" s="286"/>
-      <c r="Q211" s="286"/>
-      <c r="R211" s="286"/>
-      <c r="S211" s="286"/>
-      <c r="T211" s="286"/>
-      <c r="U211" s="286"/>
-      <c r="V211" s="286"/>
-      <c r="W211" s="286"/>
-      <c r="X211" s="286"/>
-      <c r="Y211" s="286"/>
-      <c r="Z211" s="286"/>
-      <c r="AA211" s="286"/>
-      <c r="AB211" s="286"/>
-      <c r="AC211" s="286"/>
-      <c r="AD211" s="286"/>
-      <c r="AE211" s="286"/>
-      <c r="AF211" s="286"/>
-      <c r="AG211" s="286"/>
-      <c r="AH211" s="287"/>
+      <c r="P211" s="288"/>
+      <c r="Q211" s="288"/>
+      <c r="R211" s="288"/>
+      <c r="S211" s="288"/>
+      <c r="T211" s="288"/>
+      <c r="U211" s="288"/>
+      <c r="V211" s="288"/>
+      <c r="W211" s="288"/>
+      <c r="X211" s="288"/>
+      <c r="Y211" s="288"/>
+      <c r="Z211" s="288"/>
+      <c r="AA211" s="288"/>
+      <c r="AB211" s="288"/>
+      <c r="AC211" s="288"/>
+      <c r="AD211" s="288"/>
+      <c r="AE211" s="288"/>
+      <c r="AF211" s="288"/>
+      <c r="AG211" s="288"/>
+      <c r="AH211" s="289"/>
     </row>
     <row r="212" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F212" s="328" t="s">
+      <c r="F212" s="351" t="s">
         <v>34</v>
       </c>
-      <c r="G212" s="330"/>
-      <c r="H212" s="330"/>
-      <c r="I212" s="330"/>
-      <c r="J212" s="329"/>
-      <c r="K212" s="337" t="s">
+      <c r="G212" s="362"/>
+      <c r="H212" s="362"/>
+      <c r="I212" s="362"/>
+      <c r="J212" s="352"/>
+      <c r="K212" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="L212" s="290"/>
-      <c r="M212" s="337" t="s">
+      <c r="L212" s="292"/>
+      <c r="M212" s="340" t="s">
         <v>33</v>
       </c>
-      <c r="N212" s="290"/>
-      <c r="O212" s="317" t="s">
+      <c r="N212" s="292"/>
+      <c r="O212" s="310" t="s">
         <v>496</v>
       </c>
-      <c r="P212" s="323"/>
-      <c r="Q212" s="323"/>
-      <c r="R212" s="323"/>
-      <c r="S212" s="323"/>
-      <c r="T212" s="323"/>
-      <c r="U212" s="323"/>
-      <c r="V212" s="323"/>
-      <c r="W212" s="323"/>
-      <c r="X212" s="323"/>
-      <c r="Y212" s="323"/>
-      <c r="Z212" s="323"/>
-      <c r="AA212" s="323"/>
-      <c r="AB212" s="323"/>
-      <c r="AC212" s="323"/>
-      <c r="AD212" s="323"/>
-      <c r="AE212" s="323"/>
-      <c r="AF212" s="323"/>
-      <c r="AG212" s="323"/>
-      <c r="AH212" s="324"/>
+      <c r="P212" s="357"/>
+      <c r="Q212" s="357"/>
+      <c r="R212" s="357"/>
+      <c r="S212" s="357"/>
+      <c r="T212" s="357"/>
+      <c r="U212" s="357"/>
+      <c r="V212" s="357"/>
+      <c r="W212" s="357"/>
+      <c r="X212" s="357"/>
+      <c r="Y212" s="357"/>
+      <c r="Z212" s="357"/>
+      <c r="AA212" s="357"/>
+      <c r="AB212" s="357"/>
+      <c r="AC212" s="357"/>
+      <c r="AD212" s="357"/>
+      <c r="AE212" s="357"/>
+      <c r="AF212" s="357"/>
+      <c r="AG212" s="357"/>
+      <c r="AH212" s="358"/>
     </row>
     <row r="213" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F213" s="334"/>
-      <c r="G213" s="335"/>
-      <c r="H213" s="335"/>
-      <c r="I213" s="335"/>
-      <c r="J213" s="336"/>
-      <c r="K213" s="291"/>
-      <c r="L213" s="293"/>
-      <c r="M213" s="291"/>
-      <c r="N213" s="293"/>
-      <c r="O213" s="334"/>
-      <c r="P213" s="335"/>
-      <c r="Q213" s="335"/>
-      <c r="R213" s="335"/>
-      <c r="S213" s="335"/>
-      <c r="T213" s="335"/>
-      <c r="U213" s="335"/>
-      <c r="V213" s="335"/>
-      <c r="W213" s="335"/>
-      <c r="X213" s="335"/>
-      <c r="Y213" s="335"/>
-      <c r="Z213" s="335"/>
-      <c r="AA213" s="335"/>
-      <c r="AB213" s="335"/>
-      <c r="AC213" s="335"/>
-      <c r="AD213" s="335"/>
-      <c r="AE213" s="335"/>
-      <c r="AF213" s="335"/>
-      <c r="AG213" s="335"/>
-      <c r="AH213" s="336"/>
+      <c r="F213" s="338"/>
+      <c r="G213" s="368"/>
+      <c r="H213" s="368"/>
+      <c r="I213" s="368"/>
+      <c r="J213" s="369"/>
+      <c r="K213" s="293"/>
+      <c r="L213" s="295"/>
+      <c r="M213" s="293"/>
+      <c r="N213" s="295"/>
+      <c r="O213" s="338"/>
+      <c r="P213" s="368"/>
+      <c r="Q213" s="368"/>
+      <c r="R213" s="368"/>
+      <c r="S213" s="368"/>
+      <c r="T213" s="368"/>
+      <c r="U213" s="368"/>
+      <c r="V213" s="368"/>
+      <c r="W213" s="368"/>
+      <c r="X213" s="368"/>
+      <c r="Y213" s="368"/>
+      <c r="Z213" s="368"/>
+      <c r="AA213" s="368"/>
+      <c r="AB213" s="368"/>
+      <c r="AC213" s="368"/>
+      <c r="AD213" s="368"/>
+      <c r="AE213" s="368"/>
+      <c r="AF213" s="368"/>
+      <c r="AG213" s="368"/>
+      <c r="AH213" s="369"/>
     </row>
     <row r="214" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F214" s="325"/>
-      <c r="G214" s="326"/>
-      <c r="H214" s="326"/>
-      <c r="I214" s="326"/>
-      <c r="J214" s="327"/>
-      <c r="K214" s="294"/>
-      <c r="L214" s="296"/>
-      <c r="M214" s="294"/>
-      <c r="N214" s="296"/>
-      <c r="O214" s="325"/>
-      <c r="P214" s="326"/>
-      <c r="Q214" s="326"/>
-      <c r="R214" s="326"/>
-      <c r="S214" s="326"/>
-      <c r="T214" s="326"/>
-      <c r="U214" s="326"/>
-      <c r="V214" s="326"/>
-      <c r="W214" s="326"/>
-      <c r="X214" s="326"/>
-      <c r="Y214" s="326"/>
-      <c r="Z214" s="326"/>
-      <c r="AA214" s="326"/>
-      <c r="AB214" s="326"/>
-      <c r="AC214" s="326"/>
-      <c r="AD214" s="326"/>
-      <c r="AE214" s="326"/>
-      <c r="AF214" s="326"/>
-      <c r="AG214" s="326"/>
-      <c r="AH214" s="327"/>
+      <c r="F214" s="359"/>
+      <c r="G214" s="360"/>
+      <c r="H214" s="360"/>
+      <c r="I214" s="360"/>
+      <c r="J214" s="361"/>
+      <c r="K214" s="296"/>
+      <c r="L214" s="298"/>
+      <c r="M214" s="296"/>
+      <c r="N214" s="298"/>
+      <c r="O214" s="359"/>
+      <c r="P214" s="360"/>
+      <c r="Q214" s="360"/>
+      <c r="R214" s="360"/>
+      <c r="S214" s="360"/>
+      <c r="T214" s="360"/>
+      <c r="U214" s="360"/>
+      <c r="V214" s="360"/>
+      <c r="W214" s="360"/>
+      <c r="X214" s="360"/>
+      <c r="Y214" s="360"/>
+      <c r="Z214" s="360"/>
+      <c r="AA214" s="360"/>
+      <c r="AB214" s="360"/>
+      <c r="AC214" s="360"/>
+      <c r="AD214" s="360"/>
+      <c r="AE214" s="360"/>
+      <c r="AF214" s="360"/>
+      <c r="AG214" s="360"/>
+      <c r="AH214" s="361"/>
     </row>
     <row r="215" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F215" s="279" t="s">
+      <c r="F215" s="251" t="s">
         <v>265</v>
       </c>
-      <c r="G215" s="280"/>
-      <c r="H215" s="280"/>
-      <c r="I215" s="280"/>
-      <c r="J215" s="281"/>
-      <c r="K215" s="181" t="s">
+      <c r="G215" s="252"/>
+      <c r="H215" s="252"/>
+      <c r="I215" s="252"/>
+      <c r="J215" s="253"/>
+      <c r="K215" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L215" s="183"/>
-      <c r="M215" s="181" t="s">
+      <c r="L215" s="220"/>
+      <c r="M215" s="218" t="s">
         <v>36</v>
       </c>
-      <c r="N215" s="183"/>
-      <c r="O215" s="338" t="s">
+      <c r="N215" s="220"/>
+      <c r="O215" s="370" t="s">
         <v>37</v>
       </c>
-      <c r="P215" s="339"/>
-      <c r="Q215" s="339"/>
-      <c r="R215" s="339"/>
-      <c r="S215" s="339"/>
-      <c r="T215" s="339"/>
-      <c r="U215" s="339"/>
-      <c r="V215" s="339"/>
-      <c r="W215" s="339"/>
-      <c r="X215" s="339"/>
-      <c r="Y215" s="339"/>
-      <c r="Z215" s="339"/>
-      <c r="AA215" s="339"/>
-      <c r="AB215" s="339"/>
-      <c r="AC215" s="339"/>
-      <c r="AD215" s="339"/>
-      <c r="AE215" s="339"/>
-      <c r="AF215" s="339"/>
-      <c r="AG215" s="339"/>
-      <c r="AH215" s="340"/>
+      <c r="P215" s="344"/>
+      <c r="Q215" s="344"/>
+      <c r="R215" s="344"/>
+      <c r="S215" s="344"/>
+      <c r="T215" s="344"/>
+      <c r="U215" s="344"/>
+      <c r="V215" s="344"/>
+      <c r="W215" s="344"/>
+      <c r="X215" s="344"/>
+      <c r="Y215" s="344"/>
+      <c r="Z215" s="344"/>
+      <c r="AA215" s="344"/>
+      <c r="AB215" s="344"/>
+      <c r="AC215" s="344"/>
+      <c r="AD215" s="344"/>
+      <c r="AE215" s="344"/>
+      <c r="AF215" s="344"/>
+      <c r="AG215" s="344"/>
+      <c r="AH215" s="345"/>
     </row>
     <row r="216" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F216" s="279" t="s">
+      <c r="F216" s="251" t="s">
         <v>139</v>
       </c>
-      <c r="G216" s="280"/>
-      <c r="H216" s="280"/>
-      <c r="I216" s="280"/>
-      <c r="J216" s="281"/>
-      <c r="K216" s="181" t="s">
+      <c r="G216" s="252"/>
+      <c r="H216" s="252"/>
+      <c r="I216" s="252"/>
+      <c r="J216" s="253"/>
+      <c r="K216" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L216" s="183"/>
-      <c r="M216" s="181" t="s">
+      <c r="L216" s="220"/>
+      <c r="M216" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N216" s="183"/>
-      <c r="O216" s="347" t="s">
+      <c r="N216" s="220"/>
+      <c r="O216" s="334" t="s">
         <v>497</v>
       </c>
-      <c r="P216" s="339"/>
-      <c r="Q216" s="339"/>
-      <c r="R216" s="339"/>
-      <c r="S216" s="339"/>
-      <c r="T216" s="339"/>
-      <c r="U216" s="339"/>
-      <c r="V216" s="339"/>
-      <c r="W216" s="339"/>
-      <c r="X216" s="339"/>
-      <c r="Y216" s="339"/>
-      <c r="Z216" s="339"/>
-      <c r="AA216" s="339"/>
-      <c r="AB216" s="339"/>
-      <c r="AC216" s="339"/>
-      <c r="AD216" s="339"/>
-      <c r="AE216" s="339"/>
-      <c r="AF216" s="339"/>
-      <c r="AG216" s="339"/>
-      <c r="AH216" s="340"/>
+      <c r="P216" s="344"/>
+      <c r="Q216" s="344"/>
+      <c r="R216" s="344"/>
+      <c r="S216" s="344"/>
+      <c r="T216" s="344"/>
+      <c r="U216" s="344"/>
+      <c r="V216" s="344"/>
+      <c r="W216" s="344"/>
+      <c r="X216" s="344"/>
+      <c r="Y216" s="344"/>
+      <c r="Z216" s="344"/>
+      <c r="AA216" s="344"/>
+      <c r="AB216" s="344"/>
+      <c r="AC216" s="344"/>
+      <c r="AD216" s="344"/>
+      <c r="AE216" s="344"/>
+      <c r="AF216" s="344"/>
+      <c r="AG216" s="344"/>
+      <c r="AH216" s="345"/>
     </row>
     <row r="217" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F217" s="279" t="s">
+      <c r="F217" s="251" t="s">
         <v>42</v>
       </c>
-      <c r="G217" s="280"/>
-      <c r="H217" s="280"/>
-      <c r="I217" s="280"/>
-      <c r="J217" s="281"/>
-      <c r="K217" s="181" t="s">
+      <c r="G217" s="252"/>
+      <c r="H217" s="252"/>
+      <c r="I217" s="252"/>
+      <c r="J217" s="253"/>
+      <c r="K217" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="L217" s="183"/>
-      <c r="M217" s="181" t="s">
+      <c r="L217" s="220"/>
+      <c r="M217" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="N217" s="183"/>
-      <c r="O217" s="347" t="s">
+      <c r="N217" s="220"/>
+      <c r="O217" s="334" t="s">
         <v>492</v>
       </c>
-      <c r="P217" s="339"/>
-      <c r="Q217" s="339"/>
-      <c r="R217" s="339"/>
-      <c r="S217" s="339"/>
-      <c r="T217" s="339"/>
-      <c r="U217" s="339"/>
-      <c r="V217" s="339"/>
-      <c r="W217" s="339"/>
-      <c r="X217" s="339"/>
-      <c r="Y217" s="339"/>
-      <c r="Z217" s="339"/>
-      <c r="AA217" s="339"/>
-      <c r="AB217" s="339"/>
-      <c r="AC217" s="339"/>
-      <c r="AD217" s="339"/>
-      <c r="AE217" s="339"/>
-      <c r="AF217" s="339"/>
-      <c r="AG217" s="339"/>
-      <c r="AH217" s="340"/>
+      <c r="P217" s="344"/>
+      <c r="Q217" s="344"/>
+      <c r="R217" s="344"/>
+      <c r="S217" s="344"/>
+      <c r="T217" s="344"/>
+      <c r="U217" s="344"/>
+      <c r="V217" s="344"/>
+      <c r="W217" s="344"/>
+      <c r="X217" s="344"/>
+      <c r="Y217" s="344"/>
+      <c r="Z217" s="344"/>
+      <c r="AA217" s="344"/>
+      <c r="AB217" s="344"/>
+      <c r="AC217" s="344"/>
+      <c r="AD217" s="344"/>
+      <c r="AE217" s="344"/>
+      <c r="AF217" s="344"/>
+      <c r="AG217" s="344"/>
+      <c r="AH217" s="345"/>
     </row>
     <row r="218" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F218" s="317" t="s">
+      <c r="F218" s="310" t="s">
         <v>270</v>
       </c>
-      <c r="G218" s="323"/>
-      <c r="H218" s="323"/>
-      <c r="I218" s="323"/>
-      <c r="J218" s="324"/>
-      <c r="K218" s="328" t="s">
+      <c r="G218" s="357"/>
+      <c r="H218" s="357"/>
+      <c r="I218" s="357"/>
+      <c r="J218" s="358"/>
+      <c r="K218" s="351" t="s">
         <v>35</v>
       </c>
-      <c r="L218" s="329"/>
-      <c r="M218" s="328" t="s">
+      <c r="L218" s="352"/>
+      <c r="M218" s="351" t="s">
         <v>36</v>
       </c>
-      <c r="N218" s="329"/>
-      <c r="O218" s="328" t="s">
+      <c r="N218" s="352"/>
+      <c r="O218" s="351" t="s">
         <v>43</v>
       </c>
-      <c r="P218" s="330"/>
-      <c r="Q218" s="330"/>
-      <c r="R218" s="330"/>
-      <c r="S218" s="330"/>
-      <c r="T218" s="330"/>
-      <c r="U218" s="330"/>
-      <c r="V218" s="330"/>
-      <c r="W218" s="330"/>
-      <c r="X218" s="330"/>
-      <c r="Y218" s="330"/>
-      <c r="Z218" s="330"/>
-      <c r="AA218" s="330"/>
-      <c r="AB218" s="330"/>
-      <c r="AC218" s="330"/>
-      <c r="AD218" s="330"/>
-      <c r="AE218" s="330"/>
-      <c r="AF218" s="330"/>
-      <c r="AG218" s="330"/>
-      <c r="AH218" s="329"/>
+      <c r="P218" s="362"/>
+      <c r="Q218" s="362"/>
+      <c r="R218" s="362"/>
+      <c r="S218" s="362"/>
+      <c r="T218" s="362"/>
+      <c r="U218" s="362"/>
+      <c r="V218" s="362"/>
+      <c r="W218" s="362"/>
+      <c r="X218" s="362"/>
+      <c r="Y218" s="362"/>
+      <c r="Z218" s="362"/>
+      <c r="AA218" s="362"/>
+      <c r="AB218" s="362"/>
+      <c r="AC218" s="362"/>
+      <c r="AD218" s="362"/>
+      <c r="AE218" s="362"/>
+      <c r="AF218" s="362"/>
+      <c r="AG218" s="362"/>
+      <c r="AH218" s="352"/>
     </row>
     <row r="219" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F219" s="325"/>
-      <c r="G219" s="326"/>
-      <c r="H219" s="326"/>
-      <c r="I219" s="326"/>
-      <c r="J219" s="327"/>
-      <c r="K219" s="325"/>
-      <c r="L219" s="327"/>
-      <c r="M219" s="325"/>
-      <c r="N219" s="327"/>
-      <c r="O219" s="325"/>
-      <c r="P219" s="326"/>
-      <c r="Q219" s="326"/>
-      <c r="R219" s="326"/>
-      <c r="S219" s="326"/>
-      <c r="T219" s="326"/>
-      <c r="U219" s="326"/>
-      <c r="V219" s="326"/>
-      <c r="W219" s="326"/>
-      <c r="X219" s="326"/>
-      <c r="Y219" s="326"/>
-      <c r="Z219" s="326"/>
-      <c r="AA219" s="326"/>
-      <c r="AB219" s="326"/>
-      <c r="AC219" s="326"/>
-      <c r="AD219" s="326"/>
-      <c r="AE219" s="326"/>
-      <c r="AF219" s="326"/>
-      <c r="AG219" s="326"/>
-      <c r="AH219" s="327"/>
+      <c r="F219" s="359"/>
+      <c r="G219" s="360"/>
+      <c r="H219" s="360"/>
+      <c r="I219" s="360"/>
+      <c r="J219" s="361"/>
+      <c r="K219" s="359"/>
+      <c r="L219" s="361"/>
+      <c r="M219" s="359"/>
+      <c r="N219" s="361"/>
+      <c r="O219" s="359"/>
+      <c r="P219" s="360"/>
+      <c r="Q219" s="360"/>
+      <c r="R219" s="360"/>
+      <c r="S219" s="360"/>
+      <c r="T219" s="360"/>
+      <c r="U219" s="360"/>
+      <c r="V219" s="360"/>
+      <c r="W219" s="360"/>
+      <c r="X219" s="360"/>
+      <c r="Y219" s="360"/>
+      <c r="Z219" s="360"/>
+      <c r="AA219" s="360"/>
+      <c r="AB219" s="360"/>
+      <c r="AC219" s="360"/>
+      <c r="AD219" s="360"/>
+      <c r="AE219" s="360"/>
+      <c r="AF219" s="360"/>
+      <c r="AG219" s="360"/>
+      <c r="AH219" s="361"/>
     </row>
     <row r="220" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F220" s="55"/>
@@ -45084,6 +45084,118 @@
     </row>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="F218:J219"/>
+    <mergeCell ref="K218:L219"/>
+    <mergeCell ref="M218:N219"/>
+    <mergeCell ref="F216:J216"/>
+    <mergeCell ref="O218:AH219"/>
+    <mergeCell ref="F201:J201"/>
+    <mergeCell ref="O192:AH193"/>
+    <mergeCell ref="K215:L215"/>
+    <mergeCell ref="M215:N215"/>
+    <mergeCell ref="O201:AH201"/>
+    <mergeCell ref="O194:AH194"/>
+    <mergeCell ref="O202:AH203"/>
+    <mergeCell ref="O204:AH205"/>
+    <mergeCell ref="O206:AH207"/>
+    <mergeCell ref="O208:AH209"/>
+    <mergeCell ref="O212:AH214"/>
+    <mergeCell ref="M208:N209"/>
+    <mergeCell ref="M217:N217"/>
+    <mergeCell ref="O215:AH215"/>
+    <mergeCell ref="F210:J210"/>
+    <mergeCell ref="F211:J211"/>
+    <mergeCell ref="F215:J215"/>
+    <mergeCell ref="F208:J209"/>
+    <mergeCell ref="F212:J214"/>
+    <mergeCell ref="F174:J174"/>
+    <mergeCell ref="F175:J175"/>
+    <mergeCell ref="F176:J179"/>
+    <mergeCell ref="F180:J180"/>
+    <mergeCell ref="F181:J184"/>
+    <mergeCell ref="K195:L196"/>
+    <mergeCell ref="K191:L191"/>
+    <mergeCell ref="F191:J191"/>
+    <mergeCell ref="F194:J194"/>
+    <mergeCell ref="F189:J190"/>
+    <mergeCell ref="F192:J193"/>
+    <mergeCell ref="F195:J196"/>
+    <mergeCell ref="K175:L175"/>
+    <mergeCell ref="O210:AH210"/>
+    <mergeCell ref="O211:AH211"/>
+    <mergeCell ref="K181:L184"/>
+    <mergeCell ref="K176:L179"/>
+    <mergeCell ref="F185:J186"/>
+    <mergeCell ref="F187:J188"/>
+    <mergeCell ref="K187:L188"/>
+    <mergeCell ref="K189:L190"/>
+    <mergeCell ref="M201:N201"/>
+    <mergeCell ref="F202:J203"/>
+    <mergeCell ref="F204:J205"/>
+    <mergeCell ref="F206:J207"/>
+    <mergeCell ref="O181:AH184"/>
+    <mergeCell ref="O195:AH196"/>
+    <mergeCell ref="K194:L194"/>
+    <mergeCell ref="K201:L201"/>
+    <mergeCell ref="M192:N193"/>
+    <mergeCell ref="M194:N194"/>
+    <mergeCell ref="M195:N196"/>
+    <mergeCell ref="K185:L186"/>
+    <mergeCell ref="K180:L180"/>
+    <mergeCell ref="K192:L193"/>
+    <mergeCell ref="K217:L217"/>
+    <mergeCell ref="K204:L205"/>
+    <mergeCell ref="K206:L207"/>
+    <mergeCell ref="K211:L211"/>
+    <mergeCell ref="K210:L210"/>
+    <mergeCell ref="K202:L203"/>
+    <mergeCell ref="K212:L214"/>
+    <mergeCell ref="K216:L216"/>
+    <mergeCell ref="M216:N216"/>
+    <mergeCell ref="K208:L209"/>
+    <mergeCell ref="M206:N207"/>
+    <mergeCell ref="M211:N211"/>
+    <mergeCell ref="M210:N210"/>
+    <mergeCell ref="M202:N203"/>
+    <mergeCell ref="M212:N214"/>
+    <mergeCell ref="M204:N205"/>
+    <mergeCell ref="O216:AH216"/>
+    <mergeCell ref="O217:AH217"/>
+    <mergeCell ref="M174:N174"/>
+    <mergeCell ref="K161:Z161"/>
+    <mergeCell ref="F217:J217"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AA155:AH155"/>
+    <mergeCell ref="K151:Z151"/>
+    <mergeCell ref="K152:Z152"/>
+    <mergeCell ref="K153:Z153"/>
+    <mergeCell ref="K155:Z155"/>
+    <mergeCell ref="K156:Z160"/>
+    <mergeCell ref="AA156:AH160"/>
+    <mergeCell ref="AA162:AH163"/>
+    <mergeCell ref="AA161:AH161"/>
+    <mergeCell ref="AA152:AH152"/>
+    <mergeCell ref="AA154:AH154"/>
+    <mergeCell ref="M175:N175"/>
+    <mergeCell ref="M176:N179"/>
+    <mergeCell ref="M180:N180"/>
+    <mergeCell ref="M181:N184"/>
+    <mergeCell ref="M185:N186"/>
+    <mergeCell ref="M187:N188"/>
+    <mergeCell ref="M189:N190"/>
+    <mergeCell ref="M191:N191"/>
+    <mergeCell ref="O185:AH186"/>
+    <mergeCell ref="O187:AH188"/>
+    <mergeCell ref="O189:AH190"/>
+    <mergeCell ref="O191:AH191"/>
+    <mergeCell ref="O175:AH175"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
@@ -45108,118 +45220,6 @@
     <mergeCell ref="K162:Z163"/>
     <mergeCell ref="O1:R3"/>
     <mergeCell ref="S1:Z3"/>
-    <mergeCell ref="M175:N175"/>
-    <mergeCell ref="M176:N179"/>
-    <mergeCell ref="M180:N180"/>
-    <mergeCell ref="M181:N184"/>
-    <mergeCell ref="M185:N186"/>
-    <mergeCell ref="M187:N188"/>
-    <mergeCell ref="M189:N190"/>
-    <mergeCell ref="M191:N191"/>
-    <mergeCell ref="O185:AH186"/>
-    <mergeCell ref="O187:AH188"/>
-    <mergeCell ref="O189:AH190"/>
-    <mergeCell ref="O191:AH191"/>
-    <mergeCell ref="O175:AH175"/>
-    <mergeCell ref="O216:AH216"/>
-    <mergeCell ref="O217:AH217"/>
-    <mergeCell ref="M174:N174"/>
-    <mergeCell ref="K161:Z161"/>
-    <mergeCell ref="F217:J217"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AA155:AH155"/>
-    <mergeCell ref="K151:Z151"/>
-    <mergeCell ref="K152:Z152"/>
-    <mergeCell ref="K153:Z153"/>
-    <mergeCell ref="K155:Z155"/>
-    <mergeCell ref="K156:Z160"/>
-    <mergeCell ref="AA156:AH160"/>
-    <mergeCell ref="AA162:AH163"/>
-    <mergeCell ref="AA161:AH161"/>
-    <mergeCell ref="AA152:AH152"/>
-    <mergeCell ref="AA154:AH154"/>
-    <mergeCell ref="K217:L217"/>
-    <mergeCell ref="K204:L205"/>
-    <mergeCell ref="K206:L207"/>
-    <mergeCell ref="K211:L211"/>
-    <mergeCell ref="K210:L210"/>
-    <mergeCell ref="K202:L203"/>
-    <mergeCell ref="K212:L214"/>
-    <mergeCell ref="K216:L216"/>
-    <mergeCell ref="M216:N216"/>
-    <mergeCell ref="K208:L209"/>
-    <mergeCell ref="M206:N207"/>
-    <mergeCell ref="M211:N211"/>
-    <mergeCell ref="M210:N210"/>
-    <mergeCell ref="M202:N203"/>
-    <mergeCell ref="M212:N214"/>
-    <mergeCell ref="M204:N205"/>
-    <mergeCell ref="O210:AH210"/>
-    <mergeCell ref="O211:AH211"/>
-    <mergeCell ref="K181:L184"/>
-    <mergeCell ref="K176:L179"/>
-    <mergeCell ref="F185:J186"/>
-    <mergeCell ref="F187:J188"/>
-    <mergeCell ref="K187:L188"/>
-    <mergeCell ref="K189:L190"/>
-    <mergeCell ref="M201:N201"/>
-    <mergeCell ref="F202:J203"/>
-    <mergeCell ref="F204:J205"/>
-    <mergeCell ref="F206:J207"/>
-    <mergeCell ref="O181:AH184"/>
-    <mergeCell ref="O195:AH196"/>
-    <mergeCell ref="K194:L194"/>
-    <mergeCell ref="K201:L201"/>
-    <mergeCell ref="M192:N193"/>
-    <mergeCell ref="M194:N194"/>
-    <mergeCell ref="M195:N196"/>
-    <mergeCell ref="K185:L186"/>
-    <mergeCell ref="K180:L180"/>
-    <mergeCell ref="K192:L193"/>
-    <mergeCell ref="F174:J174"/>
-    <mergeCell ref="F175:J175"/>
-    <mergeCell ref="F176:J179"/>
-    <mergeCell ref="F180:J180"/>
-    <mergeCell ref="F181:J184"/>
-    <mergeCell ref="K195:L196"/>
-    <mergeCell ref="K191:L191"/>
-    <mergeCell ref="F191:J191"/>
-    <mergeCell ref="F194:J194"/>
-    <mergeCell ref="F189:J190"/>
-    <mergeCell ref="F192:J193"/>
-    <mergeCell ref="F195:J196"/>
-    <mergeCell ref="K175:L175"/>
-    <mergeCell ref="F218:J219"/>
-    <mergeCell ref="K218:L219"/>
-    <mergeCell ref="M218:N219"/>
-    <mergeCell ref="F216:J216"/>
-    <mergeCell ref="O218:AH219"/>
-    <mergeCell ref="F201:J201"/>
-    <mergeCell ref="O192:AH193"/>
-    <mergeCell ref="K215:L215"/>
-    <mergeCell ref="M215:N215"/>
-    <mergeCell ref="O201:AH201"/>
-    <mergeCell ref="O194:AH194"/>
-    <mergeCell ref="O202:AH203"/>
-    <mergeCell ref="O204:AH205"/>
-    <mergeCell ref="O206:AH207"/>
-    <mergeCell ref="O208:AH209"/>
-    <mergeCell ref="O212:AH214"/>
-    <mergeCell ref="M208:N209"/>
-    <mergeCell ref="M217:N217"/>
-    <mergeCell ref="O215:AH215"/>
-    <mergeCell ref="F210:J210"/>
-    <mergeCell ref="F211:J211"/>
-    <mergeCell ref="F215:J215"/>
-    <mergeCell ref="F208:J209"/>
-    <mergeCell ref="F212:J214"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>

--- a/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
+++ b/020_アプリケーション開発標準/010_設計標準/UI標準(画面).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCF8226-A4BA-41F5-B9CE-B65B691143E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D7D9BC-0AB2-4918-9A09-4C8C983311E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="28" r:id="rId1"/>
@@ -7671,9 +7671,6 @@
   </si>
   <si>
     <t>詳細画面から戻る際に、前回の検索条件を復元して再検索を行う。</t>
-  </si>
-  <si>
-    <t>詳細画面から戻る際に、前回の検索条件を復元して再検索を行う。</t>
     <phoneticPr fontId="11"/>
   </si>
   <si>
@@ -7746,6 +7743,25 @@
   </si>
   <si>
     <t>前画面に戻る要件がある場合は、ブラウザの戻るボタンではなく画面の機能として戻るボタンを作成することで対応する。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>初期表示の検索結果が0件の場合、共通エラー画面を表示する。</t>
+    <rPh sb="0" eb="2">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -8319,7 +8335,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="380">
+  <cellXfs count="381">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8823,8 +8839,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="31" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -8940,86 +9040,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -9030,15 +9058,6 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9047,33 +9066,6 @@
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9147,14 +9139,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9204,6 +9214,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -9216,6 +9235,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -9223,6 +9248,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -9243,38 +9280,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9282,50 +9343,41 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -9342,77 +9394,44 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -27070,12 +27089,12 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="183">
+      <c r="I25" s="184">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
         <v>45565</v>
       </c>
-      <c r="J25" s="183"/>
-      <c r="K25" s="183"/>
+      <c r="J25" s="184"/>
+      <c r="K25" s="184"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F26" s="3"/>
@@ -27668,55 +27687,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="227" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="200" t="s">
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="228" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="209" t="s">
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="230"/>
+      <c r="S1" s="237" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="210"/>
-      <c r="Y1" s="210"/>
-      <c r="Z1" s="211"/>
-      <c r="AA1" s="190" t="s">
+      <c r="T1" s="238"/>
+      <c r="U1" s="238"/>
+      <c r="V1" s="238"/>
+      <c r="W1" s="238"/>
+      <c r="X1" s="238"/>
+      <c r="Y1" s="238"/>
+      <c r="Z1" s="239"/>
+      <c r="AA1" s="218" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="192"/>
-      <c r="AC1" s="218" t="str">
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="246" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="219"/>
-      <c r="AE1" s="219"/>
-      <c r="AF1" s="220"/>
-      <c r="AG1" s="184">
+      <c r="AD1" s="247"/>
+      <c r="AE1" s="247"/>
+      <c r="AF1" s="248"/>
+      <c r="AG1" s="212">
         <f>IF(D8="","",D8)</f>
         <v>45565</v>
       </c>
-      <c r="AH1" s="185"/>
-      <c r="AI1" s="186"/>
+      <c r="AH1" s="213"/>
+      <c r="AI1" s="214"/>
       <c r="AJ1" s="7"/>
       <c r="AK1" s="7"/>
       <c r="AL1" s="7"/>
@@ -27724,51 +27743,51 @@
       <c r="AN1" s="8"/>
     </row>
     <row r="2" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="218" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="193"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="203"/>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="205"/>
-      <c r="S2" s="212"/>
-      <c r="T2" s="213"/>
-      <c r="U2" s="213"/>
-      <c r="V2" s="213"/>
-      <c r="W2" s="213"/>
-      <c r="X2" s="213"/>
-      <c r="Y2" s="213"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="190" t="s">
+      <c r="B2" s="219"/>
+      <c r="C2" s="219"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="221"/>
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="241"/>
+      <c r="U2" s="241"/>
+      <c r="V2" s="241"/>
+      <c r="W2" s="241"/>
+      <c r="X2" s="241"/>
+      <c r="Y2" s="241"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="218" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="192"/>
-      <c r="AC2" s="196" t="str">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="224" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="197"/>
-      <c r="AE2" s="197"/>
-      <c r="AF2" s="198"/>
-      <c r="AG2" s="184" t="str">
+      <c r="AD2" s="225"/>
+      <c r="AE2" s="225"/>
+      <c r="AF2" s="226"/>
+      <c r="AG2" s="212" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="185"/>
-      <c r="AI2" s="186"/>
+      <c r="AH2" s="213"/>
+      <c r="AI2" s="214"/>
       <c r="AJ2" s="7"/>
       <c r="AK2" s="7"/>
       <c r="AL2" s="7"/>
@@ -27776,43 +27795,43 @@
       <c r="AN2" s="7"/>
     </row>
     <row r="3" spans="1:40" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="190" t="s">
+      <c r="A3" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="191"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="221"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="215"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="217"/>
-      <c r="AA3" s="190"/>
-      <c r="AB3" s="192"/>
-      <c r="AC3" s="218"/>
-      <c r="AD3" s="219"/>
-      <c r="AE3" s="219"/>
-      <c r="AF3" s="220"/>
-      <c r="AG3" s="184"/>
-      <c r="AH3" s="185"/>
-      <c r="AI3" s="186"/>
+      <c r="B3" s="219"/>
+      <c r="C3" s="219"/>
+      <c r="D3" s="220"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="234"/>
+      <c r="P3" s="235"/>
+      <c r="Q3" s="235"/>
+      <c r="R3" s="236"/>
+      <c r="S3" s="243"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="245"/>
+      <c r="AA3" s="218"/>
+      <c r="AB3" s="220"/>
+      <c r="AC3" s="246"/>
+      <c r="AD3" s="247"/>
+      <c r="AE3" s="247"/>
+      <c r="AF3" s="248"/>
+      <c r="AG3" s="212"/>
+      <c r="AH3" s="213"/>
+      <c r="AI3" s="214"/>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
       <c r="AL3" s="7"/>
@@ -27849,1190 +27868,1034 @@
       <c r="A7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="187" t="s">
+      <c r="B7" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="188"/>
-      <c r="D7" s="187" t="s">
+      <c r="C7" s="216"/>
+      <c r="D7" s="215" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="189"/>
-      <c r="F7" s="188"/>
-      <c r="G7" s="187" t="s">
+      <c r="E7" s="217"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="189"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="187" t="s">
+      <c r="H7" s="217"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="215" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="189"/>
-      <c r="L7" s="189"/>
-      <c r="M7" s="189"/>
-      <c r="N7" s="189"/>
-      <c r="O7" s="189"/>
-      <c r="P7" s="188"/>
-      <c r="Q7" s="187" t="s">
+      <c r="K7" s="217"/>
+      <c r="L7" s="217"/>
+      <c r="M7" s="217"/>
+      <c r="N7" s="217"/>
+      <c r="O7" s="217"/>
+      <c r="P7" s="216"/>
+      <c r="Q7" s="215" t="s">
         <v>5</v>
       </c>
-      <c r="R7" s="189"/>
-      <c r="S7" s="189"/>
-      <c r="T7" s="189"/>
-      <c r="U7" s="189"/>
-      <c r="V7" s="189"/>
-      <c r="W7" s="189"/>
-      <c r="X7" s="189"/>
-      <c r="Y7" s="189"/>
-      <c r="Z7" s="189"/>
-      <c r="AA7" s="189"/>
-      <c r="AB7" s="189"/>
-      <c r="AC7" s="189"/>
-      <c r="AD7" s="189"/>
-      <c r="AE7" s="188"/>
-      <c r="AF7" s="187" t="s">
+      <c r="R7" s="217"/>
+      <c r="S7" s="217"/>
+      <c r="T7" s="217"/>
+      <c r="U7" s="217"/>
+      <c r="V7" s="217"/>
+      <c r="W7" s="217"/>
+      <c r="X7" s="217"/>
+      <c r="Y7" s="217"/>
+      <c r="Z7" s="217"/>
+      <c r="AA7" s="217"/>
+      <c r="AB7" s="217"/>
+      <c r="AC7" s="217"/>
+      <c r="AD7" s="217"/>
+      <c r="AE7" s="216"/>
+      <c r="AF7" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="189"/>
-      <c r="AH7" s="189"/>
-      <c r="AI7" s="188"/>
+      <c r="AG7" s="217"/>
+      <c r="AH7" s="217"/>
+      <c r="AI7" s="216"/>
     </row>
     <row r="8" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="90">
         <v>1</v>
       </c>
-      <c r="B8" s="234" t="s">
+      <c r="B8" s="198" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="235"/>
-      <c r="D8" s="236">
+      <c r="C8" s="199"/>
+      <c r="D8" s="200">
         <v>45565</v>
       </c>
-      <c r="E8" s="237"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="239" t="s">
+      <c r="E8" s="201"/>
+      <c r="F8" s="202"/>
+      <c r="G8" s="203" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="240"/>
-      <c r="I8" s="241"/>
-      <c r="J8" s="242" t="s">
+      <c r="H8" s="204"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="206" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="243"/>
-      <c r="L8" s="243"/>
-      <c r="M8" s="243"/>
-      <c r="N8" s="243"/>
-      <c r="O8" s="243"/>
-      <c r="P8" s="244"/>
-      <c r="Q8" s="245" t="s">
+      <c r="K8" s="207"/>
+      <c r="L8" s="207"/>
+      <c r="M8" s="207"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
+      <c r="P8" s="208"/>
+      <c r="Q8" s="209" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="246"/>
-      <c r="S8" s="246"/>
-      <c r="T8" s="246"/>
-      <c r="U8" s="246"/>
-      <c r="V8" s="246"/>
-      <c r="W8" s="246"/>
-      <c r="X8" s="246"/>
-      <c r="Y8" s="246"/>
-      <c r="Z8" s="246"/>
-      <c r="AA8" s="246"/>
-      <c r="AB8" s="246"/>
-      <c r="AC8" s="246"/>
-      <c r="AD8" s="246"/>
-      <c r="AE8" s="247"/>
-      <c r="AF8" s="242" t="s">
+      <c r="R8" s="210"/>
+      <c r="S8" s="210"/>
+      <c r="T8" s="210"/>
+      <c r="U8" s="210"/>
+      <c r="V8" s="210"/>
+      <c r="W8" s="210"/>
+      <c r="X8" s="210"/>
+      <c r="Y8" s="210"/>
+      <c r="Z8" s="210"/>
+      <c r="AA8" s="210"/>
+      <c r="AB8" s="210"/>
+      <c r="AC8" s="210"/>
+      <c r="AD8" s="210"/>
+      <c r="AE8" s="211"/>
+      <c r="AF8" s="206" t="s">
         <v>23</v>
       </c>
-      <c r="AG8" s="243"/>
-      <c r="AH8" s="243"/>
-      <c r="AI8" s="244"/>
+      <c r="AG8" s="207"/>
+      <c r="AH8" s="207"/>
+      <c r="AI8" s="208"/>
     </row>
     <row r="9" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="89"/>
-      <c r="B9" s="222"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="224"/>
-      <c r="E9" s="225"/>
-      <c r="F9" s="226"/>
-      <c r="G9" s="224"/>
-      <c r="H9" s="227"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="228"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="229"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="229"/>
-      <c r="O9" s="229"/>
-      <c r="P9" s="230"/>
-      <c r="Q9" s="231"/>
-      <c r="R9" s="232"/>
-      <c r="S9" s="232"/>
-      <c r="T9" s="232"/>
-      <c r="U9" s="232"/>
-      <c r="V9" s="232"/>
-      <c r="W9" s="232"/>
-      <c r="X9" s="232"/>
-      <c r="Y9" s="232"/>
-      <c r="Z9" s="232"/>
-      <c r="AA9" s="232"/>
-      <c r="AB9" s="232"/>
-      <c r="AC9" s="232"/>
-      <c r="AD9" s="232"/>
-      <c r="AE9" s="233"/>
-      <c r="AF9" s="228"/>
-      <c r="AG9" s="229"/>
-      <c r="AH9" s="229"/>
-      <c r="AI9" s="230"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="186"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="188"/>
+      <c r="F9" s="189"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="190"/>
+      <c r="I9" s="186"/>
+      <c r="J9" s="191"/>
+      <c r="K9" s="192"/>
+      <c r="L9" s="192"/>
+      <c r="M9" s="192"/>
+      <c r="N9" s="192"/>
+      <c r="O9" s="192"/>
+      <c r="P9" s="193"/>
+      <c r="Q9" s="194"/>
+      <c r="R9" s="195"/>
+      <c r="S9" s="195"/>
+      <c r="T9" s="195"/>
+      <c r="U9" s="195"/>
+      <c r="V9" s="195"/>
+      <c r="W9" s="195"/>
+      <c r="X9" s="195"/>
+      <c r="Y9" s="195"/>
+      <c r="Z9" s="195"/>
+      <c r="AA9" s="195"/>
+      <c r="AB9" s="195"/>
+      <c r="AC9" s="195"/>
+      <c r="AD9" s="195"/>
+      <c r="AE9" s="196"/>
+      <c r="AF9" s="191"/>
+      <c r="AG9" s="192"/>
+      <c r="AH9" s="192"/>
+      <c r="AI9" s="193"/>
     </row>
     <row r="10" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="89"/>
-      <c r="B10" s="222"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="224"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="222"/>
-      <c r="H10" s="227"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="228"/>
-      <c r="K10" s="229"/>
-      <c r="L10" s="229"/>
-      <c r="M10" s="229"/>
-      <c r="N10" s="229"/>
-      <c r="O10" s="229"/>
-      <c r="P10" s="230"/>
-      <c r="Q10" s="231"/>
-      <c r="R10" s="232"/>
-      <c r="S10" s="232"/>
-      <c r="T10" s="232"/>
-      <c r="U10" s="232"/>
-      <c r="V10" s="232"/>
-      <c r="W10" s="232"/>
-      <c r="X10" s="232"/>
-      <c r="Y10" s="232"/>
-      <c r="Z10" s="232"/>
-      <c r="AA10" s="232"/>
-      <c r="AB10" s="232"/>
-      <c r="AC10" s="232"/>
-      <c r="AD10" s="232"/>
-      <c r="AE10" s="233"/>
-      <c r="AF10" s="228"/>
-      <c r="AG10" s="229"/>
-      <c r="AH10" s="229"/>
-      <c r="AI10" s="230"/>
+      <c r="B10" s="185"/>
+      <c r="C10" s="186"/>
+      <c r="D10" s="187"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="185"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="186"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
+      <c r="L10" s="192"/>
+      <c r="M10" s="192"/>
+      <c r="N10" s="192"/>
+      <c r="O10" s="192"/>
+      <c r="P10" s="193"/>
+      <c r="Q10" s="194"/>
+      <c r="R10" s="195"/>
+      <c r="S10" s="195"/>
+      <c r="T10" s="195"/>
+      <c r="U10" s="195"/>
+      <c r="V10" s="195"/>
+      <c r="W10" s="195"/>
+      <c r="X10" s="195"/>
+      <c r="Y10" s="195"/>
+      <c r="Z10" s="195"/>
+      <c r="AA10" s="195"/>
+      <c r="AB10" s="195"/>
+      <c r="AC10" s="195"/>
+      <c r="AD10" s="195"/>
+      <c r="AE10" s="196"/>
+      <c r="AF10" s="191"/>
+      <c r="AG10" s="192"/>
+      <c r="AH10" s="192"/>
+      <c r="AI10" s="193"/>
     </row>
     <row r="11" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="89"/>
-      <c r="B11" s="222"/>
-      <c r="C11" s="223"/>
-      <c r="D11" s="224"/>
-      <c r="E11" s="225"/>
-      <c r="F11" s="226"/>
-      <c r="G11" s="222"/>
-      <c r="H11" s="227"/>
-      <c r="I11" s="223"/>
-      <c r="J11" s="228"/>
-      <c r="K11" s="229"/>
-      <c r="L11" s="229"/>
-      <c r="M11" s="229"/>
-      <c r="N11" s="229"/>
-      <c r="O11" s="229"/>
-      <c r="P11" s="230"/>
-      <c r="Q11" s="231"/>
-      <c r="R11" s="232"/>
-      <c r="S11" s="232"/>
-      <c r="T11" s="232"/>
-      <c r="U11" s="232"/>
-      <c r="V11" s="232"/>
-      <c r="W11" s="232"/>
-      <c r="X11" s="232"/>
-      <c r="Y11" s="232"/>
-      <c r="Z11" s="232"/>
-      <c r="AA11" s="232"/>
-      <c r="AB11" s="232"/>
-      <c r="AC11" s="232"/>
-      <c r="AD11" s="232"/>
-      <c r="AE11" s="233"/>
-      <c r="AF11" s="228"/>
-      <c r="AG11" s="229"/>
-      <c r="AH11" s="229"/>
-      <c r="AI11" s="230"/>
+      <c r="B11" s="185"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="188"/>
+      <c r="F11" s="189"/>
+      <c r="G11" s="185"/>
+      <c r="H11" s="190"/>
+      <c r="I11" s="186"/>
+      <c r="J11" s="191"/>
+      <c r="K11" s="192"/>
+      <c r="L11" s="192"/>
+      <c r="M11" s="192"/>
+      <c r="N11" s="192"/>
+      <c r="O11" s="192"/>
+      <c r="P11" s="193"/>
+      <c r="Q11" s="194"/>
+      <c r="R11" s="195"/>
+      <c r="S11" s="195"/>
+      <c r="T11" s="195"/>
+      <c r="U11" s="195"/>
+      <c r="V11" s="195"/>
+      <c r="W11" s="195"/>
+      <c r="X11" s="195"/>
+      <c r="Y11" s="195"/>
+      <c r="Z11" s="195"/>
+      <c r="AA11" s="195"/>
+      <c r="AB11" s="195"/>
+      <c r="AC11" s="195"/>
+      <c r="AD11" s="195"/>
+      <c r="AE11" s="196"/>
+      <c r="AF11" s="191"/>
+      <c r="AG11" s="192"/>
+      <c r="AH11" s="192"/>
+      <c r="AI11" s="193"/>
     </row>
     <row r="12" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="89"/>
-      <c r="B12" s="222"/>
-      <c r="C12" s="223"/>
-      <c r="D12" s="224"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="226"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="227"/>
-      <c r="I12" s="223"/>
-      <c r="J12" s="228"/>
-      <c r="K12" s="229"/>
-      <c r="L12" s="229"/>
-      <c r="M12" s="229"/>
-      <c r="N12" s="229"/>
-      <c r="O12" s="229"/>
-      <c r="P12" s="230"/>
-      <c r="Q12" s="231"/>
-      <c r="R12" s="232"/>
-      <c r="S12" s="232"/>
-      <c r="T12" s="232"/>
-      <c r="U12" s="232"/>
-      <c r="V12" s="232"/>
-      <c r="W12" s="232"/>
-      <c r="X12" s="232"/>
-      <c r="Y12" s="232"/>
-      <c r="Z12" s="232"/>
-      <c r="AA12" s="232"/>
-      <c r="AB12" s="232"/>
-      <c r="AC12" s="232"/>
-      <c r="AD12" s="232"/>
-      <c r="AE12" s="233"/>
-      <c r="AF12" s="228"/>
-      <c r="AG12" s="229"/>
-      <c r="AH12" s="229"/>
-      <c r="AI12" s="230"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="186"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="188"/>
+      <c r="F12" s="189"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="190"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="191"/>
+      <c r="K12" s="192"/>
+      <c r="L12" s="192"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="192"/>
+      <c r="O12" s="192"/>
+      <c r="P12" s="193"/>
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195"/>
+      <c r="S12" s="195"/>
+      <c r="T12" s="195"/>
+      <c r="U12" s="195"/>
+      <c r="V12" s="195"/>
+      <c r="W12" s="195"/>
+      <c r="X12" s="195"/>
+      <c r="Y12" s="195"/>
+      <c r="Z12" s="195"/>
+      <c r="AA12" s="195"/>
+      <c r="AB12" s="195"/>
+      <c r="AC12" s="195"/>
+      <c r="AD12" s="195"/>
+      <c r="AE12" s="196"/>
+      <c r="AF12" s="191"/>
+      <c r="AG12" s="192"/>
+      <c r="AH12" s="192"/>
+      <c r="AI12" s="193"/>
     </row>
     <row r="13" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="89"/>
-      <c r="B13" s="222"/>
-      <c r="C13" s="223"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="226"/>
-      <c r="G13" s="222"/>
-      <c r="H13" s="227"/>
-      <c r="I13" s="223"/>
-      <c r="J13" s="228"/>
-      <c r="K13" s="229"/>
-      <c r="L13" s="229"/>
-      <c r="M13" s="229"/>
-      <c r="N13" s="229"/>
-      <c r="O13" s="229"/>
-      <c r="P13" s="230"/>
-      <c r="Q13" s="231"/>
-      <c r="R13" s="232"/>
-      <c r="S13" s="232"/>
-      <c r="T13" s="232"/>
-      <c r="U13" s="232"/>
-      <c r="V13" s="232"/>
-      <c r="W13" s="232"/>
-      <c r="X13" s="232"/>
-      <c r="Y13" s="232"/>
-      <c r="Z13" s="232"/>
-      <c r="AA13" s="232"/>
-      <c r="AB13" s="232"/>
-      <c r="AC13" s="232"/>
-      <c r="AD13" s="232"/>
-      <c r="AE13" s="233"/>
-      <c r="AF13" s="228"/>
-      <c r="AG13" s="229"/>
-      <c r="AH13" s="229"/>
-      <c r="AI13" s="230"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="189"/>
+      <c r="G13" s="185"/>
+      <c r="H13" s="190"/>
+      <c r="I13" s="186"/>
+      <c r="J13" s="191"/>
+      <c r="K13" s="192"/>
+      <c r="L13" s="192"/>
+      <c r="M13" s="192"/>
+      <c r="N13" s="192"/>
+      <c r="O13" s="192"/>
+      <c r="P13" s="193"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
+      <c r="S13" s="195"/>
+      <c r="T13" s="195"/>
+      <c r="U13" s="195"/>
+      <c r="V13" s="195"/>
+      <c r="W13" s="195"/>
+      <c r="X13" s="195"/>
+      <c r="Y13" s="195"/>
+      <c r="Z13" s="195"/>
+      <c r="AA13" s="195"/>
+      <c r="AB13" s="195"/>
+      <c r="AC13" s="195"/>
+      <c r="AD13" s="195"/>
+      <c r="AE13" s="196"/>
+      <c r="AF13" s="191"/>
+      <c r="AG13" s="192"/>
+      <c r="AH13" s="192"/>
+      <c r="AI13" s="193"/>
     </row>
     <row r="14" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="89"/>
-      <c r="B14" s="222"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="224"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="226"/>
-      <c r="G14" s="222"/>
-      <c r="H14" s="227"/>
-      <c r="I14" s="223"/>
-      <c r="J14" s="228"/>
-      <c r="K14" s="229"/>
-      <c r="L14" s="229"/>
-      <c r="M14" s="229"/>
-      <c r="N14" s="229"/>
-      <c r="O14" s="229"/>
-      <c r="P14" s="230"/>
-      <c r="Q14" s="231"/>
-      <c r="R14" s="232"/>
-      <c r="S14" s="232"/>
-      <c r="T14" s="232"/>
-      <c r="U14" s="232"/>
-      <c r="V14" s="232"/>
-      <c r="W14" s="232"/>
-      <c r="X14" s="232"/>
-      <c r="Y14" s="232"/>
-      <c r="Z14" s="232"/>
-      <c r="AA14" s="232"/>
-      <c r="AB14" s="232"/>
-      <c r="AC14" s="232"/>
-      <c r="AD14" s="232"/>
-      <c r="AE14" s="233"/>
-      <c r="AF14" s="228"/>
-      <c r="AG14" s="229"/>
-      <c r="AH14" s="229"/>
-      <c r="AI14" s="230"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="186"/>
+      <c r="D14" s="187"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="189"/>
+      <c r="G14" s="185"/>
+      <c r="H14" s="190"/>
+      <c r="I14" s="186"/>
+      <c r="J14" s="191"/>
+      <c r="K14" s="192"/>
+      <c r="L14" s="192"/>
+      <c r="M14" s="192"/>
+      <c r="N14" s="192"/>
+      <c r="O14" s="192"/>
+      <c r="P14" s="193"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
+      <c r="S14" s="195"/>
+      <c r="T14" s="195"/>
+      <c r="U14" s="195"/>
+      <c r="V14" s="195"/>
+      <c r="W14" s="195"/>
+      <c r="X14" s="195"/>
+      <c r="Y14" s="195"/>
+      <c r="Z14" s="195"/>
+      <c r="AA14" s="195"/>
+      <c r="AB14" s="195"/>
+      <c r="AC14" s="195"/>
+      <c r="AD14" s="195"/>
+      <c r="AE14" s="196"/>
+      <c r="AF14" s="191"/>
+      <c r="AG14" s="192"/>
+      <c r="AH14" s="192"/>
+      <c r="AI14" s="193"/>
     </row>
     <row r="15" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="89"/>
-      <c r="B15" s="222"/>
-      <c r="C15" s="223"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="225"/>
-      <c r="F15" s="226"/>
-      <c r="G15" s="222"/>
-      <c r="H15" s="227"/>
-      <c r="I15" s="223"/>
-      <c r="J15" s="228"/>
-      <c r="K15" s="229"/>
-      <c r="L15" s="229"/>
-      <c r="M15" s="229"/>
-      <c r="N15" s="229"/>
-      <c r="O15" s="229"/>
-      <c r="P15" s="230"/>
-      <c r="Q15" s="231"/>
-      <c r="R15" s="232"/>
-      <c r="S15" s="232"/>
-      <c r="T15" s="232"/>
-      <c r="U15" s="232"/>
-      <c r="V15" s="232"/>
-      <c r="W15" s="232"/>
-      <c r="X15" s="232"/>
-      <c r="Y15" s="232"/>
-      <c r="Z15" s="232"/>
-      <c r="AA15" s="232"/>
-      <c r="AB15" s="232"/>
-      <c r="AC15" s="232"/>
-      <c r="AD15" s="232"/>
-      <c r="AE15" s="233"/>
-      <c r="AF15" s="228"/>
-      <c r="AG15" s="229"/>
-      <c r="AH15" s="229"/>
-      <c r="AI15" s="230"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="189"/>
+      <c r="G15" s="185"/>
+      <c r="H15" s="190"/>
+      <c r="I15" s="186"/>
+      <c r="J15" s="191"/>
+      <c r="K15" s="192"/>
+      <c r="L15" s="192"/>
+      <c r="M15" s="192"/>
+      <c r="N15" s="192"/>
+      <c r="O15" s="192"/>
+      <c r="P15" s="193"/>
+      <c r="Q15" s="194"/>
+      <c r="R15" s="195"/>
+      <c r="S15" s="195"/>
+      <c r="T15" s="195"/>
+      <c r="U15" s="195"/>
+      <c r="V15" s="195"/>
+      <c r="W15" s="195"/>
+      <c r="X15" s="195"/>
+      <c r="Y15" s="195"/>
+      <c r="Z15" s="195"/>
+      <c r="AA15" s="195"/>
+      <c r="AB15" s="195"/>
+      <c r="AC15" s="195"/>
+      <c r="AD15" s="195"/>
+      <c r="AE15" s="196"/>
+      <c r="AF15" s="191"/>
+      <c r="AG15" s="192"/>
+      <c r="AH15" s="192"/>
+      <c r="AI15" s="193"/>
     </row>
     <row r="16" spans="1:40" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="89"/>
-      <c r="B16" s="222"/>
-      <c r="C16" s="223"/>
-      <c r="D16" s="224"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="226"/>
-      <c r="G16" s="222"/>
-      <c r="H16" s="227"/>
-      <c r="I16" s="223"/>
-      <c r="J16" s="228"/>
-      <c r="K16" s="229"/>
-      <c r="L16" s="229"/>
-      <c r="M16" s="229"/>
-      <c r="N16" s="229"/>
-      <c r="O16" s="229"/>
-      <c r="P16" s="230"/>
-      <c r="Q16" s="231"/>
-      <c r="R16" s="232"/>
-      <c r="S16" s="232"/>
-      <c r="T16" s="232"/>
-      <c r="U16" s="232"/>
-      <c r="V16" s="232"/>
-      <c r="W16" s="232"/>
-      <c r="X16" s="232"/>
-      <c r="Y16" s="232"/>
-      <c r="Z16" s="232"/>
-      <c r="AA16" s="232"/>
-      <c r="AB16" s="232"/>
-      <c r="AC16" s="232"/>
-      <c r="AD16" s="232"/>
-      <c r="AE16" s="233"/>
-      <c r="AF16" s="228"/>
-      <c r="AG16" s="229"/>
-      <c r="AH16" s="229"/>
-      <c r="AI16" s="230"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="186"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="189"/>
+      <c r="G16" s="185"/>
+      <c r="H16" s="190"/>
+      <c r="I16" s="186"/>
+      <c r="J16" s="191"/>
+      <c r="K16" s="192"/>
+      <c r="L16" s="192"/>
+      <c r="M16" s="192"/>
+      <c r="N16" s="192"/>
+      <c r="O16" s="192"/>
+      <c r="P16" s="193"/>
+      <c r="Q16" s="194"/>
+      <c r="R16" s="195"/>
+      <c r="S16" s="195"/>
+      <c r="T16" s="195"/>
+      <c r="U16" s="195"/>
+      <c r="V16" s="195"/>
+      <c r="W16" s="195"/>
+      <c r="X16" s="195"/>
+      <c r="Y16" s="195"/>
+      <c r="Z16" s="195"/>
+      <c r="AA16" s="195"/>
+      <c r="AB16" s="195"/>
+      <c r="AC16" s="195"/>
+      <c r="AD16" s="195"/>
+      <c r="AE16" s="196"/>
+      <c r="AF16" s="191"/>
+      <c r="AG16" s="192"/>
+      <c r="AH16" s="192"/>
+      <c r="AI16" s="193"/>
     </row>
     <row r="17" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="89"/>
-      <c r="B17" s="222"/>
-      <c r="C17" s="223"/>
-      <c r="D17" s="224"/>
-      <c r="E17" s="225"/>
-      <c r="F17" s="226"/>
-      <c r="G17" s="222"/>
-      <c r="H17" s="227"/>
-      <c r="I17" s="223"/>
-      <c r="J17" s="228"/>
-      <c r="K17" s="229"/>
-      <c r="L17" s="229"/>
-      <c r="M17" s="229"/>
-      <c r="N17" s="229"/>
-      <c r="O17" s="229"/>
-      <c r="P17" s="230"/>
-      <c r="Q17" s="231"/>
-      <c r="R17" s="232"/>
-      <c r="S17" s="232"/>
-      <c r="T17" s="232"/>
-      <c r="U17" s="232"/>
-      <c r="V17" s="232"/>
-      <c r="W17" s="232"/>
-      <c r="X17" s="232"/>
-      <c r="Y17" s="232"/>
-      <c r="Z17" s="232"/>
-      <c r="AA17" s="232"/>
-      <c r="AB17" s="232"/>
-      <c r="AC17" s="232"/>
-      <c r="AD17" s="232"/>
-      <c r="AE17" s="233"/>
-      <c r="AF17" s="228"/>
-      <c r="AG17" s="229"/>
-      <c r="AH17" s="229"/>
-      <c r="AI17" s="230"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="187"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="189"/>
+      <c r="G17" s="185"/>
+      <c r="H17" s="190"/>
+      <c r="I17" s="186"/>
+      <c r="J17" s="191"/>
+      <c r="K17" s="192"/>
+      <c r="L17" s="192"/>
+      <c r="M17" s="192"/>
+      <c r="N17" s="192"/>
+      <c r="O17" s="192"/>
+      <c r="P17" s="193"/>
+      <c r="Q17" s="194"/>
+      <c r="R17" s="195"/>
+      <c r="S17" s="195"/>
+      <c r="T17" s="195"/>
+      <c r="U17" s="195"/>
+      <c r="V17" s="195"/>
+      <c r="W17" s="195"/>
+      <c r="X17" s="195"/>
+      <c r="Y17" s="195"/>
+      <c r="Z17" s="195"/>
+      <c r="AA17" s="195"/>
+      <c r="AB17" s="195"/>
+      <c r="AC17" s="195"/>
+      <c r="AD17" s="195"/>
+      <c r="AE17" s="196"/>
+      <c r="AF17" s="191"/>
+      <c r="AG17" s="192"/>
+      <c r="AH17" s="192"/>
+      <c r="AI17" s="193"/>
     </row>
     <row r="18" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="89"/>
-      <c r="B18" s="222"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="224"/>
-      <c r="E18" s="225"/>
-      <c r="F18" s="226"/>
-      <c r="G18" s="222"/>
-      <c r="H18" s="227"/>
-      <c r="I18" s="223"/>
-      <c r="J18" s="228"/>
-      <c r="K18" s="229"/>
-      <c r="L18" s="229"/>
-      <c r="M18" s="229"/>
-      <c r="N18" s="229"/>
-      <c r="O18" s="229"/>
-      <c r="P18" s="230"/>
-      <c r="Q18" s="231"/>
-      <c r="R18" s="232"/>
-      <c r="S18" s="232"/>
-      <c r="T18" s="232"/>
-      <c r="U18" s="232"/>
-      <c r="V18" s="232"/>
-      <c r="W18" s="232"/>
-      <c r="X18" s="232"/>
-      <c r="Y18" s="232"/>
-      <c r="Z18" s="232"/>
-      <c r="AA18" s="232"/>
-      <c r="AB18" s="232"/>
-      <c r="AC18" s="232"/>
-      <c r="AD18" s="232"/>
-      <c r="AE18" s="233"/>
-      <c r="AF18" s="228"/>
-      <c r="AG18" s="229"/>
-      <c r="AH18" s="229"/>
-      <c r="AI18" s="230"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="187"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="189"/>
+      <c r="G18" s="185"/>
+      <c r="H18" s="190"/>
+      <c r="I18" s="186"/>
+      <c r="J18" s="191"/>
+      <c r="K18" s="192"/>
+      <c r="L18" s="192"/>
+      <c r="M18" s="192"/>
+      <c r="N18" s="192"/>
+      <c r="O18" s="192"/>
+      <c r="P18" s="193"/>
+      <c r="Q18" s="194"/>
+      <c r="R18" s="195"/>
+      <c r="S18" s="195"/>
+      <c r="T18" s="195"/>
+      <c r="U18" s="195"/>
+      <c r="V18" s="195"/>
+      <c r="W18" s="195"/>
+      <c r="X18" s="195"/>
+      <c r="Y18" s="195"/>
+      <c r="Z18" s="195"/>
+      <c r="AA18" s="195"/>
+      <c r="AB18" s="195"/>
+      <c r="AC18" s="195"/>
+      <c r="AD18" s="195"/>
+      <c r="AE18" s="196"/>
+      <c r="AF18" s="191"/>
+      <c r="AG18" s="192"/>
+      <c r="AH18" s="192"/>
+      <c r="AI18" s="193"/>
     </row>
     <row r="19" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="89"/>
-      <c r="B19" s="222"/>
-      <c r="C19" s="223"/>
-      <c r="D19" s="224"/>
-      <c r="E19" s="225"/>
-      <c r="F19" s="226"/>
-      <c r="G19" s="222"/>
-      <c r="H19" s="227"/>
-      <c r="I19" s="223"/>
-      <c r="J19" s="228"/>
-      <c r="K19" s="229"/>
-      <c r="L19" s="229"/>
-      <c r="M19" s="229"/>
-      <c r="N19" s="229"/>
-      <c r="O19" s="229"/>
-      <c r="P19" s="230"/>
-      <c r="Q19" s="231"/>
-      <c r="R19" s="232"/>
-      <c r="S19" s="232"/>
-      <c r="T19" s="232"/>
-      <c r="U19" s="232"/>
-      <c r="V19" s="232"/>
-      <c r="W19" s="232"/>
-      <c r="X19" s="232"/>
-      <c r="Y19" s="232"/>
-      <c r="Z19" s="232"/>
-      <c r="AA19" s="232"/>
-      <c r="AB19" s="232"/>
-      <c r="AC19" s="232"/>
-      <c r="AD19" s="232"/>
-      <c r="AE19" s="233"/>
-      <c r="AF19" s="228"/>
-      <c r="AG19" s="229"/>
-      <c r="AH19" s="229"/>
-      <c r="AI19" s="230"/>
+      <c r="B19" s="185"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="187"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="189"/>
+      <c r="G19" s="185"/>
+      <c r="H19" s="190"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="191"/>
+      <c r="K19" s="192"/>
+      <c r="L19" s="192"/>
+      <c r="M19" s="192"/>
+      <c r="N19" s="192"/>
+      <c r="O19" s="192"/>
+      <c r="P19" s="193"/>
+      <c r="Q19" s="194"/>
+      <c r="R19" s="195"/>
+      <c r="S19" s="195"/>
+      <c r="T19" s="195"/>
+      <c r="U19" s="195"/>
+      <c r="V19" s="195"/>
+      <c r="W19" s="195"/>
+      <c r="X19" s="195"/>
+      <c r="Y19" s="195"/>
+      <c r="Z19" s="195"/>
+      <c r="AA19" s="195"/>
+      <c r="AB19" s="195"/>
+      <c r="AC19" s="195"/>
+      <c r="AD19" s="195"/>
+      <c r="AE19" s="196"/>
+      <c r="AF19" s="191"/>
+      <c r="AG19" s="192"/>
+      <c r="AH19" s="192"/>
+      <c r="AI19" s="193"/>
     </row>
     <row r="20" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="89"/>
-      <c r="B20" s="222"/>
-      <c r="C20" s="223"/>
-      <c r="D20" s="224"/>
-      <c r="E20" s="225"/>
-      <c r="F20" s="226"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="227"/>
-      <c r="I20" s="223"/>
-      <c r="J20" s="228"/>
-      <c r="K20" s="229"/>
-      <c r="L20" s="229"/>
-      <c r="M20" s="229"/>
-      <c r="N20" s="229"/>
-      <c r="O20" s="229"/>
-      <c r="P20" s="230"/>
-      <c r="Q20" s="231"/>
-      <c r="R20" s="232"/>
-      <c r="S20" s="232"/>
-      <c r="T20" s="232"/>
-      <c r="U20" s="232"/>
-      <c r="V20" s="232"/>
-      <c r="W20" s="232"/>
-      <c r="X20" s="232"/>
-      <c r="Y20" s="232"/>
-      <c r="Z20" s="232"/>
-      <c r="AA20" s="232"/>
-      <c r="AB20" s="232"/>
-      <c r="AC20" s="232"/>
-      <c r="AD20" s="232"/>
-      <c r="AE20" s="233"/>
-      <c r="AF20" s="228"/>
-      <c r="AG20" s="229"/>
-      <c r="AH20" s="229"/>
-      <c r="AI20" s="230"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="187"/>
+      <c r="E20" s="188"/>
+      <c r="F20" s="189"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="190"/>
+      <c r="I20" s="186"/>
+      <c r="J20" s="191"/>
+      <c r="K20" s="192"/>
+      <c r="L20" s="192"/>
+      <c r="M20" s="192"/>
+      <c r="N20" s="192"/>
+      <c r="O20" s="192"/>
+      <c r="P20" s="193"/>
+      <c r="Q20" s="194"/>
+      <c r="R20" s="195"/>
+      <c r="S20" s="195"/>
+      <c r="T20" s="195"/>
+      <c r="U20" s="195"/>
+      <c r="V20" s="195"/>
+      <c r="W20" s="195"/>
+      <c r="X20" s="195"/>
+      <c r="Y20" s="195"/>
+      <c r="Z20" s="195"/>
+      <c r="AA20" s="195"/>
+      <c r="AB20" s="195"/>
+      <c r="AC20" s="195"/>
+      <c r="AD20" s="195"/>
+      <c r="AE20" s="196"/>
+      <c r="AF20" s="191"/>
+      <c r="AG20" s="192"/>
+      <c r="AH20" s="192"/>
+      <c r="AI20" s="193"/>
     </row>
     <row r="21" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="89"/>
-      <c r="B21" s="222"/>
-      <c r="C21" s="223"/>
-      <c r="D21" s="224"/>
-      <c r="E21" s="225"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="227"/>
-      <c r="I21" s="223"/>
-      <c r="J21" s="228"/>
-      <c r="K21" s="229"/>
-      <c r="L21" s="229"/>
-      <c r="M21" s="229"/>
-      <c r="N21" s="229"/>
-      <c r="O21" s="229"/>
-      <c r="P21" s="230"/>
-      <c r="Q21" s="231"/>
-      <c r="R21" s="232"/>
-      <c r="S21" s="232"/>
-      <c r="T21" s="232"/>
-      <c r="U21" s="232"/>
-      <c r="V21" s="232"/>
-      <c r="W21" s="232"/>
-      <c r="X21" s="232"/>
-      <c r="Y21" s="232"/>
-      <c r="Z21" s="232"/>
-      <c r="AA21" s="232"/>
-      <c r="AB21" s="232"/>
-      <c r="AC21" s="232"/>
-      <c r="AD21" s="232"/>
-      <c r="AE21" s="233"/>
-      <c r="AF21" s="228"/>
-      <c r="AG21" s="229"/>
-      <c r="AH21" s="229"/>
-      <c r="AI21" s="230"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="187"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="189"/>
+      <c r="G21" s="185"/>
+      <c r="H21" s="190"/>
+      <c r="I21" s="186"/>
+      <c r="J21" s="191"/>
+      <c r="K21" s="192"/>
+      <c r="L21" s="192"/>
+      <c r="M21" s="192"/>
+      <c r="N21" s="192"/>
+      <c r="O21" s="192"/>
+      <c r="P21" s="193"/>
+      <c r="Q21" s="194"/>
+      <c r="R21" s="195"/>
+      <c r="S21" s="195"/>
+      <c r="T21" s="195"/>
+      <c r="U21" s="195"/>
+      <c r="V21" s="195"/>
+      <c r="W21" s="195"/>
+      <c r="X21" s="195"/>
+      <c r="Y21" s="195"/>
+      <c r="Z21" s="195"/>
+      <c r="AA21" s="195"/>
+      <c r="AB21" s="195"/>
+      <c r="AC21" s="195"/>
+      <c r="AD21" s="195"/>
+      <c r="AE21" s="196"/>
+      <c r="AF21" s="191"/>
+      <c r="AG21" s="192"/>
+      <c r="AH21" s="192"/>
+      <c r="AI21" s="193"/>
     </row>
     <row r="22" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="89"/>
-      <c r="B22" s="222"/>
-      <c r="C22" s="223"/>
-      <c r="D22" s="224"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="222"/>
-      <c r="H22" s="227"/>
-      <c r="I22" s="223"/>
-      <c r="J22" s="228"/>
-      <c r="K22" s="229"/>
-      <c r="L22" s="229"/>
-      <c r="M22" s="229"/>
-      <c r="N22" s="229"/>
-      <c r="O22" s="229"/>
-      <c r="P22" s="230"/>
-      <c r="Q22" s="231"/>
-      <c r="R22" s="232"/>
-      <c r="S22" s="232"/>
-      <c r="T22" s="232"/>
-      <c r="U22" s="232"/>
-      <c r="V22" s="232"/>
-      <c r="W22" s="232"/>
-      <c r="X22" s="232"/>
-      <c r="Y22" s="232"/>
-      <c r="Z22" s="232"/>
-      <c r="AA22" s="232"/>
-      <c r="AB22" s="232"/>
-      <c r="AC22" s="232"/>
-      <c r="AD22" s="232"/>
-      <c r="AE22" s="233"/>
-      <c r="AF22" s="228"/>
-      <c r="AG22" s="229"/>
-      <c r="AH22" s="229"/>
-      <c r="AI22" s="230"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="187"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="189"/>
+      <c r="G22" s="185"/>
+      <c r="H22" s="190"/>
+      <c r="I22" s="186"/>
+      <c r="J22" s="191"/>
+      <c r="K22" s="192"/>
+      <c r="L22" s="192"/>
+      <c r="M22" s="192"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="192"/>
+      <c r="P22" s="193"/>
+      <c r="Q22" s="194"/>
+      <c r="R22" s="195"/>
+      <c r="S22" s="195"/>
+      <c r="T22" s="195"/>
+      <c r="U22" s="195"/>
+      <c r="V22" s="195"/>
+      <c r="W22" s="195"/>
+      <c r="X22" s="195"/>
+      <c r="Y22" s="195"/>
+      <c r="Z22" s="195"/>
+      <c r="AA22" s="195"/>
+      <c r="AB22" s="195"/>
+      <c r="AC22" s="195"/>
+      <c r="AD22" s="195"/>
+      <c r="AE22" s="196"/>
+      <c r="AF22" s="191"/>
+      <c r="AG22" s="192"/>
+      <c r="AH22" s="192"/>
+      <c r="AI22" s="193"/>
     </row>
     <row r="23" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="89"/>
-      <c r="B23" s="222"/>
-      <c r="C23" s="223"/>
-      <c r="D23" s="224"/>
-      <c r="E23" s="225"/>
-      <c r="F23" s="226"/>
-      <c r="G23" s="222"/>
-      <c r="H23" s="227"/>
-      <c r="I23" s="223"/>
-      <c r="J23" s="228"/>
-      <c r="K23" s="229"/>
-      <c r="L23" s="229"/>
-      <c r="M23" s="229"/>
-      <c r="N23" s="229"/>
-      <c r="O23" s="229"/>
-      <c r="P23" s="230"/>
-      <c r="Q23" s="231"/>
-      <c r="R23" s="232"/>
-      <c r="S23" s="232"/>
-      <c r="T23" s="232"/>
-      <c r="U23" s="232"/>
-      <c r="V23" s="232"/>
-      <c r="W23" s="232"/>
-      <c r="X23" s="232"/>
-      <c r="Y23" s="232"/>
-      <c r="Z23" s="232"/>
-      <c r="AA23" s="232"/>
-      <c r="AB23" s="232"/>
-      <c r="AC23" s="232"/>
-      <c r="AD23" s="232"/>
-      <c r="AE23" s="233"/>
-      <c r="AF23" s="228"/>
-      <c r="AG23" s="229"/>
-      <c r="AH23" s="229"/>
-      <c r="AI23" s="230"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="187"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="189"/>
+      <c r="G23" s="185"/>
+      <c r="H23" s="190"/>
+      <c r="I23" s="186"/>
+      <c r="J23" s="191"/>
+      <c r="K23" s="192"/>
+      <c r="L23" s="192"/>
+      <c r="M23" s="192"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="192"/>
+      <c r="P23" s="193"/>
+      <c r="Q23" s="194"/>
+      <c r="R23" s="195"/>
+      <c r="S23" s="195"/>
+      <c r="T23" s="195"/>
+      <c r="U23" s="195"/>
+      <c r="V23" s="195"/>
+      <c r="W23" s="195"/>
+      <c r="X23" s="195"/>
+      <c r="Y23" s="195"/>
+      <c r="Z23" s="195"/>
+      <c r="AA23" s="195"/>
+      <c r="AB23" s="195"/>
+      <c r="AC23" s="195"/>
+      <c r="AD23" s="195"/>
+      <c r="AE23" s="196"/>
+      <c r="AF23" s="191"/>
+      <c r="AG23" s="192"/>
+      <c r="AH23" s="192"/>
+      <c r="AI23" s="193"/>
     </row>
     <row r="24" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="89"/>
-      <c r="B24" s="222"/>
-      <c r="C24" s="223"/>
-      <c r="D24" s="224"/>
-      <c r="E24" s="225"/>
-      <c r="F24" s="226"/>
-      <c r="G24" s="222"/>
-      <c r="H24" s="227"/>
-      <c r="I24" s="223"/>
-      <c r="J24" s="228"/>
-      <c r="K24" s="229"/>
-      <c r="L24" s="229"/>
-      <c r="M24" s="229"/>
-      <c r="N24" s="229"/>
-      <c r="O24" s="229"/>
-      <c r="P24" s="230"/>
-      <c r="Q24" s="231"/>
-      <c r="R24" s="232"/>
-      <c r="S24" s="232"/>
-      <c r="T24" s="232"/>
-      <c r="U24" s="232"/>
-      <c r="V24" s="232"/>
-      <c r="W24" s="232"/>
-      <c r="X24" s="232"/>
-      <c r="Y24" s="232"/>
-      <c r="Z24" s="232"/>
-      <c r="AA24" s="232"/>
-      <c r="AB24" s="232"/>
-      <c r="AC24" s="232"/>
-      <c r="AD24" s="232"/>
-      <c r="AE24" s="233"/>
-      <c r="AF24" s="228"/>
-      <c r="AG24" s="229"/>
-      <c r="AH24" s="229"/>
-      <c r="AI24" s="230"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="187"/>
+      <c r="E24" s="188"/>
+      <c r="F24" s="189"/>
+      <c r="G24" s="185"/>
+      <c r="H24" s="190"/>
+      <c r="I24" s="186"/>
+      <c r="J24" s="191"/>
+      <c r="K24" s="192"/>
+      <c r="L24" s="192"/>
+      <c r="M24" s="192"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="192"/>
+      <c r="P24" s="193"/>
+      <c r="Q24" s="194"/>
+      <c r="R24" s="195"/>
+      <c r="S24" s="195"/>
+      <c r="T24" s="195"/>
+      <c r="U24" s="195"/>
+      <c r="V24" s="195"/>
+      <c r="W24" s="195"/>
+      <c r="X24" s="195"/>
+      <c r="Y24" s="195"/>
+      <c r="Z24" s="195"/>
+      <c r="AA24" s="195"/>
+      <c r="AB24" s="195"/>
+      <c r="AC24" s="195"/>
+      <c r="AD24" s="195"/>
+      <c r="AE24" s="196"/>
+      <c r="AF24" s="191"/>
+      <c r="AG24" s="192"/>
+      <c r="AH24" s="192"/>
+      <c r="AI24" s="193"/>
     </row>
     <row r="25" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="89"/>
-      <c r="B25" s="222"/>
-      <c r="C25" s="223"/>
-      <c r="D25" s="224"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="226"/>
-      <c r="G25" s="222"/>
-      <c r="H25" s="227"/>
-      <c r="I25" s="223"/>
-      <c r="J25" s="228"/>
-      <c r="K25" s="229"/>
-      <c r="L25" s="229"/>
-      <c r="M25" s="229"/>
-      <c r="N25" s="229"/>
-      <c r="O25" s="229"/>
-      <c r="P25" s="230"/>
-      <c r="Q25" s="231"/>
-      <c r="R25" s="232"/>
-      <c r="S25" s="232"/>
-      <c r="T25" s="232"/>
-      <c r="U25" s="232"/>
-      <c r="V25" s="232"/>
-      <c r="W25" s="232"/>
-      <c r="X25" s="232"/>
-      <c r="Y25" s="232"/>
-      <c r="Z25" s="232"/>
-      <c r="AA25" s="232"/>
-      <c r="AB25" s="232"/>
-      <c r="AC25" s="232"/>
-      <c r="AD25" s="232"/>
-      <c r="AE25" s="233"/>
-      <c r="AF25" s="228"/>
-      <c r="AG25" s="229"/>
-      <c r="AH25" s="229"/>
-      <c r="AI25" s="230"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="187"/>
+      <c r="E25" s="188"/>
+      <c r="F25" s="189"/>
+      <c r="G25" s="185"/>
+      <c r="H25" s="190"/>
+      <c r="I25" s="186"/>
+      <c r="J25" s="191"/>
+      <c r="K25" s="192"/>
+      <c r="L25" s="192"/>
+      <c r="M25" s="192"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="192"/>
+      <c r="P25" s="193"/>
+      <c r="Q25" s="194"/>
+      <c r="R25" s="195"/>
+      <c r="S25" s="195"/>
+      <c r="T25" s="195"/>
+      <c r="U25" s="195"/>
+      <c r="V25" s="195"/>
+      <c r="W25" s="195"/>
+      <c r="X25" s="195"/>
+      <c r="Y25" s="195"/>
+      <c r="Z25" s="195"/>
+      <c r="AA25" s="195"/>
+      <c r="AB25" s="195"/>
+      <c r="AC25" s="195"/>
+      <c r="AD25" s="195"/>
+      <c r="AE25" s="196"/>
+      <c r="AF25" s="191"/>
+      <c r="AG25" s="192"/>
+      <c r="AH25" s="192"/>
+      <c r="AI25" s="193"/>
     </row>
     <row r="26" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="89"/>
-      <c r="B26" s="222"/>
-      <c r="C26" s="223"/>
-      <c r="D26" s="224"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="226"/>
-      <c r="G26" s="222"/>
-      <c r="H26" s="227"/>
-      <c r="I26" s="223"/>
-      <c r="J26" s="228"/>
-      <c r="K26" s="229"/>
-      <c r="L26" s="229"/>
-      <c r="M26" s="229"/>
-      <c r="N26" s="229"/>
-      <c r="O26" s="229"/>
-      <c r="P26" s="230"/>
-      <c r="Q26" s="231"/>
-      <c r="R26" s="232"/>
-      <c r="S26" s="232"/>
-      <c r="T26" s="232"/>
-      <c r="U26" s="232"/>
-      <c r="V26" s="232"/>
-      <c r="W26" s="232"/>
-      <c r="X26" s="232"/>
-      <c r="Y26" s="232"/>
-      <c r="Z26" s="232"/>
-      <c r="AA26" s="232"/>
-      <c r="AB26" s="232"/>
-      <c r="AC26" s="232"/>
-      <c r="AD26" s="232"/>
-      <c r="AE26" s="233"/>
-      <c r="AF26" s="228"/>
-      <c r="AG26" s="229"/>
-      <c r="AH26" s="229"/>
-      <c r="AI26" s="230"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="187"/>
+      <c r="E26" s="188"/>
+      <c r="F26" s="189"/>
+      <c r="G26" s="185"/>
+      <c r="H26" s="190"/>
+      <c r="I26" s="186"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="192"/>
+      <c r="L26" s="192"/>
+      <c r="M26" s="192"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="192"/>
+      <c r="P26" s="193"/>
+      <c r="Q26" s="194"/>
+      <c r="R26" s="195"/>
+      <c r="S26" s="195"/>
+      <c r="T26" s="195"/>
+      <c r="U26" s="195"/>
+      <c r="V26" s="195"/>
+      <c r="W26" s="195"/>
+      <c r="X26" s="195"/>
+      <c r="Y26" s="195"/>
+      <c r="Z26" s="195"/>
+      <c r="AA26" s="195"/>
+      <c r="AB26" s="195"/>
+      <c r="AC26" s="195"/>
+      <c r="AD26" s="195"/>
+      <c r="AE26" s="196"/>
+      <c r="AF26" s="191"/>
+      <c r="AG26" s="192"/>
+      <c r="AH26" s="192"/>
+      <c r="AI26" s="193"/>
     </row>
     <row r="27" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="89"/>
-      <c r="B27" s="222"/>
-      <c r="C27" s="223"/>
-      <c r="D27" s="224"/>
-      <c r="E27" s="225"/>
-      <c r="F27" s="226"/>
-      <c r="G27" s="222"/>
-      <c r="H27" s="227"/>
-      <c r="I27" s="223"/>
-      <c r="J27" s="228"/>
-      <c r="K27" s="229"/>
-      <c r="L27" s="229"/>
-      <c r="M27" s="229"/>
-      <c r="N27" s="229"/>
-      <c r="O27" s="229"/>
-      <c r="P27" s="230"/>
-      <c r="Q27" s="231"/>
-      <c r="R27" s="232"/>
-      <c r="S27" s="232"/>
-      <c r="T27" s="232"/>
-      <c r="U27" s="232"/>
-      <c r="V27" s="232"/>
-      <c r="W27" s="232"/>
-      <c r="X27" s="232"/>
-      <c r="Y27" s="232"/>
-      <c r="Z27" s="232"/>
-      <c r="AA27" s="232"/>
-      <c r="AB27" s="232"/>
-      <c r="AC27" s="232"/>
-      <c r="AD27" s="232"/>
-      <c r="AE27" s="233"/>
-      <c r="AF27" s="228"/>
-      <c r="AG27" s="229"/>
-      <c r="AH27" s="229"/>
-      <c r="AI27" s="230"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="187"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="189"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="190"/>
+      <c r="I27" s="186"/>
+      <c r="J27" s="191"/>
+      <c r="K27" s="192"/>
+      <c r="L27" s="192"/>
+      <c r="M27" s="192"/>
+      <c r="N27" s="192"/>
+      <c r="O27" s="192"/>
+      <c r="P27" s="193"/>
+      <c r="Q27" s="194"/>
+      <c r="R27" s="195"/>
+      <c r="S27" s="195"/>
+      <c r="T27" s="195"/>
+      <c r="U27" s="195"/>
+      <c r="V27" s="195"/>
+      <c r="W27" s="195"/>
+      <c r="X27" s="195"/>
+      <c r="Y27" s="195"/>
+      <c r="Z27" s="195"/>
+      <c r="AA27" s="195"/>
+      <c r="AB27" s="195"/>
+      <c r="AC27" s="195"/>
+      <c r="AD27" s="195"/>
+      <c r="AE27" s="196"/>
+      <c r="AF27" s="191"/>
+      <c r="AG27" s="192"/>
+      <c r="AH27" s="192"/>
+      <c r="AI27" s="193"/>
     </row>
     <row r="28" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="89"/>
-      <c r="B28" s="222"/>
-      <c r="C28" s="223"/>
-      <c r="D28" s="224"/>
-      <c r="E28" s="225"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="222"/>
-      <c r="H28" s="227"/>
-      <c r="I28" s="223"/>
-      <c r="J28" s="228"/>
-      <c r="K28" s="229"/>
-      <c r="L28" s="229"/>
-      <c r="M28" s="229"/>
-      <c r="N28" s="229"/>
-      <c r="O28" s="229"/>
-      <c r="P28" s="230"/>
-      <c r="Q28" s="231"/>
-      <c r="R28" s="232"/>
-      <c r="S28" s="232"/>
-      <c r="T28" s="232"/>
-      <c r="U28" s="232"/>
-      <c r="V28" s="232"/>
-      <c r="W28" s="232"/>
-      <c r="X28" s="232"/>
-      <c r="Y28" s="232"/>
-      <c r="Z28" s="232"/>
-      <c r="AA28" s="232"/>
-      <c r="AB28" s="232"/>
-      <c r="AC28" s="232"/>
-      <c r="AD28" s="232"/>
-      <c r="AE28" s="233"/>
-      <c r="AF28" s="228"/>
-      <c r="AG28" s="229"/>
-      <c r="AH28" s="229"/>
-      <c r="AI28" s="230"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="187"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="189"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="190"/>
+      <c r="I28" s="186"/>
+      <c r="J28" s="191"/>
+      <c r="K28" s="192"/>
+      <c r="L28" s="192"/>
+      <c r="M28" s="192"/>
+      <c r="N28" s="192"/>
+      <c r="O28" s="192"/>
+      <c r="P28" s="193"/>
+      <c r="Q28" s="194"/>
+      <c r="R28" s="195"/>
+      <c r="S28" s="195"/>
+      <c r="T28" s="195"/>
+      <c r="U28" s="195"/>
+      <c r="V28" s="195"/>
+      <c r="W28" s="195"/>
+      <c r="X28" s="195"/>
+      <c r="Y28" s="195"/>
+      <c r="Z28" s="195"/>
+      <c r="AA28" s="195"/>
+      <c r="AB28" s="195"/>
+      <c r="AC28" s="195"/>
+      <c r="AD28" s="195"/>
+      <c r="AE28" s="196"/>
+      <c r="AF28" s="191"/>
+      <c r="AG28" s="192"/>
+      <c r="AH28" s="192"/>
+      <c r="AI28" s="193"/>
     </row>
     <row r="29" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="89"/>
-      <c r="B29" s="222"/>
-      <c r="C29" s="223"/>
-      <c r="D29" s="224"/>
-      <c r="E29" s="225"/>
-      <c r="F29" s="226"/>
-      <c r="G29" s="222"/>
-      <c r="H29" s="227"/>
-      <c r="I29" s="223"/>
-      <c r="J29" s="228"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="229"/>
-      <c r="M29" s="229"/>
-      <c r="N29" s="229"/>
-      <c r="O29" s="229"/>
-      <c r="P29" s="230"/>
-      <c r="Q29" s="231"/>
-      <c r="R29" s="232"/>
-      <c r="S29" s="232"/>
-      <c r="T29" s="232"/>
-      <c r="U29" s="232"/>
-      <c r="V29" s="232"/>
-      <c r="W29" s="232"/>
-      <c r="X29" s="232"/>
-      <c r="Y29" s="232"/>
-      <c r="Z29" s="232"/>
-      <c r="AA29" s="232"/>
-      <c r="AB29" s="232"/>
-      <c r="AC29" s="232"/>
-      <c r="AD29" s="232"/>
-      <c r="AE29" s="233"/>
-      <c r="AF29" s="228"/>
-      <c r="AG29" s="229"/>
-      <c r="AH29" s="229"/>
-      <c r="AI29" s="230"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="187"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="189"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="190"/>
+      <c r="I29" s="186"/>
+      <c r="J29" s="191"/>
+      <c r="K29" s="192"/>
+      <c r="L29" s="192"/>
+      <c r="M29" s="192"/>
+      <c r="N29" s="192"/>
+      <c r="O29" s="192"/>
+      <c r="P29" s="193"/>
+      <c r="Q29" s="194"/>
+      <c r="R29" s="195"/>
+      <c r="S29" s="195"/>
+      <c r="T29" s="195"/>
+      <c r="U29" s="195"/>
+      <c r="V29" s="195"/>
+      <c r="W29" s="195"/>
+      <c r="X29" s="195"/>
+      <c r="Y29" s="195"/>
+      <c r="Z29" s="195"/>
+      <c r="AA29" s="195"/>
+      <c r="AB29" s="195"/>
+      <c r="AC29" s="195"/>
+      <c r="AD29" s="195"/>
+      <c r="AE29" s="196"/>
+      <c r="AF29" s="191"/>
+      <c r="AG29" s="192"/>
+      <c r="AH29" s="192"/>
+      <c r="AI29" s="193"/>
     </row>
     <row r="30" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="89"/>
-      <c r="B30" s="222"/>
-      <c r="C30" s="223"/>
-      <c r="D30" s="224"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="226"/>
-      <c r="G30" s="222"/>
-      <c r="H30" s="227"/>
-      <c r="I30" s="223"/>
-      <c r="J30" s="228"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="229"/>
-      <c r="M30" s="229"/>
-      <c r="N30" s="229"/>
-      <c r="O30" s="229"/>
-      <c r="P30" s="230"/>
-      <c r="Q30" s="231"/>
-      <c r="R30" s="232"/>
-      <c r="S30" s="232"/>
-      <c r="T30" s="232"/>
-      <c r="U30" s="232"/>
-      <c r="V30" s="232"/>
-      <c r="W30" s="232"/>
-      <c r="X30" s="232"/>
-      <c r="Y30" s="232"/>
-      <c r="Z30" s="232"/>
-      <c r="AA30" s="232"/>
-      <c r="AB30" s="232"/>
-      <c r="AC30" s="232"/>
-      <c r="AD30" s="232"/>
-      <c r="AE30" s="233"/>
-      <c r="AF30" s="228"/>
-      <c r="AG30" s="229"/>
-      <c r="AH30" s="229"/>
-      <c r="AI30" s="230"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="188"/>
+      <c r="F30" s="189"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="190"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="192"/>
+      <c r="L30" s="192"/>
+      <c r="M30" s="192"/>
+      <c r="N30" s="192"/>
+      <c r="O30" s="192"/>
+      <c r="P30" s="193"/>
+      <c r="Q30" s="194"/>
+      <c r="R30" s="195"/>
+      <c r="S30" s="195"/>
+      <c r="T30" s="195"/>
+      <c r="U30" s="195"/>
+      <c r="V30" s="195"/>
+      <c r="W30" s="195"/>
+      <c r="X30" s="195"/>
+      <c r="Y30" s="195"/>
+      <c r="Z30" s="195"/>
+      <c r="AA30" s="195"/>
+      <c r="AB30" s="195"/>
+      <c r="AC30" s="195"/>
+      <c r="AD30" s="195"/>
+      <c r="AE30" s="196"/>
+      <c r="AF30" s="191"/>
+      <c r="AG30" s="192"/>
+      <c r="AH30" s="192"/>
+      <c r="AI30" s="193"/>
     </row>
     <row r="31" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="89"/>
-      <c r="B31" s="222"/>
-      <c r="C31" s="223"/>
-      <c r="D31" s="224"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="222"/>
-      <c r="H31" s="227"/>
-      <c r="I31" s="223"/>
-      <c r="J31" s="228"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="229"/>
-      <c r="M31" s="229"/>
-      <c r="N31" s="229"/>
-      <c r="O31" s="229"/>
-      <c r="P31" s="230"/>
-      <c r="Q31" s="231"/>
-      <c r="R31" s="232"/>
-      <c r="S31" s="232"/>
-      <c r="T31" s="232"/>
-      <c r="U31" s="232"/>
-      <c r="V31" s="232"/>
-      <c r="W31" s="232"/>
-      <c r="X31" s="232"/>
-      <c r="Y31" s="232"/>
-      <c r="Z31" s="232"/>
-      <c r="AA31" s="232"/>
-      <c r="AB31" s="232"/>
-      <c r="AC31" s="232"/>
-      <c r="AD31" s="232"/>
-      <c r="AE31" s="233"/>
-      <c r="AF31" s="228"/>
-      <c r="AG31" s="229"/>
-      <c r="AH31" s="229"/>
-      <c r="AI31" s="230"/>
+      <c r="B31" s="185"/>
+      <c r="C31" s="186"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="189"/>
+      <c r="G31" s="185"/>
+      <c r="H31" s="190"/>
+      <c r="I31" s="186"/>
+      <c r="J31" s="191"/>
+      <c r="K31" s="192"/>
+      <c r="L31" s="192"/>
+      <c r="M31" s="192"/>
+      <c r="N31" s="192"/>
+      <c r="O31" s="192"/>
+      <c r="P31" s="193"/>
+      <c r="Q31" s="194"/>
+      <c r="R31" s="195"/>
+      <c r="S31" s="195"/>
+      <c r="T31" s="195"/>
+      <c r="U31" s="195"/>
+      <c r="V31" s="195"/>
+      <c r="W31" s="195"/>
+      <c r="X31" s="195"/>
+      <c r="Y31" s="195"/>
+      <c r="Z31" s="195"/>
+      <c r="AA31" s="195"/>
+      <c r="AB31" s="195"/>
+      <c r="AC31" s="195"/>
+      <c r="AD31" s="195"/>
+      <c r="AE31" s="196"/>
+      <c r="AF31" s="191"/>
+      <c r="AG31" s="192"/>
+      <c r="AH31" s="192"/>
+      <c r="AI31" s="193"/>
     </row>
     <row r="32" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="89"/>
-      <c r="B32" s="222"/>
-      <c r="C32" s="223"/>
-      <c r="D32" s="224"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="226"/>
-      <c r="G32" s="222"/>
-      <c r="H32" s="227"/>
-      <c r="I32" s="223"/>
-      <c r="J32" s="228"/>
-      <c r="K32" s="248"/>
-      <c r="L32" s="229"/>
-      <c r="M32" s="229"/>
-      <c r="N32" s="229"/>
-      <c r="O32" s="229"/>
-      <c r="P32" s="230"/>
-      <c r="Q32" s="231"/>
-      <c r="R32" s="232"/>
-      <c r="S32" s="232"/>
-      <c r="T32" s="232"/>
-      <c r="U32" s="232"/>
-      <c r="V32" s="232"/>
-      <c r="W32" s="232"/>
-      <c r="X32" s="232"/>
-      <c r="Y32" s="232"/>
-      <c r="Z32" s="232"/>
-      <c r="AA32" s="232"/>
-      <c r="AB32" s="232"/>
-      <c r="AC32" s="232"/>
-      <c r="AD32" s="232"/>
-      <c r="AE32" s="233"/>
-      <c r="AF32" s="228"/>
-      <c r="AG32" s="229"/>
-      <c r="AH32" s="229"/>
-      <c r="AI32" s="230"/>
+      <c r="B32" s="185"/>
+      <c r="C32" s="186"/>
+      <c r="D32" s="187"/>
+      <c r="E32" s="188"/>
+      <c r="F32" s="189"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="190"/>
+      <c r="I32" s="186"/>
+      <c r="J32" s="191"/>
+      <c r="K32" s="197"/>
+      <c r="L32" s="192"/>
+      <c r="M32" s="192"/>
+      <c r="N32" s="192"/>
+      <c r="O32" s="192"/>
+      <c r="P32" s="193"/>
+      <c r="Q32" s="194"/>
+      <c r="R32" s="195"/>
+      <c r="S32" s="195"/>
+      <c r="T32" s="195"/>
+      <c r="U32" s="195"/>
+      <c r="V32" s="195"/>
+      <c r="W32" s="195"/>
+      <c r="X32" s="195"/>
+      <c r="Y32" s="195"/>
+      <c r="Z32" s="195"/>
+      <c r="AA32" s="195"/>
+      <c r="AB32" s="195"/>
+      <c r="AC32" s="195"/>
+      <c r="AD32" s="195"/>
+      <c r="AE32" s="196"/>
+      <c r="AF32" s="191"/>
+      <c r="AG32" s="192"/>
+      <c r="AH32" s="192"/>
+      <c r="AI32" s="193"/>
     </row>
     <row r="33" spans="1:35" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="89"/>
-      <c r="B33" s="222"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="226"/>
-      <c r="G33" s="222"/>
-      <c r="H33" s="227"/>
-      <c r="I33" s="223"/>
-      <c r="J33" s="228"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="229"/>
-      <c r="M33" s="229"/>
-      <c r="N33" s="229"/>
-      <c r="O33" s="229"/>
-      <c r="P33" s="230"/>
-      <c r="Q33" s="231"/>
-      <c r="R33" s="232"/>
-      <c r="S33" s="232"/>
-      <c r="T33" s="232"/>
-      <c r="U33" s="232"/>
-      <c r="V33" s="232"/>
-      <c r="W33" s="232"/>
-      <c r="X33" s="232"/>
-      <c r="Y33" s="232"/>
-      <c r="Z33" s="232"/>
-      <c r="AA33" s="232"/>
-      <c r="AB33" s="232"/>
-      <c r="AC33" s="232"/>
-      <c r="AD33" s="232"/>
-      <c r="AE33" s="233"/>
-      <c r="AF33" s="228"/>
-      <c r="AG33" s="229"/>
-      <c r="AH33" s="229"/>
-      <c r="AI33" s="230"/>
+      <c r="B33" s="185"/>
+      <c r="C33" s="186"/>
+      <c r="D33" s="187"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="189"/>
+      <c r="G33" s="185"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="191"/>
+      <c r="K33" s="192"/>
+      <c r="L33" s="192"/>
+      <c r="M33" s="192"/>
+      <c r="N33" s="192"/>
+      <c r="O33" s="192"/>
+      <c r="P33" s="193"/>
+      <c r="Q33" s="194"/>
+      <c r="R33" s="195"/>
+      <c r="S33" s="195"/>
+      <c r="T33" s="195"/>
+      <c r="U33" s="195"/>
+      <c r="V33" s="195"/>
+      <c r="W33" s="195"/>
+      <c r="X33" s="195"/>
+      <c r="Y33" s="195"/>
+      <c r="Z33" s="195"/>
+      <c r="AA33" s="195"/>
+      <c r="AB33" s="195"/>
+      <c r="AC33" s="195"/>
+      <c r="AD33" s="195"/>
+      <c r="AE33" s="196"/>
+      <c r="AF33" s="191"/>
+      <c r="AG33" s="192"/>
+      <c r="AH33" s="192"/>
+      <c r="AI33" s="193"/>
     </row>
     <row r="34" spans="1:35" ht="14" x14ac:dyDescent="0.2">
       <c r="K34" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -29056,6 +28919,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -29207,158 +29226,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="218" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="221" t="str">
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="200" t="s">
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="228" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="254" t="str">
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="230"/>
+      <c r="S1" s="250" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="210"/>
-      <c r="Y1" s="210"/>
-      <c r="Z1" s="211"/>
-      <c r="AA1" s="252" t="s">
+      <c r="T1" s="238"/>
+      <c r="U1" s="238"/>
+      <c r="V1" s="238"/>
+      <c r="W1" s="238"/>
+      <c r="X1" s="238"/>
+      <c r="Y1" s="238"/>
+      <c r="Z1" s="239"/>
+      <c r="AA1" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="253"/>
-      <c r="AC1" s="218" t="str">
+      <c r="AB1" s="252"/>
+      <c r="AC1" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="219"/>
-      <c r="AE1" s="219"/>
-      <c r="AF1" s="220"/>
-      <c r="AG1" s="249">
+      <c r="AD1" s="247"/>
+      <c r="AE1" s="247"/>
+      <c r="AF1" s="248"/>
+      <c r="AG1" s="253">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>45565</v>
       </c>
-      <c r="AH1" s="250"/>
-      <c r="AI1" s="251"/>
+      <c r="AH1" s="254"/>
+      <c r="AI1" s="255"/>
       <c r="AL1" s="91"/>
     </row>
     <row r="2" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="218" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="221" t="str">
+      <c r="B2" s="219"/>
+      <c r="C2" s="219"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="203"/>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="205"/>
-      <c r="S2" s="212"/>
-      <c r="T2" s="213"/>
-      <c r="U2" s="213"/>
-      <c r="V2" s="213"/>
-      <c r="W2" s="213"/>
-      <c r="X2" s="213"/>
-      <c r="Y2" s="213"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="252" t="s">
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="241"/>
+      <c r="U2" s="241"/>
+      <c r="V2" s="241"/>
+      <c r="W2" s="241"/>
+      <c r="X2" s="241"/>
+      <c r="Y2" s="241"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="251" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="218" t="str">
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="219"/>
-      <c r="AE2" s="219"/>
-      <c r="AF2" s="220"/>
-      <c r="AG2" s="249" t="str">
+      <c r="AD2" s="247"/>
+      <c r="AE2" s="247"/>
+      <c r="AF2" s="248"/>
+      <c r="AG2" s="253" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="250"/>
-      <c r="AI2" s="251"/>
+      <c r="AH2" s="254"/>
+      <c r="AI2" s="255"/>
     </row>
     <row r="3" spans="1:53" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="190" t="s">
+      <c r="A3" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="191"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="221" t="str">
+      <c r="B3" s="219"/>
+      <c r="C3" s="219"/>
+      <c r="D3" s="220"/>
+      <c r="E3" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="215"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="217"/>
-      <c r="AA3" s="252"/>
-      <c r="AB3" s="253"/>
-      <c r="AC3" s="218" t="str">
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="234"/>
+      <c r="P3" s="235"/>
+      <c r="Q3" s="235"/>
+      <c r="R3" s="236"/>
+      <c r="S3" s="243"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="245"/>
+      <c r="AA3" s="251"/>
+      <c r="AB3" s="252"/>
+      <c r="AC3" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="219"/>
-      <c r="AE3" s="219"/>
-      <c r="AF3" s="220"/>
-      <c r="AG3" s="249" t="str">
+      <c r="AD3" s="247"/>
+      <c r="AE3" s="247"/>
+      <c r="AF3" s="248"/>
+      <c r="AG3" s="253" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="250"/>
-      <c r="AI3" s="251"/>
+      <c r="AH3" s="254"/>
+      <c r="AI3" s="255"/>
     </row>
     <row r="4" spans="1:53" s="31" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AC4" s="92"/>
@@ -31777,6 +31796,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -31786,14 +31813,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -31816,163 +31835,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="259" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="269"/>
-      <c r="E1" s="221" t="str">
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="273" t="s">
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="265" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="274"/>
-      <c r="Q1" s="274"/>
-      <c r="R1" s="275"/>
-      <c r="S1" s="282" t="str">
+      <c r="P1" s="266"/>
+      <c r="Q1" s="266"/>
+      <c r="R1" s="267"/>
+      <c r="S1" s="274" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="283"/>
-      <c r="U1" s="283"/>
-      <c r="V1" s="283"/>
-      <c r="W1" s="283"/>
-      <c r="X1" s="283"/>
-      <c r="Y1" s="283"/>
-      <c r="Z1" s="284"/>
-      <c r="AA1" s="267" t="s">
+      <c r="T1" s="275"/>
+      <c r="U1" s="275"/>
+      <c r="V1" s="275"/>
+      <c r="W1" s="275"/>
+      <c r="X1" s="275"/>
+      <c r="Y1" s="275"/>
+      <c r="Z1" s="276"/>
+      <c r="AA1" s="259" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="269"/>
-      <c r="AC1" s="270" t="str">
+      <c r="AB1" s="261"/>
+      <c r="AC1" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="271"/>
-      <c r="AE1" s="271"/>
-      <c r="AF1" s="272"/>
-      <c r="AG1" s="255">
+      <c r="AD1" s="263"/>
+      <c r="AE1" s="263"/>
+      <c r="AF1" s="264"/>
+      <c r="AG1" s="256">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>45565</v>
       </c>
-      <c r="AH1" s="256"/>
-      <c r="AI1" s="257"/>
+      <c r="AH1" s="257"/>
+      <c r="AI1" s="258"/>
       <c r="AN1" s="17"/>
       <c r="AO1" s="17"/>
       <c r="AP1" s="17"/>
     </row>
     <row r="2" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="259" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="269"/>
-      <c r="E2" s="221" t="str">
+      <c r="B2" s="260"/>
+      <c r="C2" s="260"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="277"/>
-      <c r="Q2" s="277"/>
-      <c r="R2" s="278"/>
-      <c r="S2" s="285"/>
-      <c r="T2" s="286"/>
-      <c r="U2" s="286"/>
-      <c r="V2" s="286"/>
-      <c r="W2" s="286"/>
-      <c r="X2" s="286"/>
-      <c r="Y2" s="286"/>
-      <c r="Z2" s="287"/>
-      <c r="AA2" s="267" t="s">
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="269"/>
+      <c r="Q2" s="269"/>
+      <c r="R2" s="270"/>
+      <c r="S2" s="277"/>
+      <c r="T2" s="278"/>
+      <c r="U2" s="278"/>
+      <c r="V2" s="278"/>
+      <c r="W2" s="278"/>
+      <c r="X2" s="278"/>
+      <c r="Y2" s="278"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="259" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="269"/>
-      <c r="AC2" s="270" t="str">
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="271"/>
-      <c r="AE2" s="271"/>
-      <c r="AF2" s="272"/>
-      <c r="AG2" s="255" t="str">
+      <c r="AD2" s="263"/>
+      <c r="AE2" s="263"/>
+      <c r="AF2" s="264"/>
+      <c r="AG2" s="256" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="256"/>
-      <c r="AI2" s="257"/>
+      <c r="AH2" s="257"/>
+      <c r="AI2" s="258"/>
       <c r="AN2" s="17"/>
       <c r="AO2" s="17"/>
       <c r="AP2" s="17"/>
     </row>
     <row r="3" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="267" t="s">
+      <c r="A3" s="259" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="268"/>
-      <c r="C3" s="268"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="221" t="str">
+      <c r="B3" s="260"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="279"/>
-      <c r="P3" s="280"/>
-      <c r="Q3" s="280"/>
-      <c r="R3" s="281"/>
-      <c r="S3" s="288"/>
-      <c r="T3" s="289"/>
-      <c r="U3" s="289"/>
-      <c r="V3" s="289"/>
-      <c r="W3" s="289"/>
-      <c r="X3" s="289"/>
-      <c r="Y3" s="289"/>
-      <c r="Z3" s="290"/>
-      <c r="AA3" s="267"/>
-      <c r="AB3" s="269"/>
-      <c r="AC3" s="270" t="str">
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="271"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="280"/>
+      <c r="T3" s="281"/>
+      <c r="U3" s="281"/>
+      <c r="V3" s="281"/>
+      <c r="W3" s="281"/>
+      <c r="X3" s="281"/>
+      <c r="Y3" s="281"/>
+      <c r="Z3" s="282"/>
+      <c r="AA3" s="259"/>
+      <c r="AB3" s="261"/>
+      <c r="AC3" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="271"/>
-      <c r="AE3" s="271"/>
-      <c r="AF3" s="272"/>
-      <c r="AG3" s="255" t="str">
+      <c r="AD3" s="263"/>
+      <c r="AE3" s="263"/>
+      <c r="AF3" s="264"/>
+      <c r="AG3" s="256" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="256"/>
-      <c r="AI3" s="257"/>
+      <c r="AH3" s="257"/>
+      <c r="AI3" s="258"/>
       <c r="AN3" s="17"/>
       <c r="AO3" s="17"/>
       <c r="AP3" s="17"/>
@@ -32022,70 +32041,70 @@
       <c r="C14" s="36"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="D15" s="258" t="s">
+      <c r="D15" s="283" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="259"/>
-      <c r="F15" s="259"/>
-      <c r="G15" s="259"/>
-      <c r="H15" s="259"/>
-      <c r="I15" s="259"/>
-      <c r="J15" s="260"/>
-      <c r="K15" s="258" t="s">
+      <c r="E15" s="284"/>
+      <c r="F15" s="284"/>
+      <c r="G15" s="284"/>
+      <c r="H15" s="284"/>
+      <c r="I15" s="284"/>
+      <c r="J15" s="285"/>
+      <c r="K15" s="283" t="s">
         <v>55</v>
       </c>
-      <c r="L15" s="259"/>
-      <c r="M15" s="259"/>
-      <c r="N15" s="259"/>
-      <c r="O15" s="259"/>
-      <c r="P15" s="259"/>
-      <c r="Q15" s="259"/>
-      <c r="R15" s="259"/>
-      <c r="S15" s="259"/>
-      <c r="T15" s="259"/>
-      <c r="U15" s="259"/>
-      <c r="V15" s="259"/>
-      <c r="W15" s="259"/>
-      <c r="X15" s="259"/>
-      <c r="Y15" s="259"/>
-      <c r="Z15" s="259"/>
-      <c r="AA15" s="259"/>
-      <c r="AB15" s="259"/>
-      <c r="AC15" s="259"/>
-      <c r="AD15" s="260"/>
+      <c r="L15" s="284"/>
+      <c r="M15" s="284"/>
+      <c r="N15" s="284"/>
+      <c r="O15" s="284"/>
+      <c r="P15" s="284"/>
+      <c r="Q15" s="284"/>
+      <c r="R15" s="284"/>
+      <c r="S15" s="284"/>
+      <c r="T15" s="284"/>
+      <c r="U15" s="284"/>
+      <c r="V15" s="284"/>
+      <c r="W15" s="284"/>
+      <c r="X15" s="284"/>
+      <c r="Y15" s="284"/>
+      <c r="Z15" s="284"/>
+      <c r="AA15" s="284"/>
+      <c r="AB15" s="284"/>
+      <c r="AC15" s="284"/>
+      <c r="AD15" s="285"/>
     </row>
     <row r="16" spans="1:42" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="264" t="s">
+      <c r="D16" s="289" t="s">
         <v>269</v>
       </c>
-      <c r="E16" s="265"/>
-      <c r="F16" s="265"/>
-      <c r="G16" s="265"/>
-      <c r="H16" s="265"/>
-      <c r="I16" s="265"/>
-      <c r="J16" s="266"/>
-      <c r="K16" s="261" t="s">
+      <c r="E16" s="290"/>
+      <c r="F16" s="290"/>
+      <c r="G16" s="290"/>
+      <c r="H16" s="290"/>
+      <c r="I16" s="290"/>
+      <c r="J16" s="291"/>
+      <c r="K16" s="286" t="s">
         <v>73</v>
       </c>
-      <c r="L16" s="262"/>
-      <c r="M16" s="262"/>
-      <c r="N16" s="262"/>
-      <c r="O16" s="262"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="262"/>
-      <c r="R16" s="262"/>
-      <c r="S16" s="262"/>
-      <c r="T16" s="262"/>
-      <c r="U16" s="262"/>
-      <c r="V16" s="262"/>
-      <c r="W16" s="262"/>
-      <c r="X16" s="262"/>
-      <c r="Y16" s="262"/>
-      <c r="Z16" s="262"/>
-      <c r="AA16" s="262"/>
-      <c r="AB16" s="262"/>
-      <c r="AC16" s="262"/>
-      <c r="AD16" s="263"/>
+      <c r="L16" s="287"/>
+      <c r="M16" s="287"/>
+      <c r="N16" s="287"/>
+      <c r="O16" s="287"/>
+      <c r="P16" s="287"/>
+      <c r="Q16" s="287"/>
+      <c r="R16" s="287"/>
+      <c r="S16" s="287"/>
+      <c r="T16" s="287"/>
+      <c r="U16" s="287"/>
+      <c r="V16" s="287"/>
+      <c r="W16" s="287"/>
+      <c r="X16" s="287"/>
+      <c r="Y16" s="287"/>
+      <c r="Z16" s="287"/>
+      <c r="AA16" s="287"/>
+      <c r="AB16" s="287"/>
+      <c r="AC16" s="287"/>
+      <c r="AD16" s="288"/>
     </row>
     <row r="19" spans="3:21" s="156" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="166" t="s">
@@ -32624,6 +32643,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="K15:AD15"/>
+    <mergeCell ref="K16:AD16"/>
+    <mergeCell ref="D15:J15"/>
+    <mergeCell ref="D16:J16"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
@@ -32640,11 +32664,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="K15:AD15"/>
-    <mergeCell ref="K16:AD16"/>
-    <mergeCell ref="D15:J15"/>
-    <mergeCell ref="D16:J16"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <hyperlinks>
@@ -32690,163 +32709,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="259" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="269"/>
-      <c r="E1" s="221" t="str">
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="273" t="s">
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="274"/>
-      <c r="Q1" s="274"/>
-      <c r="R1" s="275"/>
-      <c r="S1" s="282" t="str">
+      <c r="P1" s="266"/>
+      <c r="Q1" s="266"/>
+      <c r="R1" s="267"/>
+      <c r="S1" s="274" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="283"/>
-      <c r="U1" s="283"/>
-      <c r="V1" s="283"/>
-      <c r="W1" s="283"/>
-      <c r="X1" s="283"/>
-      <c r="Y1" s="283"/>
-      <c r="Z1" s="284"/>
-      <c r="AA1" s="267" t="s">
+      <c r="T1" s="275"/>
+      <c r="U1" s="275"/>
+      <c r="V1" s="275"/>
+      <c r="W1" s="275"/>
+      <c r="X1" s="275"/>
+      <c r="Y1" s="275"/>
+      <c r="Z1" s="276"/>
+      <c r="AA1" s="259" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="269"/>
-      <c r="AC1" s="270" t="str">
+      <c r="AB1" s="261"/>
+      <c r="AC1" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="271"/>
-      <c r="AE1" s="271"/>
-      <c r="AF1" s="272"/>
-      <c r="AG1" s="291">
+      <c r="AD1" s="263"/>
+      <c r="AE1" s="263"/>
+      <c r="AF1" s="264"/>
+      <c r="AG1" s="308">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>45565</v>
       </c>
-      <c r="AH1" s="292"/>
-      <c r="AI1" s="293"/>
+      <c r="AH1" s="309"/>
+      <c r="AI1" s="310"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="259" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="269"/>
-      <c r="E2" s="221" t="str">
+      <c r="B2" s="260"/>
+      <c r="C2" s="260"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="277"/>
-      <c r="Q2" s="277"/>
-      <c r="R2" s="278"/>
-      <c r="S2" s="285"/>
-      <c r="T2" s="286"/>
-      <c r="U2" s="286"/>
-      <c r="V2" s="286"/>
-      <c r="W2" s="286"/>
-      <c r="X2" s="286"/>
-      <c r="Y2" s="286"/>
-      <c r="Z2" s="287"/>
-      <c r="AA2" s="267" t="s">
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="269"/>
+      <c r="Q2" s="269"/>
+      <c r="R2" s="270"/>
+      <c r="S2" s="277"/>
+      <c r="T2" s="278"/>
+      <c r="U2" s="278"/>
+      <c r="V2" s="278"/>
+      <c r="W2" s="278"/>
+      <c r="X2" s="278"/>
+      <c r="Y2" s="278"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="259" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="269"/>
-      <c r="AC2" s="270" t="str">
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="271"/>
-      <c r="AE2" s="271"/>
-      <c r="AF2" s="272"/>
-      <c r="AG2" s="291" t="str">
+      <c r="AD2" s="263"/>
+      <c r="AE2" s="263"/>
+      <c r="AF2" s="264"/>
+      <c r="AG2" s="308" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="292"/>
-      <c r="AI2" s="293"/>
+      <c r="AH2" s="309"/>
+      <c r="AI2" s="310"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="267" t="s">
+      <c r="A3" s="259" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="268"/>
-      <c r="C3" s="268"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="221" t="str">
+      <c r="B3" s="260"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="279"/>
-      <c r="P3" s="280"/>
-      <c r="Q3" s="280"/>
-      <c r="R3" s="281"/>
-      <c r="S3" s="288"/>
-      <c r="T3" s="289"/>
-      <c r="U3" s="289"/>
-      <c r="V3" s="289"/>
-      <c r="W3" s="289"/>
-      <c r="X3" s="289"/>
-      <c r="Y3" s="289"/>
-      <c r="Z3" s="290"/>
-      <c r="AA3" s="267"/>
-      <c r="AB3" s="269"/>
-      <c r="AC3" s="270" t="str">
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="271"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="280"/>
+      <c r="T3" s="281"/>
+      <c r="U3" s="281"/>
+      <c r="V3" s="281"/>
+      <c r="W3" s="281"/>
+      <c r="X3" s="281"/>
+      <c r="Y3" s="281"/>
+      <c r="Z3" s="282"/>
+      <c r="AA3" s="259"/>
+      <c r="AB3" s="261"/>
+      <c r="AC3" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="271"/>
-      <c r="AE3" s="271"/>
-      <c r="AF3" s="272"/>
-      <c r="AG3" s="291" t="str">
+      <c r="AD3" s="263"/>
+      <c r="AE3" s="263"/>
+      <c r="AF3" s="264"/>
+      <c r="AG3" s="308" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="292"/>
-      <c r="AI3" s="293"/>
+      <c r="AH3" s="309"/>
+      <c r="AI3" s="310"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -32962,12 +32981,12 @@
       <c r="V20" s="30"/>
     </row>
     <row r="21" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="F21" s="294" t="s">
+      <c r="F21" s="292" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="295"/>
-      <c r="H21" s="295"/>
-      <c r="I21" s="296"/>
+      <c r="G21" s="293"/>
+      <c r="H21" s="293"/>
+      <c r="I21" s="294"/>
       <c r="J21" s="58" t="s">
         <v>26</v>
       </c>
@@ -34380,17 +34399,17 @@
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="30"/>
-      <c r="G63" s="307" t="s">
+      <c r="G63" s="305" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="308"/>
-      <c r="I63" s="308"/>
-      <c r="J63" s="309"/>
-      <c r="K63" s="258" t="s">
+      <c r="H63" s="306"/>
+      <c r="I63" s="306"/>
+      <c r="J63" s="307"/>
+      <c r="K63" s="283" t="s">
         <v>69</v>
       </c>
-      <c r="L63" s="259"/>
-      <c r="M63" s="260"/>
+      <c r="L63" s="284"/>
+      <c r="M63" s="285"/>
       <c r="N63" s="58" t="s">
         <v>195</v>
       </c>
@@ -34432,17 +34451,17 @@
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
       <c r="F64" s="29"/>
-      <c r="G64" s="297" t="s">
+      <c r="G64" s="295" t="s">
         <v>560</v>
       </c>
-      <c r="H64" s="298"/>
-      <c r="I64" s="298"/>
-      <c r="J64" s="299"/>
-      <c r="K64" s="297" t="s">
+      <c r="H64" s="296"/>
+      <c r="I64" s="296"/>
+      <c r="J64" s="297"/>
+      <c r="K64" s="295" t="s">
         <v>561</v>
       </c>
-      <c r="L64" s="298"/>
-      <c r="M64" s="299"/>
+      <c r="L64" s="296"/>
+      <c r="M64" s="297"/>
       <c r="N64" s="64" t="s">
         <v>391</v>
       </c>
@@ -34484,13 +34503,13 @@
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="29"/>
-      <c r="G65" s="300"/>
-      <c r="H65" s="301"/>
-      <c r="I65" s="301"/>
-      <c r="J65" s="302"/>
-      <c r="K65" s="306"/>
-      <c r="L65" s="301"/>
-      <c r="M65" s="302"/>
+      <c r="G65" s="298"/>
+      <c r="H65" s="299"/>
+      <c r="I65" s="299"/>
+      <c r="J65" s="300"/>
+      <c r="K65" s="304"/>
+      <c r="L65" s="299"/>
+      <c r="M65" s="300"/>
       <c r="N65" s="54" t="s">
         <v>392</v>
       </c>
@@ -34532,13 +34551,13 @@
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
       <c r="F66" s="29"/>
-      <c r="G66" s="300"/>
-      <c r="H66" s="301"/>
-      <c r="I66" s="301"/>
-      <c r="J66" s="302"/>
-      <c r="K66" s="300"/>
-      <c r="L66" s="301"/>
-      <c r="M66" s="302"/>
+      <c r="G66" s="298"/>
+      <c r="H66" s="299"/>
+      <c r="I66" s="299"/>
+      <c r="J66" s="300"/>
+      <c r="K66" s="298"/>
+      <c r="L66" s="299"/>
+      <c r="M66" s="300"/>
       <c r="N66" s="54" t="s">
         <v>385</v>
       </c>
@@ -34580,13 +34599,13 @@
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
       <c r="F67" s="29"/>
-      <c r="G67" s="300"/>
-      <c r="H67" s="301"/>
-      <c r="I67" s="301"/>
-      <c r="J67" s="302"/>
-      <c r="K67" s="300"/>
-      <c r="L67" s="301"/>
-      <c r="M67" s="302"/>
+      <c r="G67" s="298"/>
+      <c r="H67" s="299"/>
+      <c r="I67" s="299"/>
+      <c r="J67" s="300"/>
+      <c r="K67" s="298"/>
+      <c r="L67" s="299"/>
+      <c r="M67" s="300"/>
       <c r="N67" s="54" t="s">
         <v>626</v>
       </c>
@@ -34628,13 +34647,13 @@
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68"/>
-      <c r="G68" s="303"/>
-      <c r="H68" s="304"/>
-      <c r="I68" s="304"/>
-      <c r="J68" s="305"/>
-      <c r="K68" s="303"/>
-      <c r="L68" s="304"/>
-      <c r="M68" s="305"/>
+      <c r="G68" s="301"/>
+      <c r="H68" s="302"/>
+      <c r="I68" s="302"/>
+      <c r="J68" s="303"/>
+      <c r="K68" s="301"/>
+      <c r="L68" s="302"/>
+      <c r="M68" s="303"/>
       <c r="N68" s="73"/>
       <c r="O68" s="74"/>
       <c r="P68" s="74"/>
@@ -35019,12 +35038,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="G64:J68"/>
-    <mergeCell ref="K64:M68"/>
-    <mergeCell ref="G63:J63"/>
-    <mergeCell ref="K63:M63"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
@@ -35041,6 +35054,12 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="G64:J68"/>
+    <mergeCell ref="K64:M68"/>
+    <mergeCell ref="G63:J63"/>
+    <mergeCell ref="K63:M63"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -35070,163 +35089,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="259" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="269"/>
-      <c r="E1" s="221" t="str">
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="310" t="s">
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="311" t="s">
         <v>95</v>
       </c>
-      <c r="P1" s="274"/>
-      <c r="Q1" s="274"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="312" t="str">
+      <c r="P1" s="266"/>
+      <c r="Q1" s="266"/>
+      <c r="R1" s="312"/>
+      <c r="S1" s="313" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="283"/>
-      <c r="U1" s="283"/>
-      <c r="V1" s="283"/>
-      <c r="W1" s="283"/>
-      <c r="X1" s="283"/>
-      <c r="Y1" s="283"/>
-      <c r="Z1" s="313"/>
-      <c r="AA1" s="267" t="s">
+      <c r="T1" s="275"/>
+      <c r="U1" s="275"/>
+      <c r="V1" s="275"/>
+      <c r="W1" s="275"/>
+      <c r="X1" s="275"/>
+      <c r="Y1" s="275"/>
+      <c r="Z1" s="314"/>
+      <c r="AA1" s="259" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="269"/>
-      <c r="AC1" s="270" t="str">
+      <c r="AB1" s="261"/>
+      <c r="AC1" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="271"/>
-      <c r="AE1" s="271"/>
-      <c r="AF1" s="272"/>
-      <c r="AG1" s="291">
+      <c r="AD1" s="263"/>
+      <c r="AE1" s="263"/>
+      <c r="AF1" s="264"/>
+      <c r="AG1" s="308">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>45565</v>
       </c>
-      <c r="AH1" s="292"/>
-      <c r="AI1" s="293"/>
+      <c r="AH1" s="309"/>
+      <c r="AI1" s="310"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="259" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="269"/>
-      <c r="E2" s="221" t="str">
+      <c r="B2" s="260"/>
+      <c r="C2" s="260"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="277"/>
-      <c r="Q2" s="277"/>
-      <c r="R2" s="278"/>
-      <c r="S2" s="285"/>
-      <c r="T2" s="286"/>
-      <c r="U2" s="286"/>
-      <c r="V2" s="286"/>
-      <c r="W2" s="286"/>
-      <c r="X2" s="286"/>
-      <c r="Y2" s="286"/>
-      <c r="Z2" s="287"/>
-      <c r="AA2" s="267" t="s">
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="269"/>
+      <c r="Q2" s="269"/>
+      <c r="R2" s="270"/>
+      <c r="S2" s="277"/>
+      <c r="T2" s="278"/>
+      <c r="U2" s="278"/>
+      <c r="V2" s="278"/>
+      <c r="W2" s="278"/>
+      <c r="X2" s="278"/>
+      <c r="Y2" s="278"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="259" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="269"/>
-      <c r="AC2" s="270" t="str">
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="271"/>
-      <c r="AE2" s="271"/>
-      <c r="AF2" s="272"/>
-      <c r="AG2" s="291" t="str">
+      <c r="AD2" s="263"/>
+      <c r="AE2" s="263"/>
+      <c r="AF2" s="264"/>
+      <c r="AG2" s="308" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="292"/>
-      <c r="AI2" s="293"/>
+      <c r="AH2" s="309"/>
+      <c r="AI2" s="310"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="267" t="s">
+      <c r="A3" s="259" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="268"/>
-      <c r="C3" s="268"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="221" t="str">
+      <c r="B3" s="260"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="279"/>
-      <c r="P3" s="280"/>
-      <c r="Q3" s="280"/>
-      <c r="R3" s="281"/>
-      <c r="S3" s="288"/>
-      <c r="T3" s="289"/>
-      <c r="U3" s="289"/>
-      <c r="V3" s="289"/>
-      <c r="W3" s="289"/>
-      <c r="X3" s="289"/>
-      <c r="Y3" s="289"/>
-      <c r="Z3" s="290"/>
-      <c r="AA3" s="267"/>
-      <c r="AB3" s="269"/>
-      <c r="AC3" s="270" t="str">
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="271"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="280"/>
+      <c r="T3" s="281"/>
+      <c r="U3" s="281"/>
+      <c r="V3" s="281"/>
+      <c r="W3" s="281"/>
+      <c r="X3" s="281"/>
+      <c r="Y3" s="281"/>
+      <c r="Z3" s="282"/>
+      <c r="AA3" s="259"/>
+      <c r="AB3" s="261"/>
+      <c r="AC3" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="271"/>
-      <c r="AE3" s="271"/>
-      <c r="AF3" s="272"/>
-      <c r="AG3" s="291" t="str">
+      <c r="AD3" s="263"/>
+      <c r="AE3" s="263"/>
+      <c r="AF3" s="264"/>
+      <c r="AG3" s="308" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="292"/>
-      <c r="AI3" s="293"/>
+      <c r="AH3" s="309"/>
+      <c r="AI3" s="310"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -35260,41 +35279,41 @@
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="E14" s="307" t="s">
+      <c r="E14" s="305" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="308"/>
-      <c r="G14" s="308"/>
-      <c r="H14" s="308"/>
-      <c r="I14" s="308"/>
-      <c r="J14" s="309"/>
-      <c r="K14" s="307" t="s">
+      <c r="F14" s="306"/>
+      <c r="G14" s="306"/>
+      <c r="H14" s="306"/>
+      <c r="I14" s="306"/>
+      <c r="J14" s="307"/>
+      <c r="K14" s="305" t="s">
         <v>101</v>
       </c>
-      <c r="L14" s="308"/>
-      <c r="M14" s="308"/>
-      <c r="N14" s="308"/>
-      <c r="O14" s="308"/>
-      <c r="P14" s="308"/>
-      <c r="Q14" s="308"/>
-      <c r="R14" s="308"/>
-      <c r="S14" s="309"/>
-      <c r="T14" s="307" t="s">
+      <c r="L14" s="306"/>
+      <c r="M14" s="306"/>
+      <c r="N14" s="306"/>
+      <c r="O14" s="306"/>
+      <c r="P14" s="306"/>
+      <c r="Q14" s="306"/>
+      <c r="R14" s="306"/>
+      <c r="S14" s="307"/>
+      <c r="T14" s="305" t="s">
         <v>93</v>
       </c>
-      <c r="U14" s="308"/>
-      <c r="V14" s="308"/>
-      <c r="W14" s="308"/>
-      <c r="X14" s="308"/>
-      <c r="Y14" s="308"/>
-      <c r="Z14" s="308"/>
-      <c r="AA14" s="308"/>
-      <c r="AB14" s="308"/>
-      <c r="AC14" s="308"/>
-      <c r="AD14" s="308"/>
-      <c r="AE14" s="308"/>
-      <c r="AF14" s="308"/>
-      <c r="AG14" s="309"/>
+      <c r="U14" s="306"/>
+      <c r="V14" s="306"/>
+      <c r="W14" s="306"/>
+      <c r="X14" s="306"/>
+      <c r="Y14" s="306"/>
+      <c r="Z14" s="306"/>
+      <c r="AA14" s="306"/>
+      <c r="AB14" s="306"/>
+      <c r="AC14" s="306"/>
+      <c r="AD14" s="306"/>
+      <c r="AE14" s="306"/>
+      <c r="AF14" s="306"/>
+      <c r="AG14" s="307"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="E15" s="80" t="s">
@@ -35879,7 +35898,7 @@
     <row r="72" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C72" s="39"/>
       <c r="G72" s="30" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="73" spans="3:7" s="175" customFormat="1" x14ac:dyDescent="0.2">
@@ -35900,8 +35919,8 @@
     </row>
     <row r="76" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C76" s="39"/>
-      <c r="G76" s="175" t="s">
-        <v>715</v>
+      <c r="G76" s="183" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="77" spans="3:7" s="175" customFormat="1" x14ac:dyDescent="0.2">
@@ -36650,7 +36669,7 @@
       <c r="C166" s="39"/>
       <c r="E166" s="179"/>
       <c r="F166" s="179" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="167" spans="3:29" s="175" customFormat="1" x14ac:dyDescent="0.2">
@@ -36658,7 +36677,7 @@
       <c r="E167" s="179"/>
       <c r="F167" s="179"/>
       <c r="G167" s="179" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="168" spans="3:29" s="175" customFormat="1" x14ac:dyDescent="0.2">
@@ -36688,7 +36707,7 @@
     <row r="172" spans="3:29" s="175" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C172" s="39"/>
       <c r="G172" s="179" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="173" spans="3:29" x14ac:dyDescent="0.2">
@@ -36989,7 +37008,7 @@
     <row r="207" spans="3:7" s="175" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C207" s="39"/>
       <c r="G207" s="179" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="208" spans="3:7" x14ac:dyDescent="0.2">
@@ -37913,12 +37932,12 @@
     </row>
     <row r="340" spans="5:34" x14ac:dyDescent="0.2">
       <c r="E340" s="175" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="341" spans="5:34" x14ac:dyDescent="0.2">
       <c r="E341" s="175" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="343" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -37926,11 +37945,6 @@
     <row r="346" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="K14:S14"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -37946,6 +37960,11 @@
     <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="E14:J14"/>
+    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AG1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>
@@ -37987,157 +38006,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="259" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="269"/>
-      <c r="E1" s="221" t="str">
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="273" t="s">
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="265" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="274"/>
-      <c r="Q1" s="274"/>
-      <c r="R1" s="275"/>
-      <c r="S1" s="282" t="str">
+      <c r="P1" s="266"/>
+      <c r="Q1" s="266"/>
+      <c r="R1" s="267"/>
+      <c r="S1" s="274" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="283"/>
-      <c r="U1" s="283"/>
-      <c r="V1" s="283"/>
-      <c r="W1" s="283"/>
-      <c r="X1" s="283"/>
-      <c r="Y1" s="283"/>
-      <c r="Z1" s="284"/>
-      <c r="AA1" s="267" t="s">
+      <c r="T1" s="275"/>
+      <c r="U1" s="275"/>
+      <c r="V1" s="275"/>
+      <c r="W1" s="275"/>
+      <c r="X1" s="275"/>
+      <c r="Y1" s="275"/>
+      <c r="Z1" s="276"/>
+      <c r="AA1" s="259" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="269"/>
-      <c r="AC1" s="270" t="str">
+      <c r="AB1" s="261"/>
+      <c r="AC1" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="271"/>
-      <c r="AE1" s="271"/>
-      <c r="AF1" s="272"/>
-      <c r="AG1" s="291">
+      <c r="AD1" s="263"/>
+      <c r="AE1" s="263"/>
+      <c r="AF1" s="264"/>
+      <c r="AG1" s="308">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>45565</v>
       </c>
-      <c r="AH1" s="292"/>
-      <c r="AI1" s="293"/>
+      <c r="AH1" s="309"/>
+      <c r="AI1" s="310"/>
     </row>
     <row r="2" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="259" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="269"/>
-      <c r="E2" s="221" t="str">
+      <c r="B2" s="260"/>
+      <c r="C2" s="260"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="277"/>
-      <c r="Q2" s="277"/>
-      <c r="R2" s="278"/>
-      <c r="S2" s="285"/>
-      <c r="T2" s="286"/>
-      <c r="U2" s="286"/>
-      <c r="V2" s="286"/>
-      <c r="W2" s="286"/>
-      <c r="X2" s="286"/>
-      <c r="Y2" s="286"/>
-      <c r="Z2" s="287"/>
-      <c r="AA2" s="267" t="s">
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="269"/>
+      <c r="Q2" s="269"/>
+      <c r="R2" s="270"/>
+      <c r="S2" s="277"/>
+      <c r="T2" s="278"/>
+      <c r="U2" s="278"/>
+      <c r="V2" s="278"/>
+      <c r="W2" s="278"/>
+      <c r="X2" s="278"/>
+      <c r="Y2" s="278"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="259" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="269"/>
-      <c r="AC2" s="270" t="str">
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="271"/>
-      <c r="AE2" s="271"/>
-      <c r="AF2" s="272"/>
-      <c r="AG2" s="291" t="str">
+      <c r="AD2" s="263"/>
+      <c r="AE2" s="263"/>
+      <c r="AF2" s="264"/>
+      <c r="AG2" s="308" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="292"/>
-      <c r="AI2" s="293"/>
+      <c r="AH2" s="309"/>
+      <c r="AI2" s="310"/>
     </row>
     <row r="3" spans="1:35" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="267" t="s">
+      <c r="A3" s="259" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="268"/>
-      <c r="C3" s="268"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="221" t="str">
+      <c r="B3" s="260"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="279"/>
-      <c r="P3" s="280"/>
-      <c r="Q3" s="280"/>
-      <c r="R3" s="281"/>
-      <c r="S3" s="288"/>
-      <c r="T3" s="289"/>
-      <c r="U3" s="289"/>
-      <c r="V3" s="289"/>
-      <c r="W3" s="289"/>
-      <c r="X3" s="289"/>
-      <c r="Y3" s="289"/>
-      <c r="Z3" s="290"/>
-      <c r="AA3" s="267"/>
-      <c r="AB3" s="269"/>
-      <c r="AC3" s="270" t="str">
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="271"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="280"/>
+      <c r="T3" s="281"/>
+      <c r="U3" s="281"/>
+      <c r="V3" s="281"/>
+      <c r="W3" s="281"/>
+      <c r="X3" s="281"/>
+      <c r="Y3" s="281"/>
+      <c r="Z3" s="282"/>
+      <c r="AA3" s="259"/>
+      <c r="AB3" s="261"/>
+      <c r="AC3" s="262" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="271"/>
-      <c r="AE3" s="271"/>
-      <c r="AF3" s="272"/>
-      <c r="AG3" s="291" t="str">
+      <c r="AD3" s="263"/>
+      <c r="AE3" s="263"/>
+      <c r="AF3" s="264"/>
+      <c r="AG3" s="308" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="292"/>
-      <c r="AI3" s="293"/>
+      <c r="AH3" s="309"/>
+      <c r="AI3" s="310"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B5" s="32" t="s">
@@ -39241,12 +39260,12 @@
     <row r="74" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A74" s="30"/>
       <c r="E74" s="30"/>
-      <c r="F74" s="258" t="s">
+      <c r="F74" s="283" t="s">
         <v>50</v>
       </c>
-      <c r="G74" s="259"/>
-      <c r="H74" s="259"/>
-      <c r="I74" s="260"/>
+      <c r="G74" s="284"/>
+      <c r="H74" s="284"/>
+      <c r="I74" s="285"/>
       <c r="J74" s="58" t="s">
         <v>187</v>
       </c>
@@ -39275,12 +39294,12 @@
     <row r="75" spans="1:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="30"/>
       <c r="E75" s="30"/>
-      <c r="F75" s="314" t="s">
+      <c r="F75" s="317" t="s">
         <v>226</v>
       </c>
-      <c r="G75" s="315"/>
-      <c r="H75" s="315"/>
-      <c r="I75" s="316"/>
+      <c r="G75" s="318"/>
+      <c r="H75" s="318"/>
+      <c r="I75" s="319"/>
       <c r="J75" s="83" t="s">
         <v>234</v>
       </c>
@@ -39310,12 +39329,12 @@
       <c r="A76" s="30"/>
       <c r="C76" s="30"/>
       <c r="E76" s="30"/>
-      <c r="F76" s="317" t="s">
+      <c r="F76" s="324" t="s">
         <v>325</v>
       </c>
-      <c r="G76" s="318"/>
-      <c r="H76" s="318"/>
-      <c r="I76" s="319"/>
+      <c r="G76" s="325"/>
+      <c r="H76" s="325"/>
+      <c r="I76" s="326"/>
       <c r="J76" s="72" t="s">
         <v>188</v>
       </c>
@@ -39345,10 +39364,10 @@
       <c r="A77" s="30"/>
       <c r="C77" s="30"/>
       <c r="E77" s="30"/>
-      <c r="F77" s="320"/>
-      <c r="G77" s="321"/>
-      <c r="H77" s="321"/>
-      <c r="I77" s="322"/>
+      <c r="F77" s="327"/>
+      <c r="G77" s="328"/>
+      <c r="H77" s="328"/>
+      <c r="I77" s="329"/>
       <c r="J77" s="73"/>
       <c r="K77" s="74"/>
       <c r="L77" s="74"/>
@@ -39373,12 +39392,12 @@
     <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A78" s="30"/>
       <c r="E78" s="30"/>
-      <c r="F78" s="314" t="s">
+      <c r="F78" s="317" t="s">
         <v>227</v>
       </c>
-      <c r="G78" s="315"/>
-      <c r="H78" s="315"/>
-      <c r="I78" s="316"/>
+      <c r="G78" s="318"/>
+      <c r="H78" s="318"/>
+      <c r="I78" s="319"/>
       <c r="J78" s="80" t="s">
         <v>189</v>
       </c>
@@ -39407,12 +39426,12 @@
     <row r="79" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A79" s="30"/>
       <c r="E79" s="30"/>
-      <c r="F79" s="314" t="s">
+      <c r="F79" s="317" t="s">
         <v>225</v>
       </c>
-      <c r="G79" s="315"/>
-      <c r="H79" s="315"/>
-      <c r="I79" s="316"/>
+      <c r="G79" s="318"/>
+      <c r="H79" s="318"/>
+      <c r="I79" s="319"/>
       <c r="J79" s="83" t="s">
         <v>192</v>
       </c>
@@ -39442,12 +39461,12 @@
     <row r="80" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A80" s="30"/>
       <c r="E80" s="30"/>
-      <c r="F80" s="314" t="s">
+      <c r="F80" s="317" t="s">
         <v>224</v>
       </c>
-      <c r="G80" s="315"/>
-      <c r="H80" s="315"/>
-      <c r="I80" s="316"/>
+      <c r="G80" s="318"/>
+      <c r="H80" s="318"/>
+      <c r="I80" s="319"/>
       <c r="J80" s="80" t="s">
         <v>190</v>
       </c>
@@ -39586,7 +39605,7 @@
       <c r="AG137" s="51"/>
     </row>
     <row r="138" spans="5:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F138" s="325">
+      <c r="F138" s="320">
         <v>1</v>
       </c>
       <c r="G138" s="64" t="s">
@@ -39622,7 +39641,7 @@
       <c r="AG138" s="51"/>
     </row>
     <row r="139" spans="5:33" x14ac:dyDescent="0.2">
-      <c r="F139" s="326"/>
+      <c r="F139" s="321"/>
       <c r="G139" s="54"/>
       <c r="H139" s="30"/>
       <c r="I139" s="30"/>
@@ -39654,7 +39673,7 @@
       <c r="AG139" s="51"/>
     </row>
     <row r="140" spans="5:33" x14ac:dyDescent="0.2">
-      <c r="F140" s="326"/>
+      <c r="F140" s="321"/>
       <c r="G140" s="54"/>
       <c r="H140" s="30"/>
       <c r="I140" s="30"/>
@@ -39686,7 +39705,7 @@
       <c r="AG140" s="51"/>
     </row>
     <row r="141" spans="5:33" x14ac:dyDescent="0.2">
-      <c r="F141" s="326"/>
+      <c r="F141" s="321"/>
       <c r="G141" s="54"/>
       <c r="H141" s="30"/>
       <c r="I141" s="30"/>
@@ -39718,7 +39737,7 @@
       <c r="AG141" s="51"/>
     </row>
     <row r="142" spans="5:33" x14ac:dyDescent="0.2">
-      <c r="F142" s="326"/>
+      <c r="F142" s="321"/>
       <c r="G142" s="54"/>
       <c r="H142" s="30"/>
       <c r="I142" s="30"/>
@@ -39750,7 +39769,7 @@
       <c r="AG142" s="51"/>
     </row>
     <row r="143" spans="5:33" x14ac:dyDescent="0.2">
-      <c r="F143" s="326"/>
+      <c r="F143" s="321"/>
       <c r="G143" s="54"/>
       <c r="H143" s="30"/>
       <c r="I143" s="30"/>
@@ -39782,7 +39801,7 @@
       <c r="AG143" s="51"/>
     </row>
     <row r="144" spans="5:33" x14ac:dyDescent="0.2">
-      <c r="F144" s="326"/>
+      <c r="F144" s="321"/>
       <c r="G144" s="54"/>
       <c r="H144" s="30"/>
       <c r="I144" s="30"/>
@@ -39814,7 +39833,7 @@
       <c r="AG144" s="51"/>
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="F145" s="327"/>
+      <c r="F145" s="322"/>
       <c r="G145" s="54"/>
       <c r="H145" s="30"/>
       <c r="I145" s="30"/>
@@ -39912,7 +39931,7 @@
       <c r="AG147" s="17"/>
     </row>
     <row r="148" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F148" s="325">
+      <c r="F148" s="320">
         <v>3</v>
       </c>
       <c r="G148" s="54" t="s">
@@ -39948,7 +39967,7 @@
       <c r="AG148" s="51"/>
     </row>
     <row r="149" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F149" s="326"/>
+      <c r="F149" s="321"/>
       <c r="G149" s="54"/>
       <c r="H149" s="30"/>
       <c r="I149" s="30"/>
@@ -39980,7 +39999,7 @@
       <c r="AG149" s="51"/>
     </row>
     <row r="150" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F150" s="326"/>
+      <c r="F150" s="321"/>
       <c r="G150" s="54"/>
       <c r="H150" s="30"/>
       <c r="I150" s="30"/>
@@ -40012,7 +40031,7 @@
       <c r="AG150" s="51"/>
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="F151" s="326"/>
+      <c r="F151" s="321"/>
       <c r="G151" s="54"/>
       <c r="H151" s="30"/>
       <c r="I151" s="30"/>
@@ -40044,7 +40063,7 @@
       <c r="AG151" s="51"/>
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="F152" s="326"/>
+      <c r="F152" s="321"/>
       <c r="G152" s="54"/>
       <c r="H152" s="30"/>
       <c r="I152" s="30"/>
@@ -40076,7 +40095,7 @@
       <c r="AG152" s="51"/>
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="F153" s="327"/>
+      <c r="F153" s="322"/>
       <c r="G153" s="54"/>
       <c r="H153" s="30"/>
       <c r="I153" s="30"/>
@@ -40108,7 +40127,7 @@
       <c r="AG153" s="51"/>
     </row>
     <row r="154" spans="1:33" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F154" s="328">
+      <c r="F154" s="323">
         <v>4</v>
       </c>
       <c r="G154" s="64" t="s">
@@ -40144,7 +40163,7 @@
       <c r="AG154" s="51"/>
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="F155" s="328"/>
+      <c r="F155" s="323"/>
       <c r="G155" s="73"/>
       <c r="H155" s="74"/>
       <c r="I155" s="74"/>
@@ -40617,7 +40636,7 @@
     </row>
     <row r="228" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A228" s="30"/>
-      <c r="F228" s="323"/>
+      <c r="F228" s="315"/>
       <c r="G228" s="83" t="s">
         <v>236</v>
       </c>
@@ -40654,7 +40673,7 @@
       <c r="AD228" s="113"/>
     </row>
     <row r="229" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="F229" s="323"/>
+      <c r="F229" s="315"/>
       <c r="G229" s="83" t="s">
         <v>276</v>
       </c>
@@ -40691,7 +40710,7 @@
       <c r="AD229" s="113"/>
     </row>
     <row r="230" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="F230" s="324"/>
+      <c r="F230" s="316"/>
       <c r="G230" s="84" t="s">
         <v>277</v>
       </c>
@@ -41202,21 +41221,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F228:F230"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F138:F145"/>
-    <mergeCell ref="F148:F153"/>
-    <mergeCell ref="F154:F155"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="F74:I74"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="F76:I77"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="AG3:AI3"/>
@@ -41229,6 +41233,21 @@
     <mergeCell ref="S1:Z3"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="F76:I77"/>
+    <mergeCell ref="F228:F230"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F138:F145"/>
+    <mergeCell ref="F148:F153"/>
+    <mergeCell ref="F154:F155"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <printOptions horizontalCentered="1"/>
@@ -41265,163 +41284,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="218" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="221" t="str">
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="273" t="s">
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="265" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="274"/>
-      <c r="Q1" s="274"/>
-      <c r="R1" s="275"/>
-      <c r="S1" s="282" t="str">
+      <c r="P1" s="266"/>
+      <c r="Q1" s="266"/>
+      <c r="R1" s="267"/>
+      <c r="S1" s="274" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>UI標準(画面)</v>
       </c>
-      <c r="T1" s="283"/>
-      <c r="U1" s="283"/>
-      <c r="V1" s="283"/>
-      <c r="W1" s="283"/>
-      <c r="X1" s="283"/>
-      <c r="Y1" s="283"/>
-      <c r="Z1" s="284"/>
-      <c r="AA1" s="190" t="s">
+      <c r="T1" s="275"/>
+      <c r="U1" s="275"/>
+      <c r="V1" s="275"/>
+      <c r="W1" s="275"/>
+      <c r="X1" s="275"/>
+      <c r="Y1" s="275"/>
+      <c r="Z1" s="276"/>
+      <c r="AA1" s="218" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="192"/>
-      <c r="AC1" s="218" t="str">
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="219"/>
-      <c r="AE1" s="219"/>
-      <c r="AF1" s="220"/>
-      <c r="AG1" s="353">
+      <c r="AD1" s="247"/>
+      <c r="AE1" s="247"/>
+      <c r="AF1" s="248"/>
+      <c r="AG1" s="365">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>45565</v>
       </c>
-      <c r="AH1" s="354"/>
-      <c r="AI1" s="355"/>
+      <c r="AH1" s="366"/>
+      <c r="AI1" s="367"/>
       <c r="AN1" s="36"/>
       <c r="AO1" s="36"/>
       <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="218" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="221" t="str">
+      <c r="B2" s="219"/>
+      <c r="C2" s="219"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="277"/>
-      <c r="Q2" s="277"/>
-      <c r="R2" s="278"/>
-      <c r="S2" s="285"/>
-      <c r="T2" s="286"/>
-      <c r="U2" s="286"/>
-      <c r="V2" s="286"/>
-      <c r="W2" s="286"/>
-      <c r="X2" s="286"/>
-      <c r="Y2" s="286"/>
-      <c r="Z2" s="287"/>
-      <c r="AA2" s="190" t="s">
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="269"/>
+      <c r="Q2" s="269"/>
+      <c r="R2" s="270"/>
+      <c r="S2" s="277"/>
+      <c r="T2" s="278"/>
+      <c r="U2" s="278"/>
+      <c r="V2" s="278"/>
+      <c r="W2" s="278"/>
+      <c r="X2" s="278"/>
+      <c r="Y2" s="278"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="218" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="192"/>
-      <c r="AC2" s="218" t="str">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="219"/>
-      <c r="AE2" s="219"/>
-      <c r="AF2" s="220"/>
-      <c r="AG2" s="353" t="str">
+      <c r="AD2" s="247"/>
+      <c r="AE2" s="247"/>
+      <c r="AF2" s="248"/>
+      <c r="AG2" s="365" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v/>
       </c>
-      <c r="AH2" s="354"/>
-      <c r="AI2" s="355"/>
+      <c r="AH2" s="366"/>
+      <c r="AI2" s="367"/>
       <c r="AN2" s="36"/>
       <c r="AO2" s="36"/>
       <c r="AP2" s="36"/>
     </row>
     <row r="3" spans="1:42" s="35" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="190" t="s">
+      <c r="A3" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="191"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="221" t="str">
+      <c r="B3" s="219"/>
+      <c r="C3" s="219"/>
+      <c r="D3" s="220"/>
+      <c r="E3" s="249" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="279"/>
-      <c r="P3" s="280"/>
-      <c r="Q3" s="280"/>
-      <c r="R3" s="281"/>
-      <c r="S3" s="288"/>
-      <c r="T3" s="289"/>
-      <c r="U3" s="289"/>
-      <c r="V3" s="289"/>
-      <c r="W3" s="289"/>
-      <c r="X3" s="289"/>
-      <c r="Y3" s="289"/>
-      <c r="Z3" s="290"/>
-      <c r="AA3" s="190"/>
-      <c r="AB3" s="192"/>
-      <c r="AC3" s="218" t="str">
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="271"/>
+      <c r="P3" s="272"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="273"/>
+      <c r="S3" s="280"/>
+      <c r="T3" s="281"/>
+      <c r="U3" s="281"/>
+      <c r="V3" s="281"/>
+      <c r="W3" s="281"/>
+      <c r="X3" s="281"/>
+      <c r="Y3" s="281"/>
+      <c r="Z3" s="282"/>
+      <c r="AA3" s="218"/>
+      <c r="AB3" s="220"/>
+      <c r="AC3" s="246" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="219"/>
-      <c r="AE3" s="219"/>
-      <c r="AF3" s="220"/>
-      <c r="AG3" s="353" t="str">
+      <c r="AD3" s="247"/>
+      <c r="AE3" s="247"/>
+      <c r="AF3" s="248"/>
+      <c r="AG3" s="365" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="354"/>
-      <c r="AI3" s="355"/>
+      <c r="AH3" s="366"/>
+      <c r="AI3" s="367"/>
       <c r="AN3" s="36"/>
       <c r="AO3" s="36"/>
       <c r="AP3" s="36"/>
@@ -41762,12 +41781,12 @@
     <row r="91" spans="4:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="92" spans="4:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E92" s="179" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="93" spans="4:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E93" s="179" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="94" spans="4:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -41904,510 +41923,510 @@
     </row>
     <row r="150" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="151" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D151" s="258" t="s">
+      <c r="D151" s="283" t="s">
         <v>320</v>
       </c>
-      <c r="E151" s="334"/>
-      <c r="F151" s="334"/>
-      <c r="G151" s="334"/>
-      <c r="H151" s="334"/>
-      <c r="I151" s="334"/>
-      <c r="J151" s="335"/>
-      <c r="K151" s="332" t="s">
+      <c r="E151" s="349"/>
+      <c r="F151" s="349"/>
+      <c r="G151" s="349"/>
+      <c r="H151" s="349"/>
+      <c r="I151" s="349"/>
+      <c r="J151" s="350"/>
+      <c r="K151" s="368" t="s">
         <v>50</v>
       </c>
-      <c r="L151" s="332"/>
-      <c r="M151" s="332"/>
-      <c r="N151" s="332"/>
-      <c r="O151" s="332"/>
-      <c r="P151" s="332"/>
-      <c r="Q151" s="332"/>
-      <c r="R151" s="332"/>
-      <c r="S151" s="332"/>
-      <c r="T151" s="332"/>
-      <c r="U151" s="332"/>
-      <c r="V151" s="332"/>
-      <c r="W151" s="332"/>
-      <c r="X151" s="332"/>
-      <c r="Y151" s="332"/>
-      <c r="Z151" s="332"/>
-      <c r="AA151" s="331" t="s">
+      <c r="L151" s="368"/>
+      <c r="M151" s="368"/>
+      <c r="N151" s="368"/>
+      <c r="O151" s="368"/>
+      <c r="P151" s="368"/>
+      <c r="Q151" s="368"/>
+      <c r="R151" s="368"/>
+      <c r="S151" s="368"/>
+      <c r="T151" s="368"/>
+      <c r="U151" s="368"/>
+      <c r="V151" s="368"/>
+      <c r="W151" s="368"/>
+      <c r="X151" s="368"/>
+      <c r="Y151" s="368"/>
+      <c r="Z151" s="368"/>
+      <c r="AA151" s="376" t="s">
         <v>51</v>
       </c>
-      <c r="AB151" s="332"/>
-      <c r="AC151" s="332"/>
-      <c r="AD151" s="332"/>
-      <c r="AE151" s="332"/>
-      <c r="AF151" s="332"/>
-      <c r="AG151" s="332"/>
-      <c r="AH151" s="332"/>
+      <c r="AB151" s="368"/>
+      <c r="AC151" s="368"/>
+      <c r="AD151" s="368"/>
+      <c r="AE151" s="368"/>
+      <c r="AF151" s="368"/>
+      <c r="AG151" s="368"/>
+      <c r="AH151" s="368"/>
     </row>
     <row r="152" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D152" s="261" t="s">
+      <c r="D152" s="286" t="s">
         <v>52</v>
       </c>
-      <c r="E152" s="262"/>
-      <c r="F152" s="262"/>
-      <c r="G152" s="262"/>
-      <c r="H152" s="262"/>
-      <c r="I152" s="262"/>
-      <c r="J152" s="263"/>
-      <c r="K152" s="352" t="s">
+      <c r="E152" s="287"/>
+      <c r="F152" s="287"/>
+      <c r="G152" s="287"/>
+      <c r="H152" s="287"/>
+      <c r="I152" s="287"/>
+      <c r="J152" s="288"/>
+      <c r="K152" s="364" t="s">
         <v>286</v>
       </c>
-      <c r="L152" s="352"/>
-      <c r="M152" s="352"/>
-      <c r="N152" s="352"/>
-      <c r="O152" s="352"/>
-      <c r="P152" s="352"/>
-      <c r="Q152" s="352"/>
-      <c r="R152" s="352"/>
-      <c r="S152" s="352"/>
-      <c r="T152" s="352"/>
-      <c r="U152" s="352"/>
-      <c r="V152" s="352"/>
-      <c r="W152" s="352"/>
-      <c r="X152" s="352"/>
-      <c r="Y152" s="352"/>
-      <c r="Z152" s="352"/>
-      <c r="AA152" s="329" t="s">
+      <c r="L152" s="364"/>
+      <c r="M152" s="364"/>
+      <c r="N152" s="364"/>
+      <c r="O152" s="364"/>
+      <c r="P152" s="364"/>
+      <c r="Q152" s="364"/>
+      <c r="R152" s="364"/>
+      <c r="S152" s="364"/>
+      <c r="T152" s="364"/>
+      <c r="U152" s="364"/>
+      <c r="V152" s="364"/>
+      <c r="W152" s="364"/>
+      <c r="X152" s="364"/>
+      <c r="Y152" s="364"/>
+      <c r="Z152" s="364"/>
+      <c r="AA152" s="370" t="s">
         <v>74</v>
       </c>
-      <c r="AB152" s="330"/>
-      <c r="AC152" s="330"/>
-      <c r="AD152" s="330"/>
-      <c r="AE152" s="330"/>
-      <c r="AF152" s="330"/>
-      <c r="AG152" s="330"/>
-      <c r="AH152" s="330"/>
+      <c r="AB152" s="371"/>
+      <c r="AC152" s="371"/>
+      <c r="AD152" s="371"/>
+      <c r="AE152" s="371"/>
+      <c r="AF152" s="371"/>
+      <c r="AG152" s="371"/>
+      <c r="AH152" s="371"/>
     </row>
     <row r="153" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D153" s="314" t="s">
+      <c r="D153" s="317" t="s">
         <v>301</v>
       </c>
-      <c r="E153" s="315"/>
-      <c r="F153" s="315"/>
-      <c r="G153" s="315"/>
-      <c r="H153" s="315"/>
-      <c r="I153" s="315"/>
-      <c r="J153" s="316"/>
-      <c r="K153" s="352" t="s">
+      <c r="E153" s="318"/>
+      <c r="F153" s="318"/>
+      <c r="G153" s="318"/>
+      <c r="H153" s="318"/>
+      <c r="I153" s="318"/>
+      <c r="J153" s="319"/>
+      <c r="K153" s="364" t="s">
         <v>287</v>
       </c>
-      <c r="L153" s="352"/>
-      <c r="M153" s="352"/>
-      <c r="N153" s="352"/>
-      <c r="O153" s="352"/>
-      <c r="P153" s="352"/>
-      <c r="Q153" s="352"/>
-      <c r="R153" s="352"/>
-      <c r="S153" s="352"/>
-      <c r="T153" s="352"/>
-      <c r="U153" s="352"/>
-      <c r="V153" s="352"/>
-      <c r="W153" s="352"/>
-      <c r="X153" s="352"/>
-      <c r="Y153" s="352"/>
-      <c r="Z153" s="352"/>
-      <c r="AA153" s="329" t="s">
+      <c r="L153" s="364"/>
+      <c r="M153" s="364"/>
+      <c r="N153" s="364"/>
+      <c r="O153" s="364"/>
+      <c r="P153" s="364"/>
+      <c r="Q153" s="364"/>
+      <c r="R153" s="364"/>
+      <c r="S153" s="364"/>
+      <c r="T153" s="364"/>
+      <c r="U153" s="364"/>
+      <c r="V153" s="364"/>
+      <c r="W153" s="364"/>
+      <c r="X153" s="364"/>
+      <c r="Y153" s="364"/>
+      <c r="Z153" s="364"/>
+      <c r="AA153" s="370" t="s">
         <v>74</v>
       </c>
-      <c r="AB153" s="330"/>
-      <c r="AC153" s="330"/>
-      <c r="AD153" s="330"/>
-      <c r="AE153" s="330"/>
-      <c r="AF153" s="330"/>
-      <c r="AG153" s="330"/>
-      <c r="AH153" s="330"/>
+      <c r="AB153" s="371"/>
+      <c r="AC153" s="371"/>
+      <c r="AD153" s="371"/>
+      <c r="AE153" s="371"/>
+      <c r="AF153" s="371"/>
+      <c r="AG153" s="371"/>
+      <c r="AH153" s="371"/>
     </row>
     <row r="154" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D154" s="340" t="s">
+      <c r="D154" s="380" t="s">
         <v>315</v>
       </c>
-      <c r="E154" s="265"/>
-      <c r="F154" s="265"/>
-      <c r="G154" s="265"/>
-      <c r="H154" s="265"/>
-      <c r="I154" s="265"/>
-      <c r="J154" s="266"/>
-      <c r="K154" s="342" t="s">
+      <c r="E154" s="290"/>
+      <c r="F154" s="290"/>
+      <c r="G154" s="290"/>
+      <c r="H154" s="290"/>
+      <c r="I154" s="290"/>
+      <c r="J154" s="291"/>
+      <c r="K154" s="372" t="s">
         <v>317</v>
       </c>
-      <c r="L154" s="343"/>
-      <c r="M154" s="343"/>
-      <c r="N154" s="343"/>
-      <c r="O154" s="343"/>
-      <c r="P154" s="343"/>
-      <c r="Q154" s="343"/>
-      <c r="R154" s="343"/>
-      <c r="S154" s="343"/>
-      <c r="T154" s="343"/>
-      <c r="U154" s="343"/>
-      <c r="V154" s="343"/>
-      <c r="W154" s="343"/>
-      <c r="X154" s="343"/>
-      <c r="Y154" s="343"/>
-      <c r="Z154" s="344"/>
-      <c r="AA154" s="342" t="s">
+      <c r="L154" s="373"/>
+      <c r="M154" s="373"/>
+      <c r="N154" s="373"/>
+      <c r="O154" s="373"/>
+      <c r="P154" s="373"/>
+      <c r="Q154" s="373"/>
+      <c r="R154" s="373"/>
+      <c r="S154" s="373"/>
+      <c r="T154" s="373"/>
+      <c r="U154" s="373"/>
+      <c r="V154" s="373"/>
+      <c r="W154" s="373"/>
+      <c r="X154" s="373"/>
+      <c r="Y154" s="373"/>
+      <c r="Z154" s="358"/>
+      <c r="AA154" s="372" t="s">
         <v>316</v>
       </c>
-      <c r="AB154" s="343"/>
-      <c r="AC154" s="343"/>
-      <c r="AD154" s="343"/>
-      <c r="AE154" s="343"/>
-      <c r="AF154" s="343"/>
-      <c r="AG154" s="343"/>
-      <c r="AH154" s="344"/>
+      <c r="AB154" s="373"/>
+      <c r="AC154" s="373"/>
+      <c r="AD154" s="373"/>
+      <c r="AE154" s="373"/>
+      <c r="AF154" s="373"/>
+      <c r="AG154" s="373"/>
+      <c r="AH154" s="358"/>
     </row>
     <row r="155" spans="3:34" ht="11.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D155" s="338"/>
-      <c r="E155" s="341" t="s">
+      <c r="D155" s="378"/>
+      <c r="E155" s="355" t="s">
         <v>319</v>
       </c>
-      <c r="F155" s="295"/>
-      <c r="G155" s="295"/>
-      <c r="H155" s="295"/>
-      <c r="I155" s="295"/>
-      <c r="J155" s="296"/>
-      <c r="K155" s="375" t="s">
+      <c r="F155" s="293"/>
+      <c r="G155" s="293"/>
+      <c r="H155" s="293"/>
+      <c r="I155" s="293"/>
+      <c r="J155" s="294"/>
+      <c r="K155" s="330" t="s">
         <v>712</v>
       </c>
-      <c r="L155" s="298"/>
-      <c r="M155" s="298"/>
-      <c r="N155" s="298"/>
-      <c r="O155" s="298"/>
-      <c r="P155" s="298"/>
-      <c r="Q155" s="298"/>
-      <c r="R155" s="298"/>
-      <c r="S155" s="298"/>
-      <c r="T155" s="298"/>
-      <c r="U155" s="298"/>
-      <c r="V155" s="298"/>
-      <c r="W155" s="298"/>
-      <c r="X155" s="298"/>
-      <c r="Y155" s="298"/>
-      <c r="Z155" s="299"/>
-      <c r="AA155" s="297" t="s">
+      <c r="L155" s="296"/>
+      <c r="M155" s="296"/>
+      <c r="N155" s="296"/>
+      <c r="O155" s="296"/>
+      <c r="P155" s="296"/>
+      <c r="Q155" s="296"/>
+      <c r="R155" s="296"/>
+      <c r="S155" s="296"/>
+      <c r="T155" s="296"/>
+      <c r="U155" s="296"/>
+      <c r="V155" s="296"/>
+      <c r="W155" s="296"/>
+      <c r="X155" s="296"/>
+      <c r="Y155" s="296"/>
+      <c r="Z155" s="297"/>
+      <c r="AA155" s="295" t="s">
         <v>321</v>
       </c>
-      <c r="AB155" s="318"/>
-      <c r="AC155" s="318"/>
-      <c r="AD155" s="318"/>
-      <c r="AE155" s="318"/>
-      <c r="AF155" s="318"/>
-      <c r="AG155" s="318"/>
-      <c r="AH155" s="319"/>
+      <c r="AB155" s="325"/>
+      <c r="AC155" s="325"/>
+      <c r="AD155" s="325"/>
+      <c r="AE155" s="325"/>
+      <c r="AF155" s="325"/>
+      <c r="AG155" s="325"/>
+      <c r="AH155" s="326"/>
     </row>
     <row r="156" spans="3:34" s="174" customFormat="1" ht="11.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D156" s="338"/>
-      <c r="E156" s="341"/>
-      <c r="F156" s="295"/>
-      <c r="G156" s="295"/>
-      <c r="H156" s="295"/>
-      <c r="I156" s="295"/>
-      <c r="J156" s="296"/>
-      <c r="K156" s="303"/>
-      <c r="L156" s="304"/>
-      <c r="M156" s="304"/>
-      <c r="N156" s="304"/>
-      <c r="O156" s="304"/>
-      <c r="P156" s="304"/>
-      <c r="Q156" s="304"/>
-      <c r="R156" s="304"/>
-      <c r="S156" s="304"/>
-      <c r="T156" s="304"/>
-      <c r="U156" s="304"/>
-      <c r="V156" s="304"/>
-      <c r="W156" s="304"/>
-      <c r="X156" s="304"/>
-      <c r="Y156" s="304"/>
-      <c r="Z156" s="305"/>
-      <c r="AA156" s="320"/>
-      <c r="AB156" s="321"/>
-      <c r="AC156" s="321"/>
-      <c r="AD156" s="321"/>
-      <c r="AE156" s="321"/>
-      <c r="AF156" s="321"/>
-      <c r="AG156" s="321"/>
-      <c r="AH156" s="322"/>
+      <c r="D156" s="378"/>
+      <c r="E156" s="355"/>
+      <c r="F156" s="293"/>
+      <c r="G156" s="293"/>
+      <c r="H156" s="293"/>
+      <c r="I156" s="293"/>
+      <c r="J156" s="294"/>
+      <c r="K156" s="301"/>
+      <c r="L156" s="302"/>
+      <c r="M156" s="302"/>
+      <c r="N156" s="302"/>
+      <c r="O156" s="302"/>
+      <c r="P156" s="302"/>
+      <c r="Q156" s="302"/>
+      <c r="R156" s="302"/>
+      <c r="S156" s="302"/>
+      <c r="T156" s="302"/>
+      <c r="U156" s="302"/>
+      <c r="V156" s="302"/>
+      <c r="W156" s="302"/>
+      <c r="X156" s="302"/>
+      <c r="Y156" s="302"/>
+      <c r="Z156" s="303"/>
+      <c r="AA156" s="327"/>
+      <c r="AB156" s="328"/>
+      <c r="AC156" s="328"/>
+      <c r="AD156" s="328"/>
+      <c r="AE156" s="328"/>
+      <c r="AF156" s="328"/>
+      <c r="AG156" s="328"/>
+      <c r="AH156" s="329"/>
     </row>
     <row r="157" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D157" s="338"/>
-      <c r="E157" s="341"/>
-      <c r="F157" s="295"/>
-      <c r="G157" s="295"/>
-      <c r="H157" s="295"/>
-      <c r="I157" s="295"/>
-      <c r="J157" s="296"/>
-      <c r="K157" s="356" t="s">
+      <c r="D157" s="378"/>
+      <c r="E157" s="355"/>
+      <c r="F157" s="293"/>
+      <c r="G157" s="293"/>
+      <c r="H157" s="293"/>
+      <c r="I157" s="293"/>
+      <c r="J157" s="294"/>
+      <c r="K157" s="369" t="s">
         <v>713</v>
       </c>
-      <c r="L157" s="352"/>
-      <c r="M157" s="352"/>
-      <c r="N157" s="352"/>
-      <c r="O157" s="352"/>
-      <c r="P157" s="352"/>
-      <c r="Q157" s="352"/>
-      <c r="R157" s="352"/>
-      <c r="S157" s="352"/>
-      <c r="T157" s="352"/>
-      <c r="U157" s="352"/>
-      <c r="V157" s="352"/>
-      <c r="W157" s="352"/>
-      <c r="X157" s="352"/>
-      <c r="Y157" s="352"/>
-      <c r="Z157" s="352"/>
-      <c r="AA157" s="329" t="s">
+      <c r="L157" s="364"/>
+      <c r="M157" s="364"/>
+      <c r="N157" s="364"/>
+      <c r="O157" s="364"/>
+      <c r="P157" s="364"/>
+      <c r="Q157" s="364"/>
+      <c r="R157" s="364"/>
+      <c r="S157" s="364"/>
+      <c r="T157" s="364"/>
+      <c r="U157" s="364"/>
+      <c r="V157" s="364"/>
+      <c r="W157" s="364"/>
+      <c r="X157" s="364"/>
+      <c r="Y157" s="364"/>
+      <c r="Z157" s="364"/>
+      <c r="AA157" s="370" t="s">
         <v>280</v>
       </c>
-      <c r="AB157" s="352"/>
-      <c r="AC157" s="352"/>
-      <c r="AD157" s="352"/>
-      <c r="AE157" s="352"/>
-      <c r="AF157" s="352"/>
-      <c r="AG157" s="352"/>
-      <c r="AH157" s="352"/>
+      <c r="AB157" s="364"/>
+      <c r="AC157" s="364"/>
+      <c r="AD157" s="364"/>
+      <c r="AE157" s="364"/>
+      <c r="AF157" s="364"/>
+      <c r="AG157" s="364"/>
+      <c r="AH157" s="364"/>
     </row>
     <row r="158" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="D158" s="338"/>
-      <c r="E158" s="341"/>
-      <c r="F158" s="295"/>
-      <c r="G158" s="295"/>
-      <c r="H158" s="295"/>
-      <c r="I158" s="295"/>
-      <c r="J158" s="296"/>
-      <c r="K158" s="352"/>
-      <c r="L158" s="352"/>
-      <c r="M158" s="352"/>
-      <c r="N158" s="352"/>
-      <c r="O158" s="352"/>
-      <c r="P158" s="352"/>
-      <c r="Q158" s="352"/>
-      <c r="R158" s="352"/>
-      <c r="S158" s="352"/>
-      <c r="T158" s="352"/>
-      <c r="U158" s="352"/>
-      <c r="V158" s="352"/>
-      <c r="W158" s="352"/>
-      <c r="X158" s="352"/>
-      <c r="Y158" s="352"/>
-      <c r="Z158" s="352"/>
-      <c r="AA158" s="352"/>
-      <c r="AB158" s="352"/>
-      <c r="AC158" s="352"/>
-      <c r="AD158" s="352"/>
-      <c r="AE158" s="352"/>
-      <c r="AF158" s="352"/>
-      <c r="AG158" s="352"/>
-      <c r="AH158" s="352"/>
+      <c r="D158" s="378"/>
+      <c r="E158" s="355"/>
+      <c r="F158" s="293"/>
+      <c r="G158" s="293"/>
+      <c r="H158" s="293"/>
+      <c r="I158" s="293"/>
+      <c r="J158" s="294"/>
+      <c r="K158" s="364"/>
+      <c r="L158" s="364"/>
+      <c r="M158" s="364"/>
+      <c r="N158" s="364"/>
+      <c r="O158" s="364"/>
+      <c r="P158" s="364"/>
+      <c r="Q158" s="364"/>
+      <c r="R158" s="364"/>
+      <c r="S158" s="364"/>
+      <c r="T158" s="364"/>
+      <c r="U158" s="364"/>
+      <c r="V158" s="364"/>
+      <c r="W158" s="364"/>
+      <c r="X158" s="364"/>
+      <c r="Y158" s="364"/>
+      <c r="Z158" s="364"/>
+      <c r="AA158" s="364"/>
+      <c r="AB158" s="364"/>
+      <c r="AC158" s="364"/>
+      <c r="AD158" s="364"/>
+      <c r="AE158" s="364"/>
+      <c r="AF158" s="364"/>
+      <c r="AG158" s="364"/>
+      <c r="AH158" s="364"/>
     </row>
     <row r="159" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="D159" s="338"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="295"/>
-      <c r="G159" s="295"/>
-      <c r="H159" s="295"/>
-      <c r="I159" s="295"/>
-      <c r="J159" s="296"/>
-      <c r="K159" s="352"/>
-      <c r="L159" s="352"/>
-      <c r="M159" s="352"/>
-      <c r="N159" s="352"/>
-      <c r="O159" s="352"/>
-      <c r="P159" s="352"/>
-      <c r="Q159" s="352"/>
-      <c r="R159" s="352"/>
-      <c r="S159" s="352"/>
-      <c r="T159" s="352"/>
-      <c r="U159" s="352"/>
-      <c r="V159" s="352"/>
-      <c r="W159" s="352"/>
-      <c r="X159" s="352"/>
-      <c r="Y159" s="352"/>
-      <c r="Z159" s="352"/>
-      <c r="AA159" s="352"/>
-      <c r="AB159" s="352"/>
-      <c r="AC159" s="352"/>
-      <c r="AD159" s="352"/>
-      <c r="AE159" s="352"/>
-      <c r="AF159" s="352"/>
-      <c r="AG159" s="352"/>
-      <c r="AH159" s="352"/>
+      <c r="D159" s="378"/>
+      <c r="E159" s="355"/>
+      <c r="F159" s="293"/>
+      <c r="G159" s="293"/>
+      <c r="H159" s="293"/>
+      <c r="I159" s="293"/>
+      <c r="J159" s="294"/>
+      <c r="K159" s="364"/>
+      <c r="L159" s="364"/>
+      <c r="M159" s="364"/>
+      <c r="N159" s="364"/>
+      <c r="O159" s="364"/>
+      <c r="P159" s="364"/>
+      <c r="Q159" s="364"/>
+      <c r="R159" s="364"/>
+      <c r="S159" s="364"/>
+      <c r="T159" s="364"/>
+      <c r="U159" s="364"/>
+      <c r="V159" s="364"/>
+      <c r="W159" s="364"/>
+      <c r="X159" s="364"/>
+      <c r="Y159" s="364"/>
+      <c r="Z159" s="364"/>
+      <c r="AA159" s="364"/>
+      <c r="AB159" s="364"/>
+      <c r="AC159" s="364"/>
+      <c r="AD159" s="364"/>
+      <c r="AE159" s="364"/>
+      <c r="AF159" s="364"/>
+      <c r="AG159" s="364"/>
+      <c r="AH159" s="364"/>
     </row>
     <row r="160" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="D160" s="338"/>
-      <c r="E160" s="341"/>
-      <c r="F160" s="295"/>
-      <c r="G160" s="295"/>
-      <c r="H160" s="295"/>
-      <c r="I160" s="295"/>
-      <c r="J160" s="296"/>
-      <c r="K160" s="352"/>
-      <c r="L160" s="352"/>
-      <c r="M160" s="352"/>
-      <c r="N160" s="352"/>
-      <c r="O160" s="352"/>
-      <c r="P160" s="352"/>
-      <c r="Q160" s="352"/>
-      <c r="R160" s="352"/>
-      <c r="S160" s="352"/>
-      <c r="T160" s="352"/>
-      <c r="U160" s="352"/>
-      <c r="V160" s="352"/>
-      <c r="W160" s="352"/>
-      <c r="X160" s="352"/>
-      <c r="Y160" s="352"/>
-      <c r="Z160" s="352"/>
-      <c r="AA160" s="352"/>
-      <c r="AB160" s="352"/>
-      <c r="AC160" s="352"/>
-      <c r="AD160" s="352"/>
-      <c r="AE160" s="352"/>
-      <c r="AF160" s="352"/>
-      <c r="AG160" s="352"/>
-      <c r="AH160" s="352"/>
+      <c r="D160" s="378"/>
+      <c r="E160" s="355"/>
+      <c r="F160" s="293"/>
+      <c r="G160" s="293"/>
+      <c r="H160" s="293"/>
+      <c r="I160" s="293"/>
+      <c r="J160" s="294"/>
+      <c r="K160" s="364"/>
+      <c r="L160" s="364"/>
+      <c r="M160" s="364"/>
+      <c r="N160" s="364"/>
+      <c r="O160" s="364"/>
+      <c r="P160" s="364"/>
+      <c r="Q160" s="364"/>
+      <c r="R160" s="364"/>
+      <c r="S160" s="364"/>
+      <c r="T160" s="364"/>
+      <c r="U160" s="364"/>
+      <c r="V160" s="364"/>
+      <c r="W160" s="364"/>
+      <c r="X160" s="364"/>
+      <c r="Y160" s="364"/>
+      <c r="Z160" s="364"/>
+      <c r="AA160" s="364"/>
+      <c r="AB160" s="364"/>
+      <c r="AC160" s="364"/>
+      <c r="AD160" s="364"/>
+      <c r="AE160" s="364"/>
+      <c r="AF160" s="364"/>
+      <c r="AG160" s="364"/>
+      <c r="AH160" s="364"/>
     </row>
     <row r="161" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="D161" s="338"/>
-      <c r="E161" s="341"/>
-      <c r="F161" s="295"/>
-      <c r="G161" s="295"/>
-      <c r="H161" s="295"/>
-      <c r="I161" s="295"/>
-      <c r="J161" s="296"/>
-      <c r="K161" s="352"/>
-      <c r="L161" s="352"/>
-      <c r="M161" s="352"/>
-      <c r="N161" s="352"/>
-      <c r="O161" s="352"/>
-      <c r="P161" s="352"/>
-      <c r="Q161" s="352"/>
-      <c r="R161" s="352"/>
-      <c r="S161" s="352"/>
-      <c r="T161" s="352"/>
-      <c r="U161" s="352"/>
-      <c r="V161" s="352"/>
-      <c r="W161" s="352"/>
-      <c r="X161" s="352"/>
-      <c r="Y161" s="352"/>
-      <c r="Z161" s="352"/>
-      <c r="AA161" s="352"/>
-      <c r="AB161" s="352"/>
-      <c r="AC161" s="352"/>
-      <c r="AD161" s="352"/>
-      <c r="AE161" s="352"/>
-      <c r="AF161" s="352"/>
-      <c r="AG161" s="352"/>
-      <c r="AH161" s="352"/>
+      <c r="D161" s="378"/>
+      <c r="E161" s="355"/>
+      <c r="F161" s="293"/>
+      <c r="G161" s="293"/>
+      <c r="H161" s="293"/>
+      <c r="I161" s="293"/>
+      <c r="J161" s="294"/>
+      <c r="K161" s="364"/>
+      <c r="L161" s="364"/>
+      <c r="M161" s="364"/>
+      <c r="N161" s="364"/>
+      <c r="O161" s="364"/>
+      <c r="P161" s="364"/>
+      <c r="Q161" s="364"/>
+      <c r="R161" s="364"/>
+      <c r="S161" s="364"/>
+      <c r="T161" s="364"/>
+      <c r="U161" s="364"/>
+      <c r="V161" s="364"/>
+      <c r="W161" s="364"/>
+      <c r="X161" s="364"/>
+      <c r="Y161" s="364"/>
+      <c r="Z161" s="364"/>
+      <c r="AA161" s="364"/>
+      <c r="AB161" s="364"/>
+      <c r="AC161" s="364"/>
+      <c r="AD161" s="364"/>
+      <c r="AE161" s="364"/>
+      <c r="AF161" s="364"/>
+      <c r="AG161" s="364"/>
+      <c r="AH161" s="364"/>
     </row>
     <row r="162" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="D162" s="338"/>
-      <c r="E162" s="341"/>
-      <c r="F162" s="295"/>
-      <c r="G162" s="295"/>
-      <c r="H162" s="295"/>
-      <c r="I162" s="295"/>
-      <c r="J162" s="296"/>
-      <c r="K162" s="351" t="s">
+      <c r="D162" s="378"/>
+      <c r="E162" s="355"/>
+      <c r="F162" s="293"/>
+      <c r="G162" s="293"/>
+      <c r="H162" s="293"/>
+      <c r="I162" s="293"/>
+      <c r="J162" s="294"/>
+      <c r="K162" s="363" t="s">
         <v>622</v>
       </c>
-      <c r="L162" s="352"/>
-      <c r="M162" s="352"/>
-      <c r="N162" s="352"/>
-      <c r="O162" s="352"/>
-      <c r="P162" s="352"/>
-      <c r="Q162" s="352"/>
-      <c r="R162" s="352"/>
-      <c r="S162" s="352"/>
-      <c r="T162" s="352"/>
-      <c r="U162" s="352"/>
-      <c r="V162" s="352"/>
-      <c r="W162" s="352"/>
-      <c r="X162" s="352"/>
-      <c r="Y162" s="352"/>
-      <c r="Z162" s="352"/>
-      <c r="AA162" s="329" t="s">
+      <c r="L162" s="364"/>
+      <c r="M162" s="364"/>
+      <c r="N162" s="364"/>
+      <c r="O162" s="364"/>
+      <c r="P162" s="364"/>
+      <c r="Q162" s="364"/>
+      <c r="R162" s="364"/>
+      <c r="S162" s="364"/>
+      <c r="T162" s="364"/>
+      <c r="U162" s="364"/>
+      <c r="V162" s="364"/>
+      <c r="W162" s="364"/>
+      <c r="X162" s="364"/>
+      <c r="Y162" s="364"/>
+      <c r="Z162" s="364"/>
+      <c r="AA162" s="370" t="s">
         <v>74</v>
       </c>
-      <c r="AB162" s="330"/>
-      <c r="AC162" s="330"/>
-      <c r="AD162" s="330"/>
-      <c r="AE162" s="330"/>
-      <c r="AF162" s="330"/>
-      <c r="AG162" s="330"/>
-      <c r="AH162" s="330"/>
+      <c r="AB162" s="371"/>
+      <c r="AC162" s="371"/>
+      <c r="AD162" s="371"/>
+      <c r="AE162" s="371"/>
+      <c r="AF162" s="371"/>
+      <c r="AG162" s="371"/>
+      <c r="AH162" s="371"/>
     </row>
     <row r="163" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D163" s="338"/>
-      <c r="E163" s="341" t="s">
+      <c r="D163" s="378"/>
+      <c r="E163" s="355" t="s">
         <v>318</v>
       </c>
-      <c r="F163" s="295"/>
-      <c r="G163" s="295"/>
-      <c r="H163" s="295"/>
-      <c r="I163" s="295"/>
-      <c r="J163" s="296"/>
-      <c r="K163" s="341" t="s">
+      <c r="F163" s="293"/>
+      <c r="G163" s="293"/>
+      <c r="H163" s="293"/>
+      <c r="I163" s="293"/>
+      <c r="J163" s="294"/>
+      <c r="K163" s="355" t="s">
         <v>621</v>
       </c>
-      <c r="L163" s="295"/>
-      <c r="M163" s="295"/>
-      <c r="N163" s="295"/>
-      <c r="O163" s="295"/>
-      <c r="P163" s="295"/>
-      <c r="Q163" s="295"/>
-      <c r="R163" s="295"/>
-      <c r="S163" s="295"/>
-      <c r="T163" s="295"/>
-      <c r="U163" s="295"/>
-      <c r="V163" s="295"/>
-      <c r="W163" s="295"/>
-      <c r="X163" s="295"/>
-      <c r="Y163" s="295"/>
-      <c r="Z163" s="296"/>
-      <c r="AA163" s="330" t="s">
+      <c r="L163" s="293"/>
+      <c r="M163" s="293"/>
+      <c r="N163" s="293"/>
+      <c r="O163" s="293"/>
+      <c r="P163" s="293"/>
+      <c r="Q163" s="293"/>
+      <c r="R163" s="293"/>
+      <c r="S163" s="293"/>
+      <c r="T163" s="293"/>
+      <c r="U163" s="293"/>
+      <c r="V163" s="293"/>
+      <c r="W163" s="293"/>
+      <c r="X163" s="293"/>
+      <c r="Y163" s="293"/>
+      <c r="Z163" s="294"/>
+      <c r="AA163" s="371" t="s">
         <v>70</v>
       </c>
-      <c r="AB163" s="330"/>
-      <c r="AC163" s="330"/>
-      <c r="AD163" s="330"/>
-      <c r="AE163" s="330"/>
-      <c r="AF163" s="330"/>
-      <c r="AG163" s="330"/>
-      <c r="AH163" s="330"/>
+      <c r="AB163" s="371"/>
+      <c r="AC163" s="371"/>
+      <c r="AD163" s="371"/>
+      <c r="AE163" s="371"/>
+      <c r="AF163" s="371"/>
+      <c r="AG163" s="371"/>
+      <c r="AH163" s="371"/>
     </row>
     <row r="164" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="D164" s="339"/>
-      <c r="E164" s="341"/>
-      <c r="F164" s="295"/>
-      <c r="G164" s="295"/>
-      <c r="H164" s="295"/>
-      <c r="I164" s="295"/>
-      <c r="J164" s="296"/>
-      <c r="K164" s="330"/>
-      <c r="L164" s="330"/>
-      <c r="M164" s="330"/>
-      <c r="N164" s="330"/>
-      <c r="O164" s="330"/>
-      <c r="P164" s="330"/>
-      <c r="Q164" s="330"/>
-      <c r="R164" s="330"/>
-      <c r="S164" s="330"/>
-      <c r="T164" s="330"/>
-      <c r="U164" s="330"/>
-      <c r="V164" s="330"/>
-      <c r="W164" s="330"/>
-      <c r="X164" s="330"/>
-      <c r="Y164" s="330"/>
-      <c r="Z164" s="330"/>
-      <c r="AA164" s="330"/>
-      <c r="AB164" s="330"/>
-      <c r="AC164" s="330"/>
-      <c r="AD164" s="330"/>
-      <c r="AE164" s="330"/>
-      <c r="AF164" s="330"/>
-      <c r="AG164" s="330"/>
-      <c r="AH164" s="330"/>
+      <c r="D164" s="379"/>
+      <c r="E164" s="355"/>
+      <c r="F164" s="293"/>
+      <c r="G164" s="293"/>
+      <c r="H164" s="293"/>
+      <c r="I164" s="293"/>
+      <c r="J164" s="294"/>
+      <c r="K164" s="371"/>
+      <c r="L164" s="371"/>
+      <c r="M164" s="371"/>
+      <c r="N164" s="371"/>
+      <c r="O164" s="371"/>
+      <c r="P164" s="371"/>
+      <c r="Q164" s="371"/>
+      <c r="R164" s="371"/>
+      <c r="S164" s="371"/>
+      <c r="T164" s="371"/>
+      <c r="U164" s="371"/>
+      <c r="V164" s="371"/>
+      <c r="W164" s="371"/>
+      <c r="X164" s="371"/>
+      <c r="Y164" s="371"/>
+      <c r="Z164" s="371"/>
+      <c r="AA164" s="371"/>
+      <c r="AB164" s="371"/>
+      <c r="AC164" s="371"/>
+      <c r="AD164" s="371"/>
+      <c r="AE164" s="371"/>
+      <c r="AF164" s="371"/>
+      <c r="AG164" s="371"/>
+      <c r="AH164" s="371"/>
     </row>
     <row r="165" spans="3:34" x14ac:dyDescent="0.2">
       <c r="D165" s="55"/>
@@ -42507,815 +42526,815 @@
     </row>
     <row r="174" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="175" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F175" s="258" t="s">
+      <c r="F175" s="283" t="s">
         <v>635</v>
       </c>
-      <c r="G175" s="334"/>
-      <c r="H175" s="334"/>
-      <c r="I175" s="334"/>
-      <c r="J175" s="335"/>
-      <c r="K175" s="336" t="s">
+      <c r="G175" s="349"/>
+      <c r="H175" s="349"/>
+      <c r="I175" s="349"/>
+      <c r="J175" s="350"/>
+      <c r="K175" s="361" t="s">
         <v>30</v>
       </c>
-      <c r="L175" s="337"/>
-      <c r="M175" s="336" t="s">
+      <c r="L175" s="362"/>
+      <c r="M175" s="361" t="s">
         <v>45</v>
       </c>
-      <c r="N175" s="337"/>
-      <c r="O175" s="333" t="s">
+      <c r="N175" s="362"/>
+      <c r="O175" s="377" t="s">
         <v>44</v>
       </c>
-      <c r="P175" s="334"/>
-      <c r="Q175" s="334"/>
-      <c r="R175" s="334"/>
-      <c r="S175" s="334"/>
-      <c r="T175" s="334"/>
-      <c r="U175" s="334"/>
-      <c r="V175" s="334"/>
-      <c r="W175" s="334"/>
-      <c r="X175" s="334"/>
-      <c r="Y175" s="334"/>
-      <c r="Z175" s="334"/>
-      <c r="AA175" s="334"/>
-      <c r="AB175" s="334"/>
-      <c r="AC175" s="334"/>
-      <c r="AD175" s="334"/>
-      <c r="AE175" s="334"/>
-      <c r="AF175" s="334"/>
-      <c r="AG175" s="334"/>
-      <c r="AH175" s="335"/>
+      <c r="P175" s="349"/>
+      <c r="Q175" s="349"/>
+      <c r="R175" s="349"/>
+      <c r="S175" s="349"/>
+      <c r="T175" s="349"/>
+      <c r="U175" s="349"/>
+      <c r="V175" s="349"/>
+      <c r="W175" s="349"/>
+      <c r="X175" s="349"/>
+      <c r="Y175" s="349"/>
+      <c r="Z175" s="349"/>
+      <c r="AA175" s="349"/>
+      <c r="AB175" s="349"/>
+      <c r="AC175" s="349"/>
+      <c r="AD175" s="349"/>
+      <c r="AE175" s="349"/>
+      <c r="AF175" s="349"/>
+      <c r="AG175" s="349"/>
+      <c r="AH175" s="350"/>
     </row>
     <row r="176" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F176" s="314" t="s">
+      <c r="F176" s="317" t="s">
         <v>282</v>
       </c>
-      <c r="G176" s="262"/>
-      <c r="H176" s="262"/>
-      <c r="I176" s="262"/>
-      <c r="J176" s="263"/>
+      <c r="G176" s="287"/>
+      <c r="H176" s="287"/>
+      <c r="I176" s="287"/>
+      <c r="J176" s="288"/>
       <c r="K176" s="345" t="s">
         <v>32</v>
       </c>
-      <c r="L176" s="299"/>
-      <c r="M176" s="342" t="s">
+      <c r="L176" s="297"/>
+      <c r="M176" s="372" t="s">
         <v>299</v>
       </c>
-      <c r="N176" s="344"/>
-      <c r="O176" s="264" t="s">
+      <c r="N176" s="358"/>
+      <c r="O176" s="289" t="s">
         <v>304</v>
       </c>
-      <c r="P176" s="347"/>
-      <c r="Q176" s="347"/>
-      <c r="R176" s="347"/>
-      <c r="S176" s="347"/>
-      <c r="T176" s="347"/>
-      <c r="U176" s="347"/>
-      <c r="V176" s="347"/>
-      <c r="W176" s="347"/>
-      <c r="X176" s="347"/>
-      <c r="Y176" s="347"/>
-      <c r="Z176" s="347"/>
-      <c r="AA176" s="347"/>
-      <c r="AB176" s="347"/>
-      <c r="AC176" s="347"/>
-      <c r="AD176" s="347"/>
-      <c r="AE176" s="347"/>
-      <c r="AF176" s="347"/>
-      <c r="AG176" s="347"/>
-      <c r="AH176" s="348"/>
+      <c r="P176" s="374"/>
+      <c r="Q176" s="374"/>
+      <c r="R176" s="374"/>
+      <c r="S176" s="374"/>
+      <c r="T176" s="374"/>
+      <c r="U176" s="374"/>
+      <c r="V176" s="374"/>
+      <c r="W176" s="374"/>
+      <c r="X176" s="374"/>
+      <c r="Y176" s="374"/>
+      <c r="Z176" s="374"/>
+      <c r="AA176" s="374"/>
+      <c r="AB176" s="374"/>
+      <c r="AC176" s="374"/>
+      <c r="AD176" s="374"/>
+      <c r="AE176" s="374"/>
+      <c r="AF176" s="374"/>
+      <c r="AG176" s="374"/>
+      <c r="AH176" s="375"/>
     </row>
     <row r="177" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F177" s="297" t="s">
+      <c r="F177" s="295" t="s">
         <v>300</v>
       </c>
-      <c r="G177" s="298"/>
-      <c r="H177" s="298"/>
-      <c r="I177" s="298"/>
-      <c r="J177" s="299"/>
+      <c r="G177" s="296"/>
+      <c r="H177" s="296"/>
+      <c r="I177" s="296"/>
+      <c r="J177" s="297"/>
       <c r="K177" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="L177" s="299"/>
-      <c r="M177" s="317" t="s">
+      <c r="L177" s="297"/>
+      <c r="M177" s="324" t="s">
         <v>334</v>
       </c>
-      <c r="N177" s="319"/>
-      <c r="O177" s="297" t="s">
+      <c r="N177" s="326"/>
+      <c r="O177" s="295" t="s">
         <v>303</v>
       </c>
-      <c r="P177" s="298"/>
-      <c r="Q177" s="298"/>
-      <c r="R177" s="298"/>
-      <c r="S177" s="298"/>
-      <c r="T177" s="298"/>
-      <c r="U177" s="298"/>
-      <c r="V177" s="298"/>
-      <c r="W177" s="298"/>
-      <c r="X177" s="298"/>
-      <c r="Y177" s="298"/>
-      <c r="Z177" s="298"/>
-      <c r="AA177" s="298"/>
-      <c r="AB177" s="298"/>
-      <c r="AC177" s="298"/>
-      <c r="AD177" s="298"/>
-      <c r="AE177" s="298"/>
-      <c r="AF177" s="298"/>
-      <c r="AG177" s="298"/>
-      <c r="AH177" s="299"/>
+      <c r="P177" s="296"/>
+      <c r="Q177" s="296"/>
+      <c r="R177" s="296"/>
+      <c r="S177" s="296"/>
+      <c r="T177" s="296"/>
+      <c r="U177" s="296"/>
+      <c r="V177" s="296"/>
+      <c r="W177" s="296"/>
+      <c r="X177" s="296"/>
+      <c r="Y177" s="296"/>
+      <c r="Z177" s="296"/>
+      <c r="AA177" s="296"/>
+      <c r="AB177" s="296"/>
+      <c r="AC177" s="296"/>
+      <c r="AD177" s="296"/>
+      <c r="AE177" s="296"/>
+      <c r="AF177" s="296"/>
+      <c r="AG177" s="296"/>
+      <c r="AH177" s="297"/>
     </row>
     <row r="178" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F178" s="306"/>
-      <c r="G178" s="301"/>
-      <c r="H178" s="301"/>
-      <c r="I178" s="301"/>
-      <c r="J178" s="302"/>
-      <c r="K178" s="300"/>
-      <c r="L178" s="302"/>
-      <c r="M178" s="357"/>
-      <c r="N178" s="358"/>
-      <c r="O178" s="306"/>
-      <c r="P178" s="301"/>
-      <c r="Q178" s="301"/>
-      <c r="R178" s="301"/>
-      <c r="S178" s="301"/>
-      <c r="T178" s="301"/>
-      <c r="U178" s="301"/>
-      <c r="V178" s="301"/>
-      <c r="W178" s="301"/>
-      <c r="X178" s="301"/>
-      <c r="Y178" s="301"/>
-      <c r="Z178" s="301"/>
-      <c r="AA178" s="301"/>
-      <c r="AB178" s="301"/>
-      <c r="AC178" s="301"/>
-      <c r="AD178" s="301"/>
-      <c r="AE178" s="301"/>
-      <c r="AF178" s="301"/>
-      <c r="AG178" s="301"/>
-      <c r="AH178" s="302"/>
+      <c r="F178" s="304"/>
+      <c r="G178" s="299"/>
+      <c r="H178" s="299"/>
+      <c r="I178" s="299"/>
+      <c r="J178" s="300"/>
+      <c r="K178" s="298"/>
+      <c r="L178" s="300"/>
+      <c r="M178" s="342"/>
+      <c r="N178" s="352"/>
+      <c r="O178" s="304"/>
+      <c r="P178" s="299"/>
+      <c r="Q178" s="299"/>
+      <c r="R178" s="299"/>
+      <c r="S178" s="299"/>
+      <c r="T178" s="299"/>
+      <c r="U178" s="299"/>
+      <c r="V178" s="299"/>
+      <c r="W178" s="299"/>
+      <c r="X178" s="299"/>
+      <c r="Y178" s="299"/>
+      <c r="Z178" s="299"/>
+      <c r="AA178" s="299"/>
+      <c r="AB178" s="299"/>
+      <c r="AC178" s="299"/>
+      <c r="AD178" s="299"/>
+      <c r="AE178" s="299"/>
+      <c r="AF178" s="299"/>
+      <c r="AG178" s="299"/>
+      <c r="AH178" s="300"/>
     </row>
     <row r="179" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F179" s="306"/>
-      <c r="G179" s="301"/>
-      <c r="H179" s="301"/>
-      <c r="I179" s="301"/>
-      <c r="J179" s="302"/>
-      <c r="K179" s="300"/>
-      <c r="L179" s="302"/>
-      <c r="M179" s="357"/>
-      <c r="N179" s="358"/>
-      <c r="O179" s="306"/>
-      <c r="P179" s="301"/>
-      <c r="Q179" s="301"/>
-      <c r="R179" s="301"/>
-      <c r="S179" s="301"/>
-      <c r="T179" s="301"/>
-      <c r="U179" s="301"/>
-      <c r="V179" s="301"/>
-      <c r="W179" s="301"/>
-      <c r="X179" s="301"/>
-      <c r="Y179" s="301"/>
-      <c r="Z179" s="301"/>
-      <c r="AA179" s="301"/>
-      <c r="AB179" s="301"/>
-      <c r="AC179" s="301"/>
-      <c r="AD179" s="301"/>
-      <c r="AE179" s="301"/>
-      <c r="AF179" s="301"/>
-      <c r="AG179" s="301"/>
-      <c r="AH179" s="302"/>
+      <c r="F179" s="304"/>
+      <c r="G179" s="299"/>
+      <c r="H179" s="299"/>
+      <c r="I179" s="299"/>
+      <c r="J179" s="300"/>
+      <c r="K179" s="298"/>
+      <c r="L179" s="300"/>
+      <c r="M179" s="342"/>
+      <c r="N179" s="352"/>
+      <c r="O179" s="304"/>
+      <c r="P179" s="299"/>
+      <c r="Q179" s="299"/>
+      <c r="R179" s="299"/>
+      <c r="S179" s="299"/>
+      <c r="T179" s="299"/>
+      <c r="U179" s="299"/>
+      <c r="V179" s="299"/>
+      <c r="W179" s="299"/>
+      <c r="X179" s="299"/>
+      <c r="Y179" s="299"/>
+      <c r="Z179" s="299"/>
+      <c r="AA179" s="299"/>
+      <c r="AB179" s="299"/>
+      <c r="AC179" s="299"/>
+      <c r="AD179" s="299"/>
+      <c r="AE179" s="299"/>
+      <c r="AF179" s="299"/>
+      <c r="AG179" s="299"/>
+      <c r="AH179" s="300"/>
     </row>
     <row r="180" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F180" s="303"/>
-      <c r="G180" s="304"/>
-      <c r="H180" s="304"/>
-      <c r="I180" s="304"/>
-      <c r="J180" s="305"/>
-      <c r="K180" s="303"/>
-      <c r="L180" s="305"/>
-      <c r="M180" s="320"/>
-      <c r="N180" s="322"/>
-      <c r="O180" s="303"/>
-      <c r="P180" s="304"/>
-      <c r="Q180" s="304"/>
-      <c r="R180" s="304"/>
-      <c r="S180" s="304"/>
-      <c r="T180" s="304"/>
-      <c r="U180" s="304"/>
-      <c r="V180" s="304"/>
-      <c r="W180" s="304"/>
-      <c r="X180" s="304"/>
-      <c r="Y180" s="304"/>
-      <c r="Z180" s="304"/>
-      <c r="AA180" s="304"/>
-      <c r="AB180" s="304"/>
-      <c r="AC180" s="304"/>
-      <c r="AD180" s="304"/>
-      <c r="AE180" s="304"/>
-      <c r="AF180" s="304"/>
-      <c r="AG180" s="304"/>
-      <c r="AH180" s="305"/>
+      <c r="F180" s="301"/>
+      <c r="G180" s="302"/>
+      <c r="H180" s="302"/>
+      <c r="I180" s="302"/>
+      <c r="J180" s="303"/>
+      <c r="K180" s="301"/>
+      <c r="L180" s="303"/>
+      <c r="M180" s="327"/>
+      <c r="N180" s="329"/>
+      <c r="O180" s="301"/>
+      <c r="P180" s="302"/>
+      <c r="Q180" s="302"/>
+      <c r="R180" s="302"/>
+      <c r="S180" s="302"/>
+      <c r="T180" s="302"/>
+      <c r="U180" s="302"/>
+      <c r="V180" s="302"/>
+      <c r="W180" s="302"/>
+      <c r="X180" s="302"/>
+      <c r="Y180" s="302"/>
+      <c r="Z180" s="302"/>
+      <c r="AA180" s="302"/>
+      <c r="AB180" s="302"/>
+      <c r="AC180" s="302"/>
+      <c r="AD180" s="302"/>
+      <c r="AE180" s="302"/>
+      <c r="AF180" s="302"/>
+      <c r="AG180" s="302"/>
+      <c r="AH180" s="303"/>
     </row>
     <row r="181" spans="6:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F181" s="345" t="s">
         <v>47</v>
       </c>
-      <c r="G181" s="298"/>
-      <c r="H181" s="298"/>
-      <c r="I181" s="298"/>
-      <c r="J181" s="299"/>
+      <c r="G181" s="296"/>
+      <c r="H181" s="296"/>
+      <c r="I181" s="296"/>
+      <c r="J181" s="297"/>
       <c r="K181" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="L181" s="299"/>
+      <c r="L181" s="297"/>
       <c r="M181" s="345" t="s">
         <v>48</v>
       </c>
-      <c r="N181" s="319"/>
-      <c r="O181" s="317" t="s">
+      <c r="N181" s="326"/>
+      <c r="O181" s="324" t="s">
         <v>307</v>
       </c>
-      <c r="P181" s="318"/>
-      <c r="Q181" s="318"/>
-      <c r="R181" s="318"/>
-      <c r="S181" s="318"/>
-      <c r="T181" s="318"/>
-      <c r="U181" s="318"/>
-      <c r="V181" s="318"/>
-      <c r="W181" s="318"/>
-      <c r="X181" s="318"/>
-      <c r="Y181" s="318"/>
-      <c r="Z181" s="318"/>
-      <c r="AA181" s="318"/>
-      <c r="AB181" s="318"/>
-      <c r="AC181" s="318"/>
-      <c r="AD181" s="318"/>
-      <c r="AE181" s="318"/>
-      <c r="AF181" s="318"/>
-      <c r="AG181" s="318"/>
-      <c r="AH181" s="319"/>
+      <c r="P181" s="325"/>
+      <c r="Q181" s="325"/>
+      <c r="R181" s="325"/>
+      <c r="S181" s="325"/>
+      <c r="T181" s="325"/>
+      <c r="U181" s="325"/>
+      <c r="V181" s="325"/>
+      <c r="W181" s="325"/>
+      <c r="X181" s="325"/>
+      <c r="Y181" s="325"/>
+      <c r="Z181" s="325"/>
+      <c r="AA181" s="325"/>
+      <c r="AB181" s="325"/>
+      <c r="AC181" s="325"/>
+      <c r="AD181" s="325"/>
+      <c r="AE181" s="325"/>
+      <c r="AF181" s="325"/>
+      <c r="AG181" s="325"/>
+      <c r="AH181" s="326"/>
     </row>
     <row r="182" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F182" s="297" t="s">
+      <c r="F182" s="295" t="s">
         <v>283</v>
       </c>
-      <c r="G182" s="298"/>
-      <c r="H182" s="298"/>
-      <c r="I182" s="298"/>
-      <c r="J182" s="299"/>
+      <c r="G182" s="296"/>
+      <c r="H182" s="296"/>
+      <c r="I182" s="296"/>
+      <c r="J182" s="297"/>
       <c r="K182" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="L182" s="299"/>
+      <c r="L182" s="297"/>
       <c r="M182" s="345" t="s">
         <v>75</v>
       </c>
-      <c r="N182" s="319"/>
-      <c r="O182" s="317" t="s">
+      <c r="N182" s="326"/>
+      <c r="O182" s="324" t="s">
         <v>308</v>
       </c>
-      <c r="P182" s="318"/>
-      <c r="Q182" s="318"/>
-      <c r="R182" s="318"/>
-      <c r="S182" s="318"/>
-      <c r="T182" s="318"/>
-      <c r="U182" s="318"/>
-      <c r="V182" s="318"/>
-      <c r="W182" s="318"/>
-      <c r="X182" s="318"/>
-      <c r="Y182" s="318"/>
-      <c r="Z182" s="318"/>
-      <c r="AA182" s="318"/>
-      <c r="AB182" s="318"/>
-      <c r="AC182" s="318"/>
-      <c r="AD182" s="318"/>
-      <c r="AE182" s="318"/>
-      <c r="AF182" s="318"/>
-      <c r="AG182" s="318"/>
-      <c r="AH182" s="319"/>
+      <c r="P182" s="325"/>
+      <c r="Q182" s="325"/>
+      <c r="R182" s="325"/>
+      <c r="S182" s="325"/>
+      <c r="T182" s="325"/>
+      <c r="U182" s="325"/>
+      <c r="V182" s="325"/>
+      <c r="W182" s="325"/>
+      <c r="X182" s="325"/>
+      <c r="Y182" s="325"/>
+      <c r="Z182" s="325"/>
+      <c r="AA182" s="325"/>
+      <c r="AB182" s="325"/>
+      <c r="AC182" s="325"/>
+      <c r="AD182" s="325"/>
+      <c r="AE182" s="325"/>
+      <c r="AF182" s="325"/>
+      <c r="AG182" s="325"/>
+      <c r="AH182" s="326"/>
     </row>
     <row r="183" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F183" s="306"/>
-      <c r="G183" s="371"/>
-      <c r="H183" s="371"/>
-      <c r="I183" s="371"/>
-      <c r="J183" s="358"/>
-      <c r="K183" s="300"/>
-      <c r="L183" s="302"/>
-      <c r="M183" s="306"/>
-      <c r="N183" s="358"/>
-      <c r="O183" s="306"/>
-      <c r="P183" s="371"/>
-      <c r="Q183" s="371"/>
-      <c r="R183" s="371"/>
-      <c r="S183" s="371"/>
-      <c r="T183" s="371"/>
-      <c r="U183" s="371"/>
-      <c r="V183" s="371"/>
-      <c r="W183" s="371"/>
-      <c r="X183" s="371"/>
-      <c r="Y183" s="371"/>
-      <c r="Z183" s="371"/>
-      <c r="AA183" s="371"/>
-      <c r="AB183" s="371"/>
-      <c r="AC183" s="371"/>
-      <c r="AD183" s="371"/>
-      <c r="AE183" s="371"/>
-      <c r="AF183" s="371"/>
-      <c r="AG183" s="371"/>
-      <c r="AH183" s="358"/>
+      <c r="F183" s="304"/>
+      <c r="G183" s="351"/>
+      <c r="H183" s="351"/>
+      <c r="I183" s="351"/>
+      <c r="J183" s="352"/>
+      <c r="K183" s="298"/>
+      <c r="L183" s="300"/>
+      <c r="M183" s="304"/>
+      <c r="N183" s="352"/>
+      <c r="O183" s="304"/>
+      <c r="P183" s="351"/>
+      <c r="Q183" s="351"/>
+      <c r="R183" s="351"/>
+      <c r="S183" s="351"/>
+      <c r="T183" s="351"/>
+      <c r="U183" s="351"/>
+      <c r="V183" s="351"/>
+      <c r="W183" s="351"/>
+      <c r="X183" s="351"/>
+      <c r="Y183" s="351"/>
+      <c r="Z183" s="351"/>
+      <c r="AA183" s="351"/>
+      <c r="AB183" s="351"/>
+      <c r="AC183" s="351"/>
+      <c r="AD183" s="351"/>
+      <c r="AE183" s="351"/>
+      <c r="AF183" s="351"/>
+      <c r="AG183" s="351"/>
+      <c r="AH183" s="352"/>
     </row>
     <row r="184" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F184" s="306"/>
-      <c r="G184" s="371"/>
-      <c r="H184" s="371"/>
-      <c r="I184" s="371"/>
-      <c r="J184" s="358"/>
-      <c r="K184" s="300"/>
-      <c r="L184" s="302"/>
-      <c r="M184" s="306"/>
-      <c r="N184" s="358"/>
-      <c r="O184" s="306"/>
-      <c r="P184" s="371"/>
-      <c r="Q184" s="371"/>
-      <c r="R184" s="371"/>
-      <c r="S184" s="371"/>
-      <c r="T184" s="371"/>
-      <c r="U184" s="371"/>
-      <c r="V184" s="371"/>
-      <c r="W184" s="371"/>
-      <c r="X184" s="371"/>
-      <c r="Y184" s="371"/>
-      <c r="Z184" s="371"/>
-      <c r="AA184" s="371"/>
-      <c r="AB184" s="371"/>
-      <c r="AC184" s="371"/>
-      <c r="AD184" s="371"/>
-      <c r="AE184" s="371"/>
-      <c r="AF184" s="371"/>
-      <c r="AG184" s="371"/>
-      <c r="AH184" s="358"/>
+      <c r="F184" s="304"/>
+      <c r="G184" s="351"/>
+      <c r="H184" s="351"/>
+      <c r="I184" s="351"/>
+      <c r="J184" s="352"/>
+      <c r="K184" s="298"/>
+      <c r="L184" s="300"/>
+      <c r="M184" s="304"/>
+      <c r="N184" s="352"/>
+      <c r="O184" s="304"/>
+      <c r="P184" s="351"/>
+      <c r="Q184" s="351"/>
+      <c r="R184" s="351"/>
+      <c r="S184" s="351"/>
+      <c r="T184" s="351"/>
+      <c r="U184" s="351"/>
+      <c r="V184" s="351"/>
+      <c r="W184" s="351"/>
+      <c r="X184" s="351"/>
+      <c r="Y184" s="351"/>
+      <c r="Z184" s="351"/>
+      <c r="AA184" s="351"/>
+      <c r="AB184" s="351"/>
+      <c r="AC184" s="351"/>
+      <c r="AD184" s="351"/>
+      <c r="AE184" s="351"/>
+      <c r="AF184" s="351"/>
+      <c r="AG184" s="351"/>
+      <c r="AH184" s="352"/>
     </row>
     <row r="185" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F185" s="320"/>
-      <c r="G185" s="321"/>
-      <c r="H185" s="321"/>
-      <c r="I185" s="321"/>
-      <c r="J185" s="322"/>
-      <c r="K185" s="303"/>
-      <c r="L185" s="305"/>
-      <c r="M185" s="320"/>
-      <c r="N185" s="322"/>
-      <c r="O185" s="320"/>
-      <c r="P185" s="321"/>
-      <c r="Q185" s="321"/>
-      <c r="R185" s="321"/>
-      <c r="S185" s="321"/>
-      <c r="T185" s="321"/>
-      <c r="U185" s="321"/>
-      <c r="V185" s="321"/>
-      <c r="W185" s="321"/>
-      <c r="X185" s="321"/>
-      <c r="Y185" s="321"/>
-      <c r="Z185" s="321"/>
-      <c r="AA185" s="321"/>
-      <c r="AB185" s="321"/>
-      <c r="AC185" s="321"/>
-      <c r="AD185" s="321"/>
-      <c r="AE185" s="321"/>
-      <c r="AF185" s="321"/>
-      <c r="AG185" s="321"/>
-      <c r="AH185" s="322"/>
+      <c r="F185" s="327"/>
+      <c r="G185" s="328"/>
+      <c r="H185" s="328"/>
+      <c r="I185" s="328"/>
+      <c r="J185" s="329"/>
+      <c r="K185" s="301"/>
+      <c r="L185" s="303"/>
+      <c r="M185" s="327"/>
+      <c r="N185" s="329"/>
+      <c r="O185" s="327"/>
+      <c r="P185" s="328"/>
+      <c r="Q185" s="328"/>
+      <c r="R185" s="328"/>
+      <c r="S185" s="328"/>
+      <c r="T185" s="328"/>
+      <c r="U185" s="328"/>
+      <c r="V185" s="328"/>
+      <c r="W185" s="328"/>
+      <c r="X185" s="328"/>
+      <c r="Y185" s="328"/>
+      <c r="Z185" s="328"/>
+      <c r="AA185" s="328"/>
+      <c r="AB185" s="328"/>
+      <c r="AC185" s="328"/>
+      <c r="AD185" s="328"/>
+      <c r="AE185" s="328"/>
+      <c r="AF185" s="328"/>
+      <c r="AG185" s="328"/>
+      <c r="AH185" s="329"/>
     </row>
     <row r="186" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F186" s="345" t="s">
         <v>38</v>
       </c>
-      <c r="G186" s="298"/>
-      <c r="H186" s="298"/>
-      <c r="I186" s="298"/>
-      <c r="J186" s="299"/>
+      <c r="G186" s="296"/>
+      <c r="H186" s="296"/>
+      <c r="I186" s="296"/>
+      <c r="J186" s="297"/>
       <c r="K186" s="345" t="s">
         <v>35</v>
       </c>
-      <c r="L186" s="299"/>
+      <c r="L186" s="297"/>
       <c r="M186" s="345" t="s">
         <v>48</v>
       </c>
-      <c r="N186" s="319"/>
-      <c r="O186" s="317" t="s">
+      <c r="N186" s="326"/>
+      <c r="O186" s="324" t="s">
         <v>494</v>
       </c>
-      <c r="P186" s="318"/>
-      <c r="Q186" s="318"/>
-      <c r="R186" s="318"/>
-      <c r="S186" s="318"/>
-      <c r="T186" s="318"/>
-      <c r="U186" s="318"/>
-      <c r="V186" s="318"/>
-      <c r="W186" s="318"/>
-      <c r="X186" s="318"/>
-      <c r="Y186" s="318"/>
-      <c r="Z186" s="318"/>
-      <c r="AA186" s="318"/>
-      <c r="AB186" s="318"/>
-      <c r="AC186" s="318"/>
-      <c r="AD186" s="318"/>
-      <c r="AE186" s="318"/>
-      <c r="AF186" s="318"/>
-      <c r="AG186" s="318"/>
-      <c r="AH186" s="319"/>
+      <c r="P186" s="325"/>
+      <c r="Q186" s="325"/>
+      <c r="R186" s="325"/>
+      <c r="S186" s="325"/>
+      <c r="T186" s="325"/>
+      <c r="U186" s="325"/>
+      <c r="V186" s="325"/>
+      <c r="W186" s="325"/>
+      <c r="X186" s="325"/>
+      <c r="Y186" s="325"/>
+      <c r="Z186" s="325"/>
+      <c r="AA186" s="325"/>
+      <c r="AB186" s="325"/>
+      <c r="AC186" s="325"/>
+      <c r="AD186" s="325"/>
+      <c r="AE186" s="325"/>
+      <c r="AF186" s="325"/>
+      <c r="AG186" s="325"/>
+      <c r="AH186" s="326"/>
     </row>
     <row r="187" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F187" s="320"/>
-      <c r="G187" s="321"/>
-      <c r="H187" s="321"/>
-      <c r="I187" s="321"/>
-      <c r="J187" s="322"/>
-      <c r="K187" s="303"/>
-      <c r="L187" s="305"/>
-      <c r="M187" s="320"/>
-      <c r="N187" s="322"/>
-      <c r="O187" s="320"/>
-      <c r="P187" s="321"/>
-      <c r="Q187" s="321"/>
-      <c r="R187" s="321"/>
-      <c r="S187" s="321"/>
-      <c r="T187" s="321"/>
-      <c r="U187" s="321"/>
-      <c r="V187" s="321"/>
-      <c r="W187" s="321"/>
-      <c r="X187" s="321"/>
-      <c r="Y187" s="321"/>
-      <c r="Z187" s="321"/>
-      <c r="AA187" s="321"/>
-      <c r="AB187" s="321"/>
-      <c r="AC187" s="321"/>
-      <c r="AD187" s="321"/>
-      <c r="AE187" s="321"/>
-      <c r="AF187" s="321"/>
-      <c r="AG187" s="321"/>
-      <c r="AH187" s="322"/>
+      <c r="F187" s="327"/>
+      <c r="G187" s="328"/>
+      <c r="H187" s="328"/>
+      <c r="I187" s="328"/>
+      <c r="J187" s="329"/>
+      <c r="K187" s="301"/>
+      <c r="L187" s="303"/>
+      <c r="M187" s="327"/>
+      <c r="N187" s="329"/>
+      <c r="O187" s="327"/>
+      <c r="P187" s="328"/>
+      <c r="Q187" s="328"/>
+      <c r="R187" s="328"/>
+      <c r="S187" s="328"/>
+      <c r="T187" s="328"/>
+      <c r="U187" s="328"/>
+      <c r="V187" s="328"/>
+      <c r="W187" s="328"/>
+      <c r="X187" s="328"/>
+      <c r="Y187" s="328"/>
+      <c r="Z187" s="328"/>
+      <c r="AA187" s="328"/>
+      <c r="AB187" s="328"/>
+      <c r="AC187" s="328"/>
+      <c r="AD187" s="328"/>
+      <c r="AE187" s="328"/>
+      <c r="AF187" s="328"/>
+      <c r="AG187" s="328"/>
+      <c r="AH187" s="329"/>
     </row>
     <row r="188" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F188" s="345" t="s">
         <v>39</v>
       </c>
-      <c r="G188" s="298"/>
-      <c r="H188" s="298"/>
-      <c r="I188" s="298"/>
-      <c r="J188" s="299"/>
+      <c r="G188" s="296"/>
+      <c r="H188" s="296"/>
+      <c r="I188" s="296"/>
+      <c r="J188" s="297"/>
       <c r="K188" s="345" t="s">
         <v>35</v>
       </c>
-      <c r="L188" s="299"/>
+      <c r="L188" s="297"/>
       <c r="M188" s="345" t="s">
         <v>78</v>
       </c>
-      <c r="N188" s="319"/>
-      <c r="O188" s="317" t="s">
+      <c r="N188" s="326"/>
+      <c r="O188" s="324" t="s">
         <v>493</v>
       </c>
-      <c r="P188" s="318"/>
-      <c r="Q188" s="318"/>
-      <c r="R188" s="318"/>
-      <c r="S188" s="318"/>
-      <c r="T188" s="318"/>
-      <c r="U188" s="318"/>
-      <c r="V188" s="318"/>
-      <c r="W188" s="318"/>
-      <c r="X188" s="318"/>
-      <c r="Y188" s="318"/>
-      <c r="Z188" s="318"/>
-      <c r="AA188" s="318"/>
-      <c r="AB188" s="318"/>
-      <c r="AC188" s="318"/>
-      <c r="AD188" s="318"/>
-      <c r="AE188" s="318"/>
-      <c r="AF188" s="318"/>
-      <c r="AG188" s="318"/>
-      <c r="AH188" s="319"/>
+      <c r="P188" s="325"/>
+      <c r="Q188" s="325"/>
+      <c r="R188" s="325"/>
+      <c r="S188" s="325"/>
+      <c r="T188" s="325"/>
+      <c r="U188" s="325"/>
+      <c r="V188" s="325"/>
+      <c r="W188" s="325"/>
+      <c r="X188" s="325"/>
+      <c r="Y188" s="325"/>
+      <c r="Z188" s="325"/>
+      <c r="AA188" s="325"/>
+      <c r="AB188" s="325"/>
+      <c r="AC188" s="325"/>
+      <c r="AD188" s="325"/>
+      <c r="AE188" s="325"/>
+      <c r="AF188" s="325"/>
+      <c r="AG188" s="325"/>
+      <c r="AH188" s="326"/>
     </row>
     <row r="189" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F189" s="320"/>
-      <c r="G189" s="321"/>
-      <c r="H189" s="321"/>
-      <c r="I189" s="321"/>
-      <c r="J189" s="322"/>
-      <c r="K189" s="303"/>
-      <c r="L189" s="305"/>
-      <c r="M189" s="320"/>
-      <c r="N189" s="322"/>
-      <c r="O189" s="320"/>
-      <c r="P189" s="321"/>
-      <c r="Q189" s="321"/>
-      <c r="R189" s="321"/>
-      <c r="S189" s="321"/>
-      <c r="T189" s="321"/>
-      <c r="U189" s="321"/>
-      <c r="V189" s="321"/>
-      <c r="W189" s="321"/>
-      <c r="X189" s="321"/>
-      <c r="Y189" s="321"/>
-      <c r="Z189" s="321"/>
-      <c r="AA189" s="321"/>
-      <c r="AB189" s="321"/>
-      <c r="AC189" s="321"/>
-      <c r="AD189" s="321"/>
-      <c r="AE189" s="321"/>
-      <c r="AF189" s="321"/>
-      <c r="AG189" s="321"/>
-      <c r="AH189" s="322"/>
+      <c r="F189" s="327"/>
+      <c r="G189" s="328"/>
+      <c r="H189" s="328"/>
+      <c r="I189" s="328"/>
+      <c r="J189" s="329"/>
+      <c r="K189" s="301"/>
+      <c r="L189" s="303"/>
+      <c r="M189" s="327"/>
+      <c r="N189" s="329"/>
+      <c r="O189" s="327"/>
+      <c r="P189" s="328"/>
+      <c r="Q189" s="328"/>
+      <c r="R189" s="328"/>
+      <c r="S189" s="328"/>
+      <c r="T189" s="328"/>
+      <c r="U189" s="328"/>
+      <c r="V189" s="328"/>
+      <c r="W189" s="328"/>
+      <c r="X189" s="328"/>
+      <c r="Y189" s="328"/>
+      <c r="Z189" s="328"/>
+      <c r="AA189" s="328"/>
+      <c r="AB189" s="328"/>
+      <c r="AC189" s="328"/>
+      <c r="AD189" s="328"/>
+      <c r="AE189" s="328"/>
+      <c r="AF189" s="328"/>
+      <c r="AG189" s="328"/>
+      <c r="AH189" s="329"/>
     </row>
     <row r="190" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F190" s="345" t="s">
         <v>136</v>
       </c>
-      <c r="G190" s="298"/>
-      <c r="H190" s="298"/>
-      <c r="I190" s="298"/>
-      <c r="J190" s="299"/>
+      <c r="G190" s="296"/>
+      <c r="H190" s="296"/>
+      <c r="I190" s="296"/>
+      <c r="J190" s="297"/>
       <c r="K190" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="L190" s="299"/>
+      <c r="L190" s="297"/>
       <c r="M190" s="345" t="s">
         <v>71</v>
       </c>
-      <c r="N190" s="319"/>
-      <c r="O190" s="297" t="s">
+      <c r="N190" s="326"/>
+      <c r="O190" s="295" t="s">
         <v>305</v>
       </c>
-      <c r="P190" s="298"/>
-      <c r="Q190" s="298"/>
-      <c r="R190" s="298"/>
-      <c r="S190" s="298"/>
-      <c r="T190" s="298"/>
-      <c r="U190" s="298"/>
-      <c r="V190" s="298"/>
-      <c r="W190" s="298"/>
-      <c r="X190" s="298"/>
-      <c r="Y190" s="298"/>
-      <c r="Z190" s="298"/>
-      <c r="AA190" s="298"/>
-      <c r="AB190" s="298"/>
-      <c r="AC190" s="298"/>
-      <c r="AD190" s="298"/>
-      <c r="AE190" s="298"/>
-      <c r="AF190" s="298"/>
-      <c r="AG190" s="298"/>
-      <c r="AH190" s="299"/>
+      <c r="P190" s="296"/>
+      <c r="Q190" s="296"/>
+      <c r="R190" s="296"/>
+      <c r="S190" s="296"/>
+      <c r="T190" s="296"/>
+      <c r="U190" s="296"/>
+      <c r="V190" s="296"/>
+      <c r="W190" s="296"/>
+      <c r="X190" s="296"/>
+      <c r="Y190" s="296"/>
+      <c r="Z190" s="296"/>
+      <c r="AA190" s="296"/>
+      <c r="AB190" s="296"/>
+      <c r="AC190" s="296"/>
+      <c r="AD190" s="296"/>
+      <c r="AE190" s="296"/>
+      <c r="AF190" s="296"/>
+      <c r="AG190" s="296"/>
+      <c r="AH190" s="297"/>
     </row>
     <row r="191" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F191" s="320"/>
-      <c r="G191" s="321"/>
-      <c r="H191" s="321"/>
-      <c r="I191" s="321"/>
-      <c r="J191" s="322"/>
-      <c r="K191" s="303"/>
-      <c r="L191" s="305"/>
-      <c r="M191" s="320"/>
-      <c r="N191" s="322"/>
-      <c r="O191" s="320"/>
-      <c r="P191" s="321"/>
-      <c r="Q191" s="321"/>
-      <c r="R191" s="321"/>
-      <c r="S191" s="321"/>
-      <c r="T191" s="321"/>
-      <c r="U191" s="321"/>
-      <c r="V191" s="321"/>
-      <c r="W191" s="321"/>
-      <c r="X191" s="321"/>
-      <c r="Y191" s="321"/>
-      <c r="Z191" s="321"/>
-      <c r="AA191" s="321"/>
-      <c r="AB191" s="321"/>
-      <c r="AC191" s="321"/>
-      <c r="AD191" s="321"/>
-      <c r="AE191" s="321"/>
-      <c r="AF191" s="321"/>
-      <c r="AG191" s="321"/>
-      <c r="AH191" s="322"/>
+      <c r="F191" s="327"/>
+      <c r="G191" s="328"/>
+      <c r="H191" s="328"/>
+      <c r="I191" s="328"/>
+      <c r="J191" s="329"/>
+      <c r="K191" s="301"/>
+      <c r="L191" s="303"/>
+      <c r="M191" s="327"/>
+      <c r="N191" s="329"/>
+      <c r="O191" s="327"/>
+      <c r="P191" s="328"/>
+      <c r="Q191" s="328"/>
+      <c r="R191" s="328"/>
+      <c r="S191" s="328"/>
+      <c r="T191" s="328"/>
+      <c r="U191" s="328"/>
+      <c r="V191" s="328"/>
+      <c r="W191" s="328"/>
+      <c r="X191" s="328"/>
+      <c r="Y191" s="328"/>
+      <c r="Z191" s="328"/>
+      <c r="AA191" s="328"/>
+      <c r="AB191" s="328"/>
+      <c r="AC191" s="328"/>
+      <c r="AD191" s="328"/>
+      <c r="AE191" s="328"/>
+      <c r="AF191" s="328"/>
+      <c r="AG191" s="328"/>
+      <c r="AH191" s="329"/>
     </row>
     <row r="192" spans="6:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F192" s="314" t="s">
+      <c r="F192" s="317" t="s">
         <v>137</v>
       </c>
-      <c r="G192" s="262"/>
-      <c r="H192" s="262"/>
-      <c r="I192" s="262"/>
-      <c r="J192" s="263"/>
-      <c r="K192" s="346" t="s">
+      <c r="G192" s="287"/>
+      <c r="H192" s="287"/>
+      <c r="I192" s="287"/>
+      <c r="J192" s="288"/>
+      <c r="K192" s="353" t="s">
         <v>46</v>
       </c>
-      <c r="L192" s="372"/>
-      <c r="M192" s="346" t="s">
+      <c r="L192" s="354"/>
+      <c r="M192" s="353" t="s">
         <v>71</v>
       </c>
-      <c r="N192" s="344"/>
-      <c r="O192" s="314" t="s">
+      <c r="N192" s="358"/>
+      <c r="O192" s="317" t="s">
         <v>306</v>
       </c>
-      <c r="P192" s="262"/>
-      <c r="Q192" s="262"/>
-      <c r="R192" s="262"/>
-      <c r="S192" s="262"/>
-      <c r="T192" s="262"/>
-      <c r="U192" s="262"/>
-      <c r="V192" s="262"/>
-      <c r="W192" s="262"/>
-      <c r="X192" s="262"/>
-      <c r="Y192" s="262"/>
-      <c r="Z192" s="262"/>
-      <c r="AA192" s="262"/>
-      <c r="AB192" s="262"/>
-      <c r="AC192" s="262"/>
-      <c r="AD192" s="262"/>
-      <c r="AE192" s="262"/>
-      <c r="AF192" s="262"/>
-      <c r="AG192" s="262"/>
-      <c r="AH192" s="263"/>
+      <c r="P192" s="287"/>
+      <c r="Q192" s="287"/>
+      <c r="R192" s="287"/>
+      <c r="S192" s="287"/>
+      <c r="T192" s="287"/>
+      <c r="U192" s="287"/>
+      <c r="V192" s="287"/>
+      <c r="W192" s="287"/>
+      <c r="X192" s="287"/>
+      <c r="Y192" s="287"/>
+      <c r="Z192" s="287"/>
+      <c r="AA192" s="287"/>
+      <c r="AB192" s="287"/>
+      <c r="AC192" s="287"/>
+      <c r="AD192" s="287"/>
+      <c r="AE192" s="287"/>
+      <c r="AF192" s="287"/>
+      <c r="AG192" s="287"/>
+      <c r="AH192" s="288"/>
     </row>
     <row r="193" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F193" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="G193" s="298"/>
-      <c r="H193" s="298"/>
-      <c r="I193" s="298"/>
-      <c r="J193" s="299"/>
+      <c r="G193" s="296"/>
+      <c r="H193" s="296"/>
+      <c r="I193" s="296"/>
+      <c r="J193" s="297"/>
       <c r="K193" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="L193" s="299"/>
+      <c r="L193" s="297"/>
       <c r="M193" s="345" t="s">
         <v>76</v>
       </c>
-      <c r="N193" s="319"/>
-      <c r="O193" s="297" t="s">
+      <c r="N193" s="326"/>
+      <c r="O193" s="295" t="s">
         <v>492</v>
       </c>
-      <c r="P193" s="318"/>
-      <c r="Q193" s="318"/>
-      <c r="R193" s="318"/>
-      <c r="S193" s="318"/>
-      <c r="T193" s="318"/>
-      <c r="U193" s="318"/>
-      <c r="V193" s="318"/>
-      <c r="W193" s="318"/>
-      <c r="X193" s="318"/>
-      <c r="Y193" s="318"/>
-      <c r="Z193" s="318"/>
-      <c r="AA193" s="318"/>
-      <c r="AB193" s="318"/>
-      <c r="AC193" s="318"/>
-      <c r="AD193" s="318"/>
-      <c r="AE193" s="318"/>
-      <c r="AF193" s="318"/>
-      <c r="AG193" s="318"/>
-      <c r="AH193" s="319"/>
+      <c r="P193" s="325"/>
+      <c r="Q193" s="325"/>
+      <c r="R193" s="325"/>
+      <c r="S193" s="325"/>
+      <c r="T193" s="325"/>
+      <c r="U193" s="325"/>
+      <c r="V193" s="325"/>
+      <c r="W193" s="325"/>
+      <c r="X193" s="325"/>
+      <c r="Y193" s="325"/>
+      <c r="Z193" s="325"/>
+      <c r="AA193" s="325"/>
+      <c r="AB193" s="325"/>
+      <c r="AC193" s="325"/>
+      <c r="AD193" s="325"/>
+      <c r="AE193" s="325"/>
+      <c r="AF193" s="325"/>
+      <c r="AG193" s="325"/>
+      <c r="AH193" s="326"/>
     </row>
     <row r="194" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F194" s="320"/>
-      <c r="G194" s="321"/>
-      <c r="H194" s="321"/>
-      <c r="I194" s="321"/>
-      <c r="J194" s="322"/>
-      <c r="K194" s="303"/>
-      <c r="L194" s="305"/>
-      <c r="M194" s="320"/>
-      <c r="N194" s="322"/>
-      <c r="O194" s="320"/>
-      <c r="P194" s="321"/>
-      <c r="Q194" s="321"/>
-      <c r="R194" s="321"/>
-      <c r="S194" s="321"/>
-      <c r="T194" s="321"/>
-      <c r="U194" s="321"/>
-      <c r="V194" s="321"/>
-      <c r="W194" s="321"/>
-      <c r="X194" s="321"/>
-      <c r="Y194" s="321"/>
-      <c r="Z194" s="321"/>
-      <c r="AA194" s="321"/>
-      <c r="AB194" s="321"/>
-      <c r="AC194" s="321"/>
-      <c r="AD194" s="321"/>
-      <c r="AE194" s="321"/>
-      <c r="AF194" s="321"/>
-      <c r="AG194" s="321"/>
-      <c r="AH194" s="322"/>
+      <c r="F194" s="327"/>
+      <c r="G194" s="328"/>
+      <c r="H194" s="328"/>
+      <c r="I194" s="328"/>
+      <c r="J194" s="329"/>
+      <c r="K194" s="301"/>
+      <c r="L194" s="303"/>
+      <c r="M194" s="327"/>
+      <c r="N194" s="329"/>
+      <c r="O194" s="327"/>
+      <c r="P194" s="328"/>
+      <c r="Q194" s="328"/>
+      <c r="R194" s="328"/>
+      <c r="S194" s="328"/>
+      <c r="T194" s="328"/>
+      <c r="U194" s="328"/>
+      <c r="V194" s="328"/>
+      <c r="W194" s="328"/>
+      <c r="X194" s="328"/>
+      <c r="Y194" s="328"/>
+      <c r="Z194" s="328"/>
+      <c r="AA194" s="328"/>
+      <c r="AB194" s="328"/>
+      <c r="AC194" s="328"/>
+      <c r="AD194" s="328"/>
+      <c r="AE194" s="328"/>
+      <c r="AF194" s="328"/>
+      <c r="AG194" s="328"/>
+      <c r="AH194" s="329"/>
     </row>
     <row r="195" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F195" s="261" t="s">
+      <c r="F195" s="286" t="s">
         <v>42</v>
       </c>
-      <c r="G195" s="262"/>
-      <c r="H195" s="262"/>
-      <c r="I195" s="262"/>
-      <c r="J195" s="263"/>
-      <c r="K195" s="346" t="s">
+      <c r="G195" s="287"/>
+      <c r="H195" s="287"/>
+      <c r="I195" s="287"/>
+      <c r="J195" s="288"/>
+      <c r="K195" s="353" t="s">
         <v>46</v>
       </c>
-      <c r="L195" s="372"/>
-      <c r="M195" s="346" t="s">
+      <c r="L195" s="354"/>
+      <c r="M195" s="353" t="s">
         <v>75</v>
       </c>
-      <c r="N195" s="344"/>
-      <c r="O195" s="314" t="s">
+      <c r="N195" s="358"/>
+      <c r="O195" s="317" t="s">
         <v>306</v>
       </c>
-      <c r="P195" s="262"/>
-      <c r="Q195" s="262"/>
-      <c r="R195" s="262"/>
-      <c r="S195" s="262"/>
-      <c r="T195" s="262"/>
-      <c r="U195" s="262"/>
-      <c r="V195" s="262"/>
-      <c r="W195" s="262"/>
-      <c r="X195" s="262"/>
-      <c r="Y195" s="262"/>
-      <c r="Z195" s="262"/>
-      <c r="AA195" s="262"/>
-      <c r="AB195" s="262"/>
-      <c r="AC195" s="262"/>
-      <c r="AD195" s="262"/>
-      <c r="AE195" s="262"/>
-      <c r="AF195" s="262"/>
-      <c r="AG195" s="262"/>
-      <c r="AH195" s="263"/>
+      <c r="P195" s="287"/>
+      <c r="Q195" s="287"/>
+      <c r="R195" s="287"/>
+      <c r="S195" s="287"/>
+      <c r="T195" s="287"/>
+      <c r="U195" s="287"/>
+      <c r="V195" s="287"/>
+      <c r="W195" s="287"/>
+      <c r="X195" s="287"/>
+      <c r="Y195" s="287"/>
+      <c r="Z195" s="287"/>
+      <c r="AA195" s="287"/>
+      <c r="AB195" s="287"/>
+      <c r="AC195" s="287"/>
+      <c r="AD195" s="287"/>
+      <c r="AE195" s="287"/>
+      <c r="AF195" s="287"/>
+      <c r="AG195" s="287"/>
+      <c r="AH195" s="288"/>
     </row>
     <row r="196" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E196" s="30"/>
-      <c r="F196" s="317" t="s">
+      <c r="F196" s="324" t="s">
         <v>267</v>
       </c>
-      <c r="G196" s="318"/>
-      <c r="H196" s="318"/>
-      <c r="I196" s="318"/>
-      <c r="J196" s="319"/>
-      <c r="K196" s="359" t="s">
+      <c r="G196" s="325"/>
+      <c r="H196" s="325"/>
+      <c r="I196" s="325"/>
+      <c r="J196" s="326"/>
+      <c r="K196" s="336" t="s">
         <v>46</v>
       </c>
-      <c r="L196" s="360"/>
+      <c r="L196" s="337"/>
       <c r="M196" s="345" t="s">
         <v>75</v>
       </c>
-      <c r="N196" s="319"/>
-      <c r="O196" s="297" t="s">
+      <c r="N196" s="326"/>
+      <c r="O196" s="295" t="s">
         <v>306</v>
       </c>
-      <c r="P196" s="298"/>
-      <c r="Q196" s="298"/>
-      <c r="R196" s="298"/>
-      <c r="S196" s="298"/>
-      <c r="T196" s="298"/>
-      <c r="U196" s="298"/>
-      <c r="V196" s="298"/>
-      <c r="W196" s="298"/>
-      <c r="X196" s="298"/>
-      <c r="Y196" s="298"/>
-      <c r="Z196" s="298"/>
-      <c r="AA196" s="298"/>
-      <c r="AB196" s="298"/>
-      <c r="AC196" s="298"/>
-      <c r="AD196" s="298"/>
-      <c r="AE196" s="298"/>
-      <c r="AF196" s="298"/>
-      <c r="AG196" s="298"/>
-      <c r="AH196" s="299"/>
+      <c r="P196" s="296"/>
+      <c r="Q196" s="296"/>
+      <c r="R196" s="296"/>
+      <c r="S196" s="296"/>
+      <c r="T196" s="296"/>
+      <c r="U196" s="296"/>
+      <c r="V196" s="296"/>
+      <c r="W196" s="296"/>
+      <c r="X196" s="296"/>
+      <c r="Y196" s="296"/>
+      <c r="Z196" s="296"/>
+      <c r="AA196" s="296"/>
+      <c r="AB196" s="296"/>
+      <c r="AC196" s="296"/>
+      <c r="AD196" s="296"/>
+      <c r="AE196" s="296"/>
+      <c r="AF196" s="296"/>
+      <c r="AG196" s="296"/>
+      <c r="AH196" s="297"/>
     </row>
     <row r="197" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E197" s="30"/>
-      <c r="F197" s="320"/>
-      <c r="G197" s="321"/>
-      <c r="H197" s="321"/>
-      <c r="I197" s="321"/>
-      <c r="J197" s="322"/>
-      <c r="K197" s="367"/>
-      <c r="L197" s="369"/>
-      <c r="M197" s="320"/>
-      <c r="N197" s="322"/>
-      <c r="O197" s="320"/>
-      <c r="P197" s="321"/>
-      <c r="Q197" s="321"/>
-      <c r="R197" s="321"/>
-      <c r="S197" s="321"/>
-      <c r="T197" s="321"/>
-      <c r="U197" s="321"/>
-      <c r="V197" s="321"/>
-      <c r="W197" s="321"/>
-      <c r="X197" s="321"/>
-      <c r="Y197" s="321"/>
-      <c r="Z197" s="321"/>
-      <c r="AA197" s="321"/>
-      <c r="AB197" s="321"/>
-      <c r="AC197" s="321"/>
-      <c r="AD197" s="321"/>
-      <c r="AE197" s="321"/>
-      <c r="AF197" s="321"/>
-      <c r="AG197" s="321"/>
-      <c r="AH197" s="322"/>
+      <c r="F197" s="327"/>
+      <c r="G197" s="328"/>
+      <c r="H197" s="328"/>
+      <c r="I197" s="328"/>
+      <c r="J197" s="329"/>
+      <c r="K197" s="333"/>
+      <c r="L197" s="335"/>
+      <c r="M197" s="327"/>
+      <c r="N197" s="329"/>
+      <c r="O197" s="327"/>
+      <c r="P197" s="328"/>
+      <c r="Q197" s="328"/>
+      <c r="R197" s="328"/>
+      <c r="S197" s="328"/>
+      <c r="T197" s="328"/>
+      <c r="U197" s="328"/>
+      <c r="V197" s="328"/>
+      <c r="W197" s="328"/>
+      <c r="X197" s="328"/>
+      <c r="Y197" s="328"/>
+      <c r="Z197" s="328"/>
+      <c r="AA197" s="328"/>
+      <c r="AB197" s="328"/>
+      <c r="AC197" s="328"/>
+      <c r="AD197" s="328"/>
+      <c r="AE197" s="328"/>
+      <c r="AF197" s="328"/>
+      <c r="AG197" s="328"/>
+      <c r="AH197" s="329"/>
     </row>
     <row r="198" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="199" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -43326,689 +43345,689 @@
     </row>
     <row r="201" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="202" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F202" s="376" t="s">
+      <c r="F202" s="339" t="s">
         <v>623</v>
       </c>
-      <c r="G202" s="377"/>
-      <c r="H202" s="377"/>
-      <c r="I202" s="377"/>
-      <c r="J202" s="378"/>
-      <c r="K202" s="363" t="s">
+      <c r="G202" s="340"/>
+      <c r="H202" s="340"/>
+      <c r="I202" s="340"/>
+      <c r="J202" s="341"/>
+      <c r="K202" s="356" t="s">
         <v>30</v>
       </c>
-      <c r="L202" s="364"/>
-      <c r="M202" s="363" t="s">
+      <c r="L202" s="357"/>
+      <c r="M202" s="356" t="s">
         <v>31</v>
       </c>
-      <c r="N202" s="364"/>
-      <c r="O202" s="258" t="s">
+      <c r="N202" s="357"/>
+      <c r="O202" s="283" t="s">
         <v>302</v>
       </c>
-      <c r="P202" s="259"/>
-      <c r="Q202" s="259"/>
-      <c r="R202" s="259"/>
-      <c r="S202" s="259"/>
-      <c r="T202" s="259"/>
-      <c r="U202" s="259"/>
-      <c r="V202" s="259"/>
-      <c r="W202" s="259"/>
-      <c r="X202" s="259"/>
-      <c r="Y202" s="259"/>
-      <c r="Z202" s="259"/>
-      <c r="AA202" s="259"/>
-      <c r="AB202" s="259"/>
-      <c r="AC202" s="259"/>
-      <c r="AD202" s="259"/>
-      <c r="AE202" s="259"/>
-      <c r="AF202" s="259"/>
-      <c r="AG202" s="259"/>
-      <c r="AH202" s="260"/>
+      <c r="P202" s="284"/>
+      <c r="Q202" s="284"/>
+      <c r="R202" s="284"/>
+      <c r="S202" s="284"/>
+      <c r="T202" s="284"/>
+      <c r="U202" s="284"/>
+      <c r="V202" s="284"/>
+      <c r="W202" s="284"/>
+      <c r="X202" s="284"/>
+      <c r="Y202" s="284"/>
+      <c r="Z202" s="284"/>
+      <c r="AA202" s="284"/>
+      <c r="AB202" s="284"/>
+      <c r="AC202" s="284"/>
+      <c r="AD202" s="284"/>
+      <c r="AE202" s="284"/>
+      <c r="AF202" s="284"/>
+      <c r="AG202" s="284"/>
+      <c r="AH202" s="285"/>
     </row>
     <row r="203" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F203" s="317" t="s">
+      <c r="F203" s="324" t="s">
         <v>282</v>
       </c>
-      <c r="G203" s="365"/>
-      <c r="H203" s="365"/>
-      <c r="I203" s="365"/>
-      <c r="J203" s="366"/>
+      <c r="G203" s="331"/>
+      <c r="H203" s="331"/>
+      <c r="I203" s="331"/>
+      <c r="J203" s="332"/>
       <c r="K203" s="345" t="s">
         <v>32</v>
       </c>
-      <c r="L203" s="299"/>
+      <c r="L203" s="297"/>
       <c r="M203" s="345" t="s">
         <v>33</v>
       </c>
-      <c r="N203" s="299"/>
-      <c r="O203" s="317" t="s">
+      <c r="N203" s="297"/>
+      <c r="O203" s="324" t="s">
         <v>284</v>
       </c>
-      <c r="P203" s="365"/>
-      <c r="Q203" s="365"/>
-      <c r="R203" s="365"/>
-      <c r="S203" s="365"/>
-      <c r="T203" s="365"/>
-      <c r="U203" s="365"/>
-      <c r="V203" s="365"/>
-      <c r="W203" s="365"/>
-      <c r="X203" s="365"/>
-      <c r="Y203" s="365"/>
-      <c r="Z203" s="365"/>
-      <c r="AA203" s="365"/>
-      <c r="AB203" s="365"/>
-      <c r="AC203" s="365"/>
-      <c r="AD203" s="365"/>
-      <c r="AE203" s="365"/>
-      <c r="AF203" s="365"/>
-      <c r="AG203" s="365"/>
-      <c r="AH203" s="366"/>
+      <c r="P203" s="331"/>
+      <c r="Q203" s="331"/>
+      <c r="R203" s="331"/>
+      <c r="S203" s="331"/>
+      <c r="T203" s="331"/>
+      <c r="U203" s="331"/>
+      <c r="V203" s="331"/>
+      <c r="W203" s="331"/>
+      <c r="X203" s="331"/>
+      <c r="Y203" s="331"/>
+      <c r="Z203" s="331"/>
+      <c r="AA203" s="331"/>
+      <c r="AB203" s="331"/>
+      <c r="AC203" s="331"/>
+      <c r="AD203" s="331"/>
+      <c r="AE203" s="331"/>
+      <c r="AF203" s="331"/>
+      <c r="AG203" s="331"/>
+      <c r="AH203" s="332"/>
     </row>
     <row r="204" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F204" s="367"/>
-      <c r="G204" s="368"/>
-      <c r="H204" s="368"/>
-      <c r="I204" s="368"/>
-      <c r="J204" s="369"/>
-      <c r="K204" s="303"/>
-      <c r="L204" s="305"/>
-      <c r="M204" s="303"/>
-      <c r="N204" s="305"/>
-      <c r="O204" s="367"/>
-      <c r="P204" s="368"/>
-      <c r="Q204" s="368"/>
-      <c r="R204" s="368"/>
-      <c r="S204" s="368"/>
-      <c r="T204" s="368"/>
-      <c r="U204" s="368"/>
-      <c r="V204" s="368"/>
-      <c r="W204" s="368"/>
-      <c r="X204" s="368"/>
-      <c r="Y204" s="368"/>
-      <c r="Z204" s="368"/>
-      <c r="AA204" s="368"/>
-      <c r="AB204" s="368"/>
-      <c r="AC204" s="368"/>
-      <c r="AD204" s="368"/>
-      <c r="AE204" s="368"/>
-      <c r="AF204" s="368"/>
-      <c r="AG204" s="368"/>
-      <c r="AH204" s="369"/>
+      <c r="F204" s="333"/>
+      <c r="G204" s="334"/>
+      <c r="H204" s="334"/>
+      <c r="I204" s="334"/>
+      <c r="J204" s="335"/>
+      <c r="K204" s="301"/>
+      <c r="L204" s="303"/>
+      <c r="M204" s="301"/>
+      <c r="N204" s="303"/>
+      <c r="O204" s="333"/>
+      <c r="P204" s="334"/>
+      <c r="Q204" s="334"/>
+      <c r="R204" s="334"/>
+      <c r="S204" s="334"/>
+      <c r="T204" s="334"/>
+      <c r="U204" s="334"/>
+      <c r="V204" s="334"/>
+      <c r="W204" s="334"/>
+      <c r="X204" s="334"/>
+      <c r="Y204" s="334"/>
+      <c r="Z204" s="334"/>
+      <c r="AA204" s="334"/>
+      <c r="AB204" s="334"/>
+      <c r="AC204" s="334"/>
+      <c r="AD204" s="334"/>
+      <c r="AE204" s="334"/>
+      <c r="AF204" s="334"/>
+      <c r="AG204" s="334"/>
+      <c r="AH204" s="335"/>
     </row>
     <row r="205" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F205" s="359" t="s">
+      <c r="F205" s="336" t="s">
         <v>40</v>
       </c>
-      <c r="G205" s="370"/>
-      <c r="H205" s="370"/>
-      <c r="I205" s="370"/>
-      <c r="J205" s="360"/>
+      <c r="G205" s="338"/>
+      <c r="H205" s="338"/>
+      <c r="I205" s="338"/>
+      <c r="J205" s="337"/>
       <c r="K205" s="345" t="s">
         <v>35</v>
       </c>
-      <c r="L205" s="299"/>
+      <c r="L205" s="297"/>
       <c r="M205" s="345" t="s">
         <v>33</v>
       </c>
-      <c r="N205" s="299"/>
-      <c r="O205" s="317" t="s">
+      <c r="N205" s="297"/>
+      <c r="O205" s="324" t="s">
         <v>487</v>
       </c>
-      <c r="P205" s="365"/>
-      <c r="Q205" s="365"/>
-      <c r="R205" s="365"/>
-      <c r="S205" s="365"/>
-      <c r="T205" s="365"/>
-      <c r="U205" s="365"/>
-      <c r="V205" s="365"/>
-      <c r="W205" s="365"/>
-      <c r="X205" s="365"/>
-      <c r="Y205" s="365"/>
-      <c r="Z205" s="365"/>
-      <c r="AA205" s="365"/>
-      <c r="AB205" s="365"/>
-      <c r="AC205" s="365"/>
-      <c r="AD205" s="365"/>
-      <c r="AE205" s="365"/>
-      <c r="AF205" s="365"/>
-      <c r="AG205" s="365"/>
-      <c r="AH205" s="366"/>
+      <c r="P205" s="331"/>
+      <c r="Q205" s="331"/>
+      <c r="R205" s="331"/>
+      <c r="S205" s="331"/>
+      <c r="T205" s="331"/>
+      <c r="U205" s="331"/>
+      <c r="V205" s="331"/>
+      <c r="W205" s="331"/>
+      <c r="X205" s="331"/>
+      <c r="Y205" s="331"/>
+      <c r="Z205" s="331"/>
+      <c r="AA205" s="331"/>
+      <c r="AB205" s="331"/>
+      <c r="AC205" s="331"/>
+      <c r="AD205" s="331"/>
+      <c r="AE205" s="331"/>
+      <c r="AF205" s="331"/>
+      <c r="AG205" s="331"/>
+      <c r="AH205" s="332"/>
     </row>
     <row r="206" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F206" s="367"/>
-      <c r="G206" s="368"/>
-      <c r="H206" s="368"/>
-      <c r="I206" s="368"/>
-      <c r="J206" s="369"/>
-      <c r="K206" s="303"/>
-      <c r="L206" s="305"/>
-      <c r="M206" s="303"/>
-      <c r="N206" s="305"/>
-      <c r="O206" s="367"/>
-      <c r="P206" s="368"/>
-      <c r="Q206" s="368"/>
-      <c r="R206" s="368"/>
-      <c r="S206" s="368"/>
-      <c r="T206" s="368"/>
-      <c r="U206" s="368"/>
-      <c r="V206" s="368"/>
-      <c r="W206" s="368"/>
-      <c r="X206" s="368"/>
-      <c r="Y206" s="368"/>
-      <c r="Z206" s="368"/>
-      <c r="AA206" s="368"/>
-      <c r="AB206" s="368"/>
-      <c r="AC206" s="368"/>
-      <c r="AD206" s="368"/>
-      <c r="AE206" s="368"/>
-      <c r="AF206" s="368"/>
-      <c r="AG206" s="368"/>
-      <c r="AH206" s="369"/>
+      <c r="F206" s="333"/>
+      <c r="G206" s="334"/>
+      <c r="H206" s="334"/>
+      <c r="I206" s="334"/>
+      <c r="J206" s="335"/>
+      <c r="K206" s="301"/>
+      <c r="L206" s="303"/>
+      <c r="M206" s="301"/>
+      <c r="N206" s="303"/>
+      <c r="O206" s="333"/>
+      <c r="P206" s="334"/>
+      <c r="Q206" s="334"/>
+      <c r="R206" s="334"/>
+      <c r="S206" s="334"/>
+      <c r="T206" s="334"/>
+      <c r="U206" s="334"/>
+      <c r="V206" s="334"/>
+      <c r="W206" s="334"/>
+      <c r="X206" s="334"/>
+      <c r="Y206" s="334"/>
+      <c r="Z206" s="334"/>
+      <c r="AA206" s="334"/>
+      <c r="AB206" s="334"/>
+      <c r="AC206" s="334"/>
+      <c r="AD206" s="334"/>
+      <c r="AE206" s="334"/>
+      <c r="AF206" s="334"/>
+      <c r="AG206" s="334"/>
+      <c r="AH206" s="335"/>
     </row>
     <row r="207" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F207" s="359" t="s">
+      <c r="F207" s="336" t="s">
         <v>41</v>
       </c>
-      <c r="G207" s="370"/>
-      <c r="H207" s="370"/>
-      <c r="I207" s="370"/>
-      <c r="J207" s="360"/>
-      <c r="K207" s="359" t="s">
+      <c r="G207" s="338"/>
+      <c r="H207" s="338"/>
+      <c r="I207" s="338"/>
+      <c r="J207" s="337"/>
+      <c r="K207" s="336" t="s">
         <v>35</v>
       </c>
-      <c r="L207" s="360"/>
-      <c r="M207" s="359" t="s">
+      <c r="L207" s="337"/>
+      <c r="M207" s="336" t="s">
         <v>33</v>
       </c>
-      <c r="N207" s="360"/>
-      <c r="O207" s="317" t="s">
+      <c r="N207" s="337"/>
+      <c r="O207" s="324" t="s">
         <v>488</v>
       </c>
-      <c r="P207" s="365"/>
-      <c r="Q207" s="365"/>
-      <c r="R207" s="365"/>
-      <c r="S207" s="365"/>
-      <c r="T207" s="365"/>
-      <c r="U207" s="365"/>
-      <c r="V207" s="365"/>
-      <c r="W207" s="365"/>
-      <c r="X207" s="365"/>
-      <c r="Y207" s="365"/>
-      <c r="Z207" s="365"/>
-      <c r="AA207" s="365"/>
-      <c r="AB207" s="365"/>
-      <c r="AC207" s="365"/>
-      <c r="AD207" s="365"/>
-      <c r="AE207" s="365"/>
-      <c r="AF207" s="365"/>
-      <c r="AG207" s="365"/>
-      <c r="AH207" s="366"/>
+      <c r="P207" s="331"/>
+      <c r="Q207" s="331"/>
+      <c r="R207" s="331"/>
+      <c r="S207" s="331"/>
+      <c r="T207" s="331"/>
+      <c r="U207" s="331"/>
+      <c r="V207" s="331"/>
+      <c r="W207" s="331"/>
+      <c r="X207" s="331"/>
+      <c r="Y207" s="331"/>
+      <c r="Z207" s="331"/>
+      <c r="AA207" s="331"/>
+      <c r="AB207" s="331"/>
+      <c r="AC207" s="331"/>
+      <c r="AD207" s="331"/>
+      <c r="AE207" s="331"/>
+      <c r="AF207" s="331"/>
+      <c r="AG207" s="331"/>
+      <c r="AH207" s="332"/>
     </row>
     <row r="208" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F208" s="367"/>
-      <c r="G208" s="368"/>
-      <c r="H208" s="368"/>
-      <c r="I208" s="368"/>
-      <c r="J208" s="369"/>
-      <c r="K208" s="361"/>
-      <c r="L208" s="362"/>
-      <c r="M208" s="361"/>
-      <c r="N208" s="362"/>
-      <c r="O208" s="367"/>
-      <c r="P208" s="368"/>
-      <c r="Q208" s="368"/>
-      <c r="R208" s="368"/>
-      <c r="S208" s="368"/>
-      <c r="T208" s="368"/>
-      <c r="U208" s="368"/>
-      <c r="V208" s="368"/>
-      <c r="W208" s="368"/>
-      <c r="X208" s="368"/>
-      <c r="Y208" s="368"/>
-      <c r="Z208" s="368"/>
-      <c r="AA208" s="368"/>
-      <c r="AB208" s="368"/>
-      <c r="AC208" s="368"/>
-      <c r="AD208" s="368"/>
-      <c r="AE208" s="368"/>
-      <c r="AF208" s="368"/>
-      <c r="AG208" s="368"/>
-      <c r="AH208" s="369"/>
+      <c r="F208" s="333"/>
+      <c r="G208" s="334"/>
+      <c r="H208" s="334"/>
+      <c r="I208" s="334"/>
+      <c r="J208" s="335"/>
+      <c r="K208" s="359"/>
+      <c r="L208" s="360"/>
+      <c r="M208" s="359"/>
+      <c r="N208" s="360"/>
+      <c r="O208" s="333"/>
+      <c r="P208" s="334"/>
+      <c r="Q208" s="334"/>
+      <c r="R208" s="334"/>
+      <c r="S208" s="334"/>
+      <c r="T208" s="334"/>
+      <c r="U208" s="334"/>
+      <c r="V208" s="334"/>
+      <c r="W208" s="334"/>
+      <c r="X208" s="334"/>
+      <c r="Y208" s="334"/>
+      <c r="Z208" s="334"/>
+      <c r="AA208" s="334"/>
+      <c r="AB208" s="334"/>
+      <c r="AC208" s="334"/>
+      <c r="AD208" s="334"/>
+      <c r="AE208" s="334"/>
+      <c r="AF208" s="334"/>
+      <c r="AG208" s="334"/>
+      <c r="AH208" s="335"/>
     </row>
     <row r="209" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F209" s="317" t="s">
+      <c r="F209" s="324" t="s">
         <v>283</v>
       </c>
-      <c r="G209" s="365"/>
-      <c r="H209" s="365"/>
-      <c r="I209" s="365"/>
-      <c r="J209" s="366"/>
+      <c r="G209" s="331"/>
+      <c r="H209" s="331"/>
+      <c r="I209" s="331"/>
+      <c r="J209" s="332"/>
       <c r="K209" s="345" t="s">
         <v>35</v>
       </c>
-      <c r="L209" s="299"/>
+      <c r="L209" s="297"/>
       <c r="M209" s="345" t="s">
         <v>33</v>
       </c>
-      <c r="N209" s="299"/>
-      <c r="O209" s="317" t="s">
+      <c r="N209" s="297"/>
+      <c r="O209" s="324" t="s">
         <v>489</v>
       </c>
-      <c r="P209" s="365"/>
-      <c r="Q209" s="365"/>
-      <c r="R209" s="365"/>
-      <c r="S209" s="365"/>
-      <c r="T209" s="365"/>
-      <c r="U209" s="365"/>
-      <c r="V209" s="365"/>
-      <c r="W209" s="365"/>
-      <c r="X209" s="365"/>
-      <c r="Y209" s="365"/>
-      <c r="Z209" s="365"/>
-      <c r="AA209" s="365"/>
-      <c r="AB209" s="365"/>
-      <c r="AC209" s="365"/>
-      <c r="AD209" s="365"/>
-      <c r="AE209" s="365"/>
-      <c r="AF209" s="365"/>
-      <c r="AG209" s="365"/>
-      <c r="AH209" s="366"/>
+      <c r="P209" s="331"/>
+      <c r="Q209" s="331"/>
+      <c r="R209" s="331"/>
+      <c r="S209" s="331"/>
+      <c r="T209" s="331"/>
+      <c r="U209" s="331"/>
+      <c r="V209" s="331"/>
+      <c r="W209" s="331"/>
+      <c r="X209" s="331"/>
+      <c r="Y209" s="331"/>
+      <c r="Z209" s="331"/>
+      <c r="AA209" s="331"/>
+      <c r="AB209" s="331"/>
+      <c r="AC209" s="331"/>
+      <c r="AD209" s="331"/>
+      <c r="AE209" s="331"/>
+      <c r="AF209" s="331"/>
+      <c r="AG209" s="331"/>
+      <c r="AH209" s="332"/>
     </row>
     <row r="210" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F210" s="367"/>
-      <c r="G210" s="368"/>
-      <c r="H210" s="368"/>
-      <c r="I210" s="368"/>
-      <c r="J210" s="369"/>
-      <c r="K210" s="303"/>
-      <c r="L210" s="305"/>
-      <c r="M210" s="303"/>
-      <c r="N210" s="305"/>
-      <c r="O210" s="367"/>
-      <c r="P210" s="368"/>
-      <c r="Q210" s="368"/>
-      <c r="R210" s="368"/>
-      <c r="S210" s="368"/>
-      <c r="T210" s="368"/>
-      <c r="U210" s="368"/>
-      <c r="V210" s="368"/>
-      <c r="W210" s="368"/>
-      <c r="X210" s="368"/>
-      <c r="Y210" s="368"/>
-      <c r="Z210" s="368"/>
-      <c r="AA210" s="368"/>
-      <c r="AB210" s="368"/>
-      <c r="AC210" s="368"/>
-      <c r="AD210" s="368"/>
-      <c r="AE210" s="368"/>
-      <c r="AF210" s="368"/>
-      <c r="AG210" s="368"/>
-      <c r="AH210" s="369"/>
+      <c r="F210" s="333"/>
+      <c r="G210" s="334"/>
+      <c r="H210" s="334"/>
+      <c r="I210" s="334"/>
+      <c r="J210" s="335"/>
+      <c r="K210" s="301"/>
+      <c r="L210" s="303"/>
+      <c r="M210" s="301"/>
+      <c r="N210" s="303"/>
+      <c r="O210" s="333"/>
+      <c r="P210" s="334"/>
+      <c r="Q210" s="334"/>
+      <c r="R210" s="334"/>
+      <c r="S210" s="334"/>
+      <c r="T210" s="334"/>
+      <c r="U210" s="334"/>
+      <c r="V210" s="334"/>
+      <c r="W210" s="334"/>
+      <c r="X210" s="334"/>
+      <c r="Y210" s="334"/>
+      <c r="Z210" s="334"/>
+      <c r="AA210" s="334"/>
+      <c r="AB210" s="334"/>
+      <c r="AC210" s="334"/>
+      <c r="AD210" s="334"/>
+      <c r="AE210" s="334"/>
+      <c r="AF210" s="334"/>
+      <c r="AG210" s="334"/>
+      <c r="AH210" s="335"/>
     </row>
     <row r="211" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F211" s="261" t="s">
+      <c r="F211" s="286" t="s">
         <v>38</v>
       </c>
-      <c r="G211" s="262"/>
-      <c r="H211" s="262"/>
-      <c r="I211" s="262"/>
-      <c r="J211" s="263"/>
-      <c r="K211" s="228" t="s">
+      <c r="G211" s="287"/>
+      <c r="H211" s="287"/>
+      <c r="I211" s="287"/>
+      <c r="J211" s="288"/>
+      <c r="K211" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="L211" s="230"/>
-      <c r="M211" s="228" t="s">
+      <c r="L211" s="193"/>
+      <c r="M211" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="N211" s="230"/>
-      <c r="O211" s="341" t="s">
+      <c r="N211" s="193"/>
+      <c r="O211" s="355" t="s">
         <v>335</v>
       </c>
-      <c r="P211" s="349"/>
-      <c r="Q211" s="349"/>
-      <c r="R211" s="349"/>
-      <c r="S211" s="349"/>
-      <c r="T211" s="349"/>
-      <c r="U211" s="349"/>
-      <c r="V211" s="349"/>
-      <c r="W211" s="349"/>
-      <c r="X211" s="349"/>
-      <c r="Y211" s="349"/>
-      <c r="Z211" s="349"/>
-      <c r="AA211" s="349"/>
-      <c r="AB211" s="349"/>
-      <c r="AC211" s="349"/>
-      <c r="AD211" s="349"/>
-      <c r="AE211" s="349"/>
-      <c r="AF211" s="349"/>
-      <c r="AG211" s="349"/>
-      <c r="AH211" s="350"/>
+      <c r="P211" s="347"/>
+      <c r="Q211" s="347"/>
+      <c r="R211" s="347"/>
+      <c r="S211" s="347"/>
+      <c r="T211" s="347"/>
+      <c r="U211" s="347"/>
+      <c r="V211" s="347"/>
+      <c r="W211" s="347"/>
+      <c r="X211" s="347"/>
+      <c r="Y211" s="347"/>
+      <c r="Z211" s="347"/>
+      <c r="AA211" s="347"/>
+      <c r="AB211" s="347"/>
+      <c r="AC211" s="347"/>
+      <c r="AD211" s="347"/>
+      <c r="AE211" s="347"/>
+      <c r="AF211" s="347"/>
+      <c r="AG211" s="347"/>
+      <c r="AH211" s="348"/>
     </row>
     <row r="212" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F212" s="261" t="s">
+      <c r="F212" s="286" t="s">
         <v>39</v>
       </c>
-      <c r="G212" s="262"/>
-      <c r="H212" s="262"/>
-      <c r="I212" s="262"/>
-      <c r="J212" s="263"/>
-      <c r="K212" s="228" t="s">
+      <c r="G212" s="287"/>
+      <c r="H212" s="287"/>
+      <c r="I212" s="287"/>
+      <c r="J212" s="288"/>
+      <c r="K212" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="L212" s="230"/>
-      <c r="M212" s="228" t="s">
+      <c r="L212" s="193"/>
+      <c r="M212" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="N212" s="230"/>
-      <c r="O212" s="341" t="s">
+      <c r="N212" s="193"/>
+      <c r="O212" s="355" t="s">
         <v>281</v>
       </c>
-      <c r="P212" s="295"/>
-      <c r="Q212" s="295"/>
-      <c r="R212" s="295"/>
-      <c r="S212" s="295"/>
-      <c r="T212" s="295"/>
-      <c r="U212" s="295"/>
-      <c r="V212" s="295"/>
-      <c r="W212" s="295"/>
-      <c r="X212" s="295"/>
-      <c r="Y212" s="295"/>
-      <c r="Z212" s="295"/>
-      <c r="AA212" s="295"/>
-      <c r="AB212" s="295"/>
-      <c r="AC212" s="295"/>
-      <c r="AD212" s="295"/>
-      <c r="AE212" s="295"/>
-      <c r="AF212" s="295"/>
-      <c r="AG212" s="295"/>
-      <c r="AH212" s="296"/>
+      <c r="P212" s="293"/>
+      <c r="Q212" s="293"/>
+      <c r="R212" s="293"/>
+      <c r="S212" s="293"/>
+      <c r="T212" s="293"/>
+      <c r="U212" s="293"/>
+      <c r="V212" s="293"/>
+      <c r="W212" s="293"/>
+      <c r="X212" s="293"/>
+      <c r="Y212" s="293"/>
+      <c r="Z212" s="293"/>
+      <c r="AA212" s="293"/>
+      <c r="AB212" s="293"/>
+      <c r="AC212" s="293"/>
+      <c r="AD212" s="293"/>
+      <c r="AE212" s="293"/>
+      <c r="AF212" s="293"/>
+      <c r="AG212" s="293"/>
+      <c r="AH212" s="294"/>
     </row>
     <row r="213" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F213" s="359" t="s">
+      <c r="F213" s="336" t="s">
         <v>34</v>
       </c>
-      <c r="G213" s="370"/>
-      <c r="H213" s="370"/>
-      <c r="I213" s="370"/>
-      <c r="J213" s="360"/>
+      <c r="G213" s="338"/>
+      <c r="H213" s="338"/>
+      <c r="I213" s="338"/>
+      <c r="J213" s="337"/>
       <c r="K213" s="345" t="s">
         <v>35</v>
       </c>
-      <c r="L213" s="299"/>
+      <c r="L213" s="297"/>
       <c r="M213" s="345" t="s">
         <v>33</v>
       </c>
-      <c r="N213" s="299"/>
-      <c r="O213" s="317" t="s">
+      <c r="N213" s="297"/>
+      <c r="O213" s="324" t="s">
         <v>490</v>
       </c>
-      <c r="P213" s="365"/>
-      <c r="Q213" s="365"/>
-      <c r="R213" s="365"/>
-      <c r="S213" s="365"/>
-      <c r="T213" s="365"/>
-      <c r="U213" s="365"/>
-      <c r="V213" s="365"/>
-      <c r="W213" s="365"/>
-      <c r="X213" s="365"/>
-      <c r="Y213" s="365"/>
-      <c r="Z213" s="365"/>
-      <c r="AA213" s="365"/>
-      <c r="AB213" s="365"/>
-      <c r="AC213" s="365"/>
-      <c r="AD213" s="365"/>
-      <c r="AE213" s="365"/>
-      <c r="AF213" s="365"/>
-      <c r="AG213" s="365"/>
-      <c r="AH213" s="366"/>
+      <c r="P213" s="331"/>
+      <c r="Q213" s="331"/>
+      <c r="R213" s="331"/>
+      <c r="S213" s="331"/>
+      <c r="T213" s="331"/>
+      <c r="U213" s="331"/>
+      <c r="V213" s="331"/>
+      <c r="W213" s="331"/>
+      <c r="X213" s="331"/>
+      <c r="Y213" s="331"/>
+      <c r="Z213" s="331"/>
+      <c r="AA213" s="331"/>
+      <c r="AB213" s="331"/>
+      <c r="AC213" s="331"/>
+      <c r="AD213" s="331"/>
+      <c r="AE213" s="331"/>
+      <c r="AF213" s="331"/>
+      <c r="AG213" s="331"/>
+      <c r="AH213" s="332"/>
     </row>
     <row r="214" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F214" s="357"/>
-      <c r="G214" s="373"/>
-      <c r="H214" s="373"/>
-      <c r="I214" s="373"/>
-      <c r="J214" s="374"/>
-      <c r="K214" s="300"/>
-      <c r="L214" s="302"/>
-      <c r="M214" s="300"/>
-      <c r="N214" s="302"/>
-      <c r="O214" s="357"/>
-      <c r="P214" s="373"/>
-      <c r="Q214" s="373"/>
-      <c r="R214" s="373"/>
-      <c r="S214" s="373"/>
-      <c r="T214" s="373"/>
-      <c r="U214" s="373"/>
-      <c r="V214" s="373"/>
-      <c r="W214" s="373"/>
-      <c r="X214" s="373"/>
-      <c r="Y214" s="373"/>
-      <c r="Z214" s="373"/>
-      <c r="AA214" s="373"/>
-      <c r="AB214" s="373"/>
-      <c r="AC214" s="373"/>
-      <c r="AD214" s="373"/>
-      <c r="AE214" s="373"/>
-      <c r="AF214" s="373"/>
-      <c r="AG214" s="373"/>
-      <c r="AH214" s="374"/>
+      <c r="F214" s="342"/>
+      <c r="G214" s="343"/>
+      <c r="H214" s="343"/>
+      <c r="I214" s="343"/>
+      <c r="J214" s="344"/>
+      <c r="K214" s="298"/>
+      <c r="L214" s="300"/>
+      <c r="M214" s="298"/>
+      <c r="N214" s="300"/>
+      <c r="O214" s="342"/>
+      <c r="P214" s="343"/>
+      <c r="Q214" s="343"/>
+      <c r="R214" s="343"/>
+      <c r="S214" s="343"/>
+      <c r="T214" s="343"/>
+      <c r="U214" s="343"/>
+      <c r="V214" s="343"/>
+      <c r="W214" s="343"/>
+      <c r="X214" s="343"/>
+      <c r="Y214" s="343"/>
+      <c r="Z214" s="343"/>
+      <c r="AA214" s="343"/>
+      <c r="AB214" s="343"/>
+      <c r="AC214" s="343"/>
+      <c r="AD214" s="343"/>
+      <c r="AE214" s="343"/>
+      <c r="AF214" s="343"/>
+      <c r="AG214" s="343"/>
+      <c r="AH214" s="344"/>
     </row>
     <row r="215" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F215" s="367"/>
-      <c r="G215" s="368"/>
-      <c r="H215" s="368"/>
-      <c r="I215" s="368"/>
-      <c r="J215" s="369"/>
-      <c r="K215" s="303"/>
-      <c r="L215" s="305"/>
-      <c r="M215" s="303"/>
-      <c r="N215" s="305"/>
-      <c r="O215" s="367"/>
-      <c r="P215" s="368"/>
-      <c r="Q215" s="368"/>
-      <c r="R215" s="368"/>
-      <c r="S215" s="368"/>
-      <c r="T215" s="368"/>
-      <c r="U215" s="368"/>
-      <c r="V215" s="368"/>
-      <c r="W215" s="368"/>
-      <c r="X215" s="368"/>
-      <c r="Y215" s="368"/>
-      <c r="Z215" s="368"/>
-      <c r="AA215" s="368"/>
-      <c r="AB215" s="368"/>
-      <c r="AC215" s="368"/>
-      <c r="AD215" s="368"/>
-      <c r="AE215" s="368"/>
-      <c r="AF215" s="368"/>
-      <c r="AG215" s="368"/>
-      <c r="AH215" s="369"/>
+      <c r="F215" s="333"/>
+      <c r="G215" s="334"/>
+      <c r="H215" s="334"/>
+      <c r="I215" s="334"/>
+      <c r="J215" s="335"/>
+      <c r="K215" s="301"/>
+      <c r="L215" s="303"/>
+      <c r="M215" s="301"/>
+      <c r="N215" s="303"/>
+      <c r="O215" s="333"/>
+      <c r="P215" s="334"/>
+      <c r="Q215" s="334"/>
+      <c r="R215" s="334"/>
+      <c r="S215" s="334"/>
+      <c r="T215" s="334"/>
+      <c r="U215" s="334"/>
+      <c r="V215" s="334"/>
+      <c r="W215" s="334"/>
+      <c r="X215" s="334"/>
+      <c r="Y215" s="334"/>
+      <c r="Z215" s="334"/>
+      <c r="AA215" s="334"/>
+      <c r="AB215" s="334"/>
+      <c r="AC215" s="334"/>
+      <c r="AD215" s="334"/>
+      <c r="AE215" s="334"/>
+      <c r="AF215" s="334"/>
+      <c r="AG215" s="334"/>
+      <c r="AH215" s="335"/>
     </row>
     <row r="216" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F216" s="261" t="s">
+      <c r="F216" s="286" t="s">
         <v>262</v>
       </c>
-      <c r="G216" s="262"/>
-      <c r="H216" s="262"/>
-      <c r="I216" s="262"/>
-      <c r="J216" s="263"/>
-      <c r="K216" s="228" t="s">
+      <c r="G216" s="287"/>
+      <c r="H216" s="287"/>
+      <c r="I216" s="287"/>
+      <c r="J216" s="288"/>
+      <c r="K216" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="L216" s="230"/>
-      <c r="M216" s="228" t="s">
+      <c r="L216" s="193"/>
+      <c r="M216" s="191" t="s">
         <v>36</v>
       </c>
-      <c r="N216" s="230"/>
-      <c r="O216" s="379" t="s">
+      <c r="N216" s="193"/>
+      <c r="O216" s="346" t="s">
         <v>37</v>
       </c>
-      <c r="P216" s="349"/>
-      <c r="Q216" s="349"/>
-      <c r="R216" s="349"/>
-      <c r="S216" s="349"/>
-      <c r="T216" s="349"/>
-      <c r="U216" s="349"/>
-      <c r="V216" s="349"/>
-      <c r="W216" s="349"/>
-      <c r="X216" s="349"/>
-      <c r="Y216" s="349"/>
-      <c r="Z216" s="349"/>
-      <c r="AA216" s="349"/>
-      <c r="AB216" s="349"/>
-      <c r="AC216" s="349"/>
-      <c r="AD216" s="349"/>
-      <c r="AE216" s="349"/>
-      <c r="AF216" s="349"/>
-      <c r="AG216" s="349"/>
-      <c r="AH216" s="350"/>
+      <c r="P216" s="347"/>
+      <c r="Q216" s="347"/>
+      <c r="R216" s="347"/>
+      <c r="S216" s="347"/>
+      <c r="T216" s="347"/>
+      <c r="U216" s="347"/>
+      <c r="V216" s="347"/>
+      <c r="W216" s="347"/>
+      <c r="X216" s="347"/>
+      <c r="Y216" s="347"/>
+      <c r="Z216" s="347"/>
+      <c r="AA216" s="347"/>
+      <c r="AB216" s="347"/>
+      <c r="AC216" s="347"/>
+      <c r="AD216" s="347"/>
+      <c r="AE216" s="347"/>
+      <c r="AF216" s="347"/>
+      <c r="AG216" s="347"/>
+      <c r="AH216" s="348"/>
     </row>
     <row r="217" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F217" s="261" t="s">
+      <c r="F217" s="286" t="s">
         <v>138</v>
       </c>
-      <c r="G217" s="262"/>
-      <c r="H217" s="262"/>
-      <c r="I217" s="262"/>
-      <c r="J217" s="263"/>
-      <c r="K217" s="228" t="s">
+      <c r="G217" s="287"/>
+      <c r="H217" s="287"/>
+      <c r="I217" s="287"/>
+      <c r="J217" s="288"/>
+      <c r="K217" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="L217" s="230"/>
-      <c r="M217" s="228" t="s">
+      <c r="L217" s="193"/>
+      <c r="M217" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="N217" s="230"/>
-      <c r="O217" s="341" t="s">
+      <c r="N217" s="193"/>
+      <c r="O217" s="355" t="s">
         <v>491</v>
       </c>
-      <c r="P217" s="349"/>
-      <c r="Q217" s="349"/>
-      <c r="R217" s="349"/>
-      <c r="S217" s="349"/>
-      <c r="T217" s="349"/>
-      <c r="U217" s="349"/>
-      <c r="V217" s="349"/>
-      <c r="W217" s="349"/>
-      <c r="X217" s="349"/>
-      <c r="Y217" s="349"/>
-      <c r="Z217" s="349"/>
-      <c r="AA217" s="349"/>
-      <c r="AB217" s="349"/>
-      <c r="AC217" s="349"/>
-      <c r="AD217" s="349"/>
-      <c r="AE217" s="349"/>
-      <c r="AF217" s="349"/>
-      <c r="AG217" s="349"/>
-      <c r="AH217" s="350"/>
+      <c r="P217" s="347"/>
+      <c r="Q217" s="347"/>
+      <c r="R217" s="347"/>
+      <c r="S217" s="347"/>
+      <c r="T217" s="347"/>
+      <c r="U217" s="347"/>
+      <c r="V217" s="347"/>
+      <c r="W217" s="347"/>
+      <c r="X217" s="347"/>
+      <c r="Y217" s="347"/>
+      <c r="Z217" s="347"/>
+      <c r="AA217" s="347"/>
+      <c r="AB217" s="347"/>
+      <c r="AC217" s="347"/>
+      <c r="AD217" s="347"/>
+      <c r="AE217" s="347"/>
+      <c r="AF217" s="347"/>
+      <c r="AG217" s="347"/>
+      <c r="AH217" s="348"/>
     </row>
     <row r="218" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F218" s="261" t="s">
+      <c r="F218" s="286" t="s">
         <v>42</v>
       </c>
-      <c r="G218" s="262"/>
-      <c r="H218" s="262"/>
-      <c r="I218" s="262"/>
-      <c r="J218" s="263"/>
-      <c r="K218" s="228" t="s">
+      <c r="G218" s="287"/>
+      <c r="H218" s="287"/>
+      <c r="I218" s="287"/>
+      <c r="J218" s="288"/>
+      <c r="K218" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="L218" s="230"/>
-      <c r="M218" s="228" t="s">
+      <c r="L218" s="193"/>
+      <c r="M218" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="N218" s="230"/>
-      <c r="O218" s="341" t="s">
+      <c r="N218" s="193"/>
+      <c r="O218" s="355" t="s">
         <v>486</v>
       </c>
-      <c r="P218" s="349"/>
-      <c r="Q218" s="349"/>
-      <c r="R218" s="349"/>
-      <c r="S218" s="349"/>
-      <c r="T218" s="349"/>
-      <c r="U218" s="349"/>
-      <c r="V218" s="349"/>
-      <c r="W218" s="349"/>
-      <c r="X218" s="349"/>
-      <c r="Y218" s="349"/>
-      <c r="Z218" s="349"/>
-      <c r="AA218" s="349"/>
-      <c r="AB218" s="349"/>
-      <c r="AC218" s="349"/>
-      <c r="AD218" s="349"/>
-      <c r="AE218" s="349"/>
-      <c r="AF218" s="349"/>
-      <c r="AG218" s="349"/>
-      <c r="AH218" s="350"/>
+      <c r="P218" s="347"/>
+      <c r="Q218" s="347"/>
+      <c r="R218" s="347"/>
+      <c r="S218" s="347"/>
+      <c r="T218" s="347"/>
+      <c r="U218" s="347"/>
+      <c r="V218" s="347"/>
+      <c r="W218" s="347"/>
+      <c r="X218" s="347"/>
+      <c r="Y218" s="347"/>
+      <c r="Z218" s="347"/>
+      <c r="AA218" s="347"/>
+      <c r="AB218" s="347"/>
+      <c r="AC218" s="347"/>
+      <c r="AD218" s="347"/>
+      <c r="AE218" s="347"/>
+      <c r="AF218" s="347"/>
+      <c r="AG218" s="347"/>
+      <c r="AH218" s="348"/>
     </row>
     <row r="219" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F219" s="317" t="s">
+      <c r="F219" s="324" t="s">
         <v>267</v>
       </c>
-      <c r="G219" s="365"/>
-      <c r="H219" s="365"/>
-      <c r="I219" s="365"/>
-      <c r="J219" s="366"/>
-      <c r="K219" s="359" t="s">
+      <c r="G219" s="331"/>
+      <c r="H219" s="331"/>
+      <c r="I219" s="331"/>
+      <c r="J219" s="332"/>
+      <c r="K219" s="336" t="s">
         <v>35</v>
       </c>
-      <c r="L219" s="360"/>
-      <c r="M219" s="359" t="s">
+      <c r="L219" s="337"/>
+      <c r="M219" s="336" t="s">
         <v>36</v>
       </c>
-      <c r="N219" s="360"/>
-      <c r="O219" s="359" t="s">
+      <c r="N219" s="337"/>
+      <c r="O219" s="336" t="s">
         <v>43</v>
       </c>
-      <c r="P219" s="370"/>
-      <c r="Q219" s="370"/>
-      <c r="R219" s="370"/>
-      <c r="S219" s="370"/>
-      <c r="T219" s="370"/>
-      <c r="U219" s="370"/>
-      <c r="V219" s="370"/>
-      <c r="W219" s="370"/>
-      <c r="X219" s="370"/>
-      <c r="Y219" s="370"/>
-      <c r="Z219" s="370"/>
-      <c r="AA219" s="370"/>
-      <c r="AB219" s="370"/>
-      <c r="AC219" s="370"/>
-      <c r="AD219" s="370"/>
-      <c r="AE219" s="370"/>
-      <c r="AF219" s="370"/>
-      <c r="AG219" s="370"/>
-      <c r="AH219" s="360"/>
+      <c r="P219" s="338"/>
+      <c r="Q219" s="338"/>
+      <c r="R219" s="338"/>
+      <c r="S219" s="338"/>
+      <c r="T219" s="338"/>
+      <c r="U219" s="338"/>
+      <c r="V219" s="338"/>
+      <c r="W219" s="338"/>
+      <c r="X219" s="338"/>
+      <c r="Y219" s="338"/>
+      <c r="Z219" s="338"/>
+      <c r="AA219" s="338"/>
+      <c r="AB219" s="338"/>
+      <c r="AC219" s="338"/>
+      <c r="AD219" s="338"/>
+      <c r="AE219" s="338"/>
+      <c r="AF219" s="338"/>
+      <c r="AG219" s="338"/>
+      <c r="AH219" s="337"/>
     </row>
     <row r="220" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F220" s="367"/>
-      <c r="G220" s="368"/>
-      <c r="H220" s="368"/>
-      <c r="I220" s="368"/>
-      <c r="J220" s="369"/>
-      <c r="K220" s="367"/>
-      <c r="L220" s="369"/>
-      <c r="M220" s="367"/>
-      <c r="N220" s="369"/>
-      <c r="O220" s="367"/>
-      <c r="P220" s="368"/>
-      <c r="Q220" s="368"/>
-      <c r="R220" s="368"/>
-      <c r="S220" s="368"/>
-      <c r="T220" s="368"/>
-      <c r="U220" s="368"/>
-      <c r="V220" s="368"/>
-      <c r="W220" s="368"/>
-      <c r="X220" s="368"/>
-      <c r="Y220" s="368"/>
-      <c r="Z220" s="368"/>
-      <c r="AA220" s="368"/>
-      <c r="AB220" s="368"/>
-      <c r="AC220" s="368"/>
-      <c r="AD220" s="368"/>
-      <c r="AE220" s="368"/>
-      <c r="AF220" s="368"/>
-      <c r="AG220" s="368"/>
-      <c r="AH220" s="369"/>
+      <c r="F220" s="333"/>
+      <c r="G220" s="334"/>
+      <c r="H220" s="334"/>
+      <c r="I220" s="334"/>
+      <c r="J220" s="335"/>
+      <c r="K220" s="333"/>
+      <c r="L220" s="335"/>
+      <c r="M220" s="333"/>
+      <c r="N220" s="335"/>
+      <c r="O220" s="333"/>
+      <c r="P220" s="334"/>
+      <c r="Q220" s="334"/>
+      <c r="R220" s="334"/>
+      <c r="S220" s="334"/>
+      <c r="T220" s="334"/>
+      <c r="U220" s="334"/>
+      <c r="V220" s="334"/>
+      <c r="W220" s="334"/>
+      <c r="X220" s="334"/>
+      <c r="Y220" s="334"/>
+      <c r="Z220" s="334"/>
+      <c r="AA220" s="334"/>
+      <c r="AB220" s="334"/>
+      <c r="AC220" s="334"/>
+      <c r="AD220" s="334"/>
+      <c r="AE220" s="334"/>
+      <c r="AF220" s="334"/>
+      <c r="AG220" s="334"/>
+      <c r="AH220" s="335"/>
     </row>
     <row r="221" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F221" s="55"/>
@@ -44713,6 +44732,118 @@
     </row>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:N2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AA153:AH153"/>
+    <mergeCell ref="AA151:AH151"/>
+    <mergeCell ref="O177:AH180"/>
+    <mergeCell ref="O181:AH181"/>
+    <mergeCell ref="O175:AH175"/>
+    <mergeCell ref="K175:L175"/>
+    <mergeCell ref="D155:D164"/>
+    <mergeCell ref="D154:J154"/>
+    <mergeCell ref="E155:J162"/>
+    <mergeCell ref="E163:J164"/>
+    <mergeCell ref="D151:J151"/>
+    <mergeCell ref="D152:J152"/>
+    <mergeCell ref="D153:J153"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="K154:Z154"/>
+    <mergeCell ref="K163:Z164"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="M186:N187"/>
+    <mergeCell ref="M188:N189"/>
+    <mergeCell ref="M190:N191"/>
+    <mergeCell ref="M192:N192"/>
+    <mergeCell ref="O186:AH187"/>
+    <mergeCell ref="O188:AH189"/>
+    <mergeCell ref="O190:AH191"/>
+    <mergeCell ref="O192:AH192"/>
+    <mergeCell ref="O176:AH176"/>
+    <mergeCell ref="O217:AH217"/>
+    <mergeCell ref="O218:AH218"/>
+    <mergeCell ref="M175:N175"/>
+    <mergeCell ref="K162:Z162"/>
+    <mergeCell ref="F218:J218"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="K151:Z151"/>
+    <mergeCell ref="K152:Z152"/>
+    <mergeCell ref="K153:Z153"/>
+    <mergeCell ref="K157:Z161"/>
+    <mergeCell ref="AA157:AH161"/>
+    <mergeCell ref="AA163:AH164"/>
+    <mergeCell ref="AA162:AH162"/>
+    <mergeCell ref="AA152:AH152"/>
+    <mergeCell ref="AA154:AH154"/>
+    <mergeCell ref="M176:N176"/>
+    <mergeCell ref="M177:N180"/>
+    <mergeCell ref="K218:L218"/>
+    <mergeCell ref="K205:L206"/>
+    <mergeCell ref="K207:L208"/>
+    <mergeCell ref="K212:L212"/>
+    <mergeCell ref="K211:L211"/>
+    <mergeCell ref="K203:L204"/>
+    <mergeCell ref="K213:L215"/>
+    <mergeCell ref="K217:L217"/>
+    <mergeCell ref="M217:N217"/>
+    <mergeCell ref="K209:L210"/>
+    <mergeCell ref="M207:N208"/>
+    <mergeCell ref="M212:N212"/>
+    <mergeCell ref="M211:N211"/>
+    <mergeCell ref="M203:N204"/>
+    <mergeCell ref="M213:N215"/>
+    <mergeCell ref="M205:N206"/>
+    <mergeCell ref="O211:AH211"/>
+    <mergeCell ref="O212:AH212"/>
+    <mergeCell ref="K182:L185"/>
+    <mergeCell ref="K177:L180"/>
+    <mergeCell ref="F186:J187"/>
+    <mergeCell ref="F188:J189"/>
+    <mergeCell ref="K188:L189"/>
+    <mergeCell ref="K190:L191"/>
+    <mergeCell ref="M202:N202"/>
+    <mergeCell ref="F203:J204"/>
+    <mergeCell ref="F205:J206"/>
+    <mergeCell ref="F207:J208"/>
+    <mergeCell ref="O182:AH185"/>
+    <mergeCell ref="O196:AH197"/>
+    <mergeCell ref="K195:L195"/>
+    <mergeCell ref="K202:L202"/>
+    <mergeCell ref="M193:N194"/>
+    <mergeCell ref="M195:N195"/>
+    <mergeCell ref="M196:N197"/>
+    <mergeCell ref="K186:L187"/>
+    <mergeCell ref="K181:L181"/>
+    <mergeCell ref="K193:L194"/>
+    <mergeCell ref="M181:N181"/>
+    <mergeCell ref="M182:N185"/>
+    <mergeCell ref="F209:J210"/>
+    <mergeCell ref="F213:J215"/>
+    <mergeCell ref="F175:J175"/>
+    <mergeCell ref="F176:J176"/>
+    <mergeCell ref="F177:J180"/>
+    <mergeCell ref="F181:J181"/>
+    <mergeCell ref="F182:J185"/>
+    <mergeCell ref="K196:L197"/>
+    <mergeCell ref="K192:L192"/>
+    <mergeCell ref="F192:J192"/>
+    <mergeCell ref="F195:J195"/>
+    <mergeCell ref="F190:J191"/>
+    <mergeCell ref="F193:J194"/>
+    <mergeCell ref="F196:J197"/>
+    <mergeCell ref="K176:L176"/>
     <mergeCell ref="K155:Z156"/>
     <mergeCell ref="AA155:AH156"/>
     <mergeCell ref="F219:J220"/>
@@ -44737,118 +44868,6 @@
     <mergeCell ref="F211:J211"/>
     <mergeCell ref="F212:J212"/>
     <mergeCell ref="F216:J216"/>
-    <mergeCell ref="F209:J210"/>
-    <mergeCell ref="F213:J215"/>
-    <mergeCell ref="F175:J175"/>
-    <mergeCell ref="F176:J176"/>
-    <mergeCell ref="F177:J180"/>
-    <mergeCell ref="F181:J181"/>
-    <mergeCell ref="F182:J185"/>
-    <mergeCell ref="K196:L197"/>
-    <mergeCell ref="K192:L192"/>
-    <mergeCell ref="F192:J192"/>
-    <mergeCell ref="F195:J195"/>
-    <mergeCell ref="F190:J191"/>
-    <mergeCell ref="F193:J194"/>
-    <mergeCell ref="F196:J197"/>
-    <mergeCell ref="K176:L176"/>
-    <mergeCell ref="O211:AH211"/>
-    <mergeCell ref="O212:AH212"/>
-    <mergeCell ref="K182:L185"/>
-    <mergeCell ref="K177:L180"/>
-    <mergeCell ref="F186:J187"/>
-    <mergeCell ref="F188:J189"/>
-    <mergeCell ref="K188:L189"/>
-    <mergeCell ref="K190:L191"/>
-    <mergeCell ref="M202:N202"/>
-    <mergeCell ref="F203:J204"/>
-    <mergeCell ref="F205:J206"/>
-    <mergeCell ref="F207:J208"/>
-    <mergeCell ref="O182:AH185"/>
-    <mergeCell ref="O196:AH197"/>
-    <mergeCell ref="K195:L195"/>
-    <mergeCell ref="K202:L202"/>
-    <mergeCell ref="M193:N194"/>
-    <mergeCell ref="M195:N195"/>
-    <mergeCell ref="M196:N197"/>
-    <mergeCell ref="K186:L187"/>
-    <mergeCell ref="K181:L181"/>
-    <mergeCell ref="K193:L194"/>
-    <mergeCell ref="M181:N181"/>
-    <mergeCell ref="M182:N185"/>
-    <mergeCell ref="K218:L218"/>
-    <mergeCell ref="K205:L206"/>
-    <mergeCell ref="K207:L208"/>
-    <mergeCell ref="K212:L212"/>
-    <mergeCell ref="K211:L211"/>
-    <mergeCell ref="K203:L204"/>
-    <mergeCell ref="K213:L215"/>
-    <mergeCell ref="K217:L217"/>
-    <mergeCell ref="M217:N217"/>
-    <mergeCell ref="K209:L210"/>
-    <mergeCell ref="M207:N208"/>
-    <mergeCell ref="M212:N212"/>
-    <mergeCell ref="M211:N211"/>
-    <mergeCell ref="M203:N204"/>
-    <mergeCell ref="M213:N215"/>
-    <mergeCell ref="M205:N206"/>
-    <mergeCell ref="O217:AH217"/>
-    <mergeCell ref="O218:AH218"/>
-    <mergeCell ref="M175:N175"/>
-    <mergeCell ref="K162:Z162"/>
-    <mergeCell ref="F218:J218"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="K151:Z151"/>
-    <mergeCell ref="K152:Z152"/>
-    <mergeCell ref="K153:Z153"/>
-    <mergeCell ref="K157:Z161"/>
-    <mergeCell ref="AA157:AH161"/>
-    <mergeCell ref="AA163:AH164"/>
-    <mergeCell ref="AA162:AH162"/>
-    <mergeCell ref="AA152:AH152"/>
-    <mergeCell ref="AA154:AH154"/>
-    <mergeCell ref="M176:N176"/>
-    <mergeCell ref="M177:N180"/>
-    <mergeCell ref="M186:N187"/>
-    <mergeCell ref="M188:N189"/>
-    <mergeCell ref="M190:N191"/>
-    <mergeCell ref="M192:N192"/>
-    <mergeCell ref="O186:AH187"/>
-    <mergeCell ref="O188:AH189"/>
-    <mergeCell ref="O190:AH191"/>
-    <mergeCell ref="O192:AH192"/>
-    <mergeCell ref="O176:AH176"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:N2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AA153:AH153"/>
-    <mergeCell ref="AA151:AH151"/>
-    <mergeCell ref="O177:AH180"/>
-    <mergeCell ref="O181:AH181"/>
-    <mergeCell ref="O175:AH175"/>
-    <mergeCell ref="K175:L175"/>
-    <mergeCell ref="D155:D164"/>
-    <mergeCell ref="D154:J154"/>
-    <mergeCell ref="E155:J162"/>
-    <mergeCell ref="E163:J164"/>
-    <mergeCell ref="D151:J151"/>
-    <mergeCell ref="D152:J152"/>
-    <mergeCell ref="D153:J153"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="K154:Z154"/>
-    <mergeCell ref="K163:Z164"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="S1:Z3"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1"/>
